--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -96,25 +96,25 @@
     <t xml:space="preserve">VS</t>
   </si>
   <si>
-    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : tel est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption de la nouvelle loi fédérale sur le DES. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : tel est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption de la nouvelle loi fédérale sur le DES. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que leur dossier médical n'a pas été transmis ou parfois trop tardivement. Il y a nécessité d'agir, et ce, d'autant plus que le dossier électronique du patient (DEP) est resté nettement en deçà des attentes en matière de diffusion et d'utilisation.
+    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que leur dossier médical n'a pas été transmis, ou parfois, trop tardivement. Il y a nécessité d'agir, et ce d'autant plus que le dossier électronique du patient (DEP) est resté nettement en deçà des attentes en matière de diffusion et d'utilisation.
 L'objectif majeur reste le même : rendre disponibles les données de santé pertinentes pour améliorer la qualité des soins, renforcer la sécurité des patients et éviter les redondances. C'est le système d'ouverture du dossier qui change pour les patients : il est désormais automatique et gratuit, avec un droit d'opposition, au lieu d'une démarche active. L'idée de base est que désormais chaque personne dispose d'un parcours de santé continu, indépendamment du lieu et du fournisseur de prestations. 
 Quels sont les principaux éléments du projet ? Premièrement, le principe de l'"opt-out" a été retenu. Comme je l'ai déjà dit, l'ouverture du dossier ne se fera plus à la demande, comme avec le DEP actuel, mais de manière automatique, avec le maintien du droit d'opposition et la possibilité de suppression ou de restriction des droits d'accès.
-Deuxièmement, dans le but d'une participation généralisée, il est prévu d'étendre l'obligation d'utilisation du dossier électronique de santé aux fournisseurs de prestations. Actuellement, tous les hôpitaux et les établissements de soins sont déjà tenus de se raccorder au dossier électronique du patient. Désormais, les médecins, les pharmaciens ou les physiothérapeutes, et d'autres prestataires du domaine ambulatoire qui exercent à la charge de l'assurance obligatoire des soins, devront utiliser le dossier électronique de santé et y saisir toutes les données de santé pertinentes pour un traitement médical. Les réticences des professionnels de la santé étaient l'une des principales causes de l'échec du dossier électronique du patient.
-Troisièmement, au lieu de multiples structures décentralisées qui rendaient complexe la mise en oeuvre du dossier électronique du patient, désormais le projet s'appuie sur une infrastructure centralisée. La commission a en effet décidé à l'unanimité que les cantons devraient se mettre d'accord sur une seule communauté nationale. Pour votre information, le regroupement des différentes communautés de référence a progressé et, depuis que la Poste s'est retirée de l'exploitation du dossier électronique du patient, celui-ci s'oriente déjà vers une communauté unique - fort probablement CARA -, dotée d'une infrastructure technique uniforme. La Confédération reste responsable du système d'information.
-Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de celles-ci sur le long terme ; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites au niveau des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
+Deuxièmement, dans le but d'une participation généralisée, il est prévu d'étendre l'obligation d'utilisation du dossier électronique de santé aux fournisseurs de prestations. Actuellement, tous les hôpitaux et les établissements de soins sont déjà tenus de se raccorder au dossier électronique du patient. Désormais, les médecins, les pharmaciens ou les physiothérapeutes et d'autres prestataires du domaine ambulatoire qui exercent à la charge de l'assurance obligatoire des soins devront utiliser le dossier électronique de santé et y saisir toutes les données de santé pertinentes pour un traitement médical. Les réticences des professionnels de la santé étaient l'une des principales causes de l'échec du dossier électronique du patient.
+Troisièmement, au lieu de multiples structures décentralisées qui rendaient complexe la mise en oeuvre du dossier électronique du patient, désormais le projet s'appuie sur une infrastructure centralisée. La commission a en effet décidé à l'unanimité que les cantons devraient se mettre d'accord sur une seule communauté nationale. Pour votre information, le regroupement des différentes communautés de référence a progressé et, depuis que la Poste s'est retirée de l'exploitation du dossier électronique du patient, celui-ci s'oriente déjà vers une communauté unique - fort probablement Cara -, dotée d'une infrastructure technique uniforme. La Confédération reste responsable du système d'information.
+Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de ces dernières sur le long terme ; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites sur le plan des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
 Cinquièmement, un financement clarifié est nécessaire. Si c'est la Confédération qui finance la mise en place et le développement de l'infrastructure, ce sont les cantons qui assumeront les coûts d'exploitation courants et garantiront l'exploitation de la communauté sur leur territoire. Dans son corapport, la Commission des finances de notre conseil relève que les estimations transmises sont imprécises et peu transparentes, notamment parce que l'on souhaite éviter tout risque d'impact négatif sur l'appel d'offres. Elle recommande ainsi de rester attentif aux conséquences budgétaires que pourraient entrainer d'éventuelles modifications apportées au projet.
 Une condition décisive pour l'acceptation et la mise en oeuvre du DES, et qui a préoccupé notre commission, est la confiance en la protection des données. La sécurité des données, leur transition ainsi que leur chiffrement ont été soigneusement analysés. Concernant ce dernier, la commission s'est penchée sur la question d'un éventuel chiffrement de bout en bout (E2EE), sur la base d'une étude de l'EPFL réalisée à la demande de l'Office fédéral de la santé publique. Prenant acte du fait qu'aucun autre système public ou national n'utilise un chiffrement E2EE strict, en raison d'insuffisances techniques, la commission estime que cette solution ne doit pas être inscrite dans la loi. Elle propose toutefois à l'unanimité que les exigences en matière de protection et de sécurité des données, ainsi que la nécessité de chiffrer les données, soient explicitement mentionnées dans un nouvel article 5a. De plus, la commission propose, à l'unanimité, de préciser que la Confédération ne peut traiter les données personnelles "que dans la mesure où cela est nécessaire au bon fonctionnement technique du système d'information DES". Il s'agit de l'article 5 alinéa 5.
-Enfin, à l'unanimité, la commission considère qu'il convient de préciser que le code source des logiciels utilisés doit être publié dans la mesure du possible (open source ; art. 5, al. 8) et que des profils d'autorisation adaptables et faciles à comprendre doivent être mis à disposition (art. 11, al. 5bis et 5ter).
-Une seconde condition est essentielle. Elle concerne la transition entre le dossier électronique du patient (DEP) et le dossier électronique de santé (DES). Quatre points critiques ont été abordés.
+Enfin, à l'unanimité, la commission considère qu'il convient de préciser que le code source des logiciels utilisés doit être publié dans la mesure du possible, donc en "open source" - il s'agit de l'article 5 alinéa 8 - et que des profils d'autorisation adaptables et faciles à comprendre doivent être mis à disposition - article 11 alinéas 5bis et 5ter.
+Une seconde condition est essentielle. Elle concerne la transition entre le DEP et le DES. Quatre points critiques ont été abordés.
 Premièrement, la loi fédérale sur le dossier électronique du patient (LDEP) sera maintenue jusqu'à la mise en oeuvre du DES pour éviter que des lacunes menacent l'exploitation, le financement et les services de base.
 Deuxièmement, le retrait de Post Sanela, prévu à la fin de 2026, doit se faire avec la garantie d'une migration ordonnée vers la communauté de référence Cara - ou vers la plateforme qui sera choisie - sans coûts supplémentaires ni pertes de données. Pour rappel, cela concerne près de 80 000 DEP ouverts, et La Poste, en tant qu'entreprise liée à la Confédération, a une responsabilité particulière à cet égard.
 Troisièmement, la capacité de raccordement technique des fournisseurs de prestations et des systèmes primaires existants avec le DES doit être garantie.
-Quatrièmement, la transition doit être accélérée, mais dans le respect des règles de l'OMC et de la loi fédérale sur les marchés publics (LMP), une procédure de gré à gré étant considérée comme risquée. En bref, une transition stable sans perte de données ni d'investissements est prioritaire. Par courrier, la commission a, de ce fait, invité à l'unanimité le Conseil fédéral à s'engager dans ce sens.
-En conclusion, par 16 voix contre 8, la commission vous recommande d'entrer en matière sur le projet. Bien qu'elle soit d'accord avec l'objectif, une minorité critique en particulier l'infrastructure centralisée, qui, selon elle, nécessitera le lancement d'un nouveau projet informatique important et risqué sur le plan fédéral, ainsi que le droit d'opposition prévu. 
-Je reviendrai à la fin des débats apporter des commentaires sur les propositions des minorités.
+Quatrièmement, la transition doit être accélérée, mais dans le respect des règles de l'OMC et de la loi fédérale sur les marchés publics, une procédure de gré à gré étant considérée comme risquée. En bref, une transition stable sans perte de données ni d'investissements est prioritaire. Par courrier, la commission a, de ce fait, invité à l'unanimité le Conseil fédéral à s'engager dans ce sens.
+En conclusion, par 16 voix contre 8, la commission vous recommande d'entrer en matière sur le projet. Bien qu'elle soit d'accord avec l'objectif, une minorité critique en particulier l'infrastructure centralisée, qui, selon elle, nécessitera le lancement d'un nouveau projet informatique important et risqué sur le plan fédéral, ainsi que le droit d'opposition prévu.
+Je reviendrai à la fin des débats apporter des commentaires sur les propositions de minorités.
 </t>
   </si>
   <si>
@@ -131,6 +131,30 @@
 Der für 2026 vorgesehene Rückzug der Post Sanela Health AG muss so erfolgen, das ist die Meinung der Kommission, dass eine geordnete Migration zu Cara gewährleistet ist. Ich kann Ihnen sagen: 80 000 Dossier sind derzeit bei der Post Sanela Health AG. Da braucht es Lösungen. Die Nachricht, dass die Post aussteigen wird, erreichte die Kommission mitten in der Beratung des Geschäftes. Wir liessen deshalb einen Zusatzbericht anfertigen. Dieser ist aber noch nicht eingetroffen - das war aber auch so geplant. Deshalb bittet Ihre Kommission den Ständerat, sich der Thematik des Anbieters nochmals anzunehmen. Der Ausstieg der Post aus dem EPD könnte auch Auswirkungen auf die Frage der Notwendigkeit einer neuen Ausschreibung haben, was schlussendlich auch zeitliche Konsequenzen haben würde. 
 Die Mehrheit Ihrer Kommission beantragt Ihnen mit 17 zu 8 Stimmen, auf die Vorlage einzutreten. Die Kommissionsmehrheit möchte Ihnen, und wahrscheinlich auch der Bevölkerung, ein Angebot machen, welches ein neues Dossier ermöglicht, das die Schwachstellen des EPD eliminiert. Es ist ein Dossier, wo die Patientinnen und Patienten selbst entscheiden können, wer darauf Zugriff hat, eines, das zentraler gesteuert ist, eines, das nicht die gleichen Fehler wiederholt, die beim EPD gemacht worden sind.
 Ich werde am Schluss noch auf die Minderheiten und den Einzelantrag eingehen. Ich überlasse jetzt gerne das Wort meinem Kommissionssprecher-Kollegen und hoffe, dass Sie ihn verstehen, weil mich haben Sie wahrscheinlich nicht verstanden.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">418690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baume-Schneider Elisabeth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion vise à permettre aux personnes en procédure d'asile, aux bénéficiaires de l'aide sociale ou de prestations complémentaires d'être, en règle générale, tenues de choisir un modèle particulier d'assurance. La motion vise certes à déroger à la règle dans des cas exceptionnels.
+Il convient de préciser que, pour les requérants d'asile et pour les personnes à protéger sans autorisation de séjour, la Confédération et les cantons peuvent d'ores et déjà restreindre le choix de l'assureur, prescr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La motion vise à permettre aux personnes en procédure d'asile, aux bénéficiaires de l'aide sociale ou de prestations complémentaires d'être, en règle générale, tenues de choisir un modèle particulier d'assurance. La motion vise certes à déroger à la règle dans des cas exceptionnels.
+Il convient de préciser que, pour les requérants d'asile et pour les personnes à protéger sans autorisation de séjour, la Confédération et les cantons peuvent d'ores et déjà restreindre le choix de l'assureur, prescrire une forme particulière d'assurance et limiter le choix des fournisseurs de prestations. Cela permet de gérer l'accès au système de santé et d'utiliser les fonds publics de manière économique en garantissant des prix moins élevés. La charge administrative est aussi fortement réduite lorsque les soins de santé des requérants d'asile sont gérés par un seul assureur ou par un petit nombre d'assureurs.
+Les cantons peuvent également accorder une réduction de primes aux assurés dont la condition économique est modeste. Les cantons déterminent à la fois les bénéficiaires et le montant, et peuvent fixer une prime de référence fondée, elle aussi, sur une assurance avec choix limité des fournisseurs de prestations. Il ne s'agit donc pas d'aborder la question de la réduction des primes, mais celle de la prime de référence, qui est basée sur une assurance avec choix limité. Pour le calcul des prestations complémentaires, la prime effective est prise en compte, mais au maximum à hauteur de la prime moyenne cantonale ou régionale. Les bénéficiaires de prestations complémentaires sont dès lors incités à choisir une prime appropriée.
+En résumé, les cantons sont largement compétents en matière de réduction des primes, de prestations complémentaires, d'aide sociale et d'impôts. Ils peuvent donc coordonner ces domaines de manière optimale. La Confédération n'est pas habilitée à édicter des prescriptions allant au-delà de ses propres compétences.
+Dès lors, je vous propose de rejeter la motion.
 </t>
   </si>
   <si>
@@ -183,16 +207,13 @@
     <t xml:space="preserve">NE</t>
   </si>
   <si>
-    <t xml:space="preserve">FR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance, là où il </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance, là où il aurait fallu des règles strictes et qui fonctionnent. 
-Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation ; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table : l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires ; l'équivalent à peu près du canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300 000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire un doublement. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le : l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne concerne pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse. C'est l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres. 
+    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance là où il </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance là où il aurait fallu des règles strictes et qui fonctionnent.
+Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation ; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table : l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires, ce qui équivaut à peu près au canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300 000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire qu'il y aurait un doublement de ces émissions. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le : l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne représente pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse et l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres.
 Le deuxième point sur lequel je veux revenir est le travail forcé. La gauche a proposé d'interdire l'importation de marchandises produites au moyen du travail forcé. La commission a malheureusement écarté cette proposition et propose, à la place, comme toujours, un suivi. Or, les observateurs de terrain sont clairs : l'esclavage moderne est une réalité bien présente, par exemple dans les plantations de l'agrobusiness. Sur ce plan également, un suivi ne libère personne.
-Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait, poser des règles contraignantes.
+Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait : poser des règles contraignantes.
 Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord fait exactement l'inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs voir ce traité pour ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie : c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.
 J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 5000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.
 Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.
@@ -244,8 +265,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I6" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I7" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -667,7 +688,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -677,18 +698,18 @@
         <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -697,22 +718,49 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
         <v>34</v>
       </c>
+      <c r="E6"/>
       <c r="F6" t="s">
         <v>35</v>
       </c>
       <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -217,6 +217,28 @@
 Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord fait exactement l'inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs voir ce traité pour ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie : c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.
 J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 5000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.
 Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">418808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuena Mauro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen, dass die zweite Schale viel gewichtiger ist und damit also der Sicherheit viel mehr Gewicht zukommt; die Bevölkerung wird mir recht geben.
 </t>
   </si>
 </sst>
@@ -265,8 +287,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I7" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I8" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I8"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -763,6 +785,35 @@
         <v>43</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -239,6 +239,107 @@
   </si>
   <si>
     <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen, dass die zweite Schale viel gewichtiger ist und damit also der Sicherheit viel mehr Gewicht zukommt; die Bevölkerung wird mir recht geben.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. La mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion en fin d'année. Les objectifs du Conseil fédéral so</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. La mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion en fin d'année. Les objectifs du Conseil fédéral sont coordonnés avec le programme de législature de 2023 à 2027. Les priorités reposent sur quatre lignes directrices : la prospérité, la cohésion, la sécurité et la durabilité. Ces lignes directrices sont elles-mêmes subdivisées en 25 objectifs. 2027 sera la quatrième et dernière année de la présente législature et le Conseil fédéral a prévu un total de 140 mesures. 
+Je vais maintenant aborder les points forts de l'année à venir et je vais me concentrer sur certaines priorités des quatre lignes directrices. Tout d'abord, la première de ces lignes directrices, la prospérité. En ce qui concerne la place financière, le Conseil fédéral soumettra un message pour modifier la loi sur les banques. Pour garantir la stabilité financière, il s'agit de renforcer les dispositifs de prévention, de liquidité et de lutte contre les crises. S'agissant des relations avec l'Union européenne, le Conseil fédéral adoptera le message sur le financement d'une participation de la Suisse aux programmes de recherche et d'éducation. Ces fonds visent une participation au programme Horizon Europe et Erasmus plus pour les années 2028 à 2034. En matière d'économie, le Conseil fédéral présentera le message sur la promotion économique pour les années 2028 à 2031. Les priorités seront l'allègement administratif et la facilitation de l'accès aux marchés internationaux pour les petites et moyennes entreprises, les PME, ainsi que le renforcement des régions. Par ailleurs, le Conseil fédéral adoptera, l'année prochaine, des messages relatifs à la révision partielle de la loi fédérale sur la sécurité des produits et sur les entraves techniques au commerce, renforçant ainsi la protection des consommateurs. De plus, le Conseil fédéral adoptera des messages sur un nouvel accord de libre-échange avec le Vietnam et sur un nouvel accord sur le numérique avec Singapour. 
+Afin de coordonner le développement du rail, de la route et du trafic d'agglomération, le Conseil fédéral adoptera le message Transport '45. Son but est de développer le rail, la route et le trafic d'agglomération de manière ciblée et coordonnée, afin de répondre aux besoins de mobilité de la population et de l'économie. 
+Dans le domaine du numérique, le Conseil fédéral adoptera la loi sur le droit d'auteur aux évolutions de l'intelligence artificielle. Il lancera également une consultation pour l'adhésion à la Convention-cadre du Conseil de l'Europe sur l'intelligence artificielle et les droits de l'homme, la démocratie et l'État de droit. 
+J'en viens maintenant à la deuxième ligne directrice, la cohésion nationale. Pour ce qui est des affaires sociales, le Conseil fédéral présentera le message AVS 2030. Cette réforme vise à consolider les finances de l'assurance pour l'horizon 2030-2040 et à l'adapter aux évolutions de la société. Le Conseil fédéral adoptera également le message relatif à une révision de la loi fédérale sur l'assurance-invalidité. Cette réforme porte sur des mesures visant à garantir la stabilité financière et à renforcer la réinsertion professionnelle. 
+En matière de santé, le Conseil fédéral adoptera le message relatif à une modification de la loi fédérale sur l'assurance-maladie portant sur l'adaptation de la franchise. L'objectif sera de réduire les coûts de la santé tout en favorisant la responsabilité individuelle des assurés. De plus, il mettra en oeuvre le principe du consentement présumé pour le don d'organes. 
+Dans le cadre de la consultation relative au message sur la promotion de la culture pour la période 2029 à 2032, le Conseil fédéral soumettra à la discussion les orientations stratégiques de la politique fédérale en matière de culture. 
+Pour ce qui est du marché du travail, le Conseil fédéral adoptera une stratégie nationale en matière de formation continue, de formation professionnelle et de formation de rattrapage pour favoriser l'entrée ou le retour en emploi.
+J'en viens maintenant à la troisième ligne directrice : la sécurité.
+Pour garantir les effectifs de l'armée et de la protection civile, le Conseil fédéral ouvrira la consultation sur l'introduction d'une obligation de servir dans la sécurité. Le projet prévoit de fusionner le service civil et la protection civile au sein d'une nouvelle entité chargée de la protection contre les catastrophes.
+S'agissant de la sécurité, le Conseil fédéral ouvrira la consultation sur une révision des bases légales relatives à la protection des infrastructures critiques. Il s'agira notamment d'améliorer sensiblement l'efficacité de la protection et de clarifier les responsabilités et les procédures.
+En matière de migration, le Conseil fédéral élaborera avec les cantons, les villes et les communes des mesures pour améliorer le système d'asile suisse.
+Sur le plan de la politique extérieure, dans le cadre de la mise en oeuvre de la stratégie de coopération internationale 2025 à 2028, le Conseil fédéral décidera de l'octroi des contributions à l'Agence des Nations Unies pour les réfugiés et au Comité international de la Croix-Rouge pour les années 2027 et 2028.
+Enfin, j'en viens à la quatrième et dernière ligne directrice : la durabilité.
+Concernant le climat, le Conseil fédéral présentera la révision de la loi sur le CO2 pour la période 2031 à 2040.
+En matière d'énergie, il adoptera une stratégie nationale sur l'efficacité énergétique qui permettra d'évaluer la consommation d'énergie et le potentiel d'efficacité dans les différents secteurs.
+Pour ce qui est de l'adaptation au changement climatique, le Conseil fédéral adoptera la stratégie Gestion de l'eau - périodes de sécheresse, fortes précipitations, qualité de l'approvisionnement en eau, protection des habitats aquatiques. Cette stratégie tiendra compte des politiques sectorielles concernées et mettra en évidence, le cas échéant, les adaptations juridiques nécessaires à la réalisation des objectifs.
+S'agissant de l'agriculture, le Conseil fédéral fixera dans la loi le cadre de la politique agricole pour les huit prochaines années avec le message sur la Politique agricole à partir de 2030, sur laquelle la procédure de consultation a récemment été ouverte.
+Concernant l'aménagement du territoire, le Conseil fédéral adoptera le message relatif à l'accélération des procédures de planification et de construction. L'objectif est de simplifier l'octroi des permis et de lutter contre les oppositions abusives.
+Parmi les points forts de l'année prochaine figure également l'adoption de plusieurs stratégies majeures. Le Conseil fédéral adoptera notamment la stratégie nationale sur la violence domestique, sexuelle et de genre, ainsi que le plan pour l'administration numérique suisse.
+En conclusion, vous trouverez la totalité des messages, rapports et stratégies détaillés dans le document relatif aux objectifs 2027. Au nom du Conseil fédéral, je vous remercie de votre coopération et de votre soutien. Le Conseil fédéral continuera à s'engager pleinement pour la défense des intérêts du pays et pour le bien de sa population.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Pierre-André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale, chères et chers collègues, Mesdames, Messieurs, je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, M. Datouo, à la tribune de la salle du Conseil national.
+Monsieur le président, votre visite est un beau témoignage de l'amitié de longue date qui unit nos deux pays. En juillet dernier, j'ai eu le plaisir de vous rencontrer, vous ainsi que des représentantes et représentants du Parlement camerounais, à Yaoundé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale, chères et chers collègues, Mesdames, Messieurs, je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, M. Datouo, à la tribune de la salle du Conseil national.
+Monsieur le président, votre visite est un beau témoignage de l'amitié de longue date qui unit nos deux pays. En juillet dernier, j'ai eu le plaisir de vous rencontrer, vous ainsi que des représentantes et représentants du Parlement camerounais, à Yaoundé, et je me réjouis de vous accueillir à mon tour, aujourd'hui, à Berne.
+J'aime à me souvenir du moment où nous avons décidé de votre venue en Suisse : nous avions visité le chantier de la nouvelle ambassade de Suisse à Yaoundé, et nous étions en train de déguster, dans votre bureau, des safous, que vous appelez aussi prunes, et c'est là que nous avons fixé la date de votre visite. Je suis heureux que nous soyons parvenus à nous revoir si rapidement.
+La Suisse et le Cameroun ont de nombreux points communs. Nos deux pays sont marqués par le multilinguisme et la diversité. Nous savons que le vivre-ensemble dans la diversité n'est pas toujours chose aisée : il doit être sans cesse réinventé, avec patience, respect et la volonté de s'écouter les uns les autres. Dialoguer régulièrement est donc indispensable. Nos parlements, aussi, entretiennent le dialogue avec succès, notamment parce que leurs liens sont humains. Tilo Frey, l'une des premières femmes à avoir été élues au Conseil national suisse en 1971 est née à Maroua au Cameroun et incarne encore aujourd'hui le lien qui unit nos deux pays. Notre coopération touche de nombreux domaines, allant de l'économie et du commerce à l'aide humanitaire, la promotion de la paix et la migration, en passant par la culture, la santé, l'agriculture, la science et même le football avec Breel Embolo.
+Le nouveau bâtiment de l'ambassade de Suisse à Yaoundé, placé sous le signe de la durabilité, reflète clairement notre volonté de façonner les relations entre nos deux pays de manière durable.
+Monsieur le président de l'Assemblée nationale, je vous souhaite, au nom du Conseil national, la bienvenue à Berne, un agréable séjour et des discussions enrichissantes. (Standing ovation)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engler Stefan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale,
+Chères et chers collègues, Mesdames, Messieurs,
+Je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, Monsieur Datouo, à la tribune de la salle du Conseil des États.
+Monsieur le président, votre visite témoigne des relations amicales qui unissent la Suisse et le Cameroun depuis de nombreuses années. Nos deux pays sont marqués par le multilinguisme et la diversité culturelle. Nous savons que le vivre-ensemble da</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale,
+Chères et chers collègues, Mesdames, Messieurs,
+Je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, Monsieur Datouo, à la tribune de la salle du Conseil des États.
+Monsieur le président, votre visite témoigne des relations amicales qui unissent la Suisse et le Cameroun depuis de nombreuses années. Nos deux pays sont marqués par le multilinguisme et la diversité culturelle. Nous savons que le vivre-ensemble dans la diversité ne va pas toujours de soi : il doit être sans cesse réinventé, avec patience, respect mutuel et la volonté de s'écouter les uns les autres. Dans ce contexte, les échanges politiques et parlementaires réguliers sont indispensables.
+Je saisis donc l'occasion de votre présence parmi nous pour remercier chaleureusement le Cameroun d'avoir accueilli la 51e session annuelle de l'Assemblée parlementaire de la Francophonie (APF), qui s'est tenue en juillet dernier à Yaoundé. Plusieurs membres de la délégation suisse auprès de l'APF y ont pris part et ont ainsi eu l'occasion d'échanger avec leurs homologues de l'espace francophone.
+Les relations entre nos deux pays s'étendent à de nombreux domaines, allant de l'économie et du commerce à l'aide humanitaire, la promotion de la paix et la migration, en passant par la culture, la santé et l'agriculture. Votre visite d'aujourd'hui nous permet d'approfondir nos échanges et, en particulier, de renforcer les relations entre nos parlements.
+Monsieur le président de l'Assemblée nationale, je vous souhaite, au nom du Conseil des Etats, la bienvenue à Berne, un agréable séjour et des discussions enrichissantes. (Applaudissements)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juillard Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+Notre société repose sur la cryp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+Notre société repose sur la cryptographie. Les paiements électroniques, les communications de l'administration, les dossiers médicaux, les identités numériques, les signatures électroniques, les systèmes industriels ou encore les infrastructures critiques dépendent tous, à des degrés divers, de mécanismes cryptographiques. Or, certains des algorithmes de cryptographie à clé publique que nous utilisons actuellement pourraient être rendus vulnérables par des ordinateurs quantiques suffisamment puissants.
+Le problème est que nous ne pouvons pas attendre le jour où un ordinateur quantique capable de casser ses protections sera disponible pour commencer à agir. Pourquoi cela ? Parce que la migration cryptographique est un processus long, complexe et coûteux. Il faut identifier les systèmes concernés, comprendre leurs dépendances, vérifier les logiciels et les équipements, travailler avec les fournisseurs, tester les nouveaux mécanismes, garantir l'interopérabilité et, dans certains cas, remplacer des systèmes qui ont une durée de vie de dix, vingt ou trente ans. Autrement dit, le moment d'agir est avant que la menace ne devienne opérationnelle.
+Il existe également un risque, déjà présent aujourd'hui, de "moissonner maintenant pour déchiffrer plus tard". Des données peuvent être capturées aujourd'hui alors qu'elles sont encore correctement protégées. Si leurs valeurs ou leur caractère confidentiel perdurent pendant dix, vingt ou trente ans, elles pourraient être déchiffrées à l'avenir lorsque les capacités technologiques le permettront. Cela concerne notamment les informations de l'État, les données médicales, les données de recherche, les secrets industriels ou certaines informations liées à la sécurité nationale. Nous devons donc raisonner non seulement en fonction de la menace actuelle, mais aussi de la durée pendant laquelle une information doit rester confidentielle.
+C'est précisément ce que vise ma motion : ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de crypto-agilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
+C'est une question de cybersécurité, mais également une question de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et beaucoup plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
+Nos partenaires internationaux avancent : l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035 en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux : préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
+Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnait l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
+Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
+En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
+Je vous invite donc à soutenir ma motion sans la lettre i, comme demandé par le Conseil fédéral, et je vous en remercie.
 </t>
   </si>
 </sst>
@@ -287,8 +388,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I8" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I12" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I12"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -814,6 +915,120 @@
         <v>50</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -315,7 +315,7 @@
 Monsieur le président, votre visite témoigne des relations amicales qui unissent la Suisse et le Cameroun depuis de nombreuses années. Nos deux pays sont marqués par le multilinguisme et la diversité culturelle. Nous savons que le vivre-ensemble dans la diversité ne va pas toujours de soi : il doit être sans cesse réinventé, avec patience, respect mutuel et la volonté de s'écouter les uns les autres. Dans ce contexte, les échanges politiques et parlementaires réguliers sont indispensables.
 Je saisis donc l'occasion de votre présence parmi nous pour remercier chaleureusement le Cameroun d'avoir accueilli la 51e session annuelle de l'Assemblée parlementaire de la Francophonie (APF), qui s'est tenue en juillet dernier à Yaoundé. Plusieurs membres de la délégation suisse auprès de l'APF y ont pris part et ont ainsi eu l'occasion d'échanger avec leurs homologues de l'espace francophone.
 Les relations entre nos deux pays s'étendent à de nombreux domaines, allant de l'économie et du commerce à l'aide humanitaire, la promotion de la paix et la migration, en passant par la culture, la santé et l'agriculture. Votre visite d'aujourd'hui nous permet d'approfondir nos échanges et, en particulier, de renforcer les relations entre nos parlements.
-Monsieur le président de l'Assemblée nationale, je vous souhaite, au nom du Conseil des Etats, la bienvenue à Berne, un agréable séjour et des discussions enrichissantes. (Applaudissements)
+Monsieur le président de l'Assemblée nationale, je vous souhaite, au nom du Conseil des États, la bienvenue à Berne, un agréable séjour et des discussions enrichissantes. (Applaudissements)
 </t>
   </si>
   <si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -213,11 +213,7 @@
     <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance là où il aurait fallu des règles strictes et qui fonctionnent.
 Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation ; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table : l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires, ce qui équivaut à peu près au canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300 000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire qu'il y aurait un doublement de ces émissions. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le : l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne représente pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse et l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres.
 Le deuxième point sur lequel je veux revenir est le travail forcé. La gauche a proposé d'interdire l'importation de marchandises produites au moyen du travail forcé. La commission a malheureusement écarté cette proposition et propose, à la place, comme toujours, un suivi. Or, les observateurs de terrain sont clairs : l'esclavage moderne est une réalité bien présente, par exemple dans les plantations de l'agrobusiness. Sur ce plan également, un suivi ne libère personne.
-Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait : poser des règles contraignantes.
-Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord fait exactement l'inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs voir ce traité pour ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie : c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.
-J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 5000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.
-Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.
-</t>
+Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait : poser des règles contraignantes.Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord fait exactement l'inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs voir ce traité pour ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie : c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 50 000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.</t>
   </si>
   <si>
     <t xml:space="preserve">418808</t>
@@ -340,6 +336,356 @@
 Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
 En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
 Je vous invite donc à soutenir ma motion sans la lettre i, comme demandé par le Conseil fédéral, et je vous en remercie.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klopfenstein Broggini Delphine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il y a des situations où appliquer une règle ne suffit pas. Il faut aussi savoir pourquoi cette règle existe et jusqu'où il est raisonnable de l'appliquer. C'est précisément le sens de la motion que je défends. On le sait, le système Dublin organise la répartition des responsabilités entre les États européens en matière d'asile. Même dans ce cas, des exceptions ont été prévues. C'est précisément de l'une d'entre elles dont nous parlons aujourd'hui.
+Cette exception, c'est la clause de souverainet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il y a des situations où appliquer une règle ne suffit pas. Il faut aussi savoir pourquoi cette règle existe et jusqu'où il est raisonnable de l'appliquer. C'est précisément le sens de la motion que je défends. On le sait, le système Dublin organise la répartition des responsabilités entre les États européens en matière d'asile. Même dans ce cas, des exceptions ont été prévues. C'est précisément de l'une d'entre elles dont nous parlons aujourd'hui.
+Cette exception, c'est la clause de souveraineté. Cette motion ne vise donc pas à réécrire le règlement Dublin ; elle vise à ce que la Suisse utilise la marge de manoeuvre que ce règlement lui donne déjà lorsqu'un enfant atteint dans sa santé risque d'être transféré. Pourquoi ? Parce qu'un enfant malade n'est pas un dossier que l'on peut transférer d'une administration à une autre sans conséquence. Un transfert peut signifier interrompre une thérapie, changer brusquement de médecin, rompre un suivi psychiatrique, ajouter de l'incertitude à un enfant qui a parfois déjà vécu la guerre, vécu la violence, vécu l'exil. Lorsqu'il s'agit d'un enfant, nous avons une responsabilité toute particulière et j'aimerais vraiment que vous l'entendiez.
+La Convention relative aux droits de l'enfant est très claire, l'intérêt supérieur de l'enfant doit être une considération primordiale dans toutes les décisions qu'on prend. Ce principe doit avoir des conséquences concrètes. Le Conseil fédéral nous répond que le SEM examine déjà chaque situation individuellement et minutieusement. Je ne mets évidemment pas en doute ce travail-là, mais c'est précisément là que nous divergeons. Nous estimons, nous, le groupe des Verts, que pour les enfants atteints dans leur santé, la pesée des intérêts doit conduire à une règle claire qui va dans le sens de leur protection. Une règle claire, c'est aussi une règle prévisible pour les familles, pour les médecins, mais également pour l'administration. Soyons pragmatiques, nous parlons ici d'un nombre limité de situations particulièrement vulnérables. Accepter que la Suisse traite ces demandes évite aussi des procédures, des recours, des expertises médicales répétées et parfois de longues batailles juridiques autour de transferts qui peuvent finalement ne pas avoir lieu.
+La protection peut aussi être une forme de pragmatisme ; on doit saisir aujourd'hui cette occasion. On nous dit également que les autres États Dublin sont tenus de garantir les soins nécessaires. C'est vrai sur le papier, mais notre responsabilité ne s'arrête pas au moment où nous remettons un enfant à un autre État. La question que nous devons nous poser aujourd'hui est très concrète. Est-ce raisonnable d'interrompre une prise en charge médicale qui fonctionne pour transférer un enfant malade ailleurs, dans un autre pays, lorsqu'un traitement est envisagé, lorsqu'un lien thérapeutique existe, lorsqu'un nouveau déplacement risque d'aggraver l'état physique ou psychique d'un enfant ? Ma réponse est clairement non. Ce n'est pas ouvrir une brèche dans le système Dublin, au contraire ; ce n'est pas créer un droit général de rester en Suisse et ce n'est certainement pas non plus un effet d'appel. Personne ne choisit la maladie grave de son enfant comme stratégie migratoire. Il s'agit simplement d'utiliser un instrument qui existe. La clause de souveraineté est un instrument qui existe dans la loi, et qui permet, à l'article 17, de protéger les enfants. Cette clause existe parce que les rédacteurs du règlement ont compris qu'aucun système administratif ne peut anticiper toutes les situations humaines.
+La Suisse a une tradition humanitaire, on le sait, mais cette tradition est en train de se perdre, cette tradition est en train de s'effriter à entendre tous les propos tenus lors de cette session extraordinaire sur l'asile. Cette tradition humanitaire, j'ai envie qu'on la maintienne, j'ai envie qu'on la renforce et c'est ici, en Suisse, notre responsabilité. Une tradition n'a de valeur que lorsqu'elle guide nos décisions au moment où elles sont difficiles, voire particulièrement difficiles. On parle de situations vraiment difficiles : on parle d'enfants qui sont malades et qu'on doit réussir à protéger. La dignité humaine ne se mesure pas à la générosité d'un discours, elle se mesure à la manière dont un État traite les plus vulnérables, lorsqu'il y a juridiquement la possibilité de faire autrement. Parmi les personnes vulnérables, les enfants malades doivent évidemment bénéficier d'une protection toute particulière. Nous pouvons demander à chaque État d'assumer ses responsabilités dans le cadre de Dublin et nous pouvons, en même temps, décider qu'un enfant malade ne payera pas le prix de cette rigueur administrative.
+Je vous remercie de votre soutien à cette motion. On parle d'enfants malades qu'on transfère dans le cadre de procédures d'asile. Utilisons cette clause de souveraineté pour les protéger réellement.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schmid Pascal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont, noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
+Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorbestraft und islamistisch radikalisiert. Er griff wahllos Mens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont, noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
+Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorbestraft und islamistisch radikalisiert. Er griff wahllos Menschen an, gefährdete zahlreiche Kinder und verletzte drei Personen teils schwer. Die einst sichere Schweiz wird immer unsicherer. Bei der Bundesanwaltschaft laufen aktuell über 140 Terrorverfahren - ein trauriger Rekord. Gemäss Nachrichtendienst des Bundes ist die Terrorbedrohung erhöht und geprägt vom Dschihadismus. Die allermeisten Dschihadisten sind Ausländer oder Doppelbürger, das bestätigte eine Studie der Fachhochschule ZHAW.
+Auch in den Gefängnissen zeigen sich die Folgen der unkontrollierten Massenmigration in unser Land. 70 Prozent der Insassen sind Ausländer, und weitere 15 Prozent sind Schweizer mit Migrationshintergrund. Das bedeutet, für Schweizer ohne Migrationshintergrund würden 15 Prozent unserer Gefängnisplätze genügen. Diese Zahlen bestätigen es eben klar, man kann es nicht schönreden. Wir haben immer mehr importierte Probleme, importierte Kriminalität und importierte Gewalt; und wir haben immer mehr Opfer.
+Personen, die eingebürgert werden, müssen seit 1992 ihren bisherigen Pass nicht mehr abgeben. Man könne ihnen - das war das Hauptargument für das Doppelbürgerrecht - den Schweizer Pass dann einfacher entziehen, wenn irgendetwas passiere, wenn sie kriminell würden. Der Bundesrat behauptet auch heute in der Stellungnahme zur Motion 26.3617, er nutze den Passentzug zur Terrorbekämpfung. Tatsächlich gab es seit dem Jahr 2000 nur gerade 10 Entzugsverfahren - nur 10 -, siebenmal wurde ein Entzug angeordnet und nur 3 Fälle sind rechtskräftig geworden; und das bei einer Million Einbürgerungen seit dem Jahr 2000. Das beweist, dass die Behörden auch bei den schwersten Verbrechen, bei Terrorgefährdern wegschauen.
+Die heutige Rechtsgrundlage für Ausbürgerungen, Artikel 42 des Bürgerrechtsgesetzes, ist eben ein zahnloser Tiger; das bestätigen die Zahlen. Deshalb braucht es eine griffige Grundlage, nicht nur eine Kann-Bestimmung, sondern eine Muss-Bestimmung. Man muss in bestimmten Fällen den Pass entziehen. Die Motion soll das bei Kapitalverbrechen und bei radikalisierten Gefährdern sicherstellen. Den Fünfer und das Weggli darf es halt nicht mehr geben: Wer seinen Heimatpass bei einer Einbürgerung behalten will, der muss es in Kauf nehmen, dass der Schweizer Pass bei schwersten Verbrechen entzogen wird; staatenlos wird dadurch niemand.
+Dschihadisten und Terroristen sind zu allem fähig. Sie wollen unseren Rechtsstaat, unsere Werte und unsere westliche Lebensweise zerstören. Nur wenn es ihnen dann irgendwann selber an den Kragen geht, berufen Sie sich gerne auf die Annehmlichkeiten unseres Rechtsstaates.
+Wir dürfen nicht warten, bis der nächste Anschlag geschieht. Unsere Bevölkerung hat ein Recht darauf, vor Verbrechern und Terroristen geschützt zu werden. Das ist die Kernaufgabe, das ist die wichtigste Aufgabe unseres Staates. Jedes Opfer ist eines zu viel. Wer unser Land terroristisch angreift oder Kapitalverbrechen begeht, hat sein Bürgerrecht verwirkt. Er ist nicht mehr Teil dieses Landes, er ist nicht mehr Teil dieser Wertegemeinschaft. Wir müssen alles daransetzen, dass solche Leute erst gar nicht zu uns kommen; und wenn sie dennoch hier sind, müssen wir alles tun, sie aus dem Land zu schaffen. Sie haben bei uns nichts verloren, sie gehören ins Gefängnis, wenn nötig ausgebürgert und zurück in ihr Heimatland.
+Es ist ein Gebot des gesunden Menschenverstandes. Kein vernünftiger Mensch in diesem Land will Terroristen und Dschihadisten hierbehalten. Das will niemand, das will kein Schweizer, das will kein Ausländer, das will kein Doppelbürger - das will niemand. Niemand will solche Leute hier bei uns behalten, und wir müssen alles dafür tun, dass sie gehen müssen.
+Ich danke Ihnen deshalb für die Annahme dieser Motion. Sie macht unser Land wieder sicherer.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehr Düsel Nina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die Landesverweisung obligatorisch sein" beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
+Die obligatorische Landesverweisung wird in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen. Die Hauptursache ist die viel zu large, oft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die Landesverweisung obligatorisch sein" beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
+Die obligatorische Landesverweisung wird in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen. Die Hauptursache ist die viel zu large, oft angewendete Härtefallklausel, obwohl sie eigentlich als Ausnahme ausgestaltet wurde. Leider ist die Härtefallklausel keine Ausnahme mehr. Von den angeordneten Landesverweisungen werden gemäss SEM schweizweit nur 63 Prozent vollzogen, und die Unterschiede im kantonalen Vollzug sind enorm. Dies macht unseren Rechtsstaat unglaubwürdig. Der Grossteil der Bevölkerung fordert bei schweren Straftaten von Ausländern mehr Ausschaffungen.
+Dänemark macht es vor und schafft Kriminelle ab einem Jahr Freiheitsstrafe automatisch aus. Dieses Gesetz trat am 1. Mai 2016 in Kraft. Es hat natürlich auch eine abschreckende Wirkung; die Asylzahlen sind seither stark zurückgegangen - ein Erfolg. Diesem wegweisenden Beispiel soll auch die Schweiz folgen: Der Gesetzgeber soll die Landesverweisung bei längeren Freiheitsstrafen für alle Konstellationen als verhältnismässig und Härtefälle als ausgeschlossen erklären.
+Der Bundesrat ist hier leider sehr zurückhaltend. Einmal mehr bringt er als Grund, dass fehlende Reisedokumente oder mangelnde Kooperation den Vollzug verunmöglichen können. Diese Hindernisse dürfen aber keinen Grund gegen einen Vollzug darstellen. Ich habe auf dem Gericht und auf der Staatsanwaltschaft gearbeitet und oft erlebt, dass Pässe und Reisedokumente verschwunden sind, vielleicht auch durch Absicht, um einer Ausschaffung zu entgehen. Wir müssen uns Dänemark anschliessen und unsere Praxis endlich verschärfen. Es darf bei Ausschaffungen auch nicht so grosse kantonale Unterschiede geben. Um eine Freiheitsstrafe von einem Jahr zu erhalten, sei dies bedingt oder unbedingt, braucht es etwas. Man kriegt nicht einfach so eine längere Freiheitsstrafe, es handelt sich nicht um Bagatelldelikte. Die Bevölkerung fordert bei Ausschaffungen schon seit längerer Zeit eine härtere Praxis, und die Europäische Menschenrechtskonvention (EMRK) darf nicht immer als Grund dagegen vorgebracht werden.
+Bitte unterstützen Sie unsere Fraktionsmotion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knutti Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei diesem Vorstoss geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
+Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei diesem Vorstoss geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
+Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5000 regulären Unterbringungsplätzen in seinen Bundesasylzentren; in besonderen Situationen soll die Kapazität sogar auf 10 000 Plätze erhöht werden können. Diese grossen Einrichtungen wirken sich auf die Gemeinde, die Schulen, den Verkehr, die Sicherheit, das lokale Gewerbe sowie grundsätzlich auf das Zusammenleben vor Ort aus. Wer diese Auswirkungen tragen muss, soll entsprechend mitbestimmen können.
+Der Bundesrat führt an, dass die Gemeinden angehört würden. Doch angehört zu werden ist nicht dasselbe wie mitzuentscheiden. Weder eine Informationsveranstaltung noch eine Stellungnahme oder ein Einspracheverfahren ersetzen die demokratische Mitsprache bzw. das Recht einer Gemeinde, einen Standort abzulehnen.
+Hier setzt der Vorstoss an. Wir wollen weder zusätzliche Bürokratie noch eine Blockade, sondern etwas ganz Einfaches: Will der Bund in einer Gemeinde ein neues Bundesasylzentrum errichten, muss die betroffene Standortgemeinde zustimmen. Dies ist kein radikaler Gedanke, sondern Ausdruck des Föderalismus und der Gemeindeautonomie - und es entspricht unserem Verständnis von Demokratie. Es darf nicht sein, dass der Bund am grünen Tisch über den Standort grosser Asylunterkünfte entscheidet, während die betroffene Bevölkerung lediglich informiert wird.
+Niemand bestreitet die Verantwortung des Bundes im Asylwesen. Diese bedeutet jedoch nicht, dass er über die Köpfe der Gemeinden hinweg entscheiden darf. Die letzten Jahre haben gezeigt, wie schnell sich die Situation im Asylbereich verändern kann. Im Jahr 2025 wurden in der Schweiz 25 000 Asylgesuche gestellt. Der Bund musste seine Unterbringungskapazitäten massiv ausbauen und hält fest, dass die Bereitstellung von Unterbringungsplätzen für Kantone und Gemeinden eine grosse Herausforderung darstellt.
+Daher muss die Verantwortung dort wahrgenommen werden, wo sie hingehört. Immer grössere Strukturen zu schaffen und den Gemeinden erst danach zu erklären, warum sie diese akzeptieren müssen - das geht nicht. Zuerst muss gefragt werden, ob eine Gemeinde dies überhaupt will. Der Bund fordert Planungssicherheit, doch auch die Gemeinden benötigen Planungssicherheit. Eine Gemeinde muss wissen, was auf ihrem Gebiet geschieht, und die Bevölkerung hat Anspruch darauf, dass ihre demokratischen Rechte ernst genommen werden.
+Des Weiteren enthält der Vorstoss eine ausdrückliche Ausnahme für den Asylnotstand. Es geht nicht darum, dass eine Gemeinde in einer ausserordentlichen Krisensituation jede staatliche Massnahme verhindern kann. Ausserhalb eines Notstandes muss jedoch gelten: keine neuen, grossen Asylunterkünfte gegen den ausdrücklichen Willen der betroffenen Standortgemeinde.
+Ich bitte Sie, den Vorstoss zu unterstützen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jans Beat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Knutti, es ist Sache der Gemeinde, das Verfahren festzulegen. Der Bundesrat kann nicht beschliessen, ob es dazu eine Volksentscheidung gibt oder nicht. Das muss die Gemeinde machen. Der Bundesrat ist in Diskussion mit den Asylregionen. 
+Ich gebe Ihnen ein Beispiel: Die Asylregion Zentralschweiz und Tessin muss aufgrund ihrer Bevölkerungsgrösse gemeinsam einen bestimmten Prozentsatz der Asylsuchenden betreuen. Dazu gehören einerseits die Bundesasylzentren mit Verfahren, dann gibt es Asylzent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Knutti, es ist Sache der Gemeinde, das Verfahren festzulegen. Der Bundesrat kann nicht beschliessen, ob es dazu eine Volksentscheidung gibt oder nicht. Das muss die Gemeinde machen. Der Bundesrat ist in Diskussion mit den Asylregionen. 
+Ich gebe Ihnen ein Beispiel: Die Asylregion Zentralschweiz und Tessin muss aufgrund ihrer Bevölkerungsgrösse gemeinsam einen bestimmten Prozentsatz der Asylsuchenden betreuen. Dazu gehören einerseits die Bundesasylzentren mit Verfahren, dann gibt es Asylzentren ohne Verfahren und die kantonalen Asylzentren. Diese Regionen sind beauftragt, die nötigen Unterbringungsplätze zu suchen. Wenn sich in einem Kanton eine Möglichkeit ergibt, dann geht in diesem Kanton respektive in der Gemeinde der ganz normale Planungsprozess voran. Wenn die Gemeinde sagt, nein, diese Nutzungsplanung akzeptieren wir nicht, das wollen wir nicht, hier hat es keinen Platz für ein Asylzentrum, dann gibt es dort auch keines. Das ist ja der Grund, warum einzelne Asylregionen bis heute nicht genügend solche Plätze zur Verfügung stellen können und andere, die sich sehr bemüht haben, bei sich eine Lösung zu finden, zum Teil stark belastet sind.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutz Gregor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen, eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023, im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen, eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023, im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, dass also Leute, die schon in sicheren Staaten leben, dann hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige neue Motive ergänzt. Es gibt eben einen Unterschied zwischen Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
+Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27. Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." Das erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis dann auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist das sicher nicht das Relevante. Trotzdem sagen Sie dann, nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, man staunt dann etwas, die über alle Gesuche 27,5 Prozent Zustimmung ergibt. Also, das sieht dann doch eher nach einer pauschalen Prüfung aus, und wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das hier erhellende Fakten zutage bringt. Dieser Fragebogen liegt oder lag dem Bundesverwaltungsgericht nämlich vor, es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche diese gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen - also Ihr Staatssekretariat, das mit diesen Fragen befasst ist - den eigentlichen Willen des Gesetzgebers, also von uns hier, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhält, würde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiellrechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
+Ich denke, hier müssen Sie, Herr Bundesrat, einmal ganz gründlich aufräumen und wirklich noch einmal über die Bücher gehen. Ich glaube, es geht nicht an, dass Bundesämter arbeiten, ohne sich ans Gesetz zu halten. Sie werden jetzt sagen, dass Sie keine Einzelfälle dokumentieren oder kommentieren. Sie werden sagen, dieses Urteil sei ein Einzelfallurteil. Ja, aber man kann dieses Urteil lesen, und es ist ganz genau dokumentiert und aktenkundig, wie hier korrespondiert wird, wie man mit diesen Einzelfällen umgeht; das geht so nicht. 
+Meine Motion möchte etwas ganz Einfaches: erstens, dass man sich im Staatssekretariat für Migration ans Gesetz hält, und zweitens, dass man diese Praxisänderung, die offensichtlich gesetzeswidrig ist, rückgängig macht und die Fälle einzeln prüft, damit diejenigen Leute Schutz und Aufnahme erhalten, die es nötig haben und nicht die ganze Welt eingeladen wird, in die Schweiz zu kommen. 
+Darum bitte ich Sie hier um Zustimmung.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das habe ich in meiner Rede vergessen, es ist sehr gut, dass ich das noch nachliefern kann. Sie verdienen hier eine Antwort. Der Bundesrat ist wirklich entschlossen, gegen diese Leute entschlossener vorzugehen. 
+Wir haben zunächst einmal die Verfahren für Leute aus Nordafrika beschleunigt, sie dauern jetzt nur noch maximal 24 Tage gegenüber etwa 100 Tagen in normalen Verfahren. Das 24-Stunden-Verfahren hat also Wirkung gezeigt, insofern, dass es nun 50 Prozent weniger Übernachtungen in Bundesasy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das habe ich in meiner Rede vergessen, es ist sehr gut, dass ich das noch nachliefern kann. Sie verdienen hier eine Antwort. Der Bundesrat ist wirklich entschlossen, gegen diese Leute entschlossener vorzugehen. 
+Wir haben zunächst einmal die Verfahren für Leute aus Nordafrika beschleunigt, sie dauern jetzt nur noch maximal 24 Tage gegenüber etwa 100 Tagen in normalen Verfahren. Das 24-Stunden-Verfahren hat also Wirkung gezeigt, insofern, dass es nun 50 Prozent weniger Übernachtungen in Bundesasylzentren gibt von Personen aus Maghreb-Staaten. Das ist ein erster Erfolg, reicht aber bei Weitem nicht. Deshalb haben wir als weitere Massnahme die Einzelbetreuung installiert. Zu allen Asylregionen gibt es jetzt sogenannte runde Tische, an denen Mitglieder von Behörden, Polizei, Asyl- und Sozialbereich und so weiter zusammensitzen. Sie schauen sich Fall für Fall an, der ihnen gemeldet wird, um sicherzustellen, dass die Leute in die Strafverfolgung überführt werden können. 
+Dann haben wir eine Taskforce eingesetzt, die ganz gezielt Vorschläge macht, wie wir in der Strafverfolgung noch griffigere Instrumente erhalten - denn diese Leute missbrauchen das System natürlich in vielerlei Hinsicht. Zum Beispiel könnte die Schwelle für Administrativhaft für solche Leute gesenkt werden, sodass wir sie besser in Haft nehmen können, um sie schneller ausschaffen zu können. Das sind alles Dinge, die wir jetzt im Rahmen der Asylstrategie für Sie vorbereiten. Hier bekommen Sie ganz konkrete Vorschläge, und das meinen wir ernst, solche wollen wir Ihnen vorlegen. 
+Ein zweiter Vorschlag, den wir im Rahmen der Asylstrategie auch mit den Kantonen und Gemeinden diskutieren, ist das vorgelagerte Zuweisungsverfahren. Menschen, die gar keine Asylgründe geltend machen, sollen auch nicht in ein Asylzentrum kommen. Sie belasten das System dort nur, verzögern die Prozesse, und oft sind es eben genau diese Personen, die dann kriminell werden. Das ist eine Realität. Das muss man auch benennen und ansprechen. Das können wir nicht akzeptieren, und mit diesem neuen Vorschlag hoffen wir, dass wir das Asylwesen in unserem Land insbesondere für Menschen, die nicht schutzbedürftig sind, weniger attraktiv machen können und diese Menschen draussen behalten können. Das soll eine abschreckende Wirkung haben, das ist das Ziel. 
+Wir sind dran, aber die Kantone und Gemeinden müssen das dann umsetzen, sie müssen die Rückkehren organisieren und auch die notwendigen Haftplätze zur Verfügung stellen. Deshalb ist es sehr wichtig, dass die Kantone hinter diesen Massnahmen stehen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gysin Greta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion.
+Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, zulässig oder zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule, sie bauen sich ein </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion.
+Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, zulässig oder zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule, sie bauen sich ein soziales Umfeld auf, und trotzdem bleibt ihr Aufenthaltsstatus provisorisch.
+Meine Motion verlangt deshalb eine pragmatische Lösung: Wer seit zehn Jahren vorläufig in der Schweiz aufgenommen ist, soll eine Aufenthaltsbewilligung erhalten. Ausnahmen bleiben selbstverständlich möglich, insbesondere bei schweren Straftaten oder wenn die Sicherheit der Schweiz gefährdet ist. Es geht nicht darum, nach kurzer Zeit automatisch ein dauerhaftes Aufenthaltsrecht zu gewähren. Es geht darum, nach zehn Jahren die rechtliche Situation an eine Realität anzupassen, die längst besteht.
+Der Bundesrat anerkennt das Problem selbst. Er weist darauf hin, dass die vorläufige Aufnahme in vielen Fällen länger dauert und dass deshalb verschiedene Massnahmen zur Verbesserung der Integration getroffen wurden. Genau hier liegt der Widerspruch. Wir investieren zu Recht in die Integration dieser Menschen. Wir wollen, dass sie eine Sprache lernen, arbeiten, eine Ausbildung absolvieren und wirtschaftlich selbstständig werden. Gleichzeitig halten wir sie über Jahre in einem Status, der ihnen sagt, eure Zukunft hier bleibt ungewiss. Das ist integrationspolitisch nicht sinnvoll.
+Oggi, dopo cinque anni è possibile presentare una domanda per ottenere un permesso di dimora. Ma questa possibilità non risolve il problema di fondo. Con la mia mozione, pongo volutamente una soglia molto alta, una soglia di dieci anni. Dopo dieci anni, non possiamo più sostenere di essere di fronte ad una situazione temporanea. Continuare a chiamarla "ammissione provvisoria" non cambia la realtà dei fatti.
+Il Consiglio federale sostiene che il sistema attuale, attraverso la possibilità di ottenere un permesso in caso di buona integrazione, crei un incentivo a integrarsi. Ma l'integrazione non dovrebbe dipendere dal mantenere le persone il più a lungo possibile in uno stato di incertezza. È vero piuttosto il contrario. Chi ha una prospettiva può pianificare la propria vita, investire nella formazione, trovare una maggiore stabilità professionale e assumersi delle responsabilità anche sul lungo termine. La sicurezza giuridica facilita l'integrazione, non la ostacola.
+Dobbiamo porci una domanda concreta. Che cosa otteniamo mantenendo lo statu quo? Se dopo dieci anni una persona non può ancora essere allontanata dalla Svizzera, non sparirà semplicemente perché continuiamo a definire provvisorio il suo statuto e rimarrà qui, ma con maggiori ostacoli alla propria integrazione sociale e professionale. Un provvisorio non può durare per sempre ed è con queste motivazioni che vi invito ad accogliere la mia mozione.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich muss zuerst im Rahmen einer persönlichen Erklärung etwas berichtigen, weil mich Herr Bundesrat Jans falsch zitiert hat. Ich habe nie davon gesprochen, dass der Abschreibungsentscheid des Bundesverwaltungsgerichts vom 20. November 2025 oder auch die anderen von mir zitierten Urteile des Bundesverwaltungsgerichts Leitentscheide gewesen seien oder eine Änderung oder Weiterentwicklung der Rechtsprechung bewirkt hätten. Im Gegenteil, ich habe gesagt, dass das Bundesverwaltungsgericht seine Praxis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich muss zuerst im Rahmen einer persönlichen Erklärung etwas berichtigen, weil mich Herr Bundesrat Jans falsch zitiert hat. Ich habe nie davon gesprochen, dass der Abschreibungsentscheid des Bundesverwaltungsgerichts vom 20. November 2025 oder auch die anderen von mir zitierten Urteile des Bundesverwaltungsgerichts Leitentscheide gewesen seien oder eine Änderung oder Weiterentwicklung der Rechtsprechung bewirkt hätten. Im Gegenteil, ich habe gesagt, dass das Bundesverwaltungsgericht seine Praxis immer bestätigt hat. Und wenn der Autor Ihrer Notiz die Debatten der letzten Jahre aufmerksam gelesen hätte, hätte er gemerkt, dass ich auch schon 2023 und 2024 genau gleich argumentiert habe. 
+Vor diesem Hintergrund nun zu meiner Frage, Herr Bundesrat Jans: Das Bundesverwaltungsgericht schreibt in diesem zitierten Entscheid, ein Fragebogen sei für eine Einzelfallprüfung ungeeignet und das Staatssekretariat für Migration schüre Erwartungen - und diese Korrespondenz, die mit verfahrensrechtlichen und materiell rechtlichen Vorgaben des Asylgesetzes nicht vereinbar sei, ist ja dokumentiert. Wie um Himmels Willen kommen Sie dann dazu, zu schreiben, es liege kein Urteil des Bundesverfassungsgerichts vor, welches die Asylpraxis gegenüber afghanischen Frauen kritisiert oder infrage stellt? Herr Bundesrat Jans, gelten gewisse Gerichtsurteile für den Justizminister nicht, wenn er es besser zu wissen glaubt, oder gelten diese Gerichtsurteile auch für den Justizminister?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graber Michael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Bundesrat, Sie haben ausgeführt, dass die Beibehaltung des Schutzstatus S für Ukrainerinnen und Ukrainer sehr wichtig sei. Gleichzeitig unterstützen sie es aber, dass junge ukrainische Männer zurück an die Front müssen. Da spielen Sie den Steigbügelhalter der EU, um Selenski weiteres Kanonenfutter anzubieten. Schauen Sie einmal hin, was in der Ukraine passiert. Da werden die jungen Männer in Busse gezwungen und als Kanonenfutter an die Front gebracht. Wie können Sie es mit Ihrem Gewissen ve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Bundesrat, Sie haben ausgeführt, dass die Beibehaltung des Schutzstatus S für Ukrainerinnen und Ukrainer sehr wichtig sei. Gleichzeitig unterstützen sie es aber, dass junge ukrainische Männer zurück an die Front müssen. Da spielen Sie den Steigbügelhalter der EU, um Selenski weiteres Kanonenfutter anzubieten. Schauen Sie einmal hin, was in der Ukraine passiert. Da werden die jungen Männer in Busse gezwungen und als Kanonenfutter an die Front gebracht. Wie können Sie es mit Ihrem Gewissen vereinbaren, junge Männer in den sicheren Tod in die Ukraine zu schicken, während andere nicht gefährdete Personengruppen aus der Ukraine in diesem Land bleiben können?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat lehnt die neun ausserordentlich traktandierten Motionen ab. Seiner Ansicht nach ist bei diesen weder die Ausserordentlichkeit noch die Dringlichkeit gegeben.
+Die Ausgangslage im Bereich Asyl präsentiert sich wie folgt: Die Asylgesuche gehen weiter zurück. In diesem Jahr verzeichnen wir fast 20 Prozent weniger Gesuche als im Vorjahr. Das SEM hat seine Prognose für 2026 um 3000 Asylgesuche gesenkt. Sie sinken somit im dritten Jahr in Folge, und wenn die tieferen Prognosen zutreffen, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat lehnt die neun ausserordentlich traktandierten Motionen ab. Seiner Ansicht nach ist bei diesen weder die Ausserordentlichkeit noch die Dringlichkeit gegeben.
+Die Ausgangslage im Bereich Asyl präsentiert sich wie folgt: Die Asylgesuche gehen weiter zurück. In diesem Jahr verzeichnen wir fast 20 Prozent weniger Gesuche als im Vorjahr. Das SEM hat seine Prognose für 2026 um 3000 Asylgesuche gesenkt. Sie sinken somit im dritten Jahr in Folge, und wenn die tieferen Prognosen zutreffen, liegen wir Ende Jahr 27 Prozent tiefer als 2023.
+Auch die Pendenzen konnten stark reduziert werden. Als ich mein Amt antrat, hatten wir fast 10 000 offene Pendenzen; aktuell sind wir bei 2500 und wollen bis Ende Jahr alle Pendenzen abgebaut haben, obwohl das SEM wegen des Entlastungsprogrammes 150 Stellen streichen musste. Weniger Asylgesuche und Pendenzen entlasten das System; die Kantone und Gemeinden beginnen dies zu spüren.
+Die Zahl der Aufgriffe von irregulär Eingereisten ist gegenüber dem Vorjahr um 50 Prozent zurückgegangen. Verschiedene Massnahmen, die wir ergriffen haben, zeigen Wirkung. Für Asylsuchende aus nordafrikanischen Ländern haben wir die Verfahren stark beschleunigt, was ebenfalls das ganze System entlastet und die Schweiz als Zielland weniger attraktiv macht. Dank der neuen Einzelfallbehandlung an den runden Tischen aller Asylregionen sowie der neu eingesetzten Taskforce konnten mehr straffällige Asylsuchende der Strafverfolgung zugeführt werden. Die Zahl der Sicherheitsvorfälle in den Bundesasylzentren hat sich innerhalb von zwei Jahren mehr als halbiert.
+Wir führen etwa doppelt so viele abgewiesene Asylsuchende zurück wie alle anderen vergleichbaren europäischen Länder. Dabei stützen wir uns auf mehr als sechzig Abkommen mit Herkunftsstaaten. Ende Mai haben wir sogar ein Abkommen mit Marokko abgeschlossen; damit konnten wir auch die Rückführungen in dieses Land verbessern. Das schaffen viele andere Länder nicht.
+Doch nicht nur bei der Rückkehr sind wir in Europa Vorreiter. Mehr als fünfzig Prozent der Flüchtlinge und vorläufig Aufgenommenen haben bei uns nach fünf Jahren einen Job, was dank Arbeit durch Ausbildung möglich ist. Dies setzen wir zusammen mit den Kantonen erfolgreich um, wie auch die OECD anerkennt.
+So viel zur Ausgangslage, nun komme ich zu den einzelnen Vorstössen.
+Ich beginne mit der Motion 26.3615 der SVP-Fraktion: Es geht hier um einen Vorstoss, den ich im Auftrag des abwesenden Bundespräsidenten vertreten muss; sie ist seinem Departement zugeordnet. Es geht um die Frage, welches Land die Arbeitslosengelder von Grenzgängerinnen und Grenzgängern bezahlt, die ihren Job verloren haben. Diese Motion will diese Frage beantworten, bevor sie sich überhaupt stellt, bevor wir überhaupt die Ausgangslage kennen. Es ist schlicht und einfach zu früh, hier schon Entscheide zu fassen. Deshalb lehnt der Bundesrat diese Motion ab. Die Änderung der EU-Verordnung 883/2004 sieht vor, dass künftig der letzte Beschäftigungsstaat für die Ausrichtung der Arbeitslosenentschädigung von Grenzgängerinnen und Grenzgängern zuständig sein soll. Aktuell ist die Situation umgekehrt geregelt, in Kombination mit einem Rückerstattungssystem zwischen Beschäftigungs- und Wohnsitzstaat. 
+Die Schweiz beteiligt sich seit dem Inkrafttreten des Freizügigkeitsabkommens an der EU-weiten Koordinierung der Systeme der sozialen Sicherheit. Dazu gehört auch die erwähnte EU-Verordnung. Heute profitieren davon nicht zuletzt Schweizerinnen und Schweizer, die in einem EU-Mitgliedstaat leben und arbeiten. Das vergessen Sie immer wieder: Es gibt auch Schweizer, die in der EU leben, und für diese gelten auch Regeln, von denen sie profitieren können. Wenn Sie eine Auslegeordnung des Systems machen, müssen Sie das berücksichtigen, bevor Sie hierzu Entscheide fällen. 
+Seit 2013 hat die Arbeitslosenversicherung mit den Leistungen der Grenzgängerinnen und Grenzgänger einen jährlichen Überschuss von durchschnittlich 280 Millionen Schweizerfranken gemacht. Aktuell wissen wir nicht, wann die Revision in der EU in Kraft treten wird. Wie frühere Anpassungen muss auch dieser EU-Beschluss das innerstaatliche Genehmigungsverfahren durchlaufen. Dann muss die EU die Verordnungsanpassung für eine nächste Sitzung des gemischten Ausschusses anmelden. Dies ist bis jetzt noch nicht geschehen. Das liegt unter anderem daran, dass das Revisionsverfahren auf EU-Ebene noch nicht abgeschlossen ist. Es fehlen noch die formelle Verabschiedung durch den Rat der EU, die Unterzeichnung durch die Rats- und Parlamentspräsidien sowie die Veröffentlichung im Amtsblatt der EU. 
+Die Haltung des Bundesrates lässt sich also wie folgt zusammenfassen: Der Bundesrat lehnt einen verfrühten Positionsbezug ab. Es ist zu früh, einen Entscheid über eine allfällige Übernahme oder Nichtübernahme der noch nicht abgeschlossenen Revision zu fällen. Der Bundesrat verfolgt die Entwicklungen aufmerksam und informiert die zuständigen parlamentarischen Kommissionen über den Stand der Arbeiten. Bisher sind das die SGK-S und beide APK. Der Bundesrat wird demnächst eine Aussprache über die Revision und die damit aufgeworfenen Fragen führen. Dabei wird er über alle möglichen Lösungen diskutieren und diese sorgfältig prüfen. 
+Aus diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
+Ich komme zur Motion 26.3617. Mit dem Entzug des Bürgerrechtes lässt sich kein Terrorakt verhindern. Dafür braucht es andere Massnahmen. Deshalb hat die Schweiz seit 2020 ihr Sicherheitsdispositiv deutlich verstärkt. Fedpol, der Nachrichtendienst und die kantonalen Strafverfolgungsbehörden greifen bei konkreten Hinweisen auf eine terroristische Gefahr präventiv ein; dazu haben sie neue Instrumente erhalten. Es stehen hier verschiedene Instrumente zur Verfügung, etwa Meldepflichten, Kontakt- und Ausreiseverbote, Ein- oder Ausgrenzungen sowie in bestimmten Fällen auch Hausarrest. Im Rahmen eines Strafverfahrens können weitere Massnahmen angeordnet werden. So wird eine beschuldigte Person in Untersuchungs- oder Sicherheitshaft genommen, wenn ein dringender Tatverdacht besteht, dass die Person weitere schwere Straftaten begehen wird, oder wenn die Person konkret damit gedroht hat, eine schwerwiegende Tat zu begehen.
+Kommen wir nun zum Entzug des Schweizer Bürgerrechtes - darum geht es ja in dieser Motion. Der Entzug des Bürgerrechtes dient nicht dazu, einer möglichen Gefahr im Voraus zu begegnen, er greift erst nach einer strafrechtlichen Verurteilung. Die Motion verlangt, dass ein Entzug des Bürgerrechtes auch bei Straftaten möglich sein soll, die keinen unmittelbaren Bezug zum Terrorismus haben. Er soll selbst dann in Betracht kommen, wenn keine strafrechtliche Verurteilung vorliegt. Das geht dem Bundesrat zu weit. Zu weit geht dem Bundesrat auch der in der Motion vorgesehene Automatismus. Die zuständigen Behörden müssen auch künftig prüfen können, ob ein Entzug des Bürgerrechtes im konkreten Einzelfall verhältnismässig ist. Der Entzug des Bürgerrechtes ist ein schwerwiegender Eingriff, und deshalb braucht es auch weiterhin eine sorgfältige Prüfung aller Umstände des Einzelfalles.
+Sie haben es bereits gehört, Bund und Kantone haben ihre Zusammenarbeit gegen Terrorismus in den letzten Jahren deutlich verstärkt. Die Behörden verfügen heute über wirksame Instrumente, um Gefahren frühzeitig zu erkennen und Straftaten zu verhindern. Die Motion würde dazu nichts beitragen, sie würde mit ihrem Automatismus aber das Prinzip der Verhältnismässigkeit verletzen - und das lehnt der Bundesrat ab.
+Der Bundesrat beantragt Ihnen, die Motion abzulehnen.
+Ich komme nun zur Motion 26.3131. Diese Motion verlangt, dass ausländische Straftäter ab einer Freiheitsstrafe von einem Jahr zwingend und ohne Ausnahme des Landes verwiesen werden. Das bedeutet konkret, in solchen Fällen soll weder die Härtefallklausel angewendet werden noch soll im Einzelfall geprüft werden, ob die Landesverweisung verhältnismässig ist. Der Bundesrat lehnt diese Forderung aus drei Gründen ab.
+Erstens möchte ich daran erinnern, dass das Parlament bei der Umsetzung der Ausschaffungs-Initiative bewusst eine Härtefallklausel geschaffen hat und dass die Durchsetzungs-Initiative, welche diese abschaffen wollte, von der Stimmbevölkerung deutlich abgelehnt wurde. Die Härtefallklausel stellt sicher, dass zentrale verfassungs- und völkerrechtliche Vorgaben eingehalten werden, und dazu gehören insbesondere das Verhältnismässigkeitsprinzip, der Schutz des Privat- und Familienlebens sowie das Non-Refoulement-Prinzip. Die Rechtsprechungen des Bundesgerichtes und des Europäischen Gerichtshofes für Menschenrechte verlangen zudem eine Prüfung des Einzelfalls. Eine zwingende Landesverweisung ab einem Jahr Freiheitsstrafe würde diese ausschliessen. Damit könnte das Gericht auch die konkreten Umstände des Einzelfalls nicht mehr berücksichtigen, und das ist mit dem übergeordnetem Recht nicht vereinbar.
+Zweitens bedeutet eine zwingende Landesverweisung noch nicht, dass diese auch tatsächlich vollzogen werden kann. Fehlende Reisedokumente oder die mangelnde Kooperation des Herkunftsstaates können den Vollzug weiterhin verhindern; daran ändert diese Motion nichts.
+Drittens zeigt die heutige Praxis: Je schwerer die Straftat, desto häufiger wird eine Landesverweisung ausgesprochen. Bei Freiheitsstrafen von ein bis zwei Jahren liegt die Quote im Jahr 2025 bei 79 Prozent, bei Freiheitsstrafen von zwei bis drei Jahren sind es bereits 86 Prozent und bei drei bis vier Jahren rund 96 Prozent. Bei mehr als vier Jahren sind es rund 93 Prozent. Bei schweren Straftaten ist die Landesverweisung damit bereits heute die klare Regel, die Härtefallklausel kommt in diesen Fällen nur zurückhaltend zur Anwendung. Fazit: Eine weitere Verschärfung ist somit weder mit dem übergeordneten Recht vereinbar noch geeignet, um die bestehenden Vollzugsprobleme zu lösen.
+Aus all diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
+Nun zur Motion Rutz Gregor 26.3668, "Korrektur der Praxisänderung in Bezug auf Asylgesuche von Afghaninnen". Diese Forderung muss Ihnen bekannt vorkommen. Am 27. Mai 2024 haben Sie die Motion Rutz Gregor 23.4241 mit gleichlautenden Forderungen abgelehnt. 
+Seit der Praxisänderung des SEM im Sommer 2023 hat sich die Situation der Frauen und Mädchen in Afghanistan weiter dramatisch verschlechtert. Ein menschenwürdiges Leben ist für Afghaninnen in ihrem Heimatland nicht mehr möglich. Deshalb geht der Gerichtshof der Europäischen Union von einer Kollektivverfolgung der afghanischen Frauen aus. Er hat mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. In Europa gilt also grundsätzlich dieselbe Haltung und Praxis wie in der Schweiz. Eine spezielle Einladung der Schweiz gibt es in diesem Sinne nicht. 
+Nichtsdestotrotz prüft das SEM nach wie vor jedes Asylgesuch von afghanischen Frauen und Mädchen, und zwar einzeln. Das SEM tritt nicht auf Dublin-Fälle ein, ebenso wenig auf Gesuche von Betroffenen, die wir in einen Drittstaat zurückschicken können. Das SEM prüft auch, ob es sich überhaupt um Afghaninnen handelt. Es führt Sicherheitsüberprüfungen durch und überprüft den Familiennachzug zum Beispiel mit DNA-Analysen. Zudem wird die Ehegemeinschaft kontrolliert. Kommt es zu Missbrauch, können bestehende Bewilligungen und das Asyl entzogen werden. An all diesen Überprüfungen hat die Praxisänderung für die Afghaninnen nichts geändert. Es gibt also nach wie vor keinen Automatismus. 
+Der in der Motion erwähnte nicht veröffentlichte Abschreibungsbeschluss des Bundesverwaltungsgerichts ist ausserdem ein rein formeller Prozessentscheid. Er hat weder eine materielle Tragweite noch eine rechtsprechungsbildende Wirkung. Das hat das Bundesverwaltungsgericht in seiner Antwort auf die Interpellation Wyssmann 26.3871, "Prozessentscheid E-2274/2020 vom 20. November 2025. Geheimjustiz am Bundesverwaltungsgericht?", selbst festgehalten. Das Bundesverwaltungsgericht stellt klar, dass es sich nicht um ein Leiturteil handelte, und der Entscheid führt weder zu einer Änderung noch zu einer Weiterentwicklung der Rechtsprechung, im Gegenteil: Das Bundesverwaltungsgericht hat die Praxis des SEM bereits in seinem Urteil vom November 2023 bestätigt. Seit diesem Urteil hat sich die Situation der Frauen in Afghanistan nochmals massiv verschlechtert und in keiner Weise verbessert, wie man dem Votum des Motionärs entnehmen könnte. 
+Zusammenfassend ist klar: Frauen und Mädchen aus Afghanistan sind Flüchtlinge. Im Verfahren schaut sich das SEM dazu jeden Fall einzeln an. Wir verhindern so Missbrauch, und gleichzeitig garantieren wir rasche Verfahren für Menschen, die sowieso in der Schweiz bleiben. Das bringt Klarheit für die Betroffenen und für die Kantone. Der Bundesrat sieht keinen Grund, auf die Praxisänderung zurückzukommen. Er beantragt Ihnen, die Motion abzulehnen. Die Zahl der Asylgesuche aus Afghanistan ist seit Kurzem übrigens deutlich zurückgegangen. Zu einem Asylgesuch scheint sich also kaum jemand besonders eingeladen zu fühlen.
+Ich komme zur Motion 26.3616: Diese Forderung ist bereits erfüllt. Der Bund ist gesetzlich verpflichtet, die Kantone und Gemeinden bei der Einrichtung der Bundesasylzentren frühzeitig einzubeziehen. Im Rahmen des Sachplanverfahrens wie auch im Plangenehmigungsverfahren werden der betroffene Kanton und die Gemeinde angehört, Herr Knutti. Das wird immer so gemacht. Das Asylwesen ist eine Verbundaufgabe von Bund, Kantonen und Gemeinden. An zwei nationalen Asylkonferenzen in den Jahren 2013 und 2014 beschlossen sie einstimmig, den Asylbereich neu zu strukturieren und in sechs Asylregionen aufzuteilen; anschliessend haben sich die drei Staatsebenen im gegenseitigen Einvernehmen darauf verständigt, wo wie viele Unterbringungsplätze zur Verfügung stehen sollen. Und seit über zehn Jahren arbeitet der Bund am Aufbau der vereinbarten 5000 Plätze. Das macht er aber nicht im Alleingang; sowohl Privatpersonen als auch die Gemeinden und Kantone haben immer die Möglichkeit, sich ins Verfahren einzubringen und Einsprache zu erheben. Das Anliegen der vorliegenden Motion ist somit bereits erfüllt.
+Der Bundesrat beantragt Ihnen deshalb, diese Motion abzulehnen.
+Nun zur Motion 24.4063: Die Motionärin begründet die vorgeschlagenen Anpassungen damit, dass vorläufig aufgenommene Personen langfristig in der Schweiz bleiben. Das stimmt. Viele können nicht in die Heimat zurück, weil dort Bürgerkrieg herrscht oder es andere Umstände gibt, die eine Rückkehr unmöglich machen. Diese Personen können gar nicht anders, als hier zu bleiben.
+Der Bundesrat will dennoch nicht automatisch eine Aufenthaltsbewilligung erteilen, weil jemand schon länger in der Schweiz lebt. Es braucht immer eine Einzelfallprüfung. Zuständig sind die Kantone. Sie prüfen, ob die Personen gut in die Schweiz integriert sind, sie sind berechtigt, entsprechende Anträge zu stellen, der Einzelfälle zu begründen. Sie berücksichtigen, ob jemand eine Landessprache spricht, ob jemand arbeitet, ob jemand die öffentliche Ordnung respektiert.
+Erst kürzlich hat Ihr Rat über die Motion Stark 25.3689, "Fehlanreize in der Asylpolitik reduzieren", beraten. Ein Thema dabei waren längere Fristen für Härtefallgesuche und folglich auch für die Erteilung einer Aufenthaltsbewilligung. Sie haben damals die bisherige Praxis bestätigt. Ein Argument in der Debatte war, dass die Möglichkeit, ein Härtefallgesuch einzureichen, ein wichtiger Anreiz für die Integration ist. Der Bundesrat teilt diese Einschätzung. Wer die Aufenthaltsbewilligung nach zehn Jahren automatisch erhält, hat diesen Anreiz nicht.
+Aus diesen Gründen beantragt der Bundesrat, auch diese Motion abzulehnen.
+Nun zur Motion 25.3058: Das Dublin-System legt klare Kriterien fest, welcher Staat für die Prüfung eines Asylgesuchs zuständig ist. Im Einzelfall kann das SEM von den Zuständigkeitsregeln abweichen, zum Beispiel aus medizinischen, sozialen oder humanitären Gründen. Das SEM prüft in jedem Einzelfall umfassend die konkreten Umstände, dabei trägt es besonders auch dem Kindswohl Rechnung; das SEM beachtet bei der Prüfung die Kinderrechtskonvention.
+Falls eine Folgebehandlung im zuständigen Dublin-Staat möglich ist, informiert das SEM noch vor der Überstellung die dortigen Behörden. Am 12. Juni 2026 ist die Asylum and Migration Management Regulation (AMMR) in Kraft getreten. Sie sieht längere Fristen vor als die bisherigen Dublin-Verordnungen, und damit bekommt der aufnehmende Staat mehr Zeit, um sich auf die Ankunft einer gesundheitlich beeinträchtigten Person vorzubereiten.
+Eine systematische Anwendung der Souveränitätsklausel lehnt der Bundesrat ab. Eine Krankheit bei einem Kind soll nicht automatisch dazu führen, dass die Schweiz das Asylgesuch selbst prüft. Der Bundesrat beantragt also, auch die Motion Klopfenstein Broggini abzulehnen.
+Ich komme zur Motion 25.4067. Der Krieg in der Ukraine dauert an. Drohnenangriffe und Angriffe auf die Infrastruktur sind in der Ukraine an der Tagesordnung, die Zahl der getöteten Zivilistinnen und Zivilisten nimmt gerade zu. Eine Stabilisierung der Lage ist derzeit nicht in Sicht. Der Bundesrat hat deshalb am 19. August 2026 entschieden, den Schutzstatus S bis zum 4. März 2028 nicht aufzuheben. Dieser Entscheid erfolgte nach einer breiten Konsultation von Kantonen, Kommunalverbänden, Sozialpartnern und weiteren staatlichen und nichtstaatlichen Akteuren. Für den Bundesrat ist klar, der Schutzstatus S ist unter den heutigen Umständen weiterhin die beste Lösung. Er ermöglicht es, die Menschen, die vor dem Krieg geflüchtet sind, wirksam zu schützen, gleichzeitig entlastet er das Asylsystem. Sie dürfen nie vergessen, dass es möglich ist, dass jemand, der den Schutzstatus nicht erhält, bei uns Asyl beantragt.
+Unser Vorgehen ist eng mit der Europäischen Union abgestimmt. Auch die EU hat den vorübergehenden Schutz bis März 2028 verlängert. Gleichzeitig übernimmt die Schweiz die neuen Regeln der EU für Dienstpflichtige. Diese Koordination ist wichtig, sie hilft, Sekundärmigration innerhalb des Schengen-Raums zu vermeiden. In Zukunft erhalten wehrpflichtige Männer aus der Ukraine bei uns keinen Schutzstatus mehr. Der Bundesrat will eine Exit-Strategie, selbstverständlich brauchen wir das, und wir sind ja längst daran, eine solche zu erarbeiten. Wir haben Ihnen auch schon Vorschläge gezeigt, die aus der Öffentlichkeit kommen.
+Der Bundesrat stützt sich auf das Konzept zur Zukunft des Status S. Dieses wurde im laufenden Jahr unter der Leitung des Staatssekretariats für Migration und der Vereinigung der kantonalen Migrationsbehörden erarbeitet. Das Konzept zeigt anhand von drei Szenarien auf, wie der Übergang zu Aufenthaltsbewilligungen oder später zu einer Aufhebung des Schutzstatus S gestaltet werden könnte. Es zeigt auch die operativen Folgen und den Ressourcenbedarf auf. Damit können sich Bund, Kantone und Gemeinden frühzeitig vorbereiten.
+Bund, Kantone, Gemeinden und Städte sind zum Schluss gekommen, dass eine Aufhebung des Schutzstatus S zum jetzigen Zeitpunkt das Asylsystem überlasten würde. Gleichzeitig würde es zu erheblichen Unsicherheiten für die schutzbedürftigen Personen führen. Vorteile sind nicht ersichtlich. Auch eine schrittweise Aufhebung ist aus Sicht des Bundesrates erst dann sinnvoll, wenn die Europäische Union entsprechende Massnahmen ergreift und wenn keine Überlastung des Asylsystems aufgrund von neuen Gesuchen mehr droht - bis dann überwiegen die Vorteile des heutigen Systems. Der Bundesrat beantragt Ihnen deshalb, die Motion abzulehnen.
+Zum Schluss zur Motion 26.3100: Die Schweiz ist bei der Rückkehr vergleichsweise erfolgreich. Wir müssen diesen Kurs konsequent weiterverfolgen und dabei alle verfügbaren Instrumente nutzen. Das sind beispielsweise Massnahmen im Europäischen Verbund oder der Visa-Hebel, also die Verknüpfung der Visapolitik mit der Rückkehr. Diesen wenden wir bereits erfolgreich an. Zudem hat der Bundesrat weiterhin auf die internationale Migrationszusammenarbeit gesetzt. Hier braucht es eine enge Verbindung zwischen Migrations- und Aussenpolitik. Die Schweiz setzt dabei grundsätzlich auf einen partnerschaftlichen Ansatz mit Drittstaaten - schlicht und einfach, weil wir festgestellt haben, dass wir damit schneller vorwärtskommen und die Ziele und Interessen der Schweiz besser erreichen können. Gleichzeitig bestehen bereits heute Möglichkeiten, um die Entwicklungszusammenarbeit anzupassen, wenn ein Schwerpunktland die Zusammenarbeit bei Migrationsfragen nicht ausreichend mitträgt. 
+Zu den Return Hubs kann ich sagen, was ich schon oft gesagt habe. Die neue EU-Rückkehrverordnung steht kurz vor der Verabschiedung, und diese sieht die Möglichkeit von Return Hubs vor. Die Schweiz als Schengen-assoziierter Staat muss die Regelung innerhalb von zwei Jahren übernehmen. Der Bundesrat hat die Machbarkeit solcher Return Hubs in Drittstaaten untersucht. Wie Sie wissen, schliesst er eine Teilnahme an einem solchen Projekt nicht aus. Die rechtlichen und praktischen Hürden sind aber hoch. Return Hubs könnten unser Asylsystem höchstens punktuell entlasten. 
+Auf nationaler Ebene konzentriert sich der Bundesrat darauf, unser nationales Asylsystem zu stärken und zu verbessern. Das ist der Ansatz, den wir mit der Asylstrategie 2027 verfolgen. Damit können wir, da sind wir überzeugt, mehr Wirkung erzielen, zusammen mit den Kantonen, Gemeinden und Städten. Der Bundesrat setzt sich bereits heute dafür ein, dass die Rückkehr und die Kooperation mit Drittstaaten weiter verbessert wird. Der eingeschlagene Weg hat sich bewährt. Wir brauchen keine zusätzliche Motion in diesem Bereich.
+Wir beantragen deshalb auch diese Motion zur Ablehnung. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserfallen Christian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Frage beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; denn die Letzten, die sich dann beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Deshalb müssen wir zusammen griffige Massnahmen definieren, damit die Asylpoliti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Frage beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; denn die Letzten, die sich dann beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Deshalb müssen wir zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in geordneten Bahnen vorangetrieben werden kann. Das Resultat in anderen Ländern, wo man das seit Jahrzehnten nicht macht, ist Zeichen genug. Dieses Resultat wollen wir in unserem Land nicht erzielen. Nehmen Sie das vielleicht einmal zur Kenntnis, wenn Sie so reagieren. 
+Es gibt in der Schweiz - um zur Motion 25.4067 der FDP-Fraktion zu kommen - 73 800 Personen mit Schutzstatus S aus der Ukraine. Das ist ein knapper Drittel aller Personen, die sich momentan in der Schweiz im Asylbereich aufhalten. Das ist eine Anzahl Personen in der Grössenordnung der Stadt St. Gallen. Hier müssen wir schon eine Strategie haben. Deshalb verlangt die FDP-Fraktion eine klare Exit-Strategie in Bezug auf den Schutzstatus S unter Berücksichtigung auch der europäischen Entwicklungen, welche zur Verlängerung desselben bis im März 2028 geführt haben. Es geht nicht, dass man den Schutzstatus S einfach pauschal in eine vorläufige Aufnahme überführt. Das würde dann bedeuten, dass diese Leute wahrscheinlich nie mehr zurückgehen. Es war damals unsere Bundesrätin Keller-Sutter, die im Namen des Bundesrates klar gesagt hat, beim Schutzstatus S handle es sich um einen "rückkehrorientierten" Status. Diesen rückkehrorientierten Status wollen wir beibehalten. Deshalb lehnen wir es eben entschieden ab, dass man die 73 800 aktiven Leute mit Schutzstatus S dann ohne Einzelfallprüfung in eine kollektive vorläufige Aufnahme überführt. 
+Es muss individuell geprüft werden. Ja, zur individuellen Prüfung von über 70 000 Personen braucht es Ressourcen. Genau aus diesem Grund beantragen wir mit dieser Motion hier eine Exit-Strategie. Wir sind ehrlich gesagt etwas irritiert darüber, dass der Bundesrat diesen Vorstoss bekämpft. Die Schweiz soll ihre Hausaufgaben machen und Ressourcen für Abklärungen einsetzen, wie diese Personen geordnet und möglichst früh zurückgeschickt und dabei juristisch unterstützt werden können. Ein sauberes Asylverfahren dieser Art ist die Grundlage dafür, dass man die Leute zurückschicken kann, sobald der Krieg hoffentlich einmal zu Ende ist. Es gilt dann ebenfalls, zum Beispiel Personen in Ausbildung zu berücksichtigen und eine verhältnismässige Frist festzusetzen, bis wann sie das Land zu verlassen haben. Das sind harte Entscheidungen, ja, aber es sind nötige Entscheidungen. Wenn wir pauschal einfach über alles hinwegsehen, dann werden wieder neue Diskussionen in diesem Land entstehen. Wir wollen nicht wieder in das alte Fahrwasser einer Asylpolitik zurückkehren, bei welcher diese Dinge eben zu wenig Berücksichtigung gefunden haben. 
+Und ja, es muss dann halt im einen oder anderen Fall die Ablehnung eines Asylgesuches stattfinden. Wir haben über die Kommission auch politisch erwirkt, dass gewisse Regionen der Ukraine als sichere Zonen eingestuft werden. Das wurde hier drin auch schon in Abrede gestellt. Es gibt aber sichere Bereiche in der Ukraine. Dort müssen andere Massstäbe gelten als in den aktiven Kriegsgebieten, denn sonst werden wir schlicht und ergreifend überschwemmt. Wenn Personen dann halt nicht freiwillig zurückgehen, muss man Druck aufsetzen, damit sie das Land verlassen. Wie gesagt, es ist ein rückkehrorientierter Status.
+Dazu benötigen wir auf Bundesebene, im Staatssekretariat, konkrete Personalplanung. Es braucht Personal, das ist für uns klar, und auch Bundesrat Jans müsste das grösste Interesse daran haben. Die Kantone und Gemeinden - da deckt sich meine Beobachtung mit meinem Vorvorredner aus der SVP-Fraktion - müssen in diesen Prozess integriert werden, sie können das nicht alles alleine ausbaden, während der Bund zuschaut. Also lieber vorher eine Exitstrategie definieren, so, wie wir sie in der Motion verlangen, anstatt dann mit "Pflästerlipolitik" in diesem heiklen Bereich die falschen Entscheidungen zu fällen.
+Ich danke Ihnen für die Unterstützung dieser Motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dass Frauen sexuelle oder geschlechtsspezifische Gewalt erleben müssen, ist inakzeptabel. Frauen haben Recht auf Schutz vor dieser Gewalt; das gilt auch für asylsuchende Frauen. Bereits heute garantieren verschiedene Massnahmen im Asylverfahren wie auch bei der Unterbringung und Betreuung, dass dieser Schutz effektiv gewährt wird. Diese Massnahmen sind aber grossmehrheitlich unbekannt. 
+Mit einem Bericht zur Erfüllung des Postulats könnte der Bundesrat dem Parlament aufzeigen, welche Massnahmen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dass Frauen sexuelle oder geschlechtsspezifische Gewalt erleben müssen, ist inakzeptabel. Frauen haben Recht auf Schutz vor dieser Gewalt; das gilt auch für asylsuchende Frauen. Bereits heute garantieren verschiedene Massnahmen im Asylverfahren wie auch bei der Unterbringung und Betreuung, dass dieser Schutz effektiv gewährt wird. Diese Massnahmen sind aber grossmehrheitlich unbekannt. 
+Mit einem Bericht zur Erfüllung des Postulats könnte der Bundesrat dem Parlament aufzeigen, welche Massnahmen in diesem Bereich in den letzten Jahren umgesetzt wurden. Gleichzeitig erhalten wir die Möglichkeit, weitere Handlungsfelder zu identifizieren und zusätzliche Massnahmen zu prüfen. Der Bundesrat beantragt Ihnen deshalb, dieses Postulat anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christ Katja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsidentin (Christ Katja, erste Vizepräsidentin): Die ausserordentliche Session zum Thema "EU und Asyl" ist damit beendet. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich werde keine Fragen beantworten, Kollege Riner. Ich habe genug von Ihrer menschenverachtenden und menschenrechtswidrigen Asylpolitik gehört. Ich werde nicht Hand bieten für noch mehr solcher Ausführungen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schilliger Peter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist von Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rechtlic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist von Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rechtlichen Grundlagen für die Verhandlung und den Einsatz sicherer Drittstaatenlösungen geschaffen werden. 
+Europa sucht seit Jahren nach Instrumenten, um die irreguläre Migration zu reduzieren, Schleusernetze zu bekämpfen und die Asylverfahren zu beschleunigen. Das Europäische Parlament hat am 5. Februar 2026 neue Regeln verabschiedet, nach denen unter anderem eine EU-weite Liste sicherer Herkunftsstaaten geschaffen wird und es Mitgliedstaaten ermöglicht wird, Abkommen mit Drittstaaten abzuschliessen, in denen Asylanträge geprüft werden können. Das Modell der Rückführungszentren und die verstärkte Verknüpfung von Rücknahmekooperationen mit anderen politischen Hebeln wie Visa oder Entwicklungshilfe werden in mehreren europäischen Debatten bereits behandelt. 
+Die Schweiz registriert immer wieder Asylgesuche von Personen, die vor ihrer Einreise bereits längere Zeit in Drittstaaten lebten, in denen keine unmittelbare Gefährdung bestand. Nach geltendem Recht ist ein Nichteintreten möglich, wenn der Drittstaat als sicher gilt. In der Praxis scheitert eine Rückführung aber häufig an fehlenden Abkommen oder an der Weigerung der betroffenen Staaten, Personen wieder aufzunehmen. Diese Lücke schwächt die Glaubwürdigkeit des Asylsystems, das dort Schutz bieten soll, wo er effektiv erforderlich ist. Dies ist Gegenstand des Postulates Caroni 23.4490, welches den Bundesrat beauftragt, in einem Bericht eine Auslegeordnung zu Asylverfahren und zum Wegweisungsvollzug im Ausland, insbesondere in Drittstaaten, vorzulegen und die Vereinbarkeit mit schweizerischen Standards zu prüfen. 
+Der Bundesrat lehnt die Motion mit der Begründung ab, die Schweiz habe eine der höchsten Rückkehrraten in Europa. Diese Aussage blendet jedoch aus, dass vor allem die Wirtschaftsflüchtlinge aus Nordafrika einen zu grossen Platz in unserer Asylstatistik einnehmen. Nicht dies allein ist ein grosses Ärgernis, sondern die Tatsache, dass genau diese Personen in der Statistik der Straftaten mit dem sehr hohen Wert von über 80 Prozent negativ auffallen. Dies führt nicht nur zu einer hohen Gefährdung der Sicherheit unserer Bevölkerung, sondern auch zu einer schlechten Akzeptanz gegenüber nachweislich schutzberechtigten Flüchtlingen. Diese nicht ausgewiesenen abgewiesenen Flüchtlinge schaden damit der humanitären Grundhaltung unserer Bevölkerung. 
+Geschätzter Herr Bundesrat Jans, die Schweiz braucht neben verstärkten Rücknahmekooperationen handhabbare Instrumente, um die Staaten, die Rücknahmen systematisch verweigern oder behindern, konsequent umgehen zu können. Gezielt eingesetzte Visa-Restriktionen und Konditionalität sind verhältnismässige internationale Standardinstrumente, die die Rücknahmebereitschaft erhöhen können, ohne den Schutzberechtigten die Rechtsmittel oder den Zugang zu internationalem Schutz zu entziehen. Ergänzend ermöglichen Rückführungszentren und Drittstaatenlösungen, abgewiesene Fälle von Personen konsequent ausserhalb Europas zu bearbeiten oder diese unterzubringen, sofern menschenrechtliche und verfahrensrechtliche Mindeststandards garantiert sind. 
+Für die Unterstützung unserer Fraktionsmotion bedanke ich mich.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steinemann Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durch Ihr Postulat soll unter anderem in Erfahrung gebracht werden, ob und wie Gewalt bei Frauen als Fluchtgrund eine Rolle spielt. Das würde mich eigentlich auch sehr interessieren. Es ist nämlich noch nicht lange her, dass über meine Postulate 25.4259, "Transparenz zu den Gründen, die zu einer vorläufigen Aufnahme führen", und 24.3290, "Transparenz in die Gründe der Asylgewährungen bringen", abgestimmt wurde. Sie wurden grossmehrheitlich überwiesen, aber nicht von Seiten der Postulantin - ausg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durch Ihr Postulat soll unter anderem in Erfahrung gebracht werden, ob und wie Gewalt bei Frauen als Fluchtgrund eine Rolle spielt. Das würde mich eigentlich auch sehr interessieren. Es ist nämlich noch nicht lange her, dass über meine Postulate 25.4259, "Transparenz zu den Gründen, die zu einer vorläufigen Aufnahme führen", und 24.3290, "Transparenz in die Gründe der Asylgewährungen bringen", abgestimmt wurde. Sie wurden grossmehrheitlich überwiesen, aber nicht von Seiten der Postulantin - ausgerechnet Rot-Grün hat nicht für diese Offenlegungen gestimmt. Das ist auch ein Grund, weshalb wir unser bestehendes System ganz grundsätzlich überdenken müssen. Möchten wir möglichst vielen Menschen Schutz bieten, können wir das unmöglich auf Schweizer Boden tun. Die Auslagerung der Asylverfahren würde eine Reduktion der irregulären Migration bewirken und damit präventive Wirkung zeitigen. Und wir würden hier unsere Strukturen entlasten. Und der Franken wäre dort viel besser investiert. 
+Leider bewegt sich in Bern nichts in diese Richtung. Hingegen sind Linke der Ansicht, dass man unendlich viele Menschen aufnehmen und integrieren kann. Wenn das heutige System uns schon an den Anschlag bringt, dann ist die Ausweitung auf neue Asylgründe nicht unbedingt das passende Rezept. Auf einen neuen Asylgrund "geschlechtsspezifische Gewalt" läuft dieses Postulat jedoch hinaus. Unsere Asylpraxis würde sich noch mehr vom Ursprungsgedanken der Genfer Flüchtlingskonvention entfernen, und international dürften wir damit Neuland betreten. Legen wir in Zukunft den Fokus auf die Aufnahme von Frauen und Mädchen, werden diese dann auch Familiennachzug machen können, mit allen Folgen. Es ist zu hoffen, dass wir mit unserem teuren und personalintensiven Asylsystem heute schon sicherstellen, dass Frauen und Mädchen angemessen untergebracht werden, damit sie hier keiner Gewalt ausgesetzt sind. 
+Vor einigen Jahren haben NGO-Aktivisten eine medial gross angelegte Kampagne über angebliche Misshandlungen durch Betreuer in Asylzentren inszeniert, die das SEM durch einen alt Bundesrichter genau untersuchen liess und deren Vorwürfe sich allesamt in Luft aufgelöst haben. Wir müssen uns also kein schlechtes Gewissen einreden lassen. 
+Bitte lehnen Sie das Postulat ab.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le président (Page Pierre-André, président): Je déclare ouverte la session extraordinaire concernant le thème "UE et asile", demandée par le groupe de l'Union démocratique du centre.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le postulat que je défends vise à renforcer la protection des femmes et des filles, par le biais d'un rapport sur la manière de mieux identifier et protéger les personnes ayant subi des violences sexuelles ou des violences sexistes fondées sur le genre. Cette demande part d'un constat simple, mais particulièrement préoccupant. Partout dans le monde, des femmes et des filles sont contraintes de fuir parce qu'elles risquent un mariage forcé, des mutilations génitales, des violences sexuelles, la t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le postulat que je défends vise à renforcer la protection des femmes et des filles, par le biais d'un rapport sur la manière de mieux identifier et protéger les personnes ayant subi des violences sexuelles ou des violences sexistes fondées sur le genre. Cette demande part d'un constat simple, mais particulièrement préoccupant. Partout dans le monde, des femmes et des filles sont contraintes de fuir parce qu'elles risquent un mariage forcé, des mutilations génitales, des violences sexuelles, la traite des êtres humains ou encore des violences domestiques auxquelles leur État ne veut ou ne peut pas mettre fin. Elles fuient, non pas malgré leur condition de femmes, mais précisément à cause de cette dernière.
+La Suisse reconnaît déjà dans certaines situations que les persécutions liées au genre peuvent justifier une protection internationale. Cette reconnaissance repose cependant encore largement sur l'interprétation juridique et sur la jurisprudence actuelle. Les violences fondées sur le genre ne sont pas toujours examinées de manière systématique ni suffisamment visible dans les procédures d'asile. C'est d'ailleurs ce que souligne le dernier rapport du réseau d'ONG de la Convention d'Istanbul. Ce dernier montre qu'il existe encore d'importantes lacunes. Les motifs d'asile liés au genre sont parfois insuffisamment pris en compte. Les risques spécifiques encourus par les femmes en cas de renvoi ne sont pas toujours évalués de manière adéquate et l'accès à un accompagnement spécialisé reste limité. Il manque également des données fiables qui permettent de mesurer l'ampleur du phénomène, mais aussi d'évaluer la qualité des décisions rendues. Le rapport demandé dans ce postulat vise précisément à combler toutes ces lacunes. Cette nécessité est également confirmée à l'échelle internationale, c'est important de le souligner. En juillet 2025, il y a une année, le Comité des Nations Unies pour l'élimination de la discrimination à l'égard des femmes a rendu trois décisions concernant la Suisse. C'est important de les entendre, car ces décisions, prises au niveau des Nations Unies, sont les suivantes : le comité a notamment critiqué la tendance des autorités à mettre en doute la crédibilité de victimes de violences lorsqu'elles ne parviennent à parler de leurs traumatismes qu'après le début de la procédure. Le comité a également relevé que certains renvois avaient été décidés sans examen suffisamment approfondi des violences et leurs conséquences psychologiques. Ce comité rappelle pourtant un principe fondamental - il faut le rappeler encore dans notre conseil - : les demandes d'asile impliquant des violences fondées sur le genre doivent faire l'objet d'un examen individuel, complet et sensible des traumatismes vécus. Les besoins médicaux, psychologiques et de réadaptation doivent également être pris en compte avant toute décision de renvoi.
+Le Conseil fédéral souligne à juste titre que la Suisse a réalisé des progrès et que les efforts entrepris dans le cadre de la Convention d'Istanbul ont été salués. C'est une bonne chose et je m'en réjouis. Reconnaître les progrès accomplis ne signifie toutefois pas considérer que tout est parfait. Une convention internationale fixe un minimum de protection ; elle n'interdit jamais de faire mieux. C'est précisément ce que vise ce postulat. Il ne crée en aucun cas un droit automatique - c'est important de le dire. Il ne modifie pas non plus les critères d'octroi à l'asile et ne dispense personne d'établir les faits. Il vise tout simplement une chose simple : analyser de manière rigoureuse des lacunes existantes et de proposer des améliorations concrètes pour que les femmes et les filles victimes de violences sexistes et sexuelles bénéficient d'une protection adaptée à leur réalité.
+Derrière ces concepts juridiques, il y a évidemment des parcours de vie, des parcours difficiles, il y a l'exil, mais il y a aussi ces femmes qui ont subi des violences et qui doivent pouvoir être protégées. Des femmes qui ont subi des violences dans leur pays d'origine doivent pouvoir être protégées par notre propre système, en Suisse. Il y a celles qui continuent d'en subir sur les routes migratoires. Il y a celles qui arrivent en Suisse avec des traumatismes profonds et qui doivent ensuite raconter des expériences extrêmement difficiles pour obtenir une protection. Nous avons la responsabilité de nous assurer que notre système est capable d'entendre ces récits - on ne demande pas grand-chose de plus -, de les comprendre et d'y répondre avec tout le professionnalisme nécessaire.
+Je vous remercie d'avance d'accepter ce postulat.
 </t>
   </si>
 </sst>
@@ -388,8 +734,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I12" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I31" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I31"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1029,6 +1375,549 @@
         <v>67</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17"/>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19"/>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>117</v>
+      </c>
+      <c r="I24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>120</v>
+      </c>
+      <c r="I25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>125</v>
+      </c>
+      <c r="I26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>127</v>
+      </c>
+      <c r="I27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" t="s">
+        <v>138</v>
+      </c>
+      <c r="I30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" t="s">
+        <v>140</v>
+      </c>
+      <c r="I31" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -99,18 +99,18 @@
     <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et de</t>
   </si>
   <si>
-    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que leur dossier médical n'a pas été transmis, ou parfois, trop tardivement. Il y a nécessité d'agir, et ce d'autant plus que le dossier électronique du patient (DEP) est resté nettement en deçà des attentes en matière de diffusion et d'utilisation.
-L'objectif majeur reste le même : rendre disponibles les données de santé pertinentes pour améliorer la qualité des soins, renforcer la sécurité des patients et éviter les redondances. C'est le système d'ouverture du dossier qui change pour les patients : il est désormais automatique et gratuit, avec un droit d'opposition, au lieu d'une démarche active. L'idée de base est que désormais chaque personne dispose d'un parcours de santé continu, indépendamment du lieu et du fournisseur de prestations. 
+    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que leur dossier médical n'a pas été transmis ou, parfois, trop tardivement. Il y a nécessité d'agir, et ce, d'autant plus que le dossier électronique du patient (DEP) est resté nettement en deçà des attentes en matière de diffusion et d'utilisation.
+L'objectif majeur reste le même : rendre disponibles les données de santé pertinentes pour améliorer la qualité des soins, renforcer la sécurité des patients et éviter les redondances. C'est le système d'ouverture du dossier qui change pour les patients : il est désormais automatique et gratuit, avec un droit d'opposition, au lieu d'une démarche active. L'idée de base est que, désormais, chaque personne dispose d'un parcours de santé continu, indépendamment du lieu et du fournisseur de prestations. 
 Quels sont les principaux éléments du projet ? Premièrement, le principe de l'"opt-out" a été retenu. Comme je l'ai déjà dit, l'ouverture du dossier ne se fera plus à la demande, comme avec le DEP actuel, mais de manière automatique, avec le maintien du droit d'opposition et la possibilité de suppression ou de restriction des droits d'accès.
 Deuxièmement, dans le but d'une participation généralisée, il est prévu d'étendre l'obligation d'utilisation du dossier électronique de santé aux fournisseurs de prestations. Actuellement, tous les hôpitaux et les établissements de soins sont déjà tenus de se raccorder au dossier électronique du patient. Désormais, les médecins, les pharmaciens ou les physiothérapeutes et d'autres prestataires du domaine ambulatoire qui exercent à la charge de l'assurance obligatoire des soins devront utiliser le dossier électronique de santé et y saisir toutes les données de santé pertinentes pour un traitement médical. Les réticences des professionnels de la santé étaient l'une des principales causes de l'échec du dossier électronique du patient.
-Troisièmement, au lieu de multiples structures décentralisées qui rendaient complexe la mise en oeuvre du dossier électronique du patient, désormais le projet s'appuie sur une infrastructure centralisée. La commission a en effet décidé à l'unanimité que les cantons devraient se mettre d'accord sur une seule communauté nationale. Pour votre information, le regroupement des différentes communautés de référence a progressé et, depuis que la Poste s'est retirée de l'exploitation du dossier électronique du patient, celui-ci s'oriente déjà vers une communauté unique - fort probablement Cara -, dotée d'une infrastructure technique uniforme. La Confédération reste responsable du système d'information.
-Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de ces dernières sur le long terme ; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites sur le plan des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
+Troisièmement, au lieu de multiples structures décentralisées qui rendaient complexe la mise en oeuvre du dossier électronique du patient, désormais, le projet s'appuie sur une infrastructure centralisée. La commission a en effet décidé à l'unanimité que les cantons devraient se mettre d'accord sur une seule communauté nationale. Pour votre information, le regroupement des différentes communautés de référence a progressé et, depuis que la Poste s'est retirée de l'exploitation du dossier électronique du patient, celui-ci s'oriente déjà vers une communauté unique - fort probablement Cara - dotée d'une infrastructure technique uniforme. La Confédération reste responsable du système d'information.
+Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de ces dernières sur le long terme ; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business, ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites sur le plan des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
 Cinquièmement, un financement clarifié est nécessaire. Si c'est la Confédération qui finance la mise en place et le développement de l'infrastructure, ce sont les cantons qui assumeront les coûts d'exploitation courants et garantiront l'exploitation de la communauté sur leur territoire. Dans son corapport, la Commission des finances de notre conseil relève que les estimations transmises sont imprécises et peu transparentes, notamment parce que l'on souhaite éviter tout risque d'impact négatif sur l'appel d'offres. Elle recommande ainsi de rester attentif aux conséquences budgétaires que pourraient entrainer d'éventuelles modifications apportées au projet.
 Une condition décisive pour l'acceptation et la mise en oeuvre du DES, et qui a préoccupé notre commission, est la confiance en la protection des données. La sécurité des données, leur transition ainsi que leur chiffrement ont été soigneusement analysés. Concernant ce dernier, la commission s'est penchée sur la question d'un éventuel chiffrement de bout en bout (E2EE), sur la base d'une étude de l'EPFL réalisée à la demande de l'Office fédéral de la santé publique. Prenant acte du fait qu'aucun autre système public ou national n'utilise un chiffrement E2EE strict, en raison d'insuffisances techniques, la commission estime que cette solution ne doit pas être inscrite dans la loi. Elle propose toutefois à l'unanimité que les exigences en matière de protection et de sécurité des données, ainsi que la nécessité de chiffrer les données, soient explicitement mentionnées dans un nouvel article 5a. De plus, la commission propose, à l'unanimité, de préciser que la Confédération ne peut traiter les données personnelles "que dans la mesure où cela est nécessaire au bon fonctionnement technique du système d'information DES". Il s'agit de l'article 5 alinéa 5.
-Enfin, à l'unanimité, la commission considère qu'il convient de préciser que le code source des logiciels utilisés doit être publié dans la mesure du possible, donc en "open source" - il s'agit de l'article 5 alinéa 8 - et que des profils d'autorisation adaptables et faciles à comprendre doivent être mis à disposition - article 11 alinéas 5bis et 5ter.
+Enfin, à l'unanimité, la commission considère qu'il convient de préciser que le code source des logiciels utilisés doit être publié, dans la mesure du possible, donc en "open source" - il s'agit de l'article 5 alinéa 8 -, et que des profils d'autorisation adaptables et faciles à comprendre doivent être mis à disposition - article 11 alinéas 5bis et 5ter.
 Une seconde condition est essentielle. Elle concerne la transition entre le DEP et le DES. Quatre points critiques ont été abordés.
 Premièrement, la loi fédérale sur le dossier électronique du patient (LDEP) sera maintenue jusqu'à la mise en oeuvre du DES pour éviter que des lacunes menacent l'exploitation, le financement et les services de base.
-Deuxièmement, le retrait de Post Sanela, prévu à la fin de 2026, doit se faire avec la garantie d'une migration ordonnée vers la communauté de référence Cara - ou vers la plateforme qui sera choisie - sans coûts supplémentaires ni pertes de données. Pour rappel, cela concerne près de 80 000 DEP ouverts, et La Poste, en tant qu'entreprise liée à la Confédération, a une responsabilité particulière à cet égard.
+Deuxièmement, le retrait de Post Sanela, prévu à la fin de 2026, doit se faire avec la garantie d'une migration ordonnée vers la communauté de référence Cara ou vers la plateforme qui sera choisie sans coûts supplémentaires ni pertes de données. Pour rappel, cela concerne près de 80 000 DEP ouverts, et, La Poste, en tant qu'entreprise liée à la Confédération, a une responsabilité particulière à cet égard.
 Troisièmement, la capacité de raccordement technique des fournisseurs de prestations et des systèmes primaires existants avec le DES doit être garantie.
 Quatrièmement, la transition doit être accélérée, mais dans le respect des règles de l'OMC et de la loi fédérale sur les marchés publics, une procédure de gré à gré étant considérée comme risquée. En bref, une transition stable sans perte de données ni d'investissements est prioritaire. Par courrier, la commission a, de ce fait, invité à l'unanimité le Conseil fédéral à s'engager dans ce sens.
 En conclusion, par 16 voix contre 8, la commission vous recommande d'entrer en matière sur le projet. Bien qu'elle soit d'accord avec l'objectif, une minorité critique en particulier l'infrastructure centralisée, qui, selon elle, nécessitera le lancement d'un nouveau projet informatique important et risqué sur le plan fédéral, ainsi que le droit d'opposition prévu.
@@ -152,7 +152,7 @@
   <si>
     <t xml:space="preserve">La motion vise à permettre aux personnes en procédure d'asile, aux bénéficiaires de l'aide sociale ou de prestations complémentaires d'être, en règle générale, tenues de choisir un modèle particulier d'assurance. La motion vise certes à déroger à la règle dans des cas exceptionnels.
 Il convient de préciser que, pour les requérants d'asile et pour les personnes à protéger sans autorisation de séjour, la Confédération et les cantons peuvent d'ores et déjà restreindre le choix de l'assureur, prescrire une forme particulière d'assurance et limiter le choix des fournisseurs de prestations. Cela permet de gérer l'accès au système de santé et d'utiliser les fonds publics de manière économique en garantissant des prix moins élevés. La charge administrative est aussi fortement réduite lorsque les soins de santé des requérants d'asile sont gérés par un seul assureur ou par un petit nombre d'assureurs.
-Les cantons peuvent également accorder une réduction de primes aux assurés dont la condition économique est modeste. Les cantons déterminent à la fois les bénéficiaires et le montant, et peuvent fixer une prime de référence fondée, elle aussi, sur une assurance avec choix limité des fournisseurs de prestations. Il ne s'agit donc pas d'aborder la question de la réduction des primes, mais celle de la prime de référence, qui est basée sur une assurance avec choix limité. Pour le calcul des prestations complémentaires, la prime effective est prise en compte, mais au maximum à hauteur de la prime moyenne cantonale ou régionale. Les bénéficiaires de prestations complémentaires sont dès lors incités à choisir une prime appropriée.
+Les cantons peuvent également accorder une réduction de primes aux assurés dont la condition économique est modeste. Les cantons déterminent à la fois les bénéficiaires et le montant et peuvent fixer une prime de référence fondée, elle aussi, sur une assurance avec choix limité des fournisseurs de prestations. Il ne s'agit donc pas d'aborder la question de la réduction des primes, mais celle de la prime de référence, qui est basée sur une assurance avec choix limité. Pour le calcul des prestations complémentaires, la prime effective est prise en compte, mais au maximum à hauteur de la prime moyenne cantonale ou régionale. Les bénéficiaires de prestations complémentaires sont dès lors incités à choisir une prime appropriée.
 En résumé, les cantons sont largement compétents en matière de réduction des primes, de prestations complémentaires, d'aide sociale et d'impôts. Ils peuvent donc coordonner ces domaines de manière optimale. La Confédération n'est pas habilitée à édicter des prescriptions allant au-delà de ses propres compétences.
 Dès lors, je vous propose de rejeter la motion.
 </t>
@@ -561,7 +561,7 @@
 Ich komme zur Motion 26.3616: Diese Forderung ist bereits erfüllt. Der Bund ist gesetzlich verpflichtet, die Kantone und Gemeinden bei der Einrichtung der Bundesasylzentren frühzeitig einzubeziehen. Im Rahmen des Sachplanverfahrens wie auch im Plangenehmigungsverfahren werden der betroffene Kanton und die Gemeinde angehört, Herr Knutti. Das wird immer so gemacht. Das Asylwesen ist eine Verbundaufgabe von Bund, Kantonen und Gemeinden. An zwei nationalen Asylkonferenzen in den Jahren 2013 und 2014 beschlossen sie einstimmig, den Asylbereich neu zu strukturieren und in sechs Asylregionen aufzuteilen; anschliessend haben sich die drei Staatsebenen im gegenseitigen Einvernehmen darauf verständigt, wo wie viele Unterbringungsplätze zur Verfügung stehen sollen. Und seit über zehn Jahren arbeitet der Bund am Aufbau der vereinbarten 5000 Plätze. Das macht er aber nicht im Alleingang; sowohl Privatpersonen als auch die Gemeinden und Kantone haben immer die Möglichkeit, sich ins Verfahren einzubringen und Einsprache zu erheben. Das Anliegen der vorliegenden Motion ist somit bereits erfüllt.
 Der Bundesrat beantragt Ihnen deshalb, diese Motion abzulehnen.
 Nun zur Motion 24.4063: Die Motionärin begründet die vorgeschlagenen Anpassungen damit, dass vorläufig aufgenommene Personen langfristig in der Schweiz bleiben. Das stimmt. Viele können nicht in die Heimat zurück, weil dort Bürgerkrieg herrscht oder es andere Umstände gibt, die eine Rückkehr unmöglich machen. Diese Personen können gar nicht anders, als hier zu bleiben.
-Der Bundesrat will dennoch nicht automatisch eine Aufenthaltsbewilligung erteilen, weil jemand schon länger in der Schweiz lebt. Es braucht immer eine Einzelfallprüfung. Zuständig sind die Kantone. Sie prüfen, ob die Personen gut in die Schweiz integriert sind, sie sind berechtigt, entsprechende Anträge zu stellen, der Einzelfälle zu begründen. Sie berücksichtigen, ob jemand eine Landessprache spricht, ob jemand arbeitet, ob jemand die öffentliche Ordnung respektiert.
+Der Bundesrat will dennoch nicht automatisch eine Aufenthaltsbewilligung erteilen, weil jemand schon länger in der Schweiz lebt. Es braucht immer eine Einzelfallprüfung. Zuständig sind die Kantone. Sie prüfen, ob die Personen gut in die Schweiz integriert sind, sie sind berechtigt, entsprechende Anträge zu stellen, die Einzelfälle zu begründen. Sie berücksichtigen, ob jemand eine Landessprache spricht, ob jemand arbeitet, ob jemand die öffentliche Ordnung respektiert.
 Erst kürzlich hat Ihr Rat über die Motion Stark 25.3689, "Fehlanreize in der Asylpolitik reduzieren", beraten. Ein Thema dabei waren längere Fristen für Härtefallgesuche und folglich auch für die Erteilung einer Aufenthaltsbewilligung. Sie haben damals die bisherige Praxis bestätigt. Ein Argument in der Debatte war, dass die Möglichkeit, ein Härtefallgesuch einzureichen, ein wichtiger Anreiz für die Integration ist. Der Bundesrat teilt diese Einschätzung. Wer die Aufenthaltsbewilligung nach zehn Jahren automatisch erhält, hat diesen Anreiz nicht.
 Aus diesen Gründen beantragt der Bundesrat, auch diese Motion abzulehnen.
 Nun zur Motion 25.3058: Das Dublin-System legt klare Kriterien fest, welcher Staat für die Prüfung eines Asylgesuchs zuständig ist. Im Einzelfall kann das SEM von den Zuständigkeitsregeln abweichen, zum Beispiel aus medizinischen, sozialen oder humanitären Gründen. Das SEM prüft in jedem Einzelfall umfassend die konkreten Umstände, dabei trägt es besonders auch dem Kindswohl Rechnung; das SEM beachtet bei der Prüfung die Kinderrechtskonvention.
@@ -686,6 +686,171 @@
 Le Conseil fédéral souligne à juste titre que la Suisse a réalisé des progrès et que les efforts entrepris dans le cadre de la Convention d'Istanbul ont été salués. C'est une bonne chose et je m'en réjouis. Reconnaître les progrès accomplis ne signifie toutefois pas considérer que tout est parfait. Une convention internationale fixe un minimum de protection ; elle n'interdit jamais de faire mieux. C'est précisément ce que vise ce postulat. Il ne crée en aucun cas un droit automatique - c'est important de le dire. Il ne modifie pas non plus les critères d'octroi à l'asile et ne dispense personne d'établir les faits. Il vise tout simplement une chose simple : analyser de manière rigoureuse des lacunes existantes et de proposer des améliorations concrètes pour que les femmes et les filles victimes de violences sexistes et sexuelles bénéficient d'une protection adaptée à leur réalité.
 Derrière ces concepts juridiques, il y a évidemment des parcours de vie, des parcours difficiles, il y a l'exil, mais il y a aussi ces femmes qui ont subi des violences et qui doivent pouvoir être protégées. Des femmes qui ont subi des violences dans leur pays d'origine doivent pouvoir être protégées par notre propre système, en Suisse. Il y a celles qui continuent d'en subir sur les routes migratoires. Il y a celles qui arrivent en Suisse avec des traumatismes profonds et qui doivent ensuite raconter des expériences extrêmement difficiles pour obtenir une protection. Nous avons la responsabilité de nous assurer que notre système est capable d'entendre ces récits - on ne demande pas grand-chose de plus -, de les comprendre et d'y répondre avec tout le professionnalisme nécessaire.
 Je vous remercie d'avance d'accepter ce postulat.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pfister Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat ist sich der Verbreitung verschiedener extremistischer Ideologien bewusst. Diese kann zu Verstössen oder zur Gefährdung der öffentlichen Sicherheit und Ordnung führen bzw. die innere oder äussere Sicherheit der Schweiz bedrohen. 
+Vor diesem Hintergrund wird seit 2023 der Nationale Aktionsplan zur Verhinderung und Bekämpfung von Radikalisierung und gewalttätigem Extremismus von Bund und Kantonen gemeinsam umgesetzt. Der Nachrichtendienst des Bundes (NDB) ist für die Beurteilung der </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat ist sich der Verbreitung verschiedener extremistischer Ideologien bewusst. Diese kann zu Verstössen oder zur Gefährdung der öffentlichen Sicherheit und Ordnung führen bzw. die innere oder äussere Sicherheit der Schweiz bedrohen. 
+Vor diesem Hintergrund wird seit 2023 der Nationale Aktionsplan zur Verhinderung und Bekämpfung von Radikalisierung und gewalttätigem Extremismus von Bund und Kantonen gemeinsam umgesetzt. Der Nachrichtendienst des Bundes (NDB) ist für die Beurteilung der Bedrohungslage in der Schweiz zuständig. Um Bedrohungen für die innere und äussere Sicherheit frühzeitig zu erkennen, zu verhindern und zu bekämpfen, unterhält er ein aktuelles Bild der Lage, beurteilt ebendiese, informiert die zuständigen Behörden auf kantonaler Ebene sowie auf Bundesebene und wendet alle gemäss Nachrichtendienstgesetz vorgesehenen Präventivmassnahmen an. 
+Der NDB wird tätig, sofern ein Gewaltbezug gegeben ist. Ein ideologischer Hintergrund von Personen, Organisationen oder anstehenden Ereignissen ohne Gewaltbezug reicht nicht aus - dies gilt auch für den Islamismus. 
+Personen, die die innere und äussere Sicherheit gefährden, können ausgewiesen werden. Aufenthaltsbewilligungen von Ausländerinnen und Ausländern können aus demselben Grund widerrufen werden. In solchen Fällen werden diese Personen aus der Schweiz ausgewiesen und können mit einem Einreiseverbot belegt werden. Auch bei Personen aus dem Asylbereich kann bei den genannten Verstössen das Asyl bzw. die angeordnete vorläufige Aufnahme entzogen werden. Bei Bedarf machen die Bundesbehörden von diesen Massnahmen Gebrauch.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amoos Emmanuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, je vous remercie de nous avoir expliqué la pratique. Ne serait-il pas plus simple de répondre aux questions telles qu'elles sont rédigées ? Je repose ma question : le Conseil fédéral peut-il nous dire si le SRC, le SEM ou Fedpol étaient informés de la tenue de ce "camp fédéral" ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angenommen - Adopté
+[VS]
+Antrag SGK-S [GZ]
+Die Motionen 19.3957 und 19.4120 nicht abschreiben
+Schriftliche Begründung [GZ]
+Die Kommission beantragt, die Motionen nicht abzuschreiben, da deren Forderung nach einer sachgerechten Vergütung der Kinder- und Jugendmedizin noch nicht erfüllt ist. Sie stellt zwar fest, dass die stationären und ambulanten Tarife im Bereich der Kinder- und Jugendmedizin weiterentwickelt wurden und diesem Bereich auch bei der zukünftigen Weiterentwicklung ein besonderes Ge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angenommen - Adopté
+[VS]
+Antrag SGK-S [GZ]
+Die Motionen 19.3957 und 19.4120 nicht abschreiben
+Schriftliche Begründung [GZ]
+Die Kommission beantragt, die Motionen nicht abzuschreiben, da deren Forderung nach einer sachgerechten Vergütung der Kinder- und Jugendmedizin noch nicht erfüllt ist. Sie stellt zwar fest, dass die stationären und ambulanten Tarife im Bereich der Kinder- und Jugendmedizin weiterentwickelt wurden und diesem Bereich auch bei der zukünftigen Weiterentwicklung ein besonderes Gewicht zukommt. Es bestehen aber weiterhin Herausforderungen, die Besonderheiten der Kinder- und Jugendmedizin sachgerecht in den Tarifen abzubilden. Zudem wurde das neue Gesamttarifsystem bestehend aus TARDOC und Ambulanten Pauschalen erst per 2026 eingeführt. Entsprechend kann aus Sicht der Kommission noch nicht beurteilt werden, inwiefern im ambulanten Bereich Verbesserungen erzielt worden sind.
+[VS]
+Proposition CSSS-E [GZ]
+Ne pas classer les motions 19.3957 et 19.4120
+Développement par écrit [GZ]
+La commission propose de ne pas classer les motions au motif que l'objectif qu'elles visent, à savoir garantir une rémunération adéquate de la médecine pédiatrique, n'est pas encore atteint. Elle constate certes que les tarifs stationnaires et ambulatoires dans le domaine de la médecine pédiatrique ont été revus et que ce domaine continuera à revêtir une importance particulière dans le cadre des développements futurs. Il reste toutefois des défis à relever pour refléter de manière adéquate, dans les tarifs, les spécificités de la médecine pédiatrique. De plus, le nouveau système tarifaire global composé de TARDOC et des forfaits ambulatoires n'a été mis en place qu'à partir de 2026. En conséquence, la commission estime qu'il n'est pas encore possible d'évaluer dans quelle mesure des améliorations ont été réalisées dans le domaine des soins ambulatoires.
+[VS]
+Präsident (Engler Stefan, Präsident): Der Bundesrat ist mit der Nichtabschreibung der beiden Motionen einverstanden.[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Antrag UREK-S [GZ]
+Die Motion 21.4318 nicht abschreiben
+Schriftliche Begründung [GZ]
+Mit der Motion wird der Bundesrat beauftragt, alle erneuerbare Gase von der CO2-Abgabe zu befreien.
+In der letzten Revision des CO2-Gesetzes wurden Erleichterungen für Kundinnen und Kunden aus der Industrie, die erneuerbare Gase konsumieren, eingeführt. So kann den Konsumenten die CO2-Abgabe zurückerstattet werden, wenn sie entweder am Emissionshandelssystem teilnehmen oder Verminderungsverpflichtungen eingehen. Zudem müssen sie im Emissionshandelssystem für ihr virtuell importiertes erneuerbares Gas keine Emissionsrechte abgeben. Gleichermassen können sich Unternehmen mit Verminderungsverpflichtungen das virtuell importierte erneuerbare Gas ihrer Emissionsverminderung anrechnen lassen. Der Bundesrat argumentiert deshalb, dass das Anliegen der Motion erfüllt ist, und beantragt deren Abschreibung.
+Die Kommission erachtet jedoch die Motion als nur teilweise erfüllt, da ausschliesslich Konsumenten von erneuerbaren Gasen aus der Industrie von der Befreiung der CO2-Abgabe profitieren. Nach Ansicht der Kommission soll die Abgabe-Befreiung für alle Kundinnen und Kunden gleichermassen gelten und damit auch für erneuerbare Gase, die zum Heizen genutzt werden. Dies, so unterstreicht die Kommission, soll der Bundesrat in der nächsten Revision des CO2-Gesetzes berücksichtigen, weshalb sie beantragt, die Motion nicht abzuschreiben.
+[VS]
+Proposition CEATE-E [GZ]
+Ne pas classer la motion 21.4318
+Développement par écrit [GZ]
+La motion charge le Conseil fédéral d'exonérer tous les gaz renouvelables de la taxe sur le CO2.
+Lors de la dernière révision de la loi sur le CO2, des allègements ont été introduits en faveur des clients industriels qui consomment des gaz renouvelables. Ainsi, la taxe sur le CO2 peut être remboursée aux consommateurs s'ils participent au système d'échange de quotas d'émission ou s'ils souscrivent à des engagements de réduction. De plus, dans le cadre du système d'échange de quotas d'émission, ils ne sont pas tenus de remettre des droits d'émission pour le gaz renouvelable qu'ils importent virtuellement. De même, les entreprises ayant souscrit à des engagements de réduction peuvent faire valoir le gaz renouvelable importé virtuellement dans le cadre de leur réduction d'émissions. Le Conseil fédéral estime donc que l'objectif de la motion est atteint et propose de classer cette dernière.
+La commission considère toutefois que l'objectif de la motion n'est que partiellement atteint, car seuls les consommateurs issus de l'industrie bénéficient de l'exonération de la taxe sur le CO2. Elle estime que l'exonération devrait s'appliquer à tous les clients de la même manière, y compris pour les gaz renouvelables utilisés pour le chauffage. Finalement, elle souligne que le Conseil fédéral devrait en tenir compte lors de la prochaine révision de la loi sur le CO2, raison pour laquelle elle propose de ne pas classer la motion.[GZ]
+[VS][GZ]
+Präsident (Engler Stefan, Präsident): Der Bundesrat ist mit der Nichtabschreibung einverstanden.[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Antrag der Mehrheit SPK-S [GZ]
+Die Motionen 24.3035 und 24.3022 abschreiben
+[VS]
+Antrag der Minderheit SPK-S [GZ]
+(Friedli Esther, Chiesa, Fässler Daniel, Gössi, Häberli-Koller)[GZ]
+Die Motionen 24.3035 und 24.3022 nicht abschreiben
+Schriftliche Begründung [GZ]
+Die Kommissionsmehrheit befürwortet den Antrag des Bundesrates auf Abschreibung der Motionen. Sie hält fest, dass diese durch die Praxisänderungen weitgehend umgesetzt wurden.
+Die Minderheit ist der Ansicht, dass die Motionen nicht abgeschrieben werden sollten, da die Situation in der Praxis nach wie vor unzufriedenstellend sei. So würden Personen mit Schutzstatus S mehrfach aus der Schweiz aus- und wieder einreisen und damit die Gemeinden, in denen sie ansässig sind, vor grosse Schwierigkeiten stellen.
+[VS]
+Proposition de la majorité CIP-E [GZ]
+Classer les motions 24.3035 et 24.3022
+[VS]
+Proposition de la minorité CIP-E [GZ]
+(Friedli Esther, Chiesa, Fässler Daniel, Gössi, Häberli-Koller)[GZ]
+Ne pas classer les motions 24.3035 et 24.3022
+Développement par écrit [GZ]
+La commission soutient la proposition du Conseil fédéral de classer les motions. Elle constate que ces dernières ont été largement mises en oeuvre via des changements de pratique. La minorité est d'avis que les motions ne doivent pas être classées car la réalité du terrain reste insatisfaisante, avec des bénéficiaires de statut S qui, à plusieurs reprises, quittent la Suisse puis reviennent, causant des difficultés aux communes qui les accueillent.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z'graggen Heidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Mehrheit der Kommission beantragt, die vorliegenden Motionen abzuschreiben. Wir folgen mehrheitlich der Argumentation des Bundesrates, wonach die Anliegen der Motionen durch entsprechende Praxisänderungen bereits weitgehend umgesetzt wurden.
+Konkret heisst das: Seit Anfang 2025 wird der Schutzstatus S beendet, wenn eine Person länger als zwei Monate abwesend ist. Bei einer Rückkehr wird das Schutzverfahren, inklusive möglicher Alternativen in anderen Staaten, neu geprüft. Zudem wurde die Reg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Mehrheit der Kommission beantragt, die vorliegenden Motionen abzuschreiben. Wir folgen mehrheitlich der Argumentation des Bundesrates, wonach die Anliegen der Motionen durch entsprechende Praxisänderungen bereits weitgehend umgesetzt wurden.
+Konkret heisst das: Seit Anfang 2025 wird der Schutzstatus S beendet, wenn eine Person länger als zwei Monate abwesend ist. Bei einer Rückkehr wird das Schutzverfahren, inklusive möglicher Alternativen in anderen Staaten, neu geprüft. Zudem wurde die Regelung für Heimatreisen angepasst. Aufenthalte im Heimat- oder Herkunftsstaat sind neu auf höchstens fünfzehn Tage pro Halbjahr begrenzt. Längere Aufenthalte können zum Entzug des Status führen. Darüber hinaus wird seit dem 1. November 2025 die regionale Differenzierung angewendet. Sie sehen: Die Begründung des Bundesrates überzeugt die Mehrheit also, und da diese Instrumente bereits in der Praxis verankert sind, erachtet die Mehrheit eine weitere Beauftragung des Bundesrates als nicht notwendig. 
+Die Minderheit wird ihre Argumente selber vortragen. Für sie ist die Situation in der Praxis nach wie vor nicht zufriedenstellend, und deshalb seien diese Motionen aufrechtzuerhalten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedli Esther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Minderheit beantragt Ihnen, die zwei vorliegenden Motionen nicht abzuschreiben. 
+Was fordern diese beiden Motionen? Sie fordern Anpassungen beim Schutzstatus S. Insbesondere soll der Schutzstatus S aberkannt bzw. nicht wiedererlangt werden, wenn erstens eine Person für eine bestimmte Aufenthaltsdauer ausreist, zweitens eine Person Rückkehrhilfe oder andere rückkehrorientierte Hilfen bezogen hat oder drittens der Schutzstatus S missbräuchlich erlangt wurde. Des Weiteren soll sichergestellt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Minderheit beantragt Ihnen, die zwei vorliegenden Motionen nicht abzuschreiben. 
+Was fordern diese beiden Motionen? Sie fordern Anpassungen beim Schutzstatus S. Insbesondere soll der Schutzstatus S aberkannt bzw. nicht wiedererlangt werden, wenn erstens eine Person für eine bestimmte Aufenthaltsdauer ausreist, zweitens eine Person Rückkehrhilfe oder andere rückkehrorientierte Hilfen bezogen hat oder drittens der Schutzstatus S missbräuchlich erlangt wurde. Des Weiteren soll sichergestellt werden, dass der Schutzstatus innerhalb des Dublin-Raums nur einmal erteilt wird. 
+Die Sprecherin der Mehrheit hat gesagt, der Bundesrat habe diese Motionen im Jahr 2025 umgesetzt. Nach Ansicht der Minderheit ist dies jedoch nur teilweise der Fall. Insbesondere wird der Schutzstatus S in der Schweiz nicht gelöscht, wenn eine Person ausreist, sondern eigentlich fast aufrechterhalten. Ich kann Ihnen einige ganz konkrete Beispiele aus meinem Kanton geben, die mir die St. Galler Gemeinden in den letzten Wochen mitgeteilt haben. Ich nenne Ihnen drei Beispiele.
+Erstes Beispiel: Vier Frauen reisten im Jahr 2022 in die Schweiz ein, im Jahr 2024 aus und sind jetzt, im Jahr 2026, wieder zurückgekehrt. Sie kommen ganz aus dem Westen der Ukraine, also einem Gebiet, das die Schweiz seit letztem Jahr als sogenanntes sicheres Gebiet erklärt hat. Das SEM hat den Schutzstatus S sofort wieder aktiviert und diese vier Frauen auf die St. Galler Gemeinden verteilt.
+Zweites Beispiel einer Familie: Die Familie reiste 2022 in die Schweiz ein und erhielt einen positiven Entscheid zum S-Status. Im Sommer 2023 reiste sie in die Ukraine zurück und beantragte Rückkehrhilfe. Im Herbst 2023 reiste die Familie erneut in die Schweiz ein und erhielt wiederum Schutz. Im November 2024 reiste sie erneut aus und verzichtete schriftlich auf den Schutz. Im Sommer 2026 reiste die Familie erneut ein und erhielt nach fünf Tagen wiederum den positiven Entscheid zum Status S. 
+Oder noch ein letztes Beispiel einer männlichen Person mit Jahrgang 1973: Sie reiste im Jahr 2022 in die Schweiz ein und erhielt den Status S. Im Sommer 2024 verzichtete sie freiwillig auf den Schutz, beantragte Rückkehrhilfe und kehrte in die Ukraine zurück. Bereits zwei Monate später reiste sie erneut in die Schweiz ein und stellte erneut ein Schutzgesuch, das im November 2024 bewilligt wurde. Im März 2025 reiste sie erneut aus, worauf der Schutzstatus formell erlosch. Im Mai 2026 reiste sie erneut ein und stellte ein neues Schutzgesuch. 
+Das sind einige Beispiele, ich könnte Ihnen noch eine ganze Reihe anführen. Das sind alles Beispiele aus St. Galler Gemeinden. Wie Sie sehen, ist die aktuelle Praxis des SEM überhaupt nicht so, wie mit den vorliegenden Motionen eigentlich gefordert und beschlossen wurde. Die Leute haben sogar Rückkehrhilfe erhalten und haben danach wieder ein Gesuch gestellt. Der Bundesrat hat diese Motionen also nur beschränkt umgesetzt. Für die Gemeinden sind gerade solche Wiedereinreisen kostspielig und oft mit viel Aufwand verbunden. Sie erschweren die Prozesse, vor allem auch, weil ja sonst noch sehr viele Fälle pendent sind.
+Vor diesem Hintergrund beantrage ich Ihnen, die Motionen nicht abzuschreiben und den Bundesrat klar zu beauftragen, diese beiden Motionen nun endlich gemäss ihrem Wortlaut umzusetzen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurni Baptiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il y a 4 ans et 3 mois, lors de la session d'été 2022 du Conseil des États, notre conseil débattait de la motion 22.3374 qui visait une augmentation progressive du budget de l'armée jusqu'à 1 pour cent du produit intérieur brut (PIB) de la Suisse en 2030. Je suis allé relire les débats. On nous disait essentiellement les choses suivantes. Le budget de l'armée a moins augmenté que les autres, les années précédentes. Il y a des retards d'investissement et la planification des dépenses pour le F-35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il y a 4 ans et 3 mois, lors de la session d'été 2022 du Conseil des États, notre conseil débattait de la motion 22.3374 qui visait une augmentation progressive du budget de l'armée jusqu'à 1 pour cent du produit intérieur brut (PIB) de la Suisse en 2030. Je suis allé relire les débats. On nous disait essentiellement les choses suivantes. Le budget de l'armée a moins augmenté que les autres, les années précédentes. Il y a des retards d'investissement et la planification des dépenses pour le F-35A ne laissera pas la marge de manoeuvre nécessaire pour procéder aux investissements nécessaires. Mais on disait aussi autre chose. Mme la conseillère fédérale Amherd, alors, le disait très clairement : avec cette augmentation à 1 pour cent, l'armée bénéficiera des moyens nécessaires. Elle disait même s'être opposée à une augmentation immédiate du budget de l'armée de 2 milliards de francs, car les projets d'investissement n'étaient pas aboutis, alors qu'avec une augmentation à 1 pour cent du PIB progressive, on parviendrait parfaitement à procéder aux investissements nécessaires. Tous les intervenants d'alors défendaient cette augmentation de cette manière. Si on faisait cet effort, alors l'effort financier nécessaire était suffisant.
+4 ans plus tard, c'est tout l'inverse qui nous est dit. Même en atteignant 1 pour cent du PIB en 2030, l'armée ne jouirait pas d'assez de moyens. Il faut 24 milliards de francs de plus que les augmentations déjà en cours pour l'armement sur une durée de 8 ans, pour le Conseil fédéral. Comment peut-on sérieusement, en 4 ans, changer pareillement son fusil d'épaule, si je peux me permettre une expression particulièrement adaptée au débat ? C'est la première raison pour laquelle je vous propose de ne pas entrer en matière. Des moyens supplémentaires très importants ont déjà été donnés à l'armée par une augmentation majeure de son budget courant et continueront d'augmenter ces prochaines années. La majorité du Parlement a donc déjà répondu aux demandes qui sont faites. Aller encore plus loin, encore plus vite, c'est une fuite en avant que nous payerons très cher.
+Mais ce n'est pas tout, si l'armée, ces dernières années, avait donné tous les gages d'une gestion saine et rigoureuse de son budget, si l'armée avait mené à bien tous les projets d'investissement complexes à satisfaction, on pourrait éventuellement discuter d'une rallonge et de la création d'un fonds. Mais c'est bien l'inverse qui s'est produit. Tous les projets complexes ont subi au mieux des retards, au pire des scandales dont le principal mérite est d'alimenter de manière extrêmement régulière les humoristes de notre pays. Le prix fixe du F-35A, un mensonge. Les surcoûts liés à cet avion, qu'il s'agisse d'infrastructures ou d'évolution des prix, énormes. Et on n'a même pas encore de garantie sur les futurs coûts d'exploitation du F-35A. Les six drones du programme ADS-15, ce projet s'est traduit par un fiasco retentissant entre vols impossibles par temps de givre et impossibilité de voler sans escorte pour un drone, sans compter les retards énormes. Le pistolet SIG Sauer P320, malgré son évaluation catastrophique et son taux d'incident élevé, la majorité du Parlement et l'armée veulent aller de l'avant. Je vais m'arrêter là, car il y aurait encore beaucoup d'autres exemples à citer, par exemple, ces fameux Patriots qu'il faut urgemment acquérir, mais qui seront livrés dans un délai inconnu, comme la grêle après les vendanges. Ce que j'essaie de vous dire, c'est qu'aujourd'hui, l'armée ne me rassure absolument pas s'agissant de la bonne utilisation des deniers publics. Nous lui avons déjà donné beaucoup de moyens supplémentaires. Nous allons continuer de le faire. Je suis extrêmement inquiet qu'avec ce fonds de l'armement, ce soit un blanc-seing, sans remise en question sur les fiascos à répétition, qui est donné. Or, ces scandales à répétition entament grandement la crédibilité de l'armée. Plutôt que de lui donner aujourd'hui encore 24 milliards de francs de plus que les augmentations déjà massives de son budget, exigeons d'abord qu'elle utilise correctement l'argent à disposition. C'est la deuxième raison de ne pas entrer en matière.
+La troisième raison de ne pas entrer en matière, c'est qu'on ne sait pas vraiment ce qu'on va acheter avec cet argent. Non, je n'exagère pas. On ne sait pas vraiment, ou plutôt pas précisément ce qu'on va acheter avec ces 24 milliards de francs du fonds. Alors oui, on nous dit qu'il y a 15 milliards de francs visant à écarter les menaces les plus probables et 9 milliards pour les surcoûts et les versements d'acomptes. Mais le problème, c'est qu'un acompte, par définition, devrait se retrouver à l'addition finale et ne représente donc pas un coût. L'autre problème, c'est que pour justifier les 15 premiers milliards, on nous parle déjà de renchérissement. On ne va tout de même pas le payer deux fois. Il y a bien un tableau public qui existe sur la planification de l'armement - état mai 2026 -, mais ce tableau est très incomplet. Concrètement, ce tableau montre quelques projets phares, mais reste muet sur des montants très importants, et cela, même dans un avenir proche. On sait, par exemple, qu'on va dépenser 3,9 milliards de francs pour le chapitre "effet contre des cibles aériennes", ce qui, pour le moins, est assez vague, et que 2 milliards de ces 3,9 milliards iront à la défense sol-air de moyenne portée.
+Quant au 1,9 milliard restant, je n'en ai aucune idée, et ce n'est pas faute d'avoir posé la question.
+C'est la même chose pour le chapitre "effet contre les cibles au sol", qui regroupe notamment la question importante de la protection contre les mini-drones. On dépensera par exemple 1,3 milliard de francs en 2028. Sur ce montant, seuls 900 millions pour les chars Leopard et la protection contre les mini-drones sont toutefois justifiés ; pour le reste, soit 400 millions, la grande muette porte décidément bien son nom.
+Je ne connais aucune autre dépense de l'État, aucun autre domaine où l'on pourrait faire preuve d'un degré de précision aussi faible sans se faire immédiatement retoquer par le Parlement. On s'apprête à voter 24 milliards de dépenses supplémentaires pour de l'armement et on ne sait pas précisément ce qu'on va acheter. Pour moi, ce n'est simplement pas sérieux.
+Finalement, je vous propose de ne pas entrer en matière, car ce rapport est un jeu de dupe. Personne dans cette salle ne peut sincèrement croire qu'une augmentation de la TVA de 0,5 pour cent pour le financement des dépenses d'armement a une quelconque chance de passer devant le peuple, ou même devant le Parlement.
+Alors, quel est le but de cet exercice ? Il est simple, politiquement : il s'agit de financer autrement ces 24 milliards. Si c'est de la manière dont la Commission des finances l'a pensé, on peut en discuter. J'ai aussi consulté les déclarations des partis politiques avant la session, qui invitent à une grande prudence. On lit par exemple qu'il faut couper 25 pour cent ou plus des dépenses de la coopération internationale - que nous avons déjà largement diminué ces dernières années - et vendre Swisscom, en renonçant au passage à plus d'un demi-milliard de dividendes - selon le PLR. On lit encore qu'il faudrait couper dans l'asile, du point de vue de l'UDC, sans vraiment prendre en compte qu'en mettant le budget de l'asile à zéro - à zéro, ce qui est parfaitement impossible -, ces 24 milliards ne seraient même pas financés à hauteur d'un sixième. Dit autrement, il faudrait pendant six ans dépenser zéro franc dans le domaine de l'asile pour pouvoir dépenser ces 24 milliards.
+Nous avons déjà fait l'exercice d'un programme d'allègement budgétaire, dont le principal but était de financer l'augmentation ordinaire du budget militaire. Je refuse que l'on doive répéter cet exercice particulièrement violent pour notre population dans le but d'acheter je ne sais pas exactement quoi, en prenant le risque majeur que cet argent soit mal utilisé et, de surcroît, dans un domaine où notre État fait des efforts majeurs.
+Je vous remercie de ne pas entrer en matière.
 </t>
   </si>
 </sst>
@@ -734,8 +899,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I31" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I37" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I37"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -1918,6 +2083,178 @@
         <v>141</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32"/>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
+        <v>150</v>
+      </c>
+      <c r="I33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>157</v>
+      </c>
+      <c r="I35" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>162</v>
+      </c>
+      <c r="I36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" t="s">
+        <v>166</v>
+      </c>
+      <c r="I37" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -68,18 +68,18 @@
   <si>
     <t xml:space="preserve">Die Digitalisierung des Gesundheitswesens ist kein Selbstzweck. Sie soll dazu beitragen, die Behandlungsqualität zu verbessern, die Patientinnensicherheit zu erhöhen und die vorhandenen Ressourcen effizienter einzusetzen.
 Heute sind zwar bereits viele Gesundheitsinformationen digital vorhanden, sie befinden sich aber häufig in unterschiedlichen Systemen und können nicht ohne Weiteres ausgetauscht und weiterverwendet werden. Dies führt zu Doppelspurigkeiten, zusätzlichem administrativem Aufwand und dazu, dass relevante Informationen nicht immer dort verfügbar sind, wo sie für eine Behandlung nötig sind oder der Patient oder die Patientin Zugriff darauf hat.
-Das heutige elektronische Patientendossier (EPD) beruht auf einer komplexen Struktur mit verschiedenen Anbietern und einem aufwendigen Eröffnungsprozess. Diese und weitere Hürden, wie auch die doppelte Freiwilligkeit, haben dazu beigetragen, dass seine Verbreitung und Nutzung deutlich hinter den Erwartungen zurückgeblieben sind - das ist eine diplomatische Ausdrucksweise.
-Mit dem neuen Bundesgesetz über das elektronische Gesundheitsdossier soll deshalb eine grundlegende Neuausrichtung erfolgen: Das EPD wird durch das elektronische Gesundheitsdossier (EGD) abgelöst. Auch Digisanté ist ein wichtiger Pfeiler der Digitalisierung im Gesundheitswesen. - Ich höre mich wegen des Lärms selbst nicht. Das ist schon okay.
+Das heutige elektronische Patientendossier (EPD) beruht auf einer komplexen Struktur mit verschiedenen Anbietern und einem aufwendigen Eröffnungsprozess. Diese und weitere Hürden, wie auch die doppelte Freiwilligkeit, haben dazu beigetragen, dass seine Verbreitung und Nutzung deutlich hinter den Erwartungen zurückgeblieben ist - das ist eine diplomatische Ausdrucksweise.
+Mit dem neuen Bundesgesetz über das elektronische Gesundheitsdossier soll deshalb eine grundlegende Neuausrichtung erfolgen: Das EPD wird durch das elektronische Gesundheitsdossier (E-GD) abgelöst. Auch Digisanté ist ein wichtiger Pfeiler der Digitalisierung im Gesundheitswesen. - Ich höre mich wegen des Lärms selbst nicht. Das ist schon okay.
 An fünf Sitzungen hat Ihre Kommission das Geschäft beraten, zahlreiche Stakeholder angehört und zahlreiche Zusatzberichte eingefordert, um die bestmögliche Entscheidungsgrundlage zu haben. Dies sind nun die Eckwerte:
-1. Es soll automatisch sein für alle. Jede Person mit Wohnsitz in der Schweiz erhält kostenlos ein EGD. Wer keines möchte, kann widersprechen - das ist das sogenannte Opt-out - oder es später löschen lassen. 
+1. Es soll automatisch sein für alle. Jede Person mit Wohnsitz in der Schweiz erhält kostenlos ein E-GD. Wer keines möchte, kann widersprechen - das ist das sogenannte Opt-out - oder es später löschen lassen. 
 2. Alle Leistungserbringenden müssen mitmachen. Neu werden auch ambulante Leistungserbringende wie Ärztinnen und Ärzte, Apotheken, Physiotherapeutinnen und Physiotherapeuten zur Nutzung verpflichtet, sofern sie über die OKP abrechnen. 
-3. Das dritte Kernelement: Relevante Gesundheitsdaten an einem Ort. Verschreibungen von Medikamenten, Laborwerte, Impfungen, Austritts- und Konsultationsberichte - all dies soll digital zugänglich sein. Die Patientinnen und Patienten behalten die Kontrolle, sie bestimmen, wer welche Daten sehen darf. Zudem soll es eine bessere technische Integration geben. Einheitliche Standards ermöglichen die automatische Übertragung aus Praxisinformationssystemen (PIS) und Klinikinformationssystemen (KIS). Damit sollen Doppelspurigkeiten und administrativer Aufwand reduziert werden. Zudem soll das Dossier stärker zentralisiert werden. Dass der Bund die zentrale technische Infrastruktur verantwortet, heisst nicht, dass er sie selbst anbieten muss. Die Kantone verantworten den Betrieb nur noch einer Gemeinschaft. Der Bundesrat liess die Anzahl der Gemeinschaften noch offen; das möchte die Kommission nicht. Damit sollen auch Lehren aus dem EPD gezogen werden, bei welchem in den Stammgemeinschaften doch ziemlich viele Millionen verloren gingen. 
+3. Das dritte Kernelement: relevante Gesundheitsdaten an einem Ort. Verschreibungen von Medikamenten, Laborwerte, Impfungen, Austritts- und Konsultationsberichte - all dies soll digital zugänglich sein. Die Patientinnen und Patienten behalten die Kontrolle, sie bestimmen, wer welche Daten sehen darf. Zudem soll es eine bessere technische Integration geben. Einheitliche Standards ermöglichen die automatische Übertragung aus Praxisinformationssystemen (PIS) und Klinikinformationssystemen (KIS). Damit sollen Doppelspurigkeiten und administrativer Aufwand reduziert werden. Zudem soll das Dossier stärker zentralisiert werden. Dass der Bund die zentrale technische Infrastruktur verantwortet, heisst nicht, dass er sie selbst anbieten muss. Die Kantone verantworten den Betrieb nur noch einer Gemeinschaft. Der Bundesrat liess die Anzahl der Gemeinschaften noch offen; das möchte die Kommission nicht. Damit sollen auch Lehren aus dem EPD gezogen werden, bei welchem in den Stammgemeinschaften doch ziemlich viele Millionen verloren gingen. 
 Zum Datenschutz: Der Bund ist für die Datensicherheit verantwortlich. Die Daten werden in der Schweiz gehalten. Ihre Kommission hat noch zahlreiche Ergänzungen im Bereich des Datenschutzes beschlossen; dazu später mehr. 
 Nach der Vorstellung dieser Eckwerte, die Sie wahrscheinlich gar nicht verstanden haben, weil es hier drin so laut ist, möchte ich nun noch zu den diskutierten Punkten kommen. 
-Zuerst zum Thema Datenschutz: Eine entscheidende Voraussetzung für die Akzeptanz und die erfolgreiche Umsetzung des EGD ist das Vertrauen in den Datenschutz. Die Datensicherheit, die Übermittlung der Daten sowie deren Verschlüsselung wurden sorgfältig geprüft.
+Zuerst zum Thema Datenschutz: Eine entscheidende Voraussetzung für die Akzeptanz und die erfolgreiche Umsetzung des E-GD ist das Vertrauen in den Datenschutz. Die Datensicherheit, die Übermittlung der Daten sowie deren Verschlüsselung wurden sorgfältig geprüft.
 Beim Letzteren hat sich die Kommission insbesondere mit der Frage einer möglichen Ende-zu-Ende-Verschlüsselung auseinandergesetzt. Grundlage dafür war eine Studie der EPFL im Auftrag des Bundesamts für Gesundheit. Angesichts der Tatsache, dass aufgrund technischer Einschränkungen kein anderes öffentliches und nationales System eine strikte Ende-zu-Ende-Verschlüsselung verwendet, ist die Kommission der Auffassung, dass eine solche Lösung nicht im Gesetz verankert werden kann und sollte. Das bedeutet nicht, dass dies nicht umgesetzt werden könnte, falls die Technik es zulassen würde, sondern lediglich, dass wir es nicht im Gesetz verankern möchten. Die Kommission beantragt Ihnen jedoch einstimmig, die Anforderungen an den Datenschutz und die Datensicherheit sowie die Notwendigkeit der Verschlüsselung der Daten ausdrücklich in einem neuen Artikel 5a festzuhalten. Ebenfalls einstimmig beantragt die Kommission die Präzisierung, dass der Bund Daten nur insoweit bearbeiten darf, als dies für den technischen Betrieb des E-GD-Informationssystems erforderlich ist; dies ist in Artikel 5 Absatz 5 geregelt. 
-Schliesslich ist die Kommission ebenfalls einstimmig der Auffassung, dass in Artikel 5 Absatz 8 klargestellt werden soll, dass der Quellcode der eingesetzten Software soweit möglich veröffentlicht werden muss - demgemäss ist sie Open Source - und dass anpassbare, leicht verständliche Berechtigungsprofile zur Verfügung gestellt werden müssen. Die Kommission beantragt alle diese Anpassungen, weil sie der Meinung ist, dass einerseits der Datenschutz eine ganz hohe Priorität hat, es aber andererseits auch praktikabel bleiben muss. Mit dieser Präzisierung soll also der Datenschutz noch stärker gewichtet werden. Für die Kommission ist ebenfalls klar - wir haben das kurz diskutiert -, dass der Datenschutz bei den Primärsystemen, also den Klinik- und den Praxisinformationssystemen, weiterhin eine Schwachstelle im Gesundheitswesen ist. Wir erwarten, dass für Primärsysteme die Mindeststandards gelten; hierzu sollte in den nächsten Monaten auch ein Postulatsbericht folgen.
-Nun komme ich noch zu Digisanté. In einem Bericht liess die Kommission die Abhängigkeit zwischen Digisanté und dem E-GD ausführlich analysieren: sie ist zeitlicher, aber auch inhaltlicher Natur. Auch wenn Digisanté nicht unmittelbar an das E-GD geknüpft ist, gibt es indirekt doch einen Zusammenhang. Damit die Digitalisierung im Gesundheitswesen vorankommt, ist Digisanté unverzichtbar. Gerade die Leistungserbringenden, das möchte ich hier noch betonen, benötigen gemäss ihren Aussagen den Swiss HDS - das ist ein Unterkapitel von Digisanté - lieber früher als später. 
+Schliesslich ist die Kommission ebenfalls einstimmig der Auffassung, dass in Artikel 5 Absatz 8 klargestellt werden soll, dass der Quellcode der eingesetzten Software, soweit möglich, veröffentlicht werden muss - demgemäss ist sie Open Source - und dass anpassbare, leicht verständliche Berechtigungsprofile zur Verfügung gestellt werden müssen. Die Kommission beantragt alle diese Anpassungen, weil sie der Meinung ist, dass einerseits der Datenschutz eine ganz hohe Priorität hat, es aber andererseits auch praktikabel bleiben muss. Mit dieser Präzisierung soll also der Datenschutz noch stärker gewichtet werden. Für die Kommission ist ebenfalls klar - wir haben das kurz diskutiert -, dass der Datenschutz bei den Primärsystemen, also den Klinik- und den Praxisinformationssystemen, weiterhin eine Schwachstelle im Gesundheitswesen ist. Wir erwarten, dass für Primärsysteme die Mindeststandards gelten; hierzu sollte in den nächsten Monaten auch ein Postulatsbericht folgen.
+Nun komme ich noch zu Digisanté. In einem Bericht liess die Kommission die Abhängigkeit zwischen Digisanté und dem E-GD ausführlich analysieren: Sie ist zeitlicher, aber auch inhaltlicher Natur. Auch wenn Digisanté nicht unmittelbar an das E-GD geknüpft ist, gibt es indirekt doch einen Zusammenhang. Damit die Digitalisierung im Gesundheitswesen vorankommt, ist Digisanté unverzichtbar. Gerade die Leistungserbringenden, das möchte ich hier noch betonen, benötigen gemäss ihren Aussagen den Swiss HDS - das ist ein Unterkapitel von Digisanté - lieber früher als später. 
 Weitere Themen waren das EPDG - also das Gesetz, das aktuell gilt, auch wenn es in der Realität nicht umgesetzt wird - und auch der Ausstieg der Post und damit der Wegfall von Sanela ab 2027. Das EPD soll bis zur Einführung des E-GD, so will es die Kommission, weitergeführt werden. Damit soll verhindert werden, dass Lücken beim Betrieb, bei der Finanzierung oder bei den grundlegenden Dienstleistungen entstehen. Der für Ende 2026 vorgesehene Rückzug der Post Sanela Health AG muss so erfolgen, dass eine geordnete Migration zu Cara gewährleistet ist - idealerweise ohne zusätzliche Kosten und ohne Datenverluste.
 </t>
   </si>
@@ -96,15 +96,15 @@
     <t xml:space="preserve">VS</t>
   </si>
   <si>
-    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé" : telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que leur dossier médical n'a pas été transmis ou, parfois, trop tardivement. Il y a nécessité d'agir, et ce, d'autant plus que le dossier électronique du patient (DEP) est resté nettement en deçà des attentes en matière de diffusion et d'utilisation.
-L'objectif majeur reste le même : rendre disponibles les données de santé pertinentes pour améliorer la qualité des soins, renforcer la sécurité des patients et éviter les redondances. C'est le système d'ouverture du dossier qui change pour les patients : il est désormais automatique et gratuit, avec un droit d'opposition, au lieu d'une démarche active. L'idée de base est que, désormais, chaque personne dispose d'un parcours de santé continu, indépendamment du lieu et du fournisseur de prestations. 
-Quels sont les principaux éléments du projet ? Premièrement, le principe de l'"opt-out" a été retenu. Comme je l'ai déjà dit, l'ouverture du dossier ne se fera plus à la demande, comme avec le DEP actuel, mais de manière automatique, avec le maintien du droit d'opposition et la possibilité de suppression ou de restriction des droits d'accès.
+    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé"[NB]: telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Un dossier électronique de santé (DES) sûr et fiable doit permettre de faire progresser la numérisation du système de santé"[NB]: telle est la première phrase du communiqué de notre commission en août dernier au moment de l'adoption du projet de nouvelle loi fédérale sur le dossier électronique de santé. Personne ne conteste la nécessité de numériser un système dans lequel les échanges électroniques d'informations médicales se généralisent. La population est lasse de devoir subir des examens et des traitements à double, parce que leur dossier médical n'a pas été transmis ou, parfois, trop tardivement. Il y a nécessité d'agir, et ce, d'autant plus que le dossier électronique du patient (DEP) est resté nettement en deçà des attentes en matière de diffusion et d'utilisation.
+L'objectif majeur reste le même[NB]: rendre disponibles les données de santé pertinentes pour améliorer la qualité des soins, renforcer la sécurité des patients et éviter les redondances. C'est le système d'ouverture du dossier qui change pour les patients[NB]: il est désormais automatique et gratuit, avec un droit d'opposition, au lieu d'une démarche active. L'idée de base est que, désormais, chaque personne dispose d'un parcours de santé continu, indépendamment du lieu et du fournisseur de prestations. 
+Quels sont les principaux éléments du projet[NB]? Premièrement, le principe de l'"opt-out" a été retenu. Comme je l'ai déjà dit, l'ouverture du dossier ne se fera plus à la demande, comme avec le DEP actuel, mais de manière automatique, avec le maintien du droit d'opposition et la possibilité de suppression ou de restriction des droits d'accès.
 Deuxièmement, dans le but d'une participation généralisée, il est prévu d'étendre l'obligation d'utilisation du dossier électronique de santé aux fournisseurs de prestations. Actuellement, tous les hôpitaux et les établissements de soins sont déjà tenus de se raccorder au dossier électronique du patient. Désormais, les médecins, les pharmaciens ou les physiothérapeutes et d'autres prestataires du domaine ambulatoire qui exercent à la charge de l'assurance obligatoire des soins devront utiliser le dossier électronique de santé et y saisir toutes les données de santé pertinentes pour un traitement médical. Les réticences des professionnels de la santé étaient l'une des principales causes de l'échec du dossier électronique du patient.
 Troisièmement, au lieu de multiples structures décentralisées qui rendaient complexe la mise en oeuvre du dossier électronique du patient, désormais, le projet s'appuie sur une infrastructure centralisée. La commission a en effet décidé à l'unanimité que les cantons devraient se mettre d'accord sur une seule communauté nationale. Pour votre information, le regroupement des différentes communautés de référence a progressé et, depuis que la Poste s'est retirée de l'exploitation du dossier électronique du patient, celui-ci s'oriente déjà vers une communauté unique - fort probablement Cara - dotée d'une infrastructure technique uniforme. La Confédération reste responsable du système d'information.
-Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de ces dernières sur le long terme ; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business, ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites sur le plan des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
+Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de ces dernières sur le long terme[NB]; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business, ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites sur le plan des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
 Cinquièmement, un financement clarifié est nécessaire. Si c'est la Confédération qui finance la mise en place et le développement de l'infrastructure, ce sont les cantons qui assumeront les coûts d'exploitation courants et garantiront l'exploitation de la communauté sur leur territoire. Dans son corapport, la Commission des finances de notre conseil relève que les estimations transmises sont imprécises et peu transparentes, notamment parce que l'on souhaite éviter tout risque d'impact négatif sur l'appel d'offres. Elle recommande ainsi de rester attentif aux conséquences budgétaires que pourraient entrainer d'éventuelles modifications apportées au projet.
 Une condition décisive pour l'acceptation et la mise en oeuvre du DES, et qui a préoccupé notre commission, est la confiance en la protection des données. La sécurité des données, leur transition ainsi que leur chiffrement ont été soigneusement analysés. Concernant ce dernier, la commission s'est penchée sur la question d'un éventuel chiffrement de bout en bout (E2EE), sur la base d'une étude de l'EPFL réalisée à la demande de l'Office fédéral de la santé publique. Prenant acte du fait qu'aucun autre système public ou national n'utilise un chiffrement E2EE strict, en raison d'insuffisances techniques, la commission estime que cette solution ne doit pas être inscrite dans la loi. Elle propose toutefois à l'unanimité que les exigences en matière de protection et de sécurité des données, ainsi que la nécessité de chiffrer les données, soient explicitement mentionnées dans un nouvel article 5a. De plus, la commission propose, à l'unanimité, de préciser que la Confédération ne peut traiter les données personnelles "que dans la mesure où cela est nécessaire au bon fonctionnement technique du système d'information DES". Il s'agit de l'article 5 alinéa 5.
 Enfin, à l'unanimité, la commission considère qu'il convient de préciser que le code source des logiciels utilisés doit être publié, dans la mesure du possible, donc en "open source" - il s'agit de l'article 5 alinéa 8 -, et que des profils d'autorisation adaptables et faciles à comprendre doivent être mis à disposition - article 11 alinéas 5bis et 5ter.
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Besten Dank, ich bin auch dankbar, wenn ich mich selbst verstehe! 
 Ich habe an folgendem Punkt geendet: Wir befinden uns momentan in einer Phase, in der wir aktuell noch ein EPD haben. Das soll auch weiterhin gelten. Der Kommission ist es ein Anliegen, dass das EPD fortgeführt wird, bis das E-GD eingeführt wird, damit es nicht zu Unterbrüchen kommt.
 Der für 2026 vorgesehene Rückzug der Post Sanela Health AG muss so erfolgen, das ist die Meinung der Kommission, dass eine geordnete Migration zu Cara gewährleistet ist. Ich kann Ihnen sagen: 80 000 Dossier sind derzeit bei der Post Sanela Health AG. Da braucht es Lösungen. Die Nachricht, dass die Post aussteigen wird, erreichte die Kommission mitten in der Beratung des Geschäftes. Wir liessen deshalb einen Zusatzbericht anfertigen. Dieser ist aber noch nicht eingetroffen - das war aber auch so geplant. Deshalb bittet Ihre Kommission den Ständerat, sich der Thematik des Anbieters nochmals anzunehmen. Der Ausstieg der Post aus dem EPD könnte auch Auswirkungen auf die Frage der Notwendigkeit einer neuen Ausschreibung haben, was schlussendlich auch zeitliche Konsequenzen haben würde. 
-Die Mehrheit Ihrer Kommission beantragt Ihnen mit 17 zu 8 Stimmen, auf die Vorlage einzutreten. Die Kommissionsmehrheit möchte Ihnen, und wahrscheinlich auch der Bevölkerung, ein Angebot machen, welches ein neues Dossier ermöglicht, das die Schwachstellen des EPD eliminiert. Es ist ein Dossier, wo die Patientinnen und Patienten selbst entscheiden können, wer darauf Zugriff hat, eines, das zentraler gesteuert ist, eines, das nicht die gleichen Fehler wiederholt, die beim EPD gemacht worden sind.
+Die Mehrheit Ihrer Kommission beantragt Ihnen mit 17 zu 8 Stimmen, auf die Vorlage einzutreten. Die Kommissionsmehrheit möchte Ihnen und wahrscheinlich auch der Bevölkerung ein Angebot machen, welches ein neues Dossier ermöglicht, das die Schwachstellen des EPD eliminiert. Es ist ein Dossier, bei dem die Patientinnen und Patienten selbst entscheiden können, wer darauf Zugriff hat, eines, das zentraler gesteuert ist, eines, das nicht die gleichen Fehler wiederholt, die beim EPD gemacht worden sind.
 Ich werde am Schluss noch auf die Minderheiten und den Einzelantrag eingehen. Ich überlasse jetzt gerne das Wort meinem Kommissionssprecher-Kollegen und hoffe, dass Sie ihn verstehen, weil mich haben Sie wahrscheinlich nicht verstanden.
 </t>
   </si>
@@ -170,8 +170,8 @@
     <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. Leur mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion de fin d'année. Les objectifs du Conseil fédéral </t>
   </si>
   <si>
-    <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. Leur mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion de fin d'année. Les objectifs du Conseil fédéral sont coordonnés avec le programme de législature 2023-2027 et les priorités reposent sur quatre lignes directrices : la prospérité, la cohésion, la sécurité et la durabilité. Ces lignes directrices sont subdivisées en 25 objectifs. L'année 2027 sera la quatrième et dernière de la présente législature. Le Conseil fédéral a prévu un total de 140 mesures.
-Je vais aborder maintenant les points forts de l'année à venir et je vais me concentrer sur certaines priorités des quatre lignes directrices. Je commence avec la première ligne directrice, qui est la prospérité. En ce qui concerne la place financière, le Conseil fédéral soumettra un message pour modifier la loi sur les banques. Pour garantir la stabilité financière, il s'agit de renforcer les dispositifs de prévention, de liquidité et de lutte contre les crises. S'agissant des relations avec l'Union européenne, le Conseil fédéral adoptera le message sur le financement d'une participation de la Suisse aux programmes de recherche et d'éducation. Ces fonds visent une participation aux programmes Horizon Europe et Erasmus plus pour les années 2028 à 2034. En matière d'économie, le Conseil fédéral présentera le message sur la promotion économique pour les années 2028 à 2031. Les priorités iront à l'allègement administratif, à la facilitation de l'accès aux marchés internationaux pour les petites et moyennes entreprises, ainsi qu'au renforcement des régions. Par ailleurs, le Conseil fédéral adoptera en 2027 des messages relatifs à la révision partielle de la loi fédérale sur la sécurité des produits et sur les entraves techniques au commerce, renforçant ainsi la protection des consommateurs.
+    <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. Leur mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion de fin d'année. Les objectifs du Conseil fédéral sont coordonnés avec le programme de législature 2023-2027, et les priorités reposent sur quatre lignes directrices[NB]: la prospérité, la cohésion, la sécurité et la durabilité. Ces lignes directrices sont subdivisées en 25 objectifs. L'année 2027 sera la quatrième et dernière de la présente législature. Le Conseil fédéral a prévu un total de 140 mesures.
+Je vais aborder maintenant les points forts de l'année à venir et me concentrer sur certaines priorités des quatre lignes directrices. Je commence avec la première, qui est la prospérité. En ce qui concerne la place financière, le Conseil fédéral soumettra un message pour modifier la loi sur les banques. Pour garantir la stabilité financière, il s'agit de renforcer les dispositifs de prévention, de liquidité et de lutte contre les crises. S'agissant des relations avec l'Union européenne, le Conseil fédéral adoptera le message sur le financement d'une participation de la Suisse aux programmes de recherche et d'éducation. Ces fonds visent une participation aux programmes Horizon Europe et Erasmus plus pour les années 2028 à 2034. En matière d'économie, le Conseil fédéral présentera le message sur la promotion économique pour les années 2028 à 2031. Les priorités iront à l'allègement administratif, à la facilitation de l'accès aux marchés internationaux pour les petites et moyennes entreprises, ainsi qu'au renforcement des régions. Par ailleurs, le Conseil fédéral adoptera en 2027 des messages relatifs à la révision partielle de la loi fédérale sur la sécurité des produits et sur les entraves techniques au commerce, renforçant ainsi la protection des consommateurs.
 De plus, le Conseil fédéral adoptera des messages sur un nouvel accord de libre-échange avec le Vietnam et sur un nouvel accord sur le numérique avec Singapour. 
 Afin de coordonner les développements du rail, de la route et du trafic d'agglomération, le Conseil fédéral adoptera le message intitulé "Transport '45". Son but est de développer le rail, la route et le trafic d'agglomération de manière ciblée et coordonnée afin de répondre aux besoins de mobilité de la population et de l'économie.
 Dans le domaine du numérique, le Conseil fédéral adaptera la loi sur les droits d'auteur aux évolutions de l'intelligence artificielle. Il lancera également une consultation pour l'adhésion à la Convention-cadre du Conseil de l'Europe sur l'intelligence artificielle et les droits de l'homme, la démocratie et l'État de droit.
@@ -179,12 +179,12 @@
 En matière de santé, le Conseil fédéral adoptera le message relatif à une modification de la loi fédérale sur l'assurance-maladie portant sur l'adaptation de la franchise. L'objectif sera de réduire les coûts de la santé, tout en favorisant la responsabilité individuelle des assurés. De plus, il mettra en oeuvre le principe du consentement présumé pour le don d'organes. 
 Dans le cadre de la consultation relative au message concernant l'encouragement de la culture pour la période 2029 à 2032, le Conseil fédéral soumettra à la discussion les orientations stratégiques de la politique fédérale en matière de culture.
 Pour ce qui est du marché du travail, le Conseil fédéral adoptera une stratégie nationale en matière de formation continue, de formation professionnelle et de formation de rattrapage pour favoriser l'entrée ou le retour en emploi.
-Je passe à la troisième ligne directrice : la sécurité.
+Je passe à la troisième ligne directrice[NB]: la sécurité.
 Pour garantir les effectifs de l'armée et de la protection civile, le Conseil fédéral ouvrira une consultation sur l'introduction d'une obligation de servir dans la sécurité. Le projet prévoit de fusionner le service civil et la protection civile au sein d'une nouvelle entité chargée de la protection contre les catastrophes.
 S'agissant de la sécurité, le Conseil fédéral ouvrira la consultation sur une révision des bases légales relatives à la protection des infrastructures critiques. Il s'agira notamment d'améliorer sensiblement l'efficacité de la protection et de clarifier les responsabilités et les procédures.
 En matière de migration, le Conseil fédéral élaborera avec les cantons, les villes et les communes des mesures pour améliorer le système d'asile suisse.
 Sur le plan de la politique extérieure, dans le cadre de la mise en oeuvre de la stratégie de coopération internationale 2025 à 2028, le Conseil fédéral décidera de l'octroi des contributions à l'Agence des Nations Unies pour les réfugiés et au Comité international de la Croix-Rouge pour les années 2027 à 2028.
-J'en viens à la quatrième et dernière ligne directrice : la durabilité.
+J'en viens à la quatrième et dernière ligne directrice[NB]: la durabilité.
 Concernant le climat, le Conseil fédéral présentera la révision de la loi sur le CO2 pour la période 2031 à 2040.
 En matière d'énergie, il adoptera une stratégie nationale sur l'efficacité énergétique qui permettra d'évaluer la consommation d'énergie et le potentiel d'efficacité dans les différents secteurs.
 Pour ce qui est de l'adaptation au changement climatique, le Conseil fédéral adoptera une stratégie "Gestion de l'eau - périodes de sécheresse, fortes précipitations, qualité de l'approvisionnement en eau, protection des habitats aquatiques". Cette stratégie tiendra compte des politiques sectorielles concernées et mettra en évidence, le cas échéant, les adaptations juridiques nécessaires à la réalisation des objectifs.
@@ -207,13 +207,17 @@
     <t xml:space="preserve">NE</t>
   </si>
   <si>
-    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance là où il </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux ; de l'argent et de la surveillance là où il aurait fallu des règles strictes et qui fonctionnent.
-Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation ; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table : l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires, ce qui équivaut à peu près au canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300 000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire qu'il y aurait un doublement de ces émissions. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le : l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne représente pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse et l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres.
-Le deuxième point sur lequel je veux revenir est le travail forcé. La gauche a proposé d'interdire l'importation de marchandises produites au moyen du travail forcé. La commission a malheureusement écarté cette proposition et propose, à la place, comme toujours, un suivi. Or, les observateurs de terrain sont clairs : l'esclavage moderne est une réalité bien présente, par exemple dans les plantations de l'agrobusiness. Sur ce plan également, un suivi ne libère personne.
-Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait : poser des règles contraignantes.Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord fait exactement l'inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs voir ce traité pour ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie : c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 50 000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.</t>
+    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux[NB]; de l'argent et de la surveillance là où </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux[NB]; de l'argent et de la surveillance là où il aurait fallu des règles strictes et qui fonctionnent.
+Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation[NB]; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table[NB]: l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires, ce qui équivaut à peu près au canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300 000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire qu'il y aurait un doublement de ces émissions. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le[NB]: l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne représente pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse et l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres.
+Le deuxième point sur lequel je veux revenir est le travail forcé. La gauche a proposé d'interdire l'importation de marchandises dont la production résulte du travail forcé. La commission a malheureusement écarté cette proposition et propose, à la place, comme toujours, un suivi. Or, les observateurs de terrain sont clairs[NB]: l'esclavage moderne est une réalité bien présente, par exemple dans les plantations de l'agrobusiness. Sur ce plan également, un suivi ne libère personne.
+Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait[NB]: poser des règles contraignantes.
+Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord produit exactement l'effet inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs considérer ce traité comme ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie[NB]: c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.
+J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 50 000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé, parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.
+Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.
+</t>
   </si>
   <si>
     <t xml:space="preserve">418808</t>
@@ -231,10 +235,10 @@
     <t xml:space="preserve">ZH</t>
   </si>
   <si>
-    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen, dass die zweite Schale viel gewichtiger ist und damit also der Sicherheit viel mehr Gewicht zukommt; die Bevölkerung wird mir recht geben.
+    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen, dass die zweite Schale viel gewichtiger ist und damit also der Sicherheit viel mehr Gewicht zukommt; die Bevölkerung wird mir recht geben.
 </t>
   </si>
   <si>
@@ -452,12 +456,12 @@
     <t xml:space="preserve">Rutz Gregor</t>
   </si>
   <si>
-    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen, eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023, im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen, eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023, im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, dass also Leute, die schon in sicheren Staaten leben, dann hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige neue Motive ergänzt. Es gibt eben einen Unterschied zwischen Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
-Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27. Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." Das erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis dann auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist das sicher nicht das Relevante. Trotzdem sagen Sie dann, nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, man staunt dann etwas, die über alle Gesuche 27,5 Prozent Zustimmung ergibt. Also, das sieht dann doch eher nach einer pauschalen Prüfung aus, und wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das hier erhellende Fakten zutage bringt. Dieser Fragebogen liegt oder lag dem Bundesverwaltungsgericht nämlich vor, es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche diese gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen - also Ihr Staatssekretariat, das mit diesen Fragen befasst ist - den eigentlichen Willen des Gesetzgebers, also von uns hier, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhält, würde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiellrechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
-Ich denke, hier müssen Sie, Herr Bundesrat, einmal ganz gründlich aufräumen und wirklich noch einmal über die Bücher gehen. Ich glaube, es geht nicht an, dass Bundesämter arbeiten, ohne sich ans Gesetz zu halten. Sie werden jetzt sagen, dass Sie keine Einzelfälle dokumentieren oder kommentieren. Sie werden sagen, dieses Urteil sei ein Einzelfallurteil. Ja, aber man kann dieses Urteil lesen, und es ist ganz genau dokumentiert und aktenkundig, wie hier korrespondiert wird, wie man mit diesen Einzelfällen umgeht; das geht so nicht. 
+    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, dass also Leute, die schon in sicheren Staaten leben, hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige neue Motive ergänzt und es eben einen Unterschied gibt zwischen Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
+Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27. Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." Es erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist diese Orientierung am EuGH sicher nicht das Relevante. Trotzdem sagen Sie dann, nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, die über alle Gesuche 97,5 Prozent Zustimmung ergibt. Das erstaunt und sieht dann doch eher nach einer pauschalen Prüfung aus. Wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das erhellende Fakten zutage bringt. Dieser Fragebogen lag dem Bundesverwaltungsgericht nämlich vor. Es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche diese gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen - also Ihr Staatssekretariat, das mit diesen Fragen befasst ist - den eigentlichen Willen des Gesetzgebers, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhält, würde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiellrechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
+Hier müssen Sie, Herr Bundesrat, einmal ganz gründlich aufräumen und wirklich noch einmal über die Bücher gehen. Es geht nicht an, dass Bundesämter arbeiten, ohne sich ans Gesetz zu halten. Sie werden jetzt sagen, dass Sie keine Einzelfälle dokumentieren oder kommentieren. Sie werden sagen, dieses Urteil sei ein Einzelfallurteil. Ja, aber man kann dieses Urteil lesen, und es ist ganz genau dokumentiert und aktenkundig, wie hier korrespondiert wird, wie man mit diesen Einzelfällen umgeht. Das geht so nicht. 
 Meine Motion möchte etwas ganz Einfaches: erstens, dass man sich im Staatssekretariat für Migration ans Gesetz hält, und zweitens, dass man diese Praxisänderung, die offensichtlich gesetzeswidrig ist, rückgängig macht und die Fälle einzeln prüft, damit diejenigen Leute Schutz und Aufnahme erhalten, die es nötig haben und nicht die ganze Welt eingeladen wird, in die Schweiz zu kommen. 
 Darum bitte ich Sie hier um Zustimmung.
 </t>
@@ -508,7 +512,7 @@
   </si>
   <si>
     <t xml:space="preserve">Ich muss zuerst im Rahmen einer persönlichen Erklärung etwas berichtigen, weil mich Herr Bundesrat Jans falsch zitiert hat. Ich habe nie davon gesprochen, dass der Abschreibungsentscheid des Bundesverwaltungsgerichts vom 20. November 2025 oder auch die anderen von mir zitierten Urteile des Bundesverwaltungsgerichts Leitentscheide gewesen seien oder eine Änderung oder Weiterentwicklung der Rechtsprechung bewirkt hätten. Im Gegenteil, ich habe gesagt, dass das Bundesverwaltungsgericht seine Praxis immer bestätigt hat. Und wenn der Autor Ihrer Notiz die Debatten der letzten Jahre aufmerksam gelesen hätte, hätte er gemerkt, dass ich auch schon 2023 und 2024 genau gleich argumentiert habe. 
-Vor diesem Hintergrund nun zu meiner Frage, Herr Bundesrat Jans: Das Bundesverwaltungsgericht schreibt in diesem zitierten Entscheid, ein Fragebogen sei für eine Einzelfallprüfung ungeeignet und das Staatssekretariat für Migration schüre Erwartungen - und diese Korrespondenz, die mit verfahrensrechtlichen und materiell rechtlichen Vorgaben des Asylgesetzes nicht vereinbar sei, ist ja dokumentiert. Wie um Himmels Willen kommen Sie dann dazu, zu schreiben, es liege kein Urteil des Bundesverfassungsgerichts vor, welches die Asylpraxis gegenüber afghanischen Frauen kritisiert oder infrage stellt? Herr Bundesrat Jans, gelten gewisse Gerichtsurteile für den Justizminister nicht, wenn er es besser zu wissen glaubt, oder gelten diese Gerichtsurteile auch für den Justizminister?
+Vor diesem Hintergrund nun zu meiner Frage, Herr Bundesrat Jans: Das Bundesverwaltungsgericht schreibt in diesem zitierten Entscheid, ein Fragebogen sei für eine Einzelfallprüfung ungeeignet und das Staatssekretariat für Migration schüre Erwartungen, die mit verfahrensrechtlichen und materiell rechtlichen Vorgaben des Asylgesetzes nicht vereinbar seien; diese Korrespondenz ist dokumentiert. Wie um Himmels Willen kommen Sie dann dazu, zu schreiben, es liege kein Urteil des Bundesverwaltungsgerichts vor, welches die Asylpraxis gegenüber afghanischen Frauen kritisiert oder infrage stellt? Herr Bundesrat Jans, gelten gewisse Gerichtsurteile für den Justizminister nicht, wenn er es besser zu wissen glaubt, oder gelten diese Gerichtsurteile auch für den Justizminister?
 </t>
   </si>
   <si>
@@ -738,12 +742,12 @@
 Antrag SGK-S [GZ]
 Die Motionen 19.3957 und 19.4120 nicht abschreiben
 Schriftliche Begründung [GZ]
-Die Kommission beantragt, die Motionen nicht abzuschreiben, da deren Forderung nach einer sachgerechten Vergütung der Kinder- und Jugendmedizin noch nicht erfüllt ist. Sie stellt zwar fest, dass die stationären und ambulanten Tarife im Bereich der Kinder- und Jugendmedizin weiterentwickelt wurden und diesem Bereich auch bei der zukünftigen Weiterentwicklung ein besonderes Gewicht zukommt. Es bestehen aber weiterhin Herausforderungen, die Besonderheiten der Kinder- und Jugendmedizin sachgerecht in den Tarifen abzubilden. Zudem wurde das neue Gesamttarifsystem bestehend aus TARDOC und Ambulanten Pauschalen erst per 2026 eingeführt. Entsprechend kann aus Sicht der Kommission noch nicht beurteilt werden, inwiefern im ambulanten Bereich Verbesserungen erzielt worden sind.
+Die Kommission beantragt, die Motionen nicht abzuschreiben, da deren Forderung nach einer sachgerechten Vergütung der Kinder- und Jugendmedizin noch nicht erfüllt ist. Sie stellt zwar fest, dass die stationären und ambulanten Tarife im Bereich der Kinder- und Jugendmedizin weiterentwickelt wurden und diesem Bereich auch bei der zukünftigen Weiterentwicklung ein besonderes Gewicht zukommt. Es bestehen aber weiterhin Herausforderungen, die Besonderheiten der Kinder- und Jugendmedizin sachgerecht in den Tarifen abzubilden. Zudem wurde das neue Gesamttarifsystem bestehend aus Tardoc und ambulanten Pauschalen erst per 2026 eingeführt. Entsprechend kann aus Sicht der Kommission noch nicht beurteilt werden, inwiefern im ambulanten Bereich Verbesserungen erzielt worden sind.
 [VS]
 Proposition CSSS-E [GZ]
 Ne pas classer les motions 19.3957 et 19.4120
 Développement par écrit [GZ]
-La commission propose de ne pas classer les motions au motif que l'objectif qu'elles visent, à savoir garantir une rémunération adéquate de la médecine pédiatrique, n'est pas encore atteint. Elle constate certes que les tarifs stationnaires et ambulatoires dans le domaine de la médecine pédiatrique ont été revus et que ce domaine continuera à revêtir une importance particulière dans le cadre des développements futurs. Il reste toutefois des défis à relever pour refléter de manière adéquate, dans les tarifs, les spécificités de la médecine pédiatrique. De plus, le nouveau système tarifaire global composé de TARDOC et des forfaits ambulatoires n'a été mis en place qu'à partir de 2026. En conséquence, la commission estime qu'il n'est pas encore possible d'évaluer dans quelle mesure des améliorations ont été réalisées dans le domaine des soins ambulatoires.
+La commission propose de ne pas classer les motions au motif que l'objectif qu'elles visent, à savoir garantir une rémunération adéquate de la médecine pédiatrique, n'est pas encore atteint. Elle constate certes que les tarifs stationnaires et ambulatoires dans le domaine de la médecine pédiatrique ont été revus et que ce domaine continuera à revêtir une importance particulière dans le cadre des développements futurs. Il reste toutefois des défis à relever pour refléter de manière adéquate, dans les tarifs, les spécificités de la médecine pédiatrique. De plus, le nouveau système tarifaire global composé de Tardoc et des forfaits ambulatoires n'a été mis en place qu'à partir de 2026. En conséquence, la commission estime qu'il n'est pas encore possible d'évaluer dans quelle mesure des améliorations ont été réalisées dans le domaine des soins ambulatoires.
 [VS]
 Präsident (Engler Stefan, Präsident): Der Bundesrat ist mit der Nichtabschreibung der beiden Motionen einverstanden.[GZ]
 [VS][GZ]
@@ -752,16 +756,12 @@
 Antrag UREK-S [GZ]
 Die Motion 21.4318 nicht abschreiben
 Schriftliche Begründung [GZ]
-Mit der Motion wird der Bundesrat beauftragt, alle erneuerbare Gase von der CO2-Abgabe zu befreien.
-In der letzten Revision des CO2-Gesetzes wurden Erleichterungen für Kundinnen und Kunden aus der Industrie, die erneuerbare Gase konsumieren, eingeführt. So kann den Konsumenten die CO2-Abgabe zurückerstattet werden, wenn sie entweder am Emissionshandelssystem teilnehmen oder Verminderungsverpflichtungen eingehen. Zudem müssen sie im Emissionshandelssystem für ihr virtuell importiertes erneuerbares Gas keine Emissionsrechte abgeben. Gleichermassen können sich Unternehmen mit Verminderungsverpflichtungen das virtuell importierte erneuerbare Gas ihrer Emissionsverminderung anrechnen lassen. Der Bundesrat argumentiert deshalb, dass das Anliegen der Motion erfüllt ist, und beantragt deren Abschreibung.
-Die Kommission erachtet jedoch die Motion als nur teilweise erfüllt, da ausschliesslich Konsumenten von erneuerbaren Gasen aus der Industrie von der Befreiung der CO2-Abgabe profitieren. Nach Ansicht der Kommission soll die Abgabe-Befreiung für alle Kundinnen und Kunden gleichermassen gelten und damit auch für erneuerbare Gase, die zum Heizen genutzt werden. Dies, so unterstreicht die Kommission, soll der Bundesrat in der nächsten Revision des CO2-Gesetzes berücksichtigen, weshalb sie beantragt, die Motion nicht abzuschreiben.
+Mit der Motion wird der Bundesrat beauftragt, alle erneuerbare Gase von der CO2-Abgabe zu befreien. In der letzten Revision des CO2-Gesetzes wurden Erleichterungen für Kundinnen und Kunden aus der Industrie, die erneuerbare Gase konsumieren, eingeführt. So kann den Konsumenten die CO2-Abgabe zurückerstattet werden, wenn sie entweder am Emissionshandelssystem teilnehmen oder Verminderungsverpflichtungen eingehen. Zudem müssen sie im Emissionshandelssystem für ihr virtuell importiertes erneuerbares Gas keine Emissionsrechte abgeben. Gleichermassen können sich Unternehmen mit Verminderungsverpflichtungen das virtuell importierte erneuerbare Gas ihrer Emissionsverminderung anrechnen lassen. Der Bundesrat argumentiert deshalb, dass das Anliegen der Motion erfüllt ist, und beantragt deren Abschreibung. Die Kommission erachtet jedoch die Motion als nur teilweise erfüllt, da ausschliesslich Konsumenten von erneuerbaren Gasen aus der Industrie von der Befreiung der CO2-Abgabe profitieren. Nach Ansicht der Kommission soll die Abgabenbefreiung für alle Kundinnen und Kunden gleichermassen gelten und damit auch für erneuerbare Gase, die zum Heizen genutzt werden. Dies, so unterstreicht die Kommission, soll der Bundesrat in der nächsten Revision des CO2-Gesetzes berücksichtigen, weshalb sie beantragt, die Motion nicht abzuschreiben.
 [VS]
 Proposition CEATE-E [GZ]
 Ne pas classer la motion 21.4318
 Développement par écrit [GZ]
-La motion charge le Conseil fédéral d'exonérer tous les gaz renouvelables de la taxe sur le CO2.
-Lors de la dernière révision de la loi sur le CO2, des allègements ont été introduits en faveur des clients industriels qui consomment des gaz renouvelables. Ainsi, la taxe sur le CO2 peut être remboursée aux consommateurs s'ils participent au système d'échange de quotas d'émission ou s'ils souscrivent à des engagements de réduction. De plus, dans le cadre du système d'échange de quotas d'émission, ils ne sont pas tenus de remettre des droits d'émission pour le gaz renouvelable qu'ils importent virtuellement. De même, les entreprises ayant souscrit à des engagements de réduction peuvent faire valoir le gaz renouvelable importé virtuellement dans le cadre de leur réduction d'émissions. Le Conseil fédéral estime donc que l'objectif de la motion est atteint et propose de classer cette dernière.
-La commission considère toutefois que l'objectif de la motion n'est que partiellement atteint, car seuls les consommateurs issus de l'industrie bénéficient de l'exonération de la taxe sur le CO2. Elle estime que l'exonération devrait s'appliquer à tous les clients de la même manière, y compris pour les gaz renouvelables utilisés pour le chauffage. Finalement, elle souligne que le Conseil fédéral devrait en tenir compte lors de la prochaine révision de la loi sur le CO2, raison pour laquelle elle propose de ne pas classer la motion.[GZ]
+La motion charge le Conseil fédéral d'exonérer tous les gaz renouvelables de la taxe sur le CO2. Lors de la dernière révision de la loi sur le CO2, des allègements ont été introduits en faveur des clients industriels qui consomment des gaz renouvelables. Ainsi, la taxe sur le CO2 peut être remboursée aux consommateurs s'ils participent au système d'échange de quotas d'émission ou s'ils souscrivent à des engagements de réduction. De plus, dans le cadre du système d'échange de quotas d'émission, ils ne sont pas tenus de remettre des droits d'émission pour le gaz renouvelable qu'ils importent virtuellement. De même, les entreprises ayant souscrit à des engagements de réduction peuvent faire valoir le gaz renouvelable importé virtuellement dans le cadre de leur réduction d'émissions. Le Conseil fédéral estime donc que l'objectif de la motion est atteint et propose de classer cette dernière. La commission considère toutefois que l'objectif de la motion n'est que partiellement atteint, car seuls les consommateurs issus de l'industrie bénéficient de l'exonération de la taxe sur le CO2. Elle estime que l'exonération devrait s'appliquer à tous les clients de la même manière, y compris pour les gaz renouvelables utilisés pour le chauffage. Finalement, elle souligne que le Conseil fédéral devrait en tenir compte lors de la prochaine révision de la loi sur le CO2, raison pour laquelle elle propose de ne pas classer la motion.[GZ]
 [VS][GZ]
 Präsident (Engler Stefan, Präsident): Der Bundesrat ist mit der Nichtabschreibung einverstanden.[GZ]
 [VS][GZ]
@@ -769,22 +769,21 @@
 [VS]
 Antrag der Mehrheit SPK-S [GZ]
 Die Motionen 24.3035 und 24.3022 abschreiben
+Schriftliche Begründung [GZ]
+Die Kommissionsmehrheit befürwortet den Antrag des Bundesrates auf Abschreibung der Motionen. Sie hält fest, dass diese durch die Praxisänderungen weitgehend umgesetzt wurden. Die Minderheit ist der Ansicht, dass die Motionen nicht abgeschrieben werden sollten, da die Situation in der Praxis nach wie vor unzufriedenstellend sei. So würden Personen mit Schutzstatus S mehrfach aus der Schweiz aus- und wieder einreisen und damit die Gemeinden, in denen sie ansässig sind, vor grosse Schwierigkeiten stellen.
 [VS]
 Antrag der Minderheit SPK-S [GZ]
 (Friedli Esther, Chiesa, Fässler Daniel, Gössi, Häberli-Koller)[GZ]
 Die Motionen 24.3035 und 24.3022 nicht abschreiben
-Schriftliche Begründung [GZ]
-Die Kommissionsmehrheit befürwortet den Antrag des Bundesrates auf Abschreibung der Motionen. Sie hält fest, dass diese durch die Praxisänderungen weitgehend umgesetzt wurden.
-Die Minderheit ist der Ansicht, dass die Motionen nicht abgeschrieben werden sollten, da die Situation in der Praxis nach wie vor unzufriedenstellend sei. So würden Personen mit Schutzstatus S mehrfach aus der Schweiz aus- und wieder einreisen und damit die Gemeinden, in denen sie ansässig sind, vor grosse Schwierigkeiten stellen.
 [VS]
 Proposition de la majorité CIP-E [GZ]
 Classer les motions 24.3035 et 24.3022
+Développement par écrit [GZ]
+La commission soutient la proposition du Conseil fédéral de classer les motions. Elle constate que ces dernières ont été largement mises en oeuvre via des changements de pratique. La minorité est d'avis que les motions ne doivent pas être classées car la réalité du terrain reste insatisfaisante, avec des bénéficiaires de statut S qui, à plusieurs reprises, quittent la Suisse puis reviennent, causant des difficultés aux communes qui les accueillent.
 [VS]
 Proposition de la minorité CIP-E [GZ]
 (Friedli Esther, Chiesa, Fässler Daniel, Gössi, Häberli-Koller)[GZ]
 Ne pas classer les motions 24.3035 et 24.3022
-Développement par écrit [GZ]
-La commission soutient la proposition du Conseil fédéral de classer les motions. Elle constate que ces dernières ont été largement mises en oeuvre via des changements de pratique. La minorité est d'avis que les motions ne doivent pas être classées car la réalité du terrain reste insatisfaisante, avec des bénéficiaires de statut S qui, à plusieurs reprises, quittent la Suisse puis reviennent, causant des difficultés aux communes qui les accueillent.
 </t>
   </si>
   <si>
@@ -851,6 +850,264 @@
 Alors, quel est le but de cet exercice ? Il est simple, politiquement : il s'agit de financer autrement ces 24 milliards. Si c'est de la manière dont la Commission des finances l'a pensé, on peut en discuter. J'ai aussi consulté les déclarations des partis politiques avant la session, qui invitent à une grande prudence. On lit par exemple qu'il faut couper 25 pour cent ou plus des dépenses de la coopération internationale - que nous avons déjà largement diminué ces dernières années - et vendre Swisscom, en renonçant au passage à plus d'un demi-milliard de dividendes - selon le PLR. On lit encore qu'il faudrait couper dans l'asile, du point de vue de l'UDC, sans vraiment prendre en compte qu'en mettant le budget de l'asile à zéro - à zéro, ce qui est parfaitement impossible -, ces 24 milliards ne seraient même pas financés à hauteur d'un sixième. Dit autrement, il faudrait pendant six ans dépenser zéro franc dans le domaine de l'asile pour pouvoir dépenser ces 24 milliards.
 Nous avons déjà fait l'exercice d'un programme d'allègement budgétaire, dont le principal but était de financer l'augmentation ordinaire du budget militaire. Je refuse que l'on doive répéter cet exercice particulièrement violent pour notre population dans le but d'acheter je ne sais pas exactement quoi, en prenant le risque majeur que cet argent soit mal utilisé et, de surcroît, dans un domaine où notre État fait des efforts majeurs.
 Je vous remercie de ne pas entrer en matière.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doch, dieser Meinung sind wir, geschätzter Herr Schilliger - danke für die Frage. Wir sind daran, die Motion Salzmann umzusetzen, die genau das verlangt: ein Konzept des Bundesrates, wie er die Rückführungen im weitesten Sinne optimieren sowie effizienter und schneller durchführen kann. Da sind wir dran, das machen wir auch im Rahmen der Asylstrategie zusammen mit den zuständigen Kantonen, Gemeinden und Städten, da sie dann vollziehen und umsetzen müssen. Sie verfügen über die polizeilichen Behö</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doch, dieser Meinung sind wir, geschätzter Herr Schilliger - danke für die Frage. Wir sind daran, die Motion Salzmann umzusetzen, die genau das verlangt: ein Konzept des Bundesrates, wie er die Rückführungen im weitesten Sinne optimieren sowie effizienter und schneller durchführen kann. Da sind wir dran, das machen wir auch im Rahmen der Asylstrategie zusammen mit den zuständigen Kantonen, Gemeinden und Städten, da sie dann vollziehen und umsetzen müssen. Sie verfügen über die polizeilichen Behörden und Kompetenzen, um das zu tun. Mit ihnen zusammen werden wir Lösungen suchen. Das Ziel bleibt für uns - es ist völlig klar, dass es schneller gehen könnte -, dass wir in diesem Bereich weitere Fortschritte machen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuerst muss ich etwas klären: Sie entscheiden bei dieser Motion nicht darüber, ob der Wegweisungsvollzug weiter optimiert und effizienter gemacht wird oder ob es mehr Rückweisungen geben wird. Nein, das wollen alle. Sie entscheiden lediglich darüber, ob der Bund eine kantonale Kompetenz an sich ziehen soll - und das, bevor eine brauchbare Lagebeschreibung, ein offensichtlicher Handlungsbedarf oder die zusätzlichen Kosten bekannt wären.
+Die gesetzlichen Grundlagen sind klar: Die Kantone sind verp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuerst muss ich etwas klären: Sie entscheiden bei dieser Motion nicht darüber, ob der Wegweisungsvollzug weiter optimiert und effizienter gemacht wird oder ob es mehr Rückweisungen geben wird. Nein, das wollen alle. Sie entscheiden lediglich darüber, ob der Bund eine kantonale Kompetenz an sich ziehen soll - und das, bevor eine brauchbare Lagebeschreibung, ein offensichtlicher Handlungsbedarf oder die zusätzlichen Kosten bekannt wären.
+Die gesetzlichen Grundlagen sind klar: Die Kantone sind verpflichtet, Wegweisungen und Landesverweisungen zu vollziehen. Schon heute ist es gemäss Ausländer- und Integrationsgesetz möglich, dass ein anderer Kanton den Vollzug übernimmt. Gewisse Kantone machen davon Gebrauch. Die Kantone regeln die Entschädigung für diese sogenannte Amtshilfe. Gleichzeitig verfügen wir heute schon über ein Anreizsystem, um die Kantone zum Vollzug zu bewegen. Einerseits haben die Kantone ein finanzielles Eigeninteresse an einem effizienten Vollzug. Jede vollzogene Wegweisung oder Landesverweisung reduziert die Kosten, die sie wegen dem Aufenthalt der betroffenen Person tragen müssen. Andererseits kann der Bund finanzielle Sanktionen ergreifen, wenn die Kantone ihre Vollzugsaufgaben im Asylbereich nicht oder nur ungenügend erfüllen. In diesen Fällen ordnet das SEM einen Subventionsstopp an.
+Im Wegweisungsvollzug haben wir genügend Anreize, die eine einheitliche Umsetzung des Bundesrechts fördern. Der Bund soll den Kantonen für eine klar geregelte gesetzliche Pflicht keine zusätzlichen finanziellen Mittel oder Entschädigungen zahlen, die über die bestehenden Pauschalen hinausgehen. Das ist weder nachhaltig noch sachlich gerechtfertigt. Angesichts der angespannten Finanzlage des Bundes ist eine solche zusätzliche Finanzhilfe auch nicht angezeigt.
+Mit der geforderten flexiblen Zuständigkeitsregelung würde der Bund erheblich in die Souveränität der Kantone eingreifen. Zudem ist unklar, wie die geforderte Regelung in der Praxis funktionieren soll. Kantonale Polizeibehörden fahnden grundsätzlich nicht eigenmächtig und ohne Absprache im Hoheitsgebiet eines anderen Kantons nach Personen, um diese festzunehmen. Sie tun dies nur, wenn eine Person flüchtet oder bei Gefahr im Verzug. Ansonsten arbeiten die kantonalen Polizeibehörden im Rahmen der Amtshilfe zusammen. Das ist auch beim Vollzug der Wegweisungen bereits heute möglich.
+Der Bundesrat unterstützt zwar das Bestreben des Motionärs, den Wegweisungsvollzug weiter zu optimieren und effizienter zu machen. Diese Motion stellt aber keine Lösung dar. Konkrete Massnahmen werden derzeit im Rahmen der Umsetzung der Motion Salzmann 23.3082 ausgearbeitet. Der Bundesrat legt das gewünschte Konzept voraussichtlich bis Ende Jahr vor.
+Vor diesem Hintergrund lehnt der Bundesrat, wie die vorberatende Kommission Ihres Rates, diese Motion ab.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auch hier stehe ich bei der Abstimmung wahrscheinlich wieder alleine da. Der Bundesrat kann jedoch - dies ist eine wichtige Botschaft - das Kernanliegen der Motion der GPK-S gut nachvollziehen: Nur wenn geschäftsrelevante Unterlagen korrekt abgelegt und aufbewahrt werden, ist das Verwaltungshandeln nachvollziehbar. Transparenz über die Tätigkeit der Bundesverwaltung ist wichtig, um das Vertrauen in den Staat und die Akzeptanz staatlichen Handelns zu stärken.
+Nach Ansicht des Bundesrates ist die </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auch hier stehe ich bei der Abstimmung wahrscheinlich wieder alleine da. Der Bundesrat kann jedoch - dies ist eine wichtige Botschaft - das Kernanliegen der Motion der GPK-S gut nachvollziehen: Nur wenn geschäftsrelevante Unterlagen korrekt abgelegt und aufbewahrt werden, ist das Verwaltungshandeln nachvollziehbar. Transparenz über die Tätigkeit der Bundesverwaltung ist wichtig, um das Vertrauen in den Staat und die Akzeptanz staatlichen Handelns zu stärken.
+Nach Ansicht des Bundesrates ist die in der Motion vorgeschlagene Verlängerung des Zugriffes auf inaktive Mailaccounts des Bundes jedoch keine zweckmässige Lösung. Einerseits wäre der Nutzen einer längerfristigen Zugriffs- und Aufbewahrungsfrist nur sehr begrenzt, da alle geschäftsrelevanten Informationen ohnehin fortlaufend aus den Mailaccounts in das elektronische Geschäftsverwaltungssystem überführt und dort bearbeitet werden müssen. Die restlichen Informationen in den Mailaccounts werden als nicht geschäftsrelevant betrachtet; jede Verwaltungseinheit muss hierzu Organisationsvorschriften erlassen und deren Einhaltung regelmässig kontrollieren.
+Andererseits stehen datenschutzrechtliche, technische sowie finanzielle Gründe einer längeren Aufbewahrungsfrist entgegen. Der im Datenschutzgesetz verankerte Grundsatz der Verhältnismässigkeit verlangt, dass Personendaten nicht länger als unbedingt erforderlich aufbewahrt werden dürfen. Zudem erfordert eine längere Aufbewahrungsdauer zusätzliche Speicherkapazitäten und erhöht das Risiko von Überschneidungen bei der Datenspeicherung. Der damit verbundene Personalaufwand sowie die Kosten für den Speicherplatz würden beachtliche Finanzmittel erfordern. Kurz gesagt stehen Kosten und Nutzen eines längeren Zugriffes auf inaktive Mailaccounts des Bundes in keinem sinnvollen Verhältnis.
+Ich erlaube mir hier noch eine Bemerkung anzufügen: In jeder Session verlasse ich die Sitzungen beider Räte mit zusätzlichen Kosten und Aufträgen - jedes Mal. Ich möchte dies hier festhalten. Mit dem Entlastungspaket verlangen Sie viel von uns; allein das SEM musste in den letzten zwei Jahren 150 Personen entlassen. Wir setzen dies um, da wir effizienter werden wollen. Dennoch werden uns jedes Mal zusätzliche Kosten aufgebürdet, was auch hier der Fall ist. Diese Beobachtung wollte ich anbringen und werde sie mir künftig angewöhnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion Maret Marianne 25.4556 fordert vom Bundesrat ein Rahmengesetz zur Verhinderung und zum Schutz vor häuslicher Gewalt, das Prävention, Opferschutz und Ahndung einheitlich regeln soll. Der Ständerat hat den Vorstoss im März klar angenommen; auch Ihre Kommission für Rechtsfragen hat die Motion im Juli mit einer Präzisierung angenommen.
+Der Bundesrat unterstützt die Motion. Die Bekämpfung häuslicher Gewalt ist eine Priorität des Bundesrates, weshalb er sein Engagement in diesem Bereich ver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion Maret Marianne 25.4556 fordert vom Bundesrat ein Rahmengesetz zur Verhinderung und zum Schutz vor häuslicher Gewalt, das Prävention, Opferschutz und Ahndung einheitlich regeln soll. Der Ständerat hat den Vorstoss im März klar angenommen; auch Ihre Kommission für Rechtsfragen hat die Motion im Juli mit einer Präzisierung angenommen.
+Der Bundesrat unterstützt die Motion. Die Bekämpfung häuslicher Gewalt ist eine Priorität des Bundesrates, weshalb er sein Engagement in diesem Bereich verstärkt hat. So arbeitet mein Departement gemeinsam mit dem Eidgenössischen Departement des Innern, den Kantonen, Gemeinden und Städten zurzeit an einer nationalen Strategie gegen häusliche, sexualisierte und geschlechtsbezogene Gewalt. Die Zivilgesellschaft wird ebenfalls eng in die Arbeiten einbezogen.
+Im Ständerat wurden die kantonalen Unterschiede beim Schutz vor häuslicher Gewalt thematisiert, da Opfer nicht überall in der Schweiz denselben Schutz erhalten und deshalb nationale Mindeststandards nötig seien. Dies würde zudem zu einer besseren Koordination zwischen Bund und Kantonen führen. Der Bundesrat teilt diese Ansicht. Die hohe Zahl der Femizide des letzten Jahres sowie die generelle Zunahme von Fällen häuslicher und sexueller Gewalt zeigen, dass der Schutz der Opfer dringend verbessert werden muss. Ein nationales Rahmengesetz kann hier helfen.
+Der Bundesrat hat darauf hingewiesen, dass für die Umsetzung der vorliegenden Motion eine Verfassungsänderung nötig ist. Lassen Sie mich das erläutern: Sowohl dem Bund als auch den Kantonen kommen Kompetenzen im Bereich des Schutzes vor häuslicher Gewalt zu. Der Bund besitzt Gesetzgebungskompetenzen im Zivil-, Straf- und Opferhilferecht. Die Kantone sind hingegen für den Vollzug zuständig, insbesondere für polizeiliche Wegweisungen, Annäherungsregionen, Kontaktverbote sowie das Bedrohungsmanagement. In Fällen häuslicher Gewalt kann die Polizei vor Ort unmittelbar Gefahren abwehren; auch die Prävention ist grösstenteils Aufgabe der Kantone.
+Nach Ansicht des Bundesrates sollte ein nationales Rahmengesetz Minimalstandards in sämtlichen Bereichen des Gewaltschutzes umfassen. Da die Kantone jedoch für zentrale Aufgaben, wie polizeiliche Schutzmassnahmen oder das Bedrohungsmanagement, zuständig sind, ist für die Umsetzung der Motion eine Verfassungsänderung nötig.
+Die Kantone haben in den letzten Jahren bei der Bekämpfung häuslicher Gewalt wichtige Arbeit geleistet; sie analysieren derzeit die kantonalen Rechtsgrundlagen und beabsichtigen, diese noch stärker zu harmonisieren. An diese Arbeiten wollen wir anknüpfen. Bei einer Annahme der Motion wird der Bundesrat die Kantone von Beginn an eng einbeziehen und gemeinsam mit ihnen prüfen, welche Kompetenzen beim Bund angesiedelt werden sollen und wofür eine Verfassungsänderung erforderlich ist.
+Am 3. Juli 2026 hat sich Ihre Kommission für Rechtsfragen mit der vorliegenden Motion befasst und sie angenommen. Dabei hat sie auch einem Antrag zugestimmt, der die Präzisierung fordert, dass der Bundesrat ein Rahmengesetz nicht nur zum Schutz vor häuslicher, sondern auch vor sexualisierter und geschlechtsbezogener Gewalt vorlegen soll. Eine solche Änderung kostet zwar Zeit, da das Geschäft nochmals in den Ständerat geht, entscheidend ist jedoch, dass diese Motion die nachfolgenden Arbeiten tatsächlich erleichtert.
+Daraus lässt sich schliessen, dass Sie für die Umsetzung ein umfassendes Gewaltverständnis anstreben. Die Änderung passt zur künftigen nationalen Strategie, wie bereits erwähnt, da sie genau diese drei Gewaltformen umfassen wird. Sie ist daher aus Sicht des Bundesrates zu begrüssen.
+Aus den eingangs genannten Gründen beantragt Ihnen der Bundesrat, die Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Häusliche Gewalt ist inakzeptabel. Der Bundesrat nimmt den Kampf dagegen sehr ernst. Deshalb unterstützt er das Anliegen der Motionärin und beantragt, die Motion anzunehmen und der Mehrheit der Kommission zu folgen.
+Dies ist eine von vielen Massnahmen und Stossrichtungen, die der Bundesrat anstrebt. Sie fügt sich in die Strategie des Bundesrates ein. Die Arbeiten an einer gemeinsamen nationalen Strategie gegen häusliche Gewalt wurden am 5. Februar 2026 lanciert. Diese führt die bisherigen Instru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Häusliche Gewalt ist inakzeptabel. Der Bundesrat nimmt den Kampf dagegen sehr ernst. Deshalb unterstützt er das Anliegen der Motionärin und beantragt, die Motion anzunehmen und der Mehrheit der Kommission zu folgen.
+Dies ist eine von vielen Massnahmen und Stossrichtungen, die der Bundesrat anstrebt. Sie fügt sich in die Strategie des Bundesrates ein. Die Arbeiten an einer gemeinsamen nationalen Strategie gegen häusliche Gewalt wurden am 5. Februar 2026 lanciert. Diese führt die bisherigen Instrumente zusammen, namentlich die Roadmap zur Bekämpfung von häuslicher Gewalt unter Federführung meines Departementes sowie den Nationalen Aktionsplan 2022-2026 zur Umsetzung der Istanbul-Konvention unter Leitung des Eidgenössischen Departementes des Innern.
+Die Strategie bündelt die bisherigen Massnahmen, sie beinhaltet auch Massnahmen, um ausländische Personen für das Thema häusliche Gewalt zu sensibilisieren. Dabei geht es vor allem darum, warum häusliche Gewalt entsteht, welche Folgen sie hat und welche rechtlichen Konsequenzen sich daraus ergeben.
+Zum Anliegen der Motion: Im Ausländer- und Integrationsgesetz sowie im Bürgerrechtsgesetz sind die Integrationskriterien geregelt. Die zuständigen Behörden berücksichtigen sie, wenn sie ausländerrechtliche Bewilligungen erteilen oder verlängern, und sie kommen auch im Einbürgerungsverfahren zur Anwendung. Integrationskriterien betreffen unter anderem die Frage, ob jemand die öffentliche Sicherheit und Ordnung beachtet oder die Werte der Bundesverfassung respektiert. Das bedeutet auch, dass nur als integriert gelten kann, wer Gewalt ablehnt.
+Wie gesagt, der Bundesrat findet es wichtig, häusliche Gewalt zu bekämpfen. Darum befürwortet er es, dass im Gesetz die Ablehnung häuslicher Gewalt als spezifisches Integrationskriterium festgehalten wird. Der Bundesrat misst den vier bisherigen Integrationskriterien im Gesetz grosse Bedeutung zu, und er wird die neue Bestimmung auf Verordnungsstufe weiter konkretisieren.
+In diesem Sinne beantragt Ihnen der Bundesrat, die Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paganini Nicolò</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kantone engagieren sich beim Vollzug von Wegweisungsentscheiden des Bundes in unterschiedlichem Ausmass. In den am 13. August dieses Jahres erfolgten Diskussionen in der Staatspolitischen Kommission Ihres Rates zur vorliegenden Motion kam über diesen Umstand ein grosser Unmut zum Ausdruck. Trotzdem beantrage ich Ihnen im Namen der Mehrheit der Kommission, die Motion Müller Damian, welche die Förderung des Vollzugs von Wegweisungen durch alle Kantone zur einheitlichen Umsetzung des Bundesrech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Kantone engagieren sich beim Vollzug von Wegweisungsentscheiden des Bundes in unterschiedlichem Ausmass. In den am 13. August dieses Jahres erfolgten Diskussionen in der Staatspolitischen Kommission Ihres Rates zur vorliegenden Motion kam über diesen Umstand ein grosser Unmut zum Ausdruck. Trotzdem beantrage ich Ihnen im Namen der Mehrheit der Kommission, die Motion Müller Damian, welche die Förderung des Vollzugs von Wegweisungen durch alle Kantone zur einheitlichen Umsetzung des Bundesrechtes verlangt, abzulehnen. Der Ständerat hat die Motion am 10. März 2026 mit 31 zu 10 Stimmen angenommen.
+Unsere Kommission hat dieses Geschäft eingehend beraten. Der Bundesrat unterstützt das Ziel und das Anliegen der Motion vollumfänglich, nämlich dass der Wegweisungsvollzug von den Kantonen konsequent umgesetzt wird. Doch sieht er, wie die Mehrheit der Kommission, in der vorliegenden Motion keine geeigneten Mittel zur Zielerreichung.
+Die Mehrheit der Kommission begründet die Ablehnung wie folgt: Erstens wird bereits an einer umfassenden Lösung gearbeitet. Im Rahmen der Umsetzung der Motion Salzmann 23.3082 erarbeitet der Bundesrat derzeit ein ausführliches Konzept zur Verbesserung des Wegweisungsvollzugs und zur Erhöhung der Zahl der Ausreisenden. Dieses Konzept basiert auf einer fundierten Analyse des gesamten Rückkehrbereichs und wird bald vorliegen. Es ist daher nicht sinnvoll, parallel dazu eine Motion zu verabschieden, die grundlegend in die Mechanik der Rückkehrprozesse eingreift, bevor die Kommission diese Berichte und Empfehlungen zur Kenntnis nehmen und diskutieren kann.
+Zweitens, und das ist der Hauptpunkt, stösst der Ansatz der Motion aus föderalistischer Sicht auf grosse Vorbehalte. Die Motion sieht finanzielle Anreize dafür vor, dass Kantone den Vollzug in anderen Kantonen übernehmen. Der Wegweisungsvollzug ist jedoch eine gesetzliche Pflicht der Kantone. Es wäre dem Wesen des Föderalismus fremd, die Kantone finanziell dafür zu belohnen, dass sie eine ihrer Kernpflichten erfüllen. Das wäre das Eingeständnis, dass Kantone ihre Pflichten nicht mehr selber wahrnehmen müssen und der Bund dann die Ersatzvornahme durch andere Kantone finanziell berappen muss. Mit Verlaub, das wäre föderalismuspolitisch gesehen eine Bankrotterklärung.
+Zudem ist die praktische Umsetzung auch kaum vorstellbar. Unsere Mehrheit in der Kommission kann sich schlicht nicht vorstellen, dass Kantone ihre Polizeikräfte aufgrund finanzieller Anreize zum Beispiel in andere Sprachregionen entsenden würden. Der Kanton Zug mit einer 100-Prozent-Quote beim Vollzug der Wegweisungsentscheidungen sucht Wege, sein Zuviel an Geld an die Einwohnerinnen und Einwohner zu bringen, aber ganz bestimmt sucht er keine neuen Einnahmequellen durch den Einsatz seiner Polizei beispielsweise in der Westschweiz. 
+Drittens gibt es Vollzugshürden, welche finanzielle Anreize nicht zum Verschwinden bringen können. Fehlende Reisedokumente etwa oder die Weigerung von Drittstaaten, ihre Staatsangehörigen zurückzunehmen, sind Hürden, die nicht einfach so beseitigt werden können.
+Was bereits heute funktioniert, sind negative Anreize. In den letzten Jahren wurden säumigen Kantonen durchschnittlich rund 3 Millionen Franken an Bundessubventionen gekürzt. Auch dafür brauchen wir keine neue Motion. 
+Für die Minderheit der Kommission ist das vorgeschlagene System ein Schritt in die richtige Richtung. Es würde den Kantonen zusätzliche Anreize bieten, Wegweisungen und Landesverweisungen systematisch und einheitlich zu vollziehen. 
+Im Namen der Kommissionsmehrheit - bei 13 zu 12 Stimmen - ersuche ich Sie aber, die vorliegende Motion abzulehnen. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Bundesrat, herzlichen Dank für Ihre Ausführungen. Es ist eine Tatsache, dass innerhalb der Schweiz grosse Unterschiede in der Umsetzung der Ausschaffungen bestehen. Sind Sie nicht der Meinung, dass neue Instrumente benötigt werden, um diesen Vollzug gesamthaft besser in den Griff zu bekommen?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de Quattro Jacqueline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est donc possible juridiquement. Ma question rejoint un peu celle de mon prédécesseur. Pourquoi ne souhaitez-vous pas appuyer cette amélioration du système qui permettrait plus d'efficacité et ainsi une meilleure acceptation par la population de notre politique d'asile ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pfister Gerhard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion wurde am 10. März dieses Jahres im Ständerat angenommen, ohne dass ein anderslautender Antrag gestellt worden wäre. Der Bundesrat hat damals und wird hoffentlich auch heute die Annahme der Motion beantragen. Ihre Kommission hat sie an der Sitzung vom 13. und 14. August beraten. Die Motion will, dass die Ablehnung häuslicher Gewalt und der Schutz von Frauen und Kindern als verbindliche Integrationskriterien ab dem ersten Aufenthaltstag festgelegt werden. Zudem sind ab der Ankunft in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion wurde am 10. März dieses Jahres im Ständerat angenommen, ohne dass ein anderslautender Antrag gestellt worden wäre. Der Bundesrat hat damals und wird hoffentlich auch heute die Annahme der Motion beantragen. Ihre Kommission hat sie an der Sitzung vom 13. und 14. August beraten. Die Motion will, dass die Ablehnung häuslicher Gewalt und der Schutz von Frauen und Kindern als verbindliche Integrationskriterien ab dem ersten Aufenthaltstag festgelegt werden. Zudem sind ab der Ankunft in der Schweiz obligatorische Schulungen gegen häusliche Gewalt, zu den Rechten der Betroffenen sowie zu den straf-, zivil- und ausländerrechtlichen Konsequenzen von Gewalt durchzuführen und verbindlich in allen Integrationsprogrammen auf Bundes-, Kantons- und Gemeindeebene zu verankern. Schliesslich soll der Bundesrat aufzeigen, welche Rechtsfolgen bei Verstössen gegen diese Integrationspflichten gelten und ob gesetzliche Anpassungen im Hinblick auf Asylstatus, Aufenthaltsrecht, Einbürgerung und Ausweisung erforderlich sind.
+Die Mehrheit Ihrer Kommission beantragt Ihnen die Annahme der Motion aus folgenden Gründen:
+Erstens ist die Bekämpfung häuslicher Gewalt eine Priorität, die eine klare rechtliche Verankerung erfordert. Zwar gehören die Beachtung der öffentlichen Sicherheit sowie die Respektierung der Werte der Bundesverfassung bereits heute zu den Integrationskriterien. Indem wir die Ablehnung häuslicher Gewalt jedoch als spezifisches Kriterium explizit auf Gesetzesstufe festhalten, verleihen wir diesem Anliegen das notwendige Gewicht und schaffen eine eindeutige Grundlage für die Praxis.
+Zweitens ist es zwar eine Selbstverständlichkeit, dass sich alle Personen, die in die Schweiz kommen, an unsere Rechtsordnung zu halten haben. Um dies aber sicherzustellen, müssen die geltenden Regeln und das hiesige Menschenbild von Beginn an unmissverständlich kommuniziert werden. Obligatorische Schulungen und Sensibilisierungsmassnahmen stellen sicher, dass jede Person über ihre Rechte und Pflichten sowie über die straf- und ausländerrechtlichen Konsequenzen von Gewalt informiert wird. 
+Drittens wird die Umsetzung dieser Massnahmen pragmatisch und ohne übermässigen bürokratischen Aufwand erfolgen können. Die Schulungen müssen keine komplexen Ausbildungsmodule sein. Sie können beispielsweise in Form von kurzen digitalen Modulen, Informationsflyern oder als integrierte Elemente in bestehenden Sprachkursen realisiert werden. Damit wird eine effektive Information gewährleistet, ohne die Kantone oder Gemeinden finanziell oder administrativ übermässig zu belasten. Aufgrund dieser Versicherung seitens des SEM lehnte die Kommission denn auch einen Antrag, auf die Verpflichtung zur Schulung zu verzichten, mit 14 zu 10 Stimmen ab. 
+Die Kommission beantragt Ihnen mit 18 zu 5 Stimmen bei 1 Enthaltung, die Motion anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamerzin Sidney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vous remercie pour votre question, Monsieur Gaillard. Cette loi vise à interdire la vente à des personnes étrangères. La vente aux Suisses n'est pas concernée par la lex Koller. Même un Suisse domicilié à l'étranger peut acheter un appartement ou une maison en Suisse. Les Suisses ne sont pas concernés par cette loi. En revanche, le but de la motion est que la procédure d'autorisation soit applicable aux résidences principales, et non pas seulement aux résidences secondaires. Cela veut dire qu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vous remercie pour votre question, Monsieur Gaillard. Cette loi vise à interdire la vente à des personnes étrangères. La vente aux Suisses n'est pas concernée par la lex Koller. Même un Suisse domicilié à l'étranger peut acheter un appartement ou une maison en Suisse. Les Suisses ne sont pas concernés par cette loi. En revanche, le but de la motion est que la procédure d'autorisation soit applicable aux résidences principales, et non pas seulement aux résidences secondaires. Cela veut dire que le Français résidant en Suisse avec un permis B ou l'Allemand résidant en Suisse avec un permis B, et non pas avec des permis C - mais c'est la question qui est encore à poser à l'auteur de la motion - seraient concernés par cette loi. Ils pourraient louer, mais ne pourraient pas acheter un appartement en Suisse. Reste à voir si, avec un permis d'établissement C, cela serait possible, mais avec un permis B, pour les Européens, cela ne serait plus possible - c'est le texte au chiffre 1 de la motion : non seulement les résidences secondaires, mais aussi les résidences principales. Relisez aussi le texte, cher collègue Gaillard.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolly Nicolas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au nom de la minorité de la Commission des institutions politiques, je vous propose d'adopter la motion Müller Damian 25.4521, "Permettre à n'importe quel canton d'exécuter un renvoi afin d'uniformiser l'application du droit fédéral". Le Conseil des États a adopté cette motion le 10 mars dernier avec une nette majorité, par 31 voix contre 10. Lors de son examen par notre Commission des institutions politiques, cette dernière, à une courte majorité, par 13 voix contre 12, a toutefois proposé de l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au nom de la minorité de la Commission des institutions politiques, je vous propose d'adopter la motion Müller Damian 25.4521, "Permettre à n'importe quel canton d'exécuter un renvoi afin d'uniformiser l'application du droit fédéral". Le Conseil des États a adopté cette motion le 10 mars dernier avec une nette majorité, par 31 voix contre 10. Lors de son examen par notre Commission des institutions politiques, cette dernière, à une courte majorité, par 13 voix contre 12, a toutefois proposé de la rejeter. Les rapporteurs en ont expliqué les motifs.
+Cette motion charge le Conseil fédéral de modifier la législation fédérale afin que tout canton puisse exécuter une décision de renvoi prononcée par la Confédération ou une expulsion judiciaire entrée en force, même lorsqu'il n'est pas le canton initialement compétent. Elle prévoit également que, si nécessaire, le canton qui assume concrètement cette tâche puisse recevoir l'indemnité fixée par la Confédération.
+Le constat à l'origine de la motion est clair : l'exécution des renvois varie sensiblement d'un canton à l'autre. Une telle disparité n'est pas satisfaisante. Lorsqu'une autorité a rendu une décision fondée sur le droit fédéral et que cette décision est entrée en force, son exécution ne devrait pas dépendre du canton dans lequel se trouve la personne concernée. Il en va de la crédibilité de notre État de droit. Une décision entrée en force doit être appliquée avec la même rigueur sur l'ensemble du territoire suisse. Cette motion évite ainsi que les défauts d'exécution d'un canton produisent durablement ses effets dans toute la Suisse.
+La motion propose une solution pragmatique : lorsqu'un canton n'exécute pas un renvoi et qu'un autre canton est en mesure de le faire, ce dernier doit pouvoir intervenir. Il ne s'agit ni de centraliser l'exécution des renvois ni de retirer leurs compétences aux cantons. Il s'agit, au contraire, de leur donner une possibilité d'action supplémentaire et de renforcer leur coopération. Cette souplesse est particulièrement importante dans un pays où les personnes concernées peuvent se déplacer d'un canton à l'autre rapidement. L'exécution d'une décision ne doit pas être paralysée par une frontière cantonale ou par une question de compétence administrative. Les autorités doivent, au contraire, pouvoir agir lorsque les conditions légales sont réunies, sans être contraintes d'engager des démarches supplémentaires qui retardent inutilement la procédure.
+La motion ne modifie par ailleurs ni les conditions matérielles d'un renvoi ni les voies de droit dont dispose la personne concernée. Elle intervient seulement lorsqu'une décision entrée en force a été prononcée. Il faut également rappeler que le départ volontaire demeure prioritaire. La motion ne remet nullement ce principe en question. Elle vise les situations dans lesquelles la décision n'est pas exécutée volontairement et où l'intervention des autorités devient nécessaire. Accorder une possibilité d'action à un autre canton permet alors d'éviter que l'inaction se prolonge indéfiniment.
+La question de l'indemnisation doit, elle aussi, être bien comprise. La minorité que je représente ne souhaite pas créer de nouvelles dépenses pour la Confédération. Comme l'a précisé l'auteur de la motion lors des débats au Conseil des États, l'objectif est simplement que l'indemnité normalement destinée au canton compétent revienne au canton qui a exécuté effectivement le renvoi.
+Cette solution apparaît logique et équitable : l'indemnisation doit suivre la prestation accomplie. Elle crée également une incitation concrète à agir, puisque le canton qui mobilise son personnel et ses moyens reçoit les ressources prévues à cet effet par la loi. Enfin, une exécution plus rapide et mieux coordonnée permet d'éviter la prolongation de procédures administratives coûteuses et de situations juridiquement incertaines, ce qui n'est dans l'intérêt de personne et en particulier pas des personnes concernées. L'efficacité de l'exécution sert donc non seulement l'État de droit, mais aussi une utilisation responsable des ressources publiques.
+Cette motion renforce l'égalité dans l'application du droit fédéral, améliore la collaboration intercantonale et consolide la crédibilité de nos institutions. Elle contribue également à faire respecter la volonté populaire exprimée en faveur de l'expulsion des criminels étrangers.
+Pour toutes ces raisons, la minorité de la commission vous invite à adopter cette motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tschopp Jean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, comment le Conseil fédéral garantit-il que d'éventuelles conséquences qui relèvent du droit des étrangers soient exclusivement liées à des infractions clairement définies et objectivables et non à des représentations culturelles ou à des modèles familiaux ? En d'autres termes, je reformule ma question : comment le Conseil fédéral garantit-il que des situations de vie comparables soient évaluées selon les mêmes critères, indépendamment de l'origine, de la religion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, comment le Conseil fédéral garantit-il que d'éventuelles conséquences qui relèvent du droit des étrangers soient exclusivement liées à des infractions clairement définies et objectivables et non à des représentations culturelles ou à des modèles familiaux ? En d'autres termes, je reformule ma question : comment le Conseil fédéral garantit-il que des situations de vie comparables soient évaluées selon les mêmes critères, indépendamment de l'origine, de la religion ou de la couleur de peau ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weber Céline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lors de sa séance des 13 et 14 août derniers, notre Commission des institutions politiques a traité de la motion Z'Graggen 25.4557, "Inscrire dans le droit d'asile, le droit des étrangers et le droit de la nationalité des obligations d'intégration claire pour lutter contre la violence domestique". Cette motion charge le Conseil fédéral d'adapter les lois précitées et, le cas échéant, d'autres actes législatifs, pour que les étrangers aient l'obligation de s'engager, en vue de leur intégration, à</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lors de sa séance des 13 et 14 août derniers, notre Commission des institutions politiques a traité de la motion Z'Graggen 25.4557, "Inscrire dans le droit d'asile, le droit des étrangers et le droit de la nationalité des obligations d'intégration claire pour lutter contre la violence domestique". Cette motion charge le Conseil fédéral d'adapter les lois précitées et, le cas échéant, d'autres actes législatifs, pour que les étrangers aient l'obligation de s'engager, en vue de leur intégration, à ne pas commettre de violences domestiques ou de violences à l'égard des femmes et des enfants, et ce, dès leur premier jour en Suisse. Pour ce faire, les étrangers doivent suivre des formations sur la violence domestique et doivent être au fait des conséquences de la violence sur le plan du droit civil, du droit pénal et du droit des étrangers.
+Les discussions au sein de la commission ont surtout porté sur les étrangers issus de l'asile et sur le concept de formation dans ce cadre. Que faut-il entendre exactement par "formation" ? Faut-il s'attendre à des surcoûts importants liés à cette formation ? Les formateurs pourraient-ils ensuite être tenus pour coresponsables si, malgré la formation, les étrangers commettent des délits ? La commission a cependant été informée qu'une simple thématisation, par exemple dans le cadre des cours de langue, peut déjà être considérée comme une formation, et que l'idée n'était pas de mettre en place un système coûteux et bureaucratique. Par ailleurs, il ne doit pas être considéré qu'en cas d'infraction, l'étranger qui commet le délit pourrait se retourner contre le formateur.
+Les discussions ont également porté sur la pertinence même d'une telle formation. En d'autres termes, est-ce vraiment le rôle de la Suisse de devoir expliquer une évidence aux étrangers qui viennent chez nous, à savoir qu'il n'y a pas de place chez nous pour les violences domestiques ? À ce sujet, il convient de préciser que si la Suisse a choisi de se doter d'un système d'asile, elle doit à ce titre se donner également les moyens d'en garantir la cohérence. Or, si nous refusons chaque mesure d'intégration au motif qu'il s'agit d'une évidence - en l'occurrence le fait que nous n'acceptions pas les violences domestiques - nous pouvons alors simplement abolir l'asile. Or, ce n'est pas la volonté de notre commission et sans doute pas non plus celle de la majorité de ce Parlement.
+Une minorité de votre commission considère que cette motion stigmatise les étrangers, raison pour laquelle elle rejette la motion. Cela dit, en permettant de renforcer le fonctionnement du système d'asile, non seulement pour intégrer les étrangers, mais également pour intervenir en cas de problème ou pour les renvoyer, la majorité de votre commission considère que cette motion va dans la bonne direction. En outre, en inscrivant spécifiquement la question de l'intégration en lien avec les violences domestiques dans la loi, nous envoyons un signal clair aux cantons pour qu'ils la prennent plus au sérieux dans leurs pratiques.
+Pour toutes ces raisons, je vous invite, au nom de la commission, à adopter la motion. Elle a été adoptée par le Conseil des États sans contre-proposition et par notre Commission des institutions politiques, par 18 voix contre 5 et 1 abstention.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La majorité de la commission vous propose de rejeter la motion Müller Damian.
+Les travaux de la commission ont montré que les instruments proposés ne sont ni nécessaires ni véritablement adaptés pour améliorer l'exécution de renvois.
+Tout d'abord, sur l'état de la situation actuelle des cantons : les différences entre les cantons, avancées pour justifier la motion, doivent être tout à fait relativisées. C'est en tout cas l'avis de la majorité de la commission. Les statistiques citées concernent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La majorité de la commission vous propose de rejeter la motion Müller Damian.
+Les travaux de la commission ont montré que les instruments proposés ne sont ni nécessaires ni véritablement adaptés pour améliorer l'exécution de renvois.
+Tout d'abord, sur l'état de la situation actuelle des cantons : les différences entre les cantons, avancées pour justifier la motion, doivent être tout à fait relativisées. C'est en tout cas l'avis de la majorité de la commission. Les statistiques citées concernent notamment les expulsions pénales, avec parfois un nombre très limité de personnes ; quelques cas suffisent alors à faire varier fortement le taux d'exécution. Il faut également distinguer une chose : les expulsions pénales des renvois relevant de l'asile ou du droit des étrangers ne répondent pas aux mêmes conditions. C'est vraiment important de faire cette distinction.
+Les discussions en commission ont aussi permis de nuancer certaines affirmations concernant les cantons romands. L'exemple du canton de Vaud a été clairement mis en avant : entre 1000 et 1200 renvois y ont été exécutés chaque année, et cela depuis plusieurs années. Plus généralement, le nombre de départs a augmenté et l'administration considère que le système suisse fonctionne globalement de manière efficace.
+Cela ne signifie pas qu'il n'existe aucune difficulté, mais les principaux obstacles ne relèvent pas nécessairement d'un manque de volonté des cantons. Il est important de voir quels sont les autres obstacles en la matière ; ce sont notamment l'absence de documents de voyage, la coopération avec les États d'origine ou encore des obstacles juridiques qui peuvent empêcher l'exécution d'un renvoi. La position de la majorité est de dire qu'un bonus financier n'apporterait absolument pas une nouvelle solution.
+Ensuite, la motion propose, pour une large part, des instruments qui existent déjà. La coopération et l'entraide entre les cantons sont déjà possibles aujourd'hui. Un canton peut déjà soutenir un autre canton dans l'exécution de ses tâches. Finalement, la motion n'apporte rien de nouveau.
+La véritable nouveauté, et la seule nouveauté, c'est le principe de l'introduction d'une incitation financière pour qu'un canton exécute des renvois à la place d'un autre. C'est particulièrement sur ce point que la majorité de la commission est sceptique. L'exécution des renvois est une compétence et une obligation des cantons. Récompenser financièrement un canton pour accomplir une tâche prévue par le droit constituerait un changement de logique et soulèverait des questions importantes du point de vue du fédéralisme et de la répartition des compétences. D'une certaine manière, on serait récompensé tout simplement parce qu'on a appliqué la loi ; c'est un peu particulier. Rien ne démontre par ailleurs qu'un canton mobiliserait davantage ses forces de police pour effectuer des renvois d'un autre canton, simplement en raison d'une indemnité financière. Il existe déjà des mécanismes financiers lorsque les cantons ne remplissent pas leurs obligations. La Confédération a des outils ; elle peut notamment suspendre certaines subventions. Selon les informations données à la commission, ces mesures représentent plus de 30 millions de francs sur les 10 dernières années.
+Pour toutes ces raisons, la commission, par 13 voix contre 12, vous recommande de rejeter la motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La violence domestique, sexuelle et la violence faite aux femmes doivent être combattues sans aucun compromis. La protection des victimes est également une exigence absolue, mais c'est précisément parce que ce combat est essentiel qu'il ne doit en aucun cas être instrumentalisé. Cette dérive est celle qu'on est en train de vivre ici, dans ce Parlement, avec une majorité qui accepte la politisation de cette thématique.
+Cette motion fait un choix politique très clair : prendre un phénomène structu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La violence domestique, sexuelle et la violence faite aux femmes doivent être combattues sans aucun compromis. La protection des victimes est également une exigence absolue, mais c'est précisément parce que ce combat est essentiel qu'il ne doit en aucun cas être instrumentalisé. Cette dérive est celle qu'on est en train de vivre ici, dans ce Parlement, avec une majorité qui accepte la politisation de cette thématique.
+Cette motion fait un choix politique très clair : prendre un phénomène structurel, qui traverse toute notre société, et choisir de le traiter sous l'angle du droit d'asile, du droit des étrangers et de la nationalité. Je dois dire mon étonnement - je dirais même mon désarroi - de voir que le Conseil fédéral, mais également la majorité de ce Parlement, se plient aussi facilement à ce cadrage.
+Le rejet de la violence et le respect des valeurs constitutionnelles font déjà partie de critères d'intégration essentiels. La violence domestique est déjà interdite et sanctionnée par notre droit, car - pour rappel - nous vivons dans un État de droit. Pourquoi faut-il maintenant inscrire spécifiquement cette question dans le droit des étrangers ? Quel message veut-on envoyer, sinon celui qu'il existerait un lien particulier entre immigration et violence domestique ?
+C'est d'autant plus problématique que les propres travaux de la Confédération nous invitent précisément à ne pas faire ce raccourci. Ces travaux ont été présentés au moment même où nous discutions de cette motion en commission. Une enquête du Bureau fédéral de l'égalité entre femmes et hommes montrait très clairement que la violence domestique était un problème systémique - un problème qui traversait toutes les populations en Suisse. Elle disait que ce n'était pas un problème d'étrangers, mais un problème général et systémique : la violence domestique existe dans toutes les couches de la société et au sein de toutes les populations. Ce rapport était très clair à cet égard.
+Cette motion est grave, parce qu'elle propose, pour traiter la question de la lutte contre les violences domestiques, de se préoccuper du passeport. Et ceci est grave. Un homme violent ne l'est pas davantage parce qu'il est étranger, et il ne l'est pas moins parce qu'il possède un passeport suisse. Une femme frappée par un Suisse n'est pas moins victime qu'une femme frappée par un étranger. Et c'est là que cette instrumentalisation devient aussi dangereuse pour les victimes. C'est pour cette raison, précisément, que le groupe des Verts rejettera cette motion. À force de fabriquer la figure de l'étranger violent, on détourne le regard de tous les auteurs qui ne correspondent pas à cette image - l'homme suisse, parfaitement intégré, socialement établi, bon père de famille en apparence. La violence domestique existe bien sûr aussi, derrière ces portes-là - on le sait bien, et toutes les enquêtes le confirment. Si nous voulons réellement protéger les femmes, alors protégeons toutes les femmes, et commençons notamment par protéger les femmes étrangères qui sont elles-mêmes victimes de violences, celles qui hésitent à dénoncer leur conjoint parce qu'elles craignent de perdre leur permis de séjour, leurs ressources ou leur sécurité. Le Bureau de prévention recommande justement une protection renforcée des victimes, indépendamment de leur statut de séjour. Voilà où nous devrions mettre notre énergie.
+Alors, oui, bien sûr, informons les personnes qui arrivent en Suisse sur les droits fondamentaux, sur l'égalité entre femmes et hommes, sur les droits des enfants, sur les conséquences pénales de la violence - bien sûr, faisons ces formations. Mais par pitié, faisons-le sans prétendre que le coeur du problème se trouve à la frontière. Nous avons besoin de prévention, bien sûr ; dans notre société, nous avons besoin de beaucoup de prévention, mais d'une prévention pour toutes et tous. Nous avons besoin de structures d'accueil suffisamment dotées, de professionnels formés, d'un meilleur accès à l'aide et d'une justice qui soit réellement centrée sur la protection des victimes, sur les femmes. La violence domestique n'est pas un problème d'asile. Je le dis encore une fois, la violence domestique n'est pas un problème d'asile, n'est pas un problème de nationalité, c'est un problème de violence, de rapport de pouvoir et de protection des victimes.
+J'aurais souhaité ici que le Conseil fédéral et la majorité de ce Parlement aient le courage de tenir cette ligne plutôt que de céder à la facilité politique qui consiste, une fois encore, à transformer l'étranger en explication commode d'un problème qui traverse toute notre société. Prenons au sérieux la lutte contre les violences faites aux femmes - une lutte trop sérieuse pour en faire un instrument de politique migratoire.
+Je vous invite, au nom du groupe des Verts, à rejeter la motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michel Matthias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Präsident, Frau Bundesrätin, geschätztes Kollegium, geschätzte Gäste aus dem Kanton meines Geburtsortes Rorschach. Das BISS ist ein wichtiger Schritt zur Modernisierung der elektronischen Kommunikation der ersten Säule. Ich unterstütze die Vorlage und möchte noch ein Element erwähnen. Es passt zu Artikel 76a, dort geht es um die Anforderungen an die elektronische Kommunikation. Ich erwähne das jetzt, weil es eigentlich ein allgemeines Anliegen ist, mit dem Ziel, dieser Vorlage noch etwas me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Präsident, Frau Bundesrätin, geschätztes Kollegium, geschätzte Gäste aus dem Kanton meines Geburtsortes Rorschach. Das BISS ist ein wichtiger Schritt zur Modernisierung der elektronischen Kommunikation der ersten Säule. Ich unterstütze die Vorlage und möchte noch ein Element erwähnen. Es passt zu Artikel 76a, dort geht es um die Anforderungen an die elektronische Kommunikation. Ich erwähne das jetzt, weil es eigentlich ein allgemeines Anliegen ist, mit dem Ziel, dieser Vorlage noch etwas mehr Biss zu geben.
+Mein Anliegen ist, dass künftig nicht nur elektronisch festgestellt werden kann, wer eine Person ist. Vielmehr muss auch zuverlässig geprüft werden, für welche Organisation diese Person handelt, in welcher Funktion, mit welcher Berechtigung. Das trifft zunehmend auch für Maschinen zu, man spricht hier von einer Vertrauensinfrastruktur. Diese soll nicht isoliert entwickelt werden. Einerseits soll die nationale Hoheit über Register, über Identitäten, über Rollen und Berechtigungen erhalten bleiben, gleichzeitig soll andererseits diese Infrastruktur von Anfang an mit internationalen Standards interoperabel sein. Das wird insbesondere dort wichtig, wo Systeme direkt miteinander kommunizieren. 
+Ein Beispiel: Ein Arbeitgeber beauftragt einen Treuhänder, eine Treuhänderin über sein oder ihr Fachsystem mit einer Ausgleichskasse zu kommunizieren. Die Ausgleichskasse wiederum muss elektronisch zuverlässig feststellen können, für welche Organisation mit welcher Berechtigung diese Treuhänderin handelt. Es geht also darum, die Interoperabilität in Artikel 76a so zu verstehen, dass sie auch für die Vertrauensinfrastruktur gilt, um sicherzustellen, dass die Standards für die elektronische Kommunikation auch die interoperable und kryptografisch überprüfbare Feststellung von Organisationszugehörigkeit, von Funktion, von Vertretungsberechtigung umfasst. Damit hätten wir dann auch ein Modell, das für andere Anwendungen - es wurde ja kurz erwähnt, man sollte keine Silos mehr bauen - verwendet werden kann, wie Easygov, das EPD und so weiter.
+Ich überlegte zuerst, einen Einzelantrag zu stellen, um das zu festigen. Ich liess mich dann im Austausch mit der Verwaltung überzeugen, dass die gesetzliche Grundlage in Artikel 76a ausreiche, um diese Anliegen auf Verordnungsstufe aufzunehmen. Ich hoffe, dass die Frau Bundesrätin das heute bestätigen kann. Falls ja, dann bitte ich darum, bestehende gemeinsame Infrastrukturen, die wir ja aufbauen, zum Beispiel die Swiyu-Vertrauensinfrastruktur, zuerst auf ihre Wiederverwendbarkeit für andere Anwendungen zu prüfen, bevor man dann sektorspezifische Insellösungen baut. Ebenso sollten international etablierte offene Standards und Modelle für organisatorische Identitäten und Vertrauensinteroperabilität berücksichtigt werden. 
+Ich möchte dazu zwei Beispiele nennen. Es gibt den sogenannten Legal Entity Identifier (LEI). Er ermöglicht weltweit eindeutige Identifikationen von Organisationen. Die auf Initiative der G-20 in Basel ansässige Global Legal Entity Identifier Foundation erweitert dieses Modell mit einem verifizierbaren Modell, um kryptografisch überprüfbare Organisationsidentitäten und Rollen zu ermöglichen. Die Schweiz ist hier auch in der Governance mit zwei Sitzen vertreten. 
+Dann gibt es noch die UNO-Organisation United Nations Centre for Trade Facilitation and Electronic Business (UN/CEFACT) - ich habe das auch jetzt gelernt. Diese verfolgt mit dem Global Registry Information Directory einen Ansatz, bei dem nationale Register bestehen bleiben, gleichzeitig aber Informationen grenzüberschreitend, maschinenlesbar auffindbar und überprüfbar sind. Es gibt hier also bestehende Modelle, die man nutzen kann.
+Abschliessend möchte ich anmerken, dass wir genau dieses Prinzip hier auch brauchen: Nationale Hoheit, gemeinsame Infrastruktur, aber von Anfang an international anschlussfähig. 
+Ich danke Ihnen, Frau Bundesrätin, wenn Sie das in der Umsetzung positiv aufnehmen.
 </t>
   </si>
 </sst>
@@ -899,8 +1156,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I37" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I53" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I53"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2255,6 +2512,460 @@
         <v>167</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" t="s">
+        <v>169</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>170</v>
+      </c>
+      <c r="I38" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>179</v>
+      </c>
+      <c r="I41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>182</v>
+      </c>
+      <c r="I42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>184</v>
+      </c>
+      <c r="B43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I43" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>189</v>
+      </c>
+      <c r="I44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" t="s">
+        <v>116</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>192</v>
+      </c>
+      <c r="I45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>194</v>
+      </c>
+      <c r="B46" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>196</v>
+      </c>
+      <c r="I46" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H47" t="s">
+        <v>200</v>
+      </c>
+      <c r="I47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>202</v>
+      </c>
+      <c r="B48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>203</v>
+      </c>
+      <c r="E48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" t="s">
+        <v>204</v>
+      </c>
+      <c r="I48" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>206</v>
+      </c>
+      <c r="B49" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>207</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>30</v>
+      </c>
+      <c r="H49" t="s">
+        <v>208</v>
+      </c>
+      <c r="I49" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>210</v>
+      </c>
+      <c r="B50" t="s">
+        <v>169</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>211</v>
+      </c>
+      <c r="E50" t="s">
+        <v>124</v>
+      </c>
+      <c r="F50" t="s">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" t="s">
+        <v>212</v>
+      </c>
+      <c r="I50" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>214</v>
+      </c>
+      <c r="B51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" t="s">
+        <v>40</v>
+      </c>
+      <c r="F51" t="s">
+        <v>71</v>
+      </c>
+      <c r="G51" t="s">
+        <v>30</v>
+      </c>
+      <c r="H51" t="s">
+        <v>215</v>
+      </c>
+      <c r="I51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>70</v>
+      </c>
+      <c r="E52" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" t="s">
+        <v>30</v>
+      </c>
+      <c r="H52" t="s">
+        <v>218</v>
+      </c>
+      <c r="I52" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" t="s">
+        <v>30</v>
+      </c>
+      <c r="H53" t="s">
+        <v>222</v>
+      </c>
+      <c r="I53" t="s">
+        <v>223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -906,7 +906,7 @@
     <t xml:space="preserve">Die Motion Maret Marianne 25.4556 fordert vom Bundesrat ein Rahmengesetz zur Verhinderung und zum Schutz vor häuslicher Gewalt, das Prävention, Opferschutz und Ahndung einheitlich regeln soll. Der Ständerat hat den Vorstoss im März klar angenommen; auch Ihre Kommission für Rechtsfragen hat die Motion im Juli mit einer Präzisierung angenommen.
 Der Bundesrat unterstützt die Motion. Die Bekämpfung häuslicher Gewalt ist eine Priorität des Bundesrates, weshalb er sein Engagement in diesem Bereich verstärkt hat. So arbeitet mein Departement gemeinsam mit dem Eidgenössischen Departement des Innern, den Kantonen, Gemeinden und Städten zurzeit an einer nationalen Strategie gegen häusliche, sexualisierte und geschlechtsbezogene Gewalt. Die Zivilgesellschaft wird ebenfalls eng in die Arbeiten einbezogen.
 Im Ständerat wurden die kantonalen Unterschiede beim Schutz vor häuslicher Gewalt thematisiert, da Opfer nicht überall in der Schweiz denselben Schutz erhalten und deshalb nationale Mindeststandards nötig seien. Dies würde zudem zu einer besseren Koordination zwischen Bund und Kantonen führen. Der Bundesrat teilt diese Ansicht. Die hohe Zahl der Femizide des letzten Jahres sowie die generelle Zunahme von Fällen häuslicher und sexueller Gewalt zeigen, dass der Schutz der Opfer dringend verbessert werden muss. Ein nationales Rahmengesetz kann hier helfen.
-Der Bundesrat hat darauf hingewiesen, dass für die Umsetzung der vorliegenden Motion eine Verfassungsänderung nötig ist. Lassen Sie mich das erläutern: Sowohl dem Bund als auch den Kantonen kommen Kompetenzen im Bereich des Schutzes vor häuslicher Gewalt zu. Der Bund besitzt Gesetzgebungskompetenzen im Zivil-, Straf- und Opferhilferecht. Die Kantone sind hingegen für den Vollzug zuständig, insbesondere für polizeiliche Wegweisungen, Annäherungsregionen, Kontaktverbote sowie das Bedrohungsmanagement. In Fällen häuslicher Gewalt kann die Polizei vor Ort unmittelbar Gefahren abwehren; auch die Prävention ist grösstenteils Aufgabe der Kantone.
+Der Bundesrat hat darauf hingewiesen, dass für die Umsetzung der vorliegenden Motion eine Verfassungsänderung nötig ist. Lassen Sie mich das erläutern: Sowohl dem Bund als auch den Kantonen kommen Kompetenzen im Bereich des Schutzes vor häuslicher Gewalt zu. Der Bund besitzt Gesetzgebungskompetenzen im Zivil-, Straf- und Opferhilferecht. Die Kantone sind hingegen für den Vollzug zuständig, insbesondere für polizeiliche Wegweisungen, Annäherungs-, Rayon- und Kontaktverbote sowie das Bedrohungsmanagement. In Fällen häuslicher Gewalt kann die Polizei vor Ort unmittelbar Gefahren abwehren; auch die Prävention ist grösstenteils Aufgabe der Kantone.
 Nach Ansicht des Bundesrates sollte ein nationales Rahmengesetz Minimalstandards in sämtlichen Bereichen des Gewaltschutzes umfassen. Da die Kantone jedoch für zentrale Aufgaben, wie polizeiliche Schutzmassnahmen oder das Bedrohungsmanagement, zuständig sind, ist für die Umsetzung der Motion eine Verfassungsänderung nötig.
 Die Kantone haben in den letzten Jahren bei der Bekämpfung häuslicher Gewalt wichtige Arbeit geleistet; sie analysieren derzeit die kantonalen Rechtsgrundlagen und beabsichtigen, diese noch stärker zu harmonisieren. An diese Arbeiten wollen wir anknüpfen. Bei einer Annahme der Motion wird der Bundesrat die Kantone von Beginn an eng einbeziehen und gemeinsam mit ihnen prüfen, welche Kompetenzen beim Bund angesiedelt werden sollen und wofür eine Verfassungsänderung erforderlich ist.
 Am 3. Juli 2026 hat sich Ihre Kommission für Rechtsfragen mit der vorliegenden Motion befasst und sie angenommen. Dabei hat sie auch einem Antrag zugestimmt, der die Präzisierung fordert, dass der Bundesrat ein Rahmengesetz nicht nur zum Schutz vor häuslicher, sondern auch vor sexualisierter und geschlechtsbezogener Gewalt vorlegen soll. Eine solche Änderung kostet zwar Zeit, da das Geschäft nochmals in den Ständerat geht, entscheidend ist jedoch, dass diese Motion die nachfolgenden Arbeiten tatsächlich erleichtert.
@@ -1108,6 +1108,30 @@
 Dann gibt es noch die UNO-Organisation United Nations Centre for Trade Facilitation and Electronic Business (UN/CEFACT) - ich habe das auch jetzt gelernt. Diese verfolgt mit dem Global Registry Information Directory einen Ansatz, bei dem nationale Register bestehen bleiben, gleichzeitig aber Informationen grenzüberschreitend, maschinenlesbar auffindbar und überprüfbar sind. Es gibt hier also bestehende Modelle, die man nutzen kann.
 Abschliessend möchte ich anmerken, dass wir genau dieses Prinzip hier auch brauchen: Nationale Hoheit, gemeinsame Infrastruktur, aber von Anfang an international anschlussfähig. 
 Ich danke Ihnen, Frau Bundesrätin, wenn Sie das in der Umsetzung positiv aufnehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poggia Mauro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le but de cette motion est que l'exception absolue qu'accorde notre loi sur la transparence à la Finma soit retirée pour que la Finma, comme tout autre service de notre administration, même si elle ne l'est pas exactement comme le rappelle à juste titre le Conseil fédéral, doive fournir des renseignements qui lui sont demandés et puisse bien évidemment également invoquer les exceptions figurant à l'article 7.
+Je rappelle que la Finma, avec la Banque nationale suisse, sont les seules deux entités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le but de cette motion est que l'exception absolue qu'accorde notre loi sur la transparence à la Finma soit retirée pour que la Finma, comme tout autre service de notre administration, même si elle ne l'est pas exactement comme le rappelle à juste titre le Conseil fédéral, doive fournir des renseignements qui lui sont demandés et puisse bien évidemment également invoquer les exceptions figurant à l'article 7.
+Je rappelle que la Finma, avec la Banque nationale suisse, sont les seules deux entités totalement couvertes par une absence de transparence, puisque l'on considère qu'elles mènent des activités dans des domaines extrêmement sensibles. Pour la Banque nationale suisse, je pense qu'il n'y a aucune discussion possible : il s'agit de la politique monétaire de notre pays et son activité ne peut pas faire l'objet d'un examen de la part des citoyens. C'est évidemment aux entités fédérales compétentes d'obtenir sur requête les explications voulues.
+En ce qui concerne la Finma, la situation est différente. Nous avons une autorité de surveillance, dont on a beaucoup parlé ces derniers temps, pas forcément en bien, qui s'occupe des marchés financiers, du système bancaire, mais également de l'ensemble des assurances privées. Aujourd'hui, la Finma n'a aucune information à donner à qui que ce soit et se retranche effectivement, comme la Banque nationale, derrière une totale opacité.
+Je rappelle que notre Département fédéral des finances et l'armée, qui, eux aussi, par définition, exercent des activités dans des domaines sensibles, sont soumis à la loi sur la transparence et peuvent faire valoir les exceptions figurant dans la loi. Je les rappelle : celles qui s'appliquent ici, c'est lorsque l'on considère que la transparence pourrait entraver l'exécution de mesures concrètes prises par l'autorité conformément à ses objectifs, le risque de compromettre la sûreté intérieure ou extérieure de la Suisse, le risque de compromettre les intérêts de la politique économique ou monétaire et le risque de révéler des secrets professionnels d'affaires ou de fabrication. Il y a donc évidemment cette protection des tiers qui peut être invoquée ou le risque de divulguer des informations fournies librement par un tiers à une autorité qui en a garanti le secret.
+On voit donc que les moyens, pour la Finma, de s'opposer à ce qu'elle devienne un livre ouvert pour le citoyen de notre pays sont présents. Ce qui est demandé, c'est simplement que la Finma soit, comme les autres interlocuteurs dans le domaine de la transparence, soumise à l'obligation de fournir des renseignements.
+J'ai été moi-même confronté à une problématique évidemment inquiétante, puisque nous avons des assureurs privés qui mènent une politique en invoquant les instructions qui leur sont données par la Finma, qui n'indiquent pas quelles sont ces instructions, parce qu'ils considèrent que la Finma leur interdit de le faire. Lorsque l'on demande à la Finma quelles sont ses instructions, elle se réfugie évidemment derrière le secret.
+Finalement, cette opacité sert donc à des mesures totalement incontrôlées par qui que ce soit, y compris par les tribunaux, puisque - je le répète - le fait de ne pas être soumis à la loi sur la transparence signifie que l'on ne peut même pas s'adresser à un tribunal pour qu'il puisse contrôler si le refus opposé par la Finma se fonde sur des intérêts supérieurs, qui existent évidemment, mais qui doivent au moins être invoqués. Ici, ce n'est pas le cas.
+Voilà la raison pour laquelle je vous demande d'adopter la motion, pour que cette exception, qui n'a pas plus de raison d'être que dans d'autres domaines sensibles de notre administration, soit enfin levée.
 </t>
   </si>
 </sst>
@@ -1156,8 +1180,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I53" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I54" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I54"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2966,6 +2990,35 @@
         <v>223</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>226</v>
+      </c>
+      <c r="E54" t="s">
+        <v>47</v>
+      </c>
+      <c r="F54" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" t="s">
+        <v>30</v>
+      </c>
+      <c r="H54" t="s">
+        <v>227</v>
+      </c>
+      <c r="I54" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -1111,10 +1111,26 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">421009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nause Reto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im europäischen Vergleich haben wir eine der tiefsten Erwerbsquoten bei Menschen aus der Ukraine mit Schutzstatus S. Das ist ein Problem, weil es viel Geld kostet. Es ist akut und wird uns auch im Rahmen der Budgetdebatte nochmals beschäftigen.
+Meine parlamentarische Initiative wollte den grösstmöglichen Anreiz für den Eintritt dieser Menschen ins Erwerbsleben schaffen. So soll eine Aufenthaltsbewilligung in der Schweiz bereits nach drei Jahren erteilt werden können, wenn die Person erwerbstätig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im europäischen Vergleich haben wir eine der tiefsten Erwerbsquoten bei Menschen aus der Ukraine mit Schutzstatus S. Das ist ein Problem, weil es viel Geld kostet. Es ist akut und wird uns auch im Rahmen der Budgetdebatte nochmals beschäftigen.
+Meine parlamentarische Initiative wollte den grösstmöglichen Anreiz für den Eintritt dieser Menschen ins Erwerbsleben schaffen. So soll eine Aufenthaltsbewilligung in der Schweiz bereits nach drei Jahren erteilt werden können, wenn die Person erwerbstätig ist. Es hätte also eine Koppelung von Aufenthalt und Erwerbstätigkeit stattgefunden. Die Arbeitgeberinnen und Arbeitgeber - übrigens viele Hoteliers, Gastrobetriebe usw. - hätten damit auch eine höhere Sicherheit erhalten, dass die Betroffenen beim möglichen Auslaufen des Schutzstatus S nicht von einem Tag auf den anderen in der Unternehmung fehlen und nicht mehr zur Verfügung stehen. Die Flüchtlinge mit Schutzstatus S hätten den maximalen Anreiz erhalten, ins Erwerbsleben einzutreten.
+Die Forderung ist klug und sinnvoll, aber leider nicht mehrheitsfähig. Die Mehrheit will auch nach vier Jahren Krieg an der Rückkehrorientierung des Schutzstatus S festhalten. Ich bin deshalb gespannt auf klügere und bessere Lösungen. Weil ich mit einer Ablehnung der Initiative kein negatives Zeichen riskieren will und hier nicht einen besseren Weg verbauen will, ziehe ich die Initiative zurück. 
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">420783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20260923</t>
   </si>
   <si>
     <t xml:space="preserve">Poggia Mauro</t>
@@ -1180,8 +1196,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I54" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I55" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I55"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -2998,25 +3014,54 @@
         <v>225</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
         <v>226</v>
       </c>
       <c r="E54" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
         <v>227</v>
       </c>
       <c r="I54" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>229</v>
+      </c>
+      <c r="B55" t="s">
+        <v>225</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>230</v>
+      </c>
+      <c r="E55" t="s">
+        <v>47</v>
+      </c>
+      <c r="F55" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" t="s">
+        <v>231</v>
+      </c>
+      <c r="I55" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -71,15 +71,16 @@
 Das heutige elektronische Patientendossier (EPD) beruht auf einer komplexen Struktur mit verschiedenen Anbietern und einem aufwendigen Eröffnungsprozess. Diese und weitere Hürden, wie auch die doppelte Freiwilligkeit, haben dazu beigetragen, dass seine Verbreitung und Nutzung deutlich hinter den Erwartungen zurückgeblieben ist - das ist eine diplomatische Ausdrucksweise.
 Mit dem neuen Bundesgesetz über das elektronische Gesundheitsdossier soll deshalb eine grundlegende Neuausrichtung erfolgen: Das EPD wird durch das elektronische Gesundheitsdossier (E-GD) abgelöst. Auch Digisanté ist ein wichtiger Pfeiler der Digitalisierung im Gesundheitswesen. - Ich höre mich wegen des Lärms selbst nicht. Das ist schon okay.
 An fünf Sitzungen hat Ihre Kommission das Geschäft beraten, zahlreiche Stakeholder angehört und zahlreiche Zusatzberichte eingefordert, um die bestmögliche Entscheidungsgrundlage zu haben. Dies sind nun die Eckwerte:
-1. Es soll automatisch sein für alle. Jede Person mit Wohnsitz in der Schweiz erhält kostenlos ein E-GD. Wer keines möchte, kann widersprechen - das ist das sogenannte Opt-out - oder es später löschen lassen. 
-2. Alle Leistungserbringenden müssen mitmachen. Neu werden auch ambulante Leistungserbringende wie Ärztinnen und Ärzte, Apotheken, Physiotherapeutinnen und Physiotherapeuten zur Nutzung verpflichtet, sofern sie über die OKP abrechnen. 
-3. Das dritte Kernelement: relevante Gesundheitsdaten an einem Ort. Verschreibungen von Medikamenten, Laborwerte, Impfungen, Austritts- und Konsultationsberichte - all dies soll digital zugänglich sein. Die Patientinnen und Patienten behalten die Kontrolle, sie bestimmen, wer welche Daten sehen darf. Zudem soll es eine bessere technische Integration geben. Einheitliche Standards ermöglichen die automatische Übertragung aus Praxisinformationssystemen (PIS) und Klinikinformationssystemen (KIS). Damit sollen Doppelspurigkeiten und administrativer Aufwand reduziert werden. Zudem soll das Dossier stärker zentralisiert werden. Dass der Bund die zentrale technische Infrastruktur verantwortet, heisst nicht, dass er sie selbst anbieten muss. Die Kantone verantworten den Betrieb nur noch einer Gemeinschaft. Der Bundesrat liess die Anzahl der Gemeinschaften noch offen; das möchte die Kommission nicht. Damit sollen auch Lehren aus dem EPD gezogen werden, bei welchem in den Stammgemeinschaften doch ziemlich viele Millionen verloren gingen. 
+1.[NB]Es soll automatisch sein für alle. Jede Person mit Wohnsitz in der Schweiz erhält kostenlos ein E-GD. Wer keines möchte, kann widersprechen - das ist das sogenannte Opt-out - oder es später löschen lassen. 
+2.[NB]Alle Leistungserbringenden müssen mitmachen. Neu werden auch ambulante Leistungserbringende wie Ärztinnen und Ärzte, Apotheken, Physiotherapeutinnen und Physiotherapeuten zur Nutzung verpflichtet, sofern sie über die OKP abrechnen. 
+3.[NB]Das dritte Kernelement: relevante Gesundheitsdaten an einem Ort. Verschreibungen von Medikamenten, Laborwerte, Impfungen, Austritts- und Konsultationsberichte - all dies soll digital zugänglich sein. Die Patientinnen und Patienten behalten die Kontrolle, sie bestimmen, wer welche Daten sehen darf. Zudem soll es eine bessere technische Integration geben. Einheitliche Standards ermöglichen die automatische Übertragung aus Praxisinformationssystemen (PIS) und Klinikinformationssystemen (KIS). Damit sollen Doppelspurigkeiten und administrativer Aufwand reduziert werden. Zudem soll das Dossier stärker zentralisiert werden. Dass der Bund die zentrale technische Infrastruktur verantwortet, heisst nicht, dass er sie selbst anbieten muss. Die Kantone verantworten den Betrieb nur noch einer Gemeinschaft. Der Bundesrat liess die Anzahl der Gemeinschaften noch offen; das möchte die Kommission nicht. Damit sollen auch Lehren aus dem EPD gezogen werden, bei welchem in den Stammgemeinschaften doch ziemlich viele Millionen verloren gingen. 
 Zum Datenschutz: Der Bund ist für die Datensicherheit verantwortlich. Die Daten werden in der Schweiz gehalten. Ihre Kommission hat noch zahlreiche Ergänzungen im Bereich des Datenschutzes beschlossen; dazu später mehr. 
 Nach der Vorstellung dieser Eckwerte, die Sie wahrscheinlich gar nicht verstanden haben, weil es hier drin so laut ist, möchte ich nun noch zu den diskutierten Punkten kommen. 
 Zuerst zum Thema Datenschutz: Eine entscheidende Voraussetzung für die Akzeptanz und die erfolgreiche Umsetzung des E-GD ist das Vertrauen in den Datenschutz. Die Datensicherheit, die Übermittlung der Daten sowie deren Verschlüsselung wurden sorgfältig geprüft.
 Beim Letzteren hat sich die Kommission insbesondere mit der Frage einer möglichen Ende-zu-Ende-Verschlüsselung auseinandergesetzt. Grundlage dafür war eine Studie der EPFL im Auftrag des Bundesamts für Gesundheit. Angesichts der Tatsache, dass aufgrund technischer Einschränkungen kein anderes öffentliches und nationales System eine strikte Ende-zu-Ende-Verschlüsselung verwendet, ist die Kommission der Auffassung, dass eine solche Lösung nicht im Gesetz verankert werden kann und sollte. Das bedeutet nicht, dass dies nicht umgesetzt werden könnte, falls die Technik es zulassen würde, sondern lediglich, dass wir es nicht im Gesetz verankern möchten. Die Kommission beantragt Ihnen jedoch einstimmig, die Anforderungen an den Datenschutz und die Datensicherheit sowie die Notwendigkeit der Verschlüsselung der Daten ausdrücklich in einem neuen Artikel 5a festzuhalten. Ebenfalls einstimmig beantragt die Kommission die Präzisierung, dass der Bund Daten nur insoweit bearbeiten darf, als dies für den technischen Betrieb des E-GD-Informationssystems erforderlich ist; dies ist in Artikel 5 Absatz 5 geregelt. 
-Schliesslich ist die Kommission ebenfalls einstimmig der Auffassung, dass in Artikel 5 Absatz 8 klargestellt werden soll, dass der Quellcode der eingesetzten Software, soweit möglich, veröffentlicht werden muss - demgemäss ist sie Open Source - und dass anpassbare, leicht verständliche Berechtigungsprofile zur Verfügung gestellt werden müssen. Die Kommission beantragt alle diese Anpassungen, weil sie der Meinung ist, dass einerseits der Datenschutz eine ganz hohe Priorität hat, es aber andererseits auch praktikabel bleiben muss. Mit dieser Präzisierung soll also der Datenschutz noch stärker gewichtet werden. Für die Kommission ist ebenfalls klar - wir haben das kurz diskutiert -, dass der Datenschutz bei den Primärsystemen, also den Klinik- und den Praxisinformationssystemen, weiterhin eine Schwachstelle im Gesundheitswesen ist. Wir erwarten, dass für Primärsysteme die Mindeststandards gelten; hierzu sollte in den nächsten Monaten auch ein Postulatsbericht folgen.
-Nun komme ich noch zu Digisanté. In einem Bericht liess die Kommission die Abhängigkeit zwischen Digisanté und dem E-GD ausführlich analysieren: Sie ist zeitlicher, aber auch inhaltlicher Natur. Auch wenn Digisanté nicht unmittelbar an das E-GD geknüpft ist, gibt es indirekt doch einen Zusammenhang. Damit die Digitalisierung im Gesundheitswesen vorankommt, ist Digisanté unverzichtbar. Gerade die Leistungserbringenden, das möchte ich hier noch betonen, benötigen gemäss ihren Aussagen den Swiss HDS - das ist ein Unterkapitel von Digisanté - lieber früher als später. 
+Schliesslich ist die Kommission ebenfalls einstimmig der Auffassung, dass in Artikel 5 Absatz 8 klargestellt werden soll, dass der Quellcode der eingesetzten Software, soweit möglich, veröffentlicht werden muss - demgemäss ist sie Open Source - und dass anpassbare, leicht verständliche Berechtigungsprofile zur Verfügung gestellt werden müssen. 
+Die Kommission beantragt alle diese Anpassungen, weil sie der Meinung ist, dass einerseits der Datenschutz eine ganz hohe Priorität hat, es aber andererseits auch praktikabel bleiben muss. Mit dieser Präzisierung soll also der Datenschutz noch stärker gewichtet werden. Für die Kommission ist ebenfalls klar - wir haben das kurz diskutiert -, dass der Datenschutz bei den Primärsystemen, also den Klinik- und den Praxisinformationssystemen, weiterhin eine Schwachstelle im Gesundheitswesen ist. Wir erwarten, dass für Primärsysteme die Mindeststandards gelten; hierzu sollte in den nächsten Monaten auch ein Postulatsbericht folgen.
+Nun komme ich noch zu Digisanté. In einem Bericht liess die Kommission die Abhängigkeit zwischen Digisanté und dem E-GD ausführlich analysieren: Sie ist zeitlicher, aber auch inhaltlicher Natur. Auch wenn Digisanté nicht unmittelbar an das E-GD geknüpft ist, gibt es indirekt doch einen Zusammenhang. Damit die Digitalisierung im Gesundheitswesen vorankommt, ist Digisanté unverzichtbar. Gerade die Leistungserbringenden, das möchte ich hier noch betonen, benötigen gemäss ihren Aussagen den Swiss Health Data Space (Swiss HDS) - das ist ein Unterkapitel von Digisanté - lieber früher als später. 
 Weitere Themen waren das EPDG - also das Gesetz, das aktuell gilt, auch wenn es in der Realität nicht umgesetzt wird - und auch der Ausstieg der Post und damit der Wegfall von Sanela ab 2027. Das EPD soll bis zur Einführung des E-GD, so will es die Kommission, weitergeführt werden. Damit soll verhindert werden, dass Lücken beim Betrieb, bei der Finanzierung oder bei den grundlegenden Dienstleistungen entstehen. Der für Ende 2026 vorgesehene Rückzug der Post Sanela Health AG muss so erfolgen, dass eine geordnete Migration zu Cara gewährleistet ist - idealerweise ohne zusätzliche Kosten und ohne Datenverluste.
 </t>
   </si>
@@ -106,11 +107,11 @@
 Troisièmement, au lieu de multiples structures décentralisées qui rendaient complexe la mise en oeuvre du dossier électronique du patient, désormais, le projet s'appuie sur une infrastructure centralisée. La commission a en effet décidé à l'unanimité que les cantons devraient se mettre d'accord sur une seule communauté nationale. Pour votre information, le regroupement des différentes communautés de référence a progressé et, depuis que la Poste s'est retirée de l'exploitation du dossier électronique du patient, celui-ci s'oriente déjà vers une communauté unique - fort probablement Cara - dotée d'une infrastructure technique uniforme. La Confédération reste responsable du système d'information.
 Quatrièmement, l'interopérabilité est l'une des conditions clés de la réussite du projet. Le dossier électronique de santé et le Swiss Health Data Space (SwissHDS) utiliseront des normes et des interfaces communes. Pour information, le dossier électronique de santé a pour but de donner à la population un accès à ses données de santé et de garantir une traçabilité de ces dernières sur le long terme[NB]; le SwissHDS, lui, permet aux fournisseurs de prestations d'échanger des données de manière structurée et automatisée - business to business, ou B2B. Les deux projets seront développés en parallèle et étroitement coordonnés. Les modifications faites sur le plan des systèmes primaires des fournisseurs de prestations pour leur raccordement au dossier électronique de santé pourront ainsi également être utilisées pour la communication B2B dans le SwissHDS.
 Cinquièmement, un financement clarifié est nécessaire. Si c'est la Confédération qui finance la mise en place et le développement de l'infrastructure, ce sont les cantons qui assumeront les coûts d'exploitation courants et garantiront l'exploitation de la communauté sur leur territoire. Dans son corapport, la Commission des finances de notre conseil relève que les estimations transmises sont imprécises et peu transparentes, notamment parce que l'on souhaite éviter tout risque d'impact négatif sur l'appel d'offres. Elle recommande ainsi de rester attentif aux conséquences budgétaires que pourraient entrainer d'éventuelles modifications apportées au projet.
-Une condition décisive pour l'acceptation et la mise en oeuvre du DES, et qui a préoccupé notre commission, est la confiance en la protection des données. La sécurité des données, leur transition ainsi que leur chiffrement ont été soigneusement analysés. Concernant ce dernier, la commission s'est penchée sur la question d'un éventuel chiffrement de bout en bout (E2EE), sur la base d'une étude de l'EPFL réalisée à la demande de l'Office fédéral de la santé publique. Prenant acte du fait qu'aucun autre système public ou national n'utilise un chiffrement E2EE strict, en raison d'insuffisances techniques, la commission estime que cette solution ne doit pas être inscrite dans la loi. Elle propose toutefois à l'unanimité que les exigences en matière de protection et de sécurité des données, ainsi que la nécessité de chiffrer les données, soient explicitement mentionnées dans un nouvel article 5a. De plus, la commission propose, à l'unanimité, de préciser que la Confédération ne peut traiter les données personnelles "que dans la mesure où cela est nécessaire au bon fonctionnement technique du système d'information DES". Il s'agit de l'article 5 alinéa 5.
+Une condition décisive pour l'acceptation et la mise en oeuvre du DES, et qui a préoccupé notre commission, est la confiance en la protection des données. La sécurité des données, leur transition ainsi que leur chiffrement ont été soigneusement analysés. Concernant ce dernier, la commission s'est penchée sur la question d'un éventuel chiffrement de bout en bout (E2EE), sur la base d'une étude de l'EPFL réalisée à la demande de l'Office fédéral de la santé publique. Prenant acte du fait qu'aucun autre système public ou national n'utilise un chiffrement E2EE strict, en raison d'insuffisances techniques, la commission estime que cette solution ne doit pas être inscrite dans la loi. Elle propose toutefois à l'unanimité que les exigences en matière de protection et de sécurité des données, ainsi que la nécessité de chiffrer les données, soient explicitement mentionnées dans un nouvel article[NB]5a. De plus, la commission propose, à l'unanimité, de préciser que la Confédération ne peut traiter les données personnelles "que dans la mesure où cela est nécessaire au bon fonctionnement technique du système d'information DES". Il s'agit de l'article 5 alinéa[NB]5.
 Enfin, à l'unanimité, la commission considère qu'il convient de préciser que le code source des logiciels utilisés doit être publié, dans la mesure du possible, donc en "open source" - il s'agit de l'article 5 alinéa 8 -, et que des profils d'autorisation adaptables et faciles à comprendre doivent être mis à disposition - article 11 alinéas 5bis et 5ter.
 Une seconde condition est essentielle. Elle concerne la transition entre le DEP et le DES. Quatre points critiques ont été abordés.
 Premièrement, la loi fédérale sur le dossier électronique du patient (LDEP) sera maintenue jusqu'à la mise en oeuvre du DES pour éviter que des lacunes menacent l'exploitation, le financement et les services de base.
-Deuxièmement, le retrait de Post Sanela, prévu à la fin de 2026, doit se faire avec la garantie d'une migration ordonnée vers la communauté de référence Cara ou vers la plateforme qui sera choisie sans coûts supplémentaires ni pertes de données. Pour rappel, cela concerne près de 80 000 DEP ouverts, et, La Poste, en tant qu'entreprise liée à la Confédération, a une responsabilité particulière à cet égard.
+Deuxièmement, le retrait de Post Sanela, prévu à la fin de 2026, doit se faire avec la garantie d'une migration ordonnée vers la communauté de référence Cara ou vers la plateforme qui sera choisie sans coûts supplémentaires ni pertes de données. Pour rappel, cela concerne près de 80[NB]000 DEP ouverts, et, La Poste, en tant qu'entreprise liée à la Confédération, a une responsabilité particulière à cet égard.
 Troisièmement, la capacité de raccordement technique des fournisseurs de prestations et des systèmes primaires existants avec le DES doit être garantie.
 Quatrièmement, la transition doit être accélérée, mais dans le respect des règles de l'OMC et de la loi fédérale sur les marchés publics, une procédure de gré à gré étant considérée comme risquée. En bref, une transition stable sans perte de données ni d'investissements est prioritaire. Par courrier, la commission a, de ce fait, invité à l'unanimité le Conseil fédéral à s'engager dans ce sens.
 En conclusion, par 16 voix contre 8, la commission vous recommande d'entrer en matière sur le projet. Bien qu'elle soit d'accord avec l'objectif, une minorité critique en particulier l'infrastructure centralisée, qui, selon elle, nécessitera le lancement d'un nouveau projet informatique important et risqué sur le plan fédéral, ainsi que le droit d'opposition prévu.
@@ -128,9 +129,9 @@
   <si>
     <t xml:space="preserve">Besten Dank, ich bin auch dankbar, wenn ich mich selbst verstehe! 
 Ich habe an folgendem Punkt geendet: Wir befinden uns momentan in einer Phase, in der wir aktuell noch ein EPD haben. Das soll auch weiterhin gelten. Der Kommission ist es ein Anliegen, dass das EPD fortgeführt wird, bis das E-GD eingeführt wird, damit es nicht zu Unterbrüchen kommt.
-Der für 2026 vorgesehene Rückzug der Post Sanela Health AG muss so erfolgen, das ist die Meinung der Kommission, dass eine geordnete Migration zu Cara gewährleistet ist. Ich kann Ihnen sagen: 80 000 Dossier sind derzeit bei der Post Sanela Health AG. Da braucht es Lösungen. Die Nachricht, dass die Post aussteigen wird, erreichte die Kommission mitten in der Beratung des Geschäftes. Wir liessen deshalb einen Zusatzbericht anfertigen. Dieser ist aber noch nicht eingetroffen - das war aber auch so geplant. Deshalb bittet Ihre Kommission den Ständerat, sich der Thematik des Anbieters nochmals anzunehmen. Der Ausstieg der Post aus dem EPD könnte auch Auswirkungen auf die Frage der Notwendigkeit einer neuen Ausschreibung haben, was schlussendlich auch zeitliche Konsequenzen haben würde. 
-Die Mehrheit Ihrer Kommission beantragt Ihnen mit 17 zu 8 Stimmen, auf die Vorlage einzutreten. Die Kommissionsmehrheit möchte Ihnen und wahrscheinlich auch der Bevölkerung ein Angebot machen, welches ein neues Dossier ermöglicht, das die Schwachstellen des EPD eliminiert. Es ist ein Dossier, bei dem die Patientinnen und Patienten selbst entscheiden können, wer darauf Zugriff hat, eines, das zentraler gesteuert ist, eines, das nicht die gleichen Fehler wiederholt, die beim EPD gemacht worden sind.
-Ich werde am Schluss noch auf die Minderheiten und den Einzelantrag eingehen. Ich überlasse jetzt gerne das Wort meinem Kommissionssprecher-Kollegen und hoffe, dass Sie ihn verstehen, weil mich haben Sie wahrscheinlich nicht verstanden.
+Der für 2026 vorgesehene Rückzug der Post Sanela Health AG muss so erfolgen, das ist die Meinung der Kommission, dass eine geordnete Migration zu Cara gewährleistet ist. Ich kann Ihnen sagen: 80[NB]000 Dossiers sind derzeit bei der Post Sanela Health AG. Da braucht es Lösungen. Die Nachricht, dass die Post aussteigen wird, erreichte die Kommission mitten in der Beratung des Geschäftes. Wir liessen deshalb einen Zusatzbericht anfertigen. Dieser ist aber noch nicht eingetroffen - das war aber auch so geplant. Deshalb bittet Ihre Kommission den Ständerat, sich der Thematik des Anbieters nochmals anzunehmen. Der Ausstieg der Post aus dem EPD könnte auch Auswirkungen auf die Frage der Notwendigkeit einer neuen Ausschreibung haben, was schlussendlich auch zeitliche Konsequenzen haben würde. 
+Ihre Kommission beantragt Ihnen mit 17 zu 8 Stimmen, auf die Vorlage einzutreten. Die Kommissionsmehrheit möchte Ihnen und wahrscheinlich auch der Bevölkerung ein Angebot machen, welches ein neues Dossier ermöglicht, das die Schwachstellen des EPD eliminiert. Es ist ein Dossier, bei dem die Patientinnen und Patienten selbst entscheiden können, wer darauf Zugriff hat, eines, das zentraler gesteuert ist, eines, das nicht die gleichen Fehler wiederholt, die beim EPD gemacht worden sind.
+Ich werde am Schluss noch auf die Minderheiten und den Einzelantrag eingehen. Ich überlasse jetzt gerne das Wort meinem Kommissionssprecher-Kollegen und hoffe, dass Sie ihn verstehen, denn mich haben Sie wahrscheinlich nicht verstanden.
 </t>
   </si>
   <si>
@@ -153,7 +154,7 @@
     <t xml:space="preserve">La motion vise à permettre aux personnes en procédure d'asile, aux bénéficiaires de l'aide sociale ou de prestations complémentaires d'être, en règle générale, tenues de choisir un modèle particulier d'assurance. La motion vise certes à déroger à la règle dans des cas exceptionnels.
 Il convient de préciser que, pour les requérants d'asile et pour les personnes à protéger sans autorisation de séjour, la Confédération et les cantons peuvent d'ores et déjà restreindre le choix de l'assureur, prescrire une forme particulière d'assurance et limiter le choix des fournisseurs de prestations. Cela permet de gérer l'accès au système de santé et d'utiliser les fonds publics de manière économique en garantissant des prix moins élevés. La charge administrative est aussi fortement réduite lorsque les soins de santé des requérants d'asile sont gérés par un seul assureur ou par un petit nombre d'assureurs.
 Les cantons peuvent également accorder une réduction de primes aux assurés dont la condition économique est modeste. Les cantons déterminent à la fois les bénéficiaires et le montant et peuvent fixer une prime de référence fondée, elle aussi, sur une assurance avec choix limité des fournisseurs de prestations. Il ne s'agit donc pas d'aborder la question de la réduction des primes, mais celle de la prime de référence, qui est basée sur une assurance avec choix limité. Pour le calcul des prestations complémentaires, la prime effective est prise en compte, mais au maximum à hauteur de la prime moyenne cantonale ou régionale. Les bénéficiaires de prestations complémentaires sont dès lors incités à choisir une prime appropriée.
-En résumé, les cantons sont largement compétents en matière de réduction des primes, de prestations complémentaires, d'aide sociale et d'impôts. Ils peuvent donc coordonner ces domaines de manière optimale. La Confédération n'est pas habilitée à édicter des prescriptions allant au-delà de ses propres compétences.
+En résumé, les cantons sont largement compétents en matière de réduction des primes, de prestations complémentaires, d'aide sociale et d'impôts. Ils peuvent donc coordonner ces domaines de manière optimale. La Confédération n'est pas habilitée à édicter des prescriptions allant au-delà de ses propres compétences. [GZ]
 Dès lors, je vous propose de rejeter la motion.
 </t>
   </si>
@@ -251,20 +252,22 @@
     <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. La mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion en fin d'année. Les objectifs du Conseil fédéral so</t>
   </si>
   <si>
-    <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. La mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion en fin d'année. Les objectifs du Conseil fédéral sont coordonnés avec le programme de législature de 2023 à 2027. Les priorités reposent sur quatre lignes directrices : la prospérité, la cohésion, la sécurité et la durabilité. Ces lignes directrices sont elles-mêmes subdivisées en 25 objectifs. 2027 sera la quatrième et dernière année de la présente législature et le Conseil fédéral a prévu un total de 140 mesures. 
-Je vais maintenant aborder les points forts de l'année à venir et je vais me concentrer sur certaines priorités des quatre lignes directrices. Tout d'abord, la première de ces lignes directrices, la prospérité. En ce qui concerne la place financière, le Conseil fédéral soumettra un message pour modifier la loi sur les banques. Pour garantir la stabilité financière, il s'agit de renforcer les dispositifs de prévention, de liquidité et de lutte contre les crises. S'agissant des relations avec l'Union européenne, le Conseil fédéral adoptera le message sur le financement d'une participation de la Suisse aux programmes de recherche et d'éducation. Ces fonds visent une participation au programme Horizon Europe et Erasmus plus pour les années 2028 à 2034. En matière d'économie, le Conseil fédéral présentera le message sur la promotion économique pour les années 2028 à 2031. Les priorités seront l'allègement administratif et la facilitation de l'accès aux marchés internationaux pour les petites et moyennes entreprises, les PME, ainsi que le renforcement des régions. Par ailleurs, le Conseil fédéral adoptera, l'année prochaine, des messages relatifs à la révision partielle de la loi fédérale sur la sécurité des produits et sur les entraves techniques au commerce, renforçant ainsi la protection des consommateurs. De plus, le Conseil fédéral adoptera des messages sur un nouvel accord de libre-échange avec le Vietnam et sur un nouvel accord sur le numérique avec Singapour. 
+    <t xml:space="preserve">La déclaration du président de la Confédération pour l'année à venir s'inscrit dans une longue tradition. Elle me donne l'occasion de vous présenter les priorités et les objectifs que le Conseil fédéral s'est fixés pour l'année prochaine. Ces objectifs permettent au Parlement de suivre l'action du Conseil fédéral tout au long de l'année et d'en apprécier les résultats. La mise en oeuvre fait ensuite l'objet d'un bilan dans le rapport de gestion en fin d'année. Les objectifs du Conseil fédéral sont coordonnés avec le programme de la législature de 2023 à 2027. Les priorités reposent sur quatre lignes directrices[NB]: la prospérité, la cohésion, la sécurité et la durabilité. Ces lignes directrices sont elles-mêmes subdivisées en 25 objectifs. 2027 sera la quatrième et dernière année de la présente législature et le Conseil fédéral a prévu un total de 140 mesures. 
+Je vais maintenant aborder les points forts de l'année à venir et je vais me concentrer sur certaines priorités des quatre lignes directrices. Tout d'abord, la première de ces lignes directrices, la prospérité.
+En ce qui concerne la place financière, le Conseil fédéral soumettra un message pour modifier la loi sur les banques. Pour garantir la stabilité financière, il s'agit de renforcer les dispositifs de prévention, de liquidité et de lutte contre les crises. S'agissant des relations avec l'Union européenne, le Conseil fédéral adoptera le message sur le financement d'une participation de la Suisse aux programmes de recherche et d'éducation. Ces fonds visent une participation aux programmes Horizon Europe et Erasmus plus pour les années 2028 à 2034. En matière d'économie, le Conseil fédéral présentera le message sur la promotion économique pour les années 2028 à 2031. Les priorités seront l'allègement administratif et la facilitation de l'accès aux marchés internationaux pour les petites et moyennes entreprises, les PME, ainsi que le renforcement des régions. Par ailleurs, le Conseil fédéral adoptera, l'année prochaine, des messages relatifs à la révision partielle de la loi fédérale sur la sécurité des produits et sur les entraves techniques au commerce, renforçant ainsi la protection des consommateurs. De plus, le Conseil fédéral adoptera des messages sur un nouvel accord de libre-échange avec le Vietnam et sur un nouvel accord sur le numérique avec Singapour. 
 Afin de coordonner le développement du rail, de la route et du trafic d'agglomération, le Conseil fédéral adoptera le message Transport '45. Son but est de développer le rail, la route et le trafic d'agglomération de manière ciblée et coordonnée, afin de répondre aux besoins de mobilité de la population et de l'économie. 
 Dans le domaine du numérique, le Conseil fédéral adoptera la loi sur le droit d'auteur aux évolutions de l'intelligence artificielle. Il lancera également une consultation pour l'adhésion à la Convention-cadre du Conseil de l'Europe sur l'intelligence artificielle et les droits de l'homme, la démocratie et l'État de droit. 
-J'en viens maintenant à la deuxième ligne directrice, la cohésion nationale. Pour ce qui est des affaires sociales, le Conseil fédéral présentera le message AVS 2030. Cette réforme vise à consolider les finances de l'assurance pour l'horizon 2030-2040 et à l'adapter aux évolutions de la société. Le Conseil fédéral adoptera également le message relatif à une révision de la loi fédérale sur l'assurance-invalidité. Cette réforme porte sur des mesures visant à garantir la stabilité financière et à renforcer la réinsertion professionnelle. 
+J'en viens maintenant à la deuxième ligne directrice, la cohésion nationale.
+Pour ce qui est des affaires sociales, le Conseil fédéral présentera le message AVS 2030. Cette réforme vise à consolider les finances de l'assurance pour l'horizon 2030-2040 et à l'adapter aux évolutions de la société. Le Conseil fédéral adoptera également le message relatif à une révision de la loi fédérale sur l'assurance-invalidité. Cette réforme porte sur des mesures visant à garantir la stabilité financière et à renforcer la réinsertion professionnelle. 
 En matière de santé, le Conseil fédéral adoptera le message relatif à une modification de la loi fédérale sur l'assurance-maladie portant sur l'adaptation de la franchise. L'objectif sera de réduire les coûts de la santé tout en favorisant la responsabilité individuelle des assurés. De plus, il mettra en oeuvre le principe du consentement présumé pour le don d'organes. 
 Dans le cadre de la consultation relative au message sur la promotion de la culture pour la période 2029 à 2032, le Conseil fédéral soumettra à la discussion les orientations stratégiques de la politique fédérale en matière de culture. 
 Pour ce qui est du marché du travail, le Conseil fédéral adoptera une stratégie nationale en matière de formation continue, de formation professionnelle et de formation de rattrapage pour favoriser l'entrée ou le retour en emploi.
-J'en viens maintenant à la troisième ligne directrice : la sécurité.
+J'en viens maintenant à la troisième ligne directrice, la sécurité.
 Pour garantir les effectifs de l'armée et de la protection civile, le Conseil fédéral ouvrira la consultation sur l'introduction d'une obligation de servir dans la sécurité. Le projet prévoit de fusionner le service civil et la protection civile au sein d'une nouvelle entité chargée de la protection contre les catastrophes.
 S'agissant de la sécurité, le Conseil fédéral ouvrira la consultation sur une révision des bases légales relatives à la protection des infrastructures critiques. Il s'agira notamment d'améliorer sensiblement l'efficacité de la protection et de clarifier les responsabilités et les procédures.
 En matière de migration, le Conseil fédéral élaborera avec les cantons, les villes et les communes des mesures pour améliorer le système d'asile suisse.
-Sur le plan de la politique extérieure, dans le cadre de la mise en oeuvre de la stratégie de coopération internationale 2025 à 2028, le Conseil fédéral décidera de l'octroi des contributions à l'Agence des Nations Unies pour les réfugiés et au Comité international de la Croix-Rouge pour les années 2027 et 2028.
-Enfin, j'en viens à la quatrième et dernière ligne directrice : la durabilité.
+Sur le plan de la politique extérieure, dans le cadre de la mise en oeuvre de la stratégie de coopération internationale de 2025 à 2028, le Conseil fédéral décidera de l'octroi des contributions à l'Agence des Nations Unies pour les réfugiés et au Comité international de la Croix-Rouge pour les années 2027 et 2028.
+Enfin, j'en viens à la quatrième et dernière ligne directrice, la durabilité.
 Concernant le climat, le Conseil fédéral présentera la révision de la loi sur le CO2 pour la période 2031 à 2040.
 En matière d'énergie, il adoptera une stratégie nationale sur l'efficacité énergétique qui permettra d'évaluer la consommation d'énergie et le potentiel d'efficacité dans les différents secteurs.
 Pour ce qui est de l'adaptation au changement climatique, le Conseil fédéral adoptera la stratégie Gestion de l'eau - périodes de sécheresse, fortes précipitations, qualité de l'approvisionnement en eau, protection des habitats aquatiques. Cette stratégie tiendra compte des politiques sectorielles concernées et mettra en évidence, le cas échéant, les adaptations juridiques nécessaires à la réalisation des objectifs.
@@ -281,14 +284,14 @@
     <t xml:space="preserve">Page Pierre-André</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale, chères et chers collègues, Mesdames, Messieurs, je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, M. Datouo, à la tribune de la salle du Conseil national.
-Monsieur le président, votre visite est un beau témoignage de l'amitié de longue date qui unit nos deux pays. En juillet dernier, j'ai eu le plaisir de vous rencontrer, vous ainsi que des représentantes et représentants du Parlement camerounais, à Yaoundé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale, chères et chers collègues, Mesdames, Messieurs, je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, M. Datouo, à la tribune de la salle du Conseil national.
+    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale, chères et chers collègues, Mesdames, Messieurs, je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, M.[NB]Datouo, à la tribune de la salle du Conseil national.
+Monsieur le président, votre visite est un beau témoignage de l'amitié de longue date qui unit nos deux pays. En juillet dernier, j'ai eu le plaisir de vous rencontrer, vous ainsi que des représentantes et représentants du Parlement camerounais, à Yaou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le président de l'Assemblée nationale, chères et chers collègues, Mesdames, Messieurs, je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, M.[NB]Datouo, à la tribune de la salle du Conseil national.
 Monsieur le président, votre visite est un beau témoignage de l'amitié de longue date qui unit nos deux pays. En juillet dernier, j'ai eu le plaisir de vous rencontrer, vous ainsi que des représentantes et représentants du Parlement camerounais, à Yaoundé, et je me réjouis de vous accueillir à mon tour, aujourd'hui, à Berne.
-J'aime à me souvenir du moment où nous avons décidé de votre venue en Suisse : nous avions visité le chantier de la nouvelle ambassade de Suisse à Yaoundé, et nous étions en train de déguster, dans votre bureau, des safous, que vous appelez aussi prunes, et c'est là que nous avons fixé la date de votre visite. Je suis heureux que nous soyons parvenus à nous revoir si rapidement.
-La Suisse et le Cameroun ont de nombreux points communs. Nos deux pays sont marqués par le multilinguisme et la diversité. Nous savons que le vivre-ensemble dans la diversité n'est pas toujours chose aisée : il doit être sans cesse réinventé, avec patience, respect et la volonté de s'écouter les uns les autres. Dialoguer régulièrement est donc indispensable. Nos parlements, aussi, entretiennent le dialogue avec succès, notamment parce que leurs liens sont humains. Tilo Frey, l'une des premières femmes à avoir été élues au Conseil national suisse en 1971 est née à Maroua au Cameroun et incarne encore aujourd'hui le lien qui unit nos deux pays. Notre coopération touche de nombreux domaines, allant de l'économie et du commerce à l'aide humanitaire, la promotion de la paix et la migration, en passant par la culture, la santé, l'agriculture, la science et même le football avec Breel Embolo.
+J'aime à me souvenir du moment où nous avons décidé de votre venue en Suisse[NB]: nous avions visité le chantier de la nouvelle ambassade de Suisse à Yaoundé, et nous étions en train de déguster, dans votre bureau, des safous, que vous appelez aussi prunes, et c'est là que nous avons fixé la date de votre visite. Je suis heureux que nous soyons parvenus à nous revoir si rapidement.
+La Suisse et le Cameroun ont de nombreux points communs. Nos deux pays sont marqués par le multilinguisme et la diversité. Nous savons que le vivre-ensemble dans la diversité n'est pas toujours chose aisée[NB]: il doit être sans cesse réinventé, avec patience, respect et la volonté de s'écouter les uns les autres. Dialoguer régulièrement est donc indispensable. Nos parlements, aussi, entretiennent le dialogue avec succès, notamment parce que leurs liens sont humains. Tilo Frey, l'une des premières femmes à avoir été élues au Conseil national suisse en 1971 est née à Maroua au Cameroun et incarne encore aujourd'hui le lien qui unit nos deux pays. Notre coopération touche de nombreux domaines, allant de l'économie et du commerce à l'aide humanitaire, la promotion de la paix et la migration, en passant par la culture, la santé, l'agriculture, la science et même le football avec Breel Embolo.
 Le nouveau bâtiment de l'ambassade de Suisse à Yaoundé, placé sous le signe de la durabilité, reflète clairement notre volonté de façonner les relations entre nos deux pays de manière durable.
 Monsieur le président de l'Assemblée nationale, je vous souhaite, au nom du Conseil national, la bienvenue à Berne, un agréable séjour et des discussions enrichissantes. (Standing ovation)
 </t>
@@ -312,7 +315,7 @@
     <t xml:space="preserve">Monsieur le président de l'Assemblée nationale,
 Chères et chers collègues, Mesdames, Messieurs,
 Je suis heureux d'accueillir aujourd'hui le président de l'Assemblée nationale du Cameroun, Monsieur Datouo, à la tribune de la salle du Conseil des États.
-Monsieur le président, votre visite témoigne des relations amicales qui unissent la Suisse et le Cameroun depuis de nombreuses années. Nos deux pays sont marqués par le multilinguisme et la diversité culturelle. Nous savons que le vivre-ensemble dans la diversité ne va pas toujours de soi : il doit être sans cesse réinventé, avec patience, respect mutuel et la volonté de s'écouter les uns les autres. Dans ce contexte, les échanges politiques et parlementaires réguliers sont indispensables.
+Monsieur le président, votre visite témoigne des relations amicales qui unissent la Suisse et le Cameroun depuis de nombreuses années. Nos deux pays sont marqués par le multilinguisme et la diversité culturelle. Nous savons que le vivre-ensemble dans la diversité ne va pas toujours de soi[NB]: il doit être sans cesse réinventé, avec patience, respect mutuel et avec la volonté de s'écouter les uns les autres. Dans ce contexte, les échanges politiques et parlementaires réguliers sont indispensables.
 Je saisis donc l'occasion de votre présence parmi nous pour remercier chaleureusement le Cameroun d'avoir accueilli la 51e session annuelle de l'Assemblée parlementaire de la Francophonie (APF), qui s'est tenue en juillet dernier à Yaoundé. Plusieurs membres de la délégation suisse auprès de l'APF y ont pris part et ont ainsi eu l'occasion d'échanger avec leurs homologues de l'espace francophone.
 Les relations entre nos deux pays s'étendent à de nombreux domaines, allant de l'économie et du commerce à l'aide humanitaire, la promotion de la paix et la migration, en passant par la culture, la santé et l'agriculture. Votre visite d'aujourd'hui nous permet d'approfondir nos échanges et, en particulier, de renforcer les relations entre nos parlements.
 Monsieur le président de l'Assemblée nationale, je vous souhaite, au nom du Conseil des États, la bienvenue à Berne, un agréable séjour et des discussions enrichissantes. (Applaudissements)
@@ -325,21 +328,21 @@
     <t xml:space="preserve">Juillard Charles</t>
   </si>
   <si>
-    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
-Notre société repose sur la cryp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple : comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple[NB]: comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
+Notre société repose sur la c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma motion porte sur un sujet encore trop peu visible, à mon avis, dans le débat public, mais qui concerne directement la sécurité de notre pays, de notre économie et de nos infrastructures. Nous parlons aujourd'hui de cryptographie post-quantique. Cela peut sembler très technique, mais en réalité, derrière ce terme se cache une question très simple[NB]: comment garantir que les données et les communications que nous protégeons aujourd'hui resteront protégées demain.
 Notre société repose sur la cryptographie. Les paiements électroniques, les communications de l'administration, les dossiers médicaux, les identités numériques, les signatures électroniques, les systèmes industriels ou encore les infrastructures critiques dépendent tous, à des degrés divers, de mécanismes cryptographiques. Or, certains des algorithmes de cryptographie à clé publique que nous utilisons actuellement pourraient être rendus vulnérables par des ordinateurs quantiques suffisamment puissants.
-Le problème est que nous ne pouvons pas attendre le jour où un ordinateur quantique capable de casser ses protections sera disponible pour commencer à agir. Pourquoi cela ? Parce que la migration cryptographique est un processus long, complexe et coûteux. Il faut identifier les systèmes concernés, comprendre leurs dépendances, vérifier les logiciels et les équipements, travailler avec les fournisseurs, tester les nouveaux mécanismes, garantir l'interopérabilité et, dans certains cas, remplacer des systèmes qui ont une durée de vie de dix, vingt ou trente ans. Autrement dit, le moment d'agir est avant que la menace ne devienne opérationnelle.
+Le problème est que nous ne pouvons pas attendre le jour où un ordinateur quantique capable de casser ses protections sera disponible pour commencer à agir. Pourquoi cela[NB]? Parce que la migration cryptographique est un processus long, complexe et coûteux. Il faut identifier les systèmes concernés, comprendre leurs dépendances, vérifier les logiciels et les équipements, travailler avec les fournisseurs, tester les nouveaux mécanismes, garantir l'interopérabilité et, dans certains cas, remplacer des systèmes qui ont une durée de vie de dix, vingt ou trente ans. Autrement dit, il faut agir avant que la menace ne devienne opérationnelle.
 Il existe également un risque, déjà présent aujourd'hui, de "moissonner maintenant pour déchiffrer plus tard". Des données peuvent être capturées aujourd'hui alors qu'elles sont encore correctement protégées. Si leurs valeurs ou leur caractère confidentiel perdurent pendant dix, vingt ou trente ans, elles pourraient être déchiffrées à l'avenir lorsque les capacités technologiques le permettront. Cela concerne notamment les informations de l'État, les données médicales, les données de recherche, les secrets industriels ou certaines informations liées à la sécurité nationale. Nous devons donc raisonner non seulement en fonction de la menace actuelle, mais aussi de la durée pendant laquelle une information doit rester confidentielle.
-C'est précisément ce que vise ma motion : ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de crypto-agilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
-C'est une question de cybersécurité, mais également une question de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et beaucoup plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
-Nos partenaires internationaux avancent : l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035 en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux : préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
-Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnait l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
+C'est précisément ce que vise ma motion[NB]: ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de cryptoagilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
+C'est une question de cybersécurité, mais également de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
+Nos partenaires internationaux avancent[NB]: l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035, en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux[NB]: préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
+Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnaît l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
 Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
-En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
-Je vous invite donc à soutenir ma motion sans la lettre i, comme demandé par le Conseil fédéral, et je vous en remercie.
+En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais, précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
+Je vous invite donc à soutenir ma motion sans la lettre i, comme le demande le Conseil fédéral, et je vous en remercie.
 </t>
   </si>
   <si>
@@ -968,8 +971,7 @@
     <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est d</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est donc possible juridiquement. Ma question rejoint un peu celle de mon prédécesseur. Pourquoi ne souhaitez-vous pas appuyer cette amélioration du système qui permettrait plus d'efficacité et ainsi une meilleure acceptation par la population de notre politique d'asile ?
-</t>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est donc possible juridiquement. Ma question rejoint un peu celle de mon prédécesseur. Pourquoi ne souhaitez-vous pas appuyer cette amélioration du système qui permettrait plus d'efficacité et ainsi une meilleure acceptation par la population de notre politique d'asile ?</t>
   </si>
   <si>
     <t xml:space="preserve">420623</t>
@@ -1148,6 +1150,534 @@
 J'ai été moi-même confronté à une problématique évidemment inquiétante, puisque nous avons des assureurs privés qui mènent une politique en invoquant les instructions qui leur sont données par la Finma, qui n'indiquent pas quelles sont ces instructions, parce qu'ils considèrent que la Finma leur interdit de le faire. Lorsque l'on demande à la Finma quelles sont ses instructions, elle se réfugie évidemment derrière le secret.
 Finalement, cette opacité sert donc à des mesures totalement incontrôlées par qui que ce soit, y compris par les tribunaux, puisque - je le répète - le fait de ne pas être soumis à la loi sur la transparence signifie que l'on ne peut même pas s'adresser à un tribunal pour qu'il puisse contrôler si le refus opposé par la Finma se fonde sur des intérêts supérieurs, qui existent évidemment, mais qui doivent au moins être invoqués. Ici, ce n'est pas le cas.
 Voilà la raison pour laquelle je vous demande d'adopter la motion, pour que cette exception, qui n'a pas plus de raison d'être que dans d'autres domaines sensibles de notre administration, soit enfin levée.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag SPK-N [GZ]
+Die Motion 23.3032 nicht abschreiben
+Schriftliche Begründung [GZ]
+Die Motion beauftragt den Bundesrat, konkrete Massnahmen zu ergreifen, um Algerien zur Rückübernahme seiner Staatsangehörigen im Rahmen von zwangsweisen Rückführungen zu bewegen. Die Kommission hat Kenntnis davon genommen, dass sich die Situation rund um die Rückführungen nach Algerien verbessert hat, die Zusammenarbeit mit diesem Land derzeit gut funktioniert und die algerischen Behörden bei der Rückübernahme al</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag SPK-N [GZ]
+Die Motion 23.3032 nicht abschreiben
+Schriftliche Begründung [GZ]
+Die Motion beauftragt den Bundesrat, konkrete Massnahmen zu ergreifen, um Algerien zur Rückübernahme seiner Staatsangehörigen im Rahmen von zwangsweisen Rückführungen zu bewegen. Die Kommission hat Kenntnis davon genommen, dass sich die Situation rund um die Rückführungen nach Algerien verbessert hat, die Zusammenarbeit mit diesem Land derzeit gut funktioniert und die algerischen Behörden bei der Rückübernahme algerischer Staatsangehöriger aus der Schweiz uneingeschränkt kooperieren. Doch auch wenn die Situation derzeit zufriedenstellend ist, gibt es keine Garantie dafür, dass dies auch so bleibt. Ein Regierungswechsel könnte ausreichen, um alles wieder infrage zu stellen. Die Kommission ersucht den Bundesrat daher, die Lage weiterhin aufmerksam zu verfolgen, damit er bei Anzeichen einer Verschlechterung unverzüglich die erforderlichen Massnahmen ergreifen kann. Daher ist an der Motion festzuhalten.
+[VS]
+Proposition CIP-N [GZ]
+Ne pas classer la motion 23.3032
+Développement par écrit [GZ]
+La motion charge le Conseil fédéral de prendre des mesures concrètes afin d'inciter l'Algérie à coopérer à la réadmission de ses ressortissants lors de renvois forcés. La commission a pris acte du fait que la situation en matière de retours en Algérie s'est améliorée, que la collaboration avec ce pays fonctionne bien à l'heure actuelle et que les autorités algériennes coopèrent pleinement à la réadmission des ressortissants algériens renvoyés de Suisse. Toutefois, même si la situation actuelle est satisfaisante, rien ne garantit que cela continuera d'être le cas à l'avenir. Un changement de gouvernement pourrait suffire à tout remettre en cause. La commission souhaite donc que le Conseil fédéral continue d'observer attentivement la situation afin de pouvoir prendre immédiatement les mesures nécessaires en cas de signes de détérioration. La motion doit par conséquent être maintenue.
+[VS]
+Le président (Page Pierre-André, président): Le Conseil fédéral se rallie à la proposition de la commission.[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Antrag GPK-N [GZ]
+Das Postulat 22.3508 nicht abschreiben
+Schriftliche Begründung [GZ]
+Der Bundesrat legt die verschiedenen Massnahmen dar, die er zur Erreichung der im Postulat festgelegten Ziele ergriffen hat. Der Bundesrat hat, wie gefordert, eine kritische Bewertung seiner Krisenorganisation vorgenommen und die Verordnung über die Krisenorganisation der Bundesverwaltung (KOBV) überarbeitet, die am 1. Februar 2025 in Kraft getreten ist. Auf dieser Grundlage hat er einen "Umsetzungsplan für die Basisorganisation im Rahmen der interdepartementalen Krisenorganisation der Bundesverwaltung" erstellt, der verschiedene Aspekte regelt, auf die die GPK in ihrem Bericht hingewiesen hat. Zudem trat 2025 die neue Verordnung über die Koordination im Sanitätsdienst in Kraft, womit die organisatorischen Grundlagen für die Reorganisation des Koordinierten Sanitätsdienstes geschaffen wurden. Schliesslich befasst sich der Entwurf zur Änderung des Epidemiengesetzes, den die GPK im Herbst 2025 im Rahmen eines Mitberichts zuhanden der SGK-S behandelt haben, mit Aspekten der Zusammenarbeit zwischen dem für das Krisenmanagement zuständigen Amt und den anderen Akteuren. Für die Kommission ist das Ziel des Postulates inhaltlich erreicht. Sie stellt jedoch fest, dass die GPK in ihrem Postulat ausdrücklich verlangt hatte, dass der Bundesrat das Ergebnis seiner Arbeiten in einem Bericht darlegt, was hier nicht der Fall ist. Die Kommission beantragt die Ablehnung des Antrages auf Abschreibung des Postulates, bis der "Bericht mit konkreten Empfehlungen zur Weiterentwicklung des nationalen Krisenmanagements" vorliegt, welchen der Bundesrat als Folge der Krisenübung vom November 2025 angekündigt hat (siehe Medienmitteilung des Bundesrates vom 7. November 2025). Darin dürften die wichtigsten Erkenntnisse und möglichen Massnahmen betreffend die Krisenorganisation enthalten sein. Ein solcher Bericht würde dem Begehren der GPK somit abschliessend Rechnung tragen.
+[VS]
+Proposition CdG-N [GZ]
+Ne pas classer le postulat 22.3508
+Développement par écrit [GZ]
+Le Conseil fédéral présente les différents travaux qu'il a menés afin de remplir les objectifs fixés par le postulat.
+Le Conseil fédéral a procédé, comme demandé, à une évaluation critique de son organisation de crise et a révisé l'ordonnance sur l'organisation de crise de l'administration fédérale (OCAF), entrée en vigueur le 1er février 2025. Sur cette base, il a établi un "Plan de mise en oeuvre de l'organisation de base dans le cadre de l'organisation de crise interdépartementale de l'administration fédérale" réglant différents aspects relevés par les CdG dans leur rapport. De plus, la nouvelle ordonnance sur la coordination dans le domaine du service sanitaire est entrée en vigueur en 2025, créant les bases organisationnelles requises pour la réorganisation du Service sanitaire coordonné. Enfin, le projet de modification de la loi sur les épidémies, que les CdG ont traité en automne 2025 dans le cadre d'un co-rapport à l'intention de la CSSS-E, aborde les aspects liés à la collaboration entre l'office chargé de la gestion de crise et les autres acteurs. Pour la commission, l'objectif du postulat est atteint au niveau du contenu. Cependant, elle note que la CdG avait explicitement demandé dans leur postulat que le Conseil fédéral fasse part du résultat de ses travaux dans un rapport, ce qui n'est pas le cas ici. La commission propose le rejet de la proposition de classement du postulat jusqu'à ce que soit disponible le "rapport avec des recommandations concrètes visant à renforcer la gestion de crise à l'échelle nationale" que le Conseil fédéral a annoncé à la suite de l'exercice intégré 2025 (cf. le communiqué de presse du Conseil fédéral du 7 novembre 2025). Ce rapport devrait contenir les principales conclusions et les mesures envisageables concernant l'organisation en cas de crise. Un tel rapport répondrait ainsi pleinement à la demande de la CdG.
+[VS]
+Le président (Page Pierre-André, président): Le Conseil fédéral se rallie à la proposition de la commission.[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Antrag der Mehrheit WAK-N [GZ]
+Die Motionen 19.3033 und 19.3043 abschreiben
+[VS]
+Antrag der Minderheit WAK-N [GZ]
+(Tuena, Bischof Edgar, Buffat, Burgherr, Hübscher, Nicolet, Pamini, Schnyder Markus)[GZ]
+Die Motionen 19.3033 und 19.3043 nicht abschreiben
+Schriftliche Begründung [GZ]
+Die Mehrheit der Kommission verweist auf die seit der Annahme der Motionen unternommenen Anstrengungen des Bundesrates zur Verbesserung der wirtschaftlichen Rahmenbedingungen. In Erfüllung der Motionen präsentierte der Bundesrat 2022 zwölf Vorhaben zur Stärkung des Wirtschaftsstandorts Schweiz, zu deren zehn bis Ende 2024 eine Botschaft vorlag. Darüber hinaus plant der Bundesrat auch weitere Massnahmen. Es ist nicht nötig, die beiden konkreten Motionen, die vor nunmehr sieben Jahren eingereicht wurden, weiterhin aufrecht zu erhalten, damit der Bundesrat seine Anstrengungen weiterverfolgt. Die Stärkung des Wirtschaftsstandortes ist ohnehin eine Daueraufgabe. Die Minderheit stellt nicht in Abrede, dass die Arbeiten des Bundesrats in die richtige Richtung zielen. Es sei jedoch wichtig, dass das Parlament die Forderung nach einer Offensive zur Stärkung des Wirtschaftsstandorts aufrechterhalte und dies durch die Nichtabschreibung der Motionen gegenüber dem Bundesrat kommuniziere. 
+[VS]
+Proposition de la majorité CER-N [GZ]
+Classer les motions 19.3033 et 19.3043
+[VS]
+Proposition de la minorité CER-N [GZ]
+(Tuena, Bischof Edgar, Buffat, Burgherr, Hübscher, Nicolet, Pamini, Schnyder Markus)[GZ]
+Ne pas classer les motions 19.3033 et 19.3043
+Développement par écrit [GZ]
+La majorité de la commission renvoie aux efforts entrepris par le Conseil fédéral, depuis l'adoption des motions, pour améliorer les conditions-cadres économiques. Le Conseil fédéral a présenté en 2022, en exécution des motions, douze projets pour renforcer la place économique suisse, dont dix ont fait l'objet d'un message avant la fin de l'année 2024. Le Conseil fédéral prévoit en outre d'autres mesures. Pour la majorité de la commission, il n'est donc plus nécessaire de maintenir ces deux motions, déposées il y a désormais sept ans, pour que le Conseil fédéral poursuive ses efforts. Elle considère par ailleurs que le renforcement de la place économique est de toute façon une tâche permanente. 
+La minorité ne conteste pas que les travaux du Conseil fédéral vont dans la bonne direction. Elle juge néanmoins important que le Parlement maintienne sa demande adressée au gouvernement de prendre des mesures visant à accroître le dynamisme de la place économique suisse et qu'il le fasse savoir au Conseil fédéral en ne classant pas ces motions. 
+[VS]
+Le président (Page Pierre-André, président): Le Conseil fédéral se rallie à la proposition de la minorité Tuena. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walti Beat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was wir hier diskutieren, wurde als mehr oder weniger technische, statistische Anpassung der Methode des Einkommensvergleichs bei den landwirtschaftlichen Einkommen präsentiert. In Tat und Wahrheit liegt dahinter aber eine politisch relevante Verschiebung der Zielsetzungen dieser Fragestellung.
+Es gibt verschiedene Gründe, weshalb ich Ihnen empfehle, die Motion abzulehnen. Zuerst wurde kritisiert, dass die Methodik des Einkommensvergleichs schon deshalb falsch sei, weil nicht Gleiches mit Gleich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was wir hier diskutieren, wurde als mehr oder weniger technische, statistische Anpassung der Methode des Einkommensvergleichs bei den landwirtschaftlichen Einkommen präsentiert. In Tat und Wahrheit liegt dahinter aber eine politisch relevante Verschiebung der Zielsetzungen dieser Fragestellung.
+Es gibt verschiedene Gründe, weshalb ich Ihnen empfehle, die Motion abzulehnen. Zuerst wurde kritisiert, dass die Methodik des Einkommensvergleichs schon deshalb falsch sei, weil nicht Gleiches mit Gleichem - die Einkommen der Selbstständigerwerbenden mit den Einkommen der Angestellten des zweiten und dritten Sektors - verglichen werde. Dies ist nicht bösem Willen, sondern mangelnder Datenlage geschuldet. Weil für die Einkommen von Selbstständigerwerbenden im Allgemeinen nicht genügend Daten vorhanden sind, muss mit etwas anderem verglichen werden. Das ist aber kein grosses Problem, weil es fast interessanter ist, die Dynamik der Einkommensentwicklung zu beobachten als die absoluten Unterschiede. Es ist die Zielsetzung, die Einkommensentwicklung zu beobachten und sicherzustellen, dass die Landwirtschaft gegenüber den Vergleichsgrössen nicht abfällt. Mit der heute angewandten Methodik kann man dies durchaus erreichen. Artikel 5 des Landwirtschaftsgesetzes verlangt, dass die Einkommenssituation der ökonomisch leistungsfähigen Betriebe verglichen wird. Dahinter steht ein Bestreben, das die Landwirtschaftspolitik ebenfalls prägt, nämlich eine auch im ökonomischen Sinne nachhaltig funktionierende Landwirtschaft zu fördern. Die Betriebe sollen in der Lage sein, Investitionen in die zukünftige Betriebsstruktur zu finanzieren, und sie sollen kräftig genug sein, um die Zukunft auch ökonomisch zu überleben. Es ist richtig, als Massstab die leistungsfähigen Betriebe heranzuziehen und nicht einfach den Durchschnitt. Das ist übrigens etwas, was man in anderen Bereichen auch macht, zum Beispiel im Gesundheitswesen. Bei der Festlegung von Spitaltarifen orientiert sich der Regulator auch an den leistungsfähigen Betrieben und nicht einfach am Durchschnitt. Unter Massgabe der heutigen landwirtschaftlichen Gesetzgebung - insbesondere des erwähnten Artikel 5 - macht die Regel, die Vergleichsgrösse beim dritten Quartil zu belassen und nicht einfach auf den Median zurückzugreifen, also durchaus Sinn.
+Schliesslich geht es darum - das ist das gesetzgeberische Element der Kritik bzw. der Grund, weshalb diese Motion gegenwärtig nicht angezeigt erscheint -, dass wir ohnehin in absehbarer Zeit in diesem Saal die Agrarpolitik 2030 plus beraten werden und Themen, die in die ökonomische Grundlogik der Landwirtschaftspolitik eingreifen, nicht im Voraus isoliert bearbeitet werden sollten, wie das mit anderen Themen leider auch schon passiert ist. Vielmehr sollten wir den ganzen Fächer der Fragestellungen insgesamt beurteilen können. Nur so können wir auch in Zukunft eine konsistente Landwirtschaftspolitik bis hin zur richtigen Organisation und Steuerung der umfangreichen Transferleistungen sicherstellen. In diesem Zusammenhang bzw. im Zusammenhang mit dem Thema dieser Motion erinnere ich daran, dass etwa 60 Prozent der landwirtschaftlichen Einkommen auf Transferleistungen beruhen. Es ist richtig, die Anpassung von Artikel 5 des Landwirtschaftsgesetzes konsistent und umsichtig vorzunehmen und diesen nicht einfach so hinzubiegen, damit es kurzfristig etwas günstiger aussieht.
+In diesem Sinne bitte ich Sie, die Motion nicht zu unterstützen, sondern das Thema dann anzugehen, wenn wir das ganze Spektrum bearbeiten, und freue mich, wenn Sie meine Minderheit unterstützen. Grazie per la vostra attenzione. Grazia fitg.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, le représentant de l'Union démocratique du centre va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la commune fusionne et devient Tr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, le représentant de l'Union démocratique du centre va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la commune fusionne et devient Tresa, il conserve le poste de syndic jusqu'à aujourd'hui et son entrée au gouvernement tessinois. En 2013, il prend la vice-présidence de l'Union démocratique du centre tessinoise, qu'il présidera ensuite pendant 10 ans, de 2016 à aujourd'hui. L'année 2019 marque un tournant dans sa carrière politique, avec son élection au Grand Conseil tessinois qu'il quittera la même année après son élection au Conseil national. Depuis son entrée en fonction au Conseil national, il est membre de la Commission des institutions politiques et de la Délégation pour les relations avec le Parlement italien. Il siégera par la suite également au sein de la Commission de rédaction de langue italienne, de la Commission de politique extérieure, ainsi que de la Commission de la politique de sécurité.
+Entrepreneur et électricien de formation, il s'engage particulièrement au sein de notre institution en faveur d'un État moins bureaucratique et pour des conditions-cadres favorables aux entreprises en déposant plusieurs interventions allant dans ce sens. Il a également consacré plusieurs de ses interventions parlementaires à la politique migratoire et d'asile, aux questions de sécurité et à la défense des intérêts du canton du Tessin.
+Plusieurs de ses motions ont été adoptées par le Parlement. Nous pouvons citer la motion 21.4076, "Permis de séjour. Rétablir le principe du centre des intérêts". Plus récemment, les Chambres fédérales ont adopté sa motion 25.4013, "Renforcer la sécurité du personnel ferroviaire et des passagers", qui doit conduire à la présentation d'un plan national visant à renforcer la sécurité dans les trains, ainsi que sa motion 25.3438, "Lutte contre le phénomène préoccupant des faux documents en Suisse", qui vise à renforcer le contrôle de l'authenticité des documents d'identité. Enfin, nous avons également adopté sa motion 23.4166, "Mettre fin à la vente en ligne des jouets dangereux pour la santé", qui doit encore être examinée par le Conseil des États.
+Après les spéciales communale, cantonale et fédérale, Piero Marchesi, ancien pilote de rallye, amorce un nouveau virage et se trouve au départ d'une nouvelle étape, l'exécutif cantonal. Nous le remercions pour son engagement au sein de notre conseil et lui souhaitons plein succès dans ses nouvelles fonctions. Et bien entendu, bonne route, Piero ! (Standing ovation; le président remet un bouquet de fleurs à M. Marchesi)[GZ]
+[VS][GZ]
+[VS][GZ]
+[VS][GZ]
+Schluss der Sitzung um 12.50 Uhr [GZ]
+La séance est levée à 12 h 50
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binder-Keller Marianne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative populaire "pour un droit de la nationalité moderne (l'initiative pour la démocratie)" a été déposée le 21 novembre 2024. Cette initiative en faveur d'un droit de la nationalité moderne préconise une réglementation nationale uniforme en matière de naturalisation ordinaire. Elle vise à supprimer les disparités cantonales, à renforcer la transparence et à garantir l'égalité des chances pour tous les candidats, quel que soit leur lieu de résidence. Les conditions de naturalisation doive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative populaire "pour un droit de la nationalité moderne (l'initiative pour la démocratie)" a été déposée le 21 novembre 2024. Cette initiative en faveur d'un droit de la nationalité moderne préconise une réglementation nationale uniforme en matière de naturalisation ordinaire. Elle vise à supprimer les disparités cantonales, à renforcer la transparence et à garantir l'égalité des chances pour tous les candidats, quel que soit leur lieu de résidence. Les conditions de naturalisation doivent être considérablement assouplies afin de permettre à un plus grand nombre de personnes vivant en Suisse de participer au processus démocratique et aux décisions politiques.
+Die Aufenthaltsdauer von Menschen, die sich in der Schweiz einbürgern wollen, sinkt so von zehn auf fünf Jahre, und eine Niederlassungsbewilligung ist nicht mehr erforderlich. So erhalten Personen den Schweizer Pass, deren Aufenthalt in der Schweiz weniger dauerhaft als bis anhin und weniger gefestigt ist. Des Weiteren sollen auch Integrationsanforderungen reduziert werden. Das bedeutet, dass leichtere strafrechtliche Verurteilungen, also wenn keine Verurteilung zu einer längerfristigen Freiheitsstrafe vorliegt, oder das Beziehen von Sozialhilfe künftig keine Ausschlusskriterien mehr darstellen sollen. Durch die Initiative werden die geltenden kantonalen Kompetenzen abgeschafft. Die Initiative will dem Bundesrat - dem Bund - die Kompetenz überweisen, die ordentliche Einbürgerung abschliessend zu regeln. Der Nationalrat hat sich als Erstrat mit einer Zweidrittelmehrheit gegen die Initiative entschieden. Er will das Schweizer Einbürgerungsverfahren weder vereinheitlichen noch vereinfachen; auch Minderheitsanträge lehnte er ab.
+La nostra commissione ha discusso l'iniziativa nel corso di due sedute. Ha chiesto all'amministrazione diversi chiarimenti. Tuttavia, analogamente al Consiglio federale, giunge alla conclusione che le competenze e i requisiti vigenti in materia di naturalizzazione si sono dimostrati validi e non dovrebbero essere modificati.
+La Commissione delle istituzioni politiche vi invita a raccomandare il rigetto dell'iniziativa, con 12 voti contro 1. Inoltre, la maggioranza della commissione non intende presentare né un controprogetto diretto né una controproposta indiretta all'iniziativa.
+Die Initiative geht gemäss der Kommission zu weit. Die deutliche Verkürzung der Mindestaufenthaltsdauer von zehn auf fünf Jahre und auch der Verzicht auf kantonale und kommunale Mindestaufenthaltsfristen führen zur Einbürgerung von Personen, deren Aufenthalt gemäss der Einschätzung der Kommission wenig gefestigt ist. Des Weiteren findet sie, dass das Vertrautsein mit den schweizerischen Lebensverhältnissen nicht mehr gegeben ist, wenn die Integrationskriterien wegfallen; damit würde eine zentrale Voraussetzung des geltenden Rechts entfallen. Des Weiteren sind die Zuständigkeiten von Bund, Kantonen und Gemeinden klar geregelt. Die Bundeskompetenzen sind gemäss Artikel 38 der Bundesverfassung relativ eng gefasst und sollten nicht ausgeweitet werden. Die Kantone müssten weiterhin Spielraum für zusätzliche Bedingungen, zum Beispiel Integrationsnachweise, und die bewährten Verfahren der Gemeindeabstimmungen behalten. Auch Rechtsgutachten warnen vor einer unzulässigen Aushöhlung der kommunalen und kantonalen Zuständigkeiten. Des Weiteren wurde moniert, dass die Anforderungen an die Sprachkompetenzen zumutbar und als Integrationskriterium wichtig seien.
+Sie sehen auf der Fahne auch die drei Minderheitsanträge: Die Initiative soll zwar abgelehnt, es soll ihr aber ein direkter Gegenvorschlag gegenübergestellt werden; die Minderheitsvertreter werden dies selber begründen. Deshalb komme ich nur summarisch zu den Argumenten der Minderheiten. Sie fanden, dass die bisherigen Einbürgerungskriterien zu restriktiv seien und insbesondere auch gut integrierte Personen mit Migrationshintergrund in handwerklichen Berufen benachteiligen würden. So könnten die geforderten Sprachprüfungen, mündlich B2 und schriftlich A1, bildungsferne, aber gesellschaftlich gut integrierte Gruppen ausschliessen. Angesichts des Fachkräftemangels und der Steuerleistungen wurde bei langjährig ansässigen Personen eine Liberalisierung als gerechtfertigt erachtet, wobei auch auf positive internationale Erfahrungen verwiesen wurde. Ausserdem wurde betont, dass eine nationale Vereinheitlichung kantonale Unterschiede abbauen, die Chancengleichheit erhöhen und durch tiefere Hürden eine breitere demokratische Partizipation ermöglicht würde, ohne die Gemeinden zu entmachten. Für die Umsetzung der drei Minderheitsanträge wäre daher eine Verfassungsänderung erforderlich.
+Die Kommissionsmehrheit empfiehlt die Initiative ohne direkten Gegenentwurf zur Ablehnung. Daneben wurden besagte Minderheitsanträge formuliert, die Minderheiten werden ihre Positionen selbst vertreten. Hier in Kürze: Es gibt eine Minderheit I (Moser), die für einen Gegenentwurf plädiert, der die erleichterte Einbürgerung von Personen der zweiten und dritten Ausländergeneration vorsieht. Die Minderheit II (Zopfi) fordert einen Gegenentwurf mit einer erleichterten Einbürgerung für Personen, die sich vor Vollendung ihres 16. Lebensjahres mindestens 5 Jahre rechtmässig und ununterbrochen in der Schweiz aufgehalten haben. Dann gibt es eine Minderheit III (Maillard Pierre-Yves), die im Gegenentwurf die erleichterte Einbürgerung für ausländische Personen beantragt, die sich seit insgesamt 25 Jahren rechtmässig in der Schweiz aufhalten, wobei das Gesetz Ausnahmen für junge in der Schweiz aufgewachsene Personen vorsehen kann. Am Schluss ist noch der Einzelantrag Fivaz Fabien zu erwähnen, der die Annahme der Initiative empfehlen will.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moser Tiana Angelina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette initiative va loin. Elle va trop loin. Je suis toutefois convaincue qu'il est nécessaire d'agir. C'est pourquoi, au nom de ma minorité, je vous propose de faciliter la naturalisation pour les étrangers de la deuxième génération.
+Die Schweiz hat einen Ausländeranteil von rund 25 Prozent, aber eine Einbürgerungsquote, die doch relativ tief liegt, bei nur 1,9 Prozent. Das schafft ein Demokratiedefizit in einem Ausmass, dass man es durchaus hinterfragen darf, ja hinterfragen muss. Viele Mensch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette initiative va loin. Elle va trop loin. Je suis toutefois convaincue qu'il est nécessaire d'agir. C'est pourquoi, au nom de ma minorité, je vous propose de faciliter la naturalisation pour les étrangers de la deuxième génération.
+Die Schweiz hat einen Ausländeranteil von rund 25 Prozent, aber eine Einbürgerungsquote, die doch relativ tief liegt, bei nur 1,9 Prozent. Das schafft ein Demokratiedefizit in einem Ausmass, dass man es durchaus hinterfragen darf, ja hinterfragen muss. Viele Menschen, die hier leben, arbeiten und Steuern zahlen, können nicht mitbestimmen. Viele von ihnen sind aber vollumfänglich integriert und auch absolut Teil unserer Gesellschaft. 2017 hat die Stimmbevölkerung ein schlankeres Verfahren für die dritte Ausländergeneration geschaffen. Wer in dritter Generation hier lebt, kann sich heute erleichtert einbürgern lassen. Das hat sich bewährt. 
+Die erleichterte Einbürgerung gilt aber heute nicht für die zweite Generation, und das möchte ich mit meinem Minderheitsantrag angehen. Derzeit leben in der Schweiz über 450 000 Ausländerinnen und Ausländer, die hier geboren sind. Sie sind hier zur Schule gegangen, sie machen im Sportclub mit, sie singen im Chor, sie engagieren sich in Vereinen; die Schweiz ist ihre Heimat. Wollen sie sich einbürgern lassen, müssen sie aber heute je nach Wohnort ein langes und oft sehr aufwendiges Verfahren durchlaufen. Heute gelten je nach Kanton sehr unterschiedliche kantonale und kommunale Wohnsitzfristen. In einigen Kantonen genügen zwei Jahre, in vielen sind es fünf. Bei denen, die umziehen, beginnt die Frist unter Umständen einfach von Neuem. Das trifft zum Beispiel Familien, die wegen einem neuen Job eines Elternteils den Kanton wechseln, aber beispielsweise auch junge Erwachsene, die für das Studium umziehen. Gerade in der kleinräumigen Schweiz sind bestehende Anforderungen schwer nachvollziehbar. Wer den Grossteil der Schulzeit in der Schweiz verbracht hat, sollte nicht dafür bestraft werden, dass die Eltern den Wohnort gewechselt haben. 
+Mit einem Wechsel zu einer erleichterten Einbürgerung würden wir eben genau für diese zweite Generation bürokratische Hürden abbauen. Im Gegensatz zur Initiative sollen die bisherigen Anforderungen an die Integration vollständig gelten. Wer sich einbürgern lassen will, muss selbstverständlich die Rechtsordnung einhalten und die Werte der Bundesverfassung respektieren. Er oder sie muss eine Landessprache beherrschen und auch die finanziellen Verpflichtungen erfüllen. Eine erfolgreiche Integration bleibt somit auch bei Personen der zweiten Generation Voraussetzung. 
+Der Gegenvorschlag ist ein moderater Schritt. Er vereinfacht das Verfahren, aber senkt die Anforderungen an die Integration nicht. Ich möchte Sie deshalb bitten, dem Antrag meiner Minderheit zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative pour la démocratie vise à uniformiser les conditions de la naturalisation ordinaire et à confier la compétence définitive en la matière à la Confédération. Concrètement, elle prévoit un droit à la naturalisation pour toute personne qui séjourne légalement en Suisse depuis cinq ans, dispose des connaissances de base dans une langue nationale, n'a pas été condamnée à une peine privative de liberté de longue durée et ne représente pas une menace pour la sécurité intérieure ou extérieur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'initiative pour la démocratie vise à uniformiser les conditions de la naturalisation ordinaire et à confier la compétence définitive en la matière à la Confédération. Concrètement, elle prévoit un droit à la naturalisation pour toute personne qui séjourne légalement en Suisse depuis cinq ans, dispose des connaissances de base dans une langue nationale, n'a pas été condamnée à une peine privative de liberté de longue durée et ne représente pas une menace pour la sécurité intérieure ou extérieure de la Suisse.
+Als Präsidentin unserer Kommission spreche ich für die Mehrheit. Die Initiative würde das heutige System der Einbürgerung in wesentlichen Punkten verändern. Die Mehrheit der Kommission beantragt Ihnen deshalb, wie es von der Kommissionssprecherin ausgeführt wurde, die Initiative ohne Gegenvorschlag abzulehnen. 
+Warum? Es geht um die Frage, ob die Einbürgerung der Beginn oder der Abschluss einer erfolgreichen Integration sein soll. Für die Kommissionsmehrheit ist es klar: Die Einbürgerung soll am Ende eines erfolgreichen Integrationsprozesses stehen. Ein rechtmässiger Aufenthalt und Grundkenntnisse einer Landessprache sind wichtige Voraussetzungen. Sie allein reichen aber nicht aus. Wer Schweizerbürgerin oder -bürger werden möchte, soll mit den schweizerischen Lebensverhältnissen vertraut sein, die Werte unserer Bundesverfassung respektieren und sich im Alltag in einer Landessprache verständigen können. Diese Integrationskriterien sind aus Sicht der Kommissionsmehrheit zentral. 
+Ein weiterer Punkt ist der vorgesehene Rechtsanspruch nach fünf Jahren. Ein solcher Anspruch würde die Einbürgerung wesentlich stärker an die Aufenthaltsdauer knüpfen. Ein rechtmässiger Aufenthalt allein sagt jedoch noch nichts darüber aus, ob eine Person tatsächlich erfolgreich integriert ist. Deshalb soll auch künftig im bewährten System zwischen Gemeinden, Bund und Kantonen eine umfassende Prüfung der Integration möglich sein. 
+Ein anderer zentraler Punkt - jetzt komme ich zur Zusammenarbeit zwischen den Staatsebenen - ist der Föderalismus. Heute sind Bund, Kantone und Gemeinden gemeinsam am Einbürgerungsverfahren beteiligt. Die Initiative möchte die abschliessende Kompetenz beim Bund konzentrieren. Die Kommissionsmehrheit anerkennt, dass die heutigen Verfahren nicht überall gleich ausgestaltet sind - das haben wir diskutiert, auch im Zusammenhang mit einem Postulatsbericht des Bundesrates -, dass es zwischen Kantonen und Gemeinden Unterschiede gibt und dass dies zu unnötigen Hürden führen kann. Die Kommission hat festgestellt, dass hier Handlungsbedarf besteht, und der Bundesrat hat uns versichert, dass er diese Aufgaben angehe bzw. dass man schon an der Arbeit sei.
+Die richtige Antwort auf diese Herausforderungen oder Fragen ist aus unserer Sicht aber nicht die vollständige Zentralisierung des Bürgerrechts; Harmonisierung ja, Zentralisierung nein. Wir können Verfahren vereinfachen, transparenter gestalten und unnötige Unterschiede abbauen, ohne die bewährte föderale Zuständigkeit aufzugeben.
+Gerade bei der Wohnsitzpflicht zeigt sich, dass unter Umständen Verbesserungen sinnvoll sind. Für den Fall, dass eine Person gut integriert ist und die Voraussetzungen für eine Einbürgerung erfüllt, sollte die Frage des Gemeindewohnsitzes vielleicht angeschaut werden. Wir können das heutige System verbessern. Es gibt auch bei der Rechtssicherheit Ansatzpunkte.
+Die Kommissionsmehrheit ist durchaus bereit, das heutige Einbürgerungsverfahren weiterzuentwickeln, auf Grundlage der Vorschläge, die uns der Bundesrat in Aussicht gestellt hat. Aber Weiterentwicklung bedeutet nicht die Senkung der Anforderungen. Mit der Demokratie-Initiative würden die Voraussetzungen für die Einbürgerung deutlich verändert, die Zuständigkeiten zwischen Bund, Kantonen und Gemeinden grundlegend neu geordnet. Die Kommissionsmehrheit ist überzeugt, dass es dafür keinen Systemwechsel braucht. Wir können, ich wiederhole mich, die bestehenden Schwachstellen beheben, ohne die Integrationsanforderungen zu reduzieren und ohne den Föderalismus beim Bürgerrecht aufzugeben. Wo kennt man die Personen am besten, die sich einbürgern lassen wollen, als in der Gemeinde, dem Ort, wo sie wohnen?
+Ich bitte Sie deshalb, der Mehrheit zu folgen und die Initiative zur Ablehnung zu empfehlen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signor presidente, gentili consigliere e consiglieri agli Stati, stimà signur president dal Cussegl dals chantuns, stimadas cusseglieras e stimads cussegliers, comme vous le savez, le Conseil fédéral recommande le rejet de l'initiative pour la démocratie. D'une part, cette initiative remettrait en cause la répartition des compétences entre la Confédération, les cantons et les communes, qui a fait ses preuves. D'autre part, elle vise à assouplir considérablement les conditions de naturalisation e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signor presidente, gentili consigliere e consiglieri agli Stati, stimà signur president dal Cussegl dals chantuns, stimadas cusseglieras e stimads cussegliers, comme vous le savez, le Conseil fédéral recommande le rejet de l'initiative pour la démocratie. D'une part, cette initiative remettrait en cause la répartition des compétences entre la Confédération, les cantons et les communes, qui a fait ses preuves. D'autre part, elle vise à assouplir considérablement les conditions de naturalisation et à instaurer un droit à la naturalisation.
+Nach Ansicht des Bundesrates hat sich die Dreistufigkeit des Bürgerrechts bewährt. Er möchte daher an den Kompetenzen der jeweiligen Staatsebene festhalten. Der Bundesrat möchte auch die Voraussetzungen für die Einbürgerungen nicht lockern. Er hat darum beschlossen, die Initiative ohne direkten Gegenvorschlag zur Ablehnung zu empfehlen.
+Im Auftrag Ihres Rates hat der Bundesrat die Gründe für die tiefe Einbürgerungsquote der zweiten Generation untersucht. Der Postulatsbericht zeigt, dass erstens aufwendige Verfahren und zweitens hohe Gebühren für Menschen der zweiten Generation die grössten Hindernisse sind, sich hier einbürgern zu lassen. Insbesondere Menschen mit tiefem Bildungsstand und geringem Einkommen werden dadurch abgehalten, den Einbürgerungsweg überhaupt auf sich zu nehmen. Der Bundesrat hat deshalb die Kantone eingeladen, gemeinsam Möglichkeiten zu prüfen, wie die Einbürgerungsverfahren vereinfacht, allenfalls harmonisiert werden können. Ein erster Austausch mit Kantonen und grossen Städten zur aktuellen Einbürgerungspraxis und zur künftigen Zusammenarbeit hat im März stattgefunden. Ziel ist es, sich über bewährte Praktiken auszutauschen und bürokratische Hürden zu überprüfen - eben ohne die bestehenden Kompetenzverteilungen oder die gesetzlichen Grundlagen zu ändern. Die Initiative würde an diesen Grundlagen rütteln, die Gegenvorschläge auch, deshalb lehnt sie der Bundesrat ab.
+Il Consiglio federale si oppone al trasferimento di competenze alla Confederazione e all'abbassamento delle condizioni per la naturalizzazione. Il Consiglio federale raccomanda di respingere l'iniziativa, senza controprogetto diretto o indiretto.
+Il Cussegl federal s'oppona al transfer da cumpetenzas a la Confederaziun ed a la reducziun da las cundiziuns per la natiralisaziun. Il Cussegl federal propona da refusar l'iniziativa senza ina cuntraproposta directa u indirecta.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zopfi Mathias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stimà signur president, stimà signur cusseglier federal, stimadas damas e stimads signurs, Sie wissen, ich bin Präsident des Schweizerischen Gemeindeverbandes, und der Gemeindeverband ist gegenüber dieser Initiative sehr skeptisch. Dies, weil die grundsätzliche Zuständigkeit der Gemeinden im Einbürgerungsverfahren mit der Demokratie-Initiative sehr stark abgeändert würde. Aber ich muss auch sagen, dass ich mit der Problemanalyse, die dieser Initiative zugrunde liegt, in weiten Teilen einverstand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stimà signur president, stimà signur cusseglier federal, stimadas damas e stimads signurs, Sie wissen, ich bin Präsident des Schweizerischen Gemeindeverbandes, und der Gemeindeverband ist gegenüber dieser Initiative sehr skeptisch. Dies, weil die grundsätzliche Zuständigkeit der Gemeinden im Einbürgerungsverfahren mit der Demokratie-Initiative sehr stark abgeändert würde. Aber ich muss auch sagen, dass ich mit der Problemanalyse, die dieser Initiative zugrunde liegt, in weiten Teilen einverstanden bin. Ich meine, dass sie einen sehr wunden Punkt in unserem Staatswesen, in unserem System anspricht. Ich möchte hier vor allem zwei Gründe anführen: 
+1. Das heutige System ist zu streng, unnötig streng. Wie wir wissen, kennen wir heute Erleichterungen für die Einbürgerung der dritten Generation. Wir wissen aber auch, dass der praktische Vollzug oder die Probleme, die sich aus dem heutigen System ergeben, dazu führen, dass Leute, die wir eindeutig zu dieser Generation zählen würden, die einer erleichterten Einbürgerung würdig ist, gar nicht zu dieser Generation gezählt werden. Ich kenne einige Beispiele von Kolleginnen und Kollegen, von denen ich gedacht hätte, dass sie einer Generation angehören, die erleichtert eingebürgert werden kann. Sie können das zum Teil aber nicht, weil vielleicht der Grossvater oder der Vater als Saisonnier in der Schweiz war, sodass beim Schulbesuch irgendwo eine Lücke entstanden ist usw. Sie kennen diese Problematik. 
+2. Studien zeigen, dass das heutige System Menschen benachteiligt, die schulisch weniger gebildet sind, die vielleicht eher in handwerklichen Beruf tätig sind und nicht dieselben finanziellen Möglichkeiten haben wie andere. Ich meine, dass das nicht nur nicht gerecht ist, sondern dass es auch überhaupt nicht in unserem Sinn ist, eine solche Unterscheidung zu machen. 
+Ich möchte zuerst auf den finanziellen Aspekt eingehen: Beim Einbürgerungswesen geht es ja nicht darum, den Staat zu bereichern; eine grosse Einnahmequelle stellt es nicht dar. Gleichzeitig gibt es aber in der Schweiz gerade in wichtigen Funktionen, etwa in handwerklichen Berufen, viele Menschen, die den Schweizer Pass nicht haben. Diese handwerklichen Berufe sind notabene jene Berufe, die wahrscheinlich nicht einfach so von der KI wegrationalisiert werden können - wie dies zum Beispiel in meinem Beruf als Anwalt und Notar zu gewissen Teilen vermutlich viel eher möglich sein wird. In diesen Berufen haben wir Menschen, die faktisch den Weg der Einbürgerung nicht mehr beschreiten.
+Man könnte jetzt sagen, das ist ja deren eigenes Problem, sie müssen das ja nicht, sie können diesen Weg beschreiten - und wenn es ihnen zu teuer ist, dann ist das auch nicht unser Problem. 
+Aber ich möchte noch auf den zweiten Aspekt kommen, nämlich den demokratischen Aspekt. Es ist eben nicht nur aus Sicht jener, die sich einbürgern lassen wollen, sondern auch aus Sicht der Gesellschaft und des Staats wünschenswert und positiv, wenn Einbürgerungen stattfinden. Die Schweiz ist ein Einwanderungsland. Weltweit erbringen Gesellschaften in Einwanderungsländern eine starke Integrationsleistung - das grosse Beispiel sind die USA, und Sie wissen, wie dort eingebürgert wird. Diese Gesellschaften sind sehr stark integrativ, weil sonst im Verlauf der Zeit faktisch eine Zweiklassengesellschaft geschaffen würde, die sich dann weiterentwickeln würde, mit Bürgerinnen und Bürgern mit vollen politischen Rechten und anderen Menschen, die diese Rechte eben nicht hätten. 
+Ein Blick in die Vergangenheit zeigt, dass das Schweizer System historisch betrachtet viel integrativer war. Grosse Einwanderungsgruppen wurden in der Schweiz immer relativ schnell politisch integriert, es gab eine Durchlässigkeit. Den Zopfis sagt man nach, dass sie als reformierte Flüchtlinge aus dem Veltlin gekommen seien. Man weiss nicht genau, ob das stimmt, aber andere protestantische Familien, die nachweislich aus dem Veltlin in die Schweiz geflüchtet sind, haben es in der Schweiz in kurzer Zeit auch in politische Ämter geschafft. Das zeigt doch, dass das frühere System sehr stark integrativ war. 
+Es ist auch typisch schweizerisch, denn unser Weg ist es, die Minderheiten, die politischen Minderheiten usw. in unser System zu integrieren und sie an diesem politischen System teilhaben zu lassen. Gerade unser politisches System mit Volksabstimmungen, mit der ständigen Äusserung des Willens des Volkes, benötigt doch, dass möglichst viele Menschen daran teilhaben können. Ich meine, typisch schweizerisch wäre eigentlich eine sehr liberale Einbürgerungspraxis und nicht eine restriktive.
+Schauen Sie deshalb den Antrag meiner Minderheit II an. Er ist nicht gerade eine komplette Aufweichung, sondern weiterhin streng, aber er setzt an einem Punkt an, nämlich bei der Kindheit und Jugend in der Schweiz. Es sollen nämlich diejenigen neu erleichtert eingebürgert werden können, die vor dem 16. Lebensjahr mindestens fünf Jahre in der Schweiz verbracht haben. Das bedeutet konkret, dass diese jungen Menschen die Schule in der Schweiz besucht haben, dass sie unsere Sprache sprechen, dass sie in ein System integriert sind, auch in jenes der schweizerischen Berufsbildung. Sie haben eine andere Nationalität, aber aus Sicht unserer Gesamtgesellschaft sind sie vollständig in der Schweiz integriert. 
+Ich glaube, diesen Schlüssel sollten wir nutzen. Ich bin der Meinung, dass das auch für unseren Staat eine riesige Chance ist und Sie keine Angst haben müssen, dass dann zu viele oder die falschen Menschen eingebürgert werden. Es werden genau diejenigen sein, die zusammen mit den Kindern aus Schweizer Familien die Schule besucht haben.
+Erlauben Sie mir noch eine oder zwei Schlussbemerkungen: Erstens unterstütze ich auch die anderen beiden Minderheitsanträge, weil ich überzeugt bin, dass wir hier eine gewisse Liberalisierung vornehmen sollten, wie es die Bundesversammlung übrigens früher schon versucht hat. Zweitens habe ich Ihnen zu Beginn gesagt, dass ich es als Präsident des Gemeindeverbandes natürlich kritisch betrachte, dass mit der Initiative die Rolle der Gemeinden abgeschwächt würde. Ich frage mich aber, ob es in unserem föderalistischen System nicht eigentlich angezeigt wäre, den Gemeinden und Kantonen mehr Freiheit dabei zu geben, Verfahrenserleichterungen für diese Generation zu schaffen. Denn dann würden die Menschen vor Ort richtigerweise entscheiden, wer in ihrer Demokratie dazugehören soll und wer nicht. Ich bin damit am Ende. (discurra sursilvan) Grazia fitg per Vossa attenziun.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signor presidente, signor consigliere federale, gentili signore e signori, la mozione è contraria al federalismo e contraria al principio di sussidiarietà - è superflua.
+Es fällt mir als Präsident der SiK - und nachdem ich am Montag die Arbeit der SiK mit Blick auf unseren Finanzierungskompromiss noch gelobt habe - natürlich schwer, mich hier gegen die Mehrheit der Kommission zu stellen. Aber ich muss Ihnen sagen: Ich glaube, hier sind der Mehrheit der SiK die sicherheitspolitischen Rösser durch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signor presidente, signor consigliere federale, gentili signore e signori, la mozione è contraria al federalismo e contraria al principio di sussidiarietà - è superflua.
+Es fällt mir als Präsident der SiK - und nachdem ich am Montag die Arbeit der SiK mit Blick auf unseren Finanzierungskompromiss noch gelobt habe - natürlich schwer, mich hier gegen die Mehrheit der Kommission zu stellen. Aber ich muss Ihnen sagen: Ich glaube, hier sind der Mehrheit der SiK die sicherheitspolitischen Rösser durchgebrannt. 
+Was das Anliegen betrifft, das jetzt auch Kollege Wicki geschildert hat, nämlich, dass gewalttätige Demonstrantinnen und Demonstranten für die Kosten aufkommen sollen, und dass möglichst verhindert werden soll, dass solche Demonstrationen überhaupt stattfinden und so weiter, so ist völlig klar, dass wir wohl alle mehr oder weniger gleicher Meinung sind. Die Frage ist aber: Erreichen wir das mit dieser Motion? Dazu möchte ich Ihnen einfach ein paar Punkte zu bedenken geben. 
+Erstens, eine bundesrechtliche Regelung der Kostenüberwälzung widerspricht ganz klar der geltenden Kompetenzverteilung. Gemäss Artikel 57 der Bundesverfassung sind die Kantone für die öffentliche Sicherheit zuständig. Es gibt hierzu eigentlich keine Diskussion und keine Auslegung, das ist klar festgelegt. Das heisst, dass die Kantone dafür zuständig sind, zu entscheiden, wann eine Veranstaltung bewilligungspflichtig ist, weil solche Veranstaltungen auch unter das Thema der öffentlichen Sicherheit fallen. Die Kantone sind dafür zuständig, die Sicherheitskonzepte einzufordern und allenfalls zu bewilligen, sie sind dafür zuständig, die Polizeiaufgebote zu dimensionieren und zu planen, und so weiter. Eine Regelung des Einzelaspekts der Kostenübernahme auf Bundesebene würde die kantonale Polizeihoheit beeinträchtigen, und sie würde eben nicht nur dem föderalistischen Prinzip zuwiderlaufen, sondern auch dem Subsidiaritätsprinzip, wonach man auf jener Ebene regelt, auf der es am zweckmässigsten und nötig ist, und nur dann auf Bundesebene regelt, wenn es notwendig wird. 
+Zweitens ist sogar unklar oder mindestens umstritten, ob für diese Bestimmung auf Stufe Bund eine verfassungsrechtliche Grundlage bestehen würde. 
+Drittens würde so eine Bestimmung keine Vereinheitlichung bringen, sondern gerade eine Verkomplizierung des Systems. Denn das Kundgebungsrecht und die Kostenregelungen müssen ja aus einer Hand kommen. Ich habe Ihnen aufgezählt, wofür die Kantone bei solchen Demonstrationen alles zuständig sind. Wenn Sie jetzt für diese eine Frage plötzlich den Spielraum einschränken, können die Kantone nicht mehr so gut auf die kantonalen Gegebenheiten eingehen, wie sie es bisher können. Wir preisen hier drin ja regelmässig - und auch heute ist das schon ein paar Mal passiert - das Prinzip der Subsidiarität. Es gibt keinen Grund, hier eine bundesrechtliche Regelung zu erlassen. Gerade die Kantone mit grossen Ballungszentren, in denen es mit höherer Wahrscheinlichkeit solche Demonstrationen gibt - Zürich, Bern, Basel oder Genf zum Beispiel -, haben detaillierte Kostenersatzregeln. Diese Kantone kennen das heute schon. Es gibt also auch keinen Handlungsbedarf; Sie würden ein Flickwerk schaffen. 
+Viertens, schauen Sie einmal den Text der Motion an. Hier bin ich natürlich bei Kollege Schmid, der vorhin gesagt hat, man müsse jeweils schauen, was genau gewollt sei, und das präzise anschauen. Die Motion zielt nicht spezifisch auf die Veranstalter von gewalttätigen Demonstrationen, sondern es würden alle Veranstalter in die Pflicht genommen. Es steht nichts von "gewalttätig" - wohl in der Begründung, aber nicht im Motionstext. Das heisst, wir würden diese unnötige Bundeskompetenz sogar noch für die ganze Breite der Demonstrationen schaffen und würden den Kantonen bei den vielen Demonstrationen wie dem 1. Mai und allem, was es sonst noch gibt, hineinfunken. 
+Nun hat der Berichterstatter, Kollege Wicki, gesagt, dass der Nationalrat dieser Motion zugestimmt habe, und das ist so, sonst wäre sie nicht bei uns. Wir haben zudem bereits einer gleichlautenden Motion zugestimmt, die mittlerweile im Nationalrat angelangt ist. Sie wissen, dass ich sowieso kein Befürworter von gleichlautenden Motionen bin. Ich finde, das führt regelmässig dazu, dass im Zweitrat der Qualitätsgedanke auf der Strecke bleibt. Aber in diesem Fall hat der Nationalrat, oder zumindest die SiK des Nationalrates, dies anders gemacht: Obwohl der Nationalrat die vorliegende Motion in der ersten Runde relativ klar gutgeheissen hat, empfiehlt die SiK-N mit 17 zu 7 Stimmen dem Nationalrat, der am 30. September über die identische Motion abstimmen wird, letztere abzulehnen. Und zwar tut die SiK-N dies mit Argumenten, die dort eine sehr breite politische Basis gefunden haben, nämlich mit den Argumenten, dass die kantonalen Polizeigesetzgebungen eine solche Änderung nicht nötig machen und dass wir nicht in dieses System hineinfunken sollten.
+Wenn Sie also hier einen Widerspruch zu einem Beschluss schaffen wollen, den der Nationalrat mit grosser Sicherheit in der nächsten Woche fassen wird - die nationalrätliche Kommission empfiehlt die Motion mit 17 zu 7 Stimmen zur Ablehnung -, dann können Sie dieser Motion zustimmen. 
+Wenn Sie aber als Zweitrat Ihrer Aufgabe hier im Ständerat gerecht werden wollen, lehnen Sie die Motion ab; schade, ist Kollegin Z'graggen jetzt nicht hier, sie hat heute die Rolle der Kantone und Gemeinden bei der Einbürgerung beschrieben, und Kollege Schmid hat in seinem Votum ebenfalls darauf verwiesen. 
+Es kann doch nicht sein, dass wir hier diesen Sündenfall begehen und die Subsidiarität dermassen stark verletzen, in einem Fall, bei dem es letztlich darum geht, ein paar Extremisten oder Spinnern ein paar Franken zu auferlegen. 
+Ich bitte Sie, die Motion entgegen dem Antrag der doch recht klaren Mehrheit der SiK abzulehnen. Nehmen wir die Aufgabe wahr, die der Ständerat hat. Ich bin sicher und kann Ihnen jetzt schon versprechen, dass sich sämtliche Kantone bei der Umsetzung nur schon aus prinzipiellen Überlegungen gegen die Motion stellen werden und wir einen Leerlauf schaffen. 
+Ich danke für die Unterstützung der Minderheit.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schmid Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La commission a examiné cette motion avec attention, en reconnaissant la gravité du problème soulevé.
+La commissione comprende l'obiettivo di proteggere meglio le vittime ma ritiene che la via proposta non sia quella giusta.
+Ich berichte Ihnen im Namen der Kommission für Rechtsfragen des Ständerates zur Motion Jaccoud 25.4224, "Geschlechtsspezifische Gewalt. Kein Opfer ohne Gerechtigkeit, kein Täter ohne Verurteilung". Die Motion verlangt, dass das geltende Recht so angepasst wird, dass Frauen, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La commission a examiné cette motion avec attention, en reconnaissant la gravité du problème soulevé.
+La commissione comprende l'obiettivo di proteggere meglio le vittime ma ritiene che la via proposta non sia quella giusta.
+Ich berichte Ihnen im Namen der Kommission für Rechtsfragen des Ständerates zur Motion Jaccoud 25.4224, "Geschlechtsspezifische Gewalt. Kein Opfer ohne Gerechtigkeit, kein Täter ohne Verurteilung". Die Motion verlangt, dass das geltende Recht so angepasst wird, dass Frauen, die Opfer geschlechtsspezifischer Gewalt geworden sind, und sich rechtswidrig in der Schweiz aufhalten, Strafanzeige erstatten oder sich an die Strafbehörden wenden können, ohne dass diese verpflichtet sind, den illegalen Aufenthalt zur Anzeige zu bringen.
+Im Titel der Motion steht: "kein Täter ohne Verurteilung". Die Motion verlangt, dass die Strafbehörden in Fällen, in denen sich Frauen illegal in der Schweiz aufhalten, diese nicht mehr strafrechtlich anzeigen müssen. Das Anliegen der Motion ist klar: Betroffene Frauen sollen nicht aus Angst vor einer Anzeige wegen ihres Aufenthaltsstatus darauf verzichten, Gewalt anzuzeigen. Es geht also darum, das Dilemma zwischen Opferschutz und möglicher Strafverfolgung wegen illegalen Aufenthalts zu entschärfen.
+Der Nationalrat hat die Motion am 11. März 2026 angenommen. Der Bundesrat beantragt ebenfalls Annahme der Motion. Der Bundesrat anerkennt, dass Frauen ohne rechtmässigen Aufenthaltsstatus, die Opfer von Gewalt werden, nicht davon abgehalten werden sollen, sich an die Strafverfolgungsbehörden zu wenden. Gleichzeitig hat der Bundesrat festgehalten, die vorgeschlagene Lösung sei kein Allheilmittel und bedeute keine Legalisierung des illegalen Aufenthalts.
+Die Kommission hat das Anliegen der Motion geprüft. Sie teilt die Einschätzung, dass Opfer geschlechtsspezifischer Gewalt Schutz brauchen, und dass Straftäter nicht deshalb straflos bleiben sollen, weil Opfer aus Angst vor migrationsrechtlichen Folgen schweigen. Die Mehrheit der Kommission ist aber zum klaren Schluss gekommen, dass die Motion am falschen Ort ansetzt. Das Problem kann nicht im Strafrecht gelöst werden. Auch Opfer anderer Straftaten als Gewaltdelikte befinden sich im gleichen Dilemma.
+Aus Sicht der Kommission ist das Strafrecht nicht die geeignete Ebene, um dieses Dilemma zu lösen. Die Motion würde bei den Strafbehörden ansetzen und dort eine Ausnahme von der Anzeige- bzw. Meldepflicht schaffen. Das überzeugt die Kommissionsmehrheit systemisch nicht. Stellen Sie sich vor, dass ein Polizist oder, je nach kantonaler Polizeiordnung, ein Staatsanwalt von der Straftat des illegalen Aufenthalts erfährt, aber dann selbst entscheiden kann, ob er eine Strafanzeige machen will. Da die Kantone im Strafrecht spezialisierte Fachabteilungen haben, könnte es auch zu unterschiedlichen und rechtsungleichen Situationen kommen; ich verweise auch auf die Kesb. Zudem sieht die Motion eine Kann-Bestimmung vor. Damit hat das Opfer wiederum keinen Schutz.
+Die Kommission weist insbesondere darauf hin, dass der Vollzug des Ausländerrechts nicht bei den Strafbehörden liegt, sondern bei den zuständigen Migrationsbehörden. Selbst wenn Strafbehörden in bestimmten Konstellationen nicht mehr verpflichtet wären, den illegalen Aufenthalt zur Anzeige zu bringen, wäre damit das migrationsrechtliche Problem nicht gelöst. Die betroffene Person hätte dadurch noch keine Garantie, während eines Strafverfahrens in der Schweiz bleiben zu können. Die Motion läuft damit ins Leere.
+Zudem sieht die Kommission rechtliche Schwierigkeiten bei der vorgeschlagenen Eingrenzung. Die Motion bezieht sich allein auf Frauen als Opfer geschlechtsspezifischer Gewalt. Damit stellt sich die Frage, weshalb diese Opferkategorie privilegiert werden soll. Auch andere Personen ohne rechtmässigen Aufenthaltsstatus können Opfer schwerer Straftaten werden und vor einem vergleichbaren Dilemma stehen. Eine nur auf eine bestimmte Opfergruppe beschränkte Regelung könnte deshalb zu rechtlich heiklen Ungleichbehandlungen führen.
+In der Kommission wurde ein Änderungsantrag beraten, der den Anwendungsbereich breiter fassen und die Frage stärker migrationsrechtlich lösen wollte. Auch dieser Antrag fand keine Mehrheit. Die Mehrheit bleibt bei ihrer Einschätzung, dass die Motion in der vorliegenden Form weder strafrechtlich noch gesetzessystematisch überzeugt.
+Die Kommission ist der Auffassung, dass das Anliegen zwar ernstzunehmen ist, bei häuslicher Gewalt konsequent eingegriffen werden muss, auch ausländerrechtlich konsequent mit Wegweisung vorgegangen werden muss, die vorgeschlagene Lösung jedoch nicht tragfähig ist. Es kann nicht sein, dass eine geschlechtsspezifische Lösung gewählt wird und nur Frauen betroffen sein sollen. Das widerspricht der Bundesverfassung. 
+Wenn der Gesetzgeber hier handeln möchte, müsste nach Ansicht der Kommissionsmehrheit wenn schon geprüft werden, ob und wie eine Lösung im Migrationsrecht ausgestaltet werden könnte, etwa mit Blick auf den befristeten Aufenthalt während eines Strafverfahrens, damit das Opfer als Zeugin den Strafverfolgungsbehörden zur Verfügung stehen kann. Die vorliegende Motion bietet dafür jedoch nicht den richtigen Rahmen. 
+Kollege Sommaruga wird Ihnen die Auffassung der Minderheit vortragen. Die Kommission für Rechtsfragen beantragt Ihnen aufgrund dieser Argumentation mit 9 zu 2 Stimmen bei 1 Enthaltung, die Motion abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Vielen Dank, Herr Bundesrat, wir haben Sie genau verstanden. Sie beantragen, die Volksinitiative zur Ablehnung zu empfehlen, und unterstützen den Antrag der Mehrheit, nicht auf den direkten Gegenentwurf einzutreten. Ein grosses Kompliment für Ihre romanische Aussprache!
+[VS]
+[VS]
+3.[NB]Gegenentwurf zur Volksinitiative "für ein modernes Bürgerrecht (Demokratie-Initiative)"
+3.[NB]Contre-projet à l'initiative populaire "pour un droit de la nationalité moderne (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Vielen Dank, Herr Bundesrat, wir haben Sie genau verstanden. Sie beantragen, die Volksinitiative zur Ablehnung zu empfehlen, und unterstützen den Antrag der Mehrheit, nicht auf den direkten Gegenentwurf einzutreten. Ein grosses Kompliment für Ihre romanische Aussprache!
+[VS]
+[VS]
+3.[NB]Gegenentwurf zur Volksinitiative "für ein modernes Bürgerrecht (Demokratie-Initiative)"
+3.[NB]Contre-projet à l'initiative populaire "pour un droit de la nationalité moderne (initiative pour la démocratie)"[GZ]
+[VS][GZ]
+Antrag der Mehrheit [GZ]
+Nichteintreten
+[VS]
+Antrag der Minderheit I [GZ]
+(Moser, Jositsch, Maillard Pierre-Yves, Zopfi)[GZ]
+Titel [GZ]
+3. Bundesbeschluss über die erleichterte Einbürgerung von Ausländerinnen und Ausländer der zweiten Generation (Gegenentwurf zur Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)") vom ...
+Ingress [GZ]
+Die Bundesversammlung der Schweizerischen Eidgenossenschaft, gestützt auf Artikel 139 Absatz 5 der Bundesverfassung, nach Prüfung der am 21. November 2024 eingereichten Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)", nach Einsicht in die Botschaft des Bundesrates vom 5. November 2025, beschliesst:
+Ziff. I Einleitung[GZ]
+Die Bundesverfassung wird wie folgt geändert:
+Ziff. I Art. 38 Titel[GZ]
+Erwerb und Verlust der Bürgerrechte
+Ziff. I Art. 38 Abs. 3 Einleitung[GZ]
+Er erleichtert die Einbürgerung von:
+Ziff. I Art. 38 Abs. 3 Bst. a[GZ]
+a. Personen der zweiten und dritten Ausländergeneration;
+Ziff. II [GZ]
+Dieser Gegenentwurf wird Volk und Ständen zur Abstimmung unterbreitet. Sofern die Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)" nicht zurückgezogen wird, wird er zusammen mit der Volksinitiative nach dem Verfahren gemäss Artikel 139b der Bundesverfassung Volk und Ständen zur Abstimmung unterbreitet.
+[VS]
+Antrag der Minderheit II [GZ]
+(Zopfi, Jositsch, Maillard Pierre-Yves)[GZ]
+Titel [GZ]
+3. Bundesbeschluss über die erleichterte Einbürgerung von Ausländerinnen und Ausländer, die sich vor dem 16. Lebensjahr mindestens fünf Jahre in der Schweiz aufgehalten haben (Gegenentwurf zur Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)") vom ...
+Ingress [GZ]
+Die Bundesversammlung der Schweizerischen Eidgenossenschaft, gestützt auf Artikel 139 Absatz 5 der Bundesverfassung, nach Prüfung der am 21. November 2024 eingereichten Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)", nach Einsicht in die Botschaft des Bundesrates vom 5. November 2025, beschliesst:
+Ziff. I Einleitung [GZ]
+Die Bundesverfassung wird wie folgt geändert:
+Ziff. I Art. 38 Titel[GZ]
+Erwerb und Verlust der Bürgerrechte
+Ziff. I Art. 38 Abs. 3 Einleitung[GZ]
+Er erleichtert die Einbürgerung von:
+Ziff. I Art. 38 Abs. 3 Bst. c[GZ]
+c. Personen, die sich vor Vollendung ihres 16. Lebensjahres mindestens fünf Jahre rechtmässig und ununterbrochen in der Schweiz aufgehalten haben;
+Ziff. II [GZ]
+Dieser Gegenentwurf wird Volk und Ständen zur Abstimmung unterbreitet. Sofern die Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)" nicht zurückgezogen wird, wird er zusammen mit der Volksinitiative nach dem Verfahren gemäss Artikel 139b der Bundesverfassung Volk und Ständen zur Abstimmung unterbreitet.
+[VS]
+Antrag der Minderheit III [GZ]
+(Maillard Pierre-Yves, Fässler Daniel, Jositsch, Moser, Zopfi)[GZ]
+Titel [GZ]
+3. Bundesbeschluss Bundesbeschluss über die erleichterte Einbürgerung bei jahrzehntelangem Aufenthalt (Gegenentwurf zur Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)") vom ...
+Ingress [GZ]
+Die Bundesversammlung der Schweizerischen Eidgenossenschaft, gestützt auf Artikel 139 Absatz 5 der Bundesverfassung, nach Prüfung der am 21. November 2024 eingereichten Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)", nach Einsicht in die Botschaft des Bundesrates vom 5. November 2025, beschliesst:
+Ziff. I Einleitung[GZ]
+Die Bundesverfassung wird wie folgt geändert:
+Ziff. I Art. 38 Titel[GZ]
+Erwerb und Verlust der Bürgerrechte
+Ziff. I Art. 38 Abs. 3 Einleitung[GZ]
+Er erleichtert die Einbürgerung von:
+Ziff. I Art. 38 Abs. 3 Bst. c[GZ]
+c. ausländischen Personen, die sich seit insgesamt 25 Jahren rechtmässig in der Schweiz aufhalten. Das Gesetz kann Ausnahmen für junge, in der Schweiz aufgewachsene Ausländerinnen und Ausländer bei der Berechnung der Aufenthaltsdauer vorsehen.
+Ziff. II [GZ]
+Dieser Gegenentwurf wird Volk und Ständen zur Abstimmung unterbreitet. Sofern die Volksinitiative "Für ein modernes Bürgerrecht (Demokratie-Initiative)" nicht zurückgezogen wird, wird er zusammen mit der Volksinitiative nach dem Verfahren gemäss Artikel 139b der Bundesverfassung Volk und Ständen zur Abstimmung unterbreitet.
+[VS]
+Proposition de la majorité [GZ]
+Ne pas entrer en matière
+[VS]
+Proposition de la minorité I [GZ]
+(Moser, Jositsch, Maillard Pierre-Yves, Zopfi)[GZ]
+Titre [GZ]
+3. Arrêté fédéral concernant la naturalisation facilitée pour les étrangers de la deuxième génération (contre-projet à l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)") du ...
+Préambule [GZ]
+L'Assemblée fédérale de la Confédération suisse, vu l'article 139 alinéa 5 de la Constitution, vu l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)" déposée le 21 novembre 2024, vu le message du Conseil fédéral du 5 novembre 2025, arrête :
+Ch. I introduction[GZ]
+La Constitution est modifiée comme suit:
+Ch. I art. 38 titre[GZ]
+Acquisition et perte de la nationalité et des droits de cité
+Ch. I art. 38 al. 3 introduction[GZ]
+Elle facilite la naturalisation :
+Ch. I art. 38 al. 3 let. a[GZ]
+a. des étrangers des deuxième et troisième générations ;
+Ch. II [GZ]
+Le présent contre-projet sera soumis au vote du peuple et des cantons. Il sera soumis au vote en même temps que l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)", si cette initiative n'est pas retirée, selon la procédure prévue à l'article 139b de la Constitution.
+[VS]
+Proposition de la minorité II [GZ]
+(Zopfi, Jositsch, Maillard Pierre-Yves)[GZ]
+Titre [GZ]
+3. Arrêté fédéral concernant la naturalisation facilitée pour les étrangers qui ont séjourné en Suisse pendant cinq ans au moins lorsqu'ils atteignent l'âge de 16 ans (contre-projet à l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)") du ...
+Préambule [GZ]
+L'Assemblée fédérale de la Confédération suisse, vu l'article 139 alinéa 5 de la Constitution, vu l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)" déposée le 21 novembre 2024, vu le message du Conseil fédéral du 5 novembre 2025, arrête :
+Ch. I introduction[GZ]
+La Constitution est modifiée comme suit :
+Ch. I art. 38 titre[GZ]
+Acquisition et perte de la nationalité et des droits de cité
+Ch. I art. 38 al. 3 introduction[GZ]
+Elle facilite la naturalisation :
+Ch. I art. 38 al. 3 let. c[GZ]
+c. des étrangers qui ont séjourné légalement et de manière ininterrompue en Suisse pendant cinq ans au moins lorsqu'ils atteignent l'âge de 16 ans ;
+Ch. II [GZ]
+Le présent contre-projet sera soumis au vote du peuple et des cantons. Il sera soumis au vote en même temps que l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)", si cette initiative n'est pas retirée, selon la procédure prévue à l'article 139b de la Constitution.
+[VS]
+Proposition de la minorité III [GZ]
+(Maillard Pierre-Yves, Fässler Daniel, Jositsch, Moser, Zopfi)[GZ]
+Titre [GZ]
+3. Arrêté fédéral concernant la naturalisation facilitée pour les personnes résidant en Suisse depuis plusieurs décennies (contre-projet à l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)") du ...
+Préambule [GZ]
+L'Assemblée fédérale de la Confédération suisse, vu l'article 139 alinéa 5 de la Constitution, vu l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)" déposée le 21 novembre 2024, vu le message du Conseil fédéral du 5 novembre 2025, arrête :
+Ch. I introduction[GZ]
+La Constitution est modifiée comme suit :
+Ch. I art. 38 titre[GZ]
+Acquisition et perte de la nationalité et des droits de cité
+Ch. I art. 38 al. 3 introduction[GZ]
+Elle facilite la naturalisation :
+Ch. I art. 38 al. 3 let. c[GZ]
+c. des étrangers qui séjournent légalement en Suisse depuis au moins 25 ans au total. La loi peut prévoir des exceptions dans le calcul de la durée de séjour pour les jeunes étrangers qui ont grandi en Suisse.
+Ch. II [GZ]
+Le présent contre-projet sera soumis au vote du peuple et des cantons. Il sera soumis au vote en même temps que l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)", si cette initiative n'est pas retirée, selon la procédure prévue à l'article 139b de la Constitution.
+[VS]
+Präsident (Engler Stefan, Präsident): Wir stimmen über die Nichteintretensanträge der Minderheiten I, II und III ab.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.[NB]Bundesbeschluss über die Volksinitiative "für ein modernes Bürgerrecht (Demokratie-Initiative)"[GZ]
+1.[NB]Arrêté fédéral concernant l'initiative populaire "pour un droit de la nationalité moderne (initiative pour la démocratie)"[GZ]
+[VS][GZ]
+Eintreten ist obligatorisch [GZ]
+L'entrée en matière est acquise de plein droit
+[VS]
+Detailberatung - Discussion par article [GZ]
+[VS][GZ]
+Titel und Ingress, Art. 1[GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Beschluss des Nationalrates
+[VS]
+Titre et</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.[NB]Bundesbeschluss über die Volksinitiative "für ein modernes Bürgerrecht (Demokratie-Initiative)"[GZ]
+1.[NB]Arrêté fédéral concernant l'initiative populaire "pour un droit de la nationalité moderne (initiative pour la démocratie)"[GZ]
+[VS][GZ]
+Eintreten ist obligatorisch [GZ]
+L'entrée en matière est acquise de plein droit
+[VS]
+Detailberatung - Discussion par article [GZ]
+[VS][GZ]
+Titel und Ingress, Art. 1[GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Beschluss des Nationalrates
+[VS]
+Titre et préambule, art. 1[GZ]
+Proposition de la commission [GZ]
+Adhérer à la décision du Conseil national[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Art. 2 [GZ]
+Antrag der Mehrheit [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Antrag der Minderheit I [GZ]
+(Moser, Jositsch, Maillard Pierre-Yves, Zopfi)[GZ]
+Abs. 1 [GZ]
+Sofern die Volksinitiative nicht zurückgezogen wird, wird sie zusammen mit dem Gegenentwurf "Bundesbeschluss über die erleichterte Einbürgerung von Ausländerinnen und Ausländer der zweiten Generation" Volk und Ständen nach dem Verfahren gemäss Artikel 139b der Bundesverfassung zur Abstimmung unterbreitet.
+Abs. 2 [GZ]
+Die Bundesversammlung empfiehlt Volk und Ständen, die Initiative abzulehnen und den Gegenentwurf anzunehmen.
+[VS]
+Antrag der Minderheit II [GZ]
+(Zopfi, Jositsch, Maillard Pierre-Yves)[GZ]
+Abs. 1 [GZ]
+Sofern die Volksinitiative nicht zurückgezogen wird, wird sie zusammen mit dem Gegenentwurf "Bundesbeschluss über die erleichterte Einbürgerung von Ausländerinnen und Ausländer, die sich vor dem 16. Lebensjahr mindestens fünf Jahre in der Schweiz aufgehalten haben" Volk und Ständen nach dem Verfahren gemäss Artikel 139b der Bundesverfassung zur Abstimmung unterbreitet.
+Abs. 2 [GZ]
+Die Bundesversammlung empfiehlt Volk und Ständen, die Initiative abzulehnen und den Gegenentwurf anzunehmen.
+[VS]
+Antrag der Minderheit III [GZ]
+(Maillard Pierre-Yves, Fässler Daniel, Jositsch, Moser, Zopfi)[GZ]
+Abs. 1 [GZ]
+Sofern die Volksinitiative nicht zurückgezogen wird, wird sie zusammen mit dem Gegenentwurf "Bundesbeschluss über die erleichterte Einbürgerung bei jahrzehntelangem Aufenthalt" Volk und Ständen nach dem Verfahren gemäss Artikel 139b der Bundesverfassung zur Abstimmung unterbreitet.
+Abs. 2 [GZ]
+Die Bundesversammlung empfiehlt Volk und Ständen, die Initiative abzulehnen und den Gegenentwurf anzunehmen.
+[VS]
+Antrag Fivaz Fabien[GZ]
+Die Bundesversammlung empfiehlt Volk und Ständen, die Initiative anzunehmen.
+[VS]
+Art. 2 [GZ]
+Proposition de la majorité [GZ]
+Adhérer au projet du Conseil fédéral
+[VS]
+Proposition de la minorité I [GZ]
+(Moser, Jositsch, Maillard Pierre-Yves, Zopfi)[GZ]
+Al. 1 [GZ]
+Si l'initiative populaire n'est pas retirée, elle sera soumise au vote du peuple et des cantons en même temps que le contre-projet "arrêté fédéral concernant la naturalisation facilitée pour les étrangers de la deuxième génération", selon la procédure prévue à l'article 139b de la Constitution.
+Al. 2 [GZ]
+L'Assemblée fédérale recommande au peuple et aux cantons de rejeter l'initiative et d'accepter le contre-projet.
+[VS]
+Proposition de la minorité II [GZ]
+(Zopfi, Jositsch, Maillard Pierre-Yves)[GZ]
+Al. 1 [GZ]
+Si l'initiative populaire n'est pas retirée, elle sera soumise au vote du peuple et des cantons en même temps que le contre-projet "arrêté fédéral concernant la naturalisation facilitée pour les étrangers qui ont séjourné en Suisse pendant cinq ans au moins lorsqu'ils atteignent l'âge de 16 ans", selon la procédure prévue à l'article 139b de la Constitution.
+Al. 2 [GZ]
+L'Assemblée fédérale recommande au peuple et aux cantons de rejeter l'initiative et d'accepter le contre-projet.
+[VS]
+Proposition de la minorité III [GZ]
+(Maillard Pierre-Yves, Fässler Daniel, Jositsch, Moser, Zopfi)[GZ]
+Al. 1 [GZ]
+Si l'initiative populaire n'est pas retirée, elle sera soumise au vote du peuple et des cantons en même temps que le contre-projet "arrêté fédéral concernant la naturalisation facilitée pour les personnes résidant en Suisse depuis plusieurs décennies", selon la procédure prévue à l'article 139b de la Constitution.
+Al. 2 [GZ]
+L'Assemblée fédérale recommande au peuple et aux cantons de rejeter l'initiative et d'accepter le contre-projet.
+[VS]
+Proposition Fivaz Fabien[GZ]
+L'Assemblée fédérale recommande au peuple et aux cantons d'accepter l'initiative.
+[VS]
+Präsident (Engler Stefan, Präsident): Die Anträge der Minderheit I (Moser), der Minderheit II (Zopfi) und der Minderheit III (Maillard Pierre-Yves) sind hinfällig geworden. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Viertel der Menschen, die in diesem Land leben, haben kein Stimmrecht, haben keinen Einfluss auf die Gesetze, die für sie gelten - ein Viertel. Sie arbeiten hier, zahlen hier ihre Steuern, ziehen hier ihre Kinder gross. Sie engagieren sich in unseren Vereinen und Verbänden. Viele von ihnen sind hier geboren. Dennoch müssen sie z. B. am 27. September zusehen, wie die Schweiz auch für sie, aber ohne sie etwas entscheidet.
+Ce n'est pas un détail statistique ; c'est une question de légitimité dé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Viertel der Menschen, die in diesem Land leben, haben kein Stimmrecht, haben keinen Einfluss auf die Gesetze, die für sie gelten - ein Viertel. Sie arbeiten hier, zahlen hier ihre Steuern, ziehen hier ihre Kinder gross. Sie engagieren sich in unseren Vereinen und Verbänden. Viele von ihnen sind hier geboren. Dennoch müssen sie z. B. am 27. September zusehen, wie die Schweiz auch für sie, aber ohne sie etwas entscheidet.
+Ce n'est pas un détail statistique ; c'est une question de légitimité démocratique. Une démocratie dans laquelle la part de la population qui décide diminue d'année en année s'affaiblit irrémédiablement.
+L'initiative que nous examinons ne propose rien de révolutionnaire. Elle pose quatre conditions : cinq ans de séjour légal, des connaissances de base dans une langue nationale, l'absence de condamnation à une peine privative de liberté de longue durée et l'absence de menace pour la sécurité du pays. Les personnes qui remplissent ces conditions ont droit à la naturalisation.
+Le premier argument que je vous présente, c'est celui du fédéralisme. Je suis attaché au fédéralisme. Je viens d'un canton qui en a fait un usage audacieux. Le canton de Neuchâtel accorde le droit de vote au niveau communal aux étrangers établis depuis le 19e siècle et le droit de vote cantonal depuis plus de 20 ans. Personne chez nous ne considère que la démocratie en a souffert. Au contraire, c'est un élément d'intégration.
+Le fédéralisme n'a jamais voulu dire que les droits fondamentaux d'une personne devaient dépendre de sa commune de domicile. Or, c'est exactement ce qui se passe aujourd'hui. Le Conseil fédéral lui-même le reconnaît dans son message. Les conditions de naturalisation ordinaires varient fortement d'un canton à l'autre et d'une commune à l'autre, au point que l'égalité des chances n'est plus garantie. C'est devenu une loterie liée à votre code postal. Il est donc cohérent que les conditions d'accès à la nationalité soient fixées au niveau fédéral. Les cantons et les communes continueraient d'ailleurs à conduire les procédures. Ce qu'ils perdent, c'est la possibilité d'appliquer des décisions de manière arbitraire.
+Deuxième argument : l'intégration devrait précéder la naturalisation. On peut poser la question autrement : comment mesure-t-on l'intégration aujourd'hui ? Par des entretiens dont le contenu varie d'une commission à l'autre, par des questions sur le nom d'une montagne locale ou les horaires de la déchetterie, par des appréciations subjectives que les procès-verbaux restituent parfois mal, au point que le Conseil fédéral a dû se pencher sur la tenue de ces procès-verbaux. Ce n'est pas une mesure de l'intégration, c'est encore une fois une loterie. Cette loterie a des effets connus - ils ont déjà été rappelés par M. Maillard. Les études commandées par la Confédération montrent que le système actuel favorise les personnes les plus formées et décourage beaucoup d'autres de déposer une demande. Il existe un biais de sélection. Nous n'écartons pas les personnes non intégrées ; nous écartons celles qui n'ont pas les moyens, le temps ou l'assurance nécessaires pour affronter la procédure. La langue, la vie dans le pays depuis cinq ans, le respect de la loi ; voilà des critères objectifs d'intégration que propose l'initiative.
+Troisième argument : le séjour de certaines personnes serait encore peu stabilisé. Cinq ans de séjour légal, ce n'est pas un passage ; c'est la durée d'une scolarité primaire, d'une formation professionnelle complète, d'un premier emploi durable. C'est d'ailleurs la norme dans plusieurs pays voisins. La Suisse figure aujourd'hui parmi les pays d'Europe où la naturalisation est la plus difficile. Je rappelle une chose à notre chambre : c'est notre commission, la Commission des institutions politiques qui a demandé au Conseil fédéral, par le postulat 22.3397, d'expliquer pourquoi si peu de jeunes de la deuxième génération se font naturaliser. Nous avons posé la bonne question, nous avons reçu du Conseil fédéral une réponse claire : les règles et les procédures sont trop hétérogènes, trop dissuasives, trop aléatoires.
+Aujourd'hui, notre conseil recommandera le rejet de l'initiative et rejettera tout contre-projet ; ce que vous faites, c'est constater un problème et décider de ne rien faire. Pourquoi donc recommander l'adoption de l'initiative ? Parce qu'une personne qui vit ici depuis des années, qui parle notre langue et respecte nos lois, fait déjà partie de la Suisse. La naturalisation ne lui donne pas une identité nouvelle ; elle reconnaît celle qu'elle a déjà construite ici. Le droit de cité ne devrait pas être un privilège accordé selon la bonne volonté d'une commission cantonale, mais un droit encadré par des critères clairs et légaux pour toutes et tous.
+Je vous invite donc à recommander l'adoption de cette initiative.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillard Pierre-Yves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Volksinitiative der Aktion Vierviertel stellt fest, dass ein Viertel der Einwohner in der Schweiz nicht an unserer Demokratie teilnehmen kann. Sie will dies ändern. Noch schlimmer ist die Situation bei der aktiven Bevölkerung: 35 Prozent der Arbeitnehmenden in unserem Land haben keinen Schweizer Pass. Bei Neugeborenen ist es ähnlich. Darum stellt die Volksinitiative folgende Frage: Welchen Anteil ihrer aktiven und jungen Bevölkerung kann eine Demokratie ausschliessen, ohne ihren Sinn und ihr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Volksinitiative der Aktion Vierviertel stellt fest, dass ein Viertel der Einwohner in der Schweiz nicht an unserer Demokratie teilnehmen kann. Sie will dies ändern. Noch schlimmer ist die Situation bei der aktiven Bevölkerung: 35 Prozent der Arbeitnehmenden in unserem Land haben keinen Schweizer Pass. Bei Neugeborenen ist es ähnlich. Darum stellt die Volksinitiative folgende Frage: Welchen Anteil ihrer aktiven und jungen Bevölkerung kann eine Demokratie ausschliessen, ohne ihren Sinn und ihre Realität zu verlieren?
+Quand un tiers des naissances dans notre pays sont des enfants qui n'ont pas de passeport suisse, quand 35 pour cent de la population active n'a pas de passeport suisse, on est dans une situation où la part de celles et ceux qui ne peuvent pas participer à notre démocratie augmente à chaque génération.
+Le nombre de naturalisations dans notre pays stagne ; il est même environ 10 pour cent plus bas aujourd'hui qu'il y a 20 ans. Je l'ai dit, un travailleur, une travailleuse sur trois dans notre pays ne peut pas voter. Il ne peut pas voter quand il s'agit des impôts qu'il paye, quand il s'agit des cotisations aux assurances sociales, quand il s'agit des prestations de ces assurances sociales auxquelles il, elle cotise. On est donc dans une situation qui est parfois même pire que dans un domaine de marché, par exemple l'assurance. Quand on veut changer les conditions générales d'une assurance, en principe on doit consulter tous les assurés. Mais quand on discute des prestations de l'AVS, près d'un tiers de celles et ceux qui cotisent à cette assurance sociale n'ont pas le droit de s'exprimer sur les prestations et sur les financements de l'assurance sociale à laquelle ils cotisent. Donc nous avons un problème et un problème qui grandit.
+Une démocratie qui exclut un travailleur sur trois qui en finance les prestations commence à avoir des problèmes de légitimité et de crédibilité. Nous avons parfois des débats sur les difficultés pour l'armée, pour la défense nationale, d'avoir suffisamment de nouvelles recrues. On a des débats sur les motifs qui pousseraient des jeunes à choisir le service civil. Certains d'entre nous demandent qu'on durcisse les critères pour accéder au service civil. Nous excluons nous-mêmes près d'un jeune sur quatre qui atteint les 18 ans sans passeport suisse. Probablement que, parmi ces jeunes, il y en a beaucoup qui seraient d'accord de faire l'effort de la défense nationale.
+Pour notre démocratie, pour notre cohésion, cette situation qui se péjore, génération après génération, devient un problème.
+La proposition que je vous fais avec ce contre-projet est très simple. Je propose qu'une naturalisation facilitée soit accessible après 25 ans de résidence en Suisse. Ce chiffre peut paraître élevé, mais il essaye d'apporter une réponse ciblée au constat que le rapport en réponse au postulat 22.3397 a fait. La Commission des institutions politiques de notre conseil avait demandé un rapport sur les raisons pour lesquelles des personnes renoncent à la naturalisation. Les constats qui ont été faits, c'est que ce sont particulièrement les personnes peu qualifiées qui renoncent à la naturalisation, notamment parce qu'elles craignent les examens et les coûts de la procédure. Ce sont essentiellement les ouvriers, qui travaillent sur nos chantiers, qui travaillent depuis des décennies pour construire notre pays, qui renoncent à accéder à la nationalité par peur des démarches et des examens, notamment de langue. Et pourtant, ils parlent notre langue, peut-être qu'ils ne sont pas très forts à l'écrit, mais oralement ils sont capables de vivre dans notre société. C'est cette peur qui explique pourquoi, comme conseillers d'État, lors des cérémonies de naturalisation, nous avions parfois des jeunes de 30 ou 40 ans qui accédaient à la nationalité - c'étaient des jeunes bien qualifiés, bien intégrés dans notre pays - alors qu'ensuite, à l'apéro, les parents de ces jeunes, qui avaient 60 ou 70 ans et qui étaient depuis 40 ou 50 ans dans notre pays, nous disaient n'avoir jamais fait la démarche parce que cela leur paraissait trop lourd et qu'ils n'étaient pas sûrs d'y arriver. Vous vous retrouvez donc face à des enfants qui sont là depuis 20 ou 30 ans, qui accèdent à la nationalité, alors que leurs parents, qui ont le double de temps de résidence dans notre pays, n'osent pas faire les démarches.
+C'est pour ces ouvriers, pour ces femmes et ces hommes qui exercent des métiers difficiles, qu'il faut une réponse adaptée. Et c'est ce que je propose. Une solution qui consiste simplement à considérer que 25 années passées dans notre pays à vivre, à travailler, à s'insérer valent bien un examen de langue. On doit pouvoir déroger à l'obligation d'un examen de langue ou d'un examen d'intégration quand on a 25 ans - un quart de siècle - de vie et de travail dans notre pays. Évidemment, les autres conditions resteraient valables. Les conditions de sécurité, les conditions liées à l'absence d'actes criminels seraient évidemment préservées. La seule chose à laquelle on pourrait déroger ce sont ces examens d'intégration. On considérerait que 25 années de vie valent bien les examens de vérification de maîtrise de la langue et de l'intégration. Voilà le concept que je vous propose.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es mitbekommen: In den letzten Monaten und Jahren sind die irregulären Einreisen nach Europa sowie die Asylgesuche stark zurückgegangen. Das hat sehr viel damit zu tun, dass die Schengen-Aussengrenzen durch die EU-Länder, aber auch durch die Schengen-assoziierten Länder wie die Schweiz stärker geschützt werden. Ein wichtiges Instrument für diesen Schutz ist der BMVI-Fonds. Davon profitiert die Schweiz doppelt: einerseits, weil er Wirkung zeigt und weniger Personen einreisen, anderersei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es mitbekommen: In den letzten Monaten und Jahren sind die irregulären Einreisen nach Europa sowie die Asylgesuche stark zurückgegangen. Das hat sehr viel damit zu tun, dass die Schengen-Aussengrenzen durch die EU-Länder, aber auch durch die Schengen-assoziierten Länder wie die Schweiz stärker geschützt werden. Ein wichtiges Instrument für diesen Schutz ist der BMVI-Fonds. Davon profitiert die Schweiz doppelt: einerseits, weil er Wirkung zeigt und weniger Personen einreisen, andererseits, weil er auch die Schweiz, die Kantone und die zuständigen Behörden bei ihren Bemühungen unterstützen kann. Dem Fonds kommt eine wichtige Aufgabe zu, zum Beispiel beim Schutz der gemeinsamen Aussengrenzen, bei der gemeinsamen Visumpolitik sowie bei Investitionen in IT-Systeme, technische Ausrüstung und die operative Zusammenarbeit. 
+Die EU hat den BMVI-Fonds für die Förderperiode 2021 bis 2027 geschaffen und ursprünglich mit 6,24 Milliarden Euro ausgestattet. Die Beiträge der assoziierten Schengen-Staaten wie der Schweiz kommen zusätzlich hinzu. Die Schweiz beteiligt sich seit dem 1. August 2024 am BMVI-Fonds. Mit der heutigen Vorlage geht es nicht darum, dass sich die Schweiz neu am Fonds beteiligt. Vielmehr wollen wir die bereits bestehende Beteiligung finanziell und programmatisch anpassen.
+Per la Svizzera, questo fondo riveste una particolare importanza, poiché in quanto Stato associato a Schengen beneficia direttamente di queste misure comuni. Il fondo contribuisce così a rafforzare la spazio Schengen nel suo complesso. Anche i Cantoni possono beneficiare direttamente dei finanziamenti del fondo per progetti concreti.
+Die EU hat den Fonds um eine Milliarde Euro aufgestockt und die zusätzlichen Mittel auf die Jahre 2025 bis 2027 verteilt. Gleichzeitig hat sie bestimmte Massnahmen bis Ende 2027 verlängert. Dadurch kann die EU bestehende Projekte weiterführen sowie neue umsetzen. Für die Schweiz bedeutet dies zwar eine leicht höhere finanzielle Beteiligung, doch sie profitiert auch von der Aufstockung. Dies schafft zusätzliche Möglichkeiten für geeignete Projekte in der Schweiz.
+In der Botschaft zum vorliegenden Durchführungsbeschluss ging der Bundesrat davon aus, dass sich der Gesamtbeitrag der Schweiz für die Fondsperiode 2021-2027 von ursprünglich rund 300 Millionen Franken auf ungefähr 323 Millionen Franken erhöht; diese Beiträge beruhten auf den damals verfügbaren Angaben und stellten eine Schätzung dar. Inzwischen liegt die definitive Berechnung der Europäischen Kommission vor. Der Gesamtbeitrag der Schweiz beläuft sich auf rund 329 Millionen Euro, woraus sich ein voraussichtlicher Gesamtaufwand von rund 304 Millionen Franken ergibt. Der Betrag liegt damit deutlich unter den 323 Millionen Franken und ist mit dem aktuellen Budget abgedeckt. Die Wechselkursentwicklung kann allenfalls dazu führen, dass sich der tatsächliche Gesamtaufwand in Schweizerfranken bis zur letzten Zahlung im Jahr 2027 noch verändert.
+Wie viel jedes Land zahlt, hängt vom sogenannten Schengen-Schlüssel ab, der das Bruttoinlandprodukt des jeweiligen Landes als Grundlage hat. Mit der vorliegenden Anpassung erhält die Schweiz zusätzliche Fördermittel von bis zu 20 Millionen Franken, die zu den bereits bestehenden hinzukommen. Das Geld wird aber nicht automatisch, sondern nur für geeignete und genehmigte Projekte ausbezahlt. Diese Mittel stehen insbesondere für Projekte zur Umsetzung des EU-Migrations- und -Asylpaktes zur Verfügung.
+Ein konkretes Beispiel ist ein Projekt im Kanton Genf, das Personen registriert und identifiziert, die irregulär in den Schengen-Raum eingereist sind. Die Konferenz der kantonalen Polizeikommandantinnen und -kommandanten unterstützt das Projekt, und die Kantonspolizei Genf setzt es um. Die Ergebnisse des Projektes sollen allen kantonalen Polizeikorps zugutekommen. Wer Mittel aus dem Fonds einsetzt, muss die einschlägigen Förderbedingungen sowie Prüf- und Kontrollmechanismen einhalten. Die Europäische Kommission und die zuständigen nationalen Behörden verwalten den Fonds und stellen im Rahmen ihrer jeweiligen Zuständigkeiten sicher, dass die Mittel regelkonform eingesetzt werden - und hier besteht Handlungsbedarf.
+Die EU-Agentur für Grundrechte hat in den vergangenen Jahren in einzelnen Staaten Pushbacks und andere Grundrechtsverletzungen festgestellt. Gleichzeitig wurden diese Staaten mit Mitteln aus dem BMVI-Fonds und damit auch mit Schweizer Mitteln unterstützt. Dies hat der Bundesrat in einem im Juni veröffentlichten Postulatsbericht festgehalten. Ein Zusammenhang zwischen der Verwendung dieser Fondsmittel und konkreten Grundrechtsverletzungen konnte jedoch nicht nachgewiesen werden.
+Für mich ist klar: Wir müssen unsere Möglichkeiten nutzen, um solche Menschenrechtsverletzungen zu verhindern. Im Rahmen der Schengen-Assoziierung hat die Schweiz Mitspracherechte, die sie aktiv nutzt. Dabei geht es nicht darum, operative Entscheide zu treffen, sondern um mehr Transparenz, klare Regeln und wirksame Kontrollen. Dafür setze ich mich sowohl im direkten Austausch mit meinen europäischen Amtskolleginnen und Amtskollegen als auch gegenüber der Europäischen Kommission ein.
+Der Bundesrat hat auf die Durchführung einer Vernehmlassung verzichtet. Die Vorlage betrifft keine wesentlichen Interessen der Kantone, enthält keine wichtigen rechtsetzenden Bestimmungen und untersteht nicht dem fakultativen Referendum. Wichtig ist: Wir müssen das nationale Recht nicht anpassen, es entsteht keine neue Verpflichtung im Grenz-, Visa- oder Asylrecht. Der Durchführungsbeschluss regelt einzig die Finanzierung und die Laufzeit des Arbeitsprogramms. Für den Bund entsteht kein zusätzlicher Personalbedarf. Für Kantone und Gemeinden entstehen ebenfalls keine neuen finanziellen oder personellen Verpflichtungen. 
+Bund und Kantone können jedoch geeignete Projekte zur Kofinanzierung einreichen. Der BMVI-Fonds leistet einen wichtigen Beitrag zum Schutz der Schengen-Aussengrenzen und damit zur Sicherheit der Schweiz.
+En tant qu'État enclavé, la Suisse bénéficie de contrôles efficaces aux frontières extérieures. C'est pourquoi elle participe solidairement aux coûts en découlant. En parallèle, notre pays peut disposer de moyens supplémentaires pour ses propres projets éligibles dans les domaines de la gestion des frontières et de la politique des visas.
+Ich beantrage Ihnen, dem einstimmigen Antrag Ihrer Kommission zu folgen und dem Entwurf zum Bundesbeschluss zuzustimmen.
 </t>
   </si>
 </sst>
@@ -1196,8 +1726,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I55" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I70" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I70"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -3064,6 +3594,437 @@
         <v>232</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>233</v>
+      </c>
+      <c r="B56" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" t="s">
+        <v>47</v>
+      </c>
+      <c r="F56" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>235</v>
+      </c>
+      <c r="I56" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>238</v>
+      </c>
+      <c r="E57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>241</v>
+      </c>
+      <c r="B58" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" t="s">
+        <v>242</v>
+      </c>
+      <c r="I58" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>244</v>
+      </c>
+      <c r="B59" t="s">
+        <v>234</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>245</v>
+      </c>
+      <c r="E59" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59" t="s">
+        <v>246</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>247</v>
+      </c>
+      <c r="I59" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>249</v>
+      </c>
+      <c r="B60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" t="s">
+        <v>124</v>
+      </c>
+      <c r="F60" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>251</v>
+      </c>
+      <c r="I60" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>253</v>
+      </c>
+      <c r="B61" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>155</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" t="s">
+        <v>156</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>254</v>
+      </c>
+      <c r="I61" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>256</v>
+      </c>
+      <c r="B62" t="s">
+        <v>234</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62"/>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>257</v>
+      </c>
+      <c r="I62" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>259</v>
+      </c>
+      <c r="B63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>260</v>
+      </c>
+      <c r="E63" t="s">
+        <v>40</v>
+      </c>
+      <c r="F63" t="s">
+        <v>124</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>261</v>
+      </c>
+      <c r="I63" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>263</v>
+      </c>
+      <c r="B64" t="s">
+        <v>234</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>260</v>
+      </c>
+      <c r="E64" t="s">
+        <v>40</v>
+      </c>
+      <c r="F64" t="s">
+        <v>124</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>264</v>
+      </c>
+      <c r="I64" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>267</v>
+      </c>
+      <c r="E65" t="s">
+        <v>116</v>
+      </c>
+      <c r="F65" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>268</v>
+      </c>
+      <c r="I65" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>271</v>
+      </c>
+      <c r="I66" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>273</v>
+      </c>
+      <c r="B67" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" t="s">
+        <v>61</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>274</v>
+      </c>
+      <c r="I67" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>276</v>
+      </c>
+      <c r="B68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" t="s">
+        <v>40</v>
+      </c>
+      <c r="F68" t="s">
+        <v>41</v>
+      </c>
+      <c r="G68" t="s">
+        <v>30</v>
+      </c>
+      <c r="H68" t="s">
+        <v>277</v>
+      </c>
+      <c r="I68" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>279</v>
+      </c>
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>280</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>35</v>
+      </c>
+      <c r="G69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H69" t="s">
+        <v>281</v>
+      </c>
+      <c r="I69" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>283</v>
+      </c>
+      <c r="B70" t="s">
+        <v>234</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70"/>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" t="s">
+        <v>30</v>
+      </c>
+      <c r="H70" t="s">
+        <v>284</v>
+      </c>
+      <c r="I70" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -212,11 +212,11 @@
   </si>
   <si>
     <t xml:space="preserve">Le Conseil national a rejeté cet accord le 17 juin dernier, pas par accident ou par distraction, mais au terme d'un long débat, et après avoir refusé une à une toutes les garanties qui auraient pu rendre ce texte un minimum acceptable. Notre commission nous propose aujourd'hui de faire la même chose, à quelques exceptions près. Elle nous propose nouvellement 517 millions de francs pour l'agriculture et un suivi régulier des engagements internationaux[NB]; de l'argent et de la surveillance là où il aurait fallu des règles strictes et qui fonctionnent.
-Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation[NB]; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table[NB]: l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires, ce qui équivaut à peu près au canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300 000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire qu'il y aurait un doublement de ces émissions. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le[NB]: l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne représente pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse et l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres.
+Le premier point sur lequel je veux revenir est la déforestation et le climat. Le Conseil national a refusé de reprendre dans cet accord le Règlement européen sur la déforestation[NB]; un texte qui interdit simplement la commercialisation de produits issus de la destruction des forêts. La commission du Conseil des États n'a malheureusement pas corrigé ce problème. Les chiffres sont pourtant sur la table[NB]: l'entrée en vigueur du traité pourrait entraîner la destruction de 900 kilomètres carrés de forêts supplémentaires, ce qui équivaut à peu près au canton de Neuchâtel. Nos échanges agricoles avec les pays du Mercosur génèrent aujourd'hui plus de 300[NB]000 tonnes de CO2 par an. L'accord y ajoute à peu près la même chose, c'est-à-dire qu'il y aurait un doublement de ces émissions. À l'importation, cette hausse tient pour l'essentiel aux dérivés du soja et à la viande bovine. Le projet du Conseil fédéral ne prévoit malheureusement rien pour en réduire l'impact. Rappelons-le[NB]: l'élevage bovin est l'un des tout premiers moteurs de la déforestation. Cet accord augmente donc la pression sur la forêt amazonienne et - j'y reviendrai - sur notre agriculture. La déforestation ne représente pas seulement des tonnes de CO2, mais aussi la destruction d'une biodiversité infiniment précieuse et l'expulsion de peuples autochtones de leurs terres. Ces choses ne se compensent pas. Un suivi ne leur rendra pas leurs terres.
 Le deuxième point sur lequel je veux revenir est le travail forcé. La gauche a proposé d'interdire l'importation de marchandises dont la production résulte du travail forcé. La commission a malheureusement écarté cette proposition et propose, à la place, comme toujours, un suivi. Or, les observateurs de terrain sont clairs[NB]: l'esclavage moderne est une réalité bien présente, par exemple dans les plantations de l'agrobusiness. Sur ce plan également, un suivi ne libère personne.
 Concernant ces deux volets, déforestation et travail forcé, cette chambre doit faire ce que l'Europe a fait[NB]: poser des règles contraignantes.
 Un troisième point important concerne notre agriculture. Nous devrions empêcher l'entrée de produits qui ne respectent pas nos normes, afin que nos agricultrices et agriculteurs puissent vivre dignement de leur travail. Cet accord produit exactement l'effet inverse. Aucune aide, aussi généreuse soit-elle, ne rendra un producteur suisse concurrentiel face au poulet brésilien. On ne corrige pas une distorsion structurelle avec un crédit d'engagement. Il faut d'ailleurs considérer ce traité comme ce qu'il est, un maillon d'une chaîne. La Chine, l'Indonésie, l'Inde, le Chili, demain peut-être la Malaisie[NB]: c'est l'accumulation de ces accords qui décidera du sort de l'agriculture et, à moyen terme, de celles et ceux qui veulent produire une alimentation saine et respectueuse de l'environnement.
-J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 50 000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé, parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.
+J'ajoute un mot sur le contenu exact de ce que nous approuvons. L'accord ouvre un contingent de 1000 tonnes de volaille, 3000 tonnes de viande bovine et 50[NB]000 hectolitres de vin en provenance du Mercosur. Ces volumes ne se substituent pas - cela a été dit par le rapporteur - aux concessions existantes. Ils s'ajoutent aux contingents que la Suisse accorde déjà aujourd'hui dans le cadre de l'OMC. Ce point mérite d'être relevé, parce que la communication du Conseil fédéral pendant les négociations allait précisément dans l'autre sens. Le Parlement se prononce donc aujourd'hui sur une ouverture plus large que celle qui lui avait été initialement présentée. C'est un problème de méthode autant que de fond.
 Le Conseil national a eu le courage de dire non. Je vous invite à en faire de même et à ne pas entrer en matière.
 </t>
   </si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -1168,7 +1168,7 @@
     <t xml:space="preserve">Antrag SPK-N [GZ]
 Die Motion 23.3032 nicht abschreiben
 Schriftliche Begründung [GZ]
-Die Motion beauftragt den Bundesrat, konkrete Massnahmen zu ergreifen, um Algerien zur Rückübernahme seiner Staatsangehörigen im Rahmen von zwangsweisen Rückführungen zu bewegen. Die Kommission hat Kenntnis davon genommen, dass sich die Situation rund um die Rückführungen nach Algerien verbessert hat, die Zusammenarbeit mit diesem Land derzeit gut funktioniert und die algerischen Behörden bei der Rückübernahme algerischer Staatsangehöriger aus der Schweiz uneingeschränkt kooperieren. Doch auch wenn die Situation derzeit zufriedenstellend ist, gibt es keine Garantie dafür, dass dies auch so bleibt. Ein Regierungswechsel könnte ausreichen, um alles wieder infrage zu stellen. Die Kommission ersucht den Bundesrat daher, die Lage weiterhin aufmerksam zu verfolgen, damit er bei Anzeichen einer Verschlechterung unverzüglich die erforderlichen Massnahmen ergreifen kann. Daher ist an der Motion festzuhalten.
+Die Motion beauftragt den Bundesrat, konkrete Massnahmen zu ergreifen, um Algerien zur Rückübernahme seiner Staatsangehörigen im Rahmen von zwangsweisen Rückführungen zu bewegen. Die Kommission hat Kenntnis davon genommen, dass sich die Situation rund um die Rückführungen nach Algerien verbessert hat, die Zusammenarbeit mit diesem Land derzeit gut funktioniert und die algerischen Behörden bei der Rückübernahme algerischer Staatsangehöriger aus der Schweiz uneingeschränkt kooperieren. Doch auch wenn die Situation derzeit zufriedenstellend ist, gibt es keine Garantie dafür, dass dies so bleibt. Ein Regierungswechsel könnte ausreichen, um alles wieder infrage zu stellen. Die Kommission ersucht den Bundesrat daher, die Lage weiterhin aufmerksam zu verfolgen, damit er bei Anzeichen einer Verschlechterung unverzüglich die erforderlichen Massnahmen ergreifen kann. Daher ist an der Motion festzuhalten.
 [VS]
 Proposition CIP-N [GZ]
 Ne pas classer la motion 23.3032
@@ -1182,7 +1182,7 @@
 Antrag GPK-N [GZ]
 Das Postulat 22.3508 nicht abschreiben
 Schriftliche Begründung [GZ]
-Der Bundesrat legt die verschiedenen Massnahmen dar, die er zur Erreichung der im Postulat festgelegten Ziele ergriffen hat. Der Bundesrat hat, wie gefordert, eine kritische Bewertung seiner Krisenorganisation vorgenommen und die Verordnung über die Krisenorganisation der Bundesverwaltung (KOBV) überarbeitet, die am 1. Februar 2025 in Kraft getreten ist. Auf dieser Grundlage hat er einen "Umsetzungsplan für die Basisorganisation im Rahmen der interdepartementalen Krisenorganisation der Bundesverwaltung" erstellt, der verschiedene Aspekte regelt, auf die die GPK in ihrem Bericht hingewiesen hat. Zudem trat 2025 die neue Verordnung über die Koordination im Sanitätsdienst in Kraft, womit die organisatorischen Grundlagen für die Reorganisation des Koordinierten Sanitätsdienstes geschaffen wurden. Schliesslich befasst sich der Entwurf zur Änderung des Epidemiengesetzes, den die GPK im Herbst 2025 im Rahmen eines Mitberichts zuhanden der SGK-S behandelt haben, mit Aspekten der Zusammenarbeit zwischen dem für das Krisenmanagement zuständigen Amt und den anderen Akteuren. Für die Kommission ist das Ziel des Postulates inhaltlich erreicht. Sie stellt jedoch fest, dass die GPK in ihrem Postulat ausdrücklich verlangt hatte, dass der Bundesrat das Ergebnis seiner Arbeiten in einem Bericht darlegt, was hier nicht der Fall ist. Die Kommission beantragt die Ablehnung des Antrages auf Abschreibung des Postulates, bis der "Bericht mit konkreten Empfehlungen zur Weiterentwicklung des nationalen Krisenmanagements" vorliegt, welchen der Bundesrat als Folge der Krisenübung vom November 2025 angekündigt hat (siehe Medienmitteilung des Bundesrates vom 7. November 2025). Darin dürften die wichtigsten Erkenntnisse und möglichen Massnahmen betreffend die Krisenorganisation enthalten sein. Ein solcher Bericht würde dem Begehren der GPK somit abschliessend Rechnung tragen.
+Der Bundesrat legt die verschiedenen Massnahmen dar, die er zur Erreichung der im Postulat festgelegten Ziele ergriffen hat. Der Bundesrat hat, wie gefordert, eine kritische Bewertung seiner Krisenorganisation vorgenommen und die Verordnung über die Krisenorganisation der Bundesverwaltung (KOBV) überarbeitet, die am 1. Februar 2025 in Kraft getreten ist. Auf dieser Grundlage hat er einen "Umsetzungsplan für die Basisorganisation im Rahmen der interdepartementalen Krisenorganisation der Bundesverwaltung" erstellt, der verschiedene Aspekte regelt, auf die die GPK in ihrem Bericht hingewiesen hat. Zudem trat 2025 die neue Verordnung über die Koordination im Sanitätsdienst in Kraft, womit die organisatorischen Grundlagen für die Reorganisation des Koordinierten Sanitätsdienstes geschaffen wurden. Schliesslich befasst sich der Entwurf zur Änderung des Epidemiengesetzes, den die GPK im Herbst 2025 im Rahmen eines Mitberichts zuhanden der SGK-S behandelt haben, mit Aspekten der Zusammenarbeit zwischen dem für das Krisenmanagement zuständigen Amt und den anderen Akteuren. Für die Kommission ist das Ziel des Postulates inhaltlich erreicht. Sie stellt jedoch fest, dass die GPK in ihrem Postulat ausdrücklich verlangt hatte, dass der Bundesrat das Ergebnis seiner Arbeiten in einem Bericht darlegt, was nicht der Fall ist. Die Kommission beantragt die Ablehnung des Antrages auf Abschreibung des Postulates, bis der "Bericht mit konkreten Empfehlungen zur Weiterentwicklung des nationalen Krisenmanagements" vorliegt, welchen der Bundesrat als Folge der Krisenübung vom November 2025 angekündigt hat (siehe Medienmitteilung des Bundesrates vom 7. November 2025). Darin dürften die wichtigsten Erkenntnisse und möglichen Massnahmen betreffend die Krisenorganisation enthalten sein. Ein solcher Bericht würde dem Begehren der GPK somit abschliessend Rechnung tragen.
 [VS]
 Proposition CdG-N [GZ]
 Ne pas classer le postulat 22.3508
@@ -1201,7 +1201,7 @@
 (Tuena, Bischof Edgar, Buffat, Burgherr, Hübscher, Nicolet, Pamini, Schnyder Markus)[GZ]
 Die Motionen 19.3033 und 19.3043 nicht abschreiben
 Schriftliche Begründung [GZ]
-Die Mehrheit der Kommission verweist auf die seit der Annahme der Motionen unternommenen Anstrengungen des Bundesrates zur Verbesserung der wirtschaftlichen Rahmenbedingungen. In Erfüllung der Motionen präsentierte der Bundesrat 2022 zwölf Vorhaben zur Stärkung des Wirtschaftsstandorts Schweiz, zu deren zehn bis Ende 2024 eine Botschaft vorlag. Darüber hinaus plant der Bundesrat auch weitere Massnahmen. Es ist nicht nötig, die beiden konkreten Motionen, die vor nunmehr sieben Jahren eingereicht wurden, weiterhin aufrecht zu erhalten, damit der Bundesrat seine Anstrengungen weiterverfolgt. Die Stärkung des Wirtschaftsstandortes ist ohnehin eine Daueraufgabe. Die Minderheit stellt nicht in Abrede, dass die Arbeiten des Bundesrats in die richtige Richtung zielen. Es sei jedoch wichtig, dass das Parlament die Forderung nach einer Offensive zur Stärkung des Wirtschaftsstandorts aufrechterhalte und dies durch die Nichtabschreibung der Motionen gegenüber dem Bundesrat kommuniziere. 
+Die Mehrheit der Kommission verweist auf die seit der Annahme der Motionen unternommenen Anstrengungen des Bundesrates zur Verbesserung der wirtschaftlichen Rahmenbedingungen. 2022 präsentierte der Bundesrat in Erfüllung der Motionen zwölf Vorhaben zur Stärkung des Wirtschaftsstandorts Schweiz. Zu zehn davon lag bis Ende 2024 eine Botschaft vor. Darüber hinaus plant der Bundesrat auch weitere Massnahmen. Es ist nicht nötig, die beiden konkreten Motionen, die vor nunmehr sieben Jahren eingereicht wurden, weiterhin aufrechtzuerhalten, damit der Bundesrat seine Anstrengungen weiterverfolgt. Die Stärkung des Wirtschaftsstandortes ist ohnehin eine Daueraufgabe. Die Minderheit stellt nicht in Abrede, dass die Arbeiten des Bundesrates in die richtige Richtung zielen. Es sei jedoch wichtig, dass das Parlament die Forderung nach einer Offensive zur Stärkung des Wirtschaftsstandorts aufrechterhalte und dies durch die Nichtabschreibung der Motionen gegenüber dem Bundesrat kommuniziere. 
 [VS]
 Proposition de la majorité CER-N [GZ]
 Classer les motions 19.3033 et 19.3043
@@ -1243,7 +1243,7 @@
     <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, le représentant de l'Union démocratique du centre va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la commune fusionne et devient Tresa, il conserve le poste de syndic jusqu'à aujourd'hui et son entrée au gouvernement tessinois. En 2013, il prend la vice-présidence de l'Union démocratique du centre tessinoise, qu'il présidera ensuite pendant 10 ans, de 2016 à aujourd'hui. L'année 2019 marque un tournant dans sa carrière politique, avec son élection au Grand Conseil tessinois qu'il quittera la même année après son élection au Conseil national. Depuis son entrée en fonction au Conseil national, il est membre de la Commission des institutions politiques et de la Délégation pour les relations avec le Parlement italien. Il siégera par la suite également au sein de la Commission de rédaction de langue italienne, de la Commission de politique extérieure, ainsi que de la Commission de la politique de sécurité.
 Entrepreneur et électricien de formation, il s'engage particulièrement au sein de notre institution en faveur d'un État moins bureaucratique et pour des conditions-cadres favorables aux entreprises en déposant plusieurs interventions allant dans ce sens. Il a également consacré plusieurs de ses interventions parlementaires à la politique migratoire et d'asile, aux questions de sécurité et à la défense des intérêts du canton du Tessin.
 Plusieurs de ses motions ont été adoptées par le Parlement. Nous pouvons citer la motion 21.4076, "Permis de séjour. Rétablir le principe du centre des intérêts". Plus récemment, les Chambres fédérales ont adopté sa motion 25.4013, "Renforcer la sécurité du personnel ferroviaire et des passagers", qui doit conduire à la présentation d'un plan national visant à renforcer la sécurité dans les trains, ainsi que sa motion 25.3438, "Lutte contre le phénomène préoccupant des faux documents en Suisse", qui vise à renforcer le contrôle de l'authenticité des documents d'identité. Enfin, nous avons également adopté sa motion 23.4166, "Mettre fin à la vente en ligne des jouets dangereux pour la santé", qui doit encore être examinée par le Conseil des États.
-Après les spéciales communale, cantonale et fédérale, Piero Marchesi, ancien pilote de rallye, amorce un nouveau virage et se trouve au départ d'une nouvelle étape, l'exécutif cantonal. Nous le remercions pour son engagement au sein de notre conseil et lui souhaitons plein succès dans ses nouvelles fonctions. Et bien entendu, bonne route, Piero ! (Standing ovation; le président remet un bouquet de fleurs à M. Marchesi)[GZ]
+Après les spéciales communale, cantonale et fédérale, Piero Marchesi, ancien pilote de rallye, amorce un nouveau virage et se trouve au départ d'une nouvelle étape, l'exécutif cantonal. Nous le remercions pour son engagement au sein de notre conseil et lui souhaitons plein succès dans ses nouvelles fonctions. Et bien entendu, bonne route, Piero ! (Standing ovation ; le président remet un bouquet de fleurs à M. Marchesi)[GZ]
 [VS][GZ]
 [VS][GZ]
 [VS][GZ]
@@ -1521,7 +1521,7 @@
 Ch. II [GZ]
 Le présent contre-projet sera soumis au vote du peuple et des cantons. Il sera soumis au vote en même temps que l'initiative populaire "Pour un droit de la nationalité moderne (initiative pour la démocratie)", si cette initiative n'est pas retirée, selon la procédure prévue à l'article 139b de la Constitution.
 [VS]
-Präsident (Engler Stefan, Präsident): Wir stimmen über die Nichteintretensanträge der Minderheiten I, II und III ab.
+Präsident (Engler Stefan, Präsident): Wir stimmen über den Nichteintretensantrag der Mehrheit ab.
 </t>
   </si>
   <si>
@@ -1563,7 +1563,7 @@
 [VS]
 Art. 2 [GZ]
 Antrag der Mehrheit [GZ]
-Zustimmung zum Entwurf des Bundesrates
+Zustimmung zum Beschluss des Nationalrates
 [VS]
 Antrag der Minderheit I [GZ]
 (Moser, Jositsch, Maillard Pierre-Yves, Zopfi)[GZ]
@@ -1591,7 +1591,7 @@
 [VS]
 Art. 2 [GZ]
 Proposition de la majorité [GZ]
-Adhérer au projet du Conseil fédéral
+Adhérer à la décision du Conseil national
 [VS]
 Proposition de la minorité I [GZ]
 (Moser, Jositsch, Maillard Pierre-Yves, Zopfi)[GZ]

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -236,10 +236,10 @@
     <t xml:space="preserve">ZH</t>
   </si>
   <si>
-    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen, dass die zweite Schale viel gewichtiger ist und damit also der Sicherheit viel mehr Gewicht zukommt; die Bevölkerung wird mir recht geben.
+    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstverständlich weiss ich das, Frau Wyss. Ich weiss aber auch, dass wir für die Entwicklungshilfe jährlich 3 Milliarden Franken ausgeben, und für das Asyl- und Flüchtlingswesen geben wir weitere 4 Milliarden Franken aus. Nehmen wir einmal die berühmte Apothekerwaage, und legen wir in die eine Schale irgendwelche Programme für die Entwicklungshilfe und in die andere Schale Projekte für die Sicherheit unseres Landes, vor allem für die Sicherheit der kritischen Infrastruktur. Dann wird man sehen, dass die zweite Schale viel gewichtiger ist und damit also der Sicherheit viel mehr Gewicht zukommt; die Bevölkerung wird mir recht geben.
 </t>
   </si>
   <si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -363,10 +363,10 @@
   </si>
   <si>
     <t xml:space="preserve">Il y a des situations où appliquer une règle ne suffit pas. Il faut aussi savoir pourquoi cette règle existe et jusqu'où il est raisonnable de l'appliquer. C'est précisément le sens de la motion que je défends. On le sait, le système Dublin organise la répartition des responsabilités entre les États européens en matière d'asile. Même dans ce cas, des exceptions ont été prévues. C'est précisément de l'une d'entre elles dont nous parlons aujourd'hui.
-Cette exception, c'est la clause de souveraineté. Cette motion ne vise donc pas à réécrire le règlement Dublin ; elle vise à ce que la Suisse utilise la marge de manoeuvre que ce règlement lui donne déjà lorsqu'un enfant atteint dans sa santé risque d'être transféré. Pourquoi ? Parce qu'un enfant malade n'est pas un dossier que l'on peut transférer d'une administration à une autre sans conséquence. Un transfert peut signifier interrompre une thérapie, changer brusquement de médecin, rompre un suivi psychiatrique, ajouter de l'incertitude à un enfant qui a parfois déjà vécu la guerre, vécu la violence, vécu l'exil. Lorsqu'il s'agit d'un enfant, nous avons une responsabilité toute particulière et j'aimerais vraiment que vous l'entendiez.
-La Convention relative aux droits de l'enfant est très claire, l'intérêt supérieur de l'enfant doit être une considération primordiale dans toutes les décisions qu'on prend. Ce principe doit avoir des conséquences concrètes. Le Conseil fédéral nous répond que le SEM examine déjà chaque situation individuellement et minutieusement. Je ne mets évidemment pas en doute ce travail-là, mais c'est précisément là que nous divergeons. Nous estimons, nous, le groupe des Verts, que pour les enfants atteints dans leur santé, la pesée des intérêts doit conduire à une règle claire qui va dans le sens de leur protection. Une règle claire, c'est aussi une règle prévisible pour les familles, pour les médecins, mais également pour l'administration. Soyons pragmatiques, nous parlons ici d'un nombre limité de situations particulièrement vulnérables. Accepter que la Suisse traite ces demandes évite aussi des procédures, des recours, des expertises médicales répétées et parfois de longues batailles juridiques autour de transferts qui peuvent finalement ne pas avoir lieu.
-La protection peut aussi être une forme de pragmatisme ; on doit saisir aujourd'hui cette occasion. On nous dit également que les autres États Dublin sont tenus de garantir les soins nécessaires. C'est vrai sur le papier, mais notre responsabilité ne s'arrête pas au moment où nous remettons un enfant à un autre État. La question que nous devons nous poser aujourd'hui est très concrète. Est-ce raisonnable d'interrompre une prise en charge médicale qui fonctionne pour transférer un enfant malade ailleurs, dans un autre pays, lorsqu'un traitement est envisagé, lorsqu'un lien thérapeutique existe, lorsqu'un nouveau déplacement risque d'aggraver l'état physique ou psychique d'un enfant ? Ma réponse est clairement non. Ce n'est pas ouvrir une brèche dans le système Dublin, au contraire ; ce n'est pas créer un droit général de rester en Suisse et ce n'est certainement pas non plus un effet d'appel. Personne ne choisit la maladie grave de son enfant comme stratégie migratoire. Il s'agit simplement d'utiliser un instrument qui existe. La clause de souveraineté est un instrument qui existe dans la loi, et qui permet, à l'article 17, de protéger les enfants. Cette clause existe parce que les rédacteurs du règlement ont compris qu'aucun système administratif ne peut anticiper toutes les situations humaines.
-La Suisse a une tradition humanitaire, on le sait, mais cette tradition est en train de se perdre, cette tradition est en train de s'effriter à entendre tous les propos tenus lors de cette session extraordinaire sur l'asile. Cette tradition humanitaire, j'ai envie qu'on la maintienne, j'ai envie qu'on la renforce et c'est ici, en Suisse, notre responsabilité. Une tradition n'a de valeur que lorsqu'elle guide nos décisions au moment où elles sont difficiles, voire particulièrement difficiles. On parle de situations vraiment difficiles : on parle d'enfants qui sont malades et qu'on doit réussir à protéger. La dignité humaine ne se mesure pas à la générosité d'un discours, elle se mesure à la manière dont un État traite les plus vulnérables, lorsqu'il y a juridiquement la possibilité de faire autrement. Parmi les personnes vulnérables, les enfants malades doivent évidemment bénéficier d'une protection toute particulière. Nous pouvons demander à chaque État d'assumer ses responsabilités dans le cadre de Dublin et nous pouvons, en même temps, décider qu'un enfant malade ne payera pas le prix de cette rigueur administrative.
+Cette exception, c'est la clause de souveraineté. Cette motion ne vise donc pas à réécrire le règlement Dublin[NB]; elle vise à ce que la Suisse utilise la marge de manoeuvre que ce règlement lui donne déjà lorsqu'un enfant atteint dans sa santé risque d'être transféré. Pourquoi[NB]? Parce qu'un enfant malade n'est pas un dossier que l'on peut transférer d'une administration à une autre sans conséquence. Un transfert peut signifier l'interruption d'une thérapie, un changement brusque de médecin, la rupture d'un suivi psychiatrique, une incertitude supplémentaire pour un enfant qui a parfois déjà vécu la guerre, la violence, l'exil. Lorsqu'il s'agit d'un enfant, nous avons une responsabilité toute particulière et j'aimerais vraiment que vous l'entendiez.
+La Convention relative aux droits de l'enfant est très claire[NB]: l'intérêt supérieur de l'enfant doit être une considération primordiale dans toutes les décisions qu'on prend. Ce principe doit avoir des conséquences concrètes. Le Conseil fédéral nous répond que le SEM examine déjà chaque situation individuellement et minutieusement. Je ne mets évidemment pas en doute ce travail-là, mais c'est précisément là que nous divergeons. Nous estimons, nous, le groupe des Verts, que pour les enfants atteints dans leur santé, la pesée des intérêts doit conduire à une règle claire qui va dans le sens de leur protection. Une règle claire, c'est aussi une règle prévisible pour les familles, pour les médecins, mais également pour l'administration. Soyons pragmatiques, nous parlons ici d'un nombre limité de situations de très grande vulnérabilité. Accepter que la Suisse traite ces demandes évite aussi des procédures, des recours, des expertises médicales répétées et, parfois, de longues batailles juridiques autour de transferts qui peuvent finalement ne pas avoir lieu.
+La protection peut aussi être une forme de pragmatisme[NB]; on doit saisir aujourd'hui cette occasion. On nous dit également que les autres États Dublin sont tenus de garantir les soins nécessaires. C'est vrai sur le papier, mais notre responsabilité ne s'arrête pas au moment où nous remettons un enfant à un autre État. La question que nous devons nous poser aujourd'hui est très concrète. Est-ce raisonnable d'interrompre une prise en charge médicale qui fonctionne pour transférer un enfant malade ailleurs, dans un autre pays, lorsqu'un traitement est envisagé, lorsqu'un lien thérapeutique existe, lorsqu'un nouveau déplacement risque d'aggraver l'état physique ou psychique d'un enfant[NB]? Ma réponse est clairement non. Ce n'est pas ouvrir une brèche dans le système Dublin, au contraire[NB]; ce n'est pas créer un droit général de rester en Suisse et ce n'est certainement pas non plus un effet d'appel. Personne ne choisit la maladie grave de son enfant comme stratégie migratoire. Il s'agit simplement d'utiliser un instrument qui existe. La clause de souveraineté est un instrument qui existe dans la loi, et qui permet, à l'article 17, de protéger les enfants. Cette clause existe parce que les rédacteurs du règlement ont compris qu'aucun système administratif ne pouvait anticiper toutes les situations humaines.
+La Suisse a une tradition humanitaire, on le sait, mais cette tradition est en train de se perdre, cette tradition est en train de s'effriter à entendre tous les propos tenus lors de cette session extraordinaire sur l'asile. Cette tradition humanitaire, j'ai envie qu'on la maintienne, j'ai envie qu'on la renforce et c'est ici, en Suisse, notre responsabilité. Une tradition n'a de valeur que lorsqu'elle guide nos décisions au moment où elles sont difficiles, voire particulièrement difficiles. On parle de situations vraiment difficiles[NB]: on parle d'enfants qui sont malades et qu'on doit réussir à protéger. La dignité humaine ne se mesure pas à la générosité d'un discours, elle se mesure à la manière dont un État traite les plus vulnérables, lorsqu'il y a juridiquement la possibilité de faire autrement. Parmi les personnes vulnérables, les enfants malades doivent évidemment bénéficier d'une protection toute particulière. Nous pouvons demander à chaque État d'assumer ses responsabilités dans le cadre de Dublin et nous pouvons, en même temps, décider qu'un enfant malade ne payera pas le prix de cette rigueur administrative.
 Je vous remercie de votre soutien à cette motion. On parle d'enfants malades qu'on transfère dans le cadre de procédures d'asile. Utilisons cette clause de souveraineté pour les protéger réellement.
 </t>
   </si>
@@ -386,12 +386,12 @@
   <si>
     <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont, noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
 Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorbestraft und islamistisch radikalisiert. Er griff wahllos Menschen an, gefährdete zahlreiche Kinder und verletzte drei Personen teils schwer. Die einst sichere Schweiz wird immer unsicherer. Bei der Bundesanwaltschaft laufen aktuell über 140 Terrorverfahren - ein trauriger Rekord. Gemäss Nachrichtendienst des Bundes ist die Terrorbedrohung erhöht und geprägt vom Dschihadismus. Die allermeisten Dschihadisten sind Ausländer oder Doppelbürger, das bestätigte eine Studie der Fachhochschule ZHAW.
-Auch in den Gefängnissen zeigen sich die Folgen der unkontrollierten Massenmigration in unser Land. 70 Prozent der Insassen sind Ausländer, und weitere 15 Prozent sind Schweizer mit Migrationshintergrund. Das bedeutet, für Schweizer ohne Migrationshintergrund würden 15 Prozent unserer Gefängnisplätze genügen. Diese Zahlen bestätigen es eben klar, man kann es nicht schönreden. Wir haben immer mehr importierte Probleme, importierte Kriminalität und importierte Gewalt; und wir haben immer mehr Opfer.
-Personen, die eingebürgert werden, müssen seit 1992 ihren bisherigen Pass nicht mehr abgeben. Man könne ihnen - das war das Hauptargument für das Doppelbürgerrecht - den Schweizer Pass dann einfacher entziehen, wenn irgendetwas passiere, wenn sie kriminell würden. Der Bundesrat behauptet auch heute in der Stellungnahme zur Motion 26.3617, er nutze den Passentzug zur Terrorbekämpfung. Tatsächlich gab es seit dem Jahr 2000 nur gerade 10 Entzugsverfahren - nur 10 -, siebenmal wurde ein Entzug angeordnet und nur 3 Fälle sind rechtskräftig geworden; und das bei einer Million Einbürgerungen seit dem Jahr 2000. Das beweist, dass die Behörden auch bei den schwersten Verbrechen, bei Terrorgefährdern wegschauen.
-Die heutige Rechtsgrundlage für Ausbürgerungen, Artikel 42 des Bürgerrechtsgesetzes, ist eben ein zahnloser Tiger; das bestätigen die Zahlen. Deshalb braucht es eine griffige Grundlage, nicht nur eine Kann-Bestimmung, sondern eine Muss-Bestimmung. Man muss in bestimmten Fällen den Pass entziehen. Die Motion soll das bei Kapitalverbrechen und bei radikalisierten Gefährdern sicherstellen. Den Fünfer und das Weggli darf es halt nicht mehr geben: Wer seinen Heimatpass bei einer Einbürgerung behalten will, der muss es in Kauf nehmen, dass der Schweizer Pass bei schwersten Verbrechen entzogen wird; staatenlos wird dadurch niemand.
+Auch in den Gefängnissen zeigen sich die Folgen der unkontrollierten Massenmigration in unser Land. 70 Prozent der Insassen sind Ausländer, und weitere 15 Prozent sind Schweizer mit Migrationshintergrund. Das bedeutet, für Schweizer ohne Migrationshintergrund würden 15 Prozent unserer Gefängnisplätze genügen. Diese Zahlen bestätigen es eben klar, man kann es nicht schönreden: Wir haben immer mehr importierte Probleme, importierte Kriminalität und importierte Gewalt; und wir haben immer mehr Opfer.
+Personen, die eingebürgert werden, müssen seit 1992 ihren bisherigen Pass nicht mehr abgeben. Man könne ihnen - das war das Hauptargument für das Doppelbürgerrecht - den Schweizer Pass dann einfacher entziehen, wenn irgendetwas passiere und sie kriminell würden. Der Bundesrat behauptet auch heute in der Stellungnahme zur Motion 26.3617, er nutze den Passentzug zur Terrorbekämpfung. Tatsächlich gab es seit dem Jahr 2000 nur gerade zehn Entzugsverfahren: Siebenmal wurde ein Entzug angeordnet, und nur drei Fälle sind rechtskräftig geworden; und das bei einer Million Einbürgerungen seit dem Jahr 2000. Das beweist, dass die Behörden auch bei den schwersten Verbrechen, bei Terrorgefährdern wegschauen.
+Die heutige Rechtsgrundlage für Ausbürgerungen, Artikel 42 des Bürgerrechtsgesetzes, ist eben ein zahnloser Tiger; das bestätigen die Zahlen. Deshalb braucht es eine griffige Grundlage, nicht nur eine Kann-Bestimmung, sondern eine Muss-Bestimmung. Man muss in bestimmten Fällen den Pass entziehen. Die Motion 26.3617 soll das bei Kapitalverbrechen und bei radikalisierten Gefährdern sicherstellen. Den Fünfer und das Weggli darf es halt nicht mehr geben: Wer seinen Heimatpass bei einer Einbürgerung behalten will, der muss es in Kauf nehmen, dass der Schweizer Pass bei schwersten Verbrechen entzogen wird; staatenlos wird dadurch niemand.
 Dschihadisten und Terroristen sind zu allem fähig. Sie wollen unseren Rechtsstaat, unsere Werte und unsere westliche Lebensweise zerstören. Nur wenn es ihnen dann irgendwann selber an den Kragen geht, berufen Sie sich gerne auf die Annehmlichkeiten unseres Rechtsstaates.
-Wir dürfen nicht warten, bis der nächste Anschlag geschieht. Unsere Bevölkerung hat ein Recht darauf, vor Verbrechern und Terroristen geschützt zu werden. Das ist die Kernaufgabe, das ist die wichtigste Aufgabe unseres Staates. Jedes Opfer ist eines zu viel. Wer unser Land terroristisch angreift oder Kapitalverbrechen begeht, hat sein Bürgerrecht verwirkt. Er ist nicht mehr Teil dieses Landes, er ist nicht mehr Teil dieser Wertegemeinschaft. Wir müssen alles daransetzen, dass solche Leute erst gar nicht zu uns kommen; und wenn sie dennoch hier sind, müssen wir alles tun, sie aus dem Land zu schaffen. Sie haben bei uns nichts verloren, sie gehören ins Gefängnis, wenn nötig ausgebürgert und zurück in ihr Heimatland.
-Es ist ein Gebot des gesunden Menschenverstandes. Kein vernünftiger Mensch in diesem Land will Terroristen und Dschihadisten hierbehalten. Das will niemand, das will kein Schweizer, das will kein Ausländer, das will kein Doppelbürger - das will niemand. Niemand will solche Leute hier bei uns behalten, und wir müssen alles dafür tun, dass sie gehen müssen.
+Wir dürfen nicht warten, bis der nächste Anschlag geschieht. Unsere Bevölkerung hat ein Recht darauf, vor Verbrechern und Terroristen geschützt zu werden. Das ist die Kernaufgabe, das ist die wichtigste Aufgabe unseres Staates. Jedes Opfer ist eines zu viel. Wer unser Land terroristisch angreift oder Kapitalverbrechen begeht, hat sein Bürgerrecht verwirkt. Er ist nicht mehr Teil dieses Landes, er ist nicht mehr Teil dieser Wertegemeinschaft. Wir müssen alles daransetzen, dass solche Leute erst gar nicht zu uns kommen; und wenn sie dennoch hier sind, müssen wir alles tun, um sie aus dem Land zu schaffen. Sie haben bei uns nichts verloren, sie gehören ins Gefängnis, wenn nötig ausgebürgert und zurück in ihr Heimatland gebracht.
+Es ist ein Gebot des gesunden Menschenverstandes. Kein vernünftiger Mensch in diesem Land will Terroristen und Dschihadisten hierbehalten. Das will niemand, das will kein Schweizer, das will kein Ausländer, das will kein Doppelbürger - das will niemand. Niemand will solche Leute hier bei uns behalten. Wir müssen alles dafür tun, dass sie gehen müssen.
 Ich danke Ihnen deshalb für die Annahme dieser Motion. Sie macht unser Land wieder sicherer.
 </t>
   </si>
@@ -402,14 +402,14 @@
     <t xml:space="preserve">Fehr Düsel Nina</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Motion "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die Landesverweisung obligatorisch sein" beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
-Die obligatorische Landesverweisung wird in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen. Die Hauptursache ist die viel zu large, oft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Motion "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die Landesverweisung obligatorisch sein" beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
+    <t xml:space="preserve">Die Motion 26.3131, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein", beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
+Die obligatorische Landesverweisung wird in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen. Die Hauptursache i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion 26.3131, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein", beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
 Die obligatorische Landesverweisung wird in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen. Die Hauptursache ist die viel zu large, oft angewendete Härtefallklausel, obwohl sie eigentlich als Ausnahme ausgestaltet wurde. Leider ist die Härtefallklausel keine Ausnahme mehr. Von den angeordneten Landesverweisungen werden gemäss SEM schweizweit nur 63 Prozent vollzogen, und die Unterschiede im kantonalen Vollzug sind enorm. Dies macht unseren Rechtsstaat unglaubwürdig. Der Grossteil der Bevölkerung fordert bei schweren Straftaten von Ausländern mehr Ausschaffungen.
 Dänemark macht es vor und schafft Kriminelle ab einem Jahr Freiheitsstrafe automatisch aus. Dieses Gesetz trat am 1. Mai 2016 in Kraft. Es hat natürlich auch eine abschreckende Wirkung; die Asylzahlen sind seither stark zurückgegangen - ein Erfolg. Diesem wegweisenden Beispiel soll auch die Schweiz folgen: Der Gesetzgeber soll die Landesverweisung bei längeren Freiheitsstrafen für alle Konstellationen als verhältnismässig und Härtefälle als ausgeschlossen erklären.
-Der Bundesrat ist hier leider sehr zurückhaltend. Einmal mehr bringt er als Grund, dass fehlende Reisedokumente oder mangelnde Kooperation den Vollzug verunmöglichen können. Diese Hindernisse dürfen aber keinen Grund gegen einen Vollzug darstellen. Ich habe auf dem Gericht und auf der Staatsanwaltschaft gearbeitet und oft erlebt, dass Pässe und Reisedokumente verschwunden sind, vielleicht auch durch Absicht, um einer Ausschaffung zu entgehen. Wir müssen uns Dänemark anschliessen und unsere Praxis endlich verschärfen. Es darf bei Ausschaffungen auch nicht so grosse kantonale Unterschiede geben. Um eine Freiheitsstrafe von einem Jahr zu erhalten, sei dies bedingt oder unbedingt, braucht es etwas. Man kriegt nicht einfach so eine längere Freiheitsstrafe, es handelt sich nicht um Bagatelldelikte. Die Bevölkerung fordert bei Ausschaffungen schon seit längerer Zeit eine härtere Praxis, und die Europäische Menschenrechtskonvention (EMRK) darf nicht immer als Grund dagegen vorgebracht werden.
+Der Bundesrat ist hier leider sehr zurückhaltend. Einmal mehr bringt er als Grund vor, dass fehlende Reisedokumente oder mangelnde Kooperation den Vollzug verunmöglichen können. Diese Hindernisse dürfen aber keinen Grund gegen einen Vollzug darstellen. Ich habe auf dem Gericht und auf der Staatsanwaltschaft gearbeitet und es oft erlebt, dass Pässe und Reisedokumente verschwunden sind, vielleicht auch durch Absicht, um einer Ausschaffung zu entgehen. Wir müssen uns Dänemark anschliessen und unsere Praxis endlich verschärfen. Es darf bei Ausschaffungen auch nicht so grosse kantonale Unterschiede geben. Um eine Freiheitsstrafe von einem Jahr zu erhalten, sei dies bedingt oder unbedingt, braucht es etwas. Man kriegt nicht einfach so eine längere Freiheitsstrafe, es handelt sich nicht um Bagatelldelikte. Die Bevölkerung fordert bei Ausschaffungen schon seit längerer Zeit eine härtere Praxis, und die Europäische Menschenrechtskonvention (EMRK) darf nicht immer als Grund dagegen vorgebracht werden.
 Bitte unterstützen Sie unsere Fraktionsmotion.
 </t>
   </si>
@@ -423,15 +423,15 @@
     <t xml:space="preserve">BE</t>
   </si>
   <si>
-    <t xml:space="preserve">Bei diesem Vorstoss geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
-Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bei diesem Vorstoss geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
+    <t xml:space="preserve">Bei der Motion 26.3616 geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
+Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bei der Motion 26.3616 geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
 Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5000 regulären Unterbringungsplätzen in seinen Bundesasylzentren; in besonderen Situationen soll die Kapazität sogar auf 10 000 Plätze erhöht werden können. Diese grossen Einrichtungen wirken sich auf die Gemeinde, die Schulen, den Verkehr, die Sicherheit, das lokale Gewerbe sowie grundsätzlich auf das Zusammenleben vor Ort aus. Wer diese Auswirkungen tragen muss, soll entsprechend mitbestimmen können.
-Der Bundesrat führt an, dass die Gemeinden angehört würden. Doch angehört zu werden ist nicht dasselbe wie mitzuentscheiden. Weder eine Informationsveranstaltung noch eine Stellungnahme oder ein Einspracheverfahren ersetzen die demokratische Mitsprache bzw. das Recht einer Gemeinde, einen Standort abzulehnen.
+Der Bundesrat führt an, dass die Gemeinden angehört würden. Doch angehört zu werden, ist nicht dasselbe wie mitzuentscheiden. Weder eine Informationsveranstaltung noch eine Stellungnahme oder ein Einspracheverfahren ersetzen die demokratische Mitsprache bzw. das Recht einer Gemeinde, einen Standort abzulehnen.
 Hier setzt der Vorstoss an. Wir wollen weder zusätzliche Bürokratie noch eine Blockade, sondern etwas ganz Einfaches: Will der Bund in einer Gemeinde ein neues Bundesasylzentrum errichten, muss die betroffene Standortgemeinde zustimmen. Dies ist kein radikaler Gedanke, sondern Ausdruck des Föderalismus und der Gemeindeautonomie - und es entspricht unserem Verständnis von Demokratie. Es darf nicht sein, dass der Bund am grünen Tisch über den Standort grosser Asylunterkünfte entscheidet, während die betroffene Bevölkerung lediglich informiert wird.
-Niemand bestreitet die Verantwortung des Bundes im Asylwesen. Diese bedeutet jedoch nicht, dass er über die Köpfe der Gemeinden hinweg entscheiden darf. Die letzten Jahre haben gezeigt, wie schnell sich die Situation im Asylbereich verändern kann. Im Jahr 2025 wurden in der Schweiz 25 000 Asylgesuche gestellt. Der Bund musste seine Unterbringungskapazitäten massiv ausbauen und hält fest, dass die Bereitstellung von Unterbringungsplätzen für Kantone und Gemeinden eine grosse Herausforderung darstellt.
+Niemand bestreitet die Verantwortung des Bundes im Asylwesen. Sie bedeutet jedoch nicht, dass er über die Köpfe der Gemeinden hinweg entscheiden darf. Die letzten Jahre haben gezeigt, wie schnell sich die Situation im Asylbereich verändern kann. Im Jahr 2025 wurden in der Schweiz 25 000 Asylgesuche gestellt. Der Bund musste seine Unterbringungskapazitäten massiv ausbauen und hält fest, dass die Bereitstellung von Unterbringungsplätzen für Kantone und Gemeinden eine grosse Herausforderung darstellt.
 Daher muss die Verantwortung dort wahrgenommen werden, wo sie hingehört. Immer grössere Strukturen zu schaffen und den Gemeinden erst danach zu erklären, warum sie diese akzeptieren müssen - das geht nicht. Zuerst muss gefragt werden, ob eine Gemeinde dies überhaupt will. Der Bund fordert Planungssicherheit, doch auch die Gemeinden benötigen Planungssicherheit. Eine Gemeinde muss wissen, was auf ihrem Gebiet geschieht, und die Bevölkerung hat Anspruch darauf, dass ihre demokratischen Rechte ernst genommen werden.
 Des Weiteren enthält der Vorstoss eine ausdrückliche Ausnahme für den Asylnotstand. Es geht nicht darum, dass eine Gemeinde in einer ausserordentlichen Krisensituation jede staatliche Massnahme verhindern kann. Ausserhalb eines Notstandes muss jedoch gelten: keine neuen, grossen Asylunterkünfte gegen den ausdrücklichen Willen der betroffenen Standortgemeinde.
 Ich bitte Sie, den Vorstoss zu unterstützen.
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t xml:space="preserve">Herr Knutti, es ist Sache der Gemeinde, das Verfahren festzulegen. Der Bundesrat kann nicht beschliessen, ob es dazu eine Volksentscheidung gibt oder nicht. Das muss die Gemeinde machen. Der Bundesrat ist in Diskussion mit den Asylregionen. 
-Ich gebe Ihnen ein Beispiel: Die Asylregion Zentralschweiz und Tessin muss aufgrund ihrer Bevölkerungsgrösse gemeinsam einen bestimmten Prozentsatz der Asylsuchenden betreuen. Dazu gehören einerseits die Bundesasylzentren mit Verfahren, dann gibt es Asylzentren ohne Verfahren und die kantonalen Asylzentren. Diese Regionen sind beauftragt, die nötigen Unterbringungsplätze zu suchen. Wenn sich in einem Kanton eine Möglichkeit ergibt, dann geht in diesem Kanton respektive in der Gemeinde der ganz normale Planungsprozess voran. Wenn die Gemeinde sagt, nein, diese Nutzungsplanung akzeptieren wir nicht, das wollen wir nicht, hier hat es keinen Platz für ein Asylzentrum, dann gibt es dort auch keines. Das ist ja der Grund, warum einzelne Asylregionen bis heute nicht genügend solche Plätze zur Verfügung stellen können und andere, die sich sehr bemüht haben, bei sich eine Lösung zu finden, zum Teil stark belastet sind.
+Ich gebe Ihnen ein Beispiel: Die Asylregion Zentralschweiz und Tessin muss aufgrund ihrer Bevölkerungsgrösse gemeinsam einen bestimmten Prozentsatz der Asylsuchenden betreuen. Dazu gehören einerseits die Bundesasylzentren mit Verfahren, dann gibt es Asylzentren ohne Verfahren und die kantonalen Asylzentren. Die Asylregionen sind beauftragt, die nötigen Unterbringungsplätze zu suchen. Wenn sich in einem Kanton eine Möglichkeit ergibt, dann geht in diesem Kanton respektive in der Gemeinde der ganz normale Planungsprozess voran. Wenn die Gemeinde sagt, nein, diese Nutzungsplanung akzeptieren sie nicht, das wollen sie nicht, bei ihr habe es keinen Platz für ein Asylzentrum, dann gibt es dort auch keines. Das ist ja der Grund, warum einzelne Asylregionen bis heute nicht genügend solche Plätze zur Verfügung stellen können und andere, die sich sehr bemüht haben, bei sich eine Lösung zu finden, zum Teil stark belastet sind.
 </t>
   </si>
   <si>
@@ -459,13 +459,13 @@
     <t xml:space="preserve">Rutz Gregor</t>
   </si>
   <si>
-    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">In meiner Motion geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, dass also Leute, die schon in sicheren Staaten leben, hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige neue Motive ergänzt und es eben einen Unterschied gibt zwischen Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
-Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27. Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." Es erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist diese Orientierung am EuGH sicher nicht das Relevante. Trotzdem sagen Sie dann, nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, die über alle Gesuche 97,5 Prozent Zustimmung ergibt. Das erstaunt und sieht dann doch eher nach einer pauschalen Prüfung aus. Wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das erhellende Fakten zutage bringt. Dieser Fragebogen lag dem Bundesverwaltungsgericht nämlich vor. Es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche diese gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen - also Ihr Staatssekretariat, das mit diesen Fragen befasst ist - den eigentlichen Willen des Gesetzgebers, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhält, würde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiellrechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
+    <t xml:space="preserve">In meiner Motion 26.3668 geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze We</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In meiner Motion 26.3668 geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, sodass Leute, die schon in sicheren Staaten leben, hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige, neue Motive ergänzt hat und dass es eben einen Unterschied gibt zwischen einer Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
+Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27. Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." (AB 2024 N 809) Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." Es erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist diese Orientierung am EuGH sicher nicht das Relevante. Trotzdem sagen Sie dann, nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, die über alle Gesuche 97,5 Prozent Zustimmung ergibt. Das erstaunt und sieht dann doch eher nach einer pauschalen Prüfung aus. Wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das erhellende Fakten zutage bringt. Dieser Fragebogen lag dem Bundesverwaltungsgericht nämlich vor. Es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche sie gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen - also Ihr Staatssekretariat, das mit diesen Fragen befasst ist - den eigentlichen Willen des Gesetzgebers, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhalte, werde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiell-rechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
 Hier müssen Sie, Herr Bundesrat, einmal ganz gründlich aufräumen und wirklich noch einmal über die Bücher gehen. Es geht nicht an, dass Bundesämter arbeiten, ohne sich ans Gesetz zu halten. Sie werden jetzt sagen, dass Sie keine Einzelfälle dokumentieren oder kommentieren. Sie werden sagen, dieses Urteil sei ein Einzelfallurteil. Ja, aber man kann dieses Urteil lesen, und es ist ganz genau dokumentiert und aktenkundig, wie hier korrespondiert wird, wie man mit diesen Einzelfällen umgeht. Das geht so nicht. 
-Meine Motion möchte etwas ganz Einfaches: erstens, dass man sich im Staatssekretariat für Migration ans Gesetz hält, und zweitens, dass man diese Praxisänderung, die offensichtlich gesetzeswidrig ist, rückgängig macht und die Fälle einzeln prüft, damit diejenigen Leute Schutz und Aufnahme erhalten, die es nötig haben und nicht die ganze Welt eingeladen wird, in die Schweiz zu kommen. 
+Meine Motion möchte etwas ganz Einfaches: Sie möchte erstens, dass man sich im Staatssekretariat für Migration ans Gesetz hält, und zweitens, dass man diese Praxisänderung, die offensichtlich gesetzeswidrig ist, rückgängig macht und die Fälle einzeln prüft, damit diejenigen Leute Schutz und Aufnahme erhalten, die es nötig haben, und nicht die ganze Welt eingeladen wird, in die Schweiz zu kommen. 
 Darum bitte ich Sie hier um Zustimmung.
 </t>
   </si>
@@ -474,13 +474,13 @@
   </si>
   <si>
     <t xml:space="preserve">Das habe ich in meiner Rede vergessen, es ist sehr gut, dass ich das noch nachliefern kann. Sie verdienen hier eine Antwort. Der Bundesrat ist wirklich entschlossen, gegen diese Leute entschlossener vorzugehen. 
-Wir haben zunächst einmal die Verfahren für Leute aus Nordafrika beschleunigt, sie dauern jetzt nur noch maximal 24 Tage gegenüber etwa 100 Tagen in normalen Verfahren. Das 24-Stunden-Verfahren hat also Wirkung gezeigt, insofern, dass es nun 50 Prozent weniger Übernachtungen in Bundesasy</t>
+Wir haben zunächst einmal die Verfahren für Leute aus Nordafrika beschleunigt, sie dauern jetzt nur noch maximal 24 Tage gegenüber etwa 100 Tagen in normalen Verfahren. Das 24-Stunden-Verfahren hat also insofern Wirkung gezeigt,als es nun 50 Prozent weniger Übernachtungen von Personen au</t>
   </si>
   <si>
     <t xml:space="preserve">Das habe ich in meiner Rede vergessen, es ist sehr gut, dass ich das noch nachliefern kann. Sie verdienen hier eine Antwort. Der Bundesrat ist wirklich entschlossen, gegen diese Leute entschlossener vorzugehen. 
-Wir haben zunächst einmal die Verfahren für Leute aus Nordafrika beschleunigt, sie dauern jetzt nur noch maximal 24 Tage gegenüber etwa 100 Tagen in normalen Verfahren. Das 24-Stunden-Verfahren hat also Wirkung gezeigt, insofern, dass es nun 50 Prozent weniger Übernachtungen in Bundesasylzentren gibt von Personen aus Maghreb-Staaten. Das ist ein erster Erfolg, reicht aber bei Weitem nicht. Deshalb haben wir als weitere Massnahme die Einzelbetreuung installiert. Zu allen Asylregionen gibt es jetzt sogenannte runde Tische, an denen Mitglieder von Behörden, Polizei, Asyl- und Sozialbereich und so weiter zusammensitzen. Sie schauen sich Fall für Fall an, der ihnen gemeldet wird, um sicherzustellen, dass die Leute in die Strafverfolgung überführt werden können. 
-Dann haben wir eine Taskforce eingesetzt, die ganz gezielt Vorschläge macht, wie wir in der Strafverfolgung noch griffigere Instrumente erhalten - denn diese Leute missbrauchen das System natürlich in vielerlei Hinsicht. Zum Beispiel könnte die Schwelle für Administrativhaft für solche Leute gesenkt werden, sodass wir sie besser in Haft nehmen können, um sie schneller ausschaffen zu können. Das sind alles Dinge, die wir jetzt im Rahmen der Asylstrategie für Sie vorbereiten. Hier bekommen Sie ganz konkrete Vorschläge, und das meinen wir ernst, solche wollen wir Ihnen vorlegen. 
-Ein zweiter Vorschlag, den wir im Rahmen der Asylstrategie auch mit den Kantonen und Gemeinden diskutieren, ist das vorgelagerte Zuweisungsverfahren. Menschen, die gar keine Asylgründe geltend machen, sollen auch nicht in ein Asylzentrum kommen. Sie belasten das System dort nur, verzögern die Prozesse, und oft sind es eben genau diese Personen, die dann kriminell werden. Das ist eine Realität. Das muss man auch benennen und ansprechen. Das können wir nicht akzeptieren, und mit diesem neuen Vorschlag hoffen wir, dass wir das Asylwesen in unserem Land insbesondere für Menschen, die nicht schutzbedürftig sind, weniger attraktiv machen können und diese Menschen draussen behalten können. Das soll eine abschreckende Wirkung haben, das ist das Ziel. 
+Wir haben zunächst einmal die Verfahren für Leute aus Nordafrika beschleunigt, sie dauern jetzt nur noch maximal 24 Tage gegenüber etwa 100 Tagen in normalen Verfahren. Das 24-Stunden-Verfahren hat also insofern Wirkung gezeigt,als es nun 50 Prozent weniger Übernachtungen von Personen aus Maghreb-Staaten in Bundesasylzentren gibt. Das ist ein erster Erfolg, reicht aber bei Weitem nicht. Deshalb haben wir als weitere Massnahme die Einzelbetreuung installiert. Zu allen Asylregionen gibt es jetzt sogenannte runde Tische, an denen Mitglieder von Behörden, Polizei, Asyl- und Sozialbereich und so weiter zusammensitzen. Sie schauen sich Fall für Fall an, der ihnen gemeldet wird, um sicherzustellen, dass die Leute in die Strafverfolgung überführt werden können. 
+Dann haben wir eine Taskforce eingesetzt, die ganz gezielt Vorschläge macht, wie wir in der Strafverfolgung noch griffigere Instrumente erhalten - denn diese Leute missbrauchen das System natürlich in vielerlei Hinsicht. Zum Beispiel könnte die Schwelle für Administrativhaft für solche Leute gesenkt werden, sodass wir sie besser in Haft nehmen können, um sie schneller ausschaffen zu können. Das sind alles Dinge, die wir jetzt im Rahmen der Asylstrategie für Sie vorbereiten. Hier bekommen Sie ganz konkrete Vorschläge, und das meinen wir ernst, solche Vorschläge wollen wir Ihnen vorlegen. 
+Ein zweiter Vorschlag, den wir im Rahmen der Asylstrategie auch mit den Kantonen und Gemeinden diskutieren, ist das vorgelagerte Zuweisungsverfahren. Menschen, die gar keine Asylgründe geltend machen, sollen auch nicht in ein Asylzentrum kommen. Sie belasten das System dort nur, verzögern die Prozesse. Oft sind es eben genau diese Personen, die dann kriminell werden. Das ist eine Realität. Das muss man auch benennen und ansprechen. Das können wir nicht akzeptieren. Mit diesem neuen Vorschlag hoffen wir, dass wir das Asylwesen in unserem Land insbesondere für Menschen, die nicht schutzbedürftig sind, weniger attraktiv machen können und dass wir diese Menschen draussen behalten können. Es soll eine abschreckende Wirkung haben, das ist das Ziel. 
 Wir sind dran, aber die Kantone und Gemeinden müssen das dann umsetzen, sie müssen die Rückkehren organisieren und auch die notwendigen Haftplätze zur Verfügung stellen. Deshalb ist es sehr wichtig, dass die Kantone hinter diesen Massnahmen stehen.
 </t>
   </si>
@@ -494,12 +494,12 @@
     <t xml:space="preserve">TI</t>
   </si>
   <si>
-    <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion.
-Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, zulässig oder zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule, sie bauen sich ein </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion.
-Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, zulässig oder zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule, sie bauen sich ein soziales Umfeld auf, und trotzdem bleibt ihr Aufenthaltsstatus provisorisch.
+    <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion 24.4063.
+Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, nicht zulässig oder nicht zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion 24.4063.
+Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, nicht zulässig oder nicht zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule, sie bauen sich ein soziales Umfeld auf, und trotzdem bleibt ihr Aufenthaltsstatus provisorisch.
 Meine Motion verlangt deshalb eine pragmatische Lösung: Wer seit zehn Jahren vorläufig in der Schweiz aufgenommen ist, soll eine Aufenthaltsbewilligung erhalten. Ausnahmen bleiben selbstverständlich möglich, insbesondere bei schweren Straftaten oder wenn die Sicherheit der Schweiz gefährdet ist. Es geht nicht darum, nach kurzer Zeit automatisch ein dauerhaftes Aufenthaltsrecht zu gewähren. Es geht darum, nach zehn Jahren die rechtliche Situation an eine Realität anzupassen, die längst besteht.
 Der Bundesrat anerkennt das Problem selbst. Er weist darauf hin, dass die vorläufige Aufnahme in vielen Fällen länger dauert und dass deshalb verschiedene Massnahmen zur Verbesserung der Integration getroffen wurden. Genau hier liegt der Widerspruch. Wir investieren zu Recht in die Integration dieser Menschen. Wir wollen, dass sie eine Sprache lernen, arbeiten, eine Ausbildung absolvieren und wirtschaftlich selbstständig werden. Gleichzeitig halten wir sie über Jahre in einem Status, der ihnen sagt, eure Zukunft hier bleibt ungewiss. Das ist integrationspolitisch nicht sinnvoll.
 Oggi, dopo cinque anni è possibile presentare una domanda per ottenere un permesso di dimora. Ma questa possibilità non risolve il problema di fondo. Con la mia mozione, pongo volutamente una soglia molto alta, una soglia di dieci anni. Dopo dieci anni, non possiamo più sostenere di essere di fronte ad una situazione temporanea. Continuare a chiamarla "ammissione provvisoria" non cambia la realtà dei fatti.
@@ -515,7 +515,7 @@
   </si>
   <si>
     <t xml:space="preserve">Ich muss zuerst im Rahmen einer persönlichen Erklärung etwas berichtigen, weil mich Herr Bundesrat Jans falsch zitiert hat. Ich habe nie davon gesprochen, dass der Abschreibungsentscheid des Bundesverwaltungsgerichts vom 20. November 2025 oder auch die anderen von mir zitierten Urteile des Bundesverwaltungsgerichts Leitentscheide gewesen seien oder eine Änderung oder Weiterentwicklung der Rechtsprechung bewirkt hätten. Im Gegenteil, ich habe gesagt, dass das Bundesverwaltungsgericht seine Praxis immer bestätigt hat. Und wenn der Autor Ihrer Notiz die Debatten der letzten Jahre aufmerksam gelesen hätte, hätte er gemerkt, dass ich auch schon 2023 und 2024 genau gleich argumentiert habe. 
-Vor diesem Hintergrund nun zu meiner Frage, Herr Bundesrat Jans: Das Bundesverwaltungsgericht schreibt in diesem zitierten Entscheid, ein Fragebogen sei für eine Einzelfallprüfung ungeeignet und das Staatssekretariat für Migration schüre Erwartungen, die mit verfahrensrechtlichen und materiell rechtlichen Vorgaben des Asylgesetzes nicht vereinbar seien; diese Korrespondenz ist dokumentiert. Wie um Himmels Willen kommen Sie dann dazu, zu schreiben, es liege kein Urteil des Bundesverwaltungsgerichts vor, welches die Asylpraxis gegenüber afghanischen Frauen kritisiert oder infrage stellt? Herr Bundesrat Jans, gelten gewisse Gerichtsurteile für den Justizminister nicht, wenn er es besser zu wissen glaubt, oder gelten diese Gerichtsurteile auch für den Justizminister?
+Vor diesem Hintergrund nun zu meiner Frage, Herr Bundesrat Jans: Das Bundesverwaltungsgericht schreibt im zitierten Entscheid, ein Fragebogen sei für eine Einzelfallprüfung ungeeignet und das Staatssekretariat für Migration schüre Erwartungen, die mit verfahrensrechtlichen und materiell-rechtlichen Vorgaben des Asylgesetzes nicht vereinbar seien; diese Korrespondenz ist dokumentiert. Wie um Himmels willen kommen Sie dann dazu, zu schreiben, es liege kein Urteil des Bundesverwaltungsgerichts vor, welches die Asylpraxis gegenüber afghanischen Frauen kritisiere oder infrage stelle? Herr Bundesrat Jans, gelten gewisse Gerichtsurteile für den Justizminister nicht, wenn er es besser zu wissen glaubt, oder gelten diese Gerichtsurteile auch für den Justizminister?
 </t>
   </si>
   <si>
@@ -525,10 +525,10 @@
     <t xml:space="preserve">Graber Michael</t>
   </si>
   <si>
-    <t xml:space="preserve">Herr Bundesrat, Sie haben ausgeführt, dass die Beibehaltung des Schutzstatus S für Ukrainerinnen und Ukrainer sehr wichtig sei. Gleichzeitig unterstützen sie es aber, dass junge ukrainische Männer zurück an die Front müssen. Da spielen Sie den Steigbügelhalter der EU, um Selenski weiteres Kanonenfutter anzubieten. Schauen Sie einmal hin, was in der Ukraine passiert. Da werden die jungen Männer in Busse gezwungen und als Kanonenfutter an die Front gebracht. Wie können Sie es mit Ihrem Gewissen ve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herr Bundesrat, Sie haben ausgeführt, dass die Beibehaltung des Schutzstatus S für Ukrainerinnen und Ukrainer sehr wichtig sei. Gleichzeitig unterstützen sie es aber, dass junge ukrainische Männer zurück an die Front müssen. Da spielen Sie den Steigbügelhalter der EU, um Selenski weiteres Kanonenfutter anzubieten. Schauen Sie einmal hin, was in der Ukraine passiert. Da werden die jungen Männer in Busse gezwungen und als Kanonenfutter an die Front gebracht. Wie können Sie es mit Ihrem Gewissen vereinbaren, junge Männer in den sicheren Tod in die Ukraine zu schicken, während andere nicht gefährdete Personengruppen aus der Ukraine in diesem Land bleiben können?
+    <t xml:space="preserve">Herr Bundesrat, Sie haben ausgeführt, dass die Beibehaltung des Schutzstatus S für Ukrainerinnen und Ukrainer sehr wichtig sei. Gleichzeitig unterstützen Sie es aber, dass junge ukrainische Männer zurück an die Front müssen. Da spielen Sie den Steigbügelhalter der EU, um Selenski weiteres Kanonenfutter anzubieten. Schauen Sie einmal hin, was in der Ukraine passiert. Da werden die jungen Männer in Busse gezwungen und als Kanonenfutter an die Front gebracht. Wie können Sie es mit Ihrem Gewissen ve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Bundesrat, Sie haben ausgeführt, dass die Beibehaltung des Schutzstatus S für Ukrainerinnen und Ukrainer sehr wichtig sei. Gleichzeitig unterstützen Sie es aber, dass junge ukrainische Männer zurück an die Front müssen. Da spielen Sie den Steigbügelhalter der EU, um Selenski weiteres Kanonenfutter anzubieten. Schauen Sie einmal hin, was in der Ukraine passiert. Da werden die jungen Männer in Busse gezwungen und als Kanonenfutter an die Front gebracht. Wie können Sie es mit Ihrem Gewissen vereinbaren, junge Männer in den sicheren Tod in die Ukraine zu schicken, während andere, nicht gefährdete Personengruppen aus der Ukraine in diesem Land bleiben können?
 </t>
   </si>
   <si>
@@ -541,44 +541,37 @@
   <si>
     <t xml:space="preserve">Der Bundesrat lehnt die neun ausserordentlich traktandierten Motionen ab. Seiner Ansicht nach ist bei diesen weder die Ausserordentlichkeit noch die Dringlichkeit gegeben.
 Die Ausgangslage im Bereich Asyl präsentiert sich wie folgt: Die Asylgesuche gehen weiter zurück. In diesem Jahr verzeichnen wir fast 20 Prozent weniger Gesuche als im Vorjahr. Das SEM hat seine Prognose für 2026 um 3000 Asylgesuche gesenkt. Sie sinken somit im dritten Jahr in Folge, und wenn die tieferen Prognosen zutreffen, liegen wir Ende Jahr 27 Prozent tiefer als 2023.
-Auch die Pendenzen konnten stark reduziert werden. Als ich mein Amt antrat, hatten wir fast 10 000 offene Pendenzen; aktuell sind wir bei 2500 und wollen bis Ende Jahr alle Pendenzen abgebaut haben, obwohl das SEM wegen des Entlastungsprogrammes 150 Stellen streichen musste. Weniger Asylgesuche und Pendenzen entlasten das System; die Kantone und Gemeinden beginnen dies zu spüren.
+Auch die Pendenzen konnten stark reduziert werden. Als ich mein Amt antrat, hatten wir fast 10 000 Pendenzen; aktuell sind wir bei 2500 und wollen bis Ende Jahr alle abgebaut haben, obwohl das SEM wegen des Entlastungsprogrammes 150 Stellen streichen musste. Weniger Asylgesuche und Pendenzen entlasten das System; die Kantone und Gemeinden beginnen dies zu spüren.
 Die Zahl der Aufgriffe von irregulär Eingereisten ist gegenüber dem Vorjahr um 50 Prozent zurückgegangen. Verschiedene Massnahmen, die wir ergriffen haben, zeigen Wirkung. Für Asylsuchende aus nordafrikanischen Ländern haben wir die Verfahren stark beschleunigt, was ebenfalls das ganze System entlastet und die Schweiz als Zielland weniger attraktiv macht. Dank der neuen Einzelfallbehandlung an den runden Tischen aller Asylregionen sowie der neu eingesetzten Taskforce konnten mehr straffällige Asylsuchende der Strafverfolgung zugeführt werden. Die Zahl der Sicherheitsvorfälle in den Bundesasylzentren hat sich innerhalb von zwei Jahren mehr als halbiert.
-Wir führen etwa doppelt so viele abgewiesene Asylsuchende zurück wie alle anderen vergleichbaren europäischen Länder. Dabei stützen wir uns auf mehr als sechzig Abkommen mit Herkunftsstaaten. Ende Mai haben wir sogar ein Abkommen mit Marokko abgeschlossen; damit konnten wir auch die Rückführungen in dieses Land verbessern. Das schaffen viele andere Länder nicht.
-Doch nicht nur bei der Rückkehr sind wir in Europa Vorreiter. Mehr als fünfzig Prozent der Flüchtlinge und vorläufig Aufgenommenen haben bei uns nach fünf Jahren einen Job, was dank Arbeit durch Ausbildung möglich ist. Dies setzen wir zusammen mit den Kantonen erfolgreich um, wie auch die OECD anerkennt.
-So viel zur Ausgangslage, nun komme ich zu den einzelnen Vorstössen.
-Ich beginne mit der Motion 26.3615 der SVP-Fraktion: Es geht hier um einen Vorstoss, den ich im Auftrag des abwesenden Bundespräsidenten vertreten muss; sie ist seinem Departement zugeordnet. Es geht um die Frage, welches Land die Arbeitslosengelder von Grenzgängerinnen und Grenzgängern bezahlt, die ihren Job verloren haben. Diese Motion will diese Frage beantworten, bevor sie sich überhaupt stellt, bevor wir überhaupt die Ausgangslage kennen. Es ist schlicht und einfach zu früh, hier schon Entscheide zu fassen. Deshalb lehnt der Bundesrat diese Motion ab. Die Änderung der EU-Verordnung 883/2004 sieht vor, dass künftig der letzte Beschäftigungsstaat für die Ausrichtung der Arbeitslosenentschädigung von Grenzgängerinnen und Grenzgängern zuständig sein soll. Aktuell ist die Situation umgekehrt geregelt, in Kombination mit einem Rückerstattungssystem zwischen Beschäftigungs- und Wohnsitzstaat. 
-Die Schweiz beteiligt sich seit dem Inkrafttreten des Freizügigkeitsabkommens an der EU-weiten Koordinierung der Systeme der sozialen Sicherheit. Dazu gehört auch die erwähnte EU-Verordnung. Heute profitieren davon nicht zuletzt Schweizerinnen und Schweizer, die in einem EU-Mitgliedstaat leben und arbeiten. Das vergessen Sie immer wieder: Es gibt auch Schweizer, die in der EU leben, und für diese gelten auch Regeln, von denen sie profitieren können. Wenn Sie eine Auslegeordnung des Systems machen, müssen Sie das berücksichtigen, bevor Sie hierzu Entscheide fällen. 
-Seit 2013 hat die Arbeitslosenversicherung mit den Leistungen der Grenzgängerinnen und Grenzgänger einen jährlichen Überschuss von durchschnittlich 280 Millionen Schweizerfranken gemacht. Aktuell wissen wir nicht, wann die Revision in der EU in Kraft treten wird. Wie frühere Anpassungen muss auch dieser EU-Beschluss das innerstaatliche Genehmigungsverfahren durchlaufen. Dann muss die EU die Verordnungsanpassung für eine nächste Sitzung des gemischten Ausschusses anmelden. Dies ist bis jetzt noch nicht geschehen. Das liegt unter anderem daran, dass das Revisionsverfahren auf EU-Ebene noch nicht abgeschlossen ist. Es fehlen noch die formelle Verabschiedung durch den Rat der EU, die Unterzeichnung durch die Rats- und Parlamentspräsidien sowie die Veröffentlichung im Amtsblatt der EU. 
-Die Haltung des Bundesrates lässt sich also wie folgt zusammenfassen: Der Bundesrat lehnt einen verfrühten Positionsbezug ab. Es ist zu früh, einen Entscheid über eine allfällige Übernahme oder Nichtübernahme der noch nicht abgeschlossenen Revision zu fällen. Der Bundesrat verfolgt die Entwicklungen aufmerksam und informiert die zuständigen parlamentarischen Kommissionen über den Stand der Arbeiten. Bisher sind das die SGK-S und beide APK. Der Bundesrat wird demnächst eine Aussprache über die Revision und die damit aufgeworfenen Fragen führen. Dabei wird er über alle möglichen Lösungen diskutieren und diese sorgfältig prüfen. 
-Aus diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
-Ich komme zur Motion 26.3617. Mit dem Entzug des Bürgerrechtes lässt sich kein Terrorakt verhindern. Dafür braucht es andere Massnahmen. Deshalb hat die Schweiz seit 2020 ihr Sicherheitsdispositiv deutlich verstärkt. Fedpol, der Nachrichtendienst und die kantonalen Strafverfolgungsbehörden greifen bei konkreten Hinweisen auf eine terroristische Gefahr präventiv ein; dazu haben sie neue Instrumente erhalten. Es stehen hier verschiedene Instrumente zur Verfügung, etwa Meldepflichten, Kontakt- und Ausreiseverbote, Ein- oder Ausgrenzungen sowie in bestimmten Fällen auch Hausarrest. Im Rahmen eines Strafverfahrens können weitere Massnahmen angeordnet werden. So wird eine beschuldigte Person in Untersuchungs- oder Sicherheitshaft genommen, wenn ein dringender Tatverdacht besteht, dass die Person weitere schwere Straftaten begehen wird, oder wenn die Person konkret damit gedroht hat, eine schwerwiegende Tat zu begehen.
+Wir führen etwa doppelt so viele abgewiesene Asylsuchende zurück wie alle anderen vergleichbaren europäischen Länder. Dabei stützen wir uns auf mehr als sechzig Abkommen mit Herkunftsstaaten. Ende Mai haben wir sogar ein Abkommen mit Marokko abgeschlossen; damit konnten wir auch die Rückführungen in dieses Land verbessern. Das schaffen viele andere Länder nicht. Doch nicht nur bei der Rückkehr sind wir in Europa Vorreiter. Mehr als fünfzig Prozent der Flüchtlinge und vorläufig Aufgenommenen haben bei uns nach fünf Jahren einen Job, was dank Arbeit durch Ausbildung möglich ist. Dies setzen wir zusammen mit den Kantonen erfolgreich um, wie auch die OECD anerkennt. So viel zur Ausgangslage.
+Nun komme ich zu den einzelnen Vorstössen. Ich beginne mit der Motion 26.3615 der SVP-Fraktion: Es geht hier um einen Vorstoss, den ich im Auftrag des abwesenden Bundespräsidenten vertreten muss; sie ist seinem Departement zugeordnet. Es geht um die Frage, welches Land die Arbeitslosengelder von Grenzgängerinnen und Grenzgängern bezahlt, die ihren Job verloren haben. Diese Motion will diese Frage beantworten, bevor sie sich überhaupt stellt, bevor wir überhaupt die Ausgangslage kennen. Es ist schlicht und einfach zu früh, hier schon Entscheide zu fällen. Deshalb lehnt der Bundesrat diese Motion ab. Die Änderung der EU-Verordnung 883/2004 sieht vor, dass künftig der letzte Beschäftigungsstaat für die Ausrichtung der Arbeitslosenentschädigung von Grenzgängerinnen und Grenzgängern zuständig sein soll. Aktuell ist die Situation umgekehrt geregelt, in Kombination mit einem Rückerstattungssystem zwischen Beschäftigungs- und Wohnsitzstaat. 
+Die Schweiz beteiligt sich seit dem Inkrafttreten des Freizügigkeitsabkommens an der EU-weiten Koordinierung der Systeme der sozialen Sicherheit. Dazu gehört auch die erwähnte EU-Verordnung. Heute profitieren davon nicht zuletzt Schweizerinnen und Schweizer, die in einem EU-Mitgliedstaat leben und arbeiten. Das vergessen Sie immer wieder. Es gibt Schweizer, die in der EU leben, und für diese gelten auch Regeln, von denen sie profitieren können. Wenn Sie eine Auslegeordnung des Systems machen, müssen Sie das berücksichtigen, bevor Sie hierzu Entscheide fällen. 
+Seit 2013 hat die Arbeitslosenversicherung mit den Leistungen der Grenzgängerinnen und Grenzgänger einen jährlichen Überschuss von durchschnittlich 280 Millionen Schweizerfranken gemacht. Aktuell wissen wir nicht, wann die Revision in der EU in Kraft treten wird. Wie frühere Anpassungen muss auch dieser EU-Beschluss das innerstaatliche Genehmigungsverfahren durchlaufen. Dann muss die EU die Verordnungsanpassung für eine nächste Sitzung des Gemischten Ausschusses anmelden. Dies ist bis jetzt noch nicht geschehen. Das liegt unter anderem daran, dass das Revisionsverfahren auf EU-Ebene noch nicht abgeschlossen ist. Es fehlen noch die formelle Verabschiedung durch den Rat der EU, die Unterzeichnung durch die Rats- und Parlamentspräsidien sowie die Veröffentlichung im Amtsblatt der EU. 
+Die Haltung des Bundesrates lässt sich also wie folgt zusammenfassen: Der Bundesrat lehnt einen verfrühten Positionsbezug ab. Es ist zu früh, um einen Entscheid über eine allfällige Übernahme oder Nichtübernahme der noch nicht abgeschlossenen Revision zu fällen. Der Bundesrat verfolgt die Entwicklungen aufmerksam und informiert die zuständigen parlamentarischen Kommissionen über den Stand der Arbeiten. Bisher sind die SGK-S und beide APK informiert worden. Der Bundesrat wird demnächst eine Aussprache über die Revision und die damit aufgeworfenen Fragen führen. Dabei wird er über alle möglichen Lösungen diskutieren und diese sorgfältig prüfen. Aus diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
+Ich komme zur Motion 26.3617. Mit dem Entzug des Bürgerrechtes lässt sich kein Terrorakt verhindern. Dafür braucht es andere Massnahmen. Deshalb hat die Schweiz seit 2020 ihr Sicherheitsdispositiv deutlich verstärkt. Das Fedpol, der Nachrichtendienst und die kantonalen Strafverfolgungsbehörden greifen bei konkreten Hinweisen auf eine terroristische Gefahr präventiv ein; dazu haben sie neue Instrumente erhalten. Es stehen hier verschiedene Instrumente zur Verfügung, etwa Meldepflichten, Kontakt- und Ausreiseverbote, Ein- oder Ausgrenzungen sowie in bestimmten Fällen auch Hausarrest. Im Rahmen eines Strafverfahrens können weitere Massnahmen angeordnet werden. So wird eine beschuldigte Person in Untersuchungs- oder Sicherheitshaft genommen, wenn ein dringender Verdacht besteht, dass sie weitere schwere Straftaten begehen wird, oder wenn sie konkret damit gedroht hat, eine schwerwiegende Tat zu begehen.
 Kommen wir nun zum Entzug des Schweizer Bürgerrechtes - darum geht es ja in dieser Motion. Der Entzug des Bürgerrechtes dient nicht dazu, einer möglichen Gefahr im Voraus zu begegnen, er greift erst nach einer strafrechtlichen Verurteilung. Die Motion verlangt, dass ein Entzug des Bürgerrechtes auch bei Straftaten möglich sein soll, die keinen unmittelbaren Bezug zum Terrorismus haben. Er soll selbst dann in Betracht kommen, wenn keine strafrechtliche Verurteilung vorliegt. Das geht dem Bundesrat zu weit. Zu weit geht dem Bundesrat auch der in der Motion vorgesehene Automatismus. Die zuständigen Behörden müssen auch künftig prüfen können, ob ein Entzug des Bürgerrechtes im konkreten Einzelfall verhältnismässig ist. Der Entzug des Bürgerrechtes ist ein schwerwiegender Eingriff, und deshalb braucht es auch weiterhin eine sorgfältige Prüfung aller Umstände des Einzelfalles.
-Sie haben es bereits gehört, Bund und Kantone haben ihre Zusammenarbeit gegen Terrorismus in den letzten Jahren deutlich verstärkt. Die Behörden verfügen heute über wirksame Instrumente, um Gefahren frühzeitig zu erkennen und Straftaten zu verhindern. Die Motion würde dazu nichts beitragen, sie würde mit ihrem Automatismus aber das Prinzip der Verhältnismässigkeit verletzen - und das lehnt der Bundesrat ab.
-Der Bundesrat beantragt Ihnen, die Motion abzulehnen.
+Sie haben es bereits gehört, Bund und Kantone haben ihre Zusammenarbeit gegen Terrorismus in den letzten Jahren deutlich verstärkt. Die Behörden verfügen heute über wirksame Instrumente, um Gefahren frühzeitig zu erkennen und Straftaten zu verhindern. Die Motion würde dazu nichts beitragen, sie würde mit ihrem Automatismus aber das Prinzip der Verhältnismässigkeit verletzen - und das lehnt der Bundesrat ab. Der Bundesrat beantragt Ihnen, die Motion abzulehnen.
 Ich komme nun zur Motion 26.3131. Diese Motion verlangt, dass ausländische Straftäter ab einer Freiheitsstrafe von einem Jahr zwingend und ohne Ausnahme des Landes verwiesen werden. Das bedeutet konkret, in solchen Fällen soll weder die Härtefallklausel angewendet werden noch soll im Einzelfall geprüft werden, ob die Landesverweisung verhältnismässig ist. Der Bundesrat lehnt diese Forderung aus drei Gründen ab.
-Erstens möchte ich daran erinnern, dass das Parlament bei der Umsetzung der Ausschaffungs-Initiative bewusst eine Härtefallklausel geschaffen hat und dass die Durchsetzungs-Initiative, welche diese abschaffen wollte, von der Stimmbevölkerung deutlich abgelehnt wurde. Die Härtefallklausel stellt sicher, dass zentrale verfassungs- und völkerrechtliche Vorgaben eingehalten werden, und dazu gehören insbesondere das Verhältnismässigkeitsprinzip, der Schutz des Privat- und Familienlebens sowie das Non-Refoulement-Prinzip. Die Rechtsprechungen des Bundesgerichtes und des Europäischen Gerichtshofes für Menschenrechte verlangen zudem eine Prüfung des Einzelfalls. Eine zwingende Landesverweisung ab einem Jahr Freiheitsstrafe würde diese ausschliessen. Damit könnte das Gericht auch die konkreten Umstände des Einzelfalls nicht mehr berücksichtigen, und das ist mit dem übergeordnetem Recht nicht vereinbar.
+Erstens möchte ich daran erinnern, dass das Parlament bei der Umsetzung der Ausschaffungs-Initiative bewusst eine Härtefallklausel geschaffen hat und dass die Durchsetzungs-Initiative, welche diese abschaffen wollte, von der Stimmbevölkerung deutlich abgelehnt wurde. Die Härtefallklausel stellt sicher, dass zentrale verfassungs- und völkerrechtliche Vorgaben eingehalten werden, und dazu gehören insbesondere das Verhältnismässigkeitsprinzip, der Schutz des Privat- und Familienlebens sowie das Non-Refoulement-Prinzip. Die Rechtsprechungen des Bundesgerichtes und des Europäischen Gerichtshofes für Menschenrechte verlangen zudem eine Prüfung des Einzelfalls. Eine zwingende Landesverweisung ab einem Jahr Freiheitsstrafe würde dies ausschliessen. Damit könnte das Gericht auch die konkreten Umstände des Einzelfalls nicht mehr berücksichtigen, und das wäre mit dem übergeordneten Recht nicht vereinbar.
 Zweitens bedeutet eine zwingende Landesverweisung noch nicht, dass diese auch tatsächlich vollzogen werden kann. Fehlende Reisedokumente oder die mangelnde Kooperation des Herkunftsstaates können den Vollzug weiterhin verhindern; daran ändert diese Motion nichts.
-Drittens zeigt die heutige Praxis: Je schwerer die Straftat, desto häufiger wird eine Landesverweisung ausgesprochen. Bei Freiheitsstrafen von ein bis zwei Jahren liegt die Quote im Jahr 2025 bei 79 Prozent, bei Freiheitsstrafen von zwei bis drei Jahren sind es bereits 86 Prozent und bei drei bis vier Jahren rund 96 Prozent. Bei mehr als vier Jahren sind es rund 93 Prozent. Bei schweren Straftaten ist die Landesverweisung damit bereits heute die klare Regel, die Härtefallklausel kommt in diesen Fällen nur zurückhaltend zur Anwendung. Fazit: Eine weitere Verschärfung ist somit weder mit dem übergeordneten Recht vereinbar noch geeignet, um die bestehenden Vollzugsprobleme zu lösen.
-Aus all diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
-Nun zur Motion Rutz Gregor 26.3668, "Korrektur der Praxisänderung in Bezug auf Asylgesuche von Afghaninnen". Diese Forderung muss Ihnen bekannt vorkommen. Am 27. Mai 2024 haben Sie die Motion Rutz Gregor 23.4241 mit gleichlautenden Forderungen abgelehnt. 
-Seit der Praxisänderung des SEM im Sommer 2023 hat sich die Situation der Frauen und Mädchen in Afghanistan weiter dramatisch verschlechtert. Ein menschenwürdiges Leben ist für Afghaninnen in ihrem Heimatland nicht mehr möglich. Deshalb geht der Gerichtshof der Europäischen Union von einer Kollektivverfolgung der afghanischen Frauen aus. Er hat mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. In Europa gilt also grundsätzlich dieselbe Haltung und Praxis wie in der Schweiz. Eine spezielle Einladung der Schweiz gibt es in diesem Sinne nicht. 
-Nichtsdestotrotz prüft das SEM nach wie vor jedes Asylgesuch von afghanischen Frauen und Mädchen, und zwar einzeln. Das SEM tritt nicht auf Dublin-Fälle ein, ebenso wenig auf Gesuche von Betroffenen, die wir in einen Drittstaat zurückschicken können. Das SEM prüft auch, ob es sich überhaupt um Afghaninnen handelt. Es führt Sicherheitsüberprüfungen durch und überprüft den Familiennachzug zum Beispiel mit DNA-Analysen. Zudem wird die Ehegemeinschaft kontrolliert. Kommt es zu Missbrauch, können bestehende Bewilligungen und das Asyl entzogen werden. An all diesen Überprüfungen hat die Praxisänderung für die Afghaninnen nichts geändert. Es gibt also nach wie vor keinen Automatismus. 
-Der in der Motion erwähnte nicht veröffentlichte Abschreibungsbeschluss des Bundesverwaltungsgerichts ist ausserdem ein rein formeller Prozessentscheid. Er hat weder eine materielle Tragweite noch eine rechtsprechungsbildende Wirkung. Das hat das Bundesverwaltungsgericht in seiner Antwort auf die Interpellation Wyssmann 26.3871, "Prozessentscheid E-2274/2020 vom 20. November 2025. Geheimjustiz am Bundesverwaltungsgericht?", selbst festgehalten. Das Bundesverwaltungsgericht stellt klar, dass es sich nicht um ein Leiturteil handelte, und der Entscheid führt weder zu einer Änderung noch zu einer Weiterentwicklung der Rechtsprechung, im Gegenteil: Das Bundesverwaltungsgericht hat die Praxis des SEM bereits in seinem Urteil vom November 2023 bestätigt. Seit diesem Urteil hat sich die Situation der Frauen in Afghanistan nochmals massiv verschlechtert und in keiner Weise verbessert, wie man dem Votum des Motionärs entnehmen könnte. 
-Zusammenfassend ist klar: Frauen und Mädchen aus Afghanistan sind Flüchtlinge. Im Verfahren schaut sich das SEM dazu jeden Fall einzeln an. Wir verhindern so Missbrauch, und gleichzeitig garantieren wir rasche Verfahren für Menschen, die sowieso in der Schweiz bleiben. Das bringt Klarheit für die Betroffenen und für die Kantone. Der Bundesrat sieht keinen Grund, auf die Praxisänderung zurückzukommen. Er beantragt Ihnen, die Motion abzulehnen. Die Zahl der Asylgesuche aus Afghanistan ist seit Kurzem übrigens deutlich zurückgegangen. Zu einem Asylgesuch scheint sich also kaum jemand besonders eingeladen zu fühlen.
-Ich komme zur Motion 26.3616: Diese Forderung ist bereits erfüllt. Der Bund ist gesetzlich verpflichtet, die Kantone und Gemeinden bei der Einrichtung der Bundesasylzentren frühzeitig einzubeziehen. Im Rahmen des Sachplanverfahrens wie auch im Plangenehmigungsverfahren werden der betroffene Kanton und die Gemeinde angehört, Herr Knutti. Das wird immer so gemacht. Das Asylwesen ist eine Verbundaufgabe von Bund, Kantonen und Gemeinden. An zwei nationalen Asylkonferenzen in den Jahren 2013 und 2014 beschlossen sie einstimmig, den Asylbereich neu zu strukturieren und in sechs Asylregionen aufzuteilen; anschliessend haben sich die drei Staatsebenen im gegenseitigen Einvernehmen darauf verständigt, wo wie viele Unterbringungsplätze zur Verfügung stehen sollen. Und seit über zehn Jahren arbeitet der Bund am Aufbau der vereinbarten 5000 Plätze. Das macht er aber nicht im Alleingang; sowohl Privatpersonen als auch die Gemeinden und Kantone haben immer die Möglichkeit, sich ins Verfahren einzubringen und Einsprache zu erheben. Das Anliegen der vorliegenden Motion ist somit bereits erfüllt.
-Der Bundesrat beantragt Ihnen deshalb, diese Motion abzulehnen.
+Drittens zeigt die heutige Praxis: Je schwerer die Straftat, desto häufiger wird eine Landesverweisung ausgesprochen. Bei Freiheitsstrafen von ein bis zwei Jahren liegt die Quote im Jahr 2025 bei 79 Prozent, bei Freiheitsstrafen von zwei bis drei Jahren sind es bereits 86 Prozent und bei drei bis vier Jahren rund 96 Prozent. Bei mehr als vier Jahren sind es rund 93 Prozent. Bei schweren Straftaten ist die Landesverweisung damit bereits heute die klare Regel, die Härtefallklausel wird in diesen Fällen nur zurückhaltend angewendet. Fazit: Eine weitere Verschärfung ist weder mit dem übergeordneten Recht vereinbar noch geeignet, um die bestehenden Vollzugsprobleme zu lösen. Aus all diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
+Nun zur Motion Rutz Gregor 26.3668, "Korrektur der Praxisänderung in Bezug auf Asylgesuche von Afghaninnen". Diese Forderung muss Ihnen bekannt vorkommen. Am 27. Mai 2024 haben Sie die Motion Rutz Gregor 23.4241 mit gleichlautenden Forderungen abgelehnt. Seit der Praxisänderung des SEM im Sommer 2023 hat sich die Situation der Frauen und Mädchen in Afghanistan weiter dramatisch verschlechtert. Ein menschenwürdiges Leben ist für Afghaninnen in ihrem Heimatland nicht mehr möglich. Deshalb geht der Gerichtshof der Europäischen Union von einer Kollektivverfolgung der afghanischen Frauen aus. Er hat mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. In Europa gilt also grundsätzlich dieselbe Haltung und Praxis wie in der Schweiz. Eine spezielle Einladung der Schweiz gibt es in diesem Sinne nicht. 
+Nichtsdestotrotz prüft das SEM nach wie vor jedes Asylgesuch einer afghanischen Frau oder eines afghanischen Mädchens, und zwar einzeln. Das SEM tritt nicht auf Dublin-Fälle ein, ebenso wenig auf Gesuche von Betroffenen, die wir in einen Drittstaat zurückschicken können. Das SEM prüft auch, ob es sich überhaupt um Afghaninnen handelt. Es führt Sicherheitsüberprüfungen durch und überprüft den Familiennachzug zum Beispiel mit DNA-Analysen. Zudem wird die Ehegemeinschaft kontrolliert. Kommt es zu Missbrauch, können bestehende Bewilligungen und das Asyl entzogen werden. An all diesen Überprüfungen hat die Praxisänderung für die Afghaninnen nichts geändert. Es gibt also nach wie vor keinen Automatismus. 
+Der in der Motion erwähnte nicht veröffentlichte Abschreibungsbeschluss des Bundesverwaltungsgerichts ist ausserdem ein rein formeller Prozessentscheid. Er hat weder eine materielle Tragweite noch eine rechtsprechungsbildende Wirkung. Das hat das Bundesverwaltungsgericht in seiner Antwort auf die Interpellation Wyssmann 26.3871, "Prozessentscheid E-2274/2020 vom 20. November 2025. Geheimjustiz am Bundesverwaltungsgericht?", selbst festgehalten. Das Bundesverwaltungsgericht stellt klar, dass es sich nicht um ein Leiturteil handelte. Der Entscheid führt weder zu einer Änderung noch zu einer Weiterentwicklung der Rechtsprechung. Das Bundesverwaltungsgericht hat die Praxis des SEM bereits in seinem Urteil vom November 2023 bestätigt. Seit diesem Urteil hat sich die Situation der Frauen in Afghanistan nochmals massiv verschlechtert und in keiner Weise verbessert, wie man es dem Votum des Motionärs hätte entnehmen können. 
+Zusammenfassend ist klar: Frauen und Mädchen aus Afghanistan sind Flüchtlinge. Im Verfahren schaut sich das SEM dazu jeden Fall einzeln an. Wir verhindern so Missbrauch, und gleichzeitig garantieren wir rasche Verfahren für Menschen, die sowieso in der Schweiz bleiben. Das bringt Klarheit für die Betroffenen und für die Kantone. Der Bundesrat sieht keinen Grund, auf die Praxisänderung zurückzukommen. Er beantragt Ihnen, die Motion abzulehnen. Die Zahl der Asylgesuche aus Afghanistan ist vor Kurzem übrigens deutlich zurückgegangen. Zur Einreichung eines Asylgesuchs scheint sich also kaum jemand besonders eingeladen zu fühlen.
+Ich komme zur Motion 26.3616: Diese Forderung ist bereits erfüllt. Der Bund ist gesetzlich verpflichtet, die Kantone und Gemeinden bei der Einrichtung von Bundesasylzentren frühzeitig einzubeziehen. Im Rahmen des Sachplanverfahrens wie auch im Plangenehmigungsverfahren werden der betroffene Kanton und die Gemeinde angehört, Herr Knutti. Das wird immer so gemacht. Das Asylwesen ist eine Verbundaufgabe von Bund, Kantonen und Gemeinden. An zwei nationalen Asylkonferenzen in den Jahren 2013 und 2014 beschlossen sie einstimmig, den Asylbereich neu zu strukturieren und in sechs Asylregionen aufzuteilen; anschliessend haben sich die drei Staatsebenen im gegenseitigen Einvernehmen darauf verständigt, wo wie viele Unterbringungsplätze zur Verfügung stehen sollen. Seit über zehn Jahren arbeitet der Bund am Aufbau der vereinbarten 5000 Plätze. Das macht er aber nicht im Alleingang; sowohl Privatpersonen als auch die Gemeinden und Kantone haben immer die Möglichkeit, sich ins Verfahren einzubringen und Einsprache zu erheben. Das Anliegen der vorliegenden Motion ist somit bereits erfüllt. Der Bundesrat beantragt Ihnen deshalb, diese Motion abzulehnen.
 Nun zur Motion 24.4063: Die Motionärin begründet die vorgeschlagenen Anpassungen damit, dass vorläufig aufgenommene Personen langfristig in der Schweiz bleiben. Das stimmt. Viele können nicht in die Heimat zurück, weil dort Bürgerkrieg herrscht oder es andere Umstände gibt, die eine Rückkehr unmöglich machen. Diese Personen können gar nicht anders, als hier zu bleiben.
-Der Bundesrat will dennoch nicht automatisch eine Aufenthaltsbewilligung erteilen, weil jemand schon länger in der Schweiz lebt. Es braucht immer eine Einzelfallprüfung. Zuständig sind die Kantone. Sie prüfen, ob die Personen gut in die Schweiz integriert sind, sie sind berechtigt, entsprechende Anträge zu stellen, die Einzelfälle zu begründen. Sie berücksichtigen, ob jemand eine Landessprache spricht, ob jemand arbeitet, ob jemand die öffentliche Ordnung respektiert.
+Der Bundesrat will dennoch nicht automatisch eine Aufenthaltsbewilligung erteilen, wenn jemand schon länger in der Schweiz lebt. Es braucht immer eine Einzelfallprüfung. Zuständig sind die Kantone. Sie prüfen, ob die Person gut in die Schweiz integriert ist; sie sind berechtigt, entsprechende Anträge zu stellen und die Einzelfälle zu begründen. Sie berücksichtigen, ob die Person eine Landessprache spricht, ob sie arbeitet, ob sie die öffentliche Ordnung respektiert.
 Erst kürzlich hat Ihr Rat über die Motion Stark 25.3689, "Fehlanreize in der Asylpolitik reduzieren", beraten. Ein Thema dabei waren längere Fristen für Härtefallgesuche und folglich auch für die Erteilung einer Aufenthaltsbewilligung. Sie haben damals die bisherige Praxis bestätigt. Ein Argument in der Debatte war, dass die Möglichkeit, ein Härtefallgesuch einzureichen, ein wichtiger Anreiz für die Integration ist. Der Bundesrat teilt diese Einschätzung. Wer die Aufenthaltsbewilligung nach zehn Jahren automatisch erhält, hat diesen Anreiz nicht.
 Aus diesen Gründen beantragt der Bundesrat, auch diese Motion abzulehnen.
-Nun zur Motion 25.3058: Das Dublin-System legt klare Kriterien fest, welcher Staat für die Prüfung eines Asylgesuchs zuständig ist. Im Einzelfall kann das SEM von den Zuständigkeitsregeln abweichen, zum Beispiel aus medizinischen, sozialen oder humanitären Gründen. Das SEM prüft in jedem Einzelfall umfassend die konkreten Umstände, dabei trägt es besonders auch dem Kindswohl Rechnung; das SEM beachtet bei der Prüfung die Kinderrechtskonvention.
-Falls eine Folgebehandlung im zuständigen Dublin-Staat möglich ist, informiert das SEM noch vor der Überstellung die dortigen Behörden. Am 12. Juni 2026 ist die Asylum and Migration Management Regulation (AMMR) in Kraft getreten. Sie sieht längere Fristen vor als die bisherigen Dublin-Verordnungen, und damit bekommt der aufnehmende Staat mehr Zeit, um sich auf die Ankunft einer gesundheitlich beeinträchtigten Person vorzubereiten.
+Nun zur Motion 25.3058: Das Dublin-System legt klare Kriterien fest, welcher Staat für die Prüfung eines Asylgesuchs zuständig ist. Im Einzelfall kann das SEM von den Zuständigkeitsregeln abweichen, zum Beispiel aus medizinischen, sozialen oder humanitären Gründen. Das SEM prüft in jedem Einzelfall umfassend die konkreten Umstände, dabei trägt es besonders auch dem Kindeswohl Rechnung; das SEM beachtet bei der Prüfung die Kinderrechtskonvention.
+Falls eine Folgebehandlung im zuständigen Dublin-Staat möglich ist, informiert das SEM noch vor der Überstellung die dortigen Behörden. Am 12. Juni 2026 ist die Asylum and Migration Management Regulation (AMMR) in Kraft getreten. Sie sieht längere Fristen vor als die bisherigen Dublin-Verordnungen; damit bekommt der aufnehmende Staat mehr Zeit, um sich auf die Ankunft einer gesundheitlich beeinträchtigten Person vorzubereiten.
 Eine systematische Anwendung der Souveränitätsklausel lehnt der Bundesrat ab. Eine Krankheit bei einem Kind soll nicht automatisch dazu führen, dass die Schweiz das Asylgesuch selbst prüft. Der Bundesrat beantragt also, auch die Motion Klopfenstein Broggini abzulehnen.
 Ich komme zur Motion 25.4067. Der Krieg in der Ukraine dauert an. Drohnenangriffe und Angriffe auf die Infrastruktur sind in der Ukraine an der Tagesordnung, die Zahl der getöteten Zivilistinnen und Zivilisten nimmt gerade zu. Eine Stabilisierung der Lage ist derzeit nicht in Sicht. Der Bundesrat hat deshalb am 19. August 2026 entschieden, den Schutzstatus S bis zum 4. März 2028 nicht aufzuheben. Dieser Entscheid erfolgte nach einer breiten Konsultation von Kantonen, Kommunalverbänden, Sozialpartnern und weiteren staatlichen und nichtstaatlichen Akteuren. Für den Bundesrat ist klar, der Schutzstatus S ist unter den heutigen Umständen weiterhin die beste Lösung. Er ermöglicht es, die Menschen, die vor dem Krieg geflüchtet sind, wirksam zu schützen, gleichzeitig entlastet er das Asylsystem. Sie dürfen nie vergessen, dass es möglich ist, dass jemand, der den Schutzstatus nicht erhält, bei uns Asyl beantragt.
-Unser Vorgehen ist eng mit der Europäischen Union abgestimmt. Auch die EU hat den vorübergehenden Schutz bis März 2028 verlängert. Gleichzeitig übernimmt die Schweiz die neuen Regeln der EU für Dienstpflichtige. Diese Koordination ist wichtig, sie hilft, Sekundärmigration innerhalb des Schengen-Raums zu vermeiden. In Zukunft erhalten wehrpflichtige Männer aus der Ukraine bei uns keinen Schutzstatus mehr. Der Bundesrat will eine Exit-Strategie, selbstverständlich brauchen wir das, und wir sind ja längst daran, eine solche zu erarbeiten. Wir haben Ihnen auch schon Vorschläge gezeigt, die aus der Öffentlichkeit kommen.
-Der Bundesrat stützt sich auf das Konzept zur Zukunft des Status S. Dieses wurde im laufenden Jahr unter der Leitung des Staatssekretariats für Migration und der Vereinigung der kantonalen Migrationsbehörden erarbeitet. Das Konzept zeigt anhand von drei Szenarien auf, wie der Übergang zu Aufenthaltsbewilligungen oder später zu einer Aufhebung des Schutzstatus S gestaltet werden könnte. Es zeigt auch die operativen Folgen und den Ressourcenbedarf auf. Damit können sich Bund, Kantone und Gemeinden frühzeitig vorbereiten.
-Bund, Kantone, Gemeinden und Städte sind zum Schluss gekommen, dass eine Aufhebung des Schutzstatus S zum jetzigen Zeitpunkt das Asylsystem überlasten würde. Gleichzeitig würde es zu erheblichen Unsicherheiten für die schutzbedürftigen Personen führen. Vorteile sind nicht ersichtlich. Auch eine schrittweise Aufhebung ist aus Sicht des Bundesrates erst dann sinnvoll, wenn die Europäische Union entsprechende Massnahmen ergreift und wenn keine Überlastung des Asylsystems aufgrund von neuen Gesuchen mehr droht - bis dann überwiegen die Vorteile des heutigen Systems. Der Bundesrat beantragt Ihnen deshalb, die Motion abzulehnen.
-Zum Schluss zur Motion 26.3100: Die Schweiz ist bei der Rückkehr vergleichsweise erfolgreich. Wir müssen diesen Kurs konsequent weiterverfolgen und dabei alle verfügbaren Instrumente nutzen. Das sind beispielsweise Massnahmen im Europäischen Verbund oder der Visa-Hebel, also die Verknüpfung der Visapolitik mit der Rückkehr. Diesen wenden wir bereits erfolgreich an. Zudem hat der Bundesrat weiterhin auf die internationale Migrationszusammenarbeit gesetzt. Hier braucht es eine enge Verbindung zwischen Migrations- und Aussenpolitik. Die Schweiz setzt dabei grundsätzlich auf einen partnerschaftlichen Ansatz mit Drittstaaten - schlicht und einfach, weil wir festgestellt haben, dass wir damit schneller vorwärtskommen und die Ziele und Interessen der Schweiz besser erreichen können. Gleichzeitig bestehen bereits heute Möglichkeiten, um die Entwicklungszusammenarbeit anzupassen, wenn ein Schwerpunktland die Zusammenarbeit bei Migrationsfragen nicht ausreichend mitträgt. 
+Unser Vorgehen ist eng mit der Europäischen Union abgestimmt. Auch die EU hat den vorübergehenden Schutz bis März 2028 verlängert. Gleichzeitig übernimmt die Schweiz die neuen Regeln der EU für Dienstpflichtige. Diese Koordination ist wichtig; sie hilft, Sekundärmigration innerhalb des Schengen-Raums zu vermeiden. In Zukunft erhalten wehrpflichtige Männer aus der Ukraine bei uns keinen Schutzstatus mehr. Der Bundesrat will eine Exit-Strategie, selbstverständlich brauchen wir das, und wir sind ja längst daran, eine solche zu erarbeiten. Wir haben Ihnen - d. H. der Öffentlichkeit - auch schon Vorschläge gezeigt.
+Der Bundesrat stützt sich auf das Konzept "Zukunft Status S". Dieses wurde im laufenden Jahr unter der Leitung des Staatssekretariats für Migration und der Vereinigung der kantonalen Migrationsbehörden erarbeitet. Das Konzept zeigt anhand von drei Szenarien auf, wie der Übergang zu Aufenthaltsbewilligungen oder später zu einer Aufhebung des Schutzstatus S gestaltet werden könnte. Es zeigt auch die operativen Folgen und den Ressourcenbedarf auf. Damit können sich Bund, Kantone und Gemeinden frühzeitig vorbereiten.
+Bund, Kantone, Gemeinden und Städte sind zum Schluss gekommen, dass eine Aufhebung des Schutzstatus S zum jetzigen Zeitpunkt das Asylsystem überlasten würde. Gleichzeitig würde es zu erheblichen Unsicherheiten für die schutzbedürftigen Personen führen. Vorteile sind nicht ersichtlich. Auch eine schrittweise Aufhebung ist aus Sicht des Bundesrates erst dann sinnvoll, wenn die Europäische Union entsprechende Massnahmen ergreift und wenn keine Überlastung des Asylsystems aufgrund von neuen Gesuchen mehr droht. Bis dann überwiegen die Vorteile des heutigen Systems. Der Bundesrat beantragt Ihnen deshalb, die Motion abzulehnen.
+Zum Schluss zur Motion 26.3100: Die Schweiz ist bei der Rückkehr vergleichsweise erfolgreich. Wir müssen diesen Kurs konsequent weiterverfolgen und dabei alle verfügbaren Instrumente nutzen. Das sind beispielsweise Massnahmen im europäischen Verbund oder der Visa-Hebel, also die Verknüpfung der Visapolitik mit der Rückkehr. Diesen wenden wir bereits erfolgreich an. Zudem hat der Bundesrat weiterhin auf die internationale Migrationszusammenarbeit gesetzt. Hier braucht es eine enge Verbindung zwischen Migrations- und Aussenpolitik. Die Schweiz setzt dabei grundsätzlich auf einen partnerschaftlichen Ansatz mit Drittstaaten - schlicht und einfach, weil wir festgestellt haben, dass wir damit schneller vorwärtskommen und die Ziele und Interessen der Schweiz besser erreichen können. Gleichzeitig bestehen bereits heute Möglichkeiten, um die Entwicklungszusammenarbeit anzupassen, wenn ein Schwerpunktland die Zusammenarbeit bei Migrationsfragen nicht ausreichend mitträgt. 
 Zu den Return Hubs kann ich sagen, was ich schon oft gesagt habe. Die neue EU-Rückkehrverordnung steht kurz vor der Verabschiedung, und diese sieht die Möglichkeit von Return Hubs vor. Die Schweiz als Schengen-assoziierter Staat muss die Regelung innerhalb von zwei Jahren übernehmen. Der Bundesrat hat die Machbarkeit solcher Return Hubs in Drittstaaten untersucht. Wie Sie wissen, schliesst er eine Teilnahme an einem solchen Projekt nicht aus. Die rechtlichen und praktischen Hürden sind aber hoch. Return Hubs könnten unser Asylsystem höchstens punktuell entlasten. 
 Auf nationaler Ebene konzentriert sich der Bundesrat darauf, unser nationales Asylsystem zu stärken und zu verbessern. Das ist der Ansatz, den wir mit der Asylstrategie 2027 verfolgen. Damit können wir, da sind wir überzeugt, mehr Wirkung erzielen, zusammen mit den Kantonen, Gemeinden und Städten. Der Bundesrat setzt sich bereits heute dafür ein, dass die Rückkehr und die Kooperation mit Drittstaaten weiter verbessert wird. Der eingeschlagene Weg hat sich bewährt. Wir brauchen keine zusätzliche Motion in diesem Bereich.
 Wir beantragen deshalb auch diese Motion zur Ablehnung. 
@@ -594,14 +587,14 @@
     <t xml:space="preserve">RL</t>
   </si>
   <si>
-    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Frage beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; denn die Letzten, die sich dann beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Deshalb müssen wir zusammen griffige Massnahmen definieren, damit die Asylpoliti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Frage beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; denn die Letzten, die sich dann beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Deshalb müssen wir zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in geordneten Bahnen vorangetrieben werden kann. Das Resultat in anderen Ländern, wo man das seit Jahrzehnten nicht macht, ist Zeichen genug. Dieses Resultat wollen wir in unserem Land nicht erzielen. Nehmen Sie das vielleicht einmal zur Kenntnis, wenn Sie so reagieren. 
-Es gibt in der Schweiz - um zur Motion 25.4067 der FDP-Fraktion zu kommen - 73 800 Personen mit Schutzstatus S aus der Ukraine. Das ist ein knapper Drittel aller Personen, die sich momentan in der Schweiz im Asylbereich aufhalten. Das ist eine Anzahl Personen in der Grössenordnung der Stadt St. Gallen. Hier müssen wir schon eine Strategie haben. Deshalb verlangt die FDP-Fraktion eine klare Exit-Strategie in Bezug auf den Schutzstatus S unter Berücksichtigung auch der europäischen Entwicklungen, welche zur Verlängerung desselben bis im März 2028 geführt haben. Es geht nicht, dass man den Schutzstatus S einfach pauschal in eine vorläufige Aufnahme überführt. Das würde dann bedeuten, dass diese Leute wahrscheinlich nie mehr zurückgehen. Es war damals unsere Bundesrätin Keller-Sutter, die im Namen des Bundesrates klar gesagt hat, beim Schutzstatus S handle es sich um einen "rückkehrorientierten" Status. Diesen rückkehrorientierten Status wollen wir beibehalten. Deshalb lehnen wir es eben entschieden ab, dass man die 73 800 aktiven Leute mit Schutzstatus S dann ohne Einzelfallprüfung in eine kollektive vorläufige Aufnahme überführt. 
-Es muss individuell geprüft werden. Ja, zur individuellen Prüfung von über 70 000 Personen braucht es Ressourcen. Genau aus diesem Grund beantragen wir mit dieser Motion hier eine Exit-Strategie. Wir sind ehrlich gesagt etwas irritiert darüber, dass der Bundesrat diesen Vorstoss bekämpft. Die Schweiz soll ihre Hausaufgaben machen und Ressourcen für Abklärungen einsetzen, wie diese Personen geordnet und möglichst früh zurückgeschickt und dabei juristisch unterstützt werden können. Ein sauberes Asylverfahren dieser Art ist die Grundlage dafür, dass man die Leute zurückschicken kann, sobald der Krieg hoffentlich einmal zu Ende ist. Es gilt dann ebenfalls, zum Beispiel Personen in Ausbildung zu berücksichtigen und eine verhältnismässige Frist festzusetzen, bis wann sie das Land zu verlassen haben. Das sind harte Entscheidungen, ja, aber es sind nötige Entscheidungen. Wenn wir pauschal einfach über alles hinwegsehen, dann werden wieder neue Diskussionen in diesem Land entstehen. Wir wollen nicht wieder in das alte Fahrwasser einer Asylpolitik zurückkehren, bei welcher diese Dinge eben zu wenig Berücksichtigung gefunden haben. 
-Und ja, es muss dann halt im einen oder anderen Fall die Ablehnung eines Asylgesuches stattfinden. Wir haben über die Kommission auch politisch erwirkt, dass gewisse Regionen der Ukraine als sichere Zonen eingestuft werden. Das wurde hier drin auch schon in Abrede gestellt. Es gibt aber sichere Bereiche in der Ukraine. Dort müssen andere Massstäbe gelten als in den aktiven Kriegsgebieten, denn sonst werden wir schlicht und ergreifend überschwemmt. Wenn Personen dann halt nicht freiwillig zurückgehen, muss man Druck aufsetzen, damit sie das Land verlassen. Wie gesagt, es ist ein rückkehrorientierter Status.
-Dazu benötigen wir auf Bundesebene, im Staatssekretariat, konkrete Personalplanung. Es braucht Personal, das ist für uns klar, und auch Bundesrat Jans müsste das grösste Interesse daran haben. Die Kantone und Gemeinden - da deckt sich meine Beobachtung mit meinem Vorvorredner aus der SVP-Fraktion - müssen in diesen Prozess integriert werden, sie können das nicht alles alleine ausbaden, während der Bund zuschaut. Also lieber vorher eine Exitstrategie definieren, so, wie wir sie in der Motion verlangen, anstatt dann mit "Pflästerlipolitik" in diesem heiklen Bereich die falschen Entscheidungen zu fällen.
+    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Fragen beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; die Letzten, die sich beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Wir müssen zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Fragen beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; die Letzten, die sich beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Wir müssen zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in geordneten Bahnen vorangetrieben werden kann. Das Resultat in anderen Ländern, wo man das seit Jahrzehnten nicht macht, ist Zeichen genug. Dieses Resultat wollen wir in unserem Land nicht erzielen. Nehmen Sie das vielleicht einmal zur Kenntnis, wenn Sie so reagieren. 
+Es gibt in der Schweiz - um zur Motion 25.4067 der FDP-Fraktion zu kommen - 73 800 Personen mit Schutzstatus S aus der Ukraine. Das ist ein knapper Drittel aller Personen, die sich momentan in der Schweiz im Asylbereich aufhalten. Das ist eine Anzahl Personen in der Grössenordnung der Stadt St. Gallen. Hier müssen wir schon eine Strategie haben. Deshalb verlangt die FDP-Fraktion eine klare Exit-Strategie in Bezug auf den Schutzstatus S unter Berücksichtigung auch der europäischen Entwicklungen, welche zur Verlängerung desselben bis im März 2028 geführt haben. Es geht nicht, dass man den Schutzstatus S einfach pauschal in eine vorläufige Aufnahme überführt. Das würde bedeuten, dass diese Leute wahrscheinlich nie mehr zurückgehen. Es war damals unsere Bundesrätin Keller-Sutter, die im Namen des Bundesrates klar gesagt hat, beim Schutzstatus S handle es sich um einen "rückkehrorientierten" Status. Diesen rückkehrorientierten Status wollen wir beibehalten. Deshalb lehnen wir es eben entschieden ab, dass man die 73 800 aktiven Leute mit Schutzstatus S dann ohne Einzelfallprüfung in eine kollektive vorläufige Aufnahme überführt. Es muss individuell geprüft werden.
+Ja, zur individuellen Prüfung von über 70 000 Personen braucht es Ressourcen. Genau aus diesem Grund beantragen wir mit dieser Motion hier eine Exit-Strategie. Wir sind ehrlich gesagt etwas irritiert darüber, dass der Bundesrat diesen Vorstoss bekämpft. Die Schweiz soll ihre Hausaufgaben machen und Ressourcen für Abklärungen einsetzen, wie diese Personen geordnet und möglichst früh zurückgeschickt und dabei juristisch unterstützt werden können. Ein sauberes Asylverfahren dieser Art ist die Grundlage dafür, dass man die Leute zurückschicken kann, sobald der Krieg - hoffentlich - einmal zu Ende ist. Es gilt dann ebenfalls, zum Beispiel Personen in Ausbildung zu berücksichtigen und eine verhältnismässige Frist festzusetzen, bis wann sie das Land zu verlassen haben. Das sind harte Entscheidungen, ja, aber es sind nötige Entscheidungen. Wenn wir pauschal einfach über alles hinwegsehen, dann werden wieder neue Diskussionen in diesem Land entstehen. Wir wollen nicht wieder in das alte Fahrwasser einer Asylpolitik zurückkehren, bei welcher diese Dinge eben zu wenig Berücksichtigung gefunden haben. 
+Und ja, es muss dann halt im einen oder anderen Fall die Ablehnung eines Asylgesuches stattfinden. Wir haben über die Kommission auch politisch erwirkt, dass gewisse Regionen der Ukraine als sichere Zonen eingestuft werden. Es wurde hier drin auch schon in Abrede gestellt, es gibt aber sichere Bereiche in der Ukraine. Dort müssen andere Massstäbe gelten als in den aktiven Kriegsgebieten, denn sonst werden wir schlicht und ergreifend überschwemmt. Wenn Personen dann halt nicht freiwillig zurückgehen, muss man Druck aufsetzen, damit sie das Land verlassen. Wie gesagt, es ist ein rückkehrorientierter Status.
+Dazu benötigen wir auf Bundesebene, im Staatssekretariat, eine konkrete Personalplanung. Es braucht Personal, das ist für uns klar, und auch Bundesrat Jans müsste das grösste Interesse daran haben. Die Kantone und Gemeinden - da deckt sich meine Beobachtung mit derjenigen meines Vorvorredners aus der SVP-Fraktion - müssen in diesen Prozess integriert werden, sie können das nicht alles alleine ausbaden, während der Bund zuschaut. Also lieber vorher eine Exit-Strategie definieren, so, wie wir sie in der Motion verlangen, anstatt dann mit "Pflästerlipolitik" in diesem heiklen Bereich die falschen Entscheidungen zu fällen.
 Ich danke Ihnen für die Unterstützung dieser Motion.
 </t>
   </si>
@@ -609,12 +602,13 @@
     <t xml:space="preserve">419717</t>
   </si>
   <si>
-    <t xml:space="preserve">Dass Frauen sexuelle oder geschlechtsspezifische Gewalt erleben müssen, ist inakzeptabel. Frauen haben Recht auf Schutz vor dieser Gewalt; das gilt auch für asylsuchende Frauen. Bereits heute garantieren verschiedene Massnahmen im Asylverfahren wie auch bei der Unterbringung und Betreuung, dass dieser Schutz effektiv gewährt wird. Diese Massnahmen sind aber grossmehrheitlich unbekannt. 
-Mit einem Bericht zur Erfüllung des Postulats könnte der Bundesrat dem Parlament aufzeigen, welche Massnahmen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dass Frauen sexuelle oder geschlechtsspezifische Gewalt erleben müssen, ist inakzeptabel. Frauen haben Recht auf Schutz vor dieser Gewalt; das gilt auch für asylsuchende Frauen. Bereits heute garantieren verschiedene Massnahmen im Asylverfahren wie auch bei der Unterbringung und Betreuung, dass dieser Schutz effektiv gewährt wird. Diese Massnahmen sind aber grossmehrheitlich unbekannt. 
-Mit einem Bericht zur Erfüllung des Postulats könnte der Bundesrat dem Parlament aufzeigen, welche Massnahmen in diesem Bereich in den letzten Jahren umgesetzt wurden. Gleichzeitig erhalten wir die Möglichkeit, weitere Handlungsfelder zu identifizieren und zusätzliche Massnahmen zu prüfen. Der Bundesrat beantragt Ihnen deshalb, dieses Postulat anzunehmen.
+    <t xml:space="preserve">Dass Frauen sexuelle oder geschlechtsspezifische Gewalt erleben müssen, ist inakzeptabel. Frauen haben Recht auf Schutz vor solcher Gewalt; das gilt auch für asylsuchende Frauen. Bereits heute garantieren verschiedene Massnahmen im Asylverfahren wie auch bei der Unterbringung und Betreuung, dass dieser Schutz effektiv gewährt wird. Diese Massnahmen sind aber grossmehrheitlich unbekannt. 
+Mit einem Bericht zur Erfüllung des Postulates könnte der Bundesrat dem Parlament aufzeigen, welche Massnahme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dass Frauen sexuelle oder geschlechtsspezifische Gewalt erleben müssen, ist inakzeptabel. Frauen haben Recht auf Schutz vor solcher Gewalt; das gilt auch für asylsuchende Frauen. Bereits heute garantieren verschiedene Massnahmen im Asylverfahren wie auch bei der Unterbringung und Betreuung, dass dieser Schutz effektiv gewährt wird. Diese Massnahmen sind aber grossmehrheitlich unbekannt. 
+Mit einem Bericht zur Erfüllung des Postulates könnte der Bundesrat dem Parlament aufzeigen, welche Massnahmen in diesem Bereich in den letzten Jahren umgesetzt wurden. Gleichzeitig erhielten wir die Möglichkeit, weitere Handlungsfelder zu identifizieren und zusätzliche Massnahmen zu prüfen.
+Der Bundesrat beantragt Ihnen deshalb, dieses Postulat anzunehmen.
 </t>
   </si>
   <si>
@@ -647,14 +641,14 @@
     <t xml:space="preserve">LU</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Motion der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist von Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rechtlic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Motion der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist von Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rechtlichen Grundlagen für die Verhandlung und den Einsatz sicherer Drittstaatenlösungen geschaffen werden. 
+    <t xml:space="preserve">Die Motion 26.3100 der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Motion 26.3100 der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rechtlichen Grundlagen für die Verhandlung und den Einsatz sicherer Drittstaatenlösungen geschaffen werden. 
 Europa sucht seit Jahren nach Instrumenten, um die irreguläre Migration zu reduzieren, Schleusernetze zu bekämpfen und die Asylverfahren zu beschleunigen. Das Europäische Parlament hat am 5. Februar 2026 neue Regeln verabschiedet, nach denen unter anderem eine EU-weite Liste sicherer Herkunftsstaaten geschaffen wird und es Mitgliedstaaten ermöglicht wird, Abkommen mit Drittstaaten abzuschliessen, in denen Asylanträge geprüft werden können. Das Modell der Rückführungszentren und die verstärkte Verknüpfung von Rücknahmekooperationen mit anderen politischen Hebeln wie Visa oder Entwicklungshilfe werden in mehreren europäischen Debatten bereits behandelt. 
-Die Schweiz registriert immer wieder Asylgesuche von Personen, die vor ihrer Einreise bereits längere Zeit in Drittstaaten lebten, in denen keine unmittelbare Gefährdung bestand. Nach geltendem Recht ist ein Nichteintreten möglich, wenn der Drittstaat als sicher gilt. In der Praxis scheitert eine Rückführung aber häufig an fehlenden Abkommen oder an der Weigerung der betroffenen Staaten, Personen wieder aufzunehmen. Diese Lücke schwächt die Glaubwürdigkeit des Asylsystems, das dort Schutz bieten soll, wo er effektiv erforderlich ist. Dies ist Gegenstand des Postulates Caroni 23.4490, welches den Bundesrat beauftragt, in einem Bericht eine Auslegeordnung zu Asylverfahren und zum Wegweisungsvollzug im Ausland, insbesondere in Drittstaaten, vorzulegen und die Vereinbarkeit mit schweizerischen Standards zu prüfen. 
-Der Bundesrat lehnt die Motion mit der Begründung ab, die Schweiz habe eine der höchsten Rückkehrraten in Europa. Diese Aussage blendet jedoch aus, dass vor allem die Wirtschaftsflüchtlinge aus Nordafrika einen zu grossen Platz in unserer Asylstatistik einnehmen. Nicht dies allein ist ein grosses Ärgernis, sondern die Tatsache, dass genau diese Personen in der Statistik der Straftaten mit dem sehr hohen Wert von über 80 Prozent negativ auffallen. Dies führt nicht nur zu einer hohen Gefährdung der Sicherheit unserer Bevölkerung, sondern auch zu einer schlechten Akzeptanz gegenüber nachweislich schutzberechtigten Flüchtlingen. Diese nicht ausgewiesenen abgewiesenen Flüchtlinge schaden damit der humanitären Grundhaltung unserer Bevölkerung. 
-Geschätzter Herr Bundesrat Jans, die Schweiz braucht neben verstärkten Rücknahmekooperationen handhabbare Instrumente, um die Staaten, die Rücknahmen systematisch verweigern oder behindern, konsequent umgehen zu können. Gezielt eingesetzte Visa-Restriktionen und Konditionalität sind verhältnismässige internationale Standardinstrumente, die die Rücknahmebereitschaft erhöhen können, ohne den Schutzberechtigten die Rechtsmittel oder den Zugang zu internationalem Schutz zu entziehen. Ergänzend ermöglichen Rückführungszentren und Drittstaatenlösungen, abgewiesene Fälle von Personen konsequent ausserhalb Europas zu bearbeiten oder diese unterzubringen, sofern menschenrechtliche und verfahrensrechtliche Mindeststandards garantiert sind. 
+Die Schweiz registriert immer wieder Asylgesuche von Personen, die vor ihrer Einreise bereits längere Zeit in Drittstaaten lebten, in denen keine unmittelbare Gefährdung bestand. Nach geltendem Recht ist ein Nichteintreten möglich, wenn der Drittstaat als sicher gilt. In der Praxis scheitert eine Rückführung aber häufig an fehlenden Abkommen oder an der Weigerung der betreffenden Staaten, Personen wieder aufzunehmen. Diese Lücke schwächt die Glaubwürdigkeit des Asylsystems, das dort Schutz bieten soll, wo er effektiv erforderlich ist. Dies ist Gegenstand des Postulates Caroni 23.4490, welches den Bundesrat beauftragt, in einem Bericht eine Auslegeordnung zu Asylverfahren und zum Wegweisungsvollzug im Ausland, insbesondere in Drittstaaten, vorzulegen und die Vereinbarkeit mit schweizerischen Standards zu prüfen. 
+Der Bundesrat lehnt die Motion mit der Begründung ab, die Schweiz habe eine der höchsten Rückkehrraten in Europa. Diese Aussage blendet jedoch aus, dass vor allem die Wirtschaftsflüchtlinge aus Nordafrika einen zu grossen Platz in unserer Asylstatistik einnehmen. Nicht dies allein ist ein grosses Ärgernis, sondern die Tatsache, dass genau diese Personen in der Statistik der Straftaten mit einem sehr hohen Wert von über 80 Prozent negativ auffallen. Dies führt nicht nur zu einer hohen Gefährdung der Sicherheit unserer Bevölkerung, sondern auch zu einer schlechten Akzeptanz gegenüber nachweislich schutzberechtigten Flüchtlingen. Diese nicht ausgewiesenen abgewiesenen Flüchtlinge schaden damit der humanitären Grundhaltung unserer Bevölkerung. 
+Geschätzter Herr Bundesrat Jans, die Schweiz braucht neben verstärkten Rücknahmekooperationen handhabbare Instrumente, um die Staaten, die Rücknahmen systematisch verweigern oder behindern, konsequent umgehen zu können. Gezielt eingesetzte Visa-Restriktionen und Konditionalität sind verhältnismässige internationale Standardinstrumente, die die Rücknahmebereitschaft erhöhen können, ohne den Schutzberechtigten die Rechtsmittel oder den Zugang zu internationalem Schutz zu entziehen. Ergänzend ermöglichen es Rückführungszentren und Drittstaatenlösungen, Fälle abgewiesener Personen konsequent ausserhalb Europas zu bearbeiten oder diese Personen unterzubringen, sofern menschenrechtliche und verfahrensrechtliche Mindeststandards garantiert sind. 
 Für die Unterstützung unserer Fraktionsmotion bedanke ich mich.
 </t>
   </si>
@@ -665,11 +659,11 @@
     <t xml:space="preserve">Steinemann Barbara</t>
   </si>
   <si>
-    <t xml:space="preserve">Durch Ihr Postulat soll unter anderem in Erfahrung gebracht werden, ob und wie Gewalt bei Frauen als Fluchtgrund eine Rolle spielt. Das würde mich eigentlich auch sehr interessieren. Es ist nämlich noch nicht lange her, dass über meine Postulate 25.4259, "Transparenz zu den Gründen, die zu einer vorläufigen Aufnahme führen", und 24.3290, "Transparenz in die Gründe der Asylgewährungen bringen", abgestimmt wurde. Sie wurden grossmehrheitlich überwiesen, aber nicht von Seiten der Postulantin - ausg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durch Ihr Postulat soll unter anderem in Erfahrung gebracht werden, ob und wie Gewalt bei Frauen als Fluchtgrund eine Rolle spielt. Das würde mich eigentlich auch sehr interessieren. Es ist nämlich noch nicht lange her, dass über meine Postulate 25.4259, "Transparenz zu den Gründen, die zu einer vorläufigen Aufnahme führen", und 24.3290, "Transparenz in die Gründe der Asylgewährungen bringen", abgestimmt wurde. Sie wurden grossmehrheitlich überwiesen, aber nicht von Seiten der Postulantin - ausgerechnet Rot-Grün hat nicht für diese Offenlegungen gestimmt. Das ist auch ein Grund, weshalb wir unser bestehendes System ganz grundsätzlich überdenken müssen. Möchten wir möglichst vielen Menschen Schutz bieten, können wir das unmöglich auf Schweizer Boden tun. Die Auslagerung der Asylverfahren würde eine Reduktion der irregulären Migration bewirken und damit präventive Wirkung zeitigen. Und wir würden hier unsere Strukturen entlasten. Und der Franken wäre dort viel besser investiert. 
-Leider bewegt sich in Bern nichts in diese Richtung. Hingegen sind Linke der Ansicht, dass man unendlich viele Menschen aufnehmen und integrieren kann. Wenn das heutige System uns schon an den Anschlag bringt, dann ist die Ausweitung auf neue Asylgründe nicht unbedingt das passende Rezept. Auf einen neuen Asylgrund "geschlechtsspezifische Gewalt" läuft dieses Postulat jedoch hinaus. Unsere Asylpraxis würde sich noch mehr vom Ursprungsgedanken der Genfer Flüchtlingskonvention entfernen, und international dürften wir damit Neuland betreten. Legen wir in Zukunft den Fokus auf die Aufnahme von Frauen und Mädchen, werden diese dann auch Familiennachzug machen können, mit allen Folgen. Es ist zu hoffen, dass wir mit unserem teuren und personalintensiven Asylsystem heute schon sicherstellen, dass Frauen und Mädchen angemessen untergebracht werden, damit sie hier keiner Gewalt ausgesetzt sind. 
+    <t xml:space="preserve">Mit Ihrem Postulat soll unter anderem in Erfahrung gebracht werden, ob und wie Gewalt bei Frauen als Fluchtgrund eine Rolle spielt. Das würde mich eigentlich auch sehr interessieren. Es ist nämlich noch nicht lange her, dass über meine Postulate 25.4259, "Transparenz zu den Gründen, die zu einer vorläufigen Aufnahme führen", und 24.3290, "Transparenz in die Gründe der Asylgewährungen bringen", abgestimmt wurde. Sie wurden grossmehrheitlich angenommen, aber nicht vonseiten der Postulantin - ausge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mit Ihrem Postulat soll unter anderem in Erfahrung gebracht werden, ob und wie Gewalt bei Frauen als Fluchtgrund eine Rolle spielt. Das würde mich eigentlich auch sehr interessieren. Es ist nämlich noch nicht lange her, dass über meine Postulate 25.4259, "Transparenz zu den Gründen, die zu einer vorläufigen Aufnahme führen", und 24.3290, "Transparenz in die Gründe der Asylgewährungen bringen", abgestimmt wurde. Sie wurden grossmehrheitlich angenommen, aber nicht vonseiten der Postulantin - ausgerechnet Rot-Grün hat nicht für diese Offenlegungen gestimmt. Das ist auch ein Grund, weshalb wir unser bestehendes System ganz grundsätzlich überdenken müssen. Möchten wir möglichst vielen Menschen Schutz bieten, so können wir das unmöglich auf Schweizer Boden tun. Die Auslagerung der Asylverfahren würde eine Reduktion der irregulären Migration bewirken und damit präventive Wirkung zeitigen, wir würden hier unsere Strukturen entlasten, und der Franken wäre dort viel besser investiert. 
+Leider bewegt sich in Bern nichts in diese Richtung. Hingegen sind Linke der Ansicht, dass man unendlich viele Menschen aufnehmen und integrieren kann. Wenn das heutige System uns schon an den Anschlag bringt, dann ist die Ausweitung auf neue Asylgründe nicht unbedingt das passende Rezept. Auf einen neuen Asylgrund "geschlechtsspezifische Gewalt" läuft dieses Postulat jedoch hinaus. Unsere Asylpraxis würde sich noch mehr vom Ursprungsgedanken der Genfer Flüchtlingskonvention entfernen, und international dürften wir damit Neuland betreten. Legen wir in Zukunft den Fokus auf die Aufnahme von Frauen und Mädchen, so werden diese dann auch einen Familiennachzug machen können, mit allen Folgen. Es ist zu hoffen, dass wir mit unserem teuren und personalintensiven Asylsystem heute schon sicherstellen, dass Frauen und Mädchen angemessen untergebracht werden, damit sie hier keiner Gewalt ausgesetzt sind. 
 Vor einigen Jahren haben NGO-Aktivisten eine medial gross angelegte Kampagne über angebliche Misshandlungen durch Betreuer in Asylzentren inszeniert, die das SEM durch einen alt Bundesrichter genau untersuchen liess und deren Vorwürfe sich allesamt in Luft aufgelöst haben. Wir müssen uns also kein schlechtes Gewissen einreden lassen. 
 Bitte lehnen Sie das Postulat ab.
 </t>
@@ -688,9 +682,9 @@
     <t xml:space="preserve">Le postulat que je défends vise à renforcer la protection des femmes et des filles, par le biais d'un rapport sur la manière de mieux identifier et protéger les personnes ayant subi des violences sexuelles ou des violences sexistes fondées sur le genre. Cette demande part d'un constat simple, mais particulièrement préoccupant. Partout dans le monde, des femmes et des filles sont contraintes de fuir parce qu'elles risquent un mariage forcé, des mutilations génitales, des violences sexuelles, la t</t>
   </si>
   <si>
-    <t xml:space="preserve">Le postulat que je défends vise à renforcer la protection des femmes et des filles, par le biais d'un rapport sur la manière de mieux identifier et protéger les personnes ayant subi des violences sexuelles ou des violences sexistes fondées sur le genre. Cette demande part d'un constat simple, mais particulièrement préoccupant. Partout dans le monde, des femmes et des filles sont contraintes de fuir parce qu'elles risquent un mariage forcé, des mutilations génitales, des violences sexuelles, la traite des êtres humains ou encore des violences domestiques auxquelles leur État ne veut ou ne peut pas mettre fin. Elles fuient, non pas malgré leur condition de femmes, mais précisément à cause de cette dernière.
-La Suisse reconnaît déjà dans certaines situations que les persécutions liées au genre peuvent justifier une protection internationale. Cette reconnaissance repose cependant encore largement sur l'interprétation juridique et sur la jurisprudence actuelle. Les violences fondées sur le genre ne sont pas toujours examinées de manière systématique ni suffisamment visible dans les procédures d'asile. C'est d'ailleurs ce que souligne le dernier rapport du réseau d'ONG de la Convention d'Istanbul. Ce dernier montre qu'il existe encore d'importantes lacunes. Les motifs d'asile liés au genre sont parfois insuffisamment pris en compte. Les risques spécifiques encourus par les femmes en cas de renvoi ne sont pas toujours évalués de manière adéquate et l'accès à un accompagnement spécialisé reste limité. Il manque également des données fiables qui permettent de mesurer l'ampleur du phénomène, mais aussi d'évaluer la qualité des décisions rendues. Le rapport demandé dans ce postulat vise précisément à combler toutes ces lacunes. Cette nécessité est également confirmée à l'échelle internationale, c'est important de le souligner. En juillet 2025, il y a une année, le Comité des Nations Unies pour l'élimination de la discrimination à l'égard des femmes a rendu trois décisions concernant la Suisse. C'est important de les entendre, car ces décisions, prises au niveau des Nations Unies, sont les suivantes : le comité a notamment critiqué la tendance des autorités à mettre en doute la crédibilité de victimes de violences lorsqu'elles ne parviennent à parler de leurs traumatismes qu'après le début de la procédure. Le comité a également relevé que certains renvois avaient été décidés sans examen suffisamment approfondi des violences et leurs conséquences psychologiques. Ce comité rappelle pourtant un principe fondamental - il faut le rappeler encore dans notre conseil - : les demandes d'asile impliquant des violences fondées sur le genre doivent faire l'objet d'un examen individuel, complet et sensible des traumatismes vécus. Les besoins médicaux, psychologiques et de réadaptation doivent également être pris en compte avant toute décision de renvoi.
-Le Conseil fédéral souligne à juste titre que la Suisse a réalisé des progrès et que les efforts entrepris dans le cadre de la Convention d'Istanbul ont été salués. C'est une bonne chose et je m'en réjouis. Reconnaître les progrès accomplis ne signifie toutefois pas considérer que tout est parfait. Une convention internationale fixe un minimum de protection ; elle n'interdit jamais de faire mieux. C'est précisément ce que vise ce postulat. Il ne crée en aucun cas un droit automatique - c'est important de le dire. Il ne modifie pas non plus les critères d'octroi à l'asile et ne dispense personne d'établir les faits. Il vise tout simplement une chose simple : analyser de manière rigoureuse des lacunes existantes et de proposer des améliorations concrètes pour que les femmes et les filles victimes de violences sexistes et sexuelles bénéficient d'une protection adaptée à leur réalité.
+    <t xml:space="preserve">Le postulat que je défends vise à renforcer la protection des femmes et des filles, par le biais d'un rapport sur la manière de mieux identifier et protéger les personnes ayant subi des violences sexuelles ou des violences sexistes fondées sur le genre. Cette demande part d'un constat simple, mais particulièrement préoccupant. Partout dans le monde, des femmes et des filles sont contraintes de fuir parce qu'elles risquent un mariage forcé, des mutilations génitales, des violences sexuelles, la traite ou encore des violences domestiques auxquelles leur État ne veut ou ne peut pas mettre fin. Elles fuient, non pas malgré leur condition de femmes, mais précisément à cause de cette dernière.
+La Suisse reconnaît déjà dans certaines situations que les persécutions liées au genre peuvent justifier une protection internationale. Cette reconnaissance repose cependant encore largement sur l'interprétation juridique et sur la jurisprudence actuelle. Les violences fondées sur le genre ne sont pas toujours examinées de manière systématique ni suffisamment visible dans les procédures d'asile. C'est d'ailleurs ce que souligne le dernier rapport du réseau d'ONG de la Convention d'Istanbul. Ce dernier montre qu'il existe encore d'importantes lacunes. Les motifs d'asile liés au genre sont parfois insuffisamment pris en compte. Les risques spécifiques encourus par les femmes en cas de renvoi ne sont pas toujours évalués de manière adéquate, et l'accès à un accompagnement spécialisé reste limité. Il manque également des données fiables qui permettent de mesurer l'ampleur du phénomène, mais aussi d'évaluer la qualité des décisions rendues. Le rapport demandé dans ce postulat vise précisément à combler toutes ces lacunes. Cette nécessité est également confirmée à l'échelle internationale, c'est important de le souligner. En juillet 2025, il y a une année, le Comité des Nations Unies pour l'élimination de la discrimination à l'égard des femmes a rendu trois décisions concernant la Suisse. C'est important de les entendre, car ces décisions, prises au niveau des Nations Unies, sont les suivantes[NB]: le comité a notamment critiqué la tendance des autorités à mettre en doute la crédibilité de victimes de violences lorsqu'elles ne parviennent à parler de leurs traumatismes qu'après le début de la procédure. Le comité a également relevé que certains renvois avaient été décidés sans examen suffisamment approfondi des violences et de leurs conséquences psychologiques. Ce comité rappelle pourtant un principe fondamental - il faut le rappeler encore dans notre conseil -[NB]: les demandes d'asile impliquant des violences fondées sur le genre doivent faire l'objet d'un examen individuel, complet et sensible des traumatismes vécus. Les besoins médicaux, psychologiques et de réadaptation doivent également être pris en compte avant toute décision de renvoi.
+Le Conseil fédéral souligne à juste titre que la Suisse a réalisé des progrès et que les efforts entrepris dans le cadre de la Convention d'Istanbul ont été salués. C'est une bonne chose et je m'en réjouis. Reconnaître les progrès accomplis ne signifie toutefois pas considérer que tout est parfait. Une convention internationale fixe un minimum de protection[NB]; elle n'interdit jamais de faire mieux. C'est précisément ce que vise ce postulat. Il ne crée en aucun cas un droit automatique - c'est important de le dire. Il ne modifie pas non plus les critères d'octroi à l'asile et ne dispense personne d'établir les faits. Il vise tout simplement une chose simple[NB]: analyser de manière rigoureuse des lacunes existantes et proposer des améliorations concrètes pour que les femmes et les filles victimes de violences sexistes et sexuelles bénéficient d'une protection adaptée à leur réalité.
 Derrière ces concepts juridiques, il y a évidemment des parcours de vie, des parcours difficiles, il y a l'exil, mais il y a aussi ces femmes qui ont subi des violences et qui doivent pouvoir être protégées. Des femmes qui ont subi des violences dans leur pays d'origine doivent pouvoir être protégées par notre propre système, en Suisse. Il y a celles qui continuent d'en subir sur les routes migratoires. Il y a celles qui arrivent en Suisse avec des traumatismes profonds et qui doivent ensuite raconter des expériences extrêmement difficiles pour obtenir une protection. Nous avons la responsabilité de nous assurer que notre système est capable d'entendre ces récits - on ne demande pas grand-chose de plus -, de les comprendre et d'y répondre avec tout le professionnalisme nécessaire.
 Je vous remercie d'avance d'accepter ce postulat.
 </t>
@@ -1237,10 +1231,10 @@
     <t xml:space="preserve">421290</t>
   </si>
   <si>
-    <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, le représentant de l'Union démocratique du centre va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la commune fusionne et devient Tr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, le représentant de l'Union démocratique du centre va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la commune fusionne et devient Tresa, il conserve le poste de syndic jusqu'à aujourd'hui et son entrée au gouvernement tessinois. En 2013, il prend la vice-présidence de l'Union démocratique du centre tessinoise, qu'il présidera ensuite pendant 10 ans, de 2016 à aujourd'hui. L'année 2019 marque un tournant dans sa carrière politique, avec son élection au Grand Conseil tessinois qu'il quittera la même année après son élection au Conseil national. Depuis son entrée en fonction au Conseil national, il est membre de la Commission des institutions politiques et de la Délégation pour les relations avec le Parlement italien. Il siégera par la suite également au sein de la Commission de rédaction de langue italienne, de la Commission de politique extérieure, ainsi que de la Commission de la politique de sécurité.
+    <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, notre collègue Piero Marchesi, représentant de l'Union démocratique du centre, va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après avoir siégé près de sept ans sous la Coupole fédérale, notre collègue Piero Marchesi, représentant de l'Union démocratique du centre, va accéder au Conseil d'État tessinois dans quelques jours. Celui qui a grandi dans le Malcantone et passé ses vacances dans la région de Blenio, a fait ses premiers pas en politique à l'âge de 18 ans, en tant qu'élu au législatif de Monteggio. En 2008, il accède à l'exécutif de cette même commune. Il en devient le syndic en 2012. En avril 2021, lorsque la commune fusionne et devient Tresa, il conserve le poste de syndic jusqu'à aujourd'hui et son entrée au gouvernement tessinois. En 2013, il prend la vice-présidence de l'Union démocratique du centre tessinoise, qu'il présidera ensuite pendant 10 ans, de 2016 à aujourd'hui. L'année 2019 marque un tournant dans sa carrière politique, avec son élection au Grand Conseil tessinois qu'il quittera la même année après son élection au Conseil national. Depuis son entrée en fonction au Conseil national, il est membre de la Commission des institutions politiques et de la Délégation pour les relations avec le Parlement italien. Il siégera par la suite également au sein de la Commission de rédaction de langue italienne, de la Commission de politique extérieure, ainsi que de la Commission de la politique de sécurité.
 Entrepreneur et électricien de formation, il s'engage particulièrement au sein de notre institution en faveur d'un État moins bureaucratique et pour des conditions-cadres favorables aux entreprises en déposant plusieurs interventions allant dans ce sens. Il a également consacré plusieurs de ses interventions parlementaires à la politique migratoire et d'asile, aux questions de sécurité et à la défense des intérêts du canton du Tessin.
 Plusieurs de ses motions ont été adoptées par le Parlement. Nous pouvons citer la motion 21.4076, "Permis de séjour. Rétablir le principe du centre des intérêts". Plus récemment, les Chambres fédérales ont adopté sa motion 25.4013, "Renforcer la sécurité du personnel ferroviaire et des passagers", qui doit conduire à la présentation d'un plan national visant à renforcer la sécurité dans les trains, ainsi que sa motion 25.3438, "Lutte contre le phénomène préoccupant des faux documents en Suisse", qui vise à renforcer le contrôle de l'authenticité des documents d'identité. Enfin, nous avons également adopté sa motion 23.4166, "Mettre fin à la vente en ligne des jouets dangereux pour la santé", qui doit encore être examinée par le Conseil des États.
 Après les spéciales communale, cantonale et fédérale, Piero Marchesi, ancien pilote de rallye, amorce un nouveau virage et se trouve au départ d'une nouvelle étape, l'exécutif cantonal. Nous le remercions pour son engagement au sein de notre conseil et lui souhaitons plein succès dans ses nouvelles fonctions. Et bien entendu, bonne route, Piero ! (Standing ovation ; le président remet un bouquet de fleurs à M. Marchesi)[GZ]
@@ -1680,6 +1674,321 @@
 Ich beantrage Ihnen, dem einstimmigen Antrag Ihrer Kommission zu folgen und dem Entwurf zum Bundesbeschluss zuzustimmen.
 </t>
   </si>
+  <si>
+    <t xml:space="preserve">421345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sommaruga Carlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En ma qualité de président de la Commission de politique extérieure (CPE), j'ai la délicate tâche d'ouvrir nos débats sur le paquet "Stabilisation et développement des relations Suisse-UE", les Bilatérales III, et plus particulièrement de présenter les décisions et les réflexions de la CPE relatives à l'entrée en matière sur l'arrêté fédéral 1 relatif à la stabilisation de la voie bilatérale.
+Je voudrais d'emblée rappeler les deux votes qui encadrent les travaux de notre commission. Le 17 avril,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En ma qualité de président de la Commission de politique extérieure (CPE), j'ai la délicate tâche d'ouvrir nos débats sur le paquet "Stabilisation et développement des relations Suisse-UE", les Bilatérales III, et plus particulièrement de présenter les décisions et les réflexions de la CPE relatives à l'entrée en matière sur l'arrêté fédéral 1 relatif à la stabilisation de la voie bilatérale.
+Je voudrais d'emblée rappeler les deux votes qui encadrent les travaux de notre commission. Le 17 avril, la CPE a décidé, par 9 voix contre 3, d'entrer en matière sur l'arrêté fédéral 1. Au terme de son examen, le 4 septembre, elle a confirmé cette orientation en adoptant l'arrêté au vote sur l'ensemble, par 9 voix contre 3 et 1 abstention. Entre ces deux votes, lors de cinq séances largement consacrées aux Bilatérales III, la commission a procédé à un examen approfondi du paquet, de ses conséquences institutionnelles et de sa mise en oeuvre en Suisse.
+Au terme de ces travaux, l'appréciation de la majorité est claire : le paquet négocié avec l'Union européenne (UE) permet de stabiliser durablement la voie bilatérale et de préserver l'accès de la Suisse aux secteurs du marché européen auxquels elle a choisi de participer et de développer notre coopération dans de nouveaux domaines tout en maintenant nos procédures constitutionnelles, nos droits démocratiques et notre organisation fédéraliste. C'est cette appréciation de la majorité que je vais vous présenter, laissant la minorité développer ses propres arguments.
+Bien que cela soit une évidence, il est important de souligner d'entrée que la question qui nous est posée n'est pas de savoir si la Suisse doit avoir ou non des relations étroites avec l'UE, mais comment elle veut les organiser. Ces relations existent. Elles sont une réalité géographique, économique, sociale, scientifique et humaine.
+L'UE et ses États membres sont de très loin nos principaux partenaires économiques. Ils sont nos voisins. Des centaines de milliers de personnes franchissent quotidiennement nos frontières, nos entreprises sont intégrées dans des chaînes de production européennes, nos universités et nos chercheurs travaillent dans des réseaux européens de recherche et nos infrastructures de transport terrestre, ferroviaire et aérien sont étroitement liées à celles de nos voisins.
+Depuis le refus de l'Espace économique européen (EEE), en 1992, la Suisse a progressivement construit une voie propre : la voie bilatérale. Cette dernière permet à notre pays de participer aux secteurs du marché intérieur que nous avons librement choisis et à différentes formes de coopération européenne, sans adhérer à l'UE ni à l'EEE.
+La majorité de la commission considère que cette voie a servi les intérêts de la Suisse et qu'elle doit être poursuivie, mais, pour pouvoir l'être, elle doit aujourd'hui être consolidée et stabilisée. Pour la majorité, on ne peut considérer que le statu quo assurera le maintien de la voie bilatérale. Ne rien faire signifie prendre le risque d'une érosion progressive et, à terme, du blocage de cette voie bilatérale. Tout accord s'inscrit dans un environnement juridique, économique et technologique qui change. Ainsi, lorsque les règles européennes sur lesquelles reposent les accords bilatéraux évoluent, il faut pouvoir adapter ces accords si nous voulons conserver des conditions équivalentes d'accès au marché.
+L'expérience de ces dernières années a montré les limites du système actuel. L'absence de mécanisme institutionnel durable a compliqué, voire empêché, l'actualisation de certains accords, avec des conséquences négatives dans plusieurs domaines économiques. On entend ici et là qu'en cas de refus du paquet, les accords bilatéraux existants continueraient simplement à s'appliquer et que la Suisse disposerait de tout le temps nécessaire pour renégocier avec l'UE, domaine par domaine et au cas par cas, les adaptations dont elle aurait besoin.
+Certes, juridiquement, un rejet du paquet par le Parlement ou le peuple n'entraînerait pas la disparition immédiate des accords existants, mais la majorité estime, de manière très claire, que laisser croire que le statu quo pourrait être durablement maintenu sans conséquence et que l'Union européenne reviendrait simplement négocier acte par acte un accès au marché correspondant aux seuls besoins de la Suisse est simplement contraire à la réalité.
+Pour la majorité, le choix est donc clair : soit accepter une érosion progressive de la voie bilatérale et l'incertitude qui en découle, soit la consolider afin qu'elle puisse fonctionner dans la durée. En invitant notre conseil à entrer en matière et à adopter l'arrêté fédéral 1, la majorité vous invite à suivre la seconde voie.
+À ce stade, il convient de souligner que les accords qui nous sont transmis pour ratification, comme les lois de mise en oeuvre et les mesures d'accompagnement qui les accompagnent, sont issus non seulement d'une négociation avec l'Union européenne, mais aussi d'un intense processus de consultation politique interne. Après l'interruption en 2021 des négociations sur l'accord institutionnel, le Conseil fédéral a développé une nouvelle approche. Il a renoncé à un accord institutionnel horizontal. Les éléments institutionnels sont désormais intégrés directement dans chacun des accords d'accès aux marchés concernés. Pour la commission, cette approche sectorielle correspond à la logique de la voie bilatérale. La Suisse choisit les domaines dans lesquels elle souhaite participer au marché intérieur européen et les obligations institutionnelles restent liées à ces accords. Il faut également rappeler que le mandat de négociation n'a pas été élaboré par le Conseil fédéral seul. Le projet adopté en décembre 2023 a fait l'objet d'une large consultation. Les Commissions de politique extérieure des deux conseils, les autres commissions parlementaires concernées, les cantons par l'intermédiaire de la Conférence des gouvernements cantonaux, les partenaires sociaux et les milieux économiques ont été invités à se prononcer.
+Cette consultation a eu des effets concrets : le Conseil fédéral a intégré dans le mandat définitif plusieurs remarques et demandes formulées au cours de la procédure, notamment sur les questions institutionnelles, la libre circulation et la protection des salaires, le transport ferroviaire international et l'électricité.
+Notre commission avait elle-même examiné le projet de mandat en janvier et février 2024. Elle avait soutenu l'orientation générale et l'ouverture des négociations, par 9 voix contre 3 et 1 abstention, tout en adressant plusieurs recommandations au Conseil fédéral.
+Le mandat définitif, adopté en mars 2024, était donc déjà le résultat d'un processus associant le Parlement, les cantons ainsi que les partenaires socioéconomiques. Ce dialogue s'est poursuivi pendant les négociations, notamment avec les Commissions de politique extérieure (CPE), où nous avons pu régulièrement obtenir des informations sur l'avancement et les résultats.
+Une fois les négociations terminées, le paraphe apposé, et avant la signature, les accords et les actes législatifs de mise en oeuvre ont été soumis à une procédure ordinaire de consultation.
+Votre commission a pris connaissance des résultats de cette consultation et les a intégrés dans son appréciation politique du paquet. Une nette majorité des participants à la consultation s'est prononcée favorablement tant sur le paquet dans son ensemble que sur le résultat des négociations. La voie bilatérale a recueilli un soutien particulièrement large par rapport aux autres options de politique européenne. La consultation a aussi fait apparaître plusieurs demandes d'amélioration concernant la mise en oeuvre en Suisse. Le Conseil fédéral en a tenu compte et a adapté sur plusieurs points les projets législatifs avant de transmettre son message au Parlement.
+Les textes législatifs de mise en oeuvre des accords que nous examinerons en détail, en passant en revue les diverses annexes de l'arrêté 1, sont donc non seulement le résultat de la négociation avec l'Union européenne, mais aussi d'un processus de consultation et d'ajustement interne à notre pays.
+Il est nécessaire, dans le cadre du débat d'entrée en matière, de rappeler les différents objectifs des accords dont le Conseil fédéral demande l'approbation. Quatorze d'entre eux, énumérés, à l'arrêté fédéral 1, visent la stabilisation de la voie bilatérale. Ils portent sur la contribution à la cohésion, la libre circulation des personnes, les obstacles techniques au commerce, les transports terrestres, les transports aériens, les transports ferroviaires, l'agriculture et la participation aux programmes européens de recherche en cours, à savoir Horizon Europe, Euratom, Digital Europe, Erasmus plus, EU4Health et Iter et les futurs programmes d'ailleurs.
+Trois autres accords faisant l'objet d'arrêtés distincts concernent le développement de la voie bilatérale dans les domaines de la sécurité des aliments, de la santé et de l'électricité. Celui relatif à l'électricité ne fait toutefois pas l'objet de nos débats lors de cette session, son traitement en commission n'étant pas encore achevé. Enfin, le paquet que nous traitons pendant cette session comprend encore un accord sur la coopération parlementaire.
+En plus de ces différents accords, le paquet inclut trois crédits d'engagement relatifs à la contribution à la cohésion et un crédit relatif au financement de la participation de la Suisse au programme Erasmus.
+Dans sa version définitive, le paquet des Bilatérales III, qui concerne 95 actes législatifs de l'UE, inclut pour la mise en oeuvre des accords trois nouvelles lois fédérales ainsi que la modification de 32 autres. L'ampleur du paquet a induit une organisation unique du travail parlementaire, celle des "corapports plus" permettant à la fois un examen spécialisé des différentes matières par les commissions thématiques et une appréciation politique d'ensemble par une commission. La nouveauté, c'est que les propositions figurant dans les "corapports plus" sont inscrites dans le dépliant.
+La CPE de votre conseil s'est vue attribuer la responsabilité principale et d'ensemble de l'examen de la partie "stabilisation" et donc de l'arrêté fédéral 1, ainsi que le volet de la contribution à la cohésion et de la participation du Parlement. Les commissions thématiques, à savoir la CIP, la CER, la CTT et la CSEC, ont pour leur part examiné les annexes et les arrêtés relevant de leurs domaines de compétences respectifs, en élaborant le cas échéant également des "corapports plus". Cette organisation a permis aux commissions spécialisées d'examiner les dispositions dans le détail tout en permettant à la CPE d'en apprécier les implications pour la politique européenne et la cohérence avec l'ensemble du résultat négocié et des projets législatifs mis en place.
+Dès le début des travaux, notre commission a toutefois considéré qu'un dossier d'une telle importance devait être examiné de manière globale et non purement sectorielle. Ainsi, lors de sa première séance de traitement des Bilatérales III, le 25 mars 2026, elle a consacré la journée entière aux auditions des cantons, des partenaires sociaux, des milieux économiques, ainsi que des spécialistes de politique européenne, d'économie, de droit constitutionnel, de droit international et de droit européen. Les auditions ont porté sur quatre grands domaines : l'appréciation du paquet sous l'angle de la politique extérieure, ses conséquences économiques, les questions institutionnelles, en particulier la reprise dynamique du droit et le règlement des différends, et la question du référendum. Les membres des autres commissions de notre conseil concernés ont été invités à y participer.
+Après cette première phase, la commission a décidé, comme déjà indiqué, par 9 voix contre 3, d'entrer en matière et, par 10 voix contre 2, de rejeter une proposition de renvoi au Conseil fédéral. Elle a procédé ensuite à la discussion par article des annexes à l'arrêté 1. Elle a examiné directement les objets relevant de sa compétence, notamment la contribution à la cohésion, la participation du Parlement et la coopération parlementaire. Elle a également fait usage de la procédure de corapport élargi - le corapport plus -, qui lui permettait de formuler des propositions dans les domaines attribués aux commissions thématiques. Elle en a fait usage notamment pour la surveillance des aides d'État, la libre circulation des personnes et la protection des salaires.
+C'est après ce travail coordonné et après avoir pris connaissance des travaux des commissions spécialisées que la Commission de politique extérieure a procédé, lors de sa séance des 3 et 4 septembre derniers, au vote sur l'ensemble. Elle a adopté l'arrêté 1, par 9 voix contre 3 et 1 abstention.
+La question de la reprise dynamique du droit européen, prévue pour les accords de participation au marché intérieur, réglée dans quatre protocoles spécifiques visés par l'article 1 de l'arrêté 1, a évidemment été discutée en profondeur par la commission, car elle touche directement la question de l'évolution dynamique des accords et en même temps la problématique de notre souveraineté et du fonctionnement de notre démocratie directe.
+La Suisse n'est pas membre de l'Union européenne et ne participe donc pas aux décisions de ses institutions comme un État membre. En revanche, dans les secteurs du marché unique couverts par les accords, elle pourra participer en amont à l'élaboration des actes européens qui peuvent la concerner et faire valoir ses intérêts. C'est le fameux "decision shaping".
+Il est judicieux de rappeler que la Suisse connaît déjà ce mécanisme dans le cadre des accords de Schengen/Dublin. On peut rappeler à ce propos l'exception en faveur de la Suisse obtenue lors de l'adoption par l'Union européenne de la Directive 2017/853 relative au contrôle de l'acquisition et de la détention d'armes, qui a permis de tenir compte de la tradition suisse concernant les armes d'ordonnance.
+Surtout, il faut le répéter, car c'est essentiel : un nouvel acte européen relevant des accords ne devient pas automatiquement applicable en Suisse. La Suisse décide librement si elle le reprend. Les quatre accords relatifs aux questions institutionnelles prévoient explicitement à l'article 6 commun que cette décision intervient selon nos propres procédures constitutionnelles. Le Parlement conserve ses compétences. Les cantons conservent les leurs. Lorsque les conditions sont remplies, le référendum reste possible. Le peuple conserve donc son droit de dire non. Il est ainsi factuellement inexact, comme cela a parfois été le cas dans notre commission, de soutenir que l'Union européenne légiférerait désormais pour la Suisse. L'Union européenne légifère pour son marché intérieur. La Suisse décide librement, conformément à ses institutions, si elle reprend une évolution du droit lorsqu'elle souhaite continuer à bénéficier des droits découlant de l'accord concerné.
+Si le Parlement ou le peuple décident de ne pas reprendre une règle jugée nécessaire au fonctionnement de l'accord, l'Union européenne peut réagir. La question déterminante dans ces cas est donc de savoir si les conséquences d'un refus suisse sont juridiquement encadrées. Elles le sont dans le cadre des dispositions sur le règlement des différends. Les mesures compensatoires dont la commission a examiné le fonctionnement en détail ne sont ni automatiques ni discrétionnaires. Elles sont soumises à des procédures précises et à un contrôle de leur proportionnalité.
+Il a été soutenu en commission, comme dans le débat public, qu'à l'avenir le peuple suisse voterait avec une épée de Damoclès au-dessus de lui et que s'il refusait de reprendre un acte européen, l'Union européenne pourrait le "punir".
+Pour la majorité, cette présentation ne correspond pas au mécanisme négocié. Un refus suisse de reprendre un développement de droit ne provoque pas automatiquement la résiliation de l'ensemble des accords et ne déclenche pas automatiquement des mesures compensatoires. Le différend doit être traité selon des mécanismes précis convenus. Les mesures compensatoires éventuelles, s'il n'y a pas d'accord au comité mixte, doivent être prises dans le périmètre défini par les accords de participation au marché. Elles ne peuvent plus être prises, par exemple, sur l'équivalence des bourses, comme cela a été le cas par le passé, ou le programme de recherche, comme cela a également été le cas par le passé. Au surplus, ces mesures doivent être proportionnées et leur proportionnalité peut être soumise au contrôle du tribunal arbitral. Lors des travaux, l'administration a rappelé que le mécanisme des mesures compensatoires, souvent décriées, n'est pas une nouveauté pour notre pays. En effet, 34 accords de libre-échange ratifiés par notre Parlement prévoient la possibilité de mesures compensatoires. Ainsi, si la Suisse viole l'accord avec la Chine, par exemple par l'adoption d'une initiative populaire, la Chine peut prendre des mesures compensatoires. Il faut ajouter que le mécanisme des mesures compensatoires fait partie intégrante de la mécanique des accords de l'OMC. Bien entendu, le nouveau système ne supprime pas complètement le rapport de force entre la Suisse et l'Union européenne, mais il l'encadre, lui donne un caractère juridique et introduit un contrôle de proportionnalité. Avec le mécanisme négocié, la Suisse conserve donc la possibilité de dire non, y compris par référendum, mais les deux parties connaissent à l'avance les règles applicables en cas de désaccord. Pour la majorité, c'est un progrès essentiel par rapport à la situation actuelle.
+Une autre préoccupation exprimée en commission, comme également dans le débat public, est que la reprise dynamique du droit européen renforcerait le Conseil fédéral et l'administration au détriment du Parlement, des cantons et de nos traditionnelles procédures de consultation. La commission a pris cette question très au sérieux. Comme nous le verrons lors de la discussion par article de l'annexe 6, la commission propose précisément de renforcer les droits d'information et de consultation du Parlement afin qu'il ne soit pas placé devant le fait accompli lorsqu'une évolution du droit européen touchant un champ d'application des accords d'accès au marché est ouverte, adoptée par l'Union européenne et soumise au processus de reprise de droit par la Suisse.
+Les Commissions de politique extérieure et les commissions thématiques compétentes pourront faire connaître leurs positions au Conseil fédéral tout au long du processus, lors du "decision shaping", pendant la procédure de reprise du droit et même durant une phase de règlement d'un éventuel différend entre la Suisse et l'Union européenne. Dans la même perspective, la commission propose d'ailleurs de créer une antenne des Services du Parlement à Bruxelles, qui renforcerait la coopération avec nos services ici présents. En plus, il y a également la coopération entre l'Assemblée fédérale et le Parlement européen.
+Le volet "stabilisation" tel qu'il ressort des travaux de la commission prévoit donc un renforcement substantiel des droits de participation du Parlement. La même réflexion vaut pour la participation des cantons. Les dispositions légales et la convention négociée entre la Confédération et les cantons permettent de les associer suffisamment tôt lorsque leurs compétences ou leurs intérêts essentiels sont concernés. La commission a pris acte, d'une part, de la position favorable au paquet adoptée le 24 octobre 2025 par la Conférence des gouvernements cantonaux, par 21 voix contre 4 et 1 abstention, et, d'autre part, de la satisfaction exprimée lors des auditions relatives à la convention conclue entre la Confédération et les cantons concernant leur participation au processus. Pour la majorité, ce large soutien des cantons au paquet et au renforcement de leur participation est politiquement significatif. Il constitue un élément important de la légitimité fédéraliste et des nouveaux mécanismes institutionnels.
+La problématique de la reprise partielle de la directive européenne sur la citoyenneté et de l'adaptation de l'accord sur la libre circulation des personnes a également été abordée de manière approfondie par la commission. Bien que la discussion par article aura lieu ultérieurement, il est important de signaler que la Commission de politique extérieure a pris acte du résultat des négociations, à savoir que cela : premièrement, ne générera qu'une augmentation extrêmement marginale du flux migratoire de quelque 200 personnes ; deuxièmement, a permis de prendre en compte les préoccupations relatives notamment à la perception des prestations sociales et aux restrictions de renvoi des citoyens étrangers ; troisièmement, a permis de disposer d'une clause de sauvegarde permettant à la Suisse de prendre des mesures en cas de graves difficultés économiques ou sociales liées à la libre circulation.
+Dans son corapport, la commission a formulé quelques mesures supplémentaires de mise en oeuvre et a soutenu la proposition de la Commission des institutions politiques (CIP) concernant l'introduction d'une taxe d'incitation dans le domaine de l'immigration.
+En cours de travaux, alors que cela n'était initialement pas prévu, la CPE a souhaité pouvoir se prononcer également sur le sujet sensible des mesures relatives au marché du travail. Le bureau de notre conseil lui a octroyé la possibilité de présenter un corapport plus. Ici aussi, le détail des propositions et des votes sera examiné lors du traitement de l'annexe y relative, à savoir l'annexe 5. À ce stade, il convient toutefois de souligner que la majorité de la CPE a soutenu les mesures proposées par le Conseil fédéral concernant l'obligation de déposer une garantie, la responsabilité concernant les sous-traitants et la protection contre le licenciement des représentants élus des travailleurs. Pour la majorité, qui s'oppose aux amendements proposés par la CER, il est essentiel pour la cohérence du paquet que la législation suisse de mise en oeuvre reste pleinement conforme aux accords négociés et surtout que le compromis trouvé entre les partenaires sociaux soit respecté.
+La CPE était directement compétente pour la nouvelle loi fédérale sur les contributions à la cohésion et pour les crédits correspondants ; elle l'a examinée en détail. Nous approfondirons cette question lors du traitement de l'annexe 3 et des arrêtés fédéraux 6, 7 et 8. Je précise toutefois que, pour la majorité de la commission, la contribution à la cohésion et son volume doivent être appréciés comme un élément de l'ensemble de notre partenariat avec l'UE. C'est la raison pour laquelle les trois crédits relatifs à la cohésion, à la migration et à l'engagement de financement supplémentaire unique en faveur de la cohésion ont chacun été approuvés par la commission.
+Il reste bien sûr l'éléphant dans la pièce, à savoir la question du référendum, qui sera traitée séparément. Donc je ne la développerai pas ici. Je précise simplement pour la clarté des débats que notre commission s'est naturellement penchée sur la question et s'est prononcée contre le référendum obligatoire sui generis. Dans un vote indicatif, car elle ne pouvait pas émettre de corapport au sujet de l'initiative parlementaire de la CIP, la commission a rejeté cette initiative parlementaire. Pour la majorité, les conditions constitutionnelles permettant d'imposer un référendum obligatoire ne sont pas remplies.
+Au terme de ses travaux, la majorité considère que l'enjeu fondamental est de donner à la voie bilatérale les moyens de fonctionner durablement. Le paquet ne supprime pas la capacité de décision de la Suisse. Il organise les conditions de notre participation au secteur du marché européen que nous avons choisi d'ouvrir par la voie bilatérale. Il maintient les compétences du Parlement et les droits populaires, renforce la participation du Parlement et des cantons et encadre juridiquement le règlement des différends. 
+Pour la majorité, défendre notre souveraineté signifie l'organiser selon les règles prévisibles en défendant notre intérêt et en préservant nos institutions démocratiques ; c'est sur la base de cette appréciation que la majorité de la Commission de politique extérieure vous recommande d'entrer en matière et d'adopter l'arrêté fédéral 1.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müller Damian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich werde mich zum Eintreten zu Wort melden und anschliessend dann nur noch zum Bundesbeschluss 5, damit Sie beruhigt in den Abend gehen können. Wir entscheiden in den nächsten Stunden, nach welchen Regeln die Schweiz ihre wirtschaftliche Beziehung zum wichtigsten Handelspartner in Zukunft gestalten wird. Wir beraten heute weder einen Beitritt zur Europäischen Union noch eine gewöhnliche technische Anpassung einzelner Abkommen.
+Meine persönliche Haltung ist klar: Ich will der Schweiz den privile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich werde mich zum Eintreten zu Wort melden und anschliessend dann nur noch zum Bundesbeschluss 5, damit Sie beruhigt in den Abend gehen können. Wir entscheiden in den nächsten Stunden, nach welchen Regeln die Schweiz ihre wirtschaftliche Beziehung zum wichtigsten Handelspartner in Zukunft gestalten wird. Wir beraten heute weder einen Beitritt zur Europäischen Union noch eine gewöhnliche technische Anpassung einzelner Abkommen.
+Meine persönliche Haltung ist klar: Ich will der Schweiz den privilegierten Zugang zum europäischen Binnenmarkt sichern, aber ich bin dezidiert gegen einen Beitritt der Schweiz zur Europäischen Union, weil der Weg des bilateralen Vertrags für uns der Schweizer Weg ist. Es gibt verschiedene Meinungen und Haltungen dazu. Ein EU-Beitritt würde unsere staatspolitische Ordnung grundlegend verändern, wie man es in den vergangenen Wochen auch immer wieder lesen konnte. Die Schweiz müsste sich in wesentlichen und in mehr Bereichen an Entscheide der EU binden; wir könnten zwar mitentscheiden, wir könnten aber auch überstimmt werden. Der Anwendungsbereich des EU-Rechtes wäre erheblich breiter als bei den vorliegenden Abkommen. Das entspricht aber nicht meinem Verständnis einer eigenständigen, föderalistischen und direktdemokratischen Schweiz.
+Gerade weil ich keinen EU-Beitritt will, bin ich für einen funktionierenden Weg des bilateralen Vertrages. Die Schweiz, ihre Unternehmen und somit auch deren Mitarbeitende profitieren enorm von diesem privilegierten Zugang zum europäischen Binnenmarkt. Dieser ermöglicht eine enge wirtschaftliche Zusammenarbeit, ohne dass die Schweiz Mitglied der EU wird. Er schafft Rechtssicherheit für Schweizer Unternehmen, sichert ihre Teilnahme an Teilen des europäischen Binnenmarktes und trägt damit zum Wohlstand unseres Landes bei. Zugleich bewahrt die Schweiz ihre politische Eigenständigkeit. Wir arbeiten dort zusammen, wo es unseren Interessen dient, ohne sämtliche Politikbereiche einer gemeinsamen Ordnung zu unterstellen. Das ist kein theoretischer Mittelweg, es ist der Schweizer Weg, der sich seit mehr als 25 Jahren bewährt hat.
+Wir sollten uns aber nichts vormachen. Der heutige Zustand bleibt nicht einfach bestehen, wenn wir dieses Paket ablehnen. Ohne geregelte Aktualisierung verlieren bestehende Abkommen schrittweise an Wirkung. Unternehmen verlieren Rechtssicherheit und den gleichberechtigten Marktzugang zu ihrer Konkurrenz. Forschung und Versorgungssicherheit werden verletzlicher. Ich erlebe das, ganz offen gesagt, in der Medizintechnik unmittelbar. Fehlt die Aktualisierung des Abkommens über die gegenseitige Anerkennung, entstehen doppelte Anforderungen, zusätzliche Kosten und somit auch Wettbewerbsnachteile.
+Das betrifft keine abstrakte Exportstatistik, es betrifft Schweizer Unternehmen, es betrifft Arbeitsplätze und letztlich auch die Versorgung der Patientinnen und Patienten in unserem Land. Der Unterschied zwischen heute und künftig ist konkret: Heute fehlt uns ein verlässliches Verfahren, um die betroffenen Marktzugangsabkommen an neue Regeln anzupassen; künftig gibt es ein solches Verfahren, die Schweiz kann sich früher einbringen und entscheidet über jede Rechtsübernahme selbst.
+Für die exportorientierten Branchen schafft das die Voraussetzung, das Abkommen über die gegenseitige Anerkennung von Konformitätsbewertungen (MRA) auch in Zukunft zu aktualisieren. Wir müssen uns bewusst sein, dass 75 Prozent aller exportierten Produkte reguliert sind und von einem Abkommen profitieren. Rund 60 Prozent unserer Exporte gehen in die EU, also zu unseren Nachbarn, und deshalb bin ich überzeugt: Zerstören wir nicht, was uns in den vergangenen fünfundzwanzig Jahren Wohlstand gebracht hat.
+Wer dieses Paket ablehnt, entscheidet sich deshalb nicht einfach für den heutigen Zustand. Er nimmt dessen schrittweise Verschlechterung in Kauf.
+Selbstverständlich muss die Schweiz die Umsetzung selbstbewusst angehen. Hier muss das Parlament den Bundesrat und vor allem die Verwaltung in die Pflicht nehmen. Genau das bedingt aber ein Eintreten auf die Vorlage und eine sorgfältige Beratung. Zwei zentrale Fragen lauten: Wie entsteht künftig unser Recht, und wer entscheidet darüber? Heute entwickelt die Europäische Union ihre Regeln weiter. Diese sind für die Schweizer Wirtschaft oft relevant, unabhängig davon, ob wir sie vertraglich übernehmen. Schweizer Unternehmen müssen europäische Anforderungen erfüllen, wenn sie ihre Produkte im europäischen Markt verkaufen wollen.
+Die Schweiz vollzieht solche Entwicklungen teilweise autonom. Wir reagieren heute häufig spät, unsere Mitwirkung ist begrenzt. Die heutigen Mitwirkungsrechte des Parlamentes sind für diese neuen Verfahren zu wenig präzise, und schon gar nicht so, dass sie etwas rechtzeitig bewirken könnten. Künftig soll die Schweiz bereits bei der Erarbeitung jener EU-Rechtsakte mitwirken können, die später für die Bilateralen Abkommen relevant werden können. Unsere Fachleute erhalten Informationen früher, sie können schweizerisches Fachwissen und schweizerische Interessen einbringen, bevor die Entscheide gefallen sind. Wir erhalten dabei kein Stimmrecht in der Europäischen Union, weil wir heute und in Zukunft nicht Mitglied werden wollen. Gegenüber heute erhalten wir aber früher Informationen und auch bessere Einflussmöglichkeiten.
+Gleichzeitig will die Aussenpolitische Kommission die Rolle unseres Parlamentes stärken; für mich ein absolut zwingender Schritt. Der Bundesrat soll die zukünftigen Kommissionen bei der Erarbeitung neuer Rechtsakte vor einer Übernahme und auch in einem Streitbeilegungsverfahren frühzeitig und umfassend einbeziehen. Zusätzlich soll das Parlament einen eigenen Sensor in Brüssel erhalten. Als Dienststelle der Parlamentsdienste soll die Schweizer Mission dort angesiedelt werden und unserem Parlament unterstellt bleiben. 
+Diese Stärkung der parlamentarischen Kontrolle ist für mich absolut zentral. Denn, ich sage es offen und direkt, ich will nicht, dass die Bundesverwaltung de facto immer mehr Kompetenzen und Einflussmöglichkeiten bekommt. Hier muss das Parlament den Bundesrat in die Pflicht nehmen und der Verwaltung klare Grenzen setzen. Unsere Verwaltung muss im Zweifel immer die Schweizer Interessen vertreten, vorauseilender Gehorsam gegenüber der EU muss konsequent unterbunden werden. 
+Aussenpolitisch zentral ist, dass es keine automatische Rechtsübernahme gibt; nicht jeder neue EU-Rechtsakt muss von der Schweiz übernommen werden. Wir arbeiten bloss in einem ganz kleinen Teil bilateral zusammen. Lehnt die Schweiz eine Übernahme ab, kann sie nicht dazu verpflichtet werden. Nach einem Streitbeilegungsverfahren können Ausgleichsmassnahmen folgen. Wenn wir eine neue Produktnorm nicht übernehmen wollen, dann dürfen wir diese Produkte nicht mehr auf dem EU-Binnenmarkt verkaufen. Dieser Ausgleich ist nachvollziehbar und aus meiner Sicht auch fair. Ein Ausgleich muss sich auf den Bereich des Binnenmarktabkommens beschränken und verhältnismässig sein. Die Schweiz kann die Verhältnismässigkeit durch das Schiedsgericht prüfen lassen. Unter bestimmten Voraussetzungen können die Massnahmen bis zu dieser Prüfung aufgeschoben werden. Auch das gehört zur ehrlichen Darstellung dieses Pakets. Souveränität bedeutet nicht, dass ein Staat keine Verpflichtungen eingeht. Souveränität bedeutet, dass er selbst entscheidet, welche Verpflichtungen seinen Interessen dienen, und auch die Folgen seiner Entscheide trägt. 
+Besonders genau habe ich die Weiterentwicklung der Personenfreizügigkeit geprüft. Ich habe mich in den Beratungen für klare Verschärfungen eingesetzt. Die Sorgen der Bevölkerung sind real. Eine Schutzklausel darf deshalb kein politisches Beruhigungsmittel sein. Sie muss anwendbar sein, nachvollziehbare Kriterien enthalten und wirksame Massnahmen ermöglichen, denn Zuwanderung hat Folgen für den Wohnungsmarkt, die Verkehrsinfrastruktur, die Schulen, das Gesundheitswesen und die Sozialwerke. Wer diese Auswirkungen ausblendet, schwächt die Akzeptanz des bilateralen Weges. 
+Die Sorgen wegen der Zuwanderung und ihrer Folgen gehen über die Personenfreizügigkeit hinaus. Das Dubliner Abkommen bringt der Schweiz in der Asylpolitik zweifellos grossen Nutzen. Ohne dieses Abkommen würde die Schweiz geradezu zum Asylmagneten Europas. Gerade in der Asylpolitik muss der Bundesrat auch darüber hinaus den Handlungsspielraum nutzen, den die Schweiz hat. Verschiedene EU-Staaten sind uns in der Asylpolitik deutlich voraus; Asylmigration und Familiennachzug haben daran zwar einen geringeren Anteil als die Personenfreizügigkeit, bei vielen realen Problemen sind sie aber die Ursache. Ich denke da an Sozialkosten für den Bund, an die Kantone und die Gemeinden, Probleme in unseren Schulen oder die steigende Kriminalität. Ich bin überzeugt, dass eine bessere Asylpolitik der Schlüssel für die Akzeptanz der dringend notwendigen Personenfreizügigkeit ist.
+Nationalrat und Ständerat, das wissen Sie, haben zahlreiche Vorstösse überwiesen. Der Bundesrat muss diese nun auch gezielt umsetzen. Hier müssen wir als Parlament die Zügel in der Hand halten und den Bundesrat in die Pflicht nehmen. Meine Position ist also klar: Ich sage Ja zu den Bilateralen III, fordere aber auch eine selbstbewusste und unbürokratische Umsetzung, wobei das Parlament dem Bundesrat und insbesondere der Verwaltung genau auf die Finger schauen muss.
+Nun noch ein Wort zu den Folgen des Referendums. Ja, Luzern und Schwyz sind sich bei der Referendumsfrage nicht einig, und das kommt unter guten Nachbarn halt auch vor. Als Standesvertreter gewichte ich die Haltung meines Kantons hoch. Die Luzerner Regierung spricht sich für das fakultative Referendum aus. Nach sorgfältiger Prüfung, auch in Zusammenarbeit mit meinem Kanton, komme ich zum gleichen Schluss.
+Die Bundesverfassung besagt klar, in welchen Fällen ein Staatsvertrag zwingend Volk und Ständen unterbreitet werden muss: beim Beitritt zu einer Organisation für kollektive Sicherheit oder zu einer supranationalen Gemeinschaft. Die Bilateralen III sind weder das eine noch das andere. Nun wird die sogenannte Sui-generis-Praxis geltend gemacht. Danach können besonders bedeutende Staatsverträge dem obligatorischen Referendum unterstellt werden, obwohl die Bundesverfassung dies nicht ausdrücklich vorsieht. Ich anerkenne, dass diese Praxis in einzelnen aussergewöhnlichen Fällen angewandt und politisch akzeptiert wurde. Als Beispiele werden die Freihandelsabkommen von 1972 sowie der EWR-Vertrag von 1992 genannt. Diese Fälle sind jedoch nicht mit der heutigen Vorlage vergleichbar; meine Vorrednerin hat das bereits erwähnt.
+Das obligatorische Referendum ist ein tragender Pfeiler unseres Bundesstaates, und gerade deshalb darf es nicht beliebig eingesetzt werden. Die Ausnahme der Sui-generis-Praxis überzeugt mich bei diesem Paket nicht. Sie darf nicht allein deshalb angewandt werden, weil die politische Bedeutung der Vorlage gross ist. Ein obligatorisches Referendum ohne klare verfassungsrechtliche Grundlage würde zudem einen Präzedenzfall schaffen, dessen Folgen für künftige Staatsverträge schwer abzuschätzen wären.
+Ich bin für eine starke demokratische Kontrolle mit einer konsequenten parlamentarischen Mitwirkung sowie für eine Schutzklausel, die wirklich greift, und ich bin dafür, dass unsere verfassungsmässigen Spielregeln gerade dann respektiert werden, wenn der politische Druck gross ist. Ich bitte Sie, auf die Vorlage einzutreten. Eintreten bedeutet keinen Blankoscheck. Es ist eine Voraussetzung dafür, dass dieses Abkommen im Interesse der Schweiz umgesetzt wird, und hier sind wir als Parlament gefordert.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germann Hannes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja, wenn man nun meinen Vorrednern zugehört hat, hatte man das Gefühl, alles wäre in bester Ordnung, die EU sei eine Traumpartnerin und die Verträge würden uns sogar stärken. Ich versuche nun, eine Position darzulegen, die vielleicht auch etwas zum Nachdenken anregen soll, möchte es aber nicht verpassen, zunächst etwas Positives zu sagen. Der Bundesrat und vor allem die Verhandlungsdelegation haben wohl gemacht, was möglich war, und das verdient Respekt - auch wenn ich anderer Meinung bin. Sehen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja, wenn man nun meinen Vorrednern zugehört hat, hatte man das Gefühl, alles wäre in bester Ordnung, die EU sei eine Traumpartnerin und die Verträge würden uns sogar stärken. Ich versuche nun, eine Position darzulegen, die vielleicht auch etwas zum Nachdenken anregen soll, möchte es aber nicht verpassen, zunächst etwas Positives zu sagen. Der Bundesrat und vor allem die Verhandlungsdelegation haben wohl gemacht, was möglich war, und das verdient Respekt - auch wenn ich anderer Meinung bin. Sehen Sie, wenn der Prototyp eines Flugzeugs eine Fehlkonstruktion ist, wird daraus wohl niemals ein taugliches Flugobjekt. Der Elefant im Raum ist zweifellos die sogenannte dynamische Rechtsübernahme: So wird das Konstrukt, das ursprünglich "Institutionelles Abkommen" (Insta) geheissen hat, inzwischen genannt. Es umfasst die Auslagerung von wichtigen Teilen der Schweizer Gesetzgebung an die Europäische Union und deren Institutionen, die ja reichlich mit Personal und Bürokratie dotiert sind; manchmal mit der Möglichkeit, noch ein wenig Einfluss zu nehmen, manchmal praktisch ohne.
+Ich erläutere dies am Beispiel des Freizügigkeitsabkommens, weil damit sogar unsere Bundesverfassung ein Stück weit ad absurdum geführt werden soll. Die im Common Understanding vorgesehene Anpassung des Freizügigkeitsabkommens ist in noch grösserem Mass als die heute geltende Fassung unvereinbar mit Artikel 121a der Bundesverfassung. Die inhaltliche Diskrepanz würde durch den vorgesehenen Ausbau der Freizügigkeit und vor allem durch die dynamische Rechtsübernahme noch deutlich verschärft. Bei der einstmaligen Erweiterung des Freizügigkeitsabkommens auf Kroatien gingen Bundesrat und Parlament zunächst nämlich davon aus, dass das Kroatienprotokoll gegen Artikel 121a der Bundesverfassung verstösst. Dennoch hat es das Parlament letztlich durch die Hintertür dann doch noch genehmigt. Wenn wir mit dem Volk ehrlich sein wollen - und das sollten wir -, spricht das alles aber für eine Revision von Artikel 121a.
+Denn mit der weitgehenden oder dereinst wohl gänzlichen Übernahme der Unionsbürgerrichtlinie (UBRL) wird der Verstoss gegen Artikel 121a der Bundesverfassung, vor allem gegen Absatz 2 dieses Artikels, noch offensichtlicher. Mit Artikel 121a BV legte das Volk einst fest, dass die Zuwanderung in die Schweiz über jährliche Höchstzahlen zu begrenzen sei und dass dies über Kontingente zu geschehen habe.
+Künftig werden die Möglichkeiten für den Erwerb eines Aufenthaltsrechts in der Schweiz sogar noch ausgeweitet, statt gemäss Bundesverfassung gezielt gesteuert zu werden. Daueraufenthalt erhält auch, wer fünf Jahre als Teilzeiterwerbender mit teilweisem Sozialhilfebezug in der Schweiz gelebt hat. Faktisch reichen dreieinhalb Jahre Erwerbsarbeit, wenn der Erwerbstätigenstatus beibehalten wird. Daueraufenthaltsrecht gilt auch für Familienangehörige, auch wenn diese nicht erwerbstätig waren. Wurde das Daueraufenthaltsrecht einmal erworben, kann es nicht mehr aufgehoben werden, auch wenn in der Folge völlige Sozialhilfeabhängigkeit eintritt. Daueraufenthaltsberechtigte haben auch Anspruch auf Familiennachzug, auch bei neuer Familiengründung.
+Insgesamt muss darum festgehalten werden, dass die UBRL gegenüber dem Freizügigkeitsabkommen verschiedene neue Aufenthaltsansprüche einführt. Gemäss Botschaft des Bundesrates hätten im Jahr 2021 etwa 690 000 Personen Anspruch auf Daueraufenthalt gehabt, also deutlich über eine halbe Million Menschen. Pro Jahr kämen zwischen 50 000 und 70 000 neue Aufenthaltsansprüche hinzu.
+Nun kann übrigens auch der Gemischte Ausschuss über die Übernahme einer Änderung der UBRL beschliessen. Sie hören richtig: kein Parlament, nicht wir - nein, der Gemischte Ausschuss. Gibt es die Möglichkeit, dagegen das Referendum zu ergreifen? Nein! Die Grundlage für das Gesetzesreferendum findet sich in Artikel 141 Absatz 1 BV. Dieser Artikel kommt aber nicht zum Tragen, denn die geänderte UBRL gilt für die Schweiz unmittelbar, also ohne dass das Schweizer Gesetz geändert wird. Ich verweise diesbezüglich auf Artikel 5 Absatz 2 des Institutionellen Protokolls zum geplanten Freizügigkeitsabkommen.
+Das Staatsvertragsreferendum wäre möglich für eine Änderung des Hauptabkommens, nicht aber gegen die Beschlüsse des Gemischten Ausschusses. Mit anderen Worten: Der Beschluss des Gemischten Ausschusses, die geänderte Unionsbürgerrichtlinie zu übernehmen, unterliegt nicht dem Referendum. Ich frage Sie: Wo liegt hier die künftige Rolle des Gesetzgebers, des Parlamentes, von uns, die wir hier im Auftrag von Volk und Ständen seit Jahr und Tag Verantwortung übernehmen? 
+Wir möchten hier drin nach bestem Wissen und Gewissen entscheiden, aber zu so etwas Fundamentalem haben wir möglicherweise nicht einmal etwas zu sagen. Wir entscheiden inskünftig also nicht mehr hier im Ratssaal, sondern verfolgen den Gesetzgebungsprozess in Teilen bestenfalls von der Zuschauertribüne aus. Damit sei nichts gegen unsere Gäste gesagt, ich freue mich über ihr Interesse; aber eigentlich ist das Parlament da, um das Volk und den Volkswillen zu vertreten. Ob wir dann auf der Zuschauertribüne hier in Bern oder im Elfenbeinturm zu Brüssel sind, spielt auch keine grosse Rolle mehr.
+Darum frage ich Sie: Welches souveräne Land delegiert wichtige Teile seiner künftigen Gesetzgebung an fremde Vertragspartner, nur um auf den EU-Markt zu dürfen? Das dürfen China und die USA sowie auch Kanada übrigens auch, und diese Länder exportieren teilweise grössere Mengen als die Schweiz; die können das also, sie müssen aber nicht einen Knebelvertrag unterzeichnen, sondern ein Handelsabkommen genügt völlig - und wir übernehmen hier eben einen ganzen Gesetzgebungsprozess. Das führt doch einfach zu weit. Welches souveräne Land delegiert wichtige Teile seiner Gesetzgebung an fremde Vertragspartner und zahlt dafür auch noch Milliarden? Das wäre etwa dasselbe, wie wenn ich mit einem Versicherer einen Vertrag abschliessen wollte und dieser Versicherer sich dann noch das Recht ausbedingen würde - analog zur dynamischen Rechtsübernahme -, den von mir unterzeichneten Vertrag in Zukunft nach eigenem Gutdünken abzuändern und auszulegen. Keiner und keine von uns würde jemals ein derartiges Vertragskonstrukt unterzeichnen, und schon gar nicht mit einer Gegenpartei, die vor allem durch bürokratische Monstergesetze, immer grössere demokratische Defizite und immer geringere wirtschaftliche Leistungsfähigkeit auffällt. 
+Ich muss hier leider etwas Gegensteuer zum Hohelied geben, das vorhin apropos Bedeutung gesungen worden ist. Bezüglich bürokratischer Monster verweise ich nur auf die Datenschutzverordnung; den Digital Services Act; das Lieferkettengesetz, ein Monstrum, bei dem man jetzt wieder zurückbuchstabieren muss; die Entwaldungsverordnung; den Green Deal, der die ganze europäische Produktionswirtschaft aus diesem Kontinent vertreibt. Ich wäre hier also nicht so optimistisch, wie Sie das sind, geschätzte Kolleginnen und Kollegen.
+Mit einem Ja zu den monströsen Vertragswerken würde die Schweiz nicht nur in finanzieller und wirtschaftlicher Hinsicht mehr geschwächt als gestärkt, sondern vor allem auch in direkt-demokratischer Hinsicht. Dort würde sogar ein irreversibler Schaden entstehen. Weil wir das nicht wollen, plädiert die Minderheit für Nichteintreten. Ich lade Sie dazu ein, der Minderheit zu folgen und ebenfalls nicht einzutreten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Ei Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Herr Präsident, Herr Bundespräsident, Herr Bundesvizepräsident, Herr Bundesrat, liebe Kolleginnen und Kollegen: "Ei Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." 
+Komm, lass uns gehen: Nach diesem Prinzip soll dieses Paket behandelt werden. Schnell, pragmatisch. So einfach können und dürfen wir an diesen Verträgen nicht vorbeigehen. Erstens sprechen wir </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Ei Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Herr Präsident, Herr Bundespräsident, Herr Bundesvizepräsident, Herr Bundesrat, liebe Kolleginnen und Kollegen: "Ei Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." 
+Komm, lass uns gehen: Nach diesem Prinzip soll dieses Paket behandelt werden. Schnell, pragmatisch. So einfach können und dürfen wir an diesen Verträgen nicht vorbeigehen. Erstens sprechen wir hier von einer wahren Gesetzeslawine. Ein gewaltiges Paket wird über Nacht auf einen Schlag in die Schweizer Rechtsordnung übernommen - 94 EU-Rechtsakte, Tausende EU-Verordnungen, Tausende von Seiten. Zum Vergleich: Ein ordentlicher schweizerischer Gesetzgebungsprozess dauert im Schnitt vier Jahre. Vier Jahre für Sorgfalt, Abwägung, demokratische Verankerung, Debatten, für das Hin und Her zwischen den Räten, bis hin zu Einigungskonferenzen. 
+Schauen wir doch einmal die Verträge von unten nach oben an. Gehen wir einmal in einen einzelnen Vertrag. Nehmen wir die Personenfreizügigkeit. Wäre nicht bereits im Abkommen über die Personenfreizügigkeit eine rote Linie überschritten? Wir schaffen ein dauerhaftes Aufenthaltsrecht nach fünf Jahren, das weiter geht als die Aufenthaltsbewilligung C, wir gewähren erweiterten Familiennachzug, und wir verzichten auf höhere Studiengebühren für EU-Studierende.
+Dem Vernehmen nach war das der Preis für die Schutzklausel. Mag die Schutzklausel diesen Preis aufwägen? Das Personenfreizügigkeitsabkommen ist ein Frontalzusammenstoss mit Artikel 121a unserer Bundesverfassung; darüber werden wir ja noch reden. Es ist ein Frontalzusammenstoss mit dem klaren Auftrag zur eigenständigen Steuerung der Zuwanderung. Also allein das Abkommen über die Personenfreizügigkeit, die Erweiterung, würden wir in dieser Form wohl nicht unterschreiben.
+Zweitens, mit den Protokollen, und das haben wir jetzt mehrfach ausgeführt gehört, kommen die institutionellen Elemente über die Verträge hinzu. Das ist ein fundamentaler Paradigmenwechsel. Die bilateralen Verträge I und II basieren auf dem klassischen Völkerrecht: Gleichberechtigung der Parteien, Änderungen nur im gegenseitigen Einvernehmen, Auslegung nach Treu und Glauben. Das, was hier heute vorliegt, bricht mit diesem Fundament. Bilaterale III - das ist eine Verharmlosung. Was hier heute vorliegt, ist ein massiver institutioneller Integrationsschritt. Entscheidend ist nicht nur der heutige Vertragsinhalt, also diese Blackbox, wie ich sie am Anfang erwähnt habe. Entscheidend ist der Mechanismus für das Recht von morgen. Mit der dynamischen Rechtsübernahme verpflichten wir uns auf Vorrat, künftige EU-Rechtsentwicklungen, meist erlassen von der EU-Kommission, die wir heute noch gar nicht kennen, zu übernehmen.
+Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und so oppositionslos in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Making.
+Drittens bedeuten die Verträge eine unannehmbare Schwächung der direkten Demokratie und des Föderalismus. Die Rechtsetzung verschiebt sich bei den betroffenen Abkommen räumlich und institutionell. Die EU und die Schweiz haben grundverschiedene Rechtssysteme: Die EU erlässt neues Recht von oben nach unten, bei uns funktioniert es gerade umgekehrt, von unten nach oben - ausgehend vom Souverän, dem Volk. Diese Systeme lassen sich nicht verbinden.
+Entscheidend ist, darüber spricht fast niemand, dass wir selber keine Gesetzgebung innerhalb der betroffenen Abkommen mehr anstossen können; wir geben die Input-Funktion für die entsprechende Gesetzgebung in die Hände der EU-Kommission.
+Zudem, das führte Herr Ständerat Schmid gerade aus, erfährt die Exekutive einen massiven Machtzuwachs. Bundesrat und Verwaltung bestimmen die Positionen, führen das Mandat und wählen die Experten aus, die uns in Brüssel vertreten sollen. Die Schweiz ist von oben nach unten organisierter Expertenstaat: "Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut! Komm, lass uns gehen."
+Viertens können die innerstaatlichen Reformen, die wir noch diskutieren werden, das Grundproblem nicht heilen. Massnahmen zur Stärkung des Parlamentes und der Kantone und Veränderungen im innerstaatlichen Recht ändern nichts an der harten Realität:
+Die Schweiz gibt die inhaltliche Kontrolle über ihr eigenes Recht ab. Wenn das Volk oder das Parlament neues Recht ablehnt, darf die EU uns mit sachfremden, sektionsübergreifenden Ausgleichsmassnahmen - ich sage das Wort jetzt halt - abstrafen. Das und die mangelnde Konkretisierung dieser Sanktionen ist doch hochproblematisch: Wenn die Folgen einer Ablehnung nicht präzise definiert sind, ist doch eine freie, informierte Willensbildung der Stimmbürgerinnen nicht mehr möglich. Dies verletzt Artikel 34 der Bundesverfassung; die freie Willensbildung und die unverfälschte Stimmabgabe sind in Artikel 34 Absatz 2 der Bundesverfassung garantiert. Es ist eines souveränen Staates unwürdig, wenn ein externer Akteur ihn vertraglich bestrafen darf. 
+Auslöser für die Verhandlungen war, gemäss den Medienmitteilungen des Bundesrates in den Anfängen, ein Stromabkommen. Für diesen Gegenwert hat die Schweiz weitreichende Konzessionen gemacht: die dynamische Rechtsübernahme und die innerstaatliche Umsetzung des EU-Beihilferechts. Wie sieht es heute aus? Nun soll ausgerechnet der Strombereich ausgeklammert und separat vorgelegt werden, weil er politisch hoch umstritten ist - das kommt nicht vom Bundesrat, das ist eine Diskussion in den Räten. Damit gerät doch die gesamte Logik des Pakets ins Wanken. Die weitreichenden Konzessionen der Schweiz bleiben bestehen, während der ursprüngliche Auslöser und zentrale Gegenwert, wegen dem man überhaupt verhandelt hat, entfällt. Die Schweiz soll also den vollen Preis für das Paket bezahlen, und das wirft die Frage auf: Wie kann man an den Verpflichtungen festhalten, wenn der Gegenwert, der die Verhandlungen ursprünglich ausgelöst hat, entfällt?
+Manchmal frage ich mich, wann genau wir in der Schweiz aufgehört haben, stolz auf unsere Freiheit, auf unser einzigartiges politisches System zu sein. Ich sehe die Versprechen eines wirtschaftlichen Nutzens. Doch die Realität zeigt, dass die tatsächliche Grössenordnung dieses Nutzens sehr umstritten ist und gar als gering beurteilt wird. Wenn wir diesen vermeintlichen Nutzen gegen den realen Verlust der Souveränität aufwiegen, ist das Ergebnis eindeutig: Der staatspolitische Preis ist zu hoch. Wenn wir auf den Zustand der EU schauen, sehen wir eine zunehmende Zentralisierung, wir sehen, dass das Subsidiaritätsprinzip ignoriert wird, und wir sehen eine enorme Machtkonzentration bei der EU-Kommission. Die wirtschaftlichen und politischen Schwächen grosser Mitgliedstaaten wie Deutschland oder Frankreich sind unübersehbar. Es gibt keinen zwingenden Grund, warum wir uns enger an dieses System binden sollten. Wer behauptet, dieses Paket sei alternativlos, verkennt die Realität und die Stärken unseres Landes. Wir sind ein finanziell gesunder, wir sind ein erfolgreicher Stabilitätsanker im Herzen Europas. Wir halten unser staatliches Haus in Ordnung. Wir haben für Milliarden von Franken eine Jahrhundertinfrastruktur gebaut, die Neat, den Alpentransit, und dies im vitalen Interesse des gesamten Kontinents.
+Dieses starke Schweizer Fundament beweist, dass die EU ein ebenso grosses Eigeninteresse an geordneten Beziehungen hat wie wir. Lassen wir uns wirklich von der Drohkulisse einschüchtern, wonach die Bilateralen I und die Bilateralen II bei einem Nein sofort beendet würden? Es gibt immer Alternativen. Wir können bestehende Abkommen punktuell und klassisch völkerrechtlich modernisieren. Die EU beweist zudem, wie beim Ceta-Abkommen oder den aktuellen Plänen für eine assoziierte Mitgliedschaft Kanadas, dass massgeschneiderte Verträge mit Drittstaaten möglich sind, ohne dass diese auf ihre Souveränität verzichten oder eine automatische Rechtsübernahme akzeptieren müssten.
+"Ei, Vater, sieh den Hut dort auf der Stange." "Was kümmert uns der Hut! Komm, lass uns gehen." Ja, gehen wir selbstbewusst an diesem Hut vorbei, treten wir nicht ein.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cassis Ignazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innanzitutto vi ringrazio per questo lungo, interessante e appassionato dibattito che ha permesso di mettere a confronto le opinioni degli uni e degli altri e che lancia formalmente anche il dibattito parlamentare sul nostro futuro rapporto con l'Unione europea. Il dibattito parlamentare è assolutamente necessario dopo tanti anni di discussione a livello più tecnico e più esecutivo. Quindi, il Consiglio federale si rallegra di questa fase parlamentare del dibattito e intende dare il suo contribu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innanzitutto vi ringrazio per questo lungo, interessante e appassionato dibattito che ha permesso di mettere a confronto le opinioni degli uni e degli altri e che lancia formalmente anche il dibattito parlamentare sul nostro futuro rapporto con l'Unione europea. Il dibattito parlamentare è assolutamente necessario dopo tanti anni di discussione a livello più tecnico e più esecutivo. Quindi, il Consiglio federale si rallegra di questa fase parlamentare del dibattito e intende dare il suo contributo con la presenza, direi abbastanza straordinaria, di tre membri dell'esecutivo.
+Worum geht es heute im Kern? Es geht um die Frage, wie die Schweiz ihre Beziehungen zu ihrer wichtigsten Partnerin und direkten Nachbarin für die kommenden Jahrzehnte gestalten will. Es geht dabei um zentrale Aufgaben unseres Staates - um Sicherheit, Unabhängigkeit und Wohlfahrt unseres Landes und letztlich um die Frage, was es braucht, damit der Schweizer Weg in Europa auch in Zukunft erfolgreich bleibt. Es geht also um unseren verfassungsmässigen Auftrag nach Artikel 2 der Bundesverfassung. 
+Das vorliegende Paket zur Stabilisierung und Weiterentwicklung der Beziehungen zur EU ist das Ergebnis eines langen und intensiven Prozesses. Es wurde in enger Zusammenarbeit mit den Kantonen, der Wirtschaft, den Sozialpartnern, denen ich hier im Namen des Bundesrates danke, und im Dialog mit den betroffenen Interessengruppen erarbeitet. Das Paket ist also kein theoretisches Modell und kein europapolitisches Wunschprojekt. Es ist die Fortsetzung des bekannten und bewährten bilateralen Wegs der Schweiz. Das heisst, es kombiniert weitgehende Marktbeteiligung und Zusammenarbeit in spezifischen Interessenbereichen mit grösstmöglicher politischer Eigenständigkeit. Dass es um diese zwei Pole geht, haben wir heute gut gespürt - je nach Abwägung geht es auf die eine oder auf die andere Seite, oder man wählt das Klügste, die Mischung von beidem, indem man diese zwei Elemente, Marktbeteiligung und politische Eigenständigkeit, miteinander kombiniert. Das Paket ist also eine konkret ausgehandelte, massgeschneiderte Lösung für konkrete Schweizer Interessen. Das Paket ist Realpolitik.
+Nous examinons ce paquet à un moment où l'environnement international connaît de profonds bouleversements. Le monde, vous l'avez dit vous-mêmes, se trouve à un tournant. Les guerres, la formation de blocs commerciaux et les rivalités entre grandes puissances remettent en question nombre de nos certitudes. De plus en plus souvent, on l'a bien vu, ce n'est pas le droit qui s'impose, mais la loi du plus fort. L'ordre international issu de l'après-guerre vacille, des accords commerciaux sont remis en cause, des droits de douane sont augmentés de manière arbitraire et des règles internationales ignorées. L'Europe doit trouver sa voie dans ce nouveau monde et la Suisse, qui fait partie de ce continent, elle aussi. Nous vivons dans une période d'incertitude. Dans une telle situation, attendre et détourner le regard serait, aux yeux du Conseil fédéral, imprudent et irresponsable. 
+Nous ne voulons pas attendre d'être contraints de réagir. Nous voulons contribuer activement à façonner de bonnes solutions.
+Sie wissen es selbst: "Gouverner, c'est prévoir."
+Die Schweiz ist keine Insel. Als stark vernetztes Land basiert unsere Stabilität auf guten Beziehungen zu unseren wichtigsten Partnern, sowohl zur EU als auch zu den USA und China sowie zu anderen wichtigen Partnern. Unsere bei Weitem wichtigste Partnerin bleibt aber die EU. Allein der Warenhandel beläuft sich auf rund 300 Milliarden Franken, und zwar jedes Jahr; oder man kann es einfach ausdrücken: Jeder zweite Exportfranken wird im Geschäft mit der EU verdient. Das zeigt: Diese Beziehung ist von zentraler Bedeutung für unser Land; ja, für den Wohlstand unserer Bevölkerung, für unsere Arbeitsplätze und somit auch für unsere Unabhängigkeit und Sicherheit. Es gibt keine Unabhängigkeit ohne Wohlstand.
+Stabile Beziehungen zur EU sind deshalb keine "quantité négligeable". Sie sind auch keine Selbstverständlichkeit. Der Bundesrat erachtet diese Beziehung als eine strategische Notwendigkeit in einer instabilen Welt. Darum müssen wir die notwendigen Schritte unternehmen, um diese Beziehungen zu stabilisieren und weiterzuentwickeln. Genau das will der Bundesrat mit diesem Paket Schweiz-EU erreichen.
+Sie wissen es: Verhandlungen führen immer zu Kompromissen. Das ist kein Mangel. Es ist das Wesen eines internationalen Abkommens. Was haben wir erreicht?
+1. Die Streitbeilegung erfolgt nicht durch den EuGH, sondern durch ein Schiedsgericht.
+2. Das Freihandelsabkommen von 1972 ist nicht Teil des Paketes - das wurde heute nicht gesagt.
+3. Die Schweiz hat in wichtigen Bereichen Ausnahmen von der dynamischen Rechtsübernahme erzielt.
+4. Unser Interesse in den Bereichen Zuwanderung und Lohnschutz sind durch Schutzkonzepte und Begleitmassnahmen abgesichert.
+Zudem stabilisiert das Verhandlungsergebnis unsere Beteiligung an unserem wichtigsten Markt: dem EU-Binnenmarkt. Es schafft Rechtssicherheit und bewahrt gleichzeitig unsere demokratischen Institutionen, die innerschweizerischen Entscheidungsverfahren, den Föderalismus und unsere Eigenständigkeit.
+Sie erinnern sich: Das Verhandlungsmandat wurde Anfang 2024 auch mit Ihnen sowie mit den Kantonen und den Sozialpartnern ausführlich und transparent konsultiert. An verschiedenen Stellen hatten Sie Ergänzungswünsche. Diese wurden berücksichtigt. Mit dem Verhandlungsergebnis wurde das Mandat nicht nur vollständig erfüllt, sondern an verschiedenen Stellen auch übertroffen, z. B. in den Bereichen der Schutzklausel, der Landwirtschaft und des Landverkehrs.
+Haben wir damit genug erreicht? Der Bundesrat ist überzeugt: Ja, das Ergebnis ist gut für die Schweiz. Das Paket, das als Bilaterale III vor Ihnen liegt, ist eine sorgfältig austarierte Gesamtbalance. Bei der inländischen Umsetzung gilt es deshalb, sich an diese Abkommen zu halten, auch im Interesse der Glaubwürdigkeit der Schweiz. Somit sage ich Ihnen auch ganz klar: Die Forderung, beim Lohnschutz an der heutigen Kautionsregelung für ausländische Sendebetriebe festzuhalten, weicht vom ausgehandelten Ergebnis ab.
+Vereinbart wurde eine Kautionspflicht im Wiederholungsfall. Ein Abweichen davon würde die Ratifizierung des Paketes durch die EU infrage stellen. 
+Für das vorliegende Verhandlungsergebnis haben wir in zwei Anläufen fast zwei Jahrzehnte lang verhandelt. Dabei mussten wir uns einer Erkenntnis stellen - das wurde heute bereits mehrmals erwähnt, und ich kann es Ihnen bestätigen: Die EU ist nicht bereit, den bilateralen Weg ohne institutionelle Elemente, ohne eine Regelung der staatlichen Beihilfen und ohne eine Verstetigung des Schweizer Beitrags zur Kohäsion weiterzuführen. 
+Die institutionellen Elemente stossen zu Recht auf reges Interesse, deshalb möchte ich nun darauf eingehen. Im Kern geht es darum, für alle Akteure im Binnenmarkt gleich lange Spiesse zu schaffen, ein "level playing field". Es geht um Rechtssicherheit, fairen Wettbewerb, verlässliche Rahmenbedingungen und um den Schutz vor Willkür und vor sachfremden Strafaktionen. Die institutionellen Elemente liegen also nicht nur im Interesse der EU, sie liegen auch im Interesse der Schweiz. Der Bundesrat hat sich dabei bewusst für einen sektoriellen Ansatz entschieden: Die institutionellen Elemente werden dort verankert, wo sie tatsächlich gebraucht werden. Das ermöglicht eine differenzierte und massgeschneiderte Lösung. Denn die Interessen der Schweiz sind nicht in jedem Bereich dieselben. 
+Nun zu einem weiteren wichtigen Punkt: Was bedeutet diese dynamische Rechtsübernahme, und was bedeutet sie nicht? Hier muss Klarheit herrschen. 
+1. Wir kennen die dynamische Rechtsübernahme bereits aus den 20 Jahren Erfahrung mit Schengen/Dublin. Sie ist nichts Neues. 
+2. Es gibt keine automatische Übernahme von EU-Recht. Dynamisch heisst, eine Übernahme erfolgt nur mit ausdrücklicher Zustimmung der Schweiz. Dabei bleiben die innerstaatlichen Zuständigkeiten und demokratischen Mitwirkungsrechte von Volk, Parlament, Kantonen und Gerichten unverändert - je nach institutioneller Zuständigkeit.
+Bei Gesetzesänderungen haben Sie und das Schweizervolk das letzte Wort - genau wie heute. 3. Die dynamische Rechtsübernahme ist klar eingegrenzt. Man hat heute in der Debatte das Gefühl gehabt, man würde jetzt 100 Prozent des EU-Rechts automatisch übernehmen. Also erstens ist es nicht automatisch, zweitens müssen wir bewusst zustimmen und drittens sind es nicht 100 Prozent. Es betrifft nur vier Abkommen des Stabilisierungsteils und drei Abkommen des Weiterentwicklungsteils. Das ist alles, nicht mehr, nicht weniger.
+Das sind MRA, Abkommen zu handelstechnischen Hemmnissen, zu Land- und Luftverkehr und zur Personenfreizügigkeit - diese drei Abkommen. Neu im Weiterentwicklungsteil wären Abkommen zum Strom, zur Lebensmittelsicherheit und - soweit notwendig - zur Gesundheit. Das ist der Perimeter der dynamischen Rechtsübernahme. Alles andere hat mit dynamischer Rechtsübernahme nichts zu tun. Die Beziehungen, die wir heute mit der EU haben, gehen viel weiter als diese sechs Abkommen.
+Was mir wirklich wichtig ist: Die ausgehandelten Ausnahmen, beispielsweise beim Landesverweis oder beim Taktfahrplan im Landverkehr, sind von der dynamischen Rechtsübernahme ausgenommen. Diese Ausnahmen müssen auch im Rahmen der Streitbeilegung respektiert werden. Da sie ausgenommen sind, gibt es eben keine Streitbeilegung. Es ist unser Recht, diese Ausnahme zu haben.
+Le nombre d'actes juridiques à reprendre est, lui aussi, limité, si on le compare avec ce qu'on a fait jusqu'ici. Dans la partie consacrée à la stabilisation, il s'agit de 19 actes législatifs de l'Union européenne. À titre de comparaison, depuis l'entrée en vigueur des Bilatérales I, nous avons repris largement et volontairement plus de 1000 actes juridiques de l'UE, cela sans possibilité de participer à leur élaboration. Avec le "decision shaping", c'est-à-dire la participation active au processus décisionnel européen, la Suisse dispose désormais du droit de faire valoir son point de vue à un stade précoce, et de contribuer à l'élaboration des décisions.
+Sie haben gesagt, Brüssel warte nicht auf uns. Auch die UNO in New York wartet nicht auf uns, und auch der Mercosur wartet nicht auf die Schweiz, aber wir werden gehört, wenn wir sachlich gut sind. Es wird uns zugehört; wir können Aufmerksamkeit bekommen, wenn wir vorbereitet und kompetent sind - das spüre ich in meiner Arbeit jeden Tag -, auch wenn wir die kleine Schweiz sind. Immerhin sind wir unter den zwanzig grössten Volkswirtschaften der Welt; das gibt uns schon eine gewisse Kraft. Damit wir genau diese Stimme und diese Kraft behalten, müssen wir weiterhin unter den zwanzig grössten Volkswirtschaften der Welt bleiben, und dafür brauchen wir Absatzmärkte und Binnenmarktbeteiligung in der EU. Wir brauchen dies sowohl mit der EU als auch mit den USA und China sowie mit vielen anderen - Kollege Parmelin wird noch dieses Jahr entsprechende Abkommen abschliessen können.
+Avec vous, les cantons, les partenaires sociaux qui se sont aussi exprimés et les autres milieux intéressés, nous pourrons ainsi intervenir dès les premières étapes du processus et faire valoir les intérêts de la Suisse. En cas de différend, la première étape reste la même qu'aujourd'hui : les parties cherchent, ensemble, une solution au sein du comité mixte. Le comité mixte n'est pas quelque chose d'externe, comme cela a été dit. Le comité mixte, ce sont les collaboratrices et collaborateurs de notre administration fédérale, ce sont des gens employés par le Conseil fédéral, que vous avez élu. C'est notre Confédération, ce n'est pas quelqu'un d'autre. Ces personnes prendront des décisions selon leur degré de compétence. Si c'est de la compétence d'un office fédéral, ce sera à ce niveau-là, autrement, elles amèneront la question au département, au Conseil fédéral et au Parlement, si le cas le demande, comme on le fait déjà aujourd'hui, ce qui n'est en rien nouveau. On connaît déjà ce système, qui est en place, qui a fait ses preuves depuis plus de 20 ans. Ce qui est nouveau - et c'est nouveau -, c'est l'intervention du tribunal arbitral paritaire lorsqu'aucune solution ne peut être trouvée. M. Würth l'a rappelé aujourd'hui.
+Quelle est la liste des divergences que nous avons aujourd'hui ? Elle tient sur 20 points, au maximum. (Sonnerie d'un téléphone) Merci pour l'intermezzo ! (Hilarité) Je crois, Mesdames et Messieurs, qu'à 8 heures 10 du soir, on peut se permettre aussi un peu de légèreté pour ne pas dramatiser le tout plus que nécessaire.
+En tout cas, ce que je voulais vous dire, qui est nouveau, c'est le tribunal arbitral paritaire lorsqu'une solution ne peut pas être trouvée. Cela servira à quelques cas par année. On nous a demandé le nombre de cas que cela concernerait : si le rythme continue comme aujourd'hui, ce seront peut-être trois, quatre ou cinq cas par année. Le tribunal arbitral tranche le différend en dernier ressort. La Cour de justice de l'Union européenne - le rapporteur vous l'a rappelé - ne tranche pas le différend. 
+Der Europäische Gerichtshof entscheidet nicht über den Streit. Er wird vom Schiedsgericht nur zur Auslegung von EU-Recht und für eine Stellungnahme angerufen; und auch das nur, wenn das Schiedsgericht dies für relevant und notwendig hält. Der Entscheid über den Streitfall bleibt beim Schiedsgericht.
+Auch bei Ausgleichsmassnahmen gilt es klar zu unterscheiden. Sie sind weder Retorsionen noch Sanktionen. Ihr Ziel ist nicht Bestrafung oder Verhaltensänderung. Sie dienen dazu, die Balance der gegenseitigen Verpflichtungen wiederherzustellen. Sie müssen verhältnismässig sein und sich im Rahmen der Binnenmarktabkommen bewegen. Sie spüren also den Handelscharakter, den Kern dieses Abkommens.
+Wichtig ist: Dank der aufschiebenden Wirkung können keine Ausgleichsmassnahmen angewendet werden, bevor das Schiedsgericht über deren Verhältnismässigkeit entschieden hat. Auch das ist eine wichtige Errungenschaft, die wir in den Verhandlungen erzielt haben.
+Les tribunaux arbitraux comme les mesures de compensation sont des instruments bien établis dans la pratique conventionnelle internationale. Vous l'avez entendu, nous les connaissons déjà : ils figurent dans 34 des 37 accords de libre-échange conclus par la Suisse. On a donc ces mesures compensatoires dans tous ces accords. On les connaît. Nous nous appuyons donc sur les instruments éprouvés du droit international conventionnel.
+Ich komme nun zur Frage des Referendums. Für den Stabilisierungsteil wie auch für den Weiterentwicklungsteil des Pakets beantragt der Bundesrat ein fakultatives Staatsvertragsreferendum. Diesen Entscheid legte der Bundesrat am 30. April 2025 ausführlich dar, und er bekräftigte ihn in seiner Stellungnahme vom 12. August dieses Jahres zur parlamentarischen Initiative "Verfassungsanpassung betreffend die Bilateralen III" der Staatspolitischen Kommission des Ständerates. Er folgt damit dem Wortlaut der geltenden Verfassung sowie der bisherigen Praxis bei den Bilateralen I und II. Das fakultative Referendum ermöglicht zudem die formelle Verknüpfung der Abkommen mit der inländischen Umsetzung, ohne das Referendum über die Umsetzung auszuschliessen. Dies ist aus demokratiepolitischer Sicht die sauberste Lösung. Schliesslich wird damit kein Präzedenzfall für künftige völkerrechtliche Verträge geschaffen.
+Der Bundesrat führte diesen Prozess integrativ und transparent. Er analysierte vertieft, prüfte verschiedene Optionen, er sondierte, konsultierte und verhandelte. Er führte eine Vernehmlassung durch, bei der sich eine deutliche Mehrheit für das Paket aussprach. Der Bundesrat hörte gut zu und nahm basierend auf dem Gehörten entsprechende Anpassungen vor.
+Permettez-moi, pour conclure, de revenir à notre point de départ. Avec ce paquet, il s'agit de stabiliser et de développer nos relations avec notre principal partenaire. Il s'agit d'inscrire dans la durée le modèle économique éprouvé de la Suisse, fondé notamment sur la voie bilatérale. Il s'agit de garantir de la sécurité juridique et de la prévisibilité dans un monde de plus en plus incertain. Ce paquet n'est pas une question d'idéologie. Il s'inscrit dans ce qui caractérise depuis des décennies les relations de la Suisse avec l'Union européenne, c'est-à-dire le pragmatisme, une politique fondée sur nos intérêts et des solutions sur mesure.
+La voie bilatérale a fait ses preuves, mais après deux décennies de négociations, une chose est claire : sans ce paquet, il n'y a pas de voie bilatérale stable pour l'avenir. C'est précisément l'objectif de ce paquet : préserver ce qui a fait ses preuves, développer ce qui doit l'être et ainsi assurer l'avenir de la voie suisse en Europe.
+Le Conseil fédéral vous recommande d'entrer en matière sur ce projet.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas vous prendre beaucoup de temps. Je voulais aborder certaines déclarations inexactes qui ont été faites au sujet du référendum, mais je les garde pour le débat sur le référendum. J'aimerais toutefois revenir sur l'un ou l'autre point.
+Je trouve que la caricature qui est faite ici de l'Union européenne, qui serait une république d'experts, alors que l'Union européenne dispose d'un Parlement, dispose d'un Sénat qui est le Conseil de l'Europe et dispose ensuite d'un gouvernement qui e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ne vais pas vous prendre beaucoup de temps. Je voulais aborder certaines déclarations inexactes qui ont été faites au sujet du référendum, mais je les garde pour le débat sur le référendum. J'aimerais toutefois revenir sur l'un ou l'autre point.
+Je trouve que la caricature qui est faite ici de l'Union européenne, qui serait une république d'experts, alors que l'Union européenne dispose d'un Parlement, dispose d'un Sénat qui est le Conseil de l'Europe et dispose ensuite d'un gouvernement qui est la Commission européenne, avec un trilogue, ne sert à rien dans le débat actuel. Ce n'est pas comme cela que l'on va avancer et créer une dynamique positive dans les relations avec l'Union européenne.
+Le deuxième point que je veux aborder, c'est la reprise dynamique du droit. Je ne vais pas revenir sur ce qui a été dit de manière très pertinente par notre collègue Wasserfallen, mais j'aimerais dire que quand on dit que la reprise dynamique du droit, c'est une reprise automatique, c'est doublement faux. C'est doublement faux. Pourquoi ? Parce qu'il y a le principe du "decision shaping". On nous dit "c'est rien, c'est rien !". Mais moi, j'aimerais vous citer les passages importants - je ne sais pas si vous les avez tous lus, chers collègues - des quatre protocoles d'accord qui portent sur les questions institutionnelles dans les quatre domaines où nous avons accès au marché de l'Union européenne.
+À l'article 4 de ces protocoles, qu'est-il écrit ? Il est écrit que lorsqu'elle aborde une proposition d'acte juridique de l'Union conformément au traité, la Commission européenne "consulte de manière informelle les experts de la Suisse de la même manière qu'elle demande l'avis des experts des États membres de l'Union pour élaborer ses propositions". En d'autres termes, on est mis au même niveau que les États membres. Je pense que c'est une concession de taille.
+Lorsqu'on parle des actes délégués de l'Union européenne, dans ce domaine également, "la Commission veille à ce que la Suisse ait la participation la plus large possible à la préparation des projets desdits actes délégués". Lorsqu'il s'agit d'actes d'exécution, il y a de même une participation de la Suisse qui est prévue. Et puis, quand il y a des comités d'experts, il y a aussi la présence d'experts de la Suisse qui est prévue. Alors on ne peut pas dire que c'est un simple copier-coller.
+Cette procédure-là, cela a été rappelé par certains intervenants qui ont soutenu l'entrée en matière, est celle qui fonctionne très bien dans le cadre des accords Schengen-Dublin. Je vous ai rappelé la problématique de l'exception suisse pour la directive sur les armes et il n'y a pas de raison que ça ne marche pas dans les quatre autres domaines qui sont concernés par ces accords. C'est en tout cas la position de la majorité.
+Je pense que la deuxième chose inexacte, c'est de dire que nous ne pourrons qu'accepter le droit européen sans autre possibilité. C'est un droit à l'élaboration duquel nous participons, mais que nous pouvons aussi refuser. Et ça, c'est clairement indiqué à l'article 6, je le rappelle, de ces quatre protocoles. C'est-à-dire que l'accomplissement d'obligations constitutionnelles par la Suisse, soit la compétence du Conseil fédéral, des cantons, du Parlement et du peuple, sont garantis.
+On a aussi évoqué l'intérêt des citoyennes et des citoyens, notamment notre collègue Schwander. Oui, les cantons, eux, se sont déjà exprimés à plusieurs reprises et ont fait savoir de manière majoritaire qu'ils sont favorables à ce paquet. Il y a des cantons qui y sont opposés, mais la majorité des cantons y est favorable. Les seuls qui ne se sont pas exprimés jusqu'à maintenant, ce sont les citoyennes et les citoyens. Alors, laissons-les s'exprimer par un référendum à la majorité simple. C'est en fait la perspective qui nous est offerte par ces accords, dans le respect de la Constitution et c'est la position de la majorité de la commission.
+Autre élément que je voulais encore indiquer, il a été dit de manière inexacte que dans le cadre du règlement des différends, c'est la Cour de justice de l'Union européenne qui décide en dernier lieu. Ce n'est pas juste. La Cour de justice de l'Union européenne ne fera qu'interpréter des concepts du droit européen, mais elle ne tranchera pas les litiges entre l'UE et la Suisse. Ces litiges seront tranchés par un tribunal arbitral constitué selon les règles générales des tribunaux arbitraux.
+Et puis j'aimerais terminer peut-être avec une remarque à l'adresse de notre collègue Friedli, qui a pris l'exemple du contrat de bail. Alors, je me sens un peu concerné en tant que président des locataires de ce pays. Peut-être que vous ne le savez pas, mais les bailleurs - "die Vermieter" - peuvent imposer aux locataires des modifications du contrat. Ils peuvent le faire par le biais d'un avis spécial et c'est aux locataires d'aller contester la modification devant la commission de conciliation. Et s'ils ne le font pas, la modification unilatérale s'applique. Mais les locataires, contrairement à la Suisse dans les contrats des Bilatérales III, ne peuvent pas aller vers l'administration et dire qu'il faudrait peut-être encore changer un peu la modification. Tandis que nous, comme pays, on peut le faire dans le cadre des accords des Bilatérales III qui nous sont proposés.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Schweiz und die EU teilen die gleichen Werte: die Achtung der Menschenwürde, die Freiheit, die Demokratie, die Gleichheit, die Rechtsstaatlichkeit, die Wahrung der Menschenrechte und den Schutz von Minderheiten. Auch deshalb ist der Bundesrat von diesen Abkommen überzeugt. Wir stärken diese Werte, wenn wir enger mit einem Partner zusammenarbeiten, der diese Werte teilt.
+Meine Kollegen haben das Gesamtbild, die strategische Dimension und die wirtschaftliche Bedeutung des Paketes aufgezeigt. I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Schweiz und die EU teilen die gleichen Werte: die Achtung der Menschenwürde, die Freiheit, die Demokratie, die Gleichheit, die Rechtsstaatlichkeit, die Wahrung der Menschenrechte und den Schutz von Minderheiten. Auch deshalb ist der Bundesrat von diesen Abkommen überzeugt. Wir stärken diese Werte, wenn wir enger mit einem Partner zusammenarbeiten, der diese Werte teilt.
+Meine Kollegen haben das Gesamtbild, die strategische Dimension und die wirtschaftliche Bedeutung des Paketes aufgezeigt. Ich möchte den Blick deshalb auf die Menschen richten, die von guten Beziehungen mit der EU profitieren. Dazu gehören die Arbeitnehmerinnen und Arbeitnehmer, dazu gehört die Bevölkerung in den Grenzregionen und überhaupt alle Schweizerinnen und Schweizer, die in der Schweiz und in der EU leben.
+Die Schweiz liegt mitten in Europa. Bei unseren Beziehungen zu unseren Nachbarländern geht es deshalb nicht nur um Verträge und Märkte, sondern um unseren Alltag. Seit Jahrhunderten schliessen wir mit unseren Nachbarn Verträge. Dabei haben wir stets darauf geachtet, unsere Souveränität und unsere Handlungsfähigkeit zu wahren, und das wollen wir auch in Zukunft. Schon die alte Eidgenossenschaft vor 500 Jahren war stark vernetzt. Dieser Tradition sind wir bis heute treu geblieben; auch die moderne Schweiz ist stark vernetzt und bleibt souverän und eigenständig.
+Der bilaterale Weg mit der Europäischen Union ist ein Beispiel dafür. Wir haben ihn an unsere Bedürfnisse angepasst, sozusagen massgeschneidert. Mit den Bilateralen III, dem Paket zur Stabilisierung und Weiterentwicklung der Beziehungen Schweiz-EU, setzen wir diesen bewährten Weg fort.
+15 Kantone grenzen an die EU, mehr als die Hälfte der Schweizer Bevölkerung lebt in einer Grenzregion. Verkehr, Tourismus, Umweltschutz, Wissensaustausch, Rettung, Strafverfolgung - in all diesen Bereichen arbeiten unsere Kantone täglich mit den Regionen jenseits der Landesgrenze zusammen. Um ihre Herausforderungen meistern zu können, sind die Grenzkantone auf die Partner jenseits der Landesgrenze angewiesen. Die Bilateralen III stabilisieren diese Zusammenarbeit.
+Davon profitieren aber nicht nur die Grenzkantone, davon profitiert die ganze Schweiz. Auch die Zahlen zeigen die Bedeutung dieser Beziehungen: 2024 machte der Warenaustausch nur zwischen der Schweiz und den Grenzregionen - ich spreche hier von Baden-Württemberg, Bayern, Vorarlberg, Grand Est, Lombardei usw. - mehr als ein Viertel des gesamten Schweizer Warenaustausches aus. Das Handelsvolumen zwischen der Schweiz und den Grenzregionen ist also ungefähr gleich gross wie jenes zwischen der Schweiz und den USA, mehr als dreimal so gross wie das zwischen der Schweiz und dem Vereinigten Königreich und viermal grösser als jenes zwischen der Schweiz und Indien. 
+Ich möchte ausserdem zwei Elemente hervorheben, die für die Bevölkerung besonders wichtig sind, die Personenfreizügigkeit und die Schutzklausel. Beginnen wir mit der Personenfreizügigkeit. Wohlstand und Zuwanderung gehen Hand in Hand. Seit der Einführung der Personenfreizügigkeit ist die Wirtschaftsleistung der Schweiz um mehr als 50 Prozent gestiegen. Gleichzeitig veränderte sich unser Arbeitsmarkt. Bereits heute gehen in der Schweiz mehr Menschen in den Ruhestand als neu in den Arbeitsmarkt eintreten. Wir sind deshalb auf Arbeitskräfte aus der EU angewiesen. Ohne die Ärztinnen aus Deutschland müssen Sie lange läuten im Spital; ohne die Servicemitarbeiterinnen aus Polen müssen Sie im Restaurant lange auf den Kaffee warten; ohne die Bauarbeiter aus Portugal stehen viele Baustellen still, mit denen wir die Strassen und den öffentlichen Verkehr ausbauen wollen. Und wenn Ihr Chef die offenen Stellen nicht besetzen kann, dann steigt bei Ihnen der Druck am Arbeitsplatz.
+Aber wichtig dabei ist: Die Zuwanderung aus der EU bleibt auf Erwerbstätigkeit ausgerichtet. Wer in die Schweiz kommen will, braucht eine Arbeitsstelle. Wer ohne Arbeit in die Schweiz ziehen will, muss über ausreichende finanzielle Mittel verfügen. Mit dem Paket ist zudem noch stärker als bisher sichergestellt, dass allfällige Missbräuche, z. B. um ein Aufenthaltsrecht zu erlangen, konsequent bekämpft werden. 
+Es wurde gesagt, der gemischte Ausschuss könne Änderungen der Unionsbürgerrichtlinie beschliessen, gegen die nicht das Referendum ergriffen werden könne. Das möchte ich richtigstellen: Erstens gibt es keine Änderungen des Abkommens ohne Mitwirkung des Parlamentes. Zweitens gilt bei wichtigen Änderungen Informationspflicht. Bei wesentlichen Änderungen gilt Konsultationspflicht. Es gibt also volle Transparenz. Und drittens untersteht ein Beschluss des gemischten Ausschusses von grosser Tragweite der Genehmigung des Parlamentes und gegebenenfalls dem Referendum.
+Das heisst, viertens, dass die Bilateralen III nichts an den Kompetenzen von Bundesrat und Parlament ändern. Auch künftig können die Behörden straffällige Ausländerinnen und Ausländer ausweisen und ausschaffen. Das bewährte Meldeverfahren, mit dem ausländische Firmen ihre Mitarbeitenden für einen Auftrag in der Schweiz anmelden müssen, können wir sogar ausbauen. Wir wissen also auch bei kurzen Arbeitseinsätzen, wer wo in der Schweiz arbeitet und können so die Lohn- und Arbeitsbedingungen kontrollieren.
+Auch beim viel diskutierten Daueraufenthaltsrecht gibt es klare Voraussetzungen. Es steht nur Erwerbstätigen und ihren Familien zu. Bezieht eine Person sechs Monate oder länger Sozialhilfe, verlängert sich die Fünfjahresfrist entsprechend. Zudem gilt ab Inkrafttreten eine einmalige Übergangsfrist von zwei Jahren, und erst danach beginnt die fünfjährige Frist zu laufen. Also kann frühestens sieben Jahre nach Inkrafttreten ein Anspruch geltend gemacht und ein Antrag gestellt werden. Die vorgesehene Lösung gibt Bund und Kantonen genügend Zeit für die nötigen Umstellungen und damit auch die Möglichkeit, Missbräuche zu verhindern und wirksam dagegen vorzugehen.
+Mit dem angepassten Freizügigkeitsabkommen wird der Familiennachzug nur sehr marginal erweitert, nämlich bei Familienangehörigen von eingetragenen Partnerschaften. Was heisst das in Zahlen? Zwischen 2012 und 2021 wurden jährlich zwischen 100 und 160 Aufenthaltsbewilligungen an nachgezogene Personen in eingetragener Partnerschaft erteilt. Daran ändert sich nichts. Das ist schon heute die Realität, die sich auf nationales Recht stützt. Neu könnten die nachgezogenen Partner - eben aus einer eingetragenen Partnerschaft, nur aus dieser - auch ihre Kinder mitnehmen. Gemäss Schätzungen könnten auf diesem Weg jährlich etwa 7 bis 12 Kinder zusätzlich in die Schweiz ziehen.
+Es ist wichtig, die Perspektive auch umzukehren. Was für EU-Bürgerinnen und EU-Bürger in der Schweiz gilt, gilt auch für Schweizerinnen und Schweizer in der EU, und das sind nicht wenige: 460 000 Schweizerinnen und Schweizer leben in der EU; das ist mehr als die Hälfte aller Auslandschweizerinnen und -schweizer.
+Unter ihnen sind viele junge Menschen, die einen Austausch machen oder in der EU studieren. Es geht darum, die Rechte dieser Menschen zu erhalten, damit sie mit den nahezu gleichen Rechten wie die Einheimischen in EU-Mitgliedstaaten leben können - was keine Selbstverständlichkeit ist -, damit sie ohne zusätzliche administrative Hürden Arbeit aufnehmen können und damit sie mit gleich hohen Studiengebühren wie die Europäerinnen und Europäer studieren können. Das dürfen Sie nicht vergessen, wenn Sie über dieses Paket diskutieren.
+Nun zur Schutzklausel: Wir haben die bestehende Schutzklausel konkretisiert und massgeblich verbessert. Künftig kann die Schweiz die Schutzklausel bei schwerwiegenden wirtschaftlichen und sozialen Problemen eigenständig aktivieren. Sie kann eigenständig Massnahmen ergreifen, um die Zuwanderung aus der EU einzuschränken. Heute braucht die Schweiz dafür die Zustimmung der EU. Das ist ein zentraler Erfolg unserer Verhandlungsdelegation. Im Rahmen der Debatte über die Anpassung des Freizügigkeitsabkommens werden Sie Gelegenheit haben, die inländische Umsetzung dieser Schutzklausel eingehend zu prüfen. Ich möchte aber hier schon betonen, dass der Bundesrat die Anliegen aus der Vernehmlassung berücksichtigt hat: einen stärkeren Einbezug der Kantone und der kantonalen Sozialpartner, Anpassungen bei den Indikatoren sowie eine stärkere Berücksichtigung der regionalen und branchenspezifischen Interessen.
+Ich komme zum Schluss. Die Bilateralen III stärken unsere Werte und sind im Interesse der Schweiz. Das Paket ist kein abstraktes europapolitisches Projekt. Es geht um Handfestes, um Wohlstand und Arbeit dank arbeitsmarktorientierter Zuwanderung und des bewährten Meldeverfahrens. Es geht um Bewegungsfreiheit für Junge und für alle Menschen, die in der EU leben oder dort studieren wollen. Es geht um Versorgungssicherheit, die wir durch Zusammenarbeit mit unseren europäischen Nachbarn stärken. Es geht um Forschung und Bildung, die vom grenzüberschreitenden Wissensaustausch profitieren. Es geht um die Zusammenarbeit in den Grenzregionen und um unsere 15 Grenzkantone.
+Der Bundesrat ist überzeugt: Das Paket Schweiz-EU ist im Interesse der Einwohnerinnen und Einwohner unseres Landes. Wir wollen, dass die Schweiz ihre Erfolgsgeschichte fortsetzen kann - mit stabilen Beziehungen zu unseren europäischen Nachbarn, mit Rechtssicherheit und mit dem notwendigen politischen Handlungsspielraum.
+Mit dem Paket Schweiz-EU wahren wir unsere Handlungsfähigkeit und unsere Souveränität mitten in Europa. Damit bleiben wir uns und unserer Geschichte treu. Wir schaffen die Voraussetzungen, um künftige Herausforderungen zu meistern und Chancen im Interesse kommender Generationen zu nutzen. Ich bitte Sie deshalb, bei der Beratung dieser wichtigen Vorlage das grosse Ganze nicht aus den Augen zu verlieren und die langfristigen Interessen der Schweiz im Blick zu haben. 
+Im Namen des Bundesrates empfehle ich Ihnen, auf die Vorlage einzutreten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserfallen Flavia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich wollte eigentlich nicht sprechen, aber ich habe der Debatte sehr aufmerksam zugehört und möchte mir trotzdem erlauben, noch auf ein paar Dinge einzugehen und eine bis zwei Minuten von Ihrer wertvollen Zeit zu stehlen. Ich bin schon erstaunt, wie nonchalant und unpräzise zum Teil mit gewissen Schlagworten operiert wurde; das möchte ich so nicht stehenlassen. Auch habe ich manchmal etwas die strategische Ebene in dieser ganzen Diskussion vermisst. 
+Natürlich kann man jetzt das vorliegende Pake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich wollte eigentlich nicht sprechen, aber ich habe der Debatte sehr aufmerksam zugehört und möchte mir trotzdem erlauben, noch auf ein paar Dinge einzugehen und eine bis zwei Minuten von Ihrer wertvollen Zeit zu stehlen. Ich bin schon erstaunt, wie nonchalant und unpräzise zum Teil mit gewissen Schlagworten operiert wurde; das möchte ich so nicht stehenlassen. Auch habe ich manchmal etwas die strategische Ebene in dieser ganzen Diskussion vermisst. 
+Natürlich kann man jetzt das vorliegende Paket mit irgendwelchen anderen Verträgen oder Zusammenarbeitsformen von irgendwelchen Inselstaaten auf dieser Welt vergleichen, aber ich fände es viel ehrlicher, wenn wir dieses Paket, wie es auf dem Tisch liegt, mit dem Status quo, den wir haben, vergleichen würden. Das wäre ein ehrlicher Ansatz gewesen. 
+Dann bin ich auch erstaunt, dass eigentlich der Widerstand, die Opposition gegen Schengen-Dublin nicht viel grösser ist. Ich meine: Bei einer Nichtübernahme einer Rechtsnorm droht bei Schengen-Dublin die Ausserkraftsetzung. Die Ausserkraftsetzung ist viel einschneidender als das, was wir dann neu mit der dynamischen Rechtsübernahme haben. Trotzdem ist eine Mehrheit für Schengen-Dublin. Unsere Rechtsordnung ist deswegen auch nicht in den Abgrund gegangen, wie vielfach insinuiert wurde. Neu sitzen wir mit am Tisch, wenn in Brüssel Regelungen entstehen - das tun wir heute nicht -, und wenn sich eine Änderung zukünftig auf unser Schweizer Gesetz durchschlagen würde, dann wird zwingend das Parlament darüber entscheiden. Das ist heute auch nicht unbedingt so. Das ist eben die dynamische Rechtsübernahme, und es ist kein Automatismus. Wie oft wurde hier, wahrscheinlich willentlich, dynamisch mit automatisch verwechselt? Bitte verwenden Sie den Terminus "automatisch" nicht mehr. 
+Esther Friedli, meine Kollegin, hat die Frage in den Raum gestellt, wo uns die EU denn überhaupt entgegengekommen sei. Als wäre das nicht ein Verhandlungspaket, für das beide Seiten aufeinander zugegangen sind. Ich kann Ihnen, Kollegin Esther Friedli, ganz viele Beispiele aufzählen: Wir haben keine Superguillotine; wir haben den sektoriellen Ansatz, der bei den staatlichen Beihilfen besonders wichtig ist; wir haben keine dynamische Rechtsübernahme, keinen EuGH beim Landwirtschaftsabkommen; wir haben die Schutzklausel; wir haben die Teilnahme an Horizon bereits seit dem 1. Januar 2025; wir haben die Nichtregressionsklausel beim Lohnschutz. Das ist jetzt eine Auswahl an Beispielen, wo uns die EU entgegengekommen ist, und das stellt uns zum Teil besser als einige EU-Mitglieder oder EWR-Mitglieder. 
+Zum Schluss möchte ich auch festhalten: Die EU ist nicht perfekt, mir gefällt auch nicht alles, was in der EU passiert, und ich weiss auch nicht, wie sich die EU weiterentwickeln wird, Kollege Rieder. Aber mit wem sonst wollen Sie geregelte und enge Beziehungen eingehen? Das möchte ich Sie fragen. Was ist eine glaubwürdige Alternative? Ich habe keine gehört heute Abend, und deswegen bitte ich Sie, einzutreten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je n'ai pas entendu de voix francophone critique jusqu'à maintenant - je serai celle-là. Stabiliser la voie bilatérale, cela sonne bien ; la question que l'on doit se poser, c'est à quel prix. Le 20 décembre 2024, Mme la conseillère fédérale Viola Amherd, alors présidente de la Confédération, et la présidente de la Commission européenne Ursula von der Leyen, annonçaient, je cite, "la conclusion réussie des négociations Suisse-UE". La veille seulement, le Conseil fédéral avait reçu un résumé des </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je n'ai pas entendu de voix francophone critique jusqu'à maintenant - je serai celle-là. Stabiliser la voie bilatérale, cela sonne bien ; la question que l'on doit se poser, c'est à quel prix. Le 20 décembre 2024, Mme la conseillère fédérale Viola Amherd, alors présidente de la Confédération, et la présidente de la Commission européenne Ursula von der Leyen, annonçaient, je cite, "la conclusion réussie des négociations Suisse-UE". La veille seulement, le Conseil fédéral avait reçu un résumé des accords, acceptés de toute évidence sans relecture politique globale. Je ne ferai pas de vilaine allusion à la lecture partielle et incomplète des contrats d'achat des F-35A, mais à l'évidence, aucun responsable politique n'a lu les 2200 pages des accords et de leurs annexes qui sont le résultat de négociations techniques, certes, aux limites des concessions que l'Union européenne était prête à accepter, mais non d'un respect de nos principes fondamentaux qui sont notre souveraineté, notre fédéralisme et notre démocratie directe. La question qui se pose n'est donc pas de savoir si ces accords sont de bons accords, mais si la couleuvre qu'ils nous obligent à avaler est d'une taille supportable au regard des avantages que l'on espère en tirer, ou mieux, des désavantages qu'il faudrait affronter en cas de rejet. 
+Deux sujets parmi d'autres sont hautement problématiques. Je les mentionnerai brièvement, parce que d'autres avant moi l'ont fait.
+La reprise dynamique du droit européen, d'abord. Elle implique à la fois l'intégration au droit suisse de normes européennes élaborées à Bruxelles, lorsqu'elles sont directement applicables, et l'interprétation des accords et de leurs dispositions d'application en fonction de la jurisprudence de la Cour de justice de l'Union européenne. Notre Tribunal fédéral serait, ainsi, non plus la plus haute instance judiciaire, mais serait subordonné à la Cour de justice de l'Union européenne, qui devrait être impérativement interpellée en cas de doute sur l'application du droit. Tout litige au sein du comité mixte quant à l'interprétation ou l'application d'une disposition serait soumis au tribunal arbitral qui, bien évidemment, sachant le soutien qu'il peut espérer de la cour, ne fera que prendre le parti de l'Union européenne.
+Quant à la clause de sauvegarde, il faut que le Conseil fédéral invoque des problèmes économiques et sociaux et que cette situation soit admise par l'Union européenne. Autant rêver : depuis quand le premier de classe aurait-il des problèmes de nature à faire pleurer le reste de l'Europe ?
+Pour faire passer la pilule, on nous dit que la Suisse peut toujours payer une pénalité fixée par l'Union européenne si elle ne veut pas reprendre une nouvelle obligation résultant du droit européen. La belle affaire ! Les votations populaires ne porteront alors plus sur la question de savoir si l'on est pour ou contre un sujet déterminé, mais si l'on est prêt à payer la pénalité fixée par l'Union européenne pour faire valoir notre avis divergent. En conclusion, la reprise dynamique du droit européen est l'antichambre qui ne porte pas son nom de l'entrée pure et simple dans l'Union européenne. Or, quand on ne veut pas se marier, on ne commence pas par se fiancer.
+Deuxième problème : l'accord de libre circulation de 1999, en vigueur depuis 2002, devrait être actualisé en intégrant les modifications intervenues. Cela impliquerait l'alignement sur la directive européenne sur la citoyenneté en matière de droit de séjour permanent, de regroupement familial ou d'accès au système social. Ainsi, après cinq ans d'activité professionnelle et sans preuve d'intégration, le permis de séjour serait accordé. Ce sont 690 000 personnes déjà présentes sur notre territoire qui en bénéficieraient, avec 50 000 à 70 000 nouvelles personnes par année, lesquelles bénéficieraient bien évidemment de prestations sociales après avoir épuisé les prestations de chômage en cas de perte d'emploi. Je vous laisse imaginer la charge supplémentaire. Le regroupement familial serait élargi, y compris pour les proches financièrement et physiquement dépendants, ainsi que pour les partenaires en relation durable attestée. Je vous laisse également imaginer les conséquences sur les prestations sociales de toute nature. Quant à la clause de sauvegarde, déjà en vigueur depuis 1999, mais jamais appliquée malgré l'explosion du nombre de travailleurs frontaliers - mon collègue tessinois Chiesa l'a rappelé pour le Tessin, inutile de vous le rappeler pour Genève - : ces travailleurs frontaliers, dont le nombre ne cesse d'augmenter, sont là au préjudice de nos jeunes en fin de formation et de nos demandeurs d'emploi. A-t-on mis en oeuvre une clause de sauvegarde ? Non.
+Je vous rappelle l'enterrement de première classe qui a été accordé à l'article 121a de notre Constitution, qui n'a jamais été appliqué. De tout cela, les secteurs de l'économie, qui soutiennent l'adoption des accords, n'ont évidemment cure. Depuis quand cette grande économie se soucie-t-elle d'ailleurs de la souveraineté ? Elle n'a pas besoin de citoyens, mais uniquement de consommateurs. En oubliant bien vite qu'il fait bon mettre son siège en Suisse, parce que la Suisse est un pays stable avec un droit prévisible. Où seraient la prévisibilité et la stabilité, si les décisions appliquées en Suisse sont prises à Bruxelles ? 
+Non, décidément, cette couleuvre est trop grande à avaler pour un estomac de démocrate suisse ; c'est la raison pour laquelle je vous invite à refuser l'entrée en matière.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiesa Marco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi invito a guardare in faccia la realtà. Questo pacchetto, che viene presentato come una stabilizzazione della via bilaterale, ha una portata che va senz'altro oltre a questa rassicurante definizione. Non si limita ad aggiornare i nostri accordi con l'Unione europea, ma modifica l'essenza del rapporto tra la Svizzera e l'UE. 
+I numeri danno la misura di questo cambiamento: 94 atti legislativi dell'Unione europea da recepire, 36 nostre leggi federali da modificare e 3 nuove leggi da creare. Il s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi invito a guardare in faccia la realtà. Questo pacchetto, che viene presentato come una stabilizzazione della via bilaterale, ha una portata che va senz'altro oltre a questa rassicurante definizione. Non si limita ad aggiornare i nostri accordi con l'Unione europea, ma modifica l'essenza del rapporto tra la Svizzera e l'UE. 
+I numeri danno la misura di questo cambiamento: 94 atti legislativi dell'Unione europea da recepire, 36 nostre leggi federali da modificare e 3 nuove leggi da creare. Il solo messaggio del Consiglio federale supera le 1000 pagine. E non finisce qui! Con la ripresa dinamica del diritto europeo alle regole di oggi si aggiungeranno anche quelle di domani. La Svizzera potrà partecipare alla sua elaborazione, potrà presentare delle osservazioni e spiegare la sua posizione. Ma essere ascoltati non significa essere considerati. Gli Stati non hanno amici, hanno interessi. Non possiamo pensare che al momento della decisione gli interessi della Svizzera vengano prima di quelli dei Paesi dell'Unione europea. 
+Una parte consistente di queste nuove norme potrà essere recepita già a livello di ordinanza. Le ordinanze, a differenza di leggi, non passano per il Parlamento e non possono sottostare a un referendum. Il mantra che ci viene ripetuto è però sempre lo stesso: quando sarà necessaria una modifica di legge, Parlamento e popolo conserveranno la facoltà di rifiutare. È vero, ma quel "no" legittimo e democratico può costarci molto caro. Gli accordi prevedono infatti misure compensative nei confronti del nostro Paese, proporzionate sottostante al controllo del Tribunale arbitrale - chiamiamole pure diplomaticamente misure compensative. Ma se scattano, un Paese che paga per aver esercitato un proprio diritto democratico non sta compensando nulla, sta semplicemente subendo una sanzione. Ecco il nodo!
+È una camicia di forza per la nostra democrazia diretta. 
+Per la minoranza della commissione il dibattito su questo pacchetto comincia esattamente qui, dallo spazio decisionale che vogliamo conservare per la Svizzera e da quanta indipendenza siamo disposti a sacrificare. 
+La domanda è una sola: stiamo collaborando con l'Unione europea da pari a pari o stiamo accettando una sorta di dipendenza istituzionale? C'è chi ci rassicura dicendo che la nostra garanzia sarà il tribunale arbitrale paritetico. Guardiamo la procedura per quella che è realmente. Da un lato, quando per decidere una controversia sarà necessario interpretare il diritto dell'Unione europea, ripreso degli accordi, il tribunale arbitrale dovrà rivolgersi alla Corte di giustizia europea. Quell'interpretazione sarà vincolante, fornita da una corte di cui la Svizzera non fa parte, evidentemente, e dove non risiede alcun giudice svizzero. Dall'altro lato, se la Svizzera deciderà di non riprendere una nuova norma, quel rifiuto potrà aprire una controversia al termine della procedura prevista dagli accordi ed esporre il nostro Paese a misure compensative. 
+Quindi la realtà è questa: non parteciperemo alla decisione finale sulle regole dell'Unione europea, che potremmo essere chiamati a recepire. Quando sarà necessario interpretare quel diritto, un'interpretazione vincolante spetterà alla Corte di giustizia dell'Unione europea, dove la Svizzera evidentemente non è rappresentata. Se decidiamo di rifiutare, quel no potrà avere delle conseguenze sulla nostra popolazione e sulle nostre aziende. Continueremo ad avere il nostro Parlamento, le nostre leggi, le nostre votazioni, e le nostre istituzioni resteranno al loro posto. Ma una parte della cornice legale entro cui la Svizzera deciderà non sarà certo scritta dagli svizzeri. Questo non è un rapporto fra pari. È un rapporto nel quale noi saremo continuamente sotto scacco dell'Unione europea.
+È questo il cambiamento istituzionale che dobbiamo avere il coraggio di affermare ad alta voce. Ma queste regole non sono astratte né chiuse nei compendi di diritto. Arrivano nella vita quotidiana di chi lavora, e questo si vede in Ticino meglio che altrove.
+Vengo al mio Cantone, che rappresento assieme al collega Regazzi. Da noi gli effetti della libera circolazione non sono teoria. Li viviamo ogni giorno. Li subiamo soprattutto nel settore terziario, dove per decenni tanti ticinesi hanno costruito il proprio percorso professionale e il proprio futuro.
+Siamo un Cantone di frontiera a diretto contatto con un mercato del lavoro dai livelli salariali sensibilmente più bassi. Conosciamo le difficoltà dei nostri giovani ad entrare in questo mercato del lavoro. Secondo la statistica ILO, in Ticino la disoccupazione giovanile raggiunge il 13 per cento. Lo ripeto: il 13 per cento. Conosciamo anche il dramma di chi dopo i 50 anni perde il posto di lavoro e si scontra con l'effetto di sostituzione. Per lo stesso posto di lavoro i nostri residenti, i nostri figli, competono con chi arriva da quel mercato, ossia con i frontalieri. Per questo, per il Ticino la clausola di salvaguardia che è stata evocata non è un mero dettaglio tecnico: è una questione di lavoro, di prospettive, di famiglie e di futuro.
+Il meccanismo prevede soglie per immigrazione netta, frontalieri, disoccupazione, aiuto sociale, tenendo conto anche di situazioni regionali e settoriali. Sulla carta sembra una risposta concreta. Ma qui sta il paradosso: quando una soglia viene superata la clausola non scatta, le misure non scattano; scatta invece un esame. Bisognerà ancora dimostrare l'esistenza di gravi difficoltà economiche o sociali riconducibili alla libera circolazione. Soltanto allora inizierà la procedura prevista dagli accordi. Quindi mi domando: se le difficoltà del Ticino saranno valutate nel contesto di un'Europa confrontata con problemi economici ben più profondi, quando saranno abbastanza gravi?
+La risposta in questa sala, francamente, la conosciamo tutti: mai!
+Mentre si esamina, si valuta e si discute, il mercato del lavoro non aspetta; sono i ticinesi ad aspettare una protezione che, nella migliore dell'ipotesi, arriverà solamente quando il danno sarà irreparabile. Una clausola di salvaguardia dovrebbe permettere di intervenire quando serve, non quando è troppo tardi. Questa non è una clausola di salvaguardia, è semplicemente un placebo.
+C'è poi un altro cambiamento importante: il nuovo diritto di soggiorno permanente. Dopo cinque anni di soggiorno in Svizzera come lavoratore, un cittadino dell'Unione europea potrà acquisire il diritto di soggiorno permanente insieme ai suoi familiari. La Svizzera ha negoziato alcune deroghe, ma il principio rimane tale. Si pone quindi una domanda decisiva: chi è considerato lavoratore? Non bisogna necessariamente lavorare a tempo pieno e nemmeno guadagnare abbastanza per essere economicamente autosufficienti. Si può conservare lo status di lavoratore, pur ricevendo l'aiuto sociale, se l'attività lavorativa è reale ed effettiva e non puramente marginale. Non è un'ipotesi, anche questa è una realtà. Il Tribunale federale, in passato ha già riconosciuto lo status di lavoratrice a una cittadina europea che lavorava, ma il cui reddito non bastava a mantenere la famiglia e riceveva contemporaneamente l'aiuto sociale. Il punto è semplice: si può essere lavoratori senza essere economicamente sufficienti e dopo cinque anni, solo cinque anni, questo status potrà aprire la porta al diritto di soggiorno permanente nel nostro Paese. 
+Qui arrivano i numeri, non vengono dagli oppositori degli accordi, vengono da un'analisi commissionata dalla Segreteria di Stato della migrazione a Ecoplan. Lo studio stima che da 3000 a 4000 persone in più potrebbero percepire l'aiuto sociale, il che comporterebbe costi supplementari dai 56 ai 74 milioni di franchi all'anno.
+Questi nuovi diritti hanno dunque un costo. È un costo che ricadrà sui Cantoni e sui Comuni e che alla fine spetterà pagare ai contribuenti del nostro Paese. Allora c'è una domanda che diventa inevitabile: quali interessi dobbiamo mettere al primo posto in politica qui in questa sala? Quando diciamo che dobbiamo preoccuparci prima di tutto di chi vive e lavora nel nostro Paese, questo lo dico spesso, qualcuno ci liquida con la parola "primanostristi". Per me "primanostrismo" non è un insulto, è semplicemente una medaglia. 
+Mi domando anche per chi dovremmo fare politica. Penso per chi in Svizzera ci vive e ci lavora, per chi cresce i propri figli, contribuisce alla crescita del Paese e si aspetta che le istituzioni difendano le proprie opportunità. Non mi preoccupo prima di ciò che penseranno a Bruxelles. Dunque, sotto questo punto di vista non ho dubbi. 
+Proprio per questo non possiamo dimenticare chi è più vicino ai cittadini nella nostra Confederazione, ossia i Cantoni. Siamo il Consiglio degli Stati, rappresentiamo i Cantoni che la nostra Costituzione definisce come sovrani. Questi accordi li riguardano direttamente. Anche loro saranno confrontati con le conseguenze delle nuove regole in materia di immigrazione, mercato del lavoro e aiuto sociale. Non a caso lo stesso Consiglio federale ha previsto una convenzione specifica per coinvolgerli nell'applicazione degli elementi istituzionali del pacchetto. Il cambiamento sarà particolarmente concreto nell'ambito degli aiuti statali, dove la Svizzera riprenderà nuove regole sostanziali e istituirà un nuovo sistema di sorveglianza. Gli aiuti previsti dovranno essere notificati a un'autorità svizzera di sorveglianza, che è una sorta di Camera indipendente all'interno della Comco, che potrà esaminarne la compatibilità con le nuove regole. Questo significa che anche decisioni prese da autorità svizzere e cantonali per sostenere determinate imprese potranno essere sottoposte a questo nuovo controllo.
+E allora la domanda concreta è questa: quanto resteremo liberi di sostenere un'azienda strategica per un Cantone o per una regione, senza entrare in conflitto con le nuove regole sugli aiuti di Stato? È un esempio che mostra quanto questi accordi tocchino anche lo spazio decisionale di chi noi tutti rappresentiamo a Berna. Eppure, c'è chi vorrebbe approvare questi accordi senza la loro maggioranza. Siamo seri: la doppia maggioranza non è un ostacolo da aggirare. È parte dell'architettura istituzionale della Svizzera. Noi possiamo discutere a lungo di diritto costituzionale, della forma di referendum da tenere in considerazione, ma la regola del gioco non si sceglie in base al risultato che si vorrebbe. Perché la paura è sempre una cattiva consigliera anche in democrazia. Siamo il Consiglio degli Stati, non possiamo difendere la voce dei Cantoni in quest'aula e considerarla superflua quando la parola passa alle urne.
+I grandi cambiamenti istituzionali raramente avvengono in un solo giorno. Avvengono un passo alla volta, una nuova regola alla volta: una procedura, un nuovo vincolo. Preso isolatamente ogni passo può sembrare sopportabile, ma il nostro compito non è quello di guardare soltanto al prossimo passo, è guardare dove porta la strada. Perché oggi decidiamo della Svizzera del 2026, ma un giorno altri siederanno al nostro posto e dovranno poter assumere democraticamente la responsabilità delle proprie decisioni.
+Noi non siamo proprietari dell'indipendenza della Svizzera, ne siamo i custodi. L'abbiamo ricevuta da chi è venuto prima di noi e abbiamo la responsabilità di consegnarla a chi verrà dopo: una Svizzera aperta alla collaborazione, capace di concludere accordi, pronta a dire sì quando essi sono nell'interesse reciproco, ma soprattutto una Svizzera ancora libera di dire di no quando ritiene che un sì non sia nell'interesse dei propri cittadini.
+Per la minoranza è qui che passa la linea tra cooperazione e sottomissione. Perché quando le regole vengono decise altrove, quando la loro interpretazione vincolante viene da fuori e quando un nostro no può avere un prezzo, si crea una dipendenza istituzionale. È questo che intendiamo quando parliamo di un rapporto che assume tratti coloniali. Noi vogliamo una Svizzera capace di discutere con l'Unione europea su un piano di parità, non una Svizzera sottomessa all'Unione europea.
+Per queste ragioni, a nome della minoranza della commissione, vi propongo di non entrare in materia.
+</t>
+  </si>
 </sst>
 </file>
 
@@ -1726,8 +2035,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I70" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I80" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I80"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -4025,6 +4334,292 @@
         <v>285</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>288</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>71</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>289</v>
+      </c>
+      <c r="I71" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>291</v>
+      </c>
+      <c r="B72" t="s">
+        <v>287</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>292</v>
+      </c>
+      <c r="E72" t="s">
+        <v>116</v>
+      </c>
+      <c r="F72" t="s">
+        <v>130</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>293</v>
+      </c>
+      <c r="I72" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>295</v>
+      </c>
+      <c r="B73" t="s">
+        <v>287</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>296</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+      <c r="F73" t="s">
+        <v>297</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>298</v>
+      </c>
+      <c r="I73" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>300</v>
+      </c>
+      <c r="B74" t="s">
+        <v>287</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>155</v>
+      </c>
+      <c r="E74" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74" t="s">
+        <v>156</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>301</v>
+      </c>
+      <c r="I74" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>303</v>
+      </c>
+      <c r="B75" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>304</v>
+      </c>
+      <c r="E75"/>
+      <c r="F75" t="s">
+        <v>101</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>305</v>
+      </c>
+      <c r="I75" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>307</v>
+      </c>
+      <c r="B76" t="s">
+        <v>287</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>288</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>71</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>308</v>
+      </c>
+      <c r="I76" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>310</v>
+      </c>
+      <c r="B77" t="s">
+        <v>287</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77"/>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>311</v>
+      </c>
+      <c r="I77" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>313</v>
+      </c>
+      <c r="B78" t="s">
+        <v>287</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>314</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>85</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>315</v>
+      </c>
+      <c r="I78" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>317</v>
+      </c>
+      <c r="B79" t="s">
+        <v>287</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>230</v>
+      </c>
+      <c r="E79" t="s">
+        <v>47</v>
+      </c>
+      <c r="F79" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79" t="s">
+        <v>30</v>
+      </c>
+      <c r="H79" t="s">
+        <v>318</v>
+      </c>
+      <c r="I79" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>320</v>
+      </c>
+      <c r="B80" t="s">
+        <v>287</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>321</v>
+      </c>
+      <c r="E80" t="s">
+        <v>47</v>
+      </c>
+      <c r="F80" t="s">
+        <v>101</v>
+      </c>
+      <c r="G80" t="s">
+        <v>322</v>
+      </c>
+      <c r="H80" t="s">
+        <v>323</v>
+      </c>
+      <c r="I80" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -1801,9 +1801,10 @@
     <t xml:space="preserve">"Ei Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Herr Präsident, Herr Bundespräsident, Herr Bundesvizepräsident, Herr Bundesrat, liebe Kolleginnen und Kollegen: "Ei Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." 
 Komm, lass uns gehen: Nach diesem Prinzip soll dieses Paket behandelt werden. Schnell, pragmatisch. So einfach können und dürfen wir an diesen Verträgen nicht vorbeigehen. Erstens sprechen wir hier von einer wahren Gesetzeslawine. Ein gewaltiges Paket wird über Nacht auf einen Schlag in die Schweizer Rechtsordnung übernommen - 94 EU-Rechtsakte, Tausende EU-Verordnungen, Tausende von Seiten. Zum Vergleich: Ein ordentlicher schweizerischer Gesetzgebungsprozess dauert im Schnitt vier Jahre. Vier Jahre für Sorgfalt, Abwägung, demokratische Verankerung, Debatten, für das Hin und Her zwischen den Räten, bis hin zu Einigungskonferenzen. 
 Schauen wir doch einmal die Verträge von unten nach oben an. Gehen wir einmal in einen einzelnen Vertrag. Nehmen wir die Personenfreizügigkeit. Wäre nicht bereits im Abkommen über die Personenfreizügigkeit eine rote Linie überschritten? Wir schaffen ein dauerhaftes Aufenthaltsrecht nach fünf Jahren, das weiter geht als die Aufenthaltsbewilligung C, wir gewähren erweiterten Familiennachzug, und wir verzichten auf höhere Studiengebühren für EU-Studierende.
-Dem Vernehmen nach war das der Preis für die Schutzklausel. Mag die Schutzklausel diesen Preis aufwägen? Das Personenfreizügigkeitsabkommen ist ein Frontalzusammenstoss mit Artikel 121a unserer Bundesverfassung; darüber werden wir ja noch reden. Es ist ein Frontalzusammenstoss mit dem klaren Auftrag zur eigenständigen Steuerung der Zuwanderung. Also allein das Abkommen über die Personenfreizügigkeit, die Erweiterung, würden wir in dieser Form wohl nicht unterschreiben.
-Zweitens, mit den Protokollen, und das haben wir jetzt mehrfach ausgeführt gehört, kommen die institutionellen Elemente über die Verträge hinzu. Das ist ein fundamentaler Paradigmenwechsel. Die bilateralen Verträge I und II basieren auf dem klassischen Völkerrecht: Gleichberechtigung der Parteien, Änderungen nur im gegenseitigen Einvernehmen, Auslegung nach Treu und Glauben. Das, was hier heute vorliegt, bricht mit diesem Fundament. Bilaterale III - das ist eine Verharmlosung. Was hier heute vorliegt, ist ein massiver institutioneller Integrationsschritt. Entscheidend ist nicht nur der heutige Vertragsinhalt, also diese Blackbox, wie ich sie am Anfang erwähnt habe. Entscheidend ist der Mechanismus für das Recht von morgen. Mit der dynamischen Rechtsübernahme verpflichten wir uns auf Vorrat, künftige EU-Rechtsentwicklungen, meist erlassen von der EU-Kommission, die wir heute noch gar nicht kennen, zu übernehmen.
-Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und so oppositionslos in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Making.
+Dem Vernehmen nach war dies der Preis für die Schutzklausel. Mag die Schutzklausel diesen Preis aufwiegen? Das Personenfreizügigkeitsabkommen ist ein Frontalzusammenstoss mit Artikel 121a unserer Bundesverfassung; darüber werden wir ja noch reden. Es widerspricht ebenso dem klaren Auftrag zur eigenständigen Steuerung der Zuwanderung. Allein das Abkommen über die Personenfreizügigkeit, die Erweiterung, würden wir in dieser Form wohl nicht unterschreiben.
+Zweitens kommen mit den Protokollen, wie wir mehrfach ausgeführt gehört haben, die institutionellen Elemente zu den Verträgen hinzu. Dies ist ein fundamentaler Paradigmenwechsel. Die bilateralen Verträge I und II basieren auf dem klassischen Völkerrecht: Gleichberechtigung der Parteien, Änderungen nur im gegenseitigen Einvernehmen, Auslegung nach Treu und Glauben. Das, was heute vorliegt, bricht mit diesem Fundament.
+"Bilaterale III" - dies ist eine Verharmlosung. Tatsächlich handelt es sich um einen massiven institutionellen Integrationsschritt. Entscheidend ist nicht nur der heutige Vertragsinhalt, also jene Blackbox, die ich am Anfang erwähnt habe, sondern der Mechanismus für das Recht von morgen. Mit der dynamischen Rechtsübernahme verpflichten wir uns auf Vorrat, künftige EU-Rechtsentwicklungen zu übernehmen, die meist von der EU-Kommission erlassen werden und die wir heute noch gar nicht kennen.
+Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und oppositionslos so in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Taking.
 Drittens bedeuten die Verträge eine unannehmbare Schwächung der direkten Demokratie und des Föderalismus. Die Rechtsetzung verschiebt sich bei den betroffenen Abkommen räumlich und institutionell. Die EU und die Schweiz haben grundverschiedene Rechtssysteme: Die EU erlässt neues Recht von oben nach unten, bei uns funktioniert es gerade umgekehrt, von unten nach oben - ausgehend vom Souverän, dem Volk. Diese Systeme lassen sich nicht verbinden.
 Entscheidend ist, darüber spricht fast niemand, dass wir selber keine Gesetzgebung innerhalb der betroffenen Abkommen mehr anstossen können; wir geben die Input-Funktion für die entsprechende Gesetzgebung in die Hände der EU-Kommission.
 Zudem, das führte Herr Ständerat Schmid gerade aus, erfährt die Exekutive einen massiven Machtzuwachs. Bundesrat und Verwaltung bestimmen die Positionen, führen das Mandat und wählen die Experten aus, die uns in Brüssel vertreten sollen. Die Schweiz ist von oben nach unten organisierter Expertenstaat: "Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut! Komm, lass uns gehen."
@@ -1812,7 +1813,7 @@
 Auslöser für die Verhandlungen war, gemäss den Medienmitteilungen des Bundesrates in den Anfängen, ein Stromabkommen. Für diesen Gegenwert hat die Schweiz weitreichende Konzessionen gemacht: die dynamische Rechtsübernahme und die innerstaatliche Umsetzung des EU-Beihilferechts. Wie sieht es heute aus? Nun soll ausgerechnet der Strombereich ausgeklammert und separat vorgelegt werden, weil er politisch hoch umstritten ist - das kommt nicht vom Bundesrat, das ist eine Diskussion in den Räten. Damit gerät doch die gesamte Logik des Pakets ins Wanken. Die weitreichenden Konzessionen der Schweiz bleiben bestehen, während der ursprüngliche Auslöser und zentrale Gegenwert, wegen dem man überhaupt verhandelt hat, entfällt. Die Schweiz soll also den vollen Preis für das Paket bezahlen, und das wirft die Frage auf: Wie kann man an den Verpflichtungen festhalten, wenn der Gegenwert, der die Verhandlungen ursprünglich ausgelöst hat, entfällt?
 Manchmal frage ich mich, wann genau wir in der Schweiz aufgehört haben, stolz auf unsere Freiheit, auf unser einzigartiges politisches System zu sein. Ich sehe die Versprechen eines wirtschaftlichen Nutzens. Doch die Realität zeigt, dass die tatsächliche Grössenordnung dieses Nutzens sehr umstritten ist und gar als gering beurteilt wird. Wenn wir diesen vermeintlichen Nutzen gegen den realen Verlust der Souveränität aufwiegen, ist das Ergebnis eindeutig: Der staatspolitische Preis ist zu hoch. Wenn wir auf den Zustand der EU schauen, sehen wir eine zunehmende Zentralisierung, wir sehen, dass das Subsidiaritätsprinzip ignoriert wird, und wir sehen eine enorme Machtkonzentration bei der EU-Kommission. Die wirtschaftlichen und politischen Schwächen grosser Mitgliedstaaten wie Deutschland oder Frankreich sind unübersehbar. Es gibt keinen zwingenden Grund, warum wir uns enger an dieses System binden sollten. Wer behauptet, dieses Paket sei alternativlos, verkennt die Realität und die Stärken unseres Landes. Wir sind ein finanziell gesunder, wir sind ein erfolgreicher Stabilitätsanker im Herzen Europas. Wir halten unser staatliches Haus in Ordnung. Wir haben für Milliarden von Franken eine Jahrhundertinfrastruktur gebaut, die Neat, den Alpentransit, und dies im vitalen Interesse des gesamten Kontinents.
 Dieses starke Schweizer Fundament beweist, dass die EU ein ebenso grosses Eigeninteresse an geordneten Beziehungen hat wie wir. Lassen wir uns wirklich von der Drohkulisse einschüchtern, wonach die Bilateralen I und die Bilateralen II bei einem Nein sofort beendet würden? Es gibt immer Alternativen. Wir können bestehende Abkommen punktuell und klassisch völkerrechtlich modernisieren. Die EU beweist zudem, wie beim Ceta-Abkommen oder den aktuellen Plänen für eine assoziierte Mitgliedschaft Kanadas, dass massgeschneiderte Verträge mit Drittstaaten möglich sind, ohne dass diese auf ihre Souveränität verzichten oder eine automatische Rechtsübernahme akzeptieren müssten.
-"Ei, Vater, sieh den Hut dort auf der Stange." "Was kümmert uns der Hut! Komm, lass uns gehen." Ja, gehen wir selbstbewusst an diesem Hut vorbei, treten wir nicht ein.
+"Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Ja, gehen wir selbstbewusst an diesem Hut vorbei, treten wir nicht ein.
 </t>
   </si>
   <si>
@@ -1871,19 +1872,21 @@
   </si>
   <si>
     <t xml:space="preserve">Je ne vais pas vous prendre beaucoup de temps. Je voulais aborder certaines déclarations inexactes qui ont été faites au sujet du référendum, mais je les garde pour le débat sur le référendum. J'aimerais toutefois revenir sur l'un ou l'autre point.
-Je trouve que la caricature qui est faite ici de l'Union européenne, qui serait une république d'experts, alors que l'Union européenne dispose d'un Parlement, dispose d'un Sénat qui est le Conseil de l'Europe et dispose ensuite d'un gouvernement qui e</t>
+Je trouve que la caricature qui est faite de l'Union européenne, qui serait une république d'experts, alors que l'Union européenne dispose d'un Parlement, dispose d'un Sénat qui est le Conseil de l'Europe et dispose ensuite d'un gouvernement qui est l</t>
   </si>
   <si>
     <t xml:space="preserve">Je ne vais pas vous prendre beaucoup de temps. Je voulais aborder certaines déclarations inexactes qui ont été faites au sujet du référendum, mais je les garde pour le débat sur le référendum. J'aimerais toutefois revenir sur l'un ou l'autre point.
-Je trouve que la caricature qui est faite ici de l'Union européenne, qui serait une république d'experts, alors que l'Union européenne dispose d'un Parlement, dispose d'un Sénat qui est le Conseil de l'Europe et dispose ensuite d'un gouvernement qui est la Commission européenne, avec un trilogue, ne sert à rien dans le débat actuel. Ce n'est pas comme cela que l'on va avancer et créer une dynamique positive dans les relations avec l'Union européenne.
-Le deuxième point que je veux aborder, c'est la reprise dynamique du droit. Je ne vais pas revenir sur ce qui a été dit de manière très pertinente par notre collègue Wasserfallen, mais j'aimerais dire que quand on dit que la reprise dynamique du droit, c'est une reprise automatique, c'est doublement faux. C'est doublement faux. Pourquoi ? Parce qu'il y a le principe du "decision shaping". On nous dit "c'est rien, c'est rien !". Mais moi, j'aimerais vous citer les passages importants - je ne sais pas si vous les avez tous lus, chers collègues - des quatre protocoles d'accord qui portent sur les questions institutionnelles dans les quatre domaines où nous avons accès au marché de l'Union européenne.
+Je trouve que la caricature qui est faite de l'Union européenne, qui serait une république d'experts, alors que l'Union européenne dispose d'un Parlement, dispose d'un Sénat qui est le Conseil de l'Europe et dispose ensuite d'un gouvernement qui est la Commission européenne, avec un trilogue, ne sert à rien dans le débat actuel. Ce n'est pas comme cela que l'on va avancer et créer une dynamique positive dans les relations avec l'Union européenne.
+Le deuxième point que je veux aborder, c'est la reprise dynamique du droit. Je ne vais pas revenir sur ce qui a été dit de manière très pertinente par Mme Wasserfallen, mais j'aimerais dire que quand on dit que la reprise dynamique du droit une reprise automatique, c'est doublement faux. C'est doublement faux. Pourquoi ? Parce qu'il y a le principe du "decision shaping". On nous dit "ce n'est rien, ce n'est rien !". Mais moi, j'aimerais vous citer les passages importants - je ne sais pas si vous les avez tous lus - des quatre protocoles d'accord qui portent sur les questions institutionnelles dans les quatre domaines où nous avons accès au marché de l'Union européenne.
 À l'article 4 de ces protocoles, qu'est-il écrit ? Il est écrit que lorsqu'elle aborde une proposition d'acte juridique de l'Union conformément au traité, la Commission européenne "consulte de manière informelle les experts de la Suisse de la même manière qu'elle demande l'avis des experts des États membres de l'Union pour élaborer ses propositions". En d'autres termes, on est mis au même niveau que les États membres. Je pense que c'est une concession de taille.
 Lorsqu'on parle des actes délégués de l'Union européenne, dans ce domaine également, "la Commission veille à ce que la Suisse ait la participation la plus large possible à la préparation des projets desdits actes délégués". Lorsqu'il s'agit d'actes d'exécution, il y a de même une participation de la Suisse qui est prévue. Et puis, quand il y a des comités d'experts, il y a aussi la présence d'experts de la Suisse qui est prévue. Alors on ne peut pas dire que c'est un simple copier-coller.
-Cette procédure-là, cela a été rappelé par certains intervenants qui ont soutenu l'entrée en matière, est celle qui fonctionne très bien dans le cadre des accords Schengen-Dublin. Je vous ai rappelé la problématique de l'exception suisse pour la directive sur les armes et il n'y a pas de raison que ça ne marche pas dans les quatre autres domaines qui sont concernés par ces accords. C'est en tout cas la position de la majorité.
-Je pense que la deuxième chose inexacte, c'est de dire que nous ne pourrons qu'accepter le droit européen sans autre possibilité. C'est un droit à l'élaboration duquel nous participons, mais que nous pouvons aussi refuser. Et ça, c'est clairement indiqué à l'article 6, je le rappelle, de ces quatre protocoles. C'est-à-dire que l'accomplissement d'obligations constitutionnelles par la Suisse, soit la compétence du Conseil fédéral, des cantons, du Parlement et du peuple, sont garantis.
+Cette procédure-là, cela a été rappelé par certains intervenants qui ont soutenu l'entrée en matière, est celle qui fonctionne très bien dans le cadre des accords Schengen-Dublin. Je vous ai rappelé la problématique de l'exception suisse pour la directive sur les armes et il n'y a pas de raison que cela ne marche pas dans les quatre autres domaines qui sont concernés par ces accords. C'est en tout cas la position de la majorité.
+Je pense que la deuxième chose inexacte, c'est de dire que nous ne pourrons qu'accepter le droit européen sans autre possibilité. C'est un droit à l'élaboration duquel nous participons, mais que nous pouvons aussi refuser. Et ça, c'est clairement indiqué à l'article 6, je le rappelle, de ces quatre protocoles. C'est-à-dire que l'accomplissement d'obligations constitutionnelles par la Suisse, soit la compétence du Conseil fédéral, des cantons, du Parlement et du peuple, est garanti.
 On a aussi évoqué l'intérêt des citoyennes et des citoyens, notamment notre collègue Schwander. Oui, les cantons, eux, se sont déjà exprimés à plusieurs reprises et ont fait savoir de manière majoritaire qu'ils sont favorables à ce paquet. Il y a des cantons qui y sont opposés, mais la majorité des cantons y est favorable. Les seuls qui ne se sont pas exprimés jusqu'à maintenant, ce sont les citoyennes et les citoyens. Alors, laissons-les s'exprimer par un référendum à la majorité simple. C'est en fait la perspective qui nous est offerte par ces accords, dans le respect de la Constitution et c'est la position de la majorité de la commission.
 Autre élément que je voulais encore indiquer, il a été dit de manière inexacte que dans le cadre du règlement des différends, c'est la Cour de justice de l'Union européenne qui décide en dernier lieu. Ce n'est pas juste. La Cour de justice de l'Union européenne ne fera qu'interpréter des concepts du droit européen, mais elle ne tranchera pas les litiges entre l'UE et la Suisse. Ces litiges seront tranchés par un tribunal arbitral constitué selon les règles générales des tribunaux arbitraux.
 Et puis j'aimerais terminer peut-être avec une remarque à l'adresse de notre collègue Friedli, qui a pris l'exemple du contrat de bail. Alors, je me sens un peu concerné en tant que président des locataires de ce pays. Peut-être que vous ne le savez pas, mais les bailleurs - "die Vermieter" - peuvent imposer aux locataires des modifications du contrat. Ils peuvent le faire par le biais d'un avis spécial et c'est aux locataires d'aller contester la modification devant la commission de conciliation. Et s'ils ne le font pas, la modification unilatérale s'applique. Mais les locataires, contrairement à la Suisse dans les contrats des Bilatérales III, ne peuvent pas aller vers l'administration et dire qu'il faudrait peut-être encore changer un peu la modification. Tandis que nous, comme pays, on peut le faire dans le cadre des accords des Bilatérales III qui nous sont proposés.
+La commission de conciliation doit tenir compte de la jurisprudence du Tribunal fédéral, comme d'ailleurs le tribunal arbitral devra tenir compte de la jurisprudence.
+Enfin, je ne vais pas répondre à toutes les remarques de M. Rieder - il n'est plus dans la salle. Il nous a fait un nombre de citations en anglais assez important et je ne peux pas m'empêcher d'en faire une aussi. Et j'irai chercher une citation de 1948 du président Truman. Et qu'avait-il dit, le président Truman ? "If you cannot convince them, confuse them."
 </t>
   </si>
   <si>
@@ -1937,16 +1940,16 @@
     <t xml:space="preserve">421713</t>
   </si>
   <si>
-    <t xml:space="preserve">Je n'ai pas entendu de voix francophone critique jusqu'à maintenant - je serai celle-là. Stabiliser la voie bilatérale, cela sonne bien ; la question que l'on doit se poser, c'est à quel prix. Le 20 décembre 2024, Mme la conseillère fédérale Viola Amherd, alors présidente de la Confédération, et la présidente de la Commission européenne Ursula von der Leyen, annonçaient, je cite, "la conclusion réussie des négociations Suisse-UE". La veille seulement, le Conseil fédéral avait reçu un résumé des </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je n'ai pas entendu de voix francophone critique jusqu'à maintenant - je serai celle-là. Stabiliser la voie bilatérale, cela sonne bien ; la question que l'on doit se poser, c'est à quel prix. Le 20 décembre 2024, Mme la conseillère fédérale Viola Amherd, alors présidente de la Confédération, et la présidente de la Commission européenne Ursula von der Leyen, annonçaient, je cite, "la conclusion réussie des négociations Suisse-UE". La veille seulement, le Conseil fédéral avait reçu un résumé des accords, acceptés de toute évidence sans relecture politique globale. Je ne ferai pas de vilaine allusion à la lecture partielle et incomplète des contrats d'achat des F-35A, mais à l'évidence, aucun responsable politique n'a lu les 2200 pages des accords et de leurs annexes qui sont le résultat de négociations techniques, certes, aux limites des concessions que l'Union européenne était prête à accepter, mais non d'un respect de nos principes fondamentaux qui sont notre souveraineté, notre fédéralisme et notre démocratie directe. La question qui se pose n'est donc pas de savoir si ces accords sont de bons accords, mais si la couleuvre qu'ils nous obligent à avaler est d'une taille supportable au regard des avantages que l'on espère en tirer, ou mieux, des désavantages qu'il faudrait affronter en cas de rejet. 
+    <t xml:space="preserve">Je n'ai pas entendu de voix francophone critique jusqu'à maintenant - je serai celle-là. Stabiliser la voie bilatérale, cela sonne bien ; la question que l'on doit se poser, c'est à quel prix. Le 20 décembre 2024, Mme la conseillère fédérale Viola Amherd, alors présidente de la Confédération, et la présidente de la Commission européenne, Ursula von der Leyen, annonçaient : "la conclusion réussie des négociations Suisse-UE". La veille seulement, le Conseil fédéral avait reçu un résumé des accords</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je n'ai pas entendu de voix francophone critique jusqu'à maintenant - je serai celle-là. Stabiliser la voie bilatérale, cela sonne bien ; la question que l'on doit se poser, c'est à quel prix. Le 20 décembre 2024, Mme la conseillère fédérale Viola Amherd, alors présidente de la Confédération, et la présidente de la Commission européenne, Ursula von der Leyen, annonçaient : "la conclusion réussie des négociations Suisse-UE". La veille seulement, le Conseil fédéral avait reçu un résumé des accords, acceptés de toute évidence sans relecture politique globale. Je ne ferai pas de vilaine allusion à la lecture partielle et incomplète des contrats d'achat des F-35A, mais, à l'évidence, aucun responsable politique n'a lu les 2200 pages des accords et de leurs annexes qui sont le résultat de négociations techniques, certes, aux limites des concessions que l'Union européenne était prête à accepter, mais non d'un respect de nos principes fondamentaux qui sont notre souveraineté, notre fédéralisme et notre démocratie directe. La question qui se pose n'est donc pas de savoir si ces accords sont de bons accords, mais si la couleuvre qu'ils nous obligent à avaler est d'une taille supportable au regard des avantages que l'on espère en tirer, ou mieux, des désavantages qu'il faudrait affronter en cas de rejet.
 Deux sujets parmi d'autres sont hautement problématiques. Je les mentionnerai brièvement, parce que d'autres avant moi l'ont fait.
 La reprise dynamique du droit européen, d'abord. Elle implique à la fois l'intégration au droit suisse de normes européennes élaborées à Bruxelles, lorsqu'elles sont directement applicables, et l'interprétation des accords et de leurs dispositions d'application en fonction de la jurisprudence de la Cour de justice de l'Union européenne. Notre Tribunal fédéral serait, ainsi, non plus la plus haute instance judiciaire, mais serait subordonné à la Cour de justice de l'Union européenne, qui devrait être impérativement interpellée en cas de doute sur l'application du droit. Tout litige au sein du comité mixte quant à l'interprétation ou l'application d'une disposition serait soumis au tribunal arbitral qui, bien évidemment, sachant le soutien qu'il peut espérer de la cour, ne fera que prendre le parti de l'Union européenne.
 Quant à la clause de sauvegarde, il faut que le Conseil fédéral invoque des problèmes économiques et sociaux et que cette situation soit admise par l'Union européenne. Autant rêver : depuis quand le premier de classe aurait-il des problèmes de nature à faire pleurer le reste de l'Europe ?
 Pour faire passer la pilule, on nous dit que la Suisse peut toujours payer une pénalité fixée par l'Union européenne si elle ne veut pas reprendre une nouvelle obligation résultant du droit européen. La belle affaire ! Les votations populaires ne porteront alors plus sur la question de savoir si l'on est pour ou contre un sujet déterminé, mais si l'on est prêt à payer la pénalité fixée par l'Union européenne pour faire valoir notre avis divergent. En conclusion, la reprise dynamique du droit européen est l'antichambre qui ne porte pas son nom de l'entrée pure et simple dans l'Union européenne. Or, quand on ne veut pas se marier, on ne commence pas par se fiancer.
-Deuxième problème : l'accord de libre circulation de 1999, en vigueur depuis 2002, devrait être actualisé en intégrant les modifications intervenues. Cela impliquerait l'alignement sur la directive européenne sur la citoyenneté en matière de droit de séjour permanent, de regroupement familial ou d'accès au système social. Ainsi, après cinq ans d'activité professionnelle et sans preuve d'intégration, le permis de séjour serait accordé. Ce sont 690 000 personnes déjà présentes sur notre territoire qui en bénéficieraient, avec 50 000 à 70 000 nouvelles personnes par année, lesquelles bénéficieraient bien évidemment de prestations sociales après avoir épuisé les prestations de chômage en cas de perte d'emploi. Je vous laisse imaginer la charge supplémentaire. Le regroupement familial serait élargi, y compris pour les proches financièrement et physiquement dépendants, ainsi que pour les partenaires en relation durable attestée. Je vous laisse également imaginer les conséquences sur les prestations sociales de toute nature. Quant à la clause de sauvegarde, déjà en vigueur depuis 1999, mais jamais appliquée malgré l'explosion du nombre de travailleurs frontaliers - mon collègue tessinois Chiesa l'a rappelé pour le Tessin, inutile de vous le rappeler pour Genève - : ces travailleurs frontaliers, dont le nombre ne cesse d'augmenter, sont là au préjudice de nos jeunes en fin de formation et de nos demandeurs d'emploi. A-t-on mis en oeuvre une clause de sauvegarde ? Non.
-Je vous rappelle l'enterrement de première classe qui a été accordé à l'article 121a de notre Constitution, qui n'a jamais été appliqué. De tout cela, les secteurs de l'économie, qui soutiennent l'adoption des accords, n'ont évidemment cure. Depuis quand cette grande économie se soucie-t-elle d'ailleurs de la souveraineté ? Elle n'a pas besoin de citoyens, mais uniquement de consommateurs. En oubliant bien vite qu'il fait bon mettre son siège en Suisse, parce que la Suisse est un pays stable avec un droit prévisible. Où seraient la prévisibilité et la stabilité, si les décisions appliquées en Suisse sont prises à Bruxelles ? 
+Deuxième problème : l'accord de libre circulation de 1999, en vigueur depuis 2002, devrait être actualisé en intégrant les modifications intervenues. Cela impliquerait l'alignement sur la directive européenne sur la citoyenneté en matière de droit de séjour permanent, de regroupement familial ou d'accès au système social. Ainsi, après cinq ans d'activité professionnelle et sans preuve d'intégration, le permis de séjour serait accordé. Ce sont 690 000 personnes déjà présentes sur notre territoire qui en bénéficieraient, avec 50 000 à 70 000 nouvelles personnes par année, lesquelles bénéficieraient bien évidemment de prestations sociales après avoir épuisé les prestations de chômage en cas de perte d'emploi. Je vous laisse imaginer la charge supplémentaire. Le regroupement familial serait élargi, y compris pour les proches financièrement et physiquement dépendants, ainsi que pour les partenaires en relation durable attestée. Je vous laisse également imaginer les conséquences sur les prestations sociales de toute nature. Quant à la clause de sauvegarde, déjà en vigueur depuis 1999, mais jamais appliquée malgré l'explosion du nombre de travailleurs frontaliers. Mon collègue tessinois Chiesa l'a rappelé pour le Tessin, inutile de vous le rappeler pour Genève : ces travailleurs frontaliers, dont le nombre ne cesse d'augmenter, sont là au préjudice de nos jeunes en fin de formation et de nos demandeurs d'emploi. A-t-on mis en oeuvre une clause de sauvegarde ? Non.
+Je vous rappelle l'enterrement de première classe qui a été accordé à l'article 121a de notre Constitution, qui n'a jamais été appliqué. De tout cela, les secteurs de l'économie, qui soutiennent l'adoption des accords, n'en ont évidemment cure. Depuis quand cette grande économie se soucie-t-elle d'ailleurs de la souveraineté ? Elle n'a pas besoin de citoyens, mais uniquement de consommateurs, oubliant bien vite qu'il fait bon mettre son siège en Suisse, parce que la Suisse est un pays stable avec un droit prévisible. Où seraient la prévisibilité et la stabilité, si les décisions appliquées en Suisse étaient prises à Bruxelles ? 
 Non, décidément, cette couleuvre est trop grande à avaler pour un estomac de démocrate suisse ; c'est la raison pour laquelle je vous invite à refuser l'entrée en matière.
 </t>
   </si>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -833,18 +833,17 @@
     <t xml:space="preserve">Hurni Baptiste</t>
   </si>
   <si>
-    <t xml:space="preserve">Il y a 4 ans et 3 mois, lors de la session d'été 2022 du Conseil des États, notre conseil débattait de la motion 22.3374 qui visait une augmentation progressive du budget de l'armée jusqu'à 1 pour cent du produit intérieur brut (PIB) de la Suisse en 2030. Je suis allé relire les débats. On nous disait essentiellement les choses suivantes. Le budget de l'armée a moins augmenté que les autres, les années précédentes. Il y a des retards d'investissement et la planification des dépenses pour le F-35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il y a 4 ans et 3 mois, lors de la session d'été 2022 du Conseil des États, notre conseil débattait de la motion 22.3374 qui visait une augmentation progressive du budget de l'armée jusqu'à 1 pour cent du produit intérieur brut (PIB) de la Suisse en 2030. Je suis allé relire les débats. On nous disait essentiellement les choses suivantes. Le budget de l'armée a moins augmenté que les autres, les années précédentes. Il y a des retards d'investissement et la planification des dépenses pour le F-35A ne laissera pas la marge de manoeuvre nécessaire pour procéder aux investissements nécessaires. Mais on disait aussi autre chose. Mme la conseillère fédérale Amherd, alors, le disait très clairement : avec cette augmentation à 1 pour cent, l'armée bénéficiera des moyens nécessaires. Elle disait même s'être opposée à une augmentation immédiate du budget de l'armée de 2 milliards de francs, car les projets d'investissement n'étaient pas aboutis, alors qu'avec une augmentation à 1 pour cent du PIB progressive, on parviendrait parfaitement à procéder aux investissements nécessaires. Tous les intervenants d'alors défendaient cette augmentation de cette manière. Si on faisait cet effort, alors l'effort financier nécessaire était suffisant.
-4 ans plus tard, c'est tout l'inverse qui nous est dit. Même en atteignant 1 pour cent du PIB en 2030, l'armée ne jouirait pas d'assez de moyens. Il faut 24 milliards de francs de plus que les augmentations déjà en cours pour l'armement sur une durée de 8 ans, pour le Conseil fédéral. Comment peut-on sérieusement, en 4 ans, changer pareillement son fusil d'épaule, si je peux me permettre une expression particulièrement adaptée au débat ? C'est la première raison pour laquelle je vous propose de ne pas entrer en matière. Des moyens supplémentaires très importants ont déjà été donnés à l'armée par une augmentation majeure de son budget courant et continueront d'augmenter ces prochaines années. La majorité du Parlement a donc déjà répondu aux demandes qui sont faites. Aller encore plus loin, encore plus vite, c'est une fuite en avant que nous payerons très cher.
-Mais ce n'est pas tout, si l'armée, ces dernières années, avait donné tous les gages d'une gestion saine et rigoureuse de son budget, si l'armée avait mené à bien tous les projets d'investissement complexes à satisfaction, on pourrait éventuellement discuter d'une rallonge et de la création d'un fonds. Mais c'est bien l'inverse qui s'est produit. Tous les projets complexes ont subi au mieux des retards, au pire des scandales dont le principal mérite est d'alimenter de manière extrêmement régulière les humoristes de notre pays. Le prix fixe du F-35A, un mensonge. Les surcoûts liés à cet avion, qu'il s'agisse d'infrastructures ou d'évolution des prix, énormes. Et on n'a même pas encore de garantie sur les futurs coûts d'exploitation du F-35A. Les six drones du programme ADS-15, ce projet s'est traduit par un fiasco retentissant entre vols impossibles par temps de givre et impossibilité de voler sans escorte pour un drone, sans compter les retards énormes. Le pistolet SIG Sauer P320, malgré son évaluation catastrophique et son taux d'incident élevé, la majorité du Parlement et l'armée veulent aller de l'avant. Je vais m'arrêter là, car il y aurait encore beaucoup d'autres exemples à citer, par exemple, ces fameux Patriots qu'il faut urgemment acquérir, mais qui seront livrés dans un délai inconnu, comme la grêle après les vendanges. Ce que j'essaie de vous dire, c'est qu'aujourd'hui, l'armée ne me rassure absolument pas s'agissant de la bonne utilisation des deniers publics. Nous lui avons déjà donné beaucoup de moyens supplémentaires. Nous allons continuer de le faire. Je suis extrêmement inquiet qu'avec ce fonds de l'armement, ce soit un blanc-seing, sans remise en question sur les fiascos à répétition, qui est donné. Or, ces scandales à répétition entament grandement la crédibilité de l'armée. Plutôt que de lui donner aujourd'hui encore 24 milliards de francs de plus que les augmentations déjà massives de son budget, exigeons d'abord qu'elle utilise correctement l'argent à disposition. C'est la deuxième raison de ne pas entrer en matière.
-La troisième raison de ne pas entrer en matière, c'est qu'on ne sait pas vraiment ce qu'on va acheter avec cet argent. Non, je n'exagère pas. On ne sait pas vraiment, ou plutôt pas précisément ce qu'on va acheter avec ces 24 milliards de francs du fonds. Alors oui, on nous dit qu'il y a 15 milliards de francs visant à écarter les menaces les plus probables et 9 milliards pour les surcoûts et les versements d'acomptes. Mais le problème, c'est qu'un acompte, par définition, devrait se retrouver à l'addition finale et ne représente donc pas un coût. L'autre problème, c'est que pour justifier les 15 premiers milliards, on nous parle déjà de renchérissement. On ne va tout de même pas le payer deux fois. Il y a bien un tableau public qui existe sur la planification de l'armement - état mai 2026 -, mais ce tableau est très incomplet. Concrètement, ce tableau montre quelques projets phares, mais reste muet sur des montants très importants, et cela, même dans un avenir proche. On sait, par exemple, qu'on va dépenser 3,9 milliards de francs pour le chapitre "effet contre des cibles aériennes", ce qui, pour le moins, est assez vague, et que 2 milliards de ces 3,9 milliards iront à la défense sol-air de moyenne portée.
-Quant au 1,9 milliard restant, je n'en ai aucune idée, et ce n'est pas faute d'avoir posé la question.
-C'est la même chose pour le chapitre "effet contre les cibles au sol", qui regroupe notamment la question importante de la protection contre les mini-drones. On dépensera par exemple 1,3 milliard de francs en 2028. Sur ce montant, seuls 900 millions pour les chars Leopard et la protection contre les mini-drones sont toutefois justifiés ; pour le reste, soit 400 millions, la grande muette porte décidément bien son nom.
+    <t xml:space="preserve">Il y a quatre ans et trois mois, lors de la session d'été 2022 du Conseil des États, notre conseil débattait de la motion 22.3374 qui visait une augmentation progressive du budget de l'armée jusqu'à 1 pour cent du produit intérieur brut (PIB) de la Suisse en 2030. Je suis allé relire les débats. On nous disait essentiellement les choses suivantes. Le budget de l'armée a moins augmenté que les autres durant les années précédentes. Il y a des retards d'investissement et la planification des dépens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il y a quatre ans et trois mois, lors de la session d'été 2022 du Conseil des États, notre conseil débattait de la motion 22.3374 qui visait une augmentation progressive du budget de l'armée jusqu'à 1 pour cent du produit intérieur brut (PIB) de la Suisse en 2030. Je suis allé relire les débats. On nous disait essentiellement les choses suivantes. Le budget de l'armée a moins augmenté que les autres durant les années précédentes. Il y a des retards d'investissement et la planification des dépenses pour le F-35A ne laissera pas la marge de manoeuvre nécessaire pour procéder aux investissements nécessaires. On disait aussi autre chose. Mme la conseillère fédérale Amherd, alors, le disait très clairement[NB]: avec cette augmentation à 1 pour cent, l'armée bénéficiera des moyens nécessaires. Elle disait même s'être opposée à une augmentation immédiate du budget de l'armée de 2 milliards de francs, car les projets d'investissement n'étaient pas aboutis, alors qu'avec une augmentation progressive à 1 pour cent du PIB, on parviendrait parfaitement à procéder aux investissements nécessaires. Tous les intervenants d'alors défendaient cette augmentation de cette manière. Si on faisait cet effort, alors l'effort financier nécessaire serait suffisant.
+quatre ans plus tard, c'est tout l'inverse qui nous est dit. Même en atteignant 1 pour cent du PIB en 2030, l'armée ne jouirait pas d'assez de moyens. Il faut 24 milliards de francs de plus que les augmentations déjà en cours pour l'armement sur une durée de 8 ans pour le Conseil fédéral. Comment peut-on sérieusement, en quatre ans, changer pareillement son fusil d'épaule, si je peux me permettre une expression particulièrement adaptée au débat[NB]? C'est la première raison pour laquelle je vous propose de ne pas entrer en matière. Des moyens supplémentaires très importants ont déjà été donnés à l'armée par une augmentation majeure de son budget courant qui continuera d'augmenter ces prochaines années. La majorité du Parlement a donc déjà répondu aux demandes qui sont faites. Aller encore plus loin, encore plus vite, c'est une fuite en avant que nous payerons très cher.
+Ce n'est pas tout, si l'armée, ces dernières années, avait donné tous les gages d'une gestion saine et rigoureuse de son budget, si l'armée avait mené à bien tous les projets d'investissement complexes à satisfaction, on pourrait éventuellement discuter d'une rallonge et de la création d'un fonds. Mais c'est bien l'inverse qui s'est produit. Tous les projets complexes ont subi au mieux des retards, au pire des scandales dont le principal mérite est d'alimenter de manière extrêmement régulière les humoristes de notre pays. Le prix fixe du F-35A est un mensonge. Les surcoûts liés à cet avion, qu'il s'agisse d'infrastructures ou d'évolution des prix, sont énormes. On n'a même pas encore de garantie sur les futurs coûts d'exploitation du F-35A. Les six drones du programme ADS-15, ce projet s'est traduit par un fiasco retentissant entre vols impossibles par temps de givre et impossibilité de voler sans escorte pour un drone, sans compter les retards énormes. Le pistolet SIG Sauer P320, malgré son évaluation catastrophique et son taux d'incidents élevé, la majorité du Parlement et l'armée veulent aller de l'avant. Je vais m'arrêter là, car il y aurait encore beaucoup d'autres exemples à citer, par exemple, ces fameux Patriot qu'il faut urgemment acquérir, mais qui seront livrés dans un délai inconnu, comme la grêle après les vendanges. Ce que j'essaie de vous dire, c'est qu'aujourd'hui, l'armée ne me rassure absolument pas s'agissant de la bonne utilisation des deniers publics. Nous lui avons déjà donné beaucoup de moyens supplémentaires. Nous allons continuer de le faire. Je suis extrêmement inquiet qu'avec ce fonds de l'armement, un blanc-seing, sans remise en question sur les fiascos à répétition, lui soit donné. Or, ces scandales à répétition entament grandement la crédibilité de l'armée. Plutôt que de lui donner aujourd'hui encore 24 milliards de francs de plus que les augmentations déjà massives de son budget, exigeons d'abord qu'elle utilise correctement l'argent à disposition. C'est la deuxième raison de ne pas entrer en matière.
+La troisième raison de ne pas entrer en matière, c'est qu'on ne sait pas vraiment ce qu'on va acheter avec cet argent. Non, je n'exagère pas. On ne sait pas vraiment, ou plutôt pas précisément ce qu'on va acheter avec ces 24 milliards de francs du fonds. Alors oui, on nous dit qu'il y a 15 milliards de francs visant à écarter les menaces les plus probables et 9 milliards pour les surcoûts et les versements d'acomptes. Mais le problème, c'est qu'un acompte, par définition, devrait se retrouver sur l'addition finale et ne représente donc pas un coût. L'autre problème, c'est que pour justifier les 15 premiers milliards, on nous parle déjà de renchérissement. On ne va tout de même pas le payer deux fois. Il y a bien un tableau public qui existe sur la planification de l'armement - état mai 2026 -, mais ce tableau est très incomplet. Concrètement, ce tableau montre quelques projets phares, mais reste muet sur des montants très importants, et cela même dans un avenir proche. On sait, par exemple, qu'on va dépenser 3,9 milliards de francs pour le chapitre "Effet contre des cibles aériennes", ce qui, pour le moins, est assez vague, et que 2 milliards de ces 3,9 milliards iront à la défense sol-air de moyenne portée. Quant au 1,9 milliard restant, je n'en ai aucune idée, et ce n'est pas faute d'avoir posé la question.
+C'est la même chose pour le chapitre "Effet contre les cibles au sol", qui regroupe notamment la question importante de la protection contre les mini-drones. On dépensera par exemple 1,3 milliard de francs en 2028. Sur ce montant, seuls 900 millions pour les chars Leopard et la protection contre les mini-drones sont toutefois justifiés[NB]; pour le reste, soit 400 millions, la grande muette porte décidément bien son nom.
 Je ne connais aucune autre dépense de l'État, aucun autre domaine où l'on pourrait faire preuve d'un degré de précision aussi faible sans se faire immédiatement retoquer par le Parlement. On s'apprête à voter 24 milliards de dépenses supplémentaires pour de l'armement et on ne sait pas précisément ce qu'on va acheter. Pour moi, ce n'est simplement pas sérieux.
 Finalement, je vous propose de ne pas entrer en matière, car ce rapport est un jeu de dupe. Personne dans cette salle ne peut sincèrement croire qu'une augmentation de la TVA de 0,5 pour cent pour le financement des dépenses d'armement a une quelconque chance de passer devant le peuple, ou même devant le Parlement.
-Alors, quel est le but de cet exercice ? Il est simple, politiquement : il s'agit de financer autrement ces 24 milliards. Si c'est de la manière dont la Commission des finances l'a pensé, on peut en discuter. J'ai aussi consulté les déclarations des partis politiques avant la session, qui invitent à une grande prudence. On lit par exemple qu'il faut couper 25 pour cent ou plus des dépenses de la coopération internationale - que nous avons déjà largement diminué ces dernières années - et vendre Swisscom, en renonçant au passage à plus d'un demi-milliard de dividendes - selon le PLR. On lit encore qu'il faudrait couper dans l'asile, du point de vue de l'UDC, sans vraiment prendre en compte qu'en mettant le budget de l'asile à zéro - à zéro, ce qui est parfaitement impossible -, ces 24 milliards ne seraient même pas financés à hauteur d'un sixième. Dit autrement, il faudrait pendant six ans dépenser zéro franc dans le domaine de l'asile pour pouvoir dépenser ces 24 milliards.
+Alors, quel est le but de cet exercice[NB]? Il est simple, politiquement[NB]: il s'agit de financer autrement ces 24 milliards. Si c'est de la manière dont la Commission des finances l'a pensé, on peut en discuter. J'ai aussi consulté les déclarations des partis politiques avant la session, qui invitent à une grande prudence. On lit par exemple qu'il faut couper 25 pour cent ou plus des dépenses de la coopération internationale - que nous avons déjà largement diminuées ces dernières années - et vendre Swisscom, en renonçant au passage à plus d'un demi-milliard de dividendes - selon le Parti libéral-radical. On lit encore qu'il faudrait couper dans l'asile, du point de vue de l'UDC, sans vraiment prendre en compte qu'en mettant le budget de l'asile à zéro - à zéro, ce qui est parfaitement impossible -, ces 24 milliards ne seraient même pas financés à hauteur d'un sixième. Dit autrement, il faudrait pendant six ans dépenser zéro franc dans le domaine de l'asile pour pouvoir dépenser ces 24 milliards.
 Nous avons déjà fait l'exercice d'un programme d'allègement budgétaire, dont le principal but était de financer l'augmentation ordinaire du budget militaire. Je refuse que l'on doive répéter cet exercice particulièrement violent pour notre population dans le but d'acheter je ne sais pas exactement quoi, en prenant le risque majeur que cet argent soit mal utilisé et, de surcroît, dans un domaine où notre État fait des efforts majeurs.
 Je vous remercie de ne pas entrer en matière.
 </t>
@@ -1761,7 +1760,7 @@
 Nun noch ein Wort zu den Folgen des Referendums. Ja, Luzern und Schwyz sind sich bei der Referendumsfrage nicht einig, und das kommt unter guten Nachbarn halt auch vor. Als Standesvertreter gewichte ich die Haltung meines Kantons hoch. Die Luzerner Regierung spricht sich für das fakultative Referendum aus. Nach sorgfältiger Prüfung, auch in Zusammenarbeit mit meinem Kanton, komme ich zum gleichen Schluss.
 Die Bundesverfassung besagt klar, in welchen Fällen ein Staatsvertrag zwingend Volk und Ständen unterbreitet werden muss: beim Beitritt zu einer Organisation für kollektive Sicherheit oder zu einer supranationalen Gemeinschaft. Die Bilateralen III sind weder das eine noch das andere. Nun wird die sogenannte Sui-generis-Praxis geltend gemacht. Danach können besonders bedeutende Staatsverträge dem obligatorischen Referendum unterstellt werden, obwohl die Bundesverfassung dies nicht ausdrücklich vorsieht. Ich anerkenne, dass diese Praxis in einzelnen aussergewöhnlichen Fällen angewandt und politisch akzeptiert wurde. Als Beispiele werden die Freihandelsabkommen von 1972 sowie der EWR-Vertrag von 1992 genannt. Diese Fälle sind jedoch nicht mit der heutigen Vorlage vergleichbar; meine Vorrednerin hat das bereits erwähnt.
 Das obligatorische Referendum ist ein tragender Pfeiler unseres Bundesstaates, und gerade deshalb darf es nicht beliebig eingesetzt werden. Die Ausnahme der Sui-generis-Praxis überzeugt mich bei diesem Paket nicht. Sie darf nicht allein deshalb angewandt werden, weil die politische Bedeutung der Vorlage gross ist. Ein obligatorisches Referendum ohne klare verfassungsrechtliche Grundlage würde zudem einen Präzedenzfall schaffen, dessen Folgen für künftige Staatsverträge schwer abzuschätzen wären.
-Ich bin für eine starke demokratische Kontrolle mit einer konsequenten parlamentarischen Mitwirkung sowie für eine Schutzklausel, die wirklich greift, und ich bin dafür, dass unsere verfassungsmässigen Spielregeln gerade dann respektiert werden, wenn der politische Druck gross ist. Ich bitte Sie, auf die Vorlage einzutreten. Eintreten bedeutet keinen Blankoscheck. Es ist eine Voraussetzung dafür, dass dieses Abkommen im Interesse der Schweiz umgesetzt wird, und hier sind wir als Parlament gefordert.
+Ich bin für eine starke demokratische Kontrolle mit einer konsequenten parlamentarischen Mitwirkung sowie für eine Schutzklausel, die wirklich greift, und ich bin dafür, dass unsere verfassungsmässigen Spielregeln gerade dann respektiert werden, wenn der politische Druck gross ist. Ich bitte Sie, auf die Vorlage einzutreten. Eintreten bedeutet keinen Blankocheque. Es ist eine Voraussetzung dafür, dass dieses Abkommen im Interesse der Schweiz umgesetzt wird, und hier sind wir als Parlament gefordert.
 </t>
   </si>
   <si>
@@ -1916,6 +1915,7 @@
 Der Bundesrat ist überzeugt: Das Paket Schweiz-EU ist im Interesse der Einwohnerinnen und Einwohner unseres Landes. Wir wollen, dass die Schweiz ihre Erfolgsgeschichte fortsetzen kann - mit stabilen Beziehungen zu unseren europäischen Nachbarn, mit Rechtssicherheit und mit dem notwendigen politischen Handlungsspielraum.
 Mit dem Paket Schweiz-EU wahren wir unsere Handlungsfähigkeit und unsere Souveränität mitten in Europa. Damit bleiben wir uns und unserer Geschichte treu. Wir schaffen die Voraussetzungen, um künftige Herausforderungen zu meistern und Chancen im Interesse kommender Generationen zu nutzen. Ich bitte Sie deshalb, bei der Beratung dieser wichtigen Vorlage das grosse Ganze nicht aus den Augen zu verlieren und die langfristigen Interessen der Schweiz im Blick zu haben. 
 Im Namen des Bundesrates empfehle ich Ihnen, auf die Vorlage einzutreten.
+[VS]
 </t>
   </si>
   <si>
@@ -1990,6 +1990,472 @@
 Noi non siamo proprietari dell'indipendenza della Svizzera, ne siamo i custodi. L'abbiamo ricevuta da chi è venuto prima di noi e abbiamo la responsabilità di consegnarla a chi verrà dopo: una Svizzera aperta alla collaborazione, capace di concludere accordi, pronta a dire sì quando essi sono nell'interesse reciproco, ma soprattutto una Svizzera ancora libera di dire di no quando ritiene che un sì non sia nell'interesse dei propri cittadini.
 Per la minoranza è qui che passa la linea tra cooperazione e sottomissione. Perché quando le regole vengono decise altrove, quando la loro interpretazione vincolante viene da fuori e quando un nostro no può avere un prezzo, si crea una dipendenza istituzionale. È questo che intendiamo quando parliamo di un rapporto che assume tratti coloniali. Noi vogliamo una Svizzera capace di discutere con l'Unione europea su un piano di parità, non una Svizzera sottomessa all'Unione europea.
 Per queste ragioni, a nome della minoranza della commissione, vi propongo di non entrare in materia.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En introduction, il faut mentionner que, ces dernières années, les cantons ont régulièrement rappelé que les dispositions en vigueur relatives au financement des soins et de la santé des détenus ne sont pas toujours claires et peuvent être sujettes à d'importantes fluctuations financières. C'est pourquoi le Conseil fédéral, soutenu en consultation par une majorité des cantons et de la Conférence des directrices et directeurs des départements cantonaux de justice et police (CCDJP), a élaboré un p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En introduction, il faut mentionner que, ces dernières années, les cantons ont régulièrement rappelé que les dispositions en vigueur relatives au financement des soins et de la santé des détenus ne sont pas toujours claires et peuvent être sujettes à d'importantes fluctuations financières. C'est pourquoi le Conseil fédéral, soutenu en consultation par une majorité des cantons et de la Conférence des directrices et directeurs des départements cantonaux de justice et police (CCDJP), a élaboré un projet visant à ce qu'à l'avenir tous les détenus disposent d'une assurance-maladie. En 2023, environ 2300 personnes détenues sur 6450, donc à peu près le tiers, n'étaient pas couvertes par l'assurance-maladie obligatoire, car elles n'avaient pas de domicile en Suisse et n'étaient donc pas soumises à l'obligation d'assurance. Comme les dispositions y relatives varient d'un canton à l'autre, il arrive que des personnes détenues sans assurance n'aient parfois qu'un accès limité aux soins médicaux, ce qui contrevient au principe d'égalité de traitement prévu dans la Constitution.
+Lors de la consultation, il a été tenu compte notamment de la préoccupation d'une majorité des participants qui s'étaient exprimés en faveur du transfert de la compétence au canton qui ordonne la détention, tant en matière de restriction du choix de l'assureur et du prestataire de soins que de respect et de contrôle de l'obligation d'assurance. Auparavant, l'avant-projet attribuait cette compétence au canton où se trouve l'établissement pénitentiaire, ce qui n'était pas considéré comme une bonne solution en cas de transfert intercantonal. Cependant, malgré les restrictions apportées, le Conseil des États a refusé d'entrer en matière sur le projet, par 33 voix contre 9. Il a émis les réserves suivantes. Les personnes concernées n'ont aucun lien avec la Suisse, puisqu'elles ne sont pas domiciliées en Suisse, et la révision proposée est en contradiction avec la systématique de la LAMal. De plus, une telle obligation risque d'entraîner une charge administrative disproportionnée si tous les détenus devaient s'affilier à une caisse d'assurance-maladie.
+Réunie en séance le 2 juillet, notre commission se rallie à la décision du Conseil des États, en insistant sur six éléments. Premièrement, on ne doit pas déroger au principe, prévu par la LAMal, selon lequel l'obligation de s'assurer ne s'applique en règle générale qu'aux personnes domiciliées en Suisse et y percevant un revenu ; cela constituerait même un avantage pour les personnes incarcérées par rapport à d'autres personnes qui se trouvent temporairement en Suisse sans avoir commis d'infraction.
+Deuxièmement, un transfert des coûts des cantons vers l'assurance obligatoire des soins n'est pas judicieux. Aujourd'hui, ce sont les cantons qui prennent en charge ces coûts ; demain, ils seraient financés par les primes. On peut craindre une charge supplémentaire pour l'ensemble des assurés, notamment en raison des frais administratifs et des coûts des prestations supérieurs à la moyenne pendant le séjour, généralement de courte durée, de ces personnes en Suisse. Dit très clairement : les coûts des traitements médicaux de ces personnes qui ne paient pas d'impôts et n'ont versé aucune prime ni aucune autre cotisation sociale dans notre pays doivent rester à la charge des cantons et être financés par les impôts.
+Troisièmement, un bon nombre des personnes concernées devraient de toute façon bénéficier de réductions de primes. En effet, la plupart des détenus sans domicile en Suisse n'ayant pas d'argent, ce sont de toute façon les communes ou le canton qui prendraient en charge les primes.
+Quatrièmement, les primes impayées ne seraient plus recouvrables pour les assureurs en raison de l'expulsion qui souvent suit la détention.
+Cinquièmement, la prise en charge médicale de ces personnes devra de toute manière être garantie, conformément à la Constitution, et cela indépendamment de l'obligation de s'assurer.
+Sixièmement, il ressort des documents que la mise en oeuvre ne serait pas aisée. En réalité, il s'agit de proposer une solution d'assurance pour les cantons, au motif d'une meilleure clarté et prévisibilité. C'est ce que souhaitent la CCDJP et la Conférence des chefs des services pénitentiaires cantonaux dans leur prise de position adressée à notre commission. Or, aujourd'hui, les cantons ont déjà une marge de manoeuvre et elle est suffisante, en matière de paiement et de restriction concernant les médecins qui traitent les personnes détenues sans domicile en Suisse.
+Vu ce qui précède, notre commission vous propose, par 16 voix contre 0 et 9 abstentions, de ne pas entrer en matière sur le projet.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SPK-S hat die Änderung des Ausländer- und Integrationsgesetzes, Anhang 4 zum Bundesbeschluss 1, beraten. Grundlagen der Beratung waren die Botschaft vom 5. Mai 2025 des Bundesrates sowie ein erweiterter Mitbericht der APK-S. Da das Ausländer- und Integrationsgesetz ein Anhang zum Bundesbeschluss 1 ist, oblag das Eintreten der APK-S. In der SPK-S wurde daher nicht über das Eintreten oder eine Gesamtabstimmung entschieden. Auch war das Personenfreizügigkeitsabkommen nicht Gegenstand der Beratu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SPK-S hat die Änderung des Ausländer- und Integrationsgesetzes, Anhang 4 zum Bundesbeschluss 1, beraten. Grundlagen der Beratung waren die Botschaft vom 5. Mai 2025 des Bundesrates sowie ein erweiterter Mitbericht der APK-S. Da das Ausländer- und Integrationsgesetz ein Anhang zum Bundesbeschluss 1 ist, oblag das Eintreten der APK-S. In der SPK-S wurde daher nicht über das Eintreten oder eine Gesamtabstimmung entschieden. Auch war das Personenfreizügigkeitsabkommen nicht Gegenstand der Beratung der SPK-S - indirekt zwar schon, aber nicht direkt.
+Worum geht es? Die vorgesehenen Änderungen des AIG resultieren aus der Notwendigkeit, das Änderungsprotokoll zum Freizügigkeitsabkommen sowie die Unionsbürgerrichtlinie 2004/38/EG im innerstaatlichen Recht abzubilden. Obwohl diese Bestimmungen grundsätzlich direkt anwendbar sind, identifiziert der Bundesrat in seiner Botschaft und in seinen Ausführungen vor der Kommission spezifische Bereiche, in denen das nationale Recht einen Handlungsspielraum bietet. Der Bundesrat beabsichtigt, diesen Spielraum gezielt zu nutzen, um die Umsetzung so präzise wie möglich an den nationalen Interessen auszurichten.
+Die geplanten Anpassungen gliedern sich in zwei Kategorien. Zur ersten Kategorie gehören die notwendigen Umsetzungen des FZA-Änderungsprotokolls; dazu gehört, das Daueraufenthaltsrecht zwingend im inländischen Recht zu verankern. Erwerbstätige EU-Staatsangehörige sowie deren Familienmitglieder erhalten nach einem Aufenthalt von fünf Jahren das Recht auf dauerhaften Aufenthalt. Des Weiteren wurden die Ausschlusskriterien in der Sozialhilfe behandelt. Ich gehe davon aus, dass wir in der Detailberatung darüber noch ausführlicher sprechen werden. Der Bundesrat hält dazu fest, dass eine zentrale Bedingung der Umsetzung die Anrechnung von Sozialhilfebezügen ist. Ein vollständiger Sozialhilfebezug von sechs Monaten oder mehr wird gemäss den Plänen nicht an die fünfjährige Frist für das Daueraufenthaltsrecht angerechnet.
+Zur zweiten Kategorie gehören strategische Begleitmassnahmen zur Nutzung des Handlungsspielraums. Diese Massnahmen sind rechtlich nicht zwingend vorgeschrieben. Der Bundesrat führt sie jedoch ein, um eine möglichst strenge und scharfe Anwendung des Abkommens zu gewährleisten. Dazu gehören die Optimierung des Datenaustauschs und die Flexibilität im Vollzug, konkret eine Einzelfallprüfung.
+In diesem Zusammenhang sind spezifische Regelungen und Instrumente vorgesehen. Im Zentrum steht die Konkretisierung der Schutzklausel. Ein Kernpunkt der Umsetzung ist die präzise Definition der Schutzklausel. Der Bundesrat will im AIG festlegen, unter welchen Bedingungen schwerwiegende wirtschaftliche oder soziale Probleme vorliegen. Er präzisiert hierzu das Verfahren für die Schutzklausel, die kantonale Mitwirkung und das Ziel der Schutzklausel. 
+Ein weiterer Punkt betrifft den Nachzug pflegebedürftiger Familienangehöriger. Der Bundesrat beabsichtigt, den Familiennachzug in Härtefällen zu erleichtern, knüpft diesen jedoch an strikte Voraussetzungen, um eine Ausweitung des Rechtsanspruchs zu verhindern.
+Das Fazit des Bundesrates war, dass die vorgeschlagene Umsetzung im AIG ein massgeschneidertes Paket darstellt, welches die Interessen der Schweiz optimal wahre. Wir haben in der Kommission an mehreren Sitzungen über das AIG debattiert und Beschlüsse gefasst. Die Vorlage des Bundesrates wurde einer eingehenden Prüfung unterzogen. Im Zentrum des Austausches standen insbesondere die Verfassungskonformität, die faktischen Auswirkungen auf die Zuwanderung sowie die staatspolitischen Implikationen der dynamischen Rechtsübernahme.
+In Bezug auf die Zuwanderungssteuerung und die Verfassungskonformität wurde in unserer Kommission intensiv diskutiert, ob die Vorlage mit Artikel 121a der Bundesverfassung vereinbar sei. Die Kommission äusserte deutliche Bedenken, ob die neuen Regelungen insbesondere im Bereich des Familiennachzugs und des Daueraufenthaltsrechts eine zusätzliche Zuwanderung generieren und damit die staatliche Steuerung untergraben bzw. Artikel 121a der Bundesverfassung verletzen würden. Das wird morgen bei der Beratung unserer parlamentarischen Initiative im Detail zu diskutieren sein. 
+Weiter ging es um das Thema des Daueraufenthaltsrechts und der Integrationsfrage. Die Kommission hinterfragte kritisch die Kriterien für das neue Daueraufenthaltsrecht. Insbesondere wurde die Sorge geäussert, dass dieses Recht eine Sogwirkung entfalten könnte oder insbesondere für Personen attraktiv werde, die aufgrund mangelnder Integration die Voraussetzungen für eine Niederlassungsbewilligung C nicht erfüllen würden. Hierzu wurde uns erläutert, dass die Kernbedingung einer Erwerbstätigkeit über fünf Jahre quasi identisch mit der für die C-Bewilligung bleibe. Es wurde eingeräumt, dass das Daueraufenthaltsrecht aufgrund des Wegfalls der Integrationsprüfung eine Alternative für bestimmte Gruppen darstelle, wobei aber die wirtschaftliche Bedingung, die echte Erwerbstätigkeit, die massgebliche Hürde sei. 
+In der Kommission hat im Zusammenhang mit dem Ausländer- und Integrationsgesetz (AIG) eine intensive Debatte über das Verhältnis zwischen dem Freizügigkeitsabkommen und dem innerstaatlichen Recht stattgefunden. Die Kommission thematisierte mit Nachdruck die sogenannte Schubert-Praxis und die Gefahr, dass hier Völkerrecht dem Landesrecht vorgehe, selbst wenn das Parlament explizit abweichende Regelungen beschliesse. Der Bundesrat legte dar, dass die neuen institutionellen Protokolle die völkerrechtliche Ausgangslage veränderten, da die Schweiz nun explizit die Möglichkeit besitze, unter Inkaufnahme von Ausgleichsmassnahmen vom Abkommen abzuweichen. In der Diskussion wurde präzisiert, dass hierbei zwei unterschiedliche Prozesse zu unterscheiden seien, die innerstaatliche Rechtsanwendung durch das Bundesgericht auf der einen Seite und das internationale Streitbeilegungsverfahren auf der anderen Seite.
+Das Thema der Schubert-Praxis, das ein Teil der parlamentarischen Initiative war, wird ja dann in der Kommission nach dieser Session vertieft. Diese Vorlage wird Ihnen in einer der nächsten Sessionen vorgelegt werden können, wahrscheinlich in der Frühjahrssession, sofern die Vernehmlassung plangemäss verläuft.
+Weiter hat die Kommission sich kritisch mit der Praxistauglichkeit der Schutzklausel auseinandergesetzt und auch hinterfragt, ob die Indikatoren genügend stark sein würden, um die Schutzmassnahmen auch wirksam zu machen. Hierzu wurde uns ausgeführt, dass vor einem Schiedsgericht primär starke Indikatoren, zum Beispiel die Arbeitslosenquote, eine erfolgreiche Aktivierung wahrscheinlich machen würden.
+Als zusätzlichen Punkt, der in der Detailberatung thematisiert und von mir kommentiert wird, hat die Kommission die Schutzklausel um eine Lenkungsabgabe ergänzt. Ein zentraler Aspekt der Diskussion war die staatspolitische Dimension der sogenannten Ausgleichsmassnahmen, die von der Kommission als Damoklesschwert bezeichnet wurden. Es wurde hinterfragt, inwiefern dies einen Eingriff in die direkte Demokratie darstellte. Der Bundesrat argumentierte, dass Ausgleichsmassnahmen ein Standardinstrument in fast allen Freihandelsabkommen seien und die neue Regelung im Vergleich zum aktuellen Status quo sogar einen Gewinn an Rechtssicherheit bedeute. Abschliessend wurden weitere Detailfragen geklärt, auf die wir in der Beratung der einzelnen Artikel zurückkommen werden.
+Damit bin ich am Ende meines Eintretensvotums angelangt. Die SPK-S musste kein Eintreten beschliessen, da dies für das gesamte Paket bereits von der APK-S beschlossen worden war.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was will meine Minderheit? Es wurde gesagt, es sind hier zwei Artikel betroffen. Beim einen Artikel bin ich in der Mehrheit, aber beim anderen in der Minderheit. Was ich grundsätzlich will, ist, dass alle, die in unser Land einwandern und einen legalen Aufenthaltstitel erhalten möchten, neben einem Pass oder einer Identitätskarte auch einen Strafregisterauszug aus ihrem Heimatland vorweisen müssen. Ich erinnere Sie daran: Der Ständerat hat in der Sommersession, also noch vor wenigen Wochen, der </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was will meine Minderheit? Es wurde gesagt, es sind hier zwei Artikel betroffen. Beim einen Artikel bin ich in der Mehrheit, aber beim anderen in der Minderheit. Was ich grundsätzlich will, ist, dass alle, die in unser Land einwandern und einen legalen Aufenthaltstitel erhalten möchten, neben einem Pass oder einer Identitätskarte auch einen Strafregisterauszug aus ihrem Heimatland vorweisen müssen. Ich erinnere Sie daran: Der Ständerat hat in der Sommersession, also noch vor wenigen Wochen, der Motion Chiesa 26.3229, "Keine Aufenthaltsbewilligungen für Kriminelle", mit 26 zu 11 Stimmen zugestimmt. Diese fordert die nötigen Gesetzesanpassungen, damit für die Erteilung einer Aufenthaltsbewilligung auch Strafregisterauszüge aus dem Herkunfts- und Heimatstaat beigezogen werden. Die gleichlautende Motion 26.3130 wurde im Nationalrat, auch in der Sommersession, mit 121 zu 70 Stimmen angenommen. Meine Minderheit möchte nun genau dieses von beiden Räten sehr deutlich angenommene Anliegen im Rahmen dieser Gesetzesberatung umsetzen. Das ist heute gängige Praxis im Kanton Tessin, und auch der Kanton Graubünden hat aufgrund verschiedener Vorkommnisse in den Südtälern zu dieser Praxis gewechselt; dies im Speziellen zur Bekämpfung von organisierter Kriminalität.
+Wir beraten nun im Rahmen des AIG über die innerschweizerische Umsetzung des aufdatierten Personenfreizügigkeitsabkommens. Dieses Abkommen wird neu mit der sogenannten Integrationsmethode umgesetzt. Es beinhaltet einige wichtige Neuerungen, so eine Ausweitung beim Familiennachzug und vor allem im Rahmen der Übernahme der Unionsbürgerrichtlinie den neuen Aufenthaltsstatus Daueraufenthalt. Mit der neuen Vergabe des Daueraufenthaltes können EU-Bürgerinnen und -Bürger, welche sich fünf Jahre in unserem Land aufhalten, das Daueraufenthaltsrecht beantragen. Damit werden sie, und damit auch ihre Familien, für immer in unserem Land bleiben können, ausser sie werden straffällig. Gerade vor diesem Hintergrund scheint es mir und meiner Minderheit zentral zu sein, dass wir genauer klären, wer in unser Land kommt. Denn was wir nicht wollen, und ich hoffe, dass wir uns hier alle einig sind, ist, dass Leute in unser Land kommen, die bereits in ihren Heimat- und Herkunftsstaaten kriminell sind oder waren. Wir alle in der Schweiz müssen für viele Bereiche immer wieder einen Straf- und Betreibungsregisterauszug vorlegen. So muss ich zum Beispiel zur Führung meines Restaurants alle fünf Jahre dem Gemeinderat meiner Wohngemeinde einen Strafregister- und einen Betreibungsregisterauszug sowie ein Handlungsfähigkeitszeugnis einreichen. Auf dieser Basis erteilt der Gemeinderat mir dann die Bewilligung zum Führen eines Restaurants. In der Kommission wurden einige andere Beispiele genannt, wo überall Strafregisterauszüge erforderlich sind. Wir prüfen also in ganz vielen Bereichen in unserem Land, ob ein Strafregisterauszug erforderlich ist. Aber wir prüfen nicht, ob Personen, die in unser Land kommen, in ihren Herkunftsländern einen Eintrag im Strafregister haben.
+Bislang konnte ein Strafregisterauszug nur bei Verdacht eingefordert werden. Aber was ist ein Verdacht? Die Vergabe von Aufenthaltsbewilligungen gerade an EU- und EFTA-Bürgerinnen und -Bürger ist ja eigentlich ein Massengeschäft, da wird kaum jeder Fall genau geprüft. Daher braucht es hier verschärfte Vorgaben. Wir diskutieren im Rahmen dieser Anpassung beim Ausländer- und Integrationsgesetz (AIG) über zusätzliche Anforderungen, wer unter welchen Titeln in unser Land kommt.
+In Artikel 13 Absatz 2 des AIG steht heute: "Die zuständige Behörde kann einen Strafregisterauszug aus dem Herkunfts- und Heimatstaat sowie weitere für das Verfahren notwendige Dokumente verlangen." Mit der vorliegenden Änderung des AIG wird nun in Zukunft Artikel 13 für EU- und EFTA-Bürgerinnen und -Bürger nicht mehr gelten. Das wurde uns in der Kommission so erläutert. Daher ist jetzt - das scheint mir noch wichtig zu sein - die Aufteilung in Artikel 13 und Artikel 15a vorgenommen worden. Neu wird für EU-Bürgerinnen und -Bürger "nur noch" Artikel 15a gelten. Bei Artikel 13 beantragt die Mehrheit - und das befürworte auch ich, da gibt es keine Minderheit -, dass für Drittstaatsangehörige neu ein Strafregisterauszug eingefordert werden soll. Ich möchte aber, dass wir diesen auch mit Blick auf die Gleichbehandlung bei EU- und EFTA-Bürgerinnen und -Bürgern einfordern, da diese die grosse Masse der Personen sind, die in unser Land kommen. Es ist für mich nicht ersichtlich, warum wir hier jetzt in zwei Klassen unterteilen und die eine bevorzugen. Von Drittstaatsangehörigen fordern wir es, von Zuwanderern über die Personenfreizügigkeit nicht.
+Ich beantrage daher, diese Kann-Bestimmung auch bei Artikel 15a durch eine Muss-Bestimmung zu ersetzen. Der Antrag der Mehrheit ist nach wie vor zu schwammig und zu unklar und löst das Problem nicht.
+Ich erlaube mir, noch auf ein Argument einzugehen. Es wird nun argumentiert, dieses eine zusätzliche Dokument würde zu mehr Bürokratie führen. Sogar die Kantone haben uns geschrieben: "Eine systematische Sicherheitsüberprüfung aller eingehenden Gesuche wäre im Vollzug nicht zu bewältigen, zumal die zuständigen kantonalen Behörden derzeit bereits stark mit Fragen im Zusammenhang mit Asylverfahren und Schutzstatus S ausgelastet sind." Diese Argumentation überrascht mich, aber sie treibt mich auch stark um und erweckt grosse Sorge. Denn, kurz gesagt, heisst dies, dass die Kantone, weil sie mit den Asylverfahren und dem Schutzstatus S schon genug zu tun haben, die restlichen Aufenthaltstitel - und das sind ja verhältnismässig viel, viel mehr - nicht mehr sorgfältig überprüfen können. So nehmen wir im Kauf, dass Menschen, die in ihren Heimatländern straffällig waren, legal in unser Land einwandern. Dabei kommt es doch gar nicht zu mehr Bürokratie. Es ist einfach ein zusätzliches Dokument, das der Antragsteller einreichen muss, also neben einem Pass oder einer Identitätskarte auch noch einen Strafregisterauszug. Nicht die Schweizer Behörde muss diesen auftreiben, sondern der Antragsteller. Und wenn dieses Dokument, der Strafregisterauszug, leer ist - und das hoffen wir ja bei den meisten -, ist alles okay. Wenn jedoch eine Person, die Einträge im Strafregister hat, in die Schweiz kommen will, müssen wir wirklich genauer hinschauen.
+Dies wird in Zukunft aufgrund der neuen Unionsbürgerrichtlinie wesentlich wichtiger. Auch wenn uns der Bundesrat in den nächsten Minuten weismachen will, dass er bei dieser Richtlinie viele Ausnahmen aushandeln konnte, wird dennoch vieles gelockert, insbesondere beim Familiennachzug. Wer fünf Jahre als EU-Bürgerin oder -Bürger in unserem Land lebt - worauf wir im Zusammenhang mit dem Daueraufenthaltsrecht noch zurückkommen werden -, kann ein Daueraufenthaltsrecht beantragen und wird unser Land nie mehr verlassen müssen.
+In diesem Zusammenhang erscheint es mir zentral, dass wir von diesen Personen neben einem Pass auch einen Strafregisterauszug ihres Heimatlandes verlangen; wenn schon Zuwanderung, dann in unseren Arbeitsmarkt. Was wir jedoch auf keinen Fall wollen, ist die Zuwanderung krimineller Personen.
+Vor diesem Hintergrund bitte ich Sie, meinem Antrag zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fässler Daniel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte einleitend ebenfalls darauf hinweisen, dass wir vor drei Monaten in diesem Rat die Motion Chiesa 26.3229 gutgeheissen haben, und zwar mit einem klaren Verhältnis von 26 zu 11 Stimmen bei 5 Enthaltungen. Sie verlangt erstens von allen Personen, welche in der Schweiz eine Aufenthaltsbewilligung beantragen, einen Strafregisterauszug zu verlangen, und zweitens, dass Personen, bei denen die Prüfung ihres Strafregisterauszuges ergibt, dass sie eine Gefahr darstellen, kein Aufenthaltsrecht e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich möchte einleitend ebenfalls darauf hinweisen, dass wir vor drei Monaten in diesem Rat die Motion Chiesa 26.3229 gutgeheissen haben, und zwar mit einem klaren Verhältnis von 26 zu 11 Stimmen bei 5 Enthaltungen. Sie verlangt erstens von allen Personen, welche in der Schweiz eine Aufenthaltsbewilligung beantragen, einen Strafregisterauszug zu verlangen, und zweitens, dass Personen, bei denen die Prüfung ihres Strafregisterauszuges ergibt, dass sie eine Gefahr darstellen, kein Aufenthaltsrecht erhalten. Wir haben diese Motion im Wissen darum gutgeheissen, dass die Forderung sowohl Personen aus Drittstaaten als auch Personen aus EU/EFTA-Ländern betrifft. Wir haben die Entscheidung im Wissen um die Begründung der ablehnenden Stellungnahme des Bundesrates getroffen, dass diese Forderung in Bezug auf EU/EFTA-Staatsangehörige gegen das Freizügigkeitsabkommen verstösst.
+Drei Monate später geht es nun darum, auch Tatsachen folgen zu lassen. Bei Artikel 13 AIG macht die Kommission das: In Abweichung zum Entwurf des Bundesrates, der beim geltenden Recht bleiben möchte, beantragt Ihnen die Staatspolitische Kommission mit Absatz 2, dass die Behörden bei Drittstaatsangehörigen nicht nur einen Strafregisterauszug verlangen können, sondern einen Strafregisterauszug verlangen müssen. Vor allem bekommen die Behörden mit Absatz 4, der neu eingefügt werden soll, die klare Vorgabe, dass der Aufenthalt zu verweigern ist, wenn sich aus der Prüfung des Strafregisterauszuges oder anderer Unterlagen ergibt, dass die betreffende Person eine Gefahr darstellt. Das steht heute so nicht im Gesetz. Dazu liegt kein Minderheitsantrag vor. Ich bin gespannt, wie der Bundesrat sich dazu äussert und ob er sich mit der entsprechenden Ergänzung des Ausländer- und Integrationsgesetzes einverstanden erklärt.
+Nun stellt sich die Frage, wie wir mit EU- und EFTA-Staatsangehörigen umgehen. Das erste Beispiel ist eigentlich ein Paradebeispiel dafür, in welcher Situation wir uns befinden. Vor drei Monaten haben wir noch eigenständig gesagt: Wir wollen auch bei EU- und EFTA-Staatsangehörigen, dass ein Strafregisterauszug verlangt wird. Drei Monate später werden wir nun zu entscheiden haben, wie wir auf die Information reagieren, dass es gegen das Freizügigkeitsabkommen verstösst, wenn wir die neuen Bestimmungen jetzt wirklich in das Gesetz schreiben und konkret umsetzen. Es wird dann jene geben, die sagen: Gut, dann tun wir das nicht, wir distanzieren uns von der Motion, wir machen einen Kniefall vor dem Freizügigkeitsabkommen und verzichten darauf, eigenständig Gesetzgebung zu betreiben. Das ist eigentlich das erste Paradebeispiel, das wir hier haben.
+Auch ich liefere Ihnen eine Anekdote. Ich habe vor einem Jahr meinen Eintrag im Anwaltsregister des Kantons St. Gallen in jenes des Kantons Appenzell-Innerhoden verlegt. Ich kann Ihnen sagen, was ich vorlegen musste: Ich musste einen Betreibungsregisterauszug und selbstverständlich auch einen Strafregisterauszug vorlegen. Zudem musste ich noch eine Bestätigung der Kindes- und Erwachsenenschutzbehörde vorlegen, dass keine Verdachtsmomente vorliegen, die mich als handlungs- und urteilsunfähig erscheinen liessen. Das ist also sogar die Praxis bei Anwälten, wenn ein Eintrag im Anwaltsregister vorgenommen oder geändert werden soll. 
+Und wir diskutieren jetzt darüber, ob wir zur Gewährleistung der Sicherheit in unserem Land auch von EU- und EFTA-Staatsangehörigen einen Strafregisterauszug verlangen wollen. Wichtig ist: Es geht nicht nur um EU- und EFTA-Staatsangehörige, sondern es geht auch um Familienangehörige von EU- und EFTA-Staatsangehörigen, die aus Drittstaaten kommen. Auch diese würden gemäss dem Entwurf des Bundesrates keinen Strafregisterauszug vorlegen müssen. 
+Ich empfehle Ihnen, hier bei der Entscheidung zu bleiben, die wir vor drei Monaten gefällt haben. Ja, das wird die EU nicht freuen. Der EU-Ministerrat wird entscheiden müssen, ob er deswegen das Vertragswerk mit der Schweiz in die Schublade legt oder ob er daran festhält. Ich meine, wir sollten unsere Souveränität nicht aufgeben, und das ist ein erster Testfall. 
+Bitte stimmen Sie bei Artikel 15a Absatz 6 mit der Minderheit.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich beginne mit der Frage, weshalb das Einfordern von Strafregisterauszügen nicht in diesem Paket ist. Die Antwort ist einfach: Das war nicht Teil des Verhandlungsmandates, und es entspricht auch nicht der heutigen Praxis. Im Rahmen des heutigen Personenfreizügigkeitsabkommens verlangen wir keine Strafregisterauszüge. Es gibt Ausnahmen: Im Kanton Tessin, oder wenn Sicherheitshinweise vorliegen, werden immer Strafregisterauszüge verlangt - aber es entspricht nicht unserer Praxis.
+Herr Schwander: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich beginne mit der Frage, weshalb das Einfordern von Strafregisterauszügen nicht in diesem Paket ist. Die Antwort ist einfach: Das war nicht Teil des Verhandlungsmandates, und es entspricht auch nicht der heutigen Praxis. Im Rahmen des heutigen Personenfreizügigkeitsabkommens verlangen wir keine Strafregisterauszüge. Es gibt Ausnahmen: Im Kanton Tessin, oder wenn Sicherheitshinweise vorliegen, werden immer Strafregisterauszüge verlangt - aber es entspricht nicht unserer Praxis.
+Herr Schwander: Sollte eines Tages das Thema aufkommen, dass wir das wirklich wollen, dann wären wir mit diesem Paket besser bedient, weil wir dann einen Streitschlichtungsmechanismus hätten und dies allenfalls mit der EU aushandeln könnten. 
+Weshalb vertritt der Bundesrat die Meinung, dass die Variante der Mehrheit für die Sicherheit unserer Bevölkerung besser ist? Ich möchte das kurz ausführen. In Artikel 13 geht es nur um die Drittstaatsangehörigen. Für Freizügigkeitsberechtigte aus EU/EFTA-Staaten gilt dann eben der neue Artikel 15a. Bei Artikel 13 beantragt die SPK-S, dass die zuständigen Behörden beim Bewilligungs- und Anmeldeverfahren systematisch einen Strafregisterauszug aus dem Herkunfts- und Heimatstaat sowie weitere für das Verfahren notwendige Dokumente einfordern sollen. Das ist eine Neuerung, die eingeführt würde. Wir können nachvollziehen, dass ein Bedürfnis nach verstärkten Kontrollen besteht. Der Bundesrat hat aber bereits in seiner Stellungnahme zu den gleichlautenden Motionen Chiesa 26.3229 und 26.3130 der SVP-Fraktion, "Keine Aufenthaltsbewilligungen für Kriminelle", geschrieben, es wäre zielführender, könnten die zuständigen Behörden - das heisst insbesondere die Kantone - weiterhin nach ihrem Ermessen entscheiden, wann sie einen Strafregisterauszug einholen. 
+Verschiedene Kantone verlangen ihn bereits heute systematisch. Zudem haben viele Kantone im Gesuchsformular für eine Ausländerbewilligung eine Selbstdeklaration standardisiert. Gesuchstellende müssen also angeben, ob sie in der Schweiz oder im Ausland strafrechtlich verurteilt wurden. Ausserdem werden im Zemis standardisierte Sicherheitsabfragen durchgeführt. Drittstaatsangehörige werden insbesondere im SIS, im Ripol sowie im System von Interpol abgefragt. Die systematische Pflicht wäre also ein zusätzlicher administrativer Aufwand für die Kantone. Der Bundesrat empfiehlt den Änderungsantrag zu Artikel 13 Absatz 2 deshalb zur Ablehnung. Er hat das immer wie geschildert gehandhabt, und die Kantone sind ja auch nicht erfreut darüber.
+Die SPK-S beantragt ausserdem, Artikel 13 um einen Absatz 4 zu ergänzen, wonach das Aufenthaltsrecht verweigert wird, wenn eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit vorliegt. Dieser Absatz 4 hält lediglich fest, was bereits heute schon gilt. Aus Sicht des Bundesrates kann dieser Absatz 4 angenommen werden. 
+Der neue Artikel 15a regelt nun die Pflichten von Staatsangehörigen der EU-Mitgliedstaaten und ihren Familienangehörigen, die sich länger als drei Monate in der Schweiz aufhalten. Er regelt zudem die Pflichten der Grenzgängerinnen und Grenzgänger, die während mehr als drei Monaten in der Schweiz arbeiten. 
+Eine Minderheit der SPK beantragt, dass systematisch ein Strafregisterauszug aus dem Herkunfts- und Heimatstaat einverlangt wird. Dieser Antrag ist abzulehnen, da er gegen das FZA verstösst. Ein Strafregisterauszug darf bei freizügigkeitsberechtigten Personen nur einverlangt werden, wenn ernsthafte Anhaltspunkte bestehen, die es rechtfertigen, einen Strafregisterauszug zum Schutz der öffentlichen Ordnung und Sicherheit einzuholen.
+Es ist zudem wichtig, zu erwähnen, dass das Einverlangen von Strafregisterauszügen nur ein Teil des Sicherheitsdispositives darstellt. Strafregister sind in der Regel erst von praktischem Nutzen, wenn eine Person rechtskräftig strafrechtlich verurteilt wurde. Andere relevante Informationen sind in der Regel darin nicht sichtbar.
+An dieser Stelle möchte ich auch noch das Schreiben der KdK vom 24. September an den Ständerat erwähnen, welches der Bundesrat in Kopie erhielt. Das Anliegen kommt aus der Vollzugsperspektive und scheint mir daher wichtig. Ich zitiere: "So hätten allfällige systematische Strafregisterauszüge, die im Rahmen des Bewilligungs- und Anmeldeverfahrens des Ausländer- und Integrationsgesetzes für Bürgerinnen und Bürger der EU eingeführt würden, einen unverhältnismässigen Aufwand für die Kantone zur Folge und dürften darüber hinaus ohnehin nur schwer mit dem FZA vereinbar sein."
+Der Bundesrat und die Mehrheit der SPK-S sehen deshalb eine andere und, wie wir denken, bessere Lösung vor. Diese knüpft an das heutige System an. Bereits heute prüfen die Behörden bei einer Anmeldung automatisch Ripol und Interpol-Abfragen. In besonderen Verdachtsfällen überprüfen sie weitere Datenbanken. Damit sieht man, ob nach einer Person gefahndet wird oder diese die Sicherheit und Ordnung gefährden könnte. Wenn eine Datenbank sicherheitsrelevante Hinweise gibt, machen die Migrationsbehörden eine vertiefte Prüfung. Ergibt diese Überprüfung, dass die betroffene Person eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit darstellt, so wird ihr das Aufenthaltsrecht nach dem FZA verweigert.
+Hinzu kommt nun der Antrag der Mehrheit Ihrer Kommission. Die Mehrheit der SPK-S schlägt einen neuen Artikel 15abis vor, der den sicherheitspolitischen Bedenken Rechnung trägt und gleichzeitig FZA-kompatibel ist. Das wäre ein gangbarer Weg. Mit diesem Antrag sind die kantonalen Behörden verpflichtet, zu überprüfen, ob EU-Staatsangehörige sowie ihre Familienangehörigen eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit darstellen. Wie sie diese Pflicht erfüllen, entscheiden die kantonalen Behörden unter Berücksichtigung der konkreten Umstände. Denkbar wäre die Selbstdeklaration, wonach die Personen angeben müssen, ob sie strafrechtlich verurteilt worden sind oder ein Strafverfahren gegen sie hängig ist. Liegt ein Verdachtsfall vor, so können die zuständigen Behörden einen Strafregisterauszug einverlangen.
+Gemeinsam mit den erwähnten Abfragen verschiedener Datenbanken wäre dies ein umfassendes Dispositiv. Aus Sicht des Bundesrates ist das wirksamer. Dabei gilt aber festzuhalten, dass auch der Antrag der Mehrheit zu einem grösseren Verwaltungsaufwand führen würde. Deshalb empfehlen die Kantonsregierungen im erwähnten Schreiben der KdK, Artikel 15abis Absatz 3 AIG mittels einer Kann-Formulierung anzupassen. Der Bundesrat hat in der Kommission jeweils auch auf den Vollzugsaufwand verwiesen. In diesem Sinne kann ich die Haltung der KdK nachvollziehen. Der Minderheitsantrag zur Anpassung von Artikel 15a Absatz 6 ist aber klar abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Folgenden geht es um das Kernstück des Ausländer- und Integrationsgesetzes, und zwar um die Schutzklausel. Der Bundesrat hat ja dieses Verhandlungsergebnis bereits öffentlich dargelegt und wertet es als grossen Erfolg, dass wir eine Schutzklausel etablieren und das im Ausländer- und Integrationsgesetz festlegen können. Die folgenden Artikel beziehen sich also auf die Umsetzung dieser Schutzklausel im innerstaatlichen Recht. 
+Bei Artikel 21b Absatz 1 geht es um die Frage, welchen Spielraum der</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Im Folgenden geht es um das Kernstück des Ausländer- und Integrationsgesetzes, und zwar um die Schutzklausel. Der Bundesrat hat ja dieses Verhandlungsergebnis bereits öffentlich dargelegt und wertet es als grossen Erfolg, dass wir eine Schutzklausel etablieren und das im Ausländer- und Integrationsgesetz festlegen können. Die folgenden Artikel beziehen sich also auf die Umsetzung dieser Schutzklausel im innerstaatlichen Recht. 
+Bei Artikel 21b Absatz 1 geht es um die Frage, welchen Spielraum der Bundesrat bei der Aktivierung der Schutzklausel hat. Die Kommissionsmehrheit hat entschieden, dass der Bundesrat weiterhin einen Ermessensspielraum haben soll. Die Kann-Formulierung bleibt, was bedeutet, dass der Bundesrat die Schutzklausel anrufen kann, aber nicht dazu verpflichtet ist, selbst wenn Probleme vorliegen würden. Damit will die Kommission vermeiden, dass die Schweiz durch einen Automatismus in einen Konflikt mit der EU gerät, ohne vorher die gesamtwirtschaftlichen Interessen abgewogen zu haben. Zudem soll die Konsultation mit den Kantonen, den Sozialpartnern und den parlamentarischen Kommissionen sichergestellt bleiben. Ein Automatismus würde diese demokratischen Abläufe und Prozesse faktisch wertlos machen. 
+Hierzu liegt aber noch der Minderheitsantrag Friedli Esther vor. Frau Ständerätin Friedli fordert eine verpflichtende Formulierung, wonach der Bundesrat unter bestimmten Voraussetzungen einen Antrag zu stellen habe. Ihr Argument ist, dass der Bundesrat die bestehende Schutzklausel bisher ja nie genutzt habe und man ihn daher gesetzlich zwingen müsse, bei schwerwiegenden Problemen in einer Region oder Branche aktiv zu werden. Die Minderheit möchte verhindern, dass der Bundesrat entscheiden kann, ob er tätig wird oder nicht; daher will sie ihn verpflichten. 
+Das Stimmenverhältnis in der Kommission war: 7 Stimmen für den Entwurf des Bundesrates, 5 Stimmen für den Antrag Friedli Esther und 1 Enthaltung. 
+Ich gehe davon aus, dass die Minderheitssprecherin selber dazu noch reden wird.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bischof Pirmin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir haben hier wieder eine Kernneuerung, die in die Umsetzungsgesetzgebung eingefügt werden soll. Ich bin überzeugt, dass diese Neuerung auch ein wesentlicher Gegenstand der Volksabstimmung bzw. des Abstimmungskampfs sein wird.
+Die Kommissionssprecherin der SPK-S hat ausgeführt, was die Idee dieser neuen Lenkungsabgabe ist: Es soll erreicht werden, dass in Zeiten hoher Arbeitslosigkeit - sei es gesamtschweizerisch, sei es in einzelnen geografischen Bereichen der Schweiz, sei es in einzelnen Bran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir haben hier wieder eine Kernneuerung, die in die Umsetzungsgesetzgebung eingefügt werden soll. Ich bin überzeugt, dass diese Neuerung auch ein wesentlicher Gegenstand der Volksabstimmung bzw. des Abstimmungskampfs sein wird.
+Die Kommissionssprecherin der SPK-S hat ausgeführt, was die Idee dieser neuen Lenkungsabgabe ist: Es soll erreicht werden, dass in Zeiten hoher Arbeitslosigkeit - sei es gesamtschweizerisch, sei es in einzelnen geografischen Bereichen der Schweiz, sei es in einzelnen Branchen, sei es bei Vorliegen einer Kombination aus diesen drei Aspekten - verhindert wird, dass ausländische Personen einschliesslich EU-Angehörige als Arbeitnehmende in die Schweiz kommen.
+Die APK-S befasste sich sehr eingehend mit dieser Frage und hiess den Antrag der SPK-S, eine solche Lenkungsabgabe einzuführen, mit 5 zu 3 Stimmen bei 5 Enthaltungen gut. Die Lenkungsabgabe soll in Bezug auf EU-Angehörige und Drittstaatenangehörige erhoben werden. Wenn sie in Bezug auf EU-Angehörige erhoben wird, darf sie gemäss dem Abkommen nur erhoben werden, sofern die Schutzklausel angerufen wurde, wie wir das vorhin gerade beschlossen haben. Bei Drittstaatenangehörigen gilt diese Voraussetzung nicht, da sie nicht unter das Freizügigkeitsabkommen und nicht unter das Paket der Bilateralen III fallen.
+Abgabepflichtig soll bei unselbstständig Erwerbenden der Arbeitgeber sein, bei selbstständig Erwerbenden der selbstständig Erwerbende und bei volljährigen Familienangehörigen von unselbstständig Erwerbenden der unselbstständig erwerbende Einwandernde. Nichterwerbstätige fallen ebenfalls unter diese Regelung, ebenso volljährige Familienangehörige von Nichterwerbstätigen. Kinder, also nicht volljährige Zuwandernde, fallen nicht unter diese Regelung.
+Der Abgabesatz ist in der Vorlage nur teilweise geregelt. Festgelegt ist ein Mindestabgabesatz von 4000 Franken pro Jahr, und zwar für Selbstständige, Unselbstständige und Nichterwerbstätige. Für volljährige Familienangehörige wurde ein Mindestabgabesatz von 2000 Franken festgelegt. Der Bundesrat hat im Übrigen die Möglichkeit, per Verordnungsrecht die Höhe der Abgabe festzulegen. Nach oben ist die Abgabe nicht begrenzt. In der Kommission wurde diskutiert, dass die Bemessungsgrundlage für den Bundesrat wohl die Höhe der Arbeitslosigkeit in einem bestimmten Bereich, einer bestimmten Region oder einer bestimmten Berufsgattung und wahrscheinlich auch die Höhe des Gehalts der einwandernden Person sein würde: Je höher das Einkommen, desto höher die Abgabe; je höher die Arbeitslosigkeit in einem bestimmten Bereich, desto höher die Abgabe.
+Die Abgabeforderung wird fällig erstmalig bei Ausstellung eines Aufenthaltsdokumentes nach dem FZA und bei Drittstaatenangehörigen bei erstmaliger Bewilligungserteilung. Die Gesetzgebung sieht auch vor, in Artikel 21c Absatz 3 Litera b, dass in den Folgejahren die Abgabe wieder fällig wird. Es ist also nicht eine einmalige Abgabe, sondern sie würde - um Wirkung zu erzielen und bei gleichbleibender Arbeitslosigkeit und weiter aktivierter Schutzklausel - im Falle von EU-Angehörigen wiederholt anfallen.
+Die zuständige Behörde meldet dem SEM die abgabepflichtigen Personen, und der Ertrag - die Kommissionssprecherin hat das gesagt - wird an die Bevölkerung zurückerstattet, immer unter Abzug der Vollzugskosten. Kantone und Gemeinden würden also vorweg für ihre Kosten entschädigt, und der Rest würde dann an die Bevölkerung rückerstattet. Wie die Rückerstattung erfolgt, hat der Bundesrat in der Verordnung zu regeln, das sehen Sie in Artikel 21c Absatz 8 Litera e, Art und Verfahren der Verteilung an die Kantone: Die öffentlich-rechtlichen Körperschaften oder Private, die das durchführen könnten, sind durch den Bundesrat festzulegen. Der Bundesrat kann Ausnahmen festlegen. Die Ausnahmen sind im Gesetz nicht definiert. Das hat in der Kommission auch zu Diskussionen Anlass gegeben. Der Bundesrat ist relativ frei in der Festlegung von Ausnahmen. Diskutiert wurde etwa die Möglichkeit, Studierende oder Teile der Studierenden in der Schweiz auszunehmen. Der Bundesrat hat hier keine gesetzlichen Rahmenbedingungen festgelegt. Insgesamt schliesst sich die APK hier der SPK an, in der Überzeugung, dass die Einführung einer solchen Zuwanderungsabgabe im Abstimmungskampf mitentscheidend sein kann.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Artikel 13, 15a und 15abis des Ausländer- und Integrationsgesetzes haben einen Zusammenhang.
+Die Kommission hat sich intensiv mit der Frage befasst, wie die Sicherheitsprüfungen bei der Erteilung von Aufenthaltsbewilligungen verschärft werden können, um die Zuwanderung straffälliger Personen effektiv zu verhindern. Im Zentrum stand die Forderung, die Einforderung von Strafregisterauszügen aus dem Herkunftsstaat von einer blossen Möglichkeit, also einer Kann-Bestimmung, in eine zwingende Pfli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Artikel 13, 15a und 15abis des Ausländer- und Integrationsgesetzes haben einen Zusammenhang.
+Die Kommission hat sich intensiv mit der Frage befasst, wie die Sicherheitsprüfungen bei der Erteilung von Aufenthaltsbewilligungen verschärft werden können, um die Zuwanderung straffälliger Personen effektiv zu verhindern. Im Zentrum stand die Forderung, die Einforderung von Strafregisterauszügen aus dem Herkunftsstaat von einer blossen Möglichkeit, also einer Kann-Bestimmung, in eine zwingende Pflicht, eine Muss-Bestimmung zu überführen. Ziel war es, eine schweizweit einheitliche Praxis zu etablieren und die Sicherheitslücken zu schliessen, die durch unterschiedliche kantonale Handhabungen entstehen.
+In der Beratung wurde ein Spannungsfeld zwischen dem legitimen Wunsch nach maximaler Sicherheit und den zwingenden Verpflichtungen aus dem Freizügigkeitsabkommen deutlich. Bundesrat und Verwaltung haben uns als Kommission darauf hingewiesen, dass eine systematische Einforderung von Strafregisterauszügen bei allen EU- und EFTA-Staatsangehörigen - das wäre Artikel 13 - als Generalverdacht gewertet würde. Dies stünde im Widerspruch zu den Abkommensverpflichtungen und würde die EU dazu veranlassen, die Gesamtbalance des gesamten Pakets der Bilateralen III infrage zu stellen. Das sei ein völkerrechtswidriger Automatismus im Ausländer- und Integrationsgesetz und könne somit die Inkraftsetzung der gesamten bilateralen Beziehungen gefährden.
+Um diesen Zielkonflikt aufzulösen hat die Kommission dann - ich rede immer von der Mehrheit der Kommission, ich gehe nachher noch kurz auf die Minderheit ein - ein Modell erarbeitet, das die Sicherheit erhöht, ohne die völkerrechtliche Stabilität zu opfern; das sind die Artikel 15a und 15abis. Die Mehrheit der Kommission spricht sich für eine Lösung aus, welche die Handlungsfähigkeit der Kantone stärkt und gleichzeitig die Rechtsfolgen präzisiert. Es geht um eine Flexibilität bei der Dokumentenbeschaffung. Die Behörden erhalten eine explizite Kompetenz, Strafregisterauszüge einzufordern. Damit wird der Spielraum für die Kantone gewahrt, in risikobehafteten Konstellationen konsequent vorzugehen, während die Konformität mit dem Freizügigkeitsabkommen gewahrt bleibt; dazu gehören die Sicherung in Datenbanken und verschärfte Rechtsfolgen.
+Die Kommission hat die Konsequenzen einer festgestellten Gefährdung präzisiert. Wenn die Überprüfung ergibt, dass eine Person eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit darstellen kann, kann das Aufenthaltsrecht eingeschränkt oder verweigert werden.
+Diesem Artikel 15abis stimmte die Kommission mit 7 zu 6 Stimmen bei 0 Enthaltungen zu. 
+Eine Minderheit der Kommission hält diese Lösung für unzureichend. Sie fordert deshalb in Artikel 15a Absatz 6 weiterhin, dass von Staatsangehörigen der EU-Mitgliedstaaten systematisch ein gültiges, anerkanntes Reisepapier sowie ein Strafregisterauszug verlangt werden muss. Damit soll eine strikte Bringschuld der Zuwanderer etabliert werden, um eine lückenlose Sicherheitsprüfung ohne administrativen Mehraufwand für die Verwaltung zu garantieren. Das bezieht sich auf Artikel 15a und betrifft also Staatsangehörige von EU-Mitgliedstaaten. 
+Jetzt gehe ich zu Artikel 13 über, der für Drittstaatenangehörige gilt. Da im Bereich der Drittstaaten keine Bindung durch das Freizügigkeitsabkommen besteht, konnte die Kommission hier eine deutlich strengere Regelung festlegen, die eine lückenlose Prüfung sicherstellen soll. Es geht um die Einführung einer zwingenden Dokumentenpflicht in Absatz 2. Die Kommission hat dort die Bestimmung verschärft; die zuständige Behörde soll neu zwingend einen Strafregisterauszug aus dem Herkunfts- oder Heimatstaat sowie weitere für das Verfahren notwendige Dokumente einfordern. Damit wird die Dokumentenpflicht für Drittstaatenangehörige von einer Ermessensentscheidung in eine gesetzliche Pflicht überführt. 
+Dann zur zwingenden Verweigerung des Aufenthaltes in Absatz 4: Ergänzend zum geltenden Recht möchte die Kommission einen neuen Absatz 4 einfügen, der die Rechtsfolge klar regelt. Er lautet: "Ergibt die Überprüfung, dass die betroffene Person eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit darstellt, so wird ihr der Aufenthalt verweigert." Diesem Antrag stimmte die Mehrheit der Kommission zu.
+Ich komme zum Fazit: Die Kommission ist mehrheitlich überzeugt, mit diesem Modell eine Lösung gefunden zu haben, die sowohl den sicherheitspolitischen Anforderungen als auch den aussenpolitischen Notwendigkeiten gerecht wird. Durch die Differenzierung zwischen EU- und EFTA-Bürgerinnen und -Bürgern und Drittstaatenangehörigen wird einerseits die geschuldete Vertragstreue gegenüber der EU, wie sie von der Verwaltung und auch vom Bundesrat sehr dezidiert betont wurde, gewahrt, und es wird andererseits dort, wo es rechtlich möglich ist, eine Verschärfung vorgenommen. Die Kombination aus zwingender Dokumentenpflicht und klarer Verweigerungsfolge bei Drittstaatenangehörigen sowie die präzisierte Rechtsfolge bei EU-Bürgern stellen sicher, dass die Kantone über eine starke gesetzliche Grundlage verfügen, um Personen mit kriminellem Hintergrund konsequent vom Aufenthalt in der Schweiz auszuschliessen. 
+Die Kommissionsmehrheit empfiehlt dem Rat daher, diese Lösung zu unterstützen; die Minderheit wird ihre Lösung selber noch vorstellen. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caroni Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorab freue ich mich sehr, dass die Idee einer Lenkungsabgabe Zustimmung in den beiden Kommissionen fand, und, wie ich spüre, jetzt auch grundsätzlich von Skeptikern hier drinnen. Sie ist mit dem Freizügigkeitsabkommen konform, das hat der Bundesrat im erwähnten Bericht ausgeführt. Sie ist auch verfassungskonform, sofern man das ganze Geld zurückverteilt - wie man es auch tut. Sie setzt richtige Anreize, nämlich, dass Schweizer Arbeitgeber sich überlegen, ob sie das Potenzial im Inland besser au</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorab freue ich mich sehr, dass die Idee einer Lenkungsabgabe Zustimmung in den beiden Kommissionen fand, und, wie ich spüre, jetzt auch grundsätzlich von Skeptikern hier drinnen. Sie ist mit dem Freizügigkeitsabkommen konform, das hat der Bundesrat im erwähnten Bericht ausgeführt. Sie ist auch verfassungskonform, sofern man das ganze Geld zurückverteilt - wie man es auch tut. Sie setzt richtige Anreize, nämlich, dass Schweizer Arbeitgeber sich überlegen, ob sie das Potenzial im Inland besser ausschöpfen können. Sie setzt auch Anreize für diejenigen, die zuwandern, und sie kompensiert gegenüber der betroffenen Bevölkerung in einem gewissen Ausmass, im Ausmass eben dieser Abgabe, allfällige Nachteile, die sie durch die Migration erleiden. Am Donnerstag übrigens, als kleiner Teaser, werden Sie dann noch Motionen auf dem Tisch haben, die diese Lenkungsabgabe auch ausserhalb einer Schutzklausel allgemein fordert. In diesem Sinne freue ich mich und empfehle, dass man das so verabschiedet, genau wie beantragt. 
+Ich gehe aber gerne noch kurz auf drei, vier Fragen ein, die seitens des Bundesrates schon präventiv und auch von Frau Wasserfallen aufgeworfen wurden. Eine Frage war, warum man diese Abgabe nicht nur einmal, sondern mehrfach erhebt. Es schiene mir falsch, sie nur einfach zu erheben. Wenn Sie zum Beispiel irgendwo eine Kurtaxe zahlen oder wenn Sie in ein Hotel gehen, dann zahlen Sie pro Zeit, die Sie dort verbringen und während der Sie die Infrastruktur mit nutzen, und nicht einfach einmalig. Und wenn Sie das nur einmalig täten, bestünde ja der umgekehrte Anreiz, dann für diese einmal bezahlte Abgabe möglichst ewig zu bleiben, damit Sie aus dieser Abgabe, die Sie bezahlt haben, möglichst viel rausholen. Aber Migration ist ja schlussendlich die Nettozuwanderung, also haben Anreize zur Rückwanderung auch etwas für sich. Wer aber länger bleiben möchte, sollte entsprechend noch länger zahlen. Nach einer gewissen Zeit kann das dann auslaufen. Das sind meine Bemerkungen zum Thema Mehrfacherhebung.
+Dann zur Administration: Wo soll man die Abgabe erheben? Ich lege Ihnen gerne offen, dass mein ursprünglicher Antrag darauf zielte, sie bei den Arbeitnehmern zu erheben. Das wäre einfach und konsequent gewesen. Alle Abgaben wären immer bei derjenigen Person erhoben worden, die ins Land kommt, die auch die Infrastruktur hier nutzt und die hier arbeiten will. Das wäre wiederum wie bei einer Kurtaxe. Diese bezahlt auch immer diejenige Person, die kommt. Es wurde dann gesagt, wir sollten die Abgabe besser bei den Arbeitgebern ansiedeln, dann hätten diese die Anreize, im Inland besser zu rekrutieren. Aber hierzu muss man sagen - das steht auch im Bericht und ist ökonomisch ohnehin klar -: Es kommt wirtschaftlich nicht darauf an, bei wem Sie die Abgabe technisch erheben. Am Schluss ist diese zusätzliche Abgabe immer Teil der Lohnverhandlungen zwischen den Parteien, und sie wird sich ziemlich genau immer gleich verteilen, egal bei wem Sie sie erheben. Wenn Sie sie beim Unternehmen erheben, wird es sein Lohnangebot etwas dämpfen. Wenn Sie sie beim Arbeitnehmer erheben, wird es teilweise seine Lohnanforderungen etwas nach oben schrauben. Das kommt etwa auf dasselbe raus. Aber administrativ hätte es den Vorteil gehabt, wenn man es beim Arbeitnehmer erfasst, dass Sie das Problem von Bundesrat Jans gerade nicht hätten, nämlich, dass sie im zweiten, dritten und vierten Jahr nicht mehr wissen, wer jetzt der Abgabepflichtige ist, bei wem er jetzt arbeitet. Es wäre immer die gleiche Person erfasst, egal wo sie arbeitet. Das wäre noch eine Idee für den Zweitrat, wenn man sich Sorgen darüber macht, wo man die Abgabe im Jahr zwei, drei und vier erheben kann. Sicher sollte man nicht den Schluss daraus ziehen, die Abgabe dann einfach nicht mehr zu erheben, weil man nicht weiss, wer gerade der Arbeitgeber ist.
+Frau Wasserfallen gebe ich gerne noch eine kurze Antwort zur Frage, wie man auf die Höhe der Beträge kam. Von der Verwaltung kam der Einwand, wenn man das komplett dem Bundesrat überlassen würde, ohne eine Mindestgrenze, dann könnte die Abgabe im Extremfall reinen Bagatellcharakter haben, rein symbolisch sein. Dann könnte man sie nicht mehr als Lenkungsabgabe taxieren, und gemäss Verwaltung wären wir dann verfassungsmässig nicht mehr kompetent, eine solche Abgabe ohne jegliche Wirkung einzuführen. Das war der Hinweis der Verwaltung, weshalb im Gesetz eine Mindestabgabe stehen müsste. Für die Höchstgrenze wurde nichts vorgeschlagen, und die Verwaltung wurde dann auch gebeten, eine Zahl vorzuschlagen. Diese Zahlen kamen also aus der Verwaltung. Es ist keine Magie, aber es sollte eine Zahl sein, die man irgendwie spürt, die einem aber auch nicht abhält, weil sie in prohibitiver Höhe ist.
+Mein letzter Punkt betrifft das Familienleben, um das es beim Einzelantrag Wasserfallen Flavia auch geht. Im Bericht des Bundesrates hierzu steht, dass man bei dieser Personengruppe auch fiskalische Argumente diskutieren kann. "Diese dürften jedoch nicht dazu führen, dass der grundrechtlich geschützte Anspruch auf familiäres Zusammenleben faktisch ausgehöhlt wird." Wenn also diese Familienabgaben jetzt exorbitant hoch wären, dann würde man dieses Zusammenleben faktisch aushöhlen. Beliebig hoch dürfen sie nicht sein, und genau das haben wir abgebildet.
+Wir haben gesagt, für kleine Köpfe, also für alle Personen unter 18 Jahren, kostet es null Franken, und das werden die allermeisten im Familiennachzug sein. Nur für den Fall, dass jemand einen Ehegatten mitbringt oder im Ausnahmefall andere erwachsene Familienangehörige, soll eine Abgabe fällig sein, und da wollen wir 50 Prozent Rabatt darauf gegeben. Wir verlangen also nur 2000 Franken. Wir haben dies extra abgestuft unter Berücksichtigung des Familiennachzugs. 
+Wenn es für erwachsene Familienangehörige auch null Franken kosten würde, wie es schon für die Kinder gilt, würde das seltsame Anreize setzen. Würde das erwachsene Kind nämlich selbstständig in die Schweiz kommen und arbeiten, wäre es ja als Arbeitnehmer hier und müsste es mindestens 4000 Franken zahlen. Wenn das erwachsene Kind aber nicht arbeitet und als Familiennachzug dabei ist, würde es plötzlich null Franken kosten. Das schien mir etwas seltsam, und von daher glaube ich, dass die Abstufung, die wir beantragen und die wir als Vorschlag der Verwaltung so entgegengenommen haben - 4000 Franken und dann 2000 Franken und dann null Franken -, sachgerecht ist. 
+In diesem Sinne biete ich Sie, den beiden Kommissionen zu folgen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artikel 41d gewährt EU-Staatsangehörigen das Recht auf Daueraufenthalt, wenn sie sich während fünf Jahren rechtmässig als selbstständig oder unselbstständig Erwerbstätige in der Schweiz aufgehalten haben. Dabei werden Zeiträume von sechs Monaten oder mehr nicht angerechnet, in denen EU-Staatsangehörige und ihre Familienangehörigen vollständig auf Sozialhilfe angewiesen sind. Das Daueraufenthaltsrecht wird nur auf Antrag geprüft. Es ist nicht mit der Niederlassungsbewilligung zu verwechseln, für </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artikel 41d gewährt EU-Staatsangehörigen das Recht auf Daueraufenthalt, wenn sie sich während fünf Jahren rechtmässig als selbstständig oder unselbstständig Erwerbstätige in der Schweiz aufgehalten haben. Dabei werden Zeiträume von sechs Monaten oder mehr nicht angerechnet, in denen EU-Staatsangehörige und ihre Familienangehörigen vollständig auf Sozialhilfe angewiesen sind. Das Daueraufenthaltsrecht wird nur auf Antrag geprüft. Es ist nicht mit der Niederlassungsbewilligung zu verwechseln, für die ausschliesslich das AIG gilt und die eine Voraussetzung für eine Einbürgerung darstellt. 
+Die SPK-S und die APK-S beantragen, diese Bestimmung mit einem zusätzlichen Absatz zu ergänzen. Wenn jemand ein Daueraufenthaltsrecht beantragt, sollen die Migrationsbehörden genauer prüfen, ob tatsächlich eine Erwerbstätigkeit ausgeübt wurde oder ob es sich nur um eine geringfügige nebensächliche Tätigkeit handelte, zum Beispiel eine Teilzeitarbeit von höchstens 50 Prozent, oder um eine Tätigkeit im Rahmen des Personalverleihs und ob gleichzeitig Sozialhilfe bezogen wurde. Wir können diese Anträge unterstützen. 
+Der Antrag der Minderheit Friedli Esther ist hingegen abzulehnen. Es ist FZA-widrig, wenn das Daueraufenthaltsrecht beim Bezug von Sozialhilfe oder Arbeitslosengeldern generell ausgeschlossen wird. EU-Staatsangehörige, die unfreiwillig arbeitslos sind, behalten während des Bezugs von Arbeitslosentaggeldern ihren Status als Erwerbstätige. Das ist so in der Unionsbürgerrichtlinie geregelt und gilt bereits unter dem geltenden Freizügigkeitsabkommen.
+Wie schon gesagt, zählen sechs Monate oder mehr mit vollständiger Sozialhilfeabhängigkeit nicht zur Fünfjahresfrist für den Erwerb des Daueraufenthaltsrechts. Ein Bezug von Sozialhilfe führt zu einem Unterbruch in der Berechnung. Die Frist beginnt aber nicht wieder bei Null. Der Antrag der SPK und der APK deckt auch die Sozialhilfe ab. So soll das Recht auf Daueraufenthalt eingehend geprüft werden, wenn eine Person Sozialhilfe bezieht oder bezogen hat. 
+Hier möchte ich insbesondere nochmals darauf hinweisen, dass EU-Staatsangehörige eine höhere Erwerbsquote als die Schweizer Bevölkerung haben. Sie liegt bei 87,3 Prozent. Bei Schweizer Bürgerinnen und Bürgern ist sie tiefer, bei 84,8 Prozent. Eingewanderte aus der EU und der EFTA arbeiten auch weniger in Teilzeit als Schweizerinnen und Schweizer. Wir profitieren enorm von der Personenfreizügigkeit. Das erlaubt vielen Familienmitgliedern bei uns, erwerbstätigen Frauen und Männern, ihrem Wunsch nachzukommen, Teilzeit zu arbeiten. Das ermöglicht ihnen die Personenfreizügigkeit. 
+Wir haben auch keine Hinweise darauf, dass die Sozialhilfe Menschen in die Schweiz lockt. Es gibt innerhalb der EU keine Evidenz, dass Personen nur aufgrund der höheren Sozialhilfeleistungen in ein anderes Mitgliedland einwandern. Ein Leben in der Sozialhilfe ist kein erstrebenswerter Zustand, auch in der Schweiz nicht. Sozialhilfe wird nicht einfach so ausbezahlt. Wenn eine Person eine zumutbare Arbeitsstelle verweigert oder sich ohne triftigen Grund weigert, ihr Arbeitspensum zu erhöhen, kann die Sozialhilfe gekürzt werden. 
+Der Schweizer Bevölkerung und den EU-Staatsangehörigen gereicht es in diesem Sinn zum Vorteil, wenn wir die Personenfreizügigkeit entsprechend weiterführen. Die Zuwanderung aus der EU verlangsamt den demografischen Wandel, erfolgt klar in den Arbeitsmarkt. Insgesamt profitiert die Schweiz stark von der Personenfreizügigkeit. 
+Ich bitte Sie deshalb, den Minderheitsantrag abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe schon in der Eintretensdebatte ausgeführt, dass sich die Staatspolitische Kommission intensiv mit den ausländerrechtlichen Fragen des EU-Pakets befasst hat. Ein zentraler Punkt war dabei die Konkretisierung der Schutzklausel und die Frage, mit welchen Instrumenten der Bund reagieren kann, wenn schwerwiegende wirtschaftliche oder soziale Probleme auftreten.
+Die Kommission ist zum Schluss gekommen, dass die bestehenden Massnahmen ergänzt werden sollen, also dieser Werkzeugkasten erweitert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe schon in der Eintretensdebatte ausgeführt, dass sich die Staatspolitische Kommission intensiv mit den ausländerrechtlichen Fragen des EU-Pakets befasst hat. Ein zentraler Punkt war dabei die Konkretisierung der Schutzklausel und die Frage, mit welchen Instrumenten der Bund reagieren kann, wenn schwerwiegende wirtschaftliche oder soziale Probleme auftreten.
+Die Kommission ist zum Schluss gekommen, dass die bestehenden Massnahmen ergänzt werden sollen, also dieser Werkzeugkasten erweitert werden soll, um eine echte Lenkungswirkung zu erzielen. Deshalb beantragt Ihnen die Kommission mit 7 zu 0 Stimmen bei 6 Enthaltungen, hier ein wirkungsvolles neues Instrument, die Lenkungsabgabe, einzuführen.
+Was hat die Kommission konkret gemacht? Der Herr Bundesrat hat ja bereits eine grundsätzliche Beurteilung vorgenommen. Wir haben im Ausländer- und Integrationsgesetz wesentliche Ergänzungen vorgenommen. Wir haben die Lenkungsabgabe explizit als gesetzliche Grundlage eingeführt; somit ist das nachher im Rahmen der Schutzklausel eine zulässige Schutz- und Ausgleichsmassnahme.
+Dann hat die Kommission die Ausgestaltung der Abgabe in Artikel 21c definiert. Die Abgabe greift sowohl bei der Zulassung von Drittstaatsangehörigen als auch bei der Ausübung des Aufenthaltsrechts von EU- und EFTA-Staatsangehörigen; der Sinn dahinter ist eine klare Steuerung bzw. Lenkungswirkung. Zur Zahlungspflicht: Bei unselbstständig Erwerbstätigen wird die Abgabe direkt bei den Arbeitgebern erhoben; damit setzen wir den Anreiz dort, wo die Entscheidung über die Rekrutierung fällt. Selbstständig Erwerbstätige, Nichterwerbstätige sowie volljährige Familienangehörige tragen die Abgabe selbst. Die Höhe der Abgabe wird festgelegt. Um eine echte Wirkung zu erzielen, haben wir Mindestbeträge festgelegt: 4000 Franken pro Jahr und Person und 2000 Franken für volljährige Familienangehörige. Die Abgabe wird nicht nur einmalig erhoben; dazu hat der Herr Bundesrat bereits gesprochen, er lehnt diese wiederkehrende Abgabe im Namen des Bundesrates ab. Gemäss Antrag unserer Kommission ist die Abgabe nicht nur einmalig bei der Bewilligung, sondern jährlich zu erheben, solange die Schutzmassnahme in Kraft ist, und - das ist wichtig - um die verfassungsrechtliche Konformität zu gewährleisten, wird der Ertrag der Abgabe nach Abzug der Vollzugskosten gleichmässig an die Bevölkerung verteilt. Das heisst, dass es eine Lenkungsabgabe ist, und das ist verfassungsmässig möglich.
+Gleichzeitig haben wir in Artikel 120dbis eine Strafbestimmung eingefügt, damit dieses Instrument nicht leerläuft. Die Kommission ist überzeugt, dass wir mit diesem Paket ein Instrument geschaffen und eingefügt haben, das die Priorität auf das inländische Arbeitskräftepotenzial legt und gleichzeitig rechtlich und finanziell sauber gelöst ist.
+Ich beantrage Ihnen im Namen der Kommission, der Lenkungsabgabe in dieser Form zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans un monde mouvementé, alors que nous comptons nos alliés et cherchons à sécuriser nos relations avec l'espace économique qui rassemble la moitié de nos exportations, la Commission des transports et des télécommunications a traité la partie relative aux transports inclus dans les Bilatérales III. Le traitement des protocoles a été réalisé à l'occasion des séances de la commission des 16 avril, 21 mai et 13 août derniers.
+À cette occasion, elle a débattu et procédé à de nombreuses auditions d'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans un monde mouvementé, alors que nous comptons nos alliés et cherchons à sécuriser nos relations avec l'espace économique qui rassemble la moitié de nos exportations, la Commission des transports et des télécommunications a traité la partie relative aux transports inclus dans les Bilatérales III. Le traitement des protocoles a été réalisé à l'occasion des séances de la commission des 16 avril, 21 mai et 13 août derniers.
+À cette occasion, elle a débattu et procédé à de nombreuses auditions d'acteurs concernés, tels que des entreprises de transport, des syndicats et des groupes de défense de divers intérêts sectoriels. L'administration a également apporté de nombreuses réponses à un projet qui ne manquait pas de soulever certaines subtilités techniques et qui, je suis heureux de le dire, a largement convaincu la commission par l'habileté de la voie qui nous est proposée. Ce soutien s'exprime sans ambages, par 11 voix contre 2. Il y a trois minorités de M. Stark et de Mme Friedli, qui prendront la parole. Au fond, elles proposent simplement de ne faire aucun changement ; ce sont des minorités qui s'opposent à l'entier des modifications des trois lois.
+De manière générale, la commission considère que le partage de certaines approches et normes techniques avec un espace économique qui représente la moitié de la valeur de nos exportations doit, dans le contexte actuel, nous réjouir. Elles permettent à nos entreprises d'exporter et à nos concitoyens de voyager vers l'étranger avec nettement moins de complications que ce que l'absence d'accord créerait. Rejeter ce projet, c'est au contraire ajouter une dose importante de tâches administratives dans la vie de chacune et chacun de nos concitoyennes et concitoyens. Notre besoin de coordination est évident ; c'est notamment très clair pour les exportateurs de ce pays.
+La commission constate par ailleurs que la proposition pallie également le risque non négligeable d'application arbitraire en notre défaveur des accords actuels en formalisant le règlement des différends. Enfin, cette partie relative aux transports du dossier n'était pas à la base un souhait de la Suisse ; c'est l'Union européenne qui a souhaité l'inclure au programme. 
+Dans ce contexte, force est de constater que l'issue de la négociation est très positive. Dans certains cas, les ouvertures concrètes acceptées sont corsetées par des procédures que nous contrôlons largement. Dans d'autres, la reprise dynamique qui était réclamée pour l'ensemble a été abandonnée pour toute une série d'exceptions qui confèrent à nos institutions une marge de manoeuvre appréciable.
+Dans le domaine des transports en particulier, la position suisse est protégée et les exceptions sont exemptes de toute reprise de droit dynamique. Parmi celles-ci, on peut citer l'interdiction de circuler la nuit ou le dimanche pour les poids lourds, la limitation du poids des mêmes poids lourds, la possibilité de modifier la RPLP sans devoir modifier l'accord ou encore la non-extension de la capacité routière suisse dans les Alpes, conformément à la disposition constitutionnelle de l'initiative des Alpes.
+Je continue maintenant spécifiquement sur le protocole d'amendement de l'accord sur les transports terrestres. En sus des exceptions déjà mentionnées, plusieurs questions ont été soulevées au cours de la procédure quant aux conséquences de l'ouverture du marché suisse du trafic international de voyageurs dans le domaine des chemins de fer. La commission a été satisfaite des précisions qui ont pu lui être apportées. La préservation des plans d'utilisation du réseau et la priorité du trafic national et cadencé pour l'attribution des sillons écartent le risque d'une arrivée massive d'opérateurs étrangers en Suisse. Je le rappelle : très peu de sillons demeurent disponibles, ce qui exclut quasiment d'office le risque de changement important quant à l'exploitation du réseau. Par ailleurs, seul le trafic international est autorisé pour les compagnies européennes. Là aussi, cela restreint largement les possibilités d'implantation d'entreprises étrangères.
+Pour ces questions, la commission a constaté la mise en place prévue d'un monitoring suisse par le truchement de la Commission des chemins de fer (Railcom) et de l'OFT. Nous serons en mesure d'assurer que les termes de cet accord que nous avons revendiqué soient respectés.
+En revanche, quand un doute, bien qu'infime, existait, la commission a cherché à s'assurer que rien ne serait laissé au hasard dans la mise en oeuvre. La volonté de sécuriser l'interprétation future des dispositions des accords selon notre interprétation des textes a guidé l'action de la commission à travers deux sujets fondamentaux.
+D'abord, les aides d'État, qui ont effectivement été traitées par la Commission de l'économie et des redevances et par notre collègue Erich Ettlin, mais qui ont pris une place importante dans les débats, puisque c'est une question assez fondamentale dans le domaine des transports. La deuxième question a été la conformité de nos pratiques avec le droit des cartels de l'Union européenne. S'agissant des aides d'État, je ne redirai pas ce que notre collègue Erich Ettlin a dit mieux que moi.
+Dans le domaine des transports, il est quand même nécessaire de préciser que trois garanties importantes ont pu nous être données : cela ne concerne pas les aides actuelles, cela ne concerne pas les subventions aux transports publics à l'interne de la Suisse et cela concerne donc uniquement le transport international. Ainsi, concrètement, le financement de l'infrastructure ou les prêts de trésorerie que la Confédération alloue aux CFF ne sont en rien empêchés par les présents protocoles. De la même manière, des subventions relatives au trafic interne restent possibles, comme d'ailleurs les subventions aux aéroports régionaux ou à Skyguide. Les auditions menées par la commission ont permis de souligner que ces champs sont clairement exclus de l'accord.
+Le seul cas de figure que la commission a pu trouver où les règles pourraient s'appliquer, c'est si la Confédération décidait de subventionner une nouvelle ligne internationale de trains, comme on peut en entendre parler. Dans ce cas, la subvention devrait également être offerte à d'autres opérateurs.
+Pour les questions d'entente internationale entre compagnies de chemins de fer, une majorité souhaite modifier l'accord. J'y reviendrai donc dans la loi sur le transport de voyageurs, à son article 6 alinéa 6.
+Dans un second temps, la commission s'est également penchée sur le second protocole dont elle était saisie, qui modifie l'accord sur le transport aérien. Les auditions menées ont permis de souligner la grande importance de la mise à jour permise par le protocole pour le secteur aéronautique suisse. Il faut rappeler que l'entrée en vigueur de l'accord sur le transport aérien date de 2002. L'ancienne mouture de cet accord a certes posé des défis réglementaires à certaines entreprises, mais la Suisse a déjà été en mesure par le passé de négocier des dérogations. Il nous a notamment été permis d'utiliser des hélicoptères légers pour le secours en montagne des personnes accidentées, ce qui est interdit ailleurs dans l'Union européenne. L'intégration accrue dans le "decision shaping" et l'accès facilité aux agences européennes que permet le protocole d'accord élargit nos possibilités de trouver de telles solutions.
+Au-delà des règles générales, le protocole aura une incidence sur le secteur concerné. Les fournisseurs de services aéronautiques gagnent par exemple, à l'occasion de la modernisation de l'accord, le droit de cabotage dans l'Union européenne. Ce droit est réciproque, mais la commission a conclu que la taille de notre marché conduirait probablement à ce que peu de cabotage étranger en Suisse soit fait. D'ailleurs, nous avons d'ores et déjà accordé ce droit de cabotage en modifiant la loi fédérale sur l'aviation la semaine passée. Il reviendra au Conseil national de confirmer que la modification proposée est bien conforme à l'accord sur le transport aérien.
+L'impact global sur l'emploi est également ressorti des discussions de la commission : deux tiers des emplois du secteur aéronautique dépendent directement de l'étranger et de l'accès au marché par la reconnaissance des normes suisses. À l'inverse, le statu quo ne semblait pas envisageable. Un rejet fait largement craindre une perte assez massive d'emplois dans le secteur aéronautique. Cette perspective serait largement préoccupante pour nos savoir-faire industriels et pour les deux tiers des emplois du secteur qui dépendent du commerce avec l'Union européenne.
+Enfin, j'aimerais aborder plusieurs éléments que la commission a traités au regard des modalités de mise en oeuvre et de collaboration interinstitutionnelle. Un système d'alerte précoce permettant de signaler et d'accompagner les modifications de règlements européens, ce dès le début du processus, a notamment été confirmé. Cela devrait permettre d'intégrer au mieux le Parlement dans le processus. Les commissions concernées seront informées en amont du "decision shaping" afin d'assurer leur capacité d'intervention. Les cantons seront quant à eux inclus selon le modèle en vigueur pour les accords de Schengen/Dublin.
+Pour celles et ceux qui s'inquièteraient de l'inflation réglementaire que ces protocoles d'accord sur les transports feraient peser sur notre pays : les auditions ont permis de rappeler qu'une partie très substantielle est déjà intégrée depuis l'entrée en vigueur des accords en 2002. Pour le reste, les tendances en cours à Bruxelles ouvrent des perspectives réjouissantes. La Commission européenne cherche actuellement à simplifier la complexité des réglementations via les lois "Omnibus". La tendance est donc également positive de ce côté-là, qu'il s'agisse des aides d'État dans le domaine des transports ou des réglementations techniques.
+Je vous encourage donc à suivre l'avis de la commission et à accepter la version de la majorité. Je vous demande également d'adopter la proposition d'amendement qui confirme la sécurité juridique que nous souhaitons s'agissant des ententes et des entreprises concessionnées au niveau international. C'est là l'exemple de la marge de manoeuvre que nous conservons pour limiter d'éventuelles conséquences et maximiser notre intérêt pour notre prospérité et simplifier la vie de nos concitoyens.
+Finalement, Monsieur le président, permettez-moi d'apporter un mot sur les propositions de minorité qui ont été déposées : comme les minorités s'opposent à l'ensemble des lois, je n'aurai pas besoin de reprendre la parole, mon rapport ayant été fait.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Der Bundesrat schliesst sich dem Antrag der WAK und der APK an.[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Ziff. I Art. 21b [GZ]
+Antrag der Mehrheit SPK-S[GZ]
+Abs. 1-4, 7-11 [GZ]
+Zustimmung zum Entwurf des Bundesrates
+Abs. 5 [GZ]
+Der Bundesrat prüft mindestens einmal pro Jahr gestützt auf geeignete Indikatoren, insbesondere in den Bereichen der Zuwanderung, des Arbeitsmarkts, der sozialen Sicherheit, des Wohnungswesens und des Verkehrs, ob schwerwiegende wirtscha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Der Bundesrat schliesst sich dem Antrag der WAK und der APK an.[GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Ziff. I Art. 21b [GZ]
+Antrag der Mehrheit SPK-S[GZ]
+Abs. 1-4, 7-11 [GZ]
+Zustimmung zum Entwurf des Bundesrates
+Abs. 5 [GZ]
+Der Bundesrat prüft mindestens einmal pro Jahr gestützt auf geeignete Indikatoren, insbesondere in den Bereichen der Zuwanderung, des Arbeitsmarkts, der sozialen Sicherheit, des Wohnungswesens und des Verkehrs, ob schwerwiegende wirtschaftliche oder soziale Probleme nach Absatz 1 in der ganzen Schweiz, in einer bestimmten Region oder in einer bestimmten Branche vorliegen. Erreicht oder überschreitet die Nettozuwanderung gestützt auf das FZA oder die Zunahme der Beschäftigung von Grenzgängerinnen und Grenzgängern, der Arbeitslosigkeit oder des Sozialhilfebezugs einen vom Bundesrat festgelegten Schwellenwert, so muss der Bundesrat die Ergreifung von Massnahmen nach Absatz 6 prüfen. Ab Veröffentlichung der Daten entscheidet der Bundesrat innert vier Monaten über einen Antrag an den Gemischten Ausschuss gemäss Artikel 14a Absatz 1 FZA zur Aktivierung der Schutzklausel.
+Abs. 6[GZ]
+...
+e. eine Lenkungsabgabe gemäss Artikel 21c.
+[VS]
+Antrag der Minderheit SPK-S[GZ]
+(Friedli Esther, Engler, Gössi, Jositsch, Schwander)[GZ]
+Abs. 1 [GZ]
+... oder sozialen Problemen, so stellt der Bundesrat im Hinblick auf deren Beseitigung einen Antrag an den Gemischten Ausschuss gemäss Artikel 14a Absatz 1 FZA. Er kann ...
+[VS]
+Antrag APK-S[GZ]
+Abs. 1-4, 7-11[GZ]
+Zustimmung zum Entwurf des Bundesrates
+Abs. 5 [GZ]
+... eine entsprechende Prüfung vornehmen. Ab Veröffentlichung der Daten entscheidet der Bundesrat innert vier Monaten über einen Antrag an den Gemischten Ausschuss gemäss Artikel 14a Absatz 1 FZA zur Aktivierung der Schutzklausel.
+Abs. 6[GZ]
+...
+e. eine Lenkungsabgabe gemäss Artikel 21c.
+[VS]
+Ch. I art. 21b [GZ]
+Proposition de la majorité CIP-E[GZ]
+Al. 1-4, 7-11[GZ]
+Adhérer au projet du Conseil fédéral
+Al. 5 [GZ]
+Le Conseil fédéral évalue au moins une fois par année la présence de difficultés sérieuses d'ordre économique ou social au sens de l'alinéa 1 dans toute la Suisse ou dans une région ou une branche déterminée sur la base d'indicateurs appropriés, notamment dans les domaines de l'immigration, du marché du travail, de la sécurité sociale, du logement et des transports. Il examine la possibilité de prendre des mesures au sens de l'alinéa 6 lorsque l'immigration nette induite par l'ALCP, la croissance de l'emploi frontalier, la hausse du chômage ou l'augmentation du recours à l'aide sociale atteint ou dépasse un seuil qu'il a fixé. Dans les quatre mois suivant la publication des données, le Conseil fédéral décide d'adresser ou non au comité mixte une demande d'activation de la clause de sauvegarde conformément à l'article 14bis paragraphe 1 ALCP.
+Al. 6[GZ]
+...
+e. une taxe d'incitation selon l'article 21c.
+[VS]
+Proposition de la minorité CIP-E[GZ]
+(Friedli Esther, Engler, Gössi, Jositsch, Schwander)[GZ]
+Al. 1 [GZ]
+... ou une branche déterminées, le Conseil fédéral dépose une demande auprès ...
+[VS]
+Proposition CPE-E[GZ]
+Al. 1-4, 7-11 [GZ]
+Adhérer au projet du Conseil fédéral
+Al. 5 [GZ]
+... pour toute la Suisse. Dans les quatre mois suivant la publication des données, le Conseil fédéral décide d'adresser ou non au comité mixte une demande d'activation de la clause de sauvegarde conformément à l'article 14bis paragraphe 1 ALCP.
+Al. 6[GZ]
+...
+e. une taxe d'incitation selon l'article 21c.
+[VS]
+Ziff. I Art. 21c [GZ]
+Antrag WAK-S/APK-S[GZ]
+Al. 1 [GZ]
+Als Schutzmassnahmen oder Ausgleichsmassnahme im Sinne von Artikel 21b Absatz 6 kann der Bund eine Lenkungsabgabe erheben bei der Zulassung von Drittstaatsange hörigen sowie bei der Ausübung des Aufenthaltsrechts von mehr als drei Monaten nach dem FZA durch Staatsangehörige der EU-Mitgliedstaaten.
+Al. 1bis[GZ]
+Abgabepflichtig sind:
+a. die Arbeitgeber, für Personen mit einem Aufenthalt als unselbstständig Erwerbstätige;
+b. Personen mit einem Aufenthalt als unselbstständig Erwerbstätige, für ihre volljährigen Familien angehörigen;
+c. Personen mit einem Aufenthalt als selbstständig Erwerbstätige, für sich und ihre volljährigen Familienangehörigen;
+d. Personen mit einem Aufenthalt als Nichterwerbstätige, für sich und ihre volljährigen Familienangehörigen.
+Abs. 2[GZ]
+Der Abgabesatz beträgt pro Jahr und pro Person nach Absatz 1:
+a. für unselbstständig Erwerbstätige: mindestens 4000 Franken;
+b. für selbstständig Erwerbstätige: mindestens 4000 Franken;
+c. für Nichterwerbstätige: mindestens 4000 Franken;
+d. für volljährige Familienangehörige: mindestens 2000 Franken.
+Abs. 3[GZ]
+Die Abgabeforderung entsteht und wird fällig:
+a. mit der erstmaligen Ausstellung eines Aufenthaltsdokumentes nach dem FZA oder der erstmaligen Bewilligungserteilung;
+b. zu Beginn jedes folgenden Jahres, solange die Massnahme andauert.
+Abs. 4 [GZ]
+Die zuständige Behörde meldet dem SEM die abgabepflichtige Person unmittelbar nach der Ausstellung des Aufenthaltsdokumentes oder der Bewilligungserteilung.
+Abs. 5 [GZ]
+Das SEM bezieht die Abgabe bei der abgabepflichtigen Person.
+Abs. 6 [GZ]
+Der Ertrag der Abgabe wird ein schliesslich Zinsen nach Abzug der Vollzugskosten gleichmässig an die Bevölkerung verteilt.
+Abs. 7 [GZ]
+Das SEM betreibt Informations- und Dokumentationssysteme für die elektronische Durchführung von Verfahren nach diesem Artikel.
+Abs. 8[GZ]
+Der Bundesrat regelt:
+a. die Höhe der Abgabe, die geeignet ist, den jeweiligen mit der Anwendung des FZA verbundenen schwerwiegenden wirtschaftlichen oder sozialen Probleme entgegenzuwirken;
+b. das Verfahren für die Erhebung der Abgabe;
+c. die Zahlungsfrist;
+d. die Ausnahmen von der Abgabepflicht;
+e. Art und Verfahren der Verteilung; er kann die Kantone, öffentlich-rechtliche Körperschaften oder Private mit der Verteilung beauftragen;
+f. die Verfahren, die elektronisch durchgeführt werden.
+[VS]
+Antrag Wasserfallen Flavia[GZ]
+Abs. 1bis Bst. b[GZ]
+Streichen
+Abs. 1bis Bst. c[GZ]
+Personen mit einem Aufenthalt als selbstständig Erwerbstätige;
+Abs. 1bis Bst. d[GZ]
+Personen mit einem Aufenthalt als Nichterwerbstätige.
+Abs. 2 Bst. d[GZ]
+Streichen
+[VS]
+Ch. I art. 21c [GZ]
+Proposition CER-E/CPE-E[GZ]
+Al. 1 [GZ]
+Á titre de mesure de protection ou de mesure de rééquilibrage au sens de l'article 21b alinéa 6 la Confédération peut percevoir une taxe d'incitation lors de l'admission de ressortissants d'États tiers et lors de l'exercice, par des ressortissants des États membres de l'UE, du droit de séjour de plus de trois mois prévu par l'ALCP.
+Al. 1bis[GZ]
+Sont assujettis à la taxe :
+a. les employeurs des personnes qui séjournent en tant que travail leurs salariés ;
+b. les personnes qui séjournent en tant que travailleurs salariés, pour les membres de leur famille majeurs ;
+c. les personnes qui séjournent en tant que travailleurs indépendants, pour elles-mêmes et les membres de leur famille majeurs ;
+d. les personnes qui séjournent sans exercer d'activité lucrative, pour elles-mêmes et les membres de leur famille majeurs.
+Al. 2[GZ]
+Le montant annuel de la taxe par personne visée à l'alinéa 1 s'élève à :
+a. au moins 4000 francs pour les travailleurs salariés ;
+b. au moins 4000 francs pour les travailleurs indépendants ;
+c. au moins 4000 francs pour les personnes n'exerçant pas d'activité lucrative ;
+d. au moins 2000 francs pour les membres de la famille majeurs.
+Al. 3[GZ]
+La créance relative à la taxe prend naissance et devient exigible :
+a. dès la première délivrance d'un document de séjour prévu par l'ALCP ou le premier octroi d'une autorisation ;
+b. au début de chaque année suivante, tant que la mesure est en vigueur.
+Al. 4 [GZ]
+L'autorité compétente annonce la personne assujettie au SEM immédiatement après la délivrance du document de séjour ou l'octroi de l'autorisation.
+Al. 5 [GZ]
+Le SEM perçoit la taxe auprès de la personne assujettie.
+Al. 6 [GZ]
+Le produit de la taxe, intérêts compris, est réparti de façon égale au sein de la population après déduction des frais d'exécution.
+Al. 7 [GZ]
+Le SEM gère des systèmes d'information et de documentation pour la mise en oeuvre électronique des procédures définies dans le présent article.
+Al. 8[GZ]
+Le Conseil fédéral fixe :
+a. le montant de la taxe qui est adéquat pour remédier aux problèmes économiques ou sociaux graves liés à l'application de l'ALCP ;
+b. la procédure de perception de la taxe ;
+c. le délai de paiement ;
+d. les exceptions à l'obligation de payer la taxe ;
+e. les modalités et la procédure de répartition ; il peut charger les cantons, les collectivités de droit public ou des particuliers de la répartition ;
+f. les procédures qui sont effectuées par voie électronique.
+[VS]
+Proposition Wasserfallen Flavia[GZ]
+Al. 1bis let. b[GZ]
+Biffer
+Al. 1bis let. c[GZ]
+les personnes qui séjournent en tant que travailleurs indépendants ;
+Al. 1bis let. d[GZ]
+les personnes qui séjournent sans exercer d'activité lucrative.
+Al. 2 let. d[GZ]
+Biffer
+[VS]
+Ziff. I Art. 21b Abs. 1 - Ch. I art. 21b al. 1[GZ]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir befinden uns hier in einem sehr, sehr wichtigen Teil der Vorlage, bei einer Neuerung des Ausländer- und Integrationsgesetzes respektive der Aufdatierung des Personenfreizügigkeitsabkommens. Es ist nämlich die Übernahme, oder einige sagen die Teilübernahme, der Unionsbürgerrichtlinie der Europäischen Union. Hier geht es darum, dass Bürgerinnen und Bürger der Europäischen Union, die sich fünf Jahre in unserem Land aufhalten, ein Daueraufenthaltsrecht erlangen. Ich habe es vorhin schon gesagt: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir befinden uns hier in einem sehr, sehr wichtigen Teil der Vorlage, bei einer Neuerung des Ausländer- und Integrationsgesetzes respektive der Aufdatierung des Personenfreizügigkeitsabkommens. Es ist nämlich die Übernahme, oder einige sagen die Teilübernahme, der Unionsbürgerrichtlinie der Europäischen Union. Hier geht es darum, dass Bürgerinnen und Bürger der Europäischen Union, die sich fünf Jahre in unserem Land aufhalten, ein Daueraufenthaltsrecht erlangen. Ich habe es vorhin schon gesagt: Mit dem Daueraufenthaltsrecht wird man unser Land nie mehr verlassen, ausser man ist wirklich in hohem Mass straffällig. Alle anderen Personen werden in unserem Land bleiben.
+Es braucht für dieses Daueraufenthaltsrecht auch keine Erfüllung von Kriterien zur Integration. Man muss nicht einmal vorweisen, dass man eine Landessprache spricht. Also es ist eigentlich nur daran festgemacht, dass man fünf Jahre in unserem Land arbeitstätig ist. Ich komme danach dann noch dazu, was diese fünfjährige Arbeitstätigkeit wirklich bedeutet. 
+Kollege Fässler hat vorhin erwähnt, was das eigentlich bedeutet, und es ist mir schon wichtig, auch das noch einmal etwas auszuführen. Das hat nämlich auch sehr grosse Auswirkungen in Bezug auf den Familiennachzug. Zum Beispiel kommt ein Spanier, der mit einer Marokkanerin verheiratet ist, in die Schweiz. Er kann dann nicht nur seine Frau, seine Kinder und seine Eltern in die Schweiz nachkommen lassen, denn der Familiennachzug gilt auch für die marokkanischen Schwiegereltern und allfällige Stiefkinder. All diese Personen haben nach fünf Jahren das Recht auf Daueraufenthalt in unserem Land. Wir fördern den Familiennachzug für pflegebedürftige Angehörige und weitere Familienmitglieder ja sogar noch. Auch hier erwähne ich noch einmal das, was wir gestern diskutiert haben: Im Zusammenhang mit der dynamischen Rechtsübernahme wissen wir noch nicht, was die EU in Zukunft alles beschliessen wird, gerade in Bezug auf die Unionsbürgerrichtlinie oder auf den Familiennachzug.
+Der Bundesrat hat in seiner Botschaft ausgeführt, dass im Jahr 2021 fast 700 000 Personen in unserem Land das Anrecht auf ein Daueraufenthaltsrecht hatten. Fast 700 000 Personen! Und er sagt weiter, es wären dann pro Jahr zwischen 20 000 und 30 000, denn es ist ja jetzt dann einmal quasi die grosse Masse. Diese 700 000 Personen können das Daueraufenthaltsrecht beantragen. Das bedeutet, und das ist das Wichtige, dass sie auch Sozialhilfe beziehen können. Sie können Sozialhilfe beziehen, und es droht ihnen keine Ausweisung mehr.
+Angesichts dessen bin ich überzeugt: Das wird eine gewisse Sogwirkung haben, und es wird in zweierlei Hinsicht eine Sogwirkung haben. Zum einen wird die Schweiz noch attraktiver für Zuwanderung, und zum anderen gibt es einen gewissen Anreiz, dass man, wenn man fünf Jahre hier ist und gearbeitet hat, eigentlich gar nicht mehr arbeiten muss. Denn man weiss, man muss die Schweiz ja gar nicht mehr verlassen. Damit entfällt etwas der Anreiz, um zu arbeiten.
+Der Bundesrat hat dazu eine Untersuchung von Ecoplan in Auftrag gegeben, und auch der Bundesrat kommt zum Schluss, dass das Auswirkungen haben wird, und zwar vor allem Auswirkungen auf unsere Sozialversicherungen und Auswirkungen auf die Sozialhilfe. Die Studie sagt, dass pro Jahr - der "range" ist gross - zwischen 4000 bis 20 000 Personen mehr in die Sozialhilfe kommen könnten. Er rechnet mit Kosten von 50 bis über 100 Millionen Franken mehr pro Jahr, etwa 22 Millionen Franken mehr pro Jahr für die ALV, und es werden 7 bis 8 Millionen Franken mehr für die Ergänzungsleistungen sein. Der grösste Teil der Kosten wird ja auf die Gemeinden und die Kantone zukommen, im Bereich der Sozialhilfe. Also all diese Leute, die jetzt schon hier sind und dann das Daueraufenthaltsrecht beantragen können, haben danach Anrecht auf das volle Programm unseres Sozialversicherungssystems.
+Bei meinem Antrag geht es darum, wem wir dieses Daueraufenthaltsrecht erteilen und ob wir gewisse Einschränkungen vornehmen. Wir haben in der Kommission mehrfach sehr präzise nachgefragt, wie das denn eigentlich ist. Es heisst, man müsse fünf Jahre arbeiten. Aber in der Kommission wurde uns bestätigt, dass es eigentlich reicht, wenn eine Person zwischen drei und dreieinhalb Jahren arbeitet. Es ist nämlich so, dass man einen Teil davon auch arbeitslos sein kann, wenn man sich beim RAV meldet, und man kann sechs Monate lang Sozialhilfe beziehen. Ich sage es jetzt mal so: Man muss diese fünf Jahre irgendwie mit Arbeiten, Arbeitslosigkeit und auch noch etwas Sozialhilfe erreichen, und dann gilt man als arbeitstätig. Ich finde, das müssen wir schon berücksichtigen, wenn wir darüber sprechen, wem wir dieses Recht auf Daueraufenthalt erteilen.
+Es stellt sich die Frage, ob wir einer Person das Daueraufenthaltsrecht geben, die Sozialhilfe bezieht oder arbeitslos ist und diese fünf Jahre erreicht. Ich meine: nein. Es kann doch nicht sein, dass wir einer Person, von der wir jetzt schon wissen, dass sie in finanziellen Schwierigkeiten ist und es wahrscheinlich schwierig sein wird, dass sie sich und ihre Familie selbstständig ernähren und finanzieren kann, das Daueraufenthaltsrecht geben. Damit setzen wir ja den Anreiz, dass sie danach gar nicht mehr arbeiten muss, weil sie in unserem Land bleiben und Sozialhilfe beziehen kann.
+Deshalb ist meine Minderheit der Meinung: Wenn wir schon ein Daueraufenthaltsrecht vergeben, können wir es den Personen vergeben, die arbeiten - aber nicht Personen, die zum Zeitpunkt des Gesuchs arbeitslos sind. Es geht wirklich um den Zeitpunkt, in dem sie das Gesuch stellen. Es kann nicht sein, dass Personen, die arbeitslos sind oder Sozialhilfe beziehen, ein Gesuch für ein Daueraufenthaltsrecht stellen können. Ich glaube, es kann nicht im Sinne des Erfinders sein, dass wir diesen Personen ein Daueraufenthaltsrecht geben.
+Ich bitte Sie daher, meiner Minderheit zu folgen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bevor ich auf Artikel 21c und die Lenkungsabgabe zu sprechen komme, möchte ich ganz kurz zuhanden des Amtlichen Bulletins in Bezug auf Artikel 21b Absatz 5 festhalten, dass wir dort trotz der Differenz, die zwischen den Anträgen der SPK-S und der APK-S im Wortlaut besteht, der Formulierung der SPK-S gefolgt sind. Es gab darüber keine Abstimmung. Damit ist der Bundesrat, wenn er aufgrund seiner Prüfung feststellt, dass ein Schwellenwert überschritten ist, in der Pflicht, nicht einfach irgendwelch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bevor ich auf Artikel 21c und die Lenkungsabgabe zu sprechen komme, möchte ich ganz kurz zuhanden des Amtlichen Bulletins in Bezug auf Artikel 21b Absatz 5 festhalten, dass wir dort trotz der Differenz, die zwischen den Anträgen der SPK-S und der APK-S im Wortlaut besteht, der Formulierung der SPK-S gefolgt sind. Es gab darüber keine Abstimmung. Damit ist der Bundesrat, wenn er aufgrund seiner Prüfung feststellt, dass ein Schwellenwert überschritten ist, in der Pflicht, nicht einfach irgendwelche entsprechenden Massnahmen zu prüfen, sondern Massnahmen nach Absatz 6; dies zuhanden des Amtlichen Bulletins.
+Nun zur Lenkungsabgabe. Dazu vorweg zwei Feststellungen: Erstens habe ich in Diskussionen verschiedentlich festgestellt, dass die Leute - nicht in diesem Rat, aber ausserhalb - der Auffassung sind, man führe hier generell eine Lenkungsabgabe ein. Das ist nicht der Fall. Es handelt sich um eine Schutzmassnahme, die der Bundesrat ergreifen kann, wenn die Voraussetzungen dafür gegeben sind.
+Zweitens möchte ich bemerken, dass der Antrag der SPK-S auf einem Formulierungsvorschlag der Verwaltung basiert, der integral übernommen wurde. Diesen Formulierungsvorschlag arbeitete die Verwaltung im Auftrag der SPK-S aus.
+Ich beschränke mich auf zwei Themen. Zur Frage, wer bei unselbstständig Erwerbstätigen abgabepflichtig sein soll: Hier bin ich, anders als mein Vorredner, der Auffassung, dass es richtig ist, was die SPK-S und die APK-S beantragen, nämlich, dass der Arbeitgeber in die Pflicht genommen werden muss. Gerade die Arbeitgeber müssen sich bewusst sein, dass sie das inländische Arbeitskräftepotenzial, das vorhanden ist, wirklich stärker ausschöpfen müssen; sie sollen nicht aufgrund der Tatsache, dass sie ausländischen Arbeitnehmenden einen tieferen Lohn zahlen können, auf diese zurückgreifen.
+Es gibt dafür viele Beispiele. Man kann die Zuwanderungsstatistik mit der Arbeitslosenstatistik vergleichen, und dabei stellt man fest, dass gerade in Branchen, in denen die Arbeitslosigkeit ausserordentlich stark gestiegen ist, beispielsweise in der Finanz- und Beratungsbranche oder im IT-Bereich, eine aussergewöhnlich hohe Zuwanderung stattgefunden hat, obwohl umgekehrt die Arbeitslosigkeit in der Schweiz stark gestiegen ist. Ich glaube, hier tun wir gut daran, den Arbeitgebern das Signal zu geben, dass sie das inländische Arbeitskräftepotenzial stärker auszuschöpfen haben.
+Nun zum Einzelantrag Wasserfallen Flavia: Selbstverständlich haben wir über die Frage diskutiert, ob Familienangehörige einbezogen und verpflichtet werden sollen, ebenfalls eine Abgabe zu leisten - eine Abgabe, die notabene halb so hoch ist wie die Abgabe der Personen, die als Arbeitnehmende in die Schweiz kommen. Es lohnt sich vielleicht, sich zwei Dinge vor Augen zu führen: Wenn man sich die Jahresstatistik Zuwanderung 2025 anschaut, dann stellt man fest, dass damals 84 000 Personen aus EU/EFTA-Staaten in den Schweizer Arbeitsmarkt einwanderten. Darüber hinaus wanderten 22 000 Personen, also etwas mehr als ein Viertel dieser Anzahl, über den Familiennachzug ein, also nicht in den Arbeitsmarkt.
+Es ist davon auszugehen, dass nach dem neuen Regime, welches gelten wird, wenn dieser EU-Pakt angenommen wird, der Familiennachzug deutlich steigen wird, weil ein Daueraufenthaltsrecht auch für Familienangehörige wie Ehepartner, unmündige erwachsene Kinder, Eltern und sogar Schwiegereltern gilt, auch wenn diese nicht arbeitstätig sind; für Schwiegereltern gilt es jedoch nur, wenn sie unterstützungsbedürftig sind. All diese Familienangehörigen haben künftig einen selbstständigen Anspruch auf das Daueraufenthaltsrecht, mit allen Rechten, die daraus abgeleitet werden. In diesem Sinne sind sie eine eigenständige Kategorie von Personen, die gemäss Daueraufenthaltsrecht in die Schweiz einwandern können und dürfen. Also sollen auch sie von einer allfälligen Lenkungsabgabe umfasst werden, mit dem Privileg, dass die Abgabe für sie um 50 Prozent reduziert ist.
+In diesem Sinne bitte ich Sie, den beiden Kommissionen zu folgen und den Einzelantrag Wasserfallen Flavia abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'aimerais préciser que, dans la commission, on a effectivement essayé de se demander non pas seulement quelles pièces les personnes qui veulent venir s'établir en Suisse doivent montrer aux autorités qui décident ensuite de la possibilité de s'installer, mais surtout ce qu'on en fait. Toutes les propositions qui étaient faites visaient simplement à convenir qu'il faut amener ce document, cet extrait du casier judiciaire, mais personne ne semblait se préoccuper de savoir que devaient ensuite fai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J'aimerais préciser que, dans la commission, on a effectivement essayé de se demander non pas seulement quelles pièces les personnes qui veulent venir s'établir en Suisse doivent montrer aux autorités qui décident ensuite de la possibilité de s'installer, mais surtout ce qu'on en fait. Toutes les propositions qui étaient faites visaient simplement à convenir qu'il faut amener ce document, cet extrait du casier judiciaire, mais personne ne semblait se préoccuper de savoir que devaient ensuite faire les autorités cantonales de cette pièce. Quelle était la gradation ? Quel est le type de délit qui justifie un refus ? Toutes ces questions ne sont pas réglées. Or, ce sont elles qui sont les plus importantes.
+C'est dans ce sens que la majorité a travaillé, puisqu'elle propose au moins de convenir que quand il y a menace pour la sécurité, l'ordre ou la santé publics, le permis n'est pas donné. C'est ce qui compte. Savoir quelle systématicité on exige en matière de production de cette pièce est relativement secondaire par rapport à l'objectif qui est d'éviter que des personnes qui peuvent troubler gravement l'ordre public soient admises chez nous.
+C'est ce que la majorité a fait. Elle a précisé que cet examen doit être fait par les autorités cantonales et que les personnes concernées ont l'obligation de collaborer. S'il y a donc un soupçon de risque pour la sécurité, l'ordre ou la santé publics, les autorités cantonales peuvent demander des pièces, peut-être pas seulement l'extrait du casier judiciaire, mais d'autres également qui permettront d'instruire cette demande. Je crois que la majorité a fait une proposition pragmatique, compatible avec le traité de libre circulation et qui atteint l'objectif, qui est d'essayer de respecter la sécurité publique.
+Enfin, j'ajoute une dernière chose par rapport à ce qu'a dit M. Daniel Fässler : la question de savoir si nous pouvons légiférer ou pas en infraction avec l'Accord sur la libre circulation des personnes, ce n'est pas à cause de ce nouveau traité qu'on devrait se la poser. On se la serait également posée si l'on n'avait pas eu le nouveau traité à discuter. De manière générale, quand on signe un traité, on doit ensuite se demander si on le respecte encore ou si on ne le respecte plus et, si on ne le respecte plus, quelles seront les conséquences de l'autre partie, si on décide de s'affranchir du traité. Sur ce plan, il n'y a donc rien de nouveau par rapport à la situation actuelle.
+C'est la raison pour laquelle je vous invite à suivre la majorité de la commission.
 </t>
   </si>
 </sst>
@@ -2038,8 +2504,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I80" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I96" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I96"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -4623,6 +5089,466 @@
         <v>324</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>325</v>
+      </c>
+      <c r="B81" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" t="s">
+        <v>30</v>
+      </c>
+      <c r="H81" t="s">
+        <v>327</v>
+      </c>
+      <c r="I81" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>329</v>
+      </c>
+      <c r="B82" t="s">
+        <v>326</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>155</v>
+      </c>
+      <c r="E82" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" t="s">
+        <v>156</v>
+      </c>
+      <c r="G82" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>330</v>
+      </c>
+      <c r="I82" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>332</v>
+      </c>
+      <c r="B83" t="s">
+        <v>326</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>160</v>
+      </c>
+      <c r="E83" t="s">
+        <v>47</v>
+      </c>
+      <c r="F83" t="s">
+        <v>161</v>
+      </c>
+      <c r="G83" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>333</v>
+      </c>
+      <c r="I83" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>335</v>
+      </c>
+      <c r="B84" t="s">
+        <v>326</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>336</v>
+      </c>
+      <c r="E84" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" t="s">
+        <v>337</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>338</v>
+      </c>
+      <c r="I84" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>340</v>
+      </c>
+      <c r="B85" t="s">
+        <v>326</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>89</v>
+      </c>
+      <c r="E85"/>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" t="s">
+        <v>341</v>
+      </c>
+      <c r="I85" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>343</v>
+      </c>
+      <c r="B86" t="s">
+        <v>326</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
+        <v>155</v>
+      </c>
+      <c r="E86" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86" t="s">
+        <v>156</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>344</v>
+      </c>
+      <c r="I86" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>346</v>
+      </c>
+      <c r="B87" t="s">
+        <v>326</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>347</v>
+      </c>
+      <c r="E87" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" t="s">
+        <v>348</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>349</v>
+      </c>
+      <c r="I87" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>351</v>
+      </c>
+      <c r="B88" t="s">
+        <v>326</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>155</v>
+      </c>
+      <c r="E88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88" t="s">
+        <v>156</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
+        <v>352</v>
+      </c>
+      <c r="I88" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>354</v>
+      </c>
+      <c r="B89" t="s">
+        <v>326</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>355</v>
+      </c>
+      <c r="E89" t="s">
+        <v>116</v>
+      </c>
+      <c r="F89" t="s">
+        <v>356</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" t="s">
+        <v>357</v>
+      </c>
+      <c r="I89" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>359</v>
+      </c>
+      <c r="B90" t="s">
+        <v>326</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>89</v>
+      </c>
+      <c r="E90"/>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" t="s">
+        <v>360</v>
+      </c>
+      <c r="I90" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>362</v>
+      </c>
+      <c r="B91" t="s">
+        <v>326</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>155</v>
+      </c>
+      <c r="E91" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" t="s">
+        <v>156</v>
+      </c>
+      <c r="G91" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" t="s">
+        <v>363</v>
+      </c>
+      <c r="I91" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>365</v>
+      </c>
+      <c r="B92" t="s">
+        <v>326</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>165</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
+        <v>366</v>
+      </c>
+      <c r="I92" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>368</v>
+      </c>
+      <c r="B93" t="s">
+        <v>326</v>
+      </c>
+      <c r="C93" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" t="s">
+        <v>60</v>
+      </c>
+      <c r="E93" t="s">
+        <v>20</v>
+      </c>
+      <c r="F93" t="s">
+        <v>61</v>
+      </c>
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" t="s">
+        <v>369</v>
+      </c>
+      <c r="I93" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>371</v>
+      </c>
+      <c r="B94" t="s">
+        <v>326</v>
+      </c>
+      <c r="C94" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" t="s">
+        <v>160</v>
+      </c>
+      <c r="E94" t="s">
+        <v>47</v>
+      </c>
+      <c r="F94" t="s">
+        <v>161</v>
+      </c>
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
+        <v>372</v>
+      </c>
+      <c r="I94" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>374</v>
+      </c>
+      <c r="B95" t="s">
+        <v>326</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" t="s">
+        <v>336</v>
+      </c>
+      <c r="E95" t="s">
+        <v>20</v>
+      </c>
+      <c r="F95" t="s">
+        <v>337</v>
+      </c>
+      <c r="G95" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" t="s">
+        <v>375</v>
+      </c>
+      <c r="I95" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>377</v>
+      </c>
+      <c r="B96" t="s">
+        <v>326</v>
+      </c>
+      <c r="C96" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" t="s">
+        <v>280</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>35</v>
+      </c>
+      <c r="G96" t="s">
+        <v>30</v>
+      </c>
+      <c r="H96" t="s">
+        <v>378</v>
+      </c>
+      <c r="I96" t="s">
+        <v>379</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -339,7 +339,7 @@
 C'est précisément ce que vise ma motion[NB]: ne pas céder à la panique et ne pas imposer une technologie particulière, mais planifier la transition de manière progressive, coordonnée et fondée sur les risques. C'est un élément essentiel. Sans inventaire, nous ne pouvons pas piloter correctement une migration. C'est pourquoi la notion de cryptoagilité est particulièrement importante. Nos systèmes doivent être conçus de manière à pouvoir faire évoluer leurs mécanismes cryptographiques sans devoir tout reconstruire à chaque changement de standard.
 C'est une question de cybersécurité, mais également de bonne gestion des deniers publics. Si une migration anticipée peut être planifiée, une migration imposée dans l'urgence risque quant à elle d'être beaucoup plus coûteuse, plus complexe et plus risquée. La Suisse ne part heureusement pas de zéro. La Confédération a déjà identifié cette problématique et dispose de compétences importantes dans le domaine de la cybersécurité et de l'informatique. Ce qui manque encore, c'est précisément une vision nationale, commune, avec des responsabilités, des priorités et des échéances clairement définies.
 Nos partenaires internationaux avancent[NB]: l'Union européenne travaille sur la transition vers la cryptographie post-quantique, et les États-Unis, le Royaume-Uni, la France et l'Allemagne ont également engagé des démarches. La motion prévoit à juste titre des échéances différenciées, une priorité aux cas à haut risque d'ici 2030, puis une transition progressive des autres systèmes critiques ou sensibles d'ici 2035, en fonction de la maturité des standards et de l'interopérabilité. Cette approche permet d'éviter deux erreurs. La première serait de ne rien faire en attendant que la menace soit certaine. La seconde serait d'imposer aujourd'hui des investissements massifs dans des technologies qui pourraient encore évoluer. La bonne réponse se situe entre les deux[NB]: préparer maintenant, migrer progressivement et adapter les exigences sur le plan des risques.
-Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnaît l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
+Permettez-moi de revenir encore quelques instants sur l'avis du Conseil fédéral. Il reconnaît l'importance du sujet et je l'en remercie, mais il rejette le point relatif au soutien aux cantons, aux PME, aux entreprises et aux hautes écoles au motif que certaines mesures dépasseraient les compétences actuelles de la Confédération. Je me rallie à sa proposition et ne conteste pas le rejet de la lettre[NB]i. Je souhaite néanmoins, pour la clarté des délibérations et la mise en oeuvre à venir, préciser l'esprit de cette lettre[NB]i. Mon intention n'a jamais été de créer une compétence fédérale nouvelle ni de transférer à la Confédération une responsabilité qui incombe aux cantons, aux entreprises et aux hautes écoles en matière de cybersécurité, car la responsabilité individuelle de chaque acteur demeure entière. Sur ce point, je partage entièrement l'analyse du Conseil fédéral.
 Ce que visait la lettre i, c'est la coordination et non le soutien financier. Une transition vers la cryptographie post-quantique, conduite en ordre dispersé, sans référentiel commun ni interopérabilité, coûterait beaucoup plus cher à tous et affaiblirait la sécurité de l'ensemble. Je prends donc acte du fait que le Conseil fédéral, dans le cadre de ses compétences, assurera cette coordination, avec la mise à disposition de lignes directrices, de modèles d'inventaire, de tests d'interopérabilité et de retours d'expériences utiles aux cantons et à l'économie. Je forme le voeu que le rapport biennal, prévu à la lettre c, rende compte de la manière dont cette coordination est assurée afin que le Parlement puisse en suivre les effets.
 En résumé et pour conclure, la cryptographie post-quantique n'est peut-être pas encore une urgence visible pour la population. Mais, précisément parce que la transition prendra du temps, il est nécessaire d'agir aujourd'hui avant que cela ne devienne une urgence.
 Je vous invite donc à soutenir ma motion sans la lettre i, comme le demande le Conseil fédéral, et je vous en remercie.
@@ -719,7 +719,7 @@
     <t xml:space="preserve">Amoos Emmanuel</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le conseiller fédéral, je vous remercie de nous avoir expliqué la pratique. Ne serait-il pas plus simple de répondre aux questions telles qu'elles sont rédigées ? Je repose ma question : le Conseil fédéral peut-il nous dire si le SRC, le SEM ou Fedpol étaient informés de la tenue de ce "camp fédéral" ?
+    <t xml:space="preserve">Monsieur le conseiller fédéral, je vous remercie de nous avoir expliqué la pratique. Ne serait-il pas plus simple de répondre aux questions telles qu'elles sont rédigées[NB]? Je repose ma question[NB]: le Conseil fédéral peut-il nous dire si le SRC, le SEM ou Fedpol étaient informés de la tenue de ce "camp fédéral"[NB]?
 </t>
   </si>
   <si>
@@ -964,7 +964,8 @@
     <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est d</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est donc possible juridiquement. Ma question rejoint un peu celle de mon prédécesseur. Pourquoi ne souhaitez-vous pas appuyer cette amélioration du système qui permettrait plus d'efficacité et ainsi une meilleure acceptation par la population de notre politique d'asile ?</t>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, cette motion donne la possibilité aux collaboratrices et aux collaborateurs du SEM d'obtenir des compétences dans le domaine de la détention administrative. Effectivement, on sait qu'un certain nombre de cantons n'utilisent qu'avec parcimonie cet instrument au détriment de l'efficacité du retour. Nous avons la possibilité d'améliorer un système pour augmenter l'efficacité de ces renvois. On sait que cette détention administrative a fonctionné par le passé. C'est donc possible juridiquement. Ma question rejoint un peu celle de mon prédécesseur. Pourquoi ne souhaitez-vous pas appuyer cette amélioration du système qui permettrait plus d'efficacité et ainsi une meilleure acceptation par la population de notre politique d'asile[NB]?
+</t>
   </si>
   <si>
     <t xml:space="preserve">420623</t>
@@ -994,7 +995,7 @@
     <t xml:space="preserve">Je vous remercie pour votre question, Monsieur Gaillard. Cette loi vise à interdire la vente à des personnes étrangères. La vente aux Suisses n'est pas concernée par la lex Koller. Même un Suisse domicilié à l'étranger peut acheter un appartement ou une maison en Suisse. Les Suisses ne sont pas concernés par cette loi. En revanche, le but de la motion est que la procédure d'autorisation soit applicable aux résidences principales, et non pas seulement aux résidences secondaires. Cela veut dire qu</t>
   </si>
   <si>
-    <t xml:space="preserve">Je vous remercie pour votre question, Monsieur Gaillard. Cette loi vise à interdire la vente à des personnes étrangères. La vente aux Suisses n'est pas concernée par la lex Koller. Même un Suisse domicilié à l'étranger peut acheter un appartement ou une maison en Suisse. Les Suisses ne sont pas concernés par cette loi. En revanche, le but de la motion est que la procédure d'autorisation soit applicable aux résidences principales, et non pas seulement aux résidences secondaires. Cela veut dire que le Français résidant en Suisse avec un permis B ou l'Allemand résidant en Suisse avec un permis B, et non pas avec des permis C - mais c'est la question qui est encore à poser à l'auteur de la motion - seraient concernés par cette loi. Ils pourraient louer, mais ne pourraient pas acheter un appartement en Suisse. Reste à voir si, avec un permis d'établissement C, cela serait possible, mais avec un permis B, pour les Européens, cela ne serait plus possible - c'est le texte au chiffre 1 de la motion : non seulement les résidences secondaires, mais aussi les résidences principales. Relisez aussi le texte, cher collègue Gaillard.
+    <t xml:space="preserve">Je vous remercie pour votre question, Monsieur Gaillard. Cette loi vise à interdire la vente à des personnes étrangères. La vente aux Suisses n'est pas concernée par la lex Koller. Même un Suisse domicilié à l'étranger peut acheter un appartement ou une maison en Suisse. Les Suisses ne sont pas concernés par cette loi. En revanche, le but de la motion est que la procédure d'autorisation soit applicable aux résidences principales, et non pas seulement aux résidences secondaires. Cela veut dire que le Français résidant en Suisse avec un permis B ou l'Allemand résidant en Suisse avec un permis B, et non pas avec des permis C - mais c'est la question qui est encore à poser à l'auteur de la motion -, seraient concernés par cette loi. Ils pourraient louer, mais ne pourraient pas acheter un appartement en Suisse. Reste à voir si, avec un permis d'établissement C, cela serait possible, mais avec un permis B, pour les Européens, cela ne serait plus possible. C'est le texte au chiffre 1 de la motion[NB]: non seulement les résidences secondaires, mais aussi les résidences principales. Relisez aussi le texte, cher collègue Gaillard.
 </t>
   </si>
   <si>
@@ -1009,11 +1010,11 @@
   <si>
     <t xml:space="preserve">Au nom de la minorité de la Commission des institutions politiques, je vous propose d'adopter la motion Müller Damian 25.4521, "Permettre à n'importe quel canton d'exécuter un renvoi afin d'uniformiser l'application du droit fédéral". Le Conseil des États a adopté cette motion le 10 mars dernier avec une nette majorité, par 31 voix contre 10. Lors de son examen par notre Commission des institutions politiques, cette dernière, à une courte majorité, par 13 voix contre 12, a toutefois proposé de la rejeter. Les rapporteurs en ont expliqué les motifs.
 Cette motion charge le Conseil fédéral de modifier la législation fédérale afin que tout canton puisse exécuter une décision de renvoi prononcée par la Confédération ou une expulsion judiciaire entrée en force, même lorsqu'il n'est pas le canton initialement compétent. Elle prévoit également que, si nécessaire, le canton qui assume concrètement cette tâche puisse recevoir l'indemnité fixée par la Confédération.
-Le constat à l'origine de la motion est clair : l'exécution des renvois varie sensiblement d'un canton à l'autre. Une telle disparité n'est pas satisfaisante. Lorsqu'une autorité a rendu une décision fondée sur le droit fédéral et que cette décision est entrée en force, son exécution ne devrait pas dépendre du canton dans lequel se trouve la personne concernée. Il en va de la crédibilité de notre État de droit. Une décision entrée en force doit être appliquée avec la même rigueur sur l'ensemble du territoire suisse. Cette motion évite ainsi que les défauts d'exécution d'un canton produisent durablement ses effets dans toute la Suisse.
-La motion propose une solution pragmatique : lorsqu'un canton n'exécute pas un renvoi et qu'un autre canton est en mesure de le faire, ce dernier doit pouvoir intervenir. Il ne s'agit ni de centraliser l'exécution des renvois ni de retirer leurs compétences aux cantons. Il s'agit, au contraire, de leur donner une possibilité d'action supplémentaire et de renforcer leur coopération. Cette souplesse est particulièrement importante dans un pays où les personnes concernées peuvent se déplacer d'un canton à l'autre rapidement. L'exécution d'une décision ne doit pas être paralysée par une frontière cantonale ou par une question de compétence administrative. Les autorités doivent, au contraire, pouvoir agir lorsque les conditions légales sont réunies, sans être contraintes d'engager des démarches supplémentaires qui retardent inutilement la procédure.
+Le constat à l'origine de la motion est clair[NB]: l'exécution des renvois varie sensiblement d'un canton à l'autre. Une telle disparité n'est pas satisfaisante. Lorsqu'une autorité a rendu une décision fondée sur le droit fédéral et que cette décision est entrée en force, son exécution ne devrait pas dépendre du canton dans lequel se trouve la personne concernée. Il en va de la crédibilité de notre État de droit. Une décision entrée en force doit être appliquée avec la même rigueur sur l'ensemble du territoire suisse. Cette motion évite ainsi que les défauts d'exécution d'un canton produisent durablement ses effets dans toute la Suisse.
+La motion propose une solution pragmatique[NB]: lorsqu'un canton n'exécute pas un renvoi et qu'un autre canton est en mesure de le faire, ce dernier doit pouvoir intervenir. Il ne s'agit ni de centraliser l'exécution des renvois ni de retirer leurs compétences aux cantons. Il s'agit, au contraire, de leur donner une possibilité d'action supplémentaire et de renforcer leur coopération. Cette souplesse est particulièrement importante dans un pays où les personnes concernées peuvent se déplacer d'un canton à l'autre rapidement. L'exécution d'une décision ne doit pas être paralysée par une frontière cantonale ou par une question de compétence administrative. Les autorités doivent, au contraire, pouvoir agir lorsque les conditions légales sont réunies, sans être contraintes d'engager des démarches supplémentaires qui retardent inutilement la procédure.
 La motion ne modifie par ailleurs ni les conditions matérielles d'un renvoi ni les voies de droit dont dispose la personne concernée. Elle intervient seulement lorsqu'une décision entrée en force a été prononcée. Il faut également rappeler que le départ volontaire demeure prioritaire. La motion ne remet nullement ce principe en question. Elle vise les situations dans lesquelles la décision n'est pas exécutée volontairement et où l'intervention des autorités devient nécessaire. Accorder une possibilité d'action à un autre canton permet alors d'éviter que l'inaction se prolonge indéfiniment.
 La question de l'indemnisation doit, elle aussi, être bien comprise. La minorité que je représente ne souhaite pas créer de nouvelles dépenses pour la Confédération. Comme l'a précisé l'auteur de la motion lors des débats au Conseil des États, l'objectif est simplement que l'indemnité normalement destinée au canton compétent revienne au canton qui a exécuté effectivement le renvoi.
-Cette solution apparaît logique et équitable : l'indemnisation doit suivre la prestation accomplie. Elle crée également une incitation concrète à agir, puisque le canton qui mobilise son personnel et ses moyens reçoit les ressources prévues à cet effet par la loi. Enfin, une exécution plus rapide et mieux coordonnée permet d'éviter la prolongation de procédures administratives coûteuses et de situations juridiquement incertaines, ce qui n'est dans l'intérêt de personne et en particulier pas des personnes concernées. L'efficacité de l'exécution sert donc non seulement l'État de droit, mais aussi une utilisation responsable des ressources publiques.
+Cette solution apparaît logique et équitable[NB]: l'indemnisation doit suivre la prestation accomplie. Elle crée également une incitation concrète à agir, puisque le canton qui mobilise son personnel et ses moyens reçoit les ressources prévues à cet effet par la loi. Enfin, une exécution plus rapide et mieux coordonnée permet d'éviter la prolongation de procédures administratives coûteuses et de situations juridiquement incertaines, ce qui n'est dans l'intérêt de personne et en particulier pas des personnes concernées. L'efficacité de l'exécution sert donc non seulement l'État de droit, mais aussi une utilisation responsable des ressources publiques.
 Cette motion renforce l'égalité dans l'application du droit fédéral, améliore la collaboration intercantonale et consolide la crédibilité de nos institutions. Elle contribue également à faire respecter la volonté populaire exprimée en faveur de l'expulsion des criminels étrangers.
 Pour toutes ces raisons, la minorité de la commission vous invite à adopter cette motion.
 </t>
@@ -1025,10 +1026,10 @@
     <t xml:space="preserve">Tschopp Jean</t>
   </si>
   <si>
-    <t xml:space="preserve">Monsieur le conseiller fédéral, comment le Conseil fédéral garantit-il que d'éventuelles conséquences qui relèvent du droit des étrangers soient exclusivement liées à des infractions clairement définies et objectivables et non à des représentations culturelles ou à des modèles familiaux ? En d'autres termes, je reformule ma question : comment le Conseil fédéral garantit-il que des situations de vie comparables soient évaluées selon les mêmes critères, indépendamment de l'origine, de la religion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monsieur le conseiller fédéral, comment le Conseil fédéral garantit-il que d'éventuelles conséquences qui relèvent du droit des étrangers soient exclusivement liées à des infractions clairement définies et objectivables et non à des représentations culturelles ou à des modèles familiaux ? En d'autres termes, je reformule ma question : comment le Conseil fédéral garantit-il que des situations de vie comparables soient évaluées selon les mêmes critères, indépendamment de l'origine, de la religion ou de la couleur de peau ?
+    <t xml:space="preserve">Monsieur le conseiller fédéral, comment le Conseil fédéral garantit-il que d'éventuelles conséquences qui relèvent du droit des étrangers soient exclusivement liées à des infractions clairement définies et objectivables et non à des représentations culturelles ou à des modèles familiaux[NB]? En d'autres termes, je reformule ma question[NB]: comment le Conseil fédéral garantit-il que des situations de vie comparables soient évaluées selon les mêmes critères, indépendamment de l'origine, de la rel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur le conseiller fédéral, comment le Conseil fédéral garantit-il que d'éventuelles conséquences qui relèvent du droit des étrangers soient exclusivement liées à des infractions clairement définies et objectivables et non à des représentations culturelles ou à des modèles familiaux[NB]? En d'autres termes, je reformule ma question[NB]: comment le Conseil fédéral garantit-il que des situations de vie comparables soient évaluées selon les mêmes critères, indépendamment de l'origine, de la religion ou de la couleur de peau[NB]?
 </t>
   </si>
   <si>
@@ -1042,8 +1043,8 @@
   </si>
   <si>
     <t xml:space="preserve">Lors de sa séance des 13 et 14 août derniers, notre Commission des institutions politiques a traité de la motion Z'Graggen 25.4557, "Inscrire dans le droit d'asile, le droit des étrangers et le droit de la nationalité des obligations d'intégration claire pour lutter contre la violence domestique". Cette motion charge le Conseil fédéral d'adapter les lois précitées et, le cas échéant, d'autres actes législatifs, pour que les étrangers aient l'obligation de s'engager, en vue de leur intégration, à ne pas commettre de violences domestiques ou de violences à l'égard des femmes et des enfants, et ce, dès leur premier jour en Suisse. Pour ce faire, les étrangers doivent suivre des formations sur la violence domestique et doivent être au fait des conséquences de la violence sur le plan du droit civil, du droit pénal et du droit des étrangers.
-Les discussions au sein de la commission ont surtout porté sur les étrangers issus de l'asile et sur le concept de formation dans ce cadre. Que faut-il entendre exactement par "formation" ? Faut-il s'attendre à des surcoûts importants liés à cette formation ? Les formateurs pourraient-ils ensuite être tenus pour coresponsables si, malgré la formation, les étrangers commettent des délits ? La commission a cependant été informée qu'une simple thématisation, par exemple dans le cadre des cours de langue, peut déjà être considérée comme une formation, et que l'idée n'était pas de mettre en place un système coûteux et bureaucratique. Par ailleurs, il ne doit pas être considéré qu'en cas d'infraction, l'étranger qui commet le délit pourrait se retourner contre le formateur.
-Les discussions ont également porté sur la pertinence même d'une telle formation. En d'autres termes, est-ce vraiment le rôle de la Suisse de devoir expliquer une évidence aux étrangers qui viennent chez nous, à savoir qu'il n'y a pas de place chez nous pour les violences domestiques ? À ce sujet, il convient de préciser que si la Suisse a choisi de se doter d'un système d'asile, elle doit à ce titre se donner également les moyens d'en garantir la cohérence. Or, si nous refusons chaque mesure d'intégration au motif qu'il s'agit d'une évidence - en l'occurrence le fait que nous n'acceptions pas les violences domestiques - nous pouvons alors simplement abolir l'asile. Or, ce n'est pas la volonté de notre commission et sans doute pas non plus celle de la majorité de ce Parlement.
+Les discussions au sein de la commission ont surtout porté sur les étrangers issus de l'asile et sur le concept de formation dans ce cadre. Que faut-il entendre exactement par "formation"[NB]? Faut-il s'attendre à des surcoûts importants liés à cette formation[NB]? Les formateurs pourraient-ils ensuite être tenus pour coresponsables si, malgré la formation, les étrangers commettaient des délits[NB]? La commission a cependant été informée qu'une simple thématisation, par exemple dans le cadre des cours de langue, peut déjà être considérée comme une formation, et que l'idée n'était pas de mettre en place un système coûteux et bureaucratique. Par ailleurs, il ne doit pas être considéré qu'en cas d'infraction l'étranger qui commettrait le délit pourrait se retourner contre le formateur.
+Les discussions ont également porté sur la pertinence même d'une telle formation. En d'autres termes, est-ce vraiment le rôle de la Suisse de devoir expliquer une évidence aux étrangers qui viennent chez nous, à savoir qu'il n'y a pas de place chez nous pour les violences domestiques[NB]? À ce sujet, il convient de préciser que si la Suisse a choisi de se doter d'un système d'asile, elle doit à ce titre se donner également les moyens d'en garantir la cohérence. Or, si nous refusons chaque mesure d'intégration au motif qu'il s'agit d'une évidence - en l'occurrence le fait que nous n'acceptions pas les violences domestiques -, nous pouvons alors simplement abolir l'asile. Or, ce n'est pas la volonté de notre commission et sans doute pas non plus celle de la majorité de ce Parlement.
 Une minorité de votre commission considère que cette motion stigmatise les étrangers, raison pour laquelle elle rejette la motion. Cela dit, en permettant de renforcer le fonctionnement du système d'asile, non seulement pour intégrer les étrangers, mais également pour intervenir en cas de problème ou pour les renvoyer, la majorité de votre commission considère que cette motion va dans la bonne direction. En outre, en inscrivant spécifiquement la question de l'intégration en lien avec les violences domestiques dans la loi, nous envoyons un signal clair aux cantons pour qu'ils la prennent plus au sérieux dans leurs pratiques.
 Pour toutes ces raisons, je vous invite, au nom de la commission, à adopter la motion. Elle a été adoptée par le Conseil des États sans contre-proposition et par notre Commission des institutions politiques, par 18 voix contre 5 et 1 abstention.
 </t>
@@ -1054,16 +1055,16 @@
   <si>
     <t xml:space="preserve">La majorité de la commission vous propose de rejeter la motion Müller Damian.
 Les travaux de la commission ont montré que les instruments proposés ne sont ni nécessaires ni véritablement adaptés pour améliorer l'exécution de renvois.
-Tout d'abord, sur l'état de la situation actuelle des cantons : les différences entre les cantons, avancées pour justifier la motion, doivent être tout à fait relativisées. C'est en tout cas l'avis de la majorité de la commission. Les statistiques citées concernent </t>
+Tout d'abord, sur l'état de la situation actuelle des cantons, les différences entre les cantons avancées pour justifier la motion doivent être tout à fait relativisées. C'est en tout cas l'avis de la majorité de la commission. Les statistiques citées concernent not</t>
   </si>
   <si>
     <t xml:space="preserve">La majorité de la commission vous propose de rejeter la motion Müller Damian.
 Les travaux de la commission ont montré que les instruments proposés ne sont ni nécessaires ni véritablement adaptés pour améliorer l'exécution de renvois.
-Tout d'abord, sur l'état de la situation actuelle des cantons : les différences entre les cantons, avancées pour justifier la motion, doivent être tout à fait relativisées. C'est en tout cas l'avis de la majorité de la commission. Les statistiques citées concernent notamment les expulsions pénales, avec parfois un nombre très limité de personnes ; quelques cas suffisent alors à faire varier fortement le taux d'exécution. Il faut également distinguer une chose : les expulsions pénales des renvois relevant de l'asile ou du droit des étrangers ne répondent pas aux mêmes conditions. C'est vraiment important de faire cette distinction.
-Les discussions en commission ont aussi permis de nuancer certaines affirmations concernant les cantons romands. L'exemple du canton de Vaud a été clairement mis en avant : entre 1000 et 1200 renvois y ont été exécutés chaque année, et cela depuis plusieurs années. Plus généralement, le nombre de départs a augmenté et l'administration considère que le système suisse fonctionne globalement de manière efficace.
-Cela ne signifie pas qu'il n'existe aucune difficulté, mais les principaux obstacles ne relèvent pas nécessairement d'un manque de volonté des cantons. Il est important de voir quels sont les autres obstacles en la matière ; ce sont notamment l'absence de documents de voyage, la coopération avec les États d'origine ou encore des obstacles juridiques qui peuvent empêcher l'exécution d'un renvoi. La position de la majorité est de dire qu'un bonus financier n'apporterait absolument pas une nouvelle solution.
+Tout d'abord, sur l'état de la situation actuelle des cantons, les différences entre les cantons avancées pour justifier la motion doivent être tout à fait relativisées. C'est en tout cas l'avis de la majorité de la commission. Les statistiques citées concernent notamment les expulsions pénales, avec parfois un nombre très limité de personnes[NB]; quelques cas suffisent alors à faire varier fortement le taux d'exécution. Il faut également distinguer une chose[NB]: les expulsions pénales des renvois relevant de l'asile ou du droit des étrangers ne répondent pas aux mêmes conditions. C'est vraiment important de faire cette distinction.
+Les discussions en commission ont aussi permis de nuancer certaines affirmations concernant les cantons romands. L'exemple du canton de Vaud a été clairement mis en avant[NB]: entre 1000 et 1200 renvois y ont été exécutés chaque année, et cela depuis plusieurs années. Plus généralement, le nombre de départs a augmenté et l'administration considère que le système suisse fonctionne globalement de manière efficace.
+Cela ne signifie pas qu'il n'existe aucune difficulté, mais les principaux obstacles ne relèvent pas nécessairement d'un manque de volonté des cantons. Il est important de voir quels sont les autres obstacles en la matière[NB]; ce sont notamment l'absence de documents de voyage, la coopération avec les États d'origine ou encore des obstacles juridiques qui peuvent empêcher l'exécution d'un renvoi. La position de la majorité est de dire qu'un bonus financier n'apporterait absolument pas une nouvelle solution.
 Ensuite, la motion propose, pour une large part, des instruments qui existent déjà. La coopération et l'entraide entre les cantons sont déjà possibles aujourd'hui. Un canton peut déjà soutenir un autre canton dans l'exécution de ses tâches. Finalement, la motion n'apporte rien de nouveau.
-La véritable nouveauté, et la seule nouveauté, c'est le principe de l'introduction d'une incitation financière pour qu'un canton exécute des renvois à la place d'un autre. C'est particulièrement sur ce point que la majorité de la commission est sceptique. L'exécution des renvois est une compétence et une obligation des cantons. Récompenser financièrement un canton pour accomplir une tâche prévue par le droit constituerait un changement de logique et soulèverait des questions importantes du point de vue du fédéralisme et de la répartition des compétences. D'une certaine manière, on serait récompensé tout simplement parce qu'on a appliqué la loi ; c'est un peu particulier. Rien ne démontre par ailleurs qu'un canton mobiliserait davantage ses forces de police pour effectuer des renvois d'un autre canton, simplement en raison d'une indemnité financière. Il existe déjà des mécanismes financiers lorsque les cantons ne remplissent pas leurs obligations. La Confédération a des outils ; elle peut notamment suspendre certaines subventions. Selon les informations données à la commission, ces mesures représentent plus de 30 millions de francs sur les 10 dernières années.
+La véritable nouveauté, et la seule nouveauté, c'est le principe de l'introduction d'une incitation financière pour qu'un canton exécute des renvois à la place d'un autre. C'est particulièrement sur ce point que la majorité de la commission est sceptique. L'exécution des renvois est une compétence et une obligation des cantons. Récompenser financièrement un canton pour accomplir une tâche prévue par le droit constituerait un changement de logique et soulèverait des questions importantes du point de vue du fédéralisme et de la répartition des compétences. D'une certaine manière, on serait récompensé tout simplement parce qu'on a appliqué la loi[NB]; c'est un peu particulier. Rien ne démontre par ailleurs qu'un canton mobiliserait davantage ses forces de police pour effectuer des renvois d'un autre canton, simplement en raison d'une indemnité financière. Il existe déjà des mécanismes financiers lorsque les cantons ne remplissent pas leurs obligations. La Confédération a des outils[NB]; elle peut notamment suspendre certaines subventions. Selon les informations données à la commission, ces mesures représentent plus de 30 millions de francs sur les 10 dernières années.
 Pour toutes ces raisons, la commission, par 13 voix contre 12, vous recommande de rejeter la motion.
 </t>
   </si>
@@ -1072,16 +1073,16 @@
   </si>
   <si>
     <t xml:space="preserve">La violence domestique, sexuelle et la violence faite aux femmes doivent être combattues sans aucun compromis. La protection des victimes est également une exigence absolue, mais c'est précisément parce que ce combat est essentiel qu'il ne doit en aucun cas être instrumentalisé. Cette dérive est celle qu'on est en train de vivre ici, dans ce Parlement, avec une majorité qui accepte la politisation de cette thématique.
-Cette motion fait un choix politique très clair : prendre un phénomène structu</t>
+Cette motion fait un choix politique très clair[NB]: prendre un phénomène stru</t>
   </si>
   <si>
     <t xml:space="preserve">La violence domestique, sexuelle et la violence faite aux femmes doivent être combattues sans aucun compromis. La protection des victimes est également une exigence absolue, mais c'est précisément parce que ce combat est essentiel qu'il ne doit en aucun cas être instrumentalisé. Cette dérive est celle qu'on est en train de vivre ici, dans ce Parlement, avec une majorité qui accepte la politisation de cette thématique.
-Cette motion fait un choix politique très clair : prendre un phénomène structurel, qui traverse toute notre société, et choisir de le traiter sous l'angle du droit d'asile, du droit des étrangers et de la nationalité. Je dois dire mon étonnement - je dirais même mon désarroi - de voir que le Conseil fédéral, mais également la majorité de ce Parlement, se plient aussi facilement à ce cadrage.
-Le rejet de la violence et le respect des valeurs constitutionnelles font déjà partie de critères d'intégration essentiels. La violence domestique est déjà interdite et sanctionnée par notre droit, car - pour rappel - nous vivons dans un État de droit. Pourquoi faut-il maintenant inscrire spécifiquement cette question dans le droit des étrangers ? Quel message veut-on envoyer, sinon celui qu'il existerait un lien particulier entre immigration et violence domestique ?
-C'est d'autant plus problématique que les propres travaux de la Confédération nous invitent précisément à ne pas faire ce raccourci. Ces travaux ont été présentés au moment même où nous discutions de cette motion en commission. Une enquête du Bureau fédéral de l'égalité entre femmes et hommes montrait très clairement que la violence domestique était un problème systémique - un problème qui traversait toutes les populations en Suisse. Elle disait que ce n'était pas un problème d'étrangers, mais un problème général et systémique : la violence domestique existe dans toutes les couches de la société et au sein de toutes les populations. Ce rapport était très clair à cet égard.
-Cette motion est grave, parce qu'elle propose, pour traiter la question de la lutte contre les violences domestiques, de se préoccuper du passeport. Et ceci est grave. Un homme violent ne l'est pas davantage parce qu'il est étranger, et il ne l'est pas moins parce qu'il possède un passeport suisse. Une femme frappée par un Suisse n'est pas moins victime qu'une femme frappée par un étranger. Et c'est là que cette instrumentalisation devient aussi dangereuse pour les victimes. C'est pour cette raison, précisément, que le groupe des Verts rejettera cette motion. À force de fabriquer la figure de l'étranger violent, on détourne le regard de tous les auteurs qui ne correspondent pas à cette image - l'homme suisse, parfaitement intégré, socialement établi, bon père de famille en apparence. La violence domestique existe bien sûr aussi, derrière ces portes-là - on le sait bien, et toutes les enquêtes le confirment. Si nous voulons réellement protéger les femmes, alors protégeons toutes les femmes, et commençons notamment par protéger les femmes étrangères qui sont elles-mêmes victimes de violences, celles qui hésitent à dénoncer leur conjoint parce qu'elles craignent de perdre leur permis de séjour, leurs ressources ou leur sécurité. Le Bureau de prévention recommande justement une protection renforcée des victimes, indépendamment de leur statut de séjour. Voilà où nous devrions mettre notre énergie.
-Alors, oui, bien sûr, informons les personnes qui arrivent en Suisse sur les droits fondamentaux, sur l'égalité entre femmes et hommes, sur les droits des enfants, sur les conséquences pénales de la violence - bien sûr, faisons ces formations. Mais par pitié, faisons-le sans prétendre que le coeur du problème se trouve à la frontière. Nous avons besoin de prévention, bien sûr ; dans notre société, nous avons besoin de beaucoup de prévention, mais d'une prévention pour toutes et tous. Nous avons besoin de structures d'accueil suffisamment dotées, de professionnels formés, d'un meilleur accès à l'aide et d'une justice qui soit réellement centrée sur la protection des victimes, sur les femmes. La violence domestique n'est pas un problème d'asile. Je le dis encore une fois, la violence domestique n'est pas un problème d'asile, n'est pas un problème de nationalité, c'est un problème de violence, de rapport de pouvoir et de protection des victimes.
-J'aurais souhaité ici que le Conseil fédéral et la majorité de ce Parlement aient le courage de tenir cette ligne plutôt que de céder à la facilité politique qui consiste, une fois encore, à transformer l'étranger en explication commode d'un problème qui traverse toute notre société. Prenons au sérieux la lutte contre les violences faites aux femmes - une lutte trop sérieuse pour en faire un instrument de politique migratoire.
+Cette motion fait un choix politique très clair[NB]: prendre un phénomène structurel, qui traverse toute notre société, et choisir de le traiter sous l'angle du droit d'asile, du droit des étrangers et de la nationalité. Je dois dire mon étonnement - je dirais même mon désarroi - de voir que le Conseil fédéral, mais également la majorité de ce Parlement, se plient aussi facilement à ce cadrage.
+Le rejet de la violence et le respect des valeurs constitutionnelles font déjà partie de critères d'intégration essentiels. La violence domestique est déjà interdite et sanctionnée par notre droit, car - pour rappel - nous vivons dans un État de droit. Pourquoi faut-il maintenant inscrire spécifiquement cette question dans le droit des étrangers[NB]? Quel message veut-on envoyer, sinon celui qu'il existerait un lien particulier entre immigration et violence domestique[NB]?
+C'est d'autant plus problématique que les propres travaux de la Confédération nous invitent précisément à ne pas faire ce raccourci. Ces travaux ont été présentés au moment même où nous discutions de cette motion en commission. Une enquête du Bureau fédéral de l'égalité entre femmes et hommes montrait très clairement que la violence domestique était un problème systémique - un problème qui traversait toutes les populations en Suisse. Elle disait que ce n'était pas un problème d'étrangers, mais un problème général et systémique[NB]: la violence domestique existe dans toutes les couches de la société et au sein de toutes les populations. Ce rapport était très clair à cet égard.
+Cette motion est grave, parce qu'elle propose, pour traiter la question de la lutte contre les violences domestiques, de se préoccuper du passeport. Et ceci est grave. Un homme violent ne l'est pas davantage parce qu'il est étranger, et il ne l'est pas moins parce qu'il possède un passeport suisse. Une femme frappée par un Suisse n'est pas moins victime qu'une femme frappée par un étranger. Et c'est là que cette instrumentalisation devient aussi dangereuse pour les victimes. C'est pour cette raison, précisément, que le groupe des Verts rejettera cette motion. À force de fabriquer la figure de l'étranger violent, on détourne le regard de tous les auteurs qui ne correspondent pas à cette image - l'homme suisse, parfaitement intégré, socialement établi, bon père de famille en apparence. La violence domestique existe bien sûr aussi, derrière ces portes-là, on le sait bien, et toutes les enquêtes le confirment. Si nous voulons réellement protéger les femmes, alors protégeons toutes les femmes, et commençons notamment par protéger les femmes étrangères qui sont elles-mêmes victimes de violences, celles qui hésitent à dénoncer leur conjoint parce qu'elles craignent de perdre leur permis de séjour, leurs ressources ou leur sécurité. Le Bureau de prévention recommande justement une protection renforcée des victimes, indépendamment de leur statut de séjour. Voilà où nous devrions mettre notre énergie.
+Alors, oui, bien sûr, informons les personnes qui arrivent en Suisse sur les droits fondamentaux, sur l'égalité entre femmes et hommes, sur les droits des enfants, sur les conséquences pénales de la violence. Bien sûr, faisons ces formations. Mais par pitié, faisons-le sans prétendre que le coeur du problème se trouve à la frontière. Nous avons besoin de prévention, bien sûr[NB]; dans notre société, nous avons besoin de beaucoup de prévention, mais d'une prévention pour toutes et tous. Nous avons besoin de structures d'accueil suffisamment dotées, de professionnels formés, d'un meilleur accès à l'aide et d'une justice qui soit réellement centrée sur la protection des victimes, sur les femmes. La violence domestique n'est pas un problème d'asile. Je le dis encore une fois, la violence domestique n'est pas un problème d'asile, n'est pas un problème de nationalité, c'est un problème de violence, de rapport de pouvoir et de protection des victimes.
+J'aurais souhaité ici que le Conseil fédéral et la majorité de ce Parlement aient le courage de tenir cette ligne plutôt que de céder à la facilité politique qui consiste, une fois encore, à transformer l'étranger en explication commode d'un problème qui traverse toute notre société. Prenons au sérieux la lutte contre les violences faites aux femmes[NB]; une lutte trop sérieuse pour en faire un instrument de politique migratoire.
 Je vous invite, au nom du groupe des Verts, à rejeter la motion.
 </t>
   </si>
@@ -1703,7 +1704,7 @@
 Le mandat définitif, adopté en mars 2024, était donc déjà le résultat d'un processus associant le Parlement, les cantons ainsi que les partenaires socioéconomiques. Ce dialogue s'est poursuivi pendant les négociations, notamment avec les Commissions de politique extérieure (CPE), où nous avons pu régulièrement obtenir des informations sur l'avancement et les résultats.
 Une fois les négociations terminées, le paraphe apposé, et avant la signature, les accords et les actes législatifs de mise en oeuvre ont été soumis à une procédure ordinaire de consultation.
 Votre commission a pris connaissance des résultats de cette consultation et les a intégrés dans son appréciation politique du paquet. Une nette majorité des participants à la consultation s'est prononcée favorablement tant sur le paquet dans son ensemble que sur le résultat des négociations. La voie bilatérale a recueilli un soutien particulièrement large par rapport aux autres options de politique européenne. La consultation a aussi fait apparaître plusieurs demandes d'amélioration concernant la mise en oeuvre en Suisse. Le Conseil fédéral en a tenu compte et a adapté sur plusieurs points les projets législatifs avant de transmettre son message au Parlement.
-Les textes législatifs de mise en oeuvre des accords que nous examinerons en détail, en passant en revue les diverses annexes de l'arrêté 1, sont donc non seulement le résultat de la négociation avec l'Union européenne, mais aussi d'un processus de consultation et d'ajustement interne à notre pays.
+Les textes législatifs de mise en oeuvre des accords que nous examinerons en détail, en passant en revue les divers de l'arrêté 1, sont donc non seulement le résultat de la négociation avec l'Union européenne, mais aussi d'un processus de consultation et d'ajustement interne à notre pays.
 Il est nécessaire, dans le cadre du débat d'entrée en matière, de rappeler les différents objectifs des accords dont le Conseil fédéral demande l'approbation. Quatorze d'entre eux, énumérés, à l'arrêté fédéral 1, visent la stabilisation de la voie bilatérale. Ils portent sur la contribution à la cohésion, la libre circulation des personnes, les obstacles techniques au commerce, les transports terrestres, les transports aériens, les transports ferroviaires, l'agriculture et la participation aux programmes européens de recherche en cours, à savoir Horizon Europe, Euratom, Digital Europe, Erasmus plus, EU4Health et Iter et les futurs programmes d'ailleurs.
 Trois autres accords faisant l'objet d'arrêtés distincts concernent le développement de la voie bilatérale dans les domaines de la sécurité des aliments, de la santé et de l'électricité. Celui relatif à l'électricité ne fait toutefois pas l'objet de nos débats lors de cette session, son traitement en commission n'étant pas encore achevé. Enfin, le paquet que nous traitons pendant cette session comprend encore un accord sur la coopération parlementaire.
 En plus de ces différents accords, le paquet inclut trois crédits d'engagement relatifs à la contribution à la cohésion et un crédit relatif au financement de la participation de la Suisse au programme Erasmus.
@@ -1803,17 +1804,9 @@
 Dem Vernehmen nach war dies der Preis für die Schutzklausel. Mag die Schutzklausel diesen Preis aufwiegen? Das Personenfreizügigkeitsabkommen ist ein Frontalzusammenstoss mit Artikel 121a unserer Bundesverfassung; darüber werden wir ja noch reden. Es widerspricht ebenso dem klaren Auftrag zur eigenständigen Steuerung der Zuwanderung. Allein das Abkommen über die Personenfreizügigkeit, die Erweiterung, würden wir in dieser Form wohl nicht unterschreiben.
 Zweitens kommen mit den Protokollen, wie wir mehrfach ausgeführt gehört haben, die institutionellen Elemente zu den Verträgen hinzu. Dies ist ein fundamentaler Paradigmenwechsel. Die bilateralen Verträge I und II basieren auf dem klassischen Völkerrecht: Gleichberechtigung der Parteien, Änderungen nur im gegenseitigen Einvernehmen, Auslegung nach Treu und Glauben. Das, was heute vorliegt, bricht mit diesem Fundament.
 "Bilaterale III" - dies ist eine Verharmlosung. Tatsächlich handelt es sich um einen massiven institutionellen Integrationsschritt. Entscheidend ist nicht nur der heutige Vertragsinhalt, also jene Blackbox, die ich am Anfang erwähnt habe, sondern der Mechanismus für das Recht von morgen. Mit der dynamischen Rechtsübernahme verpflichten wir uns auf Vorrat, künftige EU-Rechtsentwicklungen zu übernehmen, die meist von der EU-Kommission erlassen werden und die wir heute noch gar nicht kennen.
-Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und oppositionslos so in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Taking.
-Drittens bedeuten die Verträge eine unannehmbare Schwächung der direkten Demokratie und des Föderalismus. Die Rechtsetzung verschiebt sich bei den betroffenen Abkommen räumlich und institutionell. Die EU und die Schweiz haben grundverschiedene Rechtssysteme: Die EU erlässt neues Recht von oben nach unten, bei uns funktioniert es gerade umgekehrt, von unten nach oben - ausgehend vom Souverän, dem Volk. Diese Systeme lassen sich nicht verbinden.
-Entscheidend ist, darüber spricht fast niemand, dass wir selber keine Gesetzgebung innerhalb der betroffenen Abkommen mehr anstossen können; wir geben die Input-Funktion für die entsprechende Gesetzgebung in die Hände der EU-Kommission.
-Zudem, das führte Herr Ständerat Schmid gerade aus, erfährt die Exekutive einen massiven Machtzuwachs. Bundesrat und Verwaltung bestimmen die Positionen, führen das Mandat und wählen die Experten aus, die uns in Brüssel vertreten sollen. Die Schweiz ist von oben nach unten organisierter Expertenstaat: "Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut! Komm, lass uns gehen."
-Viertens können die innerstaatlichen Reformen, die wir noch diskutieren werden, das Grundproblem nicht heilen. Massnahmen zur Stärkung des Parlamentes und der Kantone und Veränderungen im innerstaatlichen Recht ändern nichts an der harten Realität:
-Die Schweiz gibt die inhaltliche Kontrolle über ihr eigenes Recht ab. Wenn das Volk oder das Parlament neues Recht ablehnt, darf die EU uns mit sachfremden, sektionsübergreifenden Ausgleichsmassnahmen - ich sage das Wort jetzt halt - abstrafen. Das und die mangelnde Konkretisierung dieser Sanktionen ist doch hochproblematisch: Wenn die Folgen einer Ablehnung nicht präzise definiert sind, ist doch eine freie, informierte Willensbildung der Stimmbürgerinnen nicht mehr möglich. Dies verletzt Artikel 34 der Bundesverfassung; die freie Willensbildung und die unverfälschte Stimmabgabe sind in Artikel 34 Absatz 2 der Bundesverfassung garantiert. Es ist eines souveränen Staates unwürdig, wenn ein externer Akteur ihn vertraglich bestrafen darf. 
+Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und oppositionslos so in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Taking.Drittens bedeuten die Verträge eine unannehmbare Schwächung der direkten Demokratie und des Föderalismus. Die Rechtsetzung verschiebt sich bei den betroffenen Abkommen räumlich und institutionell. Die EU und die Schweiz haben grundverschiedene Rechtssysteme: Die EU erlässt neues Recht von oben nach unten, bei uns funktioniert es gerade umgekehrt, von unten nach oben - ausgehend vom Souverän, dem Volk. Diese Systeme lassen sich nicht verbinden.Entscheidend ist, darüber spricht fast niemand, dass wir selber keine Gesetzgebung innerhalb der betroffenen Abkommen mehr anstossen können; wir geben die Input-Funktion für die entsprechende Gesetzgebung in die Hände der EU-Kommission.Zudem, das führte Herr Ständerat Schmid gerade aus, erfährt die Exekutive einen massiven Machtzuwachs. Bundesrat und Verwaltung bestimmen die Positionen, führen das Mandat und wählen die Experten aus, die uns in Brüssel vertreten sollen. Die Schweiz ist kein von oben nach unten organisierter Expertenstaat: "Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut! Komm, lass uns gehen."Viertens können die innerstaatlichen Reformen, die wir noch diskutieren werden, das Grundproblem nicht heilen. Massnahmen zur Stärkung des Parlamentes und der Kantone und Anpassungen im innerstaatlichen Recht ändern nichts an der harten Realität:Die Schweiz gibt die inhaltliche Kontrolle über ihr eigenes Recht ab. Wenn das Volk oder das Parlament neues Recht ablehnt, darf die EU uns mit sachfremden, sektionsübergreifenden Ausgleichsmassnahmen - ich sage das Wort jetzt halt - abstrafen. Das und die mangelnde Konkretisierung dieser Sanktionen ist doch hochproblematisch: Wenn die Folgen einer Ablehnung nicht präzise definiert sind, ist doch eine freie, informierte Willensbildung der Stimmbürgerinnen nicht mehr möglich. Dies verletzt Artikel 34 der Bundesverfassung; die freie Willensbildung und die unverfälschte Stimmabgabe sind in Artikel 34 Absatz 2 der Bundesverfassung garantiert. Es ist eines souveränen Staates unwürdig, wenn ein externer Akteur ihn vertraglich bestrafen darf. 
 Auslöser für die Verhandlungen war, gemäss den Medienmitteilungen des Bundesrates in den Anfängen, ein Stromabkommen. Für diesen Gegenwert hat die Schweiz weitreichende Konzessionen gemacht: die dynamische Rechtsübernahme und die innerstaatliche Umsetzung des EU-Beihilferechts. Wie sieht es heute aus? Nun soll ausgerechnet der Strombereich ausgeklammert und separat vorgelegt werden, weil er politisch hoch umstritten ist - das kommt nicht vom Bundesrat, das ist eine Diskussion in den Räten. Damit gerät doch die gesamte Logik des Pakets ins Wanken. Die weitreichenden Konzessionen der Schweiz bleiben bestehen, während der ursprüngliche Auslöser und zentrale Gegenwert, wegen dem man überhaupt verhandelt hat, entfällt. Die Schweiz soll also den vollen Preis für das Paket bezahlen, und das wirft die Frage auf: Wie kann man an den Verpflichtungen festhalten, wenn der Gegenwert, der die Verhandlungen ursprünglich ausgelöst hat, entfällt?
-Manchmal frage ich mich, wann genau wir in der Schweiz aufgehört haben, stolz auf unsere Freiheit, auf unser einzigartiges politisches System zu sein. Ich sehe die Versprechen eines wirtschaftlichen Nutzens. Doch die Realität zeigt, dass die tatsächliche Grössenordnung dieses Nutzens sehr umstritten ist und gar als gering beurteilt wird. Wenn wir diesen vermeintlichen Nutzen gegen den realen Verlust der Souveränität aufwiegen, ist das Ergebnis eindeutig: Der staatspolitische Preis ist zu hoch. Wenn wir auf den Zustand der EU schauen, sehen wir eine zunehmende Zentralisierung, wir sehen, dass das Subsidiaritätsprinzip ignoriert wird, und wir sehen eine enorme Machtkonzentration bei der EU-Kommission. Die wirtschaftlichen und politischen Schwächen grosser Mitgliedstaaten wie Deutschland oder Frankreich sind unübersehbar. Es gibt keinen zwingenden Grund, warum wir uns enger an dieses System binden sollten. Wer behauptet, dieses Paket sei alternativlos, verkennt die Realität und die Stärken unseres Landes. Wir sind ein finanziell gesunder, wir sind ein erfolgreicher Stabilitätsanker im Herzen Europas. Wir halten unser staatliches Haus in Ordnung. Wir haben für Milliarden von Franken eine Jahrhundertinfrastruktur gebaut, die Neat, den Alpentransit, und dies im vitalen Interesse des gesamten Kontinents.
-Dieses starke Schweizer Fundament beweist, dass die EU ein ebenso grosses Eigeninteresse an geordneten Beziehungen hat wie wir. Lassen wir uns wirklich von der Drohkulisse einschüchtern, wonach die Bilateralen I und die Bilateralen II bei einem Nein sofort beendet würden? Es gibt immer Alternativen. Wir können bestehende Abkommen punktuell und klassisch völkerrechtlich modernisieren. Die EU beweist zudem, wie beim Ceta-Abkommen oder den aktuellen Plänen für eine assoziierte Mitgliedschaft Kanadas, dass massgeschneiderte Verträge mit Drittstaaten möglich sind, ohne dass diese auf ihre Souveränität verzichten oder eine automatische Rechtsübernahme akzeptieren müssten.
-"Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Ja, gehen wir selbstbewusst an diesem Hut vorbei, treten wir nicht ein.
-</t>
+Manchmal frage ich mich, wann genau wir in der Schweiz aufgehört haben, stolz auf unsere Freiheit, auf unser einzigartiges politisches System zu sein. Ich sehe die Versprechen eines wirtschaftlichen Nutzens. Doch die Realität zeigt, dass die tatsächliche Grössenordnung dieses Nutzens sehr umstritten ist und gar als gering beurteilt wird. Wenn wir diesen vermeintlichen Nutzen gegen den realen Verlust der Souveränität aufwiegen, ist das Ergebnis eindeutig: Der staatspolitische Preis ist zu hoch. Wenn wir auf den Zustand der EU schauen, sehen wir eine zunehmende Zentralisierung, wir sehen, dass das Subsidiaritätsprinzip ignoriert wird, und wir sehen eine enorme Machtkonzentration bei der EU-Kommission. Die wirtschaftlichen und politischen Schwächen grosser Mitgliedstaaten wie Deutschland oder Frankreich sind unübersehbar. Es gibt keinen zwingenden Grund, warum wir uns enger an dieses System binden sollten. Wer behauptet, dieses Paket sei alternativlos, verkennt die Realität und die Stärken unseres Landes. Wir sind ein finanziell gesunder, wir sind ein erfolgreicher Stabilitätsanker im Herzen Europas. Wir halten unser staatliches Haus in Ordnung. Wir haben für Milliarden von Franken eine Jahrhundertinfrastruktur gebaut, die Neat, den Alpentransit, und dies im vitalen Interesse des gesamten Kontinents.Dieses starke Schweizer Fundament beweist, dass die EU ein ebenso grosses Eigeninteresse an geordneten Beziehungen hat wie wir. Lassen wir uns wirklich von der Drohkulisse einschüchtern, wonach die Bilateralen I und die Bilateralen II bei einem Nein sofort beendet würden? Es gibt immer Alternativen. Wir können bestehende Abkommen punktuell und klassisch völkerrechtlich modernisieren. Die EU beweist zudem, wie beim Ceta-Abkommen oder den aktuellen Plänen für eine assoziierte Mitgliedschaft Kanadas, dass massgeschneiderte Verträge mit Drittstaaten möglich sind, ohne dass diese auf ihre Souveränität verzichten oder eine automatische Rechtsübernahme akzeptieren müssten."Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Ja, gehen wir selbstbewusst an diesem Hut vorbei, treten wir nicht ein.</t>
   </si>
   <si>
     <t xml:space="preserve">421742</t>
@@ -2070,7 +2063,7 @@
     <t xml:space="preserve">Ich möchte einleitend ebenfalls darauf hinweisen, dass wir vor drei Monaten in diesem Rat die Motion Chiesa 26.3229 gutgeheissen haben, und zwar mit einem klaren Verhältnis von 26 zu 11 Stimmen bei 5 Enthaltungen. Sie verlangt erstens von allen Personen, welche in der Schweiz eine Aufenthaltsbewilligung beantragen, einen Strafregisterauszug zu verlangen, und zweitens, dass Personen, bei denen die Prüfung ihres Strafregisterauszuges ergibt, dass sie eine Gefahr darstellen, kein Aufenthaltsrecht erhalten. Wir haben diese Motion im Wissen darum gutgeheissen, dass die Forderung sowohl Personen aus Drittstaaten als auch Personen aus EU/EFTA-Ländern betrifft. Wir haben die Entscheidung im Wissen um die Begründung der ablehnenden Stellungnahme des Bundesrates getroffen, dass diese Forderung in Bezug auf EU/EFTA-Staatsangehörige gegen das Freizügigkeitsabkommen verstösst.
 Drei Monate später geht es nun darum, auch Tatsachen folgen zu lassen. Bei Artikel 13 AIG macht die Kommission das: In Abweichung zum Entwurf des Bundesrates, der beim geltenden Recht bleiben möchte, beantragt Ihnen die Staatspolitische Kommission mit Absatz 2, dass die Behörden bei Drittstaatsangehörigen nicht nur einen Strafregisterauszug verlangen können, sondern einen Strafregisterauszug verlangen müssen. Vor allem bekommen die Behörden mit Absatz 4, der neu eingefügt werden soll, die klare Vorgabe, dass der Aufenthalt zu verweigern ist, wenn sich aus der Prüfung des Strafregisterauszuges oder anderer Unterlagen ergibt, dass die betreffende Person eine Gefahr darstellt. Das steht heute so nicht im Gesetz. Dazu liegt kein Minderheitsantrag vor. Ich bin gespannt, wie der Bundesrat sich dazu äussert und ob er sich mit der entsprechenden Ergänzung des Ausländer- und Integrationsgesetzes einverstanden erklärt.
 Nun stellt sich die Frage, wie wir mit EU- und EFTA-Staatsangehörigen umgehen. Das erste Beispiel ist eigentlich ein Paradebeispiel dafür, in welcher Situation wir uns befinden. Vor drei Monaten haben wir noch eigenständig gesagt: Wir wollen auch bei EU- und EFTA-Staatsangehörigen, dass ein Strafregisterauszug verlangt wird. Drei Monate später werden wir nun zu entscheiden haben, wie wir auf die Information reagieren, dass es gegen das Freizügigkeitsabkommen verstösst, wenn wir die neuen Bestimmungen jetzt wirklich in das Gesetz schreiben und konkret umsetzen. Es wird dann jene geben, die sagen: Gut, dann tun wir das nicht, wir distanzieren uns von der Motion, wir machen einen Kniefall vor dem Freizügigkeitsabkommen und verzichten darauf, eigenständig Gesetzgebung zu betreiben. Das ist eigentlich das erste Paradebeispiel, das wir hier haben.
-Auch ich liefere Ihnen eine Anekdote. Ich habe vor einem Jahr meinen Eintrag im Anwaltsregister des Kantons St. Gallen in jenes des Kantons Appenzell-Innerhoden verlegt. Ich kann Ihnen sagen, was ich vorlegen musste: Ich musste einen Betreibungsregisterauszug und selbstverständlich auch einen Strafregisterauszug vorlegen. Zudem musste ich noch eine Bestätigung der Kindes- und Erwachsenenschutzbehörde vorlegen, dass keine Verdachtsmomente vorliegen, die mich als handlungs- und urteilsunfähig erscheinen liessen. Das ist also sogar die Praxis bei Anwälten, wenn ein Eintrag im Anwaltsregister vorgenommen oder geändert werden soll. 
+Auch ich liefere Ihnen eine Anekdote. Ich habe vor einem Jahr meinen Eintrag im Anwaltsregister des Kantons St. Gallen in jenes des Kantons Appenzell Innerhoden verlegt. Ich kann Ihnen sagen, was ich vorlegen musste: Ich musste einen Betreibungsregisterauszug und selbstverständlich auch einen Strafregisterauszug vorlegen. Zudem musste ich noch eine Bestätigung der Kindes- und Erwachsenenschutzbehörde vorlegen, dass keine Verdachtsmomente vorliegen, die mich als handlungs- und urteilsunfähig erscheinen liessen. Das ist also sogar die Praxis bei Anwälten, wenn ein Eintrag im Anwaltsregister vorgenommen oder geändert werden soll. 
 Und wir diskutieren jetzt darüber, ob wir zur Gewährleistung der Sicherheit in unserem Land auch von EU- und EFTA-Staatsangehörigen einen Strafregisterauszug verlangen wollen. Wichtig ist: Es geht nicht nur um EU- und EFTA-Staatsangehörige, sondern es geht auch um Familienangehörige von EU- und EFTA-Staatsangehörigen, die aus Drittstaaten kommen. Auch diese würden gemäss dem Entwurf des Bundesrates keinen Strafregisterauszug vorlegen müssen. 
 Ich empfehle Ihnen, hier bei der Entscheidung zu bleiben, die wir vor drei Monaten gefällt haben. Ja, das wird die EU nicht freuen. Der EU-Ministerrat wird entscheiden müssen, ob er deswegen das Vertragswerk mit der Schweiz in die Schublade legt oder ob er daran festhält. Ich meine, wir sollten unsere Souveränität nicht aufgeben, und das ist ein erster Testfall. 
 Bitte stimmen Sie bei Artikel 15a Absatz 6 mit der Minderheit.
@@ -2247,31 +2240,33 @@
     <t xml:space="preserve">422069</t>
   </si>
   <si>
-    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Der Bundesrat schliesst sich dem Antrag der WAK und der APK an.[GZ]
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Der Bundesrat schliesst sich dem Antrag der WAK-S und der APK-S an.[GZ]
 [VS][GZ]
 Angenommen - Adopté
 [VS]
-Ziff. I Art. 21b [GZ]
+Art. 21b [GZ]
 Antrag der Mehrheit SPK-S[GZ]
-Abs. 1-4, 7-11 [GZ]
+Abs. 1-4[GZ]
 Zustimmung zum Entwurf des Bundesrates
 Abs. 5 [GZ]
-Der Bundesrat prüft mindestens einmal pro Jahr gestützt auf geeignete Indikatoren, insbesondere in den Bereichen der Zuwanderung, des Arbeitsmarkts, der sozialen Sicherheit, des Wohnungswesens und des Verkehrs, ob schwerwiegende wirtscha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Der Bundesrat schliesst sich dem Antrag der WAK und der APK an.[GZ]
+Der Bundesrat prüft mindestens einmal pro Jahr gestützt auf geeignete Indikatoren, insbesondere in den Bereichen der Zuwanderung, des Arbeitsmarkts, der sozialen Sicherheit, des Wohnungswesens und des Verkehrs, ob schwerwiegende wirtschaftliche ode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Der Bundesrat schliesst sich dem Antrag der WAK-S und der APK-S an.[GZ]
 [VS][GZ]
 Angenommen - Adopté
 [VS]
-Ziff. I Art. 21b [GZ]
+Art. 21b [GZ]
 Antrag der Mehrheit SPK-S[GZ]
-Abs. 1-4, 7-11 [GZ]
+Abs. 1-4[GZ]
 Zustimmung zum Entwurf des Bundesrates
 Abs. 5 [GZ]
 Der Bundesrat prüft mindestens einmal pro Jahr gestützt auf geeignete Indikatoren, insbesondere in den Bereichen der Zuwanderung, des Arbeitsmarkts, der sozialen Sicherheit, des Wohnungswesens und des Verkehrs, ob schwerwiegende wirtschaftliche oder soziale Probleme nach Absatz 1 in der ganzen Schweiz, in einer bestimmten Region oder in einer bestimmten Branche vorliegen. Erreicht oder überschreitet die Nettozuwanderung gestützt auf das FZA oder die Zunahme der Beschäftigung von Grenzgängerinnen und Grenzgängern, der Arbeitslosigkeit oder des Sozialhilfebezugs einen vom Bundesrat festgelegten Schwellenwert, so muss der Bundesrat die Ergreifung von Massnahmen nach Absatz 6 prüfen. Ab Veröffentlichung der Daten entscheidet der Bundesrat innert vier Monaten über einen Antrag an den Gemischten Ausschuss gemäss Artikel 14a Absatz 1 FZA zur Aktivierung der Schutzklausel.
 Abs. 6[GZ]
 ...
 e. eine Lenkungsabgabe gemäss Artikel 21c.
+Abs. 7-11 [GZ]
+Zustimmung zum Entwurf des Bundesrates
 [VS]
 Antrag der Minderheit SPK-S[GZ]
 (Friedli Esther, Engler, Gössi, Jositsch, Schwander)[GZ]
@@ -2279,23 +2274,27 @@
 ... oder sozialen Problemen, so stellt der Bundesrat im Hinblick auf deren Beseitigung einen Antrag an den Gemischten Ausschuss gemäss Artikel 14a Absatz 1 FZA. Er kann ...
 [VS]
 Antrag APK-S[GZ]
-Abs. 1-4, 7-11[GZ]
+Abs. 1-4[GZ]
 Zustimmung zum Entwurf des Bundesrates
 Abs. 5 [GZ]
 ... eine entsprechende Prüfung vornehmen. Ab Veröffentlichung der Daten entscheidet der Bundesrat innert vier Monaten über einen Antrag an den Gemischten Ausschuss gemäss Artikel 14a Absatz 1 FZA zur Aktivierung der Schutzklausel.
 Abs. 6[GZ]
 ...
 e. eine Lenkungsabgabe gemäss Artikel 21c.
-[VS]
-Ch. I art. 21b [GZ]
+Abs. 7-11[GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Art. 21b [GZ]
 Proposition de la majorité CIP-E[GZ]
-Al. 1-4, 7-11[GZ]
+Al. 1-4[GZ]
 Adhérer au projet du Conseil fédéral
 Al. 5 [GZ]
 Le Conseil fédéral évalue au moins une fois par année la présence de difficultés sérieuses d'ordre économique ou social au sens de l'alinéa 1 dans toute la Suisse ou dans une région ou une branche déterminée sur la base d'indicateurs appropriés, notamment dans les domaines de l'immigration, du marché du travail, de la sécurité sociale, du logement et des transports. Il examine la possibilité de prendre des mesures au sens de l'alinéa 6 lorsque l'immigration nette induite par l'ALCP, la croissance de l'emploi frontalier, la hausse du chômage ou l'augmentation du recours à l'aide sociale atteint ou dépasse un seuil qu'il a fixé. Dans les quatre mois suivant la publication des données, le Conseil fédéral décide d'adresser ou non au comité mixte une demande d'activation de la clause de sauvegarde conformément à l'article 14bis paragraphe 1 ALCP.
 Al. 6[GZ]
 ...
 e. une taxe d'incitation selon l'article 21c.
+Al. 7-11[GZ]
+Adhérer au projet du Conseil fédéral
 [VS]
 Proposition de la minorité CIP-E[GZ]
 (Friedli Esther, Engler, Gössi, Jositsch, Schwander)[GZ]
@@ -2303,15 +2302,17 @@
 ... ou une branche déterminées, le Conseil fédéral dépose une demande auprès ...
 [VS]
 Proposition CPE-E[GZ]
-Al. 1-4, 7-11 [GZ]
+Al. 1-4[GZ]
 Adhérer au projet du Conseil fédéral
 Al. 5 [GZ]
 ... pour toute la Suisse. Dans les quatre mois suivant la publication des données, le Conseil fédéral décide d'adresser ou non au comité mixte une demande d'activation de la clause de sauvegarde conformément à l'article 14bis paragraphe 1 ALCP.
 Al. 6[GZ]
 ...
 e. une taxe d'incitation selon l'article 21c.
-[VS]
-Ziff. I Art. 21c [GZ]
+Al. 7-11 [GZ]
+Adhérer au projet du Conseil fédéral
+[VS]
+Art. 21c [GZ]
 Antrag WAK-S/APK-S[GZ]
 Al. 1 [GZ]
 Als Schutzmassnahmen oder Ausgleichsmassnahme im Sinne von Artikel 21b Absatz 6 kann der Bund eine Lenkungsabgabe erheben bei der Zulassung von Drittstaatsange hörigen sowie bei der Ausübung des Aufenthaltsrechts von mehr als drei Monaten nach dem FZA durch Staatsangehörige der EU-Mitgliedstaaten.
@@ -2352,13 +2353,13 @@
 Abs. 1bis Bst. b[GZ]
 Streichen
 Abs. 1bis Bst. c[GZ]
-Personen mit einem Aufenthalt als selbstständig Erwerbstätige;
+c. Personen mit einem Aufenthalt als selbstständig Erwerbstätige;
 Abs. 1bis Bst. d[GZ]
-Personen mit einem Aufenthalt als Nichterwerbstätige.
+d. Personen mit einem Aufenthalt als Nichterwerbstätige.
 Abs. 2 Bst. d[GZ]
 Streichen
 [VS]
-Ch. I art. 21c [GZ]
+Art. 21c [GZ]
 Proposition CER-E/CPE-E[GZ]
 Al. 1 [GZ]
 Á titre de mesure de protection ou de mesure de rééquilibrage au sens de l'article 21b alinéa 6 la Confédération peut percevoir une taxe d'incitation lors de l'admission de ressortissants d'États tiers et lors de l'exercice, par des ressortissants des États membres de l'UE, du droit de séjour de plus de trois mois prévu par l'ALCP.
@@ -2399,13 +2400,13 @@
 Al. 1bis let. b[GZ]
 Biffer
 Al. 1bis let. c[GZ]
-les personnes qui séjournent en tant que travailleurs indépendants ;
+c. les personnes qui séjournent en tant que travailleurs indépendants ;
 Al. 1bis let. d[GZ]
-les personnes qui séjournent sans exercer d'activité lucrative.
+d. les personnes qui séjournent sans exercer d'activité lucrative.
 Al. 2 let. d[GZ]
 Biffer
 [VS]
-Ziff. I Art. 21b Abs. 1 - Ch. I art. 21b al. 1[GZ]
+Art. 21b Abs. 1 - Art. 21b al. 1[GZ]
 </t>
   </si>
   <si>
@@ -2456,6 +2457,514 @@
 C'est ce que la majorité a fait. Elle a précisé que cet examen doit être fait par les autorités cantonales et que les personnes concernées ont l'obligation de collaborer. S'il y a donc un soupçon de risque pour la sécurité, l'ordre ou la santé publics, les autorités cantonales peuvent demander des pièces, peut-être pas seulement l'extrait du casier judiciaire, mais d'autres également qui permettront d'instruire cette demande. Je crois que la majorité a fait une proposition pragmatique, compatible avec le traité de libre circulation et qui atteint l'objectif, qui est d'essayer de respecter la sécurité publique.
 Enfin, j'ajoute une dernière chose par rapport à ce qu'a dit M. Daniel Fässler : la question de savoir si nous pouvons légiférer ou pas en infraction avec l'Accord sur la libre circulation des personnes, ce n'est pas à cause de ce nouveau traité qu'on devrait se la poser. On se la serait également posée si l'on n'avait pas eu le nouveau traité à discuter. De manière générale, quand on signe un traité, on doit ensuite se demander si on le respecte encore ou si on ne le respecte plus et, si on ne le respecte plus, quelles seront les conséquences de l'autre partie, si on décide de s'affranchir du traité. Sur ce plan, il n'y a donc rien de nouveau par rapport à la situation actuelle.
 C'est la raison pour laquelle je vous invite à suivre la majorité de la commission.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20260930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir sprechen heute einmal mehr und sicher nicht das letzte Mal über Ideen, wie wir die Armee finanzieren können. Ich möchte ein paar Vorbemerkungen machen. 
+Frau Bundesrätin, Herr Bundesrat, Sie haben es sich schon sehr einfach gemacht. Wenn ich in meinem privaten Haushalt mehr Ausgaben habe, dann schaue ich, dass ich die Ausgaben neu orientieren kann, dass ich neue Prioritäten setzen kann, aber ich kann nicht einfach schauen, wo ich mehr einnehmen kann. Der Bundesrat hat diese Aufgabe nicht gem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir sprechen heute einmal mehr und sicher nicht das letzte Mal über Ideen, wie wir die Armee finanzieren können. Ich möchte ein paar Vorbemerkungen machen. 
+Frau Bundesrätin, Herr Bundesrat, Sie haben es sich schon sehr einfach gemacht. Wenn ich in meinem privaten Haushalt mehr Ausgaben habe, dann schaue ich, dass ich die Ausgaben neu orientieren kann, dass ich neue Prioritäten setzen kann, aber ich kann nicht einfach schauen, wo ich mehr einnehmen kann. Der Bundesrat hat diese Aufgabe nicht gemacht. Er hat sie nicht gemacht. Er hat einfach gesagt, wir nehmen mehr Geld ein aus der Mehrwertsteuer. 
+Ich möchte Ihnen sagen, dass auch wir die Armee stärken wollen. Sie haben recht, Herr Nause, es braucht 24 Milliarden Franken zusätzlich. Wenn ich mir aber etwas anschaue, wo im Bundesbudget von heute etwa 90 Milliarden Franken - in vier Jahren sind wir bei 100 Milliarden Franken - die Gelder hingehen, dann muss ich schon sagen, dass man da durchaus Geld für die Armee freischaufeln könnte. Es sind vier Milliarden Franken pro Jahr für das Asylwesen eingestellt. Es sind über drei Milliarden Franken für die Entwicklungszusammenarbeit eingestellt. Wir haben nie gesagt, dass wir einen Trinkwasserbrunnen streichen wollen - Frau Funiciello ist ja gar nicht da, es interessiert sie gar nicht, das ist ja klar - , aber wir haben Ihnen aufgezeigt, wo Einsparungen möglich sind. Da finde ich es schon fragwürdig, dass wir es hingekriegt haben, aus diesen rund 3 Milliarden Franken gerade mal 20 Millionen Franken einzusparen. 
+Es liegt ein Faktenblatt des Finanzdepartementes vor, das besagt, dass die Idee des Ständerates nicht schuldenbremsenkonform ist. Ich muss Ihnen sagen, ich möchte am Morgen, wenn ich aufstehe, noch in den Spiegel schauen können. Ich möchte nicht, dass wir der jungen Generation einen Schuldenberg hinterlassen. Aber ich will, dass die Sicherheit der Schweiz gestärkt wird, und da muss ich Ihnen sagen, dass in diesem Budget von 90 Milliarden Franken Verschiebungen möglich sein müssen. 
+Unsere Motion sieht genau das vor. Wir wollen Priorisierungen und Effizienzsteigerungen im Eigenbereich; übrigens, Herr Bundesrat Pfister, auch im VBS. Wir wollen Priorisierungen bestehender und geplanter mehrjähriger Finanzbeschlüsse; ich habe vorhin aufgezeigt, wo. Wir wollen weitere Massnahmen bei den gebundenen Ausgaben, beispielsweise die Einführung eines Flexibilisierungsmechanismus. So kommen wir zum Ziel. Aber wenn Sie einfach nur sagen, wir brauchen mehr Geld für die Armee, und Sie dieses Geld aus Zusatzeinnahmen nehmen, dann muss ich Ihnen sagen, dass das für die SVP-Fraktion schwierig wird. Ich möchte insbesondere Sie, liebe Kolleginnen und Kollegen aus dem bürgerlichen Lager, bitten, hier Hand zu bieten. Klar, bei den Linken steht die Abschaffung der Armee immer noch im Parteiprogramm, und dazu stehen sie, das wollen sie nicht rausnehmen. Aber Sie stehen wie wir ein für die Armee. Bieten Sie hier Hand. Danke für die Unterstützung dieser Fraktionsmotion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herr Bundesrat, 4 Milliarden Franken geben wir jährlich für das Asyl- und Flüchtlingswesen aus, mehr als 3 Milliarden Franken für die Entwicklungszusammenarbeit. Sie sind nicht bereit, da nur einen einzigen Franken einzusparen, Sie kommen stattdessen mit einer Mehrwertsteuererhöhung als Lösung. Wir brauchen, Herr Kollege Nause sagte das, 2,5 Milliarden Franken im Jahr. Können Sie uns erklären, wie diese Diskussion im Bundesrat ablief? (Teilweise Heiterkeit)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gartmann Walter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SVP-Fraktion steht ohne Wenn und Aber hinter einer starken und verteidigungsfähigen Schweizer Armee. Es braucht mehr Geld für die Verteidigungsfähigkeit und nicht wie bisher für mehr Bürokratie, gescheiterte Projekte und schlecht verhandelte Beschaffungen. Aber wir sagen ebenso klar: Die notwendige Stärkung unserer Armee darf nicht zum Freipass für immer mehr neue Steuern werden. 
+Die Bundesverfassung gibt uns den klaren Auftrag. Artikel 58 Absatz 2 hält fest: "Die Armee dient der Kriegsverh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SVP-Fraktion steht ohne Wenn und Aber hinter einer starken und verteidigungsfähigen Schweizer Armee. Es braucht mehr Geld für die Verteidigungsfähigkeit und nicht wie bisher für mehr Bürokratie, gescheiterte Projekte und schlecht verhandelte Beschaffungen. Aber wir sagen ebenso klar: Die notwendige Stärkung unserer Armee darf nicht zum Freipass für immer mehr neue Steuern werden. 
+Die Bundesverfassung gibt uns den klaren Auftrag. Artikel 58 Absatz 2 hält fest: "Die Armee dient der Kriegsverhinderung und trägt bei zur Erhaltung des Friedens; sie verteidigt das Land und seine Bevölkerung." Das ist kein Wunschkonzert, das ist ein klarer Verfassungsauftrag. Wer einen Verfassungsauftrag erfüllen muss, hat im Bundeshaushalt entsprechende Prioritäten zu setzen.
+Der Bund gibt 2027 rund 94 Milliarden Franken aus. Mir kann niemand erklären, dass es bei einem solchen Haushalt unmöglich sein soll, die Verteidigungsfähigkeit unseres eigenen Landes ordentlich zu finanzieren. Es fehlt nicht am Geld, es fehlt an der Prioritätensetzung. Bevor man den Bürgerinnen und Bürgern über die Mehrwertsteuer erneut ins Portemonnaie greifen will, muss der Bund zuerst seine Hausaufgaben machen. Dazu gehört auch ausdrücklich das VBS. 
+Die SVP-Fraktion fordert nicht einfach mehr Finanzen für die Armee. Nein, wir fordern mehr Kampfkraft, mehr Verteidigungsfähigkeit für jeden eingesetzten Franken. Das bedeutet weniger Bürokratie, weniger Doppelspurigkeiten, schlankere Verwaltungsstrukturen und effizientere Beschaffungsprozesse. Wir brauchen mehr Soldaten und Systeme, die im Ernstfall funktionieren, und nicht immer mehr Stellen, Sitzungen, Konzepte und Papier im Büroapparat. Das heisst kurz und bündig: Büroapparat verkleinern, Effizienz erhöhen, Mittel konsequent zur Truppe und nah an die Verteidigungsfähigkeit verschieben. Genau dies muss ab heute auch das Credo im VBS sein. Dass dies möglich ist, zeigt der Bundesrat ansatzweise auch selbst. Zusätzliche Mittel für NDB und BABS sollen durch Priorisierungen innerhalb des VBS finanziert sein. Genau dieses Prinzip muss zukünftig überall konsequent angewendet werden. 
+Aber auch ausserhalb des VBS müssen wir endlich Prioritäten setzen. Wir geben Milliarden Franken für die internationale Zusammenarbeit aus. Wir haben hohe Ausgaben im Asyl- und Migrationsbereich. Gleichzeitig sollen wir unserer eigenen Bevölkerung erklären, für die Verteidigung unseres Landes sei im ordentlichen Bundeshaushalt kein Geld mehr vorhanden. Das versteht doch kein Mensch. 
+Für die SVP gilt deshalb ein klarer Grundsatz, nämlich "Switzerland first". Das bedeutet nicht, dass sich die Schweiz von der Welt abwendet. Es bedeutet aber sehr wohl, dass die Sicherheit der eigenen Bevölkerung und die Verteidigung des eigenen Landes zuerst kommt. Wir haben die Armee über Jahrzehnte hinweg finanziell zurückgefahren. 1990 flossen noch 1,33 Prozent des BIP in die Armee. 2025 waren es nur noch 0,67 Prozent. So geht es nicht weiter. Wir müssen dies dringend jetzt und heute korrigieren. 
+Diese Korrektur muss über Priorisierung, Umschichtung und Effizienzsteigerung erfolgen und nicht, wie fast schon auf Bundesebene üblich, reflexartig immer über neue Einnahmen und Steuern. Die SVP verlangt ganz klar, dass das Aufwuchsziel der Armee im ordentlichen Bundeshaushalt sichergestellt wird. Das VBS muss seinen Büroapparat verkleinern und seine Effizienz deutlich steigern. Nicht sicherheitsrelevante Bundesausgaben, insbesondere auch bei der Entwicklungshilfe sowie im Asyl- und Migrationsbereich, müssen konsequent überprüft und priorisiert werden. Es stellt sich hier einmal mehr die Frage: Was ist die erste Pflicht unseres Staates? Die Antwort steht in der Bundesverfassung: Land und Bevölkerung schützen. Wer fast 94 Milliarden Franken pro Jahr ausgibt, muss fähig sein, genügend Geld für die Kernaufgabe bereitzustellen. 
+Ich danke Ihnen für die Unterstützung unserer Motion.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie vermischen hier etwas: Ich habe nicht vom Klima gesprochen, ich habe von Kürzungen im Asylwesen und bei der Entwicklungshilfe gesprochen. Ich denke, wir werden das Klima nicht retten, indem wir nur demonstrieren und grüne Anliegen einbringen. Wir müssen uns der Situation stellen. Wir können z. B. Wasser zurückhalten, Staubecken bauen - das wäre richtig. Mit einer guten Armee können wir diese Staubecken und all das, was wir tun, gut sichern.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schauen Sie, Herr Kollege, ich habe das schon mehrmals gesagt: Immer, wenn ich solche Entscheide treffen muss, sehe ich eine alte Apothekerwaage vor mir mit zwei Schalen. Wenn ich in der einen Schale die Sicherheit unseres Landes habe und in der anderen Gelder, um irgendwelche Projekte im Asylwesen zu finanzieren, dann können Sie sich selbst vorstellen, welche Schale die schwerere ist: Es ist definitiv die Schale mit der Sicherheit unseres Landes. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Ventura Linda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Forderung ist in diesem Vorstoss so nicht enthalten. Darum möchte ich auf Ihre Frage auch keine differenzierte Antwort geben. Aber ich bin dagegen, dass man bei der Diskussion der Armeefinanzierung immer auf die Sans-Papiers und die Flüchtlinge schiesst, wie Sie es tun. Dagegen wehre ich mich.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag der Mehrheit [GZ]
+Eintreten
+[VS]
+Antrag der Minderheit [GZ]
+(Schmid Pascal, Buffat, Fischer Benjamin, Glarner, Knutti, Kolly, Riner, Rutz Gregor)[GZ]
+Rückweisung des Geschäftes an den Bundesrat[GZ]
+mit dem Auftrag, [GZ]
+- zwei separate Vorlagen vorzulegen (Förderung der Erwerbstätigkeit von Personen mit Schutzstatus S und Zulassungserleichterungen für in der Schweiz ausgebildete Drittstaatsangehörige); und 
+- darin in Nachachtung von Artikel 121a der Bundesverfassung an die Zulassungserle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antrag der Mehrheit [GZ]
+Eintreten
+[VS]
+Antrag der Minderheit [GZ]
+(Schmid Pascal, Buffat, Fischer Benjamin, Glarner, Knutti, Kolly, Riner, Rutz Gregor)[GZ]
+Rückweisung des Geschäftes an den Bundesrat[GZ]
+mit dem Auftrag, [GZ]
+- zwei separate Vorlagen vorzulegen (Förderung der Erwerbstätigkeit von Personen mit Schutzstatus S und Zulassungserleichterungen für in der Schweiz ausgebildete Drittstaatsangehörige); und 
+- darin in Nachachtung von Artikel 121a der Bundesverfassung an die Zulassungserleichterungen geknüpfte zahlenmässige Reduktionsmassnahmen, allenfalls in anderen Bereichen des Ausländer- und Asylrechts, festzulegen.
+[VS]
+Proposition de la commission [GZ]
+Entrer en matière
+[VS]
+Antrag der Minderheit [GZ]
+(Schmid Pascal, Buffat, Fischer Benjamin, Glarner, Knutti, Kolly, Riner, Rutz Gregor)[GZ]
+Renvoyer l'objet au Conseil fédéral [GZ]
+avec mandat [GZ]
+- de présenter deux projets distincts (promotion de l'activité lucrative des personnes bénéficiant du statut de protection S et facilitation de l'admission des ressortissants d'Etats tiers formés en Suisse) et 
+- d'y prévoir des mesures de réduction numériques liées aux facilitations des admissions, éventuellement d'autres domaines du droit d'asile et des étrangers, conformément à l'article 121a de la Constitution.
+[VS]
+Le président (Page Pierre-André, président): Nous allons mener un seul débat sur l'entrée en matière et la discussion par article. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avec ce projet, le Conseil fédéral et la majorité de la commission entendent faciliter l'accès au marché du travail pour deux groupes de personnes. Premièrement, les personnes au bénéfice du statut de protection S doivent être mieux intégrées sur le marché du travail. Les Ukrainiennes et Ukrainiens sans activité professionnelle seront désormais inscrits auprès du service public de l'emploi. Les employés qui exercent une activité lucrative pourront, à certaines conditions, avoir la possibilité de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avec ce projet, le Conseil fédéral et la majorité de la commission entendent faciliter l'accès au marché du travail pour deux groupes de personnes. Premièrement, les personnes au bénéfice du statut de protection S doivent être mieux intégrées sur le marché du travail. Les Ukrainiennes et Ukrainiens sans activité professionnelle seront désormais inscrits auprès du service public de l'emploi. Les employés qui exercent une activité lucrative pourront, à certaines conditions, avoir la possibilité de changer de canton. Les titulaires d'un permis S voulant travailler ne doivent pas se heurter à des obstacles administratifs. C'est d'autant plus vrai en situation de pénurie de personnel dans toute une série de secteurs d'activité, notamment dans les soins.
+Deuxièmement, les facilités d'admission sont étendues aux ressortissants étrangers diplômés d'une formation professionnelle supérieure en Suisse ainsi qu'aux postdoctorants. Ces aménagements, comme exception au système de priorité des travailleurs indigènes, sont conditionnés à l'intérêt scientifique ou économique majeur de l'activité. Étendre cette possibilité aux diplômés en Suisse en cas de lien avec l'activité visée serait une option "win-win" pour l'employé comme pour notre pays. C'est la raison pour laquelle nous vous demandons de soutenir la proposition de la minorité I (Kälin) de la commission à l'article 21 alinéa 3 de la loi fédérale sur les étrangers et l'intégration. Nous permettrons ainsi à ces profils de mettre à profit leurs qualifications acquises, ce qui est également un atout pour notre pays.
+Le projet apporte des améliorations ciblées et judicieuses en matière d'intégration sur le marché de l'emploi. Il n'existe aucune raison objective de le scinder et de le retarder. Nous refusons de lier ces améliorations de l'accès au marché de l'emploi à des restrictions supplémentaires dans d'autres domaines du droit de la migration et de l'asile. Un tel durcissement apporterait un signal contradictoire face à l'objectif d'intégration de la révision de cette loi.
+Mais ce n'est pas tout. Nous voulons aller plus loin en soutenant la proposition de la minorité I (Kälin) qui crée un droit au changement de canton lorsqu'un rapport de travail existe dans le canton de destination, ou est concrètement imminent, et que la personne est indépendante de l'aide sociale ou que le changement de canton réduirait cette dépendance. Les obligations de garde, le trajet et les horaires de travail doivent être pris en compte. Le changement de canton est ainsi résolument orienté vers l'objectif d'intégration sur le marché du travail.
+Je vous remercie d'entrer en matière sur cette révision de loi et de suivre les minorités I (Kälin), II (Dünki-Bättig) et III (Dünki-Bättig).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat verfolgt das Ziel, das inländische Arbeitskräftepotenzial konsequent zu fördern. Warum? Wenn die Schweizer Firmen ihre offenen Stellen mit Leuten besetzen können, die schon da sind, dann müssen sie weniger im Ausland rekrutieren, dann geht die Zuwanderung tendenziell zurück. Das ist das Ziel dieser Vorlage; das war das Versprechen des Bundesrates im Zusammenhang mit der Nachhaltigkeits-Initiative. Mit dieser Vorlage setzt er dieses Versprechen um - er bricht es nicht, wie Sie zum T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Bundesrat verfolgt das Ziel, das inländische Arbeitskräftepotenzial konsequent zu fördern. Warum? Wenn die Schweizer Firmen ihre offenen Stellen mit Leuten besetzen können, die schon da sind, dann müssen sie weniger im Ausland rekrutieren, dann geht die Zuwanderung tendenziell zurück. Das ist das Ziel dieser Vorlage; das war das Versprechen des Bundesrates im Zusammenhang mit der Nachhaltigkeits-Initiative. Mit dieser Vorlage setzt er dieses Versprechen um - er bricht es nicht, wie Sie zum Teil behauptet haben, sondern er setzt es um. Sie verstösst in keiner Weise gegen Artikel 121a der Bundesverfassung. Eine Kompensation ist nicht nötig, weil die Drittländer-Kontingentierung mit dieser Vorlage nicht erhöht wird. 
+Der vorliegende Entwurf enthält zwei Massnahmen. Die erste Massnahme betrifft Personen mit Schutzstatus S, die zweite Massnahme betrifft ausländische Absolventinnen und Absolventen von Schweizer Ausbildungen. 
+Ich beginne mit den Massnahmen für Personen mit Schutzstatus S. Die kantonalen Sozialhilfebehörden werden stellenlose Personen mit Schutzstatus S bei der öffentlichen Arbeitsvermittlung melden müssen. Zudem werden diese Personen bei Erwerbstätigkeit einfacher den Kanton wechseln können. Wieso schlägt der Bundesrat diese Anpassungen vor? Arbeit ist ein zentraler Schlüssel für eine gelungene Integration. Sie schafft wirtschaftliche Unabhängigkeit, fördert den Spracherwerb im Alltag und ermöglicht soziale Kontakte. In den letzten Jahren konnten wir positive Erfahrungen im Bereich der Integrationsförderung von anerkannten Flüchtlingen und vorläufig aufgenommenen Personen sammeln. Die Integrationsagenda war und ist immer noch zentral für diese positive Entwicklung. 
+Wir haben aber auch positive Erfahrungen mit dem Ersatz des Bewilligungsverfahrens durch eine einfache Meldepflicht für eine Erwerbstätigkeit gemacht. Damit wurde der administrative Aufwand für Arbeitgebende deutlich reduziert. Die Hürde, Geflüchtete einzustellen, ist gesunken. 
+Zudem wurde der Kantonswechsel bei Erwerbstätigkeit erleichtert und eine Meldepflicht bei der öffentlichen Arbeitsvermittlung für stellensuchende Personen geschaffen. Wer eine Stelle in einem anderen Kanton hat, kann sie heute auch antreten; genau das war das Ziel. Diese Massnahmen gelten heute bereits für anerkannte Flüchtlinge und vorläufig aufgenommene Personen. Der Bundesrat will diesen positiven Effekt künftig auch für Personen mit Schutzstatus S erzielen. Deshalb sollen die bewährten Massnahmen zur Förderung der Erwerbstätigkeit von vorläufig aufgenommenen Personen auch beim Schutzstatus S zur Anwendung kommen. 
+Ich komme zur zweiten Massnahme. In der Praxis erhalten ausländische Absolventinnen und Absolventen der höheren Berufsbildung sowie Postdoktorandinnen und Postdoktoranden häufig keine Aufenthaltsbewilligung für eine Erwerbstätigkeit, weil der Inländervorrang gilt. Die vorgeschlagene Änderung hebt die Prüfung des Inländervorrangs auf. Der Bundesrat hat dieser Aufhebung aber Schranken gesetzt. Die geplante Erwerbstätigkeit muss von hohem wissenschaftlichem oder wirtschaftlichem Interesse für den Schweizer Arbeitsmarkt sein. Im Bereich der höheren Berufsbildung betrifft die Änderung vor allem zwei Gruppen von Drittstaatsangehörigen: erstens Absolventinnen und Absolventen anerkannter höherer Fachschulen, zweitens Personen mit einem eidgenössischen Fachausweis oder Diplom, die ihre gesamte Aus- und Weiterbildung in der Schweiz absolviert haben. 2025 erwarben über 800 Drittstaatsangehörige einen Abschluss der höheren Berufsbildung; davon waren gut 450 in einer höheren Fachschule.
+Zu den Folgen der Vorlage für Bund und Kantone; ich beginne mit den Massnahmen für Personen mit einem Schutzstatus. Die Gesuche um Kantonswechsel können mit den bestehenden Ressourcen bearbeitet werden. Auch die Meldepflicht bei der öffentlichen Arbeitsvermittlung führt nicht zu direkten finanziellen Mehraufwänden für den Bund. Für den Ausgleichsfonds der Arbeitslosenversicherung entstehen aber Mehrkosten, weil mehr Personen die öffentliche Arbeitsvermittlung nutzen werden. Gleichzeitig dürften mehr Personen mit Schutzstatus S eine Arbeit finden, und das senkt die Sozialhilfekosten, die der Bund den Kantonen zurückerstattet. Diese Einsparungen dürften die Mehrkosten deutlich übersteigen. 
+Zu den Konsequenzen des zweiten Teils der Vorlage: Bei den Absolventinnen und Absolventen der Berufsbildung erwartet das SEM lediglich einen zusätzlichen Anteil an Gesuchen im zweistelligen Bereich pro Jahr. Bei den Postdoktorandinnen und Postdoktoranden kommen zwar rund 300 bis 400 Personen potenziell infrage, tatsächlich dürften aber deutlich weniger von der neuen Regelung Gebrauch machen. Die Konsequenzen sind somit auch hier begrenzt.
+Bevor ich zum Schluss komme, möchte ich noch zurückblicken. Die Vorlage, die Sie heute beraten, geht auf die Rückweisung der Botschaft vom 19. Oktober 2022 zur Änderung des Ausländer- und Integrationsgesetzes zurück. Das Parlament verlangte vom Bundesrat eine neue Lösung, die mit Artikel 121a der Bundesverfassung vereinbar ist und gleichzeitig qualifizierten ausländischen Absolventinnen und Absolventen den Zugang zum Schweizer Arbeitsmarkt erleichtert. Mit der Vorlage hier setzt der Bundesrat diesen Auftrag um. Die Bewilligungen werden weiterhin den bestehenden Kontingenten für Drittstaatsangehörige angerechnet, sodass die Zuwanderung genau gleich steuerbar bleibt wie vorher. 
+Eine Minderheit Ihrer Kommission beantragt, die Vorlage erneut an den Bundesrat zurückzuweisen. Einerseits sollen die Änderungen auf zwei separate Vorlagen aufgeteilt werden, andererseits sollen zusätzliche Massnahmen vorgesehen werden, um die mit den Zulassungserleichterungen verbundene Zuwanderung auszugleichen.
+Der Bundesrat sieht dafür keinen Anlass. Die Aufteilung der Vorlage bringt nichts. Die verschiedenen Elemente der Vorlage verfolgen denselben Zweck und gehören inhaltlich zusammen. Der Zugang zum Arbeitsmarkt soll für bestimmte Drittstaatsangehörige erleichtert werden. Dadurch wird ihre Teilhabe am wirtschaftlichen Leben ermöglicht und zugleich ein Beitrag zur Deckung des Arbeitskräftebedarfs geleistet. Auch die erleichterte Zulassung von Personen, die ihre Ausbildung an einer anerkannten Schweizer Bildungsinstitution abgeschlossen haben, dient genau diesem Ziel. Der Bundesrat beantragt deshalb, eine Aufteilung der Vorlage abzulehnen. 
+Zusätzliche Massnahmen im Zuwanderungsbereich braucht es wegen dieser Änderungen nicht, weil diese Vorlage nicht zusätzlich Migration auslöst. Sie richtet lediglich die Zuwanderung gezielt an den Bedürfnissen der Schweiz aus. Genau dies wird erreicht, wenn qualifizierte Personen, die in der Schweiz eine Ausbildung an einer höheren Fachschule abgeschlossen haben oder als Postdoktorandinnen und Postdoktoranden tätig waren, ihr erworbenes Wissen auch auf dem Schweizer Arbeitsmarkt einsetzen können. Personen mit Schutzstatus S fallen nicht unter Artikel 121a BV. Sie halten sich bereits rechtmässig in der Schweiz auf, sie sind schon da. Diese Bestimmungen führen daher nicht zu zusätzlicher Zuwanderung.
+Aus diesen Gründen empfiehlt der Bundesrat die Ablehnung des Rückweisungsantrages.
+Die SPK-N beantragt zudem mit der vorliegenden Vorlage, das Geschäft 22.067, "Ausländer- und Integrationsgesetz. Zulassungserleichterung für Ausländerinnen und Ausländer mit Schweizer Hochschulabschluss", abzuschreiben. Der Bundesrat unterstützt diesen Antrag, da das Geschäft gegenstandslos geworden ist. 
+Ihre Kommission hat die Vorlage mit 16 zu 9 Stimmen angenommen. Der Bundesrat beantragt, auf die Vorlage einzutreten und den Entwurf gemäss dem Antrag der Mehrheit Ihrer Kommission anzunehmen.
+Ich äussere mich jetzt noch zu den Minderheits- und Mehrheitsanträgen. Ich starte mit dem Antrag der Mehrheit zur Anpassung der Formulierung in Artikel 21 Absatz 3 des AIG rund um das Postdoktorat. Der Bundesrat unterstützt den Vorschlag der Kommissionsmehrheit. Die neue Formulierung stimmt mit dem bundesrätlichen Entwurf überein und schafft Klarheit. 
+Der Bundesrat lehnt den Antrag der Minderheit I zur Anpassung von Artikel 21 Absatz 3 des AIG ab. Der vorgeschlagene Bezug zum erworbenen Abschluss lässt einen zu grossen Interpretationsspielraum zu. Der Vorschlag des Bundesrates mit dem Zusatz "von wirtschaftlichem Interesse" schafft hingegen Klarheit. Vom Inländervorrang wird nur dort abgewichen werden können, wo auf dem Arbeitsmarkt tatsächlich ein ausgewiesener Bedarf besteht. Davon können insbesondere Berufe profitieren, in denen Fachkräfte fehlen, etwa in der Pflege oder in der Hotellerie. 
+Ich komme zum Antrag der Minderheit II. Die Minderheit II schlägt vor, Artikel 21 Absatz 3 zu streichen. Der Antrag würde die vom Parlament geforderte Zulassungserleichterung für ausländische Absolventinnen und Absolventen der höheren Berufsbildung sowie für Postdoktorandinnen und Postdoktoranden faktisch aushebeln. Und damit würde ein zentrales Element der Rückweisung fehlen oder wegfallen. Ziel der vorgeschlagenen Regelung ist es eben, gerade diesen Personen den Zugang zum Schweizer Arbeitsmarkt zu erleichtern. Artikel 21 Absatz 3 setzt damit den klaren Willen des Parlamentes um. Aus diesen Gründen lehnt der Bundesrat diesen Antrag ab.
+Ich komme zum Artikel 53 Absatz 5. Der Bundesrat lehnt den Antrag der Minderheit Steinemann ab. Diese will die Änderung von Absatz 5 streichen. Der Bundesrat ist überzeugt, dass die Meldepflicht die Erwerbstätigenquote erhöht und folglich unter dem Strich sinnvoll und kostensparend ist. Bei den Arbeitsvermittlungsstellen entsteht ein zusätzlicher Aufwand, aber der lohnt sich. Durch die Erhöhung der Erwerbstätigenquote von Personen mit vorübergehendem Schutz sind beim Bund Einsparungen bei der Subventionierung, also bei der Erstattung von Sozialhilfe an die Kantone, zu erwarten. Mit jeder zusätzlichen erwerbstätigen Person reduzieren sich die Beiträge des Bundes im Bereich der Globalpauschale. Auch bei den Kantonen sind Einsparungen bei der Ausrichtung der Sozialhilfe zu erwarten. 
+Der Bundesrat lehnt bei Artikel 75a auch die Anträge der Minderheiten I, II und III ab. Er versteht das Anliegen der Minderheiten. Auch der Bundesrat möchte die Erwerbsquote von Schutzbedürftigen, vorläufig aufgenommenen und anerkannten Flüchtlingen generell weiter erhöhen und deren Sozialhilfeabhängigkeit reduzieren. Deshalb möchte der Bundesrat verschiedene Erleichterungen, die sich bei vorläufig aufgenommenen Personen bewährt haben, künftig auch für Schutzbedürftige vorsehen. Weitergehende Erleichterungen, die ausschliesslich für Personen mit Schutzstatus S gelten, würden zu einer Besserstellung gegenüber vorläufig aufgenommenen Personen führen. Dies wäre aus Sicht des Bundesrates nicht gerechtfertigt. Aus diesem Grund lehnt der Bundesrat die Anträge der drei Minderheiten ab. 
+Der Bundesrat verweist, was die Minderheiten II und III anbelangt, auf seine Ausführungen, die ich jetzt gerade zur Minderheit I gemacht habe. 
+Schliesslich richte ich am Schluss im Namen des Bundesrates die Bitte an Sie, dem Antrag der Mehrheit Ihrer Kommission zuzustimmen, die Minderheitsanträge abzulehnen und ansonsten der Vorlage zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous l'avez entendu, nous sommes saisis en tout de sept propositions de minorité. Je vais vous exposer les résultats des débats en commission pour l'ensemble de ces propositions.
+La minorité Schmid Pascal vous propose de renvoyer le projet au Conseil fédéral pour le scinder en deux projets distincts. Permettez-moi ici une remarque personnelle : en regroupant dans un même message un certain nombre de modifications, certes différentes, mais ayant toutes trait au même sujet, à savoir l'employabilit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous l'avez entendu, nous sommes saisis en tout de sept propositions de minorité. Je vais vous exposer les résultats des débats en commission pour l'ensemble de ces propositions.
+La minorité Schmid Pascal vous propose de renvoyer le projet au Conseil fédéral pour le scinder en deux projets distincts. Permettez-moi ici une remarque personnelle : en regroupant dans un même message un certain nombre de modifications, certes différentes, mais ayant toutes trait au même sujet, à savoir l'employabilité des étrangers, le Conseil fédéral a fait preuve d'efficacité. Demander maintenant au Conseil fédéral de revenir avec deux projets distincts, alors que ce projet est débattu depuis de nombreuses années déjà, voilà qui n'a clairement pas convaincu notre commission. Par 16 voix contre 9, notre commission a refusé la proposition défendue par la minorité Schmid Pascal.
+À l'article 21 alinéa 3, la minorité I (Kälin) vous propose d'étendre la possibilité d'admission d'un étranger ou d'une étrangère, si l'activité lucrative visée est en adéquation avec le diplôme obtenu. La majorité de notre commission a cependant considéré qu'il n'était pas acceptable d'enlever à l'État, en l'occurrence aux cantons, la possibilité de gérer les admissions en fonction des besoins de l'économie. Par 15 voix contre 9, la commission vous invite à rejeter cette proposition.
+Toujours au même article, la minorité II (Schmid Pascal) propose de biffer l'entier de l'alinéa. Cela reviendrait non seulement à purement et simplement ignorer la mise en oeuvre de la motion Dobler Marcel adoptée par les deux chambres, mais aussi à durcir la loi par rapport au droit en vigueur. Ce n'est clairement pas ce que le législateur a voulu. Par 16 voix contre 9, la commission a par conséquent refusé cette proposition. Je vous invite, au nom de la majorité, à en faire autant.
+À l'article 53 alinéa 5, la minorité Steinemann propose de biffer l'obligation d'annonce aux autorités cantonales. Or, dans le droit en vigueur, cette obligation existe déjà pour les réfugiés reconnus et les personnes admises à titre provisoire. Cette mesure a d'ailleurs fait ses preuves pour ces catégories de personnes, raison pour laquelle la commission souhaite l'étendre au personnes à protéger, c'est-à-dire aux titulaires d'un statut S, afin de permettre une intégration plus rapide au marché du travail et de réduire le recours à l'aide sociale. Notre commission a rejeté la proposition défendue par la minorité Steinemann, par 15 voix contre 9.
+Les trois minorités à l'article 75a, à savoir les minorités I (Kälin), II (Dünki-Bättig) et III (Dünki-Bättig), proposent toutes un assouplissement de la possibilité de changer de canton de résidence.
+Globalement, la majorité de notre commission a considéré que ces propositions de minorité pouvaient certes, d'une certaine manière, faciliter l'intégration dans le monde du travail des personnes à protéger, mais qu'en revanche, les risques liés au tourisme d'assurances sociales étaient trop grands par rapport aux avantages que ces propositions de minorité pourraient apporter.
+S'agissant de la minorité I (Kälin), des formulations sont trop peu précises, comme "rapports sur le point d'être établis" - que veut dire "sur le point de" ? - ou encore "changement de canton qui permettra vraisemblablement de mettre fin à la dépendance à l'aide sociale" - comment évaluer le concept de "vraisemblablement" ? Bref, aux yeux de votre commission, ces formulations étaient trop peu précises pour être acceptables. De plus, avec cette minorité, des demandes de changement de cantons pourraient être déposées, y compris durant la période d'essai d'un nouveau contrat de travail, ce qui peut être de nature à favoriser le tourisme d'aide sociale. 
+Par 17 voix contre 8 voix, la commission vous invite à rejeter cette proposition.
+Le même raisonnement vaut pour la proposition défendue par la minorité II (Dünki-Bättig), rejetée par 16 voix contre 8 et 1 abstention.
+Quant à la minorité III (Dünki-Bättig), je dois vous rendre attentifs sur une imprécision sur le plan de la traduction. Il s'agit d'une remarque personnelle vu que j'ai relevé cette imprécision en préparant mon rapport de commission. En effet, en allemand, le texte traite de "familiärer Betreuungspflichten", ce qui correspond à des obligations en lien avec la garde d'enfants par exemple. En revanche, en français, le texte parle simplement d'"obligations familiales", ce qui est nettement plus large que le terme allemand de "Betreuungspflichten" et peut également comprendre des activités telles qu'amener son fils au foot. La notion de "Betreuung" a disparu de la version française. Or, vu la direction prise par les discussions en commission, il paraît évident que l'idée n'est pas que le SEM tienne compte de simples obligations familiales pour accorder ou non le droit de changer de canton. Ceci dit, par 16 voix contre 8 et 1 abstention, la commission vous invite à rejeter cette proposition.
+En conclusion, avec ce projet de modification de la loi fédérale sur les étrangers et l'intégration, nous plaçons les jalons nécessaires pour favoriser l'intégration sur le marché du travail des personnes pour lesquelles la Suisse a investi dans la formation ou pour les personnes qui se trouvent déjà chez nous et pour lesquelles il serait plus pertinent de travailler que de percevoir l'aide sociale.
+Par 16 voix contre 9 au vote sur l'ensemble, la commission a accepté les modifications de la loi fédérale sur les étrangers et l'intégration et je vous invite à en faire autant. Je le redis : le projet qui vous est proposé aujourd'hui est en tous points compatible avec l'article 121a de la Constitution.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ziff. II Einleitung [GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Ch. II introduction [GZ]
+Proposition de la commission [GZ]
+Adhérer au projet du Conseil fédéral [GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Ziff. II Art. 75a [GZ]
+Antrag der Mehrheit [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Antrag der Minderheit I[GZ]
+(Kälin, Dünki-Bättig, Gysin Greta, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Abs. 1 [GZ]
+... absolviert, hat Anspru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ziff. II Einleitung [GZ]
+Antrag der Kommission [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Ch. II introduction [GZ]
+Proposition de la commission [GZ]
+Adhérer au projet du Conseil fédéral [GZ]
+[VS][GZ]
+Angenommen - Adopté
+[VS]
+Ziff. II Art. 75a [GZ]
+Antrag der Mehrheit [GZ]
+Zustimmung zum Entwurf des Bundesrates
+[VS]
+Antrag der Minderheit I[GZ]
+(Kälin, Dünki-Bättig, Gysin Greta, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Abs. 1 [GZ]
+... absolviert, hat Anspruch auf einen Kantonswechsel, sofern:
+a. ein Arbeitsverhältnis im Zielkanton besteht oder konkret bevorsteht;
+b. die betroffene Person überwiegend von der Sozialhilfe unabhängig ist oder durch den Kantonswechsel eine Sozialhilfeabhängigkeit voraussichtlich abgebaut werden kann.
+Abs. 2 [GZ]
+Das SEM berücksichtigt bei der Beurteilung die individuelle Situation der betroffenen Person, insbesondere Betreuungspflichten gegenüber Kindern oder anderen Familienangehörigen, sowie den Arbeitsweg und die Arbeitszeiten. Die vollständige Sozialhilfeunabhängigkeit aller Familienangehörigen ist keine zwingende Voraussetzung. (Rest streichen)
+[VS]
+Antrag der Minderheit II[GZ]
+(Dünki-Bättig, Gysin Greta, Kälin, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Abs. 2 Bst. a [GZ]
+a. die Person für sich und ihre Familienangehörigen keine oder nur teilweise Sozialhilfe bezieht; und
+[VS]
+Antrag der Minderheit III[GZ]
+(Dünki-Bättig, Gysin Greta, Kälin, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Abs. 2 Bst. b [GZ]
+b. ... aufgrund des Arbeitsweges, der Arbeitszeiten oder familiärer Betreuungspflichten nicht zumutbar ist.
+[VS]
+Ch. II art. 75a [GZ]
+Proposition de la majorité [GZ]
+Adhérer au projet du Conseil fédéral
+[VS]
+Proposition de la minorité I[GZ]
+(Kälin, Dünki-Bättig, Gysin Greta, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Al. 1 [GZ]
+... de résidence a le droit de changer de canton :
+a. s'il existe des rapports de travail dans le canton en question ou que de tels rapports sont sur le point d'être établi ;
+b. si la personne concernée est, pour l'essentiel, indépendante de l'aide sociale ou que le changement de canton permettra vraisemblablement de mettre fin à sa dépendance à l'aide sociale.
+Al. 2 [GZ]
+Lors de l'examen de la demande, le SEM tient compte de la situation individuelle de la personne concernée, notamment la prise en charge d'enfants ou d'autres membres de la famille ainsi que le déplacement vers le lieu de travail et les horaires de travail. L'indépendance complète de toute la famille vis-à-vis de l'aide sociale ne constitue pas une condition impérative. (Biffer le reste)
+[VS]
+Proposition de la minorité II[GZ]
+(Dünki-Bättig, Gysin Greta, Kälin, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Al. 2 let. a [GZ]
+a. si la personne ne perçoit aucune prestation ou uniquement certaines prestations de l'aide sociale ni pour elle ni pour les membres de sa famille, et
+[VS]
+Proposition de la minorité III[GZ]
+(Dünki-Bättig, Gysin Greta, Kälin, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
+Al. 2 let. b [GZ]
+b. ... l'horaire de travail, le trajet pour se rendre au travail ou des obligations familiales ne permettent pas d'exiger raisonnablement qu'elle reste dans son canton de résidence.
+[VS]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsieur Wandfluh, si j'ai bien compris votre prise de parole, à la fin, vous avez reproché aux partis, dont je fais partie, qui ont demandé ce débat urgent de vouloir uniquement occuper la scène pour les médias et pour la télévision. Que faut-il penser des nombreuses sessions extraordinaires demandées par l'UDC sur l'asile ? N'y a-t-il pas aussi une volonté de médiatisation ?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objet sur lequel nous débattons aujourd'hui a déjà une longue histoire derrière lui et un certain nombre d'allers-retours entre le Conseil national et le Conseil des États, d'une part, ainsi qu'entre les chambres et le Conseil fédéral, d'autre part.
+Cet objet fait suite à l'adoption de la motion Dobler Marcel 17.3067, "Si la Suisse paie la formation coûteuse de spécialistes, ils doivent aussi pouvoir travailler ici". Cette motion avait été adoptée par notre conseil le 20 septembre 2018, puis p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objet sur lequel nous débattons aujourd'hui a déjà une longue histoire derrière lui et un certain nombre d'allers-retours entre le Conseil national et le Conseil des États, d'une part, ainsi qu'entre les chambres et le Conseil fédéral, d'autre part.
+Cet objet fait suite à l'adoption de la motion Dobler Marcel 17.3067, "Si la Suisse paie la formation coûteuse de spécialistes, ils doivent aussi pouvoir travailler ici". Cette motion avait été adoptée par notre conseil le 20 septembre 2018, puis par le Conseil des États le 19 mars 2019. Le Conseil fédéral était alors venu avec une proposition de modification de la loi fédérale sur les étrangers et l'intégration (LEI) le 19 octobre 2022. Cette modification prévoyait que, lors de leur admission sur le marché du travail, les ressortissants d'États tiers qui ont obtenu un master ou un doctorat dans une université suisse ou une école polytechnique fédérale dans un domaine souffrant d'une pénurie avérée de personnel qualifié ne devaient pas être soumis au contingentement fixé pour les citoyens des pays tiers.
+Alors que notre conseil voulait aller encore plus loin que le Conseil fédéral, en élargissant l'admission facilitée à tous les titulaires d'un diplôme suisse de degré tertiaire, y compris les brevets et diplômes fédéraux, ainsi qu'aux postdoctorants, le Conseil des États, lui, a remis en question la constitutionnalité de la modification de loi telle que proposée par le Conseil fédéral, notamment en lien avec l'article 121a de la Constitution, qui prévoit des contingents pour les ressortissants de pays tiers. Le 19 décembre 2023, l'objet avait finalement été renvoyé au Conseil fédéral afin que ce dernier propose une modification qui respecte aussi bien la motion Dobler Marcel que la Constitution. 
+Pour ajouter un peu de complexité dans cette histoire, le Conseil fédéral avait entre-temps proposé de rejeter la motion Atici 22.4105, "Lutter contre la pénurie de personnel qualifié en tirant parti de tous les diplômés de la formation professionnelle supérieure". Le Conseil fédéral justifiait cette proposition de rejet par le fait que les objectifs de la motion Atici pourraient être repris dans le cadre de la nouvelle modification de la LEI que le Conseil fédéral devait donc proposer.
+Enfin, le Conseil fédéral a également profité de ce renvoi pour intégrer dans le nouveau projet de modification les mesures permettant d'atteindre plus facilement les objectifs en matière d'intégration sur le marché du travail des personnes bénéficiant de la protection provisoire, c'est-à-dire les personnes au bénéfice du statut S.
+L'objet sur lequel nous débattons aujourd'hui tient donc compte de la motion Dobler Marcel, de la motion Atici, des mesures pour les statuts S et de la conformité avec la Constitution.
+Venons-en donc aux modifications proposées. Elles sont de l'ordre de trois.
+Premièrement, à l'avenir, les titulaires d'un diplôme d'une école professionnelle supérieure suisse, ainsi que les personnes ayant travaillé en tant que postdoctorantes en Suisse, pourront être admises de façon simplifiée, à l'instar des titulaires d'un diplôme académique. En d'autres termes, ces personnes ne seront plus soumises à l'examen de l'ordre de priorité. La question des postdoctorants a été largement discutée en commission. En effet, un postdoctorat n'est pas une formation, et ne délivre donc, à ce titre, pas de diplôme. En outre, un postdoctorat peut en théorie durer une semaine comme plusieurs années. Ainsi, si les diplômés de hautes écoles ou de formations supérieures ont souvent séjourné plusieurs années en Suisse et sont donc souvent bien intégrés, on ne peut pas nécessairement en dire autant des postdoctorants. Une entreprise pourrait financer des contrats de postdoctorants de quelques mois à peine dans des chaires universitaires, dans le seul but de faire venir de la main-d'oeuvre en Suisse. D'ailleurs, des espions chinois ou des membres de la mafia pourraient également profiter de cette faille pour entrer en Suisse. Ce n'est pas de la science-fiction, puisque cela a déjà été le cas par le passé. La commission de notre conseil a donc souhaité préciser quelque peu la formulation à l'article 21 alinéa 3. Il conviendra de s'assurer, dans la pratique, qu'il n'y a pas d'abus à ce niveau-là et que les universités et EPF seront aidées, le cas échéant.
+Deuxièmement, s'agissant cette fois-ci des titulaires du statut S, la loi est modifiée en ce sens que les autorités cantonales devront annoncer au service public de l'emploi les personnes à protéger, les titulaires d'un statut S, donc, comme c'est déjà le cas pour les réfugiés reconnus et les personnes admises à titre provisoire.
+Troisièmement, une personne au bénéfice du statut S, qui exerce une activité lucrative ou suit une formation dans un canton autre que son canton de résidence, pourra désormais faire une demande de changement de canton, pour autant qu'elle ne bénéficie pas de l'aide sociale, que les rapports de travail existent depuis plus de douze mois, ou que le trajet entre le domicile et le lieu de travail n'est pas raisonnablement exigible.
+L'entrée en matière a été décidée par notre commission à l'unanimité. Je vous invite à en faire autant. Je reviendrai sur les propositions de minorité dans un deuxième temps, une fois que les personnes ayant déposé ces propositions les auront présentées.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es gehört: Die Verstetigung des Schweizer Beitrags ab 2030 ist ein notwendiges Element des Pakets Schweiz-EU. Es ist aber letztlich auch nichts Neues. Mit dem Schweizer Beitrag beteiligt sich unser Land seit 2007 an der Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU sowie an der Stärkung des Migrationsmanagements. Wir investieren damit in die Stabilität und den Zusammenhalt in Europa und vertiefen gleichzeitig die bilateralen Beziehungen mit den EU-Mitgliedern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sie haben es gehört: Die Verstetigung des Schweizer Beitrags ab 2030 ist ein notwendiges Element des Pakets Schweiz-EU. Es ist aber letztlich auch nichts Neues. Mit dem Schweizer Beitrag beteiligt sich unser Land seit 2007 an der Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU sowie an der Stärkung des Migrationsmanagements. Wir investieren damit in die Stabilität und den Zusammenhalt in Europa und vertiefen gleichzeitig die bilateralen Beziehungen mit den EU-Mitgliedern.
+Die Europäische Union fordert grundsätzlich von allen Staaten, die am Binnenmarkt der EU teilnehmen, einen Beitrag an die Kohäsion. Entsprechend leisten auch die EWR-Mitglieder Island, Liechtenstein und Norwegen seit 1994 einen regelmässigen Beitrag. Dieser beträgt derzeit rund 440 Millionen Franken pro Jahr, wobei Norwegen 97 Prozent davon zahlt; selbstverständlich, Island und Liechtenstein sind auch kleinere Staaten. Auch mit dem Vereinigten Königreich verhandelt die EU aktuell über einen Kohäsionsbeitrag.
+Als Teil des Pakets schafft das Beitragsabkommen einen klaren, vorhersehbaren Rahmen für einen regelmässigen Schweizer Beitrag an die Kohäsion und die Bewältigung wichtiger gemeinsamer Herausforderungen wie zum Beispiel im Bereich der Migration. Der Beitrag gliedert sich in Beitragsperioden von jeweils sieben Jahren, für den ersten Beitrag wäre das die Periode 2030-2036. Zu diesem ersten Beitrag enthält das Beitragsabkommen bereits spezifische Elemente, darunter die Höhe des Beitrags von 350 Millionen Franken pro Jahr für die Schweiz.
+Die Mittel fliessen wie bisher nicht ins EU-Budget in Brüssel. Sie werden direkt in den Partnerstaaten für gemeinsam vereinbarte Programme und Projekte eingesetzt, genau wie es seit zwanzig Jahren passiert. Die thematischen Schwerpunkte werden zusammen mit den Partnerstaaten festgelegt. Dabei wird die Schweiz ihre strategischen Interessen und ihre Expertise, wie beispielsweise in der dualen Berufsbildung, aktiv einbringen.
+Le projet de loi sur les contributions à la cohésion fait partie intégrante du projet. Cette loi est nécessaire en tant que nouvelle base juridique pour la mise en oeuvre de l'accord dans le domaine de la cohésion. 
+Vous vous rappelez : la loi fédérale sur la coopération avec les États d'Europe de l'Est, qui constituait la base juridique des contributions, n'est plus en vigueur depuis fin 2024. Cette nouvelle loi définit la manière dont la Suisse soutient les programmes et les projets dans le cadre de la contribution. Elle régit la coopération avec des tiers, la sélection des partenaires suisses, le financement des contributions ainsi que les compétences. Elle contient en outre des dispositions relatives à l'évaluation et à l'établissement de rapports. 
+Dans le cadre de la consultation, la nécessité d'une implication accrue des partenaires suisses dans la mise en oeuvre de la contribution a été soulignée. Il y a donc un peu plus de "Swissness" avec l'article 2 alinéa 4. Le Conseil fédéral a donné suite à ces demandes : la loi prévoit des procédures simplifiées en vue de la promotion ciblée de partenariats avec les acteurs suisses.
+Der Schweizer Beitrag ist ein notwendiges Element des Pakets Schweiz-EU, er stärkt die Präsenz und Sichtbarkeit der Schweiz in den Partnerstaaten. Eine verbesserte soziale und wirtschaftliche Entwicklung in diesen Ländern kommt auch der Schweiz zugute. Der Schweizer Beitrag ist keine Einbahnstrasse, er stärkt europäische Volkswirtschaften und schafft gleichzeitig Vorteile für die Schweiz durch mehr Handel, mehr Investitionen und engere wirtschaftliche Verflechtungen.
+Der Bundesrat empfiehlt Ihnen deshalb, dem Kohäsionsbeitragsgesetz zuzustimmen. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous vous penchez maintenant sur la thématique de la participation des cantons, du Parlement et du public dans le cadre du paquet suisse-UE et, en particulier, sur les éléments institutionnels prévus dans les accords relatifs au marché intérieur et, par analogie, dans l'accord sur la santé.
+De façon générale, la proposition du Conseil fédéral dans ce domaine vise à assurer la plus grande transparence et inclusivité possible, à définir des processus clairs et prévisibles ainsi qu'à créer de la co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous vous penchez maintenant sur la thématique de la participation des cantons, du Parlement et du public dans le cadre du paquet suisse-UE et, en particulier, sur les éléments institutionnels prévus dans les accords relatifs au marché intérieur et, par analogie, dans l'accord sur la santé.
+De façon générale, la proposition du Conseil fédéral dans ce domaine vise à assurer la plus grande transparence et inclusivité possible, à définir des processus clairs et prévisibles ainsi qu'à créer de la confiance. Au vu de ces objectifs, le Conseil fédéral propose des adaptations à la loi fédérale sur la participation des cantons à la politique extérieure de la Confédération, à la loi sur le Parlement et à la loi sur l'organisation du gouvernement et de l'administration. Je présenterai ces propositions dans l'ordre du dépliant.
+Les commissions en charge de l'examen préliminaire ont déjà discuté de ces éléments de façon intensive et fait des propositions supplémentaires que vous voyez sur le dépliant. Ces propositions vont globalement dans la même direction que celles prévues par le Conseil fédéral. Nous y reviendrons plus tard point par point, mais d'abord, je vais vous présenter celles du Conseil fédéral. J'ai déjà rappelé les points clés des éléments institutionnels lors du débat d'entrée en matière. Je n'y reviendrai donc pas ici.
+Der Bundesrat sieht vor, die Mitwirkung der Kantone im Bereich des Pakets Schweiz-EU in einer Vereinbarung zwischen dem Bund und den Kantonen zu regeln, analog zur bestehenden Vereinbarung zwischen Bund und Kantonen im Bereich der Schengen/Dublin-Assoziierung. Die Vereinbarung zwischen Bund und Kantonen zum Paket Schweiz-EU wurde von der Bundesverwaltung und der Konferenz der Kantonsregierungen ausgearbeitet. Der Bundesrat hat den Entwurf an seiner Sitzung vom 22. April 2026 genehmigt und veröffentlicht. Damit die Vereinbarung in Kraft treten kann, braucht es aber eine Kompetenzgrundlage im Bundesgesetz über die Mitwirkung der Kantone an der Aussenpolitik des Bundes. Entsprechend ist in Anhang 6 des Entwurfs 1 ein Vorschlag für einen neuen Artikel 5a dieses Bundesgesetzes enthalten. Materiell bleibt die Vereinbarung im Rahmen des geltenden Bundesgesetzes und des Artikels 55 der Bundesverfassung.
+Zu den Vorschlägen des Bundesrates betreffend die Mitwirkung des Parlamentes: Im Parlamentsgesetz sieht der Bundesrat die Schaffung zweier neuer Bestimmungen, nämlich Artikel 147a und Artikel 152a, sowie formelle Änderungen des bestehenden Artikels 148 vor. Mit dem neuen Artikel 147a sieht der Bundesrat vor, dem Parlament einmal pro Legislaturperiode im Rahmen seines Berichts über den Stand der Beziehungen zur EU ein Monitoring über die Funktionsweise der institutionellen Elemente des Pakets Schweiz-EU vorzulegen. Zudem sieht der Bundesrat vor, alle Informationen zu den aussenpolitischen Berichten in diesem neuen Artikel 147a zusammenzufassen, was zu Änderungen des bestehenden Artikels 148 führt.
+Der Bundesrat beabsichtigt zudem, die Rolle des Parlamentes bei allen institutionellen Mechanismen sicherzustellen und klare interne Prozesse zu definieren. Die Grundlage für diesen Ansatz des Bundesrates ist die Informationsplattform. Auf dieser Plattform werden alle öffentlichen Dokumente der EU zum Decision Shaping zugänglich gemacht werden. Auch das Parlament wird auf diese Dokumente Zugriff haben. Diese Veröffentlichungspflicht ist in einem neuen Artikel 40a des Regierungs- und Verwaltungsorganisationsgesetzes vorgesehen; ich werde darauf zurückkommen.
+Basierend auf dieser totalen Transparenz sieht der Bundesrat in Bezug auf die Mitwirkung des Parlamentes vor, einen neuen Artikel 152a ParlG zu schaffen. Dieser soll die Informations- und Konsultationsprozesse und -rechte des Parlamentes im Rahmen des Decision Shaping spezifisch regeln. In diesem Rahmen werden die für die Aussenpolitik zuständigen Kommissionen sowie neu auch die anderen kompetenten Fachkommissionen miteinbezogen. Zudem will der Bundesrat die Mitwirkung des Parlamentes an den weiteren Prozessen der institutionellen Elemente - dynamische Rechtsübernahme, Streitbeilegung und Ausgleichsmassnahmen - im Rahmen des bestehenden Artikels 152 ParlG sicherstellen. Die genauen Modalitäten der Mitwirkung des Parlamentes auf der Grundlage von Artikel 152 und 152a ParlG werden in einer Weisung des Bundesrates geregelt werden. Die Weisung soll parallel zur Beratung dieses Pakets unter Einbezug der Ratspräsidien, der zuständigen Kommissionen und der Parlamentsdienste erarbeitet werden. Diese Konsultation wurde bereits am 13. März dieses Jahres lanciert.
+Mit diesen Vorschlägen will der Bundesrat die geltende Kompetenzordnung und die bewährten Prozesse auch im Bereich der institutionellen Elemente beibehalten. Konkret: Die bestehenden, in der Praxis bewährten Kriterien, die eine Information des Parlamentes bei wichtigen Entwicklungen und eine Konsultation des Parlamentes zu wesentlichen Vorhaben und bedeutenden Verhandlungen vorsehen, sollen auf die verschiedenen Etappen der institutionellen Elemente angewendet werden. Im Bereich des Decision Shaping und der dynamischen Rechtsübernahme sieht der Bundesrat auch bei wichtigen Rechtsakten eine Information der zuständigen parlamentarischen Kommissionen sowie bei wesentlichen Rechtsakten eine Konsultation vor. Wichtig sind Rechtsakte, die in den Kompetenzbereich des Parlamentes fallen. Wesentlich sind Rechtsakte von einer zusätzlichen besonderen Wichtigkeit und/oder politischen Sensibilität.
+Pro memoria: Die Übernahme von EU-Rechtsakten in das jeweils betroffene Abkommen muss am Schluss vom Parlament genehmigt werden, sofern dieses die Kompetenz dafür nicht in einem Bundesgesetz an den Bundesrat delegiert. Das ist eine sehr wichtige Bemerkung, auch für die Souveränitätsdebatte.
+Der Bundesrat schlägt auch vor, dass das Parlament bei wichtigen und wesentlichen Etappen des Streitbeilegungsverfahrens inklusive Ausgleichsmassnahmen informiert bzw. konsultiert wird. Sie sehen also immer diese zwei Schienen, je nach Wichtigkeit der Information.
+Zusätzlich gestützt auf Artikel 152 Absatz 5 ParlG und den neuen Artikel 152a Absatz 4 ParlG kann das Parlament bereits heute und in Zukunft jederzeit eine Information oder eine Konsultation verlangen. Die Veröffentlichung aller öffentlichen Dokumente der EU betreffend das "decision shaping" wird es dem Parlament erlauben, den Überblick über die Rechtsentwicklungen im Binnenmarktbereich und beim Gesundheitsabkommen zu behalten und sich eigenständig einzubringen.
+Schliesslich zur Mitwirkung der Öffentlichkeit: Wie bereits erwähnt, will der Bundesrat im Zusammenhang mit dem "decision shaping" Transparenz und Inklusivität schaffen. In Artikel 40a RVOG schlägt er daher die Veröffentlichung aller für das "decision shaping" relevanten öffentlichen Dokumente der EU an einem zentralen Ort vor, eine sogenannte elektronische Informationsplattform. Die ständigen Teilnehmer an den Vernehmlassungsverfahren und die weiteren interessierten Kreise sollen zusätzlich über die Veröffentlichung benachrichtigt werden. Die Arbeiten, die die Gestaltung dieser Informationsplattform betreffen, sind bereits in Gang. Die Schaffung dieses neuen Artikels 40a RVOG würde eine Änderung des Titels des bestehenden Artikels 40 zur Folge haben.
+Zusammengefasst: Der Bundesrat misst der innerstaatlichen Umsetzung des Pakets Schweiz-EU und insbesondere der institutionellen Elemente eine grosse Bedeutung zu. Wie ich zu Beginn meiner Ausführungen erwähnt habe, haben seine Vorschläge im Bereich der Mitwirkung der Kantone, des Parlamentes und der Öffentlichkeit zum Ziel, grösstmögliche Transparenz und Inklusivität sicherzustellen, klare und vorhersehbare Prozesse zu definieren sowie Vertrauen zu schaffen. Gleichzeitig ist es wichtig, dass der geltenden Kompetenzordnung und den in der Praxis bewährten Prozessen grundsätzlich Rechnung getragen wird und dass in diesem Zusammenhang kein Bürokratiemonster geschaffen wird.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roth Franziska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachten ist. W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachten ist. Wir schaffen damit aussenpolitisch viel Goodwill und verstärken das Interesse am Schweizer Know-how vor Ort. Als Land, das sektoriell in hohem Masse in den Binnenmarkt integriert ist und von diesem mehr als mancher EU-Mitgliedstaat profitiert, hat die Schweiz bisher zweimal einen Kohäsionsbeitrag angenommen und ihm zugestimmt. Zuerst tat sie dies im Rahmen der Bilateralen II als Erweiterungsbeitrag zugunsten der zehn im Jahre 2004 beigetretenen EU-Mitgliedstaaten. Seit 2009 gab es dann einen zweiten Beitrag, dessen Rechtsgrundlage aber im Jahr 2024 ausgelaufen ist. Deshalb braucht es zur Verstetigung nun ein neues Abkommen, ein neues Umsetzungsgesetz und dann im zweiten Schritt auch neue Kredite. Ihre Kommission hatte sich also in dreifacher Hinsicht mit dem Kommissionsbeitrag zu befassen: mit dem Abkommen zur Verstetigung des Beitrags, mit dem dazugehörenden innerstaatlichen Umsetzungsgesetz und mit drei Verpflichtungskrediten für die dritte Beitragsperiode in den sieben Jahren von 2030 bis und mit 2036 und einer Überbrückung.
+Am wenigsten Diskussionen gab es in Ihrer Kommission über die Genehmigung des Abkommens mit der EU über den regelmässigen finanziellen Beitrag der Schweiz zur Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU. Dieses Abkommen gehört zum Stabilisierungsteil des Pakets. Es ist nicht möglich, separat darüber abzustimmen. Es kann nicht aus dem Paket gebrochen werden. Bekanntlich geht der Paketansatz auf einen Wunsch der Schweiz zurück, und die EU hat diesen Wunsch erfüllt. Entsprechend haben die Schweiz und die EU die Verhandlungen über das Paket je mit einer einzigen Unterschrift abgeschlossen. Das Paket bildet eine Einheit, und Sie stimmen dem Abkommen über die Verträge des Kohäsionsbeitrags also im Rahmen Ihrer Genehmigung des Gesamtpakets "Stabilisierung und Weiterentwicklung der Beziehungen Schweiz-EU (Bilaterale III)" zu. Ihre Kommission empfiehlt Ihnen, mit Ihrem Ja zum Bundesbeschluss über die Stabilisierung von fünf bestehenden Abkommen, zu zwei neuen Binnenmarktabkommen und zu einem neuen Kooperationsabkommen auch dem Abkommen über den Kohäsionsbeitrag zuzustimmen, das eben zum Stabilisierungsteil gehört. 
+Mehr zu reden gab in Ihrer Kommission das innerstaatliche Umsetzungsgesetz, das Bundesgesetz über die Beiträge der Schweiz zur Stärkung der Kohäsion in Europa. Das Kohäsionsbeitragsgesetz hält fest, wie die Schweiz die Programme und Projekte im Rahmen des Beitrags unterstützt. Es regelt die Zusammenarbeit mit Dritten, die Auswahl von Schweizer Partnern, die Finanzierung der Beiträge sowie die Zuständigkeiten. Zudem enthält es Bestimmungen zur Evaluation und Berichterstattung. Ihre Kommission trat an ihrer April-Sitzung auf das neue Kohäsionsbeitragsgesetz ein und befasste sich an zwei weiteren Sitzungen im Mai und August mit den Einzelheiten. Dazu unterbreitete Ihre Kommission der Verwaltung und dem Bundesrat zahlreiche Fragen. Sie betrafen die Konsultation des Parlamentes zu den Themenbereichen, die der Bundesrat dem gemischten Ausschuss vorlegen möchte, die laufende Berichterstattung über den Stand der Umsetzung des jeweils laufenden Beitrages, das Verhältnis des Kohäsionsbeitrags zum gesetzlichen Rahmen über das öffentliche Beschaffungswesen und die Finanzhilfe - der immer vorgeht -, den geplanten Überwachungsmechanismus der Schweiz, damit der Schweizer Beitrag auf allen Ebenen ordnungsgemäss umgesetzt wird, und, ganz wichtig, die Zusammenarbeit mit dem Schweizer Privatsektor und der Wissenschaft, die gezielt gefördert werden soll. Darunter fällt auch der Bereich der Berufsbildung, weil auch Schweizer Unternehmen ein genuines Interesse an Fachkräften vor Ort haben. Zudem wurden auch Fragen zu den in Artikel 11 verankerten periodischen Evaluations- und Wirksamkeitsberichten gestellt.
+Zusammenfassend lässt sich sagen, dass die Verwaltung all diese Fragen zur Befriedigung Ihrer Kommission beantwortet hat. Namentlich bekräftigte der Bundesrat, dass er bereits über das Parlamentsgesetz verpflichtet ist, Ihre Kommission zu den Prioritäten zu konsultieren, wie er den Kohäsionsbeitrag in seinem Memorandum of Understanding mit der EU umsetzen will. 
+Kritische Fragen löste der überraschende Antrag des Bundesrates aus, von der bewährten Zusammenarbeit des SECO und der DEZA bei der Umsetzung des Schweizer Kohäsionsbeitrages abzuweichen. Der Bundesrat hat die Zerschlagung dieser Zusammenarbeit am 24. Juni 2026 beschlossen, zeitlich gesehen also zwischen unseren beiden Kommissionssitzungen zur Beratung des Umsetzungsgesetzes. Wichtige Fragen konnten damit nicht wirklich vertieft werden. Im Vernehmlassungsverfahren war die gemeinsame Zuständigkeit von SECO und DEZA ja noch unbestritten gewesen. Entsprechend sah der Bundesrat in seiner Botschaft und im Gesetzesentwurf vom März 2026 in Artikel 10 vor, an der gemeinsamen Zuständigkeit von EDA, unserem Aussendepartement, und WBF, unserem Wirtschaftsdepartement, festzuhalten. Das ergibt auch Sinn, geht es doch beim Kohäsionsbeitrag sowohl um Aussenpolitik als auch um Wirtschaftspolitik.
+In der Kommission beantragte der Bundesrat aber, die explizite Erwähnung des EDA in Artikel 10 zu streichen und stattdessen in Artikel 9 und 11 die alleinige Zuständigkeit des SECO zur Umsetzung des Kohäsionsbeitrages vorzusehen. Zwar wurde uns gesagt, dass EDA solle auf einer politisch-strategischen Ebene weiterhin mitreden könne. Genau dies strich der Bundesrat aber aus seinem ursprünglichen Entwurf, was zu intensiven Diskussionen Anlass gab.
+Fragen warf auch das Verhältnis zur Botschaft über die internationale Zusammenarbeit ab 2029 auf, die ja noch gar nicht vorliegt. So ist die DEZA in mehreren Beitrittskandidaten der EU engagiert, was im Fall des Beitritts zu neuen Problemen führen könnte, wenn gesetzlich vorgeschrieben ist, nur noch das SECO dürfe zuständig sein. Dann gibt es die Migrationsprogramme, die teilweise auch über den Kohäsionsbeitrag finanziert werden, für die heute aber das SEM zuständig ist. 
+Ein Kommissionsmitglied schlug deshalb vor, im Gesetz einfach von den zuständigen Behörden zu sprechen und offen zu lassen, wer wann was macht. Denn üblicherweise ist es nicht Sache des Gesetzgebers, sondern des Bundesrates, in diesem Detaillierungsgrad Zuständigkeiten zu definieren. 
+Zu reden gab auch die fehlende Information an die Öffentlichkeit über die Abänderung der Zuständigkeiten. Botschaften und Finanztabellen enthalten nun Angaben, die gar nicht mehr zutreffen. Der Bundesrat sieht dennoch nicht vor, das nachzuholen. Zwar liegt Ihnen dazu kein Antrag vor, möglicherweise wird sich der Nationalrat aber noch mit diesen Fragen befassen. 
+Auf Wunsch der Verwaltung fügte Ihre Kommission ferner den neuen Absatz 4 bei Artikel 2 ein: Es seien bei der Umsetzung der Schweizer Beiträge die strategischen Interessen der Schweiz zu berücksichtigen. Der Bundesrat hat sich dieser Selbstverständlichkeit dann nicht widersetzt. Der im neuen Artikel 147a des Parlamentsgesetzes vorgesehene Legislaturbericht über den Stand der Beziehung zur EU wird zum Kohäsionsbeitrag ein explizites Kapitel über die Wirkung des Mitteleinsatzes und die Zielerreichung aufweisen, was dort dann noch ergänzt werden soll. 
+Im Ergebnis beantragt Ihnen die Kommission dann schlussendlich mit 10 zu 2 Stimmen bei 1 Enthaltung Zustimmung zum Kohäsionsbeitragsgesetz.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après les interventions de nos collègues Germann et Stark, on ne peut pas rester sans rien dire. J'ai présidé les travaux de notre commission. D'abord, j'aimerais indiquer qu'il ne s'agit pas du tout d'une position défensive. Il s'agit d'une position offensive pour renforcer les droits du Parlement à tous les stades du processus de négociation, du développement futur du droit européen. Cependant, il ne s'agit pas ici du droit européen dans son ensemble, mais uniquement du droit européen sur les </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après les interventions de nos collègues Germann et Stark, on ne peut pas rester sans rien dire. J'ai présidé les travaux de notre commission. D'abord, j'aimerais indiquer qu'il ne s'agit pas du tout d'une position défensive. Il s'agit d'une position offensive pour renforcer les droits du Parlement à tous les stades du processus de négociation, du développement futur du droit européen. Cependant, il ne s'agit pas ici du droit européen dans son ensemble, mais uniquement du droit européen sur les accords d'accès au marché. Il ne s'agit que de ces domaines.
+Je le rappelle - cela a été dit de manière très complète dans le rapport de notre collègue Würth - : ce sont trois domaines dans lesquels on renforce les droits. Premièrement, il s'agit du "decision shaping", domaine extrêmement important : on peut participer, aux côtés du Conseil fédéral, pour donner notre impulsion parlementaire. Deuxièmement, la reprise dynamique du droit : on peut participer à la définition de la mise en oeuvre de ce qui a été négocié. Troisièmement, élément extrêmement important aussi : la participation aux procédures de règlement des différends, domaine dans lequel nous pouvons, en tant que Parlement, influencer le Conseil fédéral avec nos impulsions. Nous voyons donc que c'est important.
+On vient nous dire aussi : mais on ne saura qu'au dernier moment ce qui va se passer. Non, la commission a décidé - et c'est extrêmement important - d'avoir un délégué à Bruxelles qui peut justement examiner quelles tendances se dessinent, que ce soit à la Commission ou au Parlement européens, sur des thèmes relatifs aux accords d'accès au marché qui concernent la Suisse. Est-ce quelque chose de nouveau ? Non, je rappelle que ce processus existe pour Schengen-Dublin, mais nous n'avons pas de participation parlementaire. Les commissions sont-elles dépassées ? Non, la Commission des institutions politiques suit toutes les évolutions soumises au Parlement et elle fait son travail - et ce, même si nous sommes des parlementaires de milice -, parfois en relevant des éléments critiques, parfois en appuyant la proposition soumise.
+Je ne crois pas qu'il faille peindre le diable sur la muraille. La proposition de la commission soumise aujourd'hui, et qui a été très bien expliquée, techniquement, par notre collègue Würth, ne fait que renforcer nos droits. On ne peut pas en même temps déplorer l'absence de participation dans le processus avec l'Union européenne et, lorsqu'il y a une volonté de renforcer les droits, les critiquer et dire que cela ne sert à rien. 
+Je vous invite à soutenir les propositions de la Commission de politique extérieure.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission de politique extérieure du Conseil des États (CPE-E) a examiné en profondeur la question du référendum applicable à la partie "stabilisation" des Bilatérales III. Elle a procédé également à des auditions, certes pas publiques, mais des auditions étendues et elle a également publié le résultat de ces auditions avec les documents qui lui ont été remis. La commission a aussi entendu le Conseil fédéral, demandé des éclaircissements juridiques et transmis son appréciation à la Commissio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission de politique extérieure du Conseil des États (CPE-E) a examiné en profondeur la question du référendum applicable à la partie "stabilisation" des Bilatérales III. Elle a procédé également à des auditions, certes pas publiques, mais des auditions étendues et elle a également publié le résultat de ces auditions avec les documents qui lui ont été remis. La commission a aussi entendu le Conseil fédéral, demandé des éclaircissements juridiques et transmis son appréciation à la Commission des institutions politiques (CIP) dans un corapport plus.
+La majorité de la CPE-E vous propose de suivre le Conseil fédéral : les accords doivent être soumis au référendum facultatif. C'est d'abord la solution prévue explicitement par notre Constitution. L'article 140 réserve le référendum obligatoire pour les traités internationaux d'adhésion à une organisation de sécurité collective ou à une communauté supranationale. Les Bilatérales III ne réalisent aucune de ces deux conditions. Elles contiennent en revanche d'importantes dispositions fixant des règles de droit. Leur approbation relève donc de manière évidente du référendum facultatif conformément à l'article 141 de la Constitution. Ce référendum peut d'ailleurs, il faut le rappeler, être demandé par huit cantons s'ils le désirent.
+Ceci dit, les gouvernements cantonaux ont également pu pleinement faire connaître leur position. Réunis en assemblée plénière extraordinaire le 24 octobre 2025, les gouvernements cantonaux ont soutenu le paquet des accords par 21 voix contre 4 et 1 abstention, cela a déjà été dit. Sur la question précise du référendum, 15 cantons se sont prononcés pour le référendum facultatif, 10 pour le référendum obligatoire et un canton s'est abstenu. Cette prise de position interdit donc de dire que les cantons n'ont pas pu s'exprimer.
+La deuxième question est celle de la mise en oeuvre d'un référendum obligatoire sui generis. La base juridique d'un tel référendum obligatoire est contestée. Les professeurs entendus par la commission, qui sont rejoints par l'écrasante majorité des professeurs de droit constitutionnel et de droit public en Suisse - il n'y a pas une controverse aussi large qu'on veut bien le dire à ce sujet - estiment que la Constitution en vigueur, de 1999, ne donne pas au Parlement la faculté de soumettre de son propre chef un traité au référendum obligatoire et qu'une pratique coutumière suffisante fait défaut.
+L'Office fédéral de la justice rappelle, dans une note qui nous a été remise, que les trois précédents invoqués pour justifier le référendum sui generis - la Société des Nations en 1920, l'accord de libre-échange avec la Communauté économique européenne en 1972 et l'Espace économique européen en 1992 - sont trop rares et trop différents pour constituer une règle générale d'un droit coutumier. L'Office fédéral de la justice a également examiné l'hypothèse où l'on admettrait malgré tout un tel référendum, par analogie avec la révision constitutionnelle. Son champ serait alors extrêmement étroit et il faudrait que le traité écarte manifestement un élément fondamental de notre Constitution : les droits politiques dans le domaine de l'accord, le coeur de la répartition des compétences ou la garantie institutionnelle essentielle. À elle seule, l'importance politique d'un accord ne suffit pas.
+Or, les Bilatérales III, malgré ce que dit la rapporteuse de la CIP, ne franchissent pas ce seuil. La reprise du droit pertinent de l'Union européenne dans notre ordre juridique n'est pas automatique. Les décisions suisses sont prises selon nos procédures constitutionnelles, le Parlement conserve ses compétences et les droits populaires demeurent applicables. Dans la mesure où aucun élément fondamental de notre Constitution n'est écarté, les conditions d'un éventuel référendum sui generis ne sont pas réunies.
+Le précédent relatif aux accords d'association à l'espace Schengen-Dublin confirme cette appréciation. En 2004, lors de l'examen des Bilatérales II, le conseiller national Christoph Mörgeli avait proposé de soumettre les accords d'association à Schengen et à Dublin au référendum obligatoire sui generis. De fait, faire usage du référendum obligatoire correspondait à sa volonté. Le Conseil national avait rejeté cette proposition, par 120 voix contre 57. Or, Schengen-Dublin prévoyait déjà une reprise dynamique du droit européen, avec un mécanisme bien plus rigide que celui des Bilatérales III : avec un refus du développement de Schengen-Dublin, l'association prenait fin, ou prend fin, à l'issue de la procédure prévue par l'accord. Pour les accords d'accès au marché des Bilatérales III, on l'a dit, un refus suisse peut entraîner des mesures de compensation proportionnées, mais non une fin automatique.
+Il n'y a donc aucun argument juridique, ni même politique, qui justifierait de rompre aujourd'hui avec la pratique retenue pour Schengen-Dublin. Ce précédent montre aussi que le choix du référendum a des conséquences réelles. Schengen-Dublin a été accepté par 54,6 pour cent des voix lors d'un référendum facultatif. Le professeur Adrian Vatter a exposé devant la CIP-E que, compte tenu de la répartition actuelle de la population entre les cantons, il faut environ 55 pour cent des voix populaires pour obtenir également la majorité des cantons. Cela illustre clairement le poids de la double majorité et finalement le veto posé par une minorité de la population.
+J'aimerais rappeler que le peuple s'est d'ailleurs déjà prononcé sur l'extension du référendum obligatoire applicable aux traités. L'initiative populaire de l'Asin en 2009, "Pour le renforcement des droits populaires dans la politique étrangère (accords internationaux : la parole au peuple !)", visait notamment à soumettre au référendum obligatoire les traités qui, selon le chiffre 2 proposé dans l'initiative, "obligent la Suisse à reprendre des futures dispositions fixant des règles de droit dans les domaines importants" ou - selon le chiffre 4 - "entraînent de nouvelles dépenses uniques de plus d'un milliard de francs, ou de nouvelles dépenses récurrentes de plus de 100 millions de francs." Le 17 juin 2012, cette initiative a été rejetée par 75,28 pour cent des votants et, il faut le souligner, par tous les cantons. Ce résultat n'interdit pas de proposer une révision de la Constitution. Cependant, il est contraire à tous les principes du droit et de la bonne foi de changer les règles uniquement pour un cas particulier et en plus en plein milieu de la partie.
+J'en viens enfin à la proposition de la minorité Rieder et à l'article 121a de la Constitution. Cette proposition repose sur l'idée que le protocole modifiant l'Accord sur la libre circulation des personnes serait incompatible avec l'interdiction de conclure des traités empêchant la Suisse de gérer l'immigration de manière autonome. Notre collègue propose de résoudre ce conflit supposé au moyen de deux arrêtés liés. Le premier inscrirait une dérogation à l'article 121a dans une disposition transitoire de la Constitution. Il serait obligatoirement soumis au peuple et aux cantons. Si cette modification était acceptée, l'arrêté approuvant les accords serait ensuite publié et pourrait faire l'objet d'un référendum facultatif. Voilà le fondement juridique et le mécanisme démocratique de sa proposition. Ce n'est pas un référendum sui generis, c'est un référendum specialis, une révision constitutionnelle suivie,le cas échéant, de la possibilité d'un second vote.
+La majorité de la CPE-E rejette les prémices du mécanisme. Elle estime que la modification négociée ne retire pas à la Suisse sa capacité de gérer l'immigration au sens de l'article 121a. Les chiffres présentés en commission sont éclairants : dans la pratique actuelle, comme l'a rappelé hier encore le Conseil fédéral, 100 à 160 partenaires enregistrés et 7 à 12 enfants sont déjà admis chaque année au titre du regroupement familial. Ces chiffres ne représentent donc pas une prévision d'arrivées supplémentaires dues aux Bilatérales III. Le regroupement facilité d'autres proches resterait soumis à un examen individuel. Les cas comparables observés aujourd'hui se comptent en quelques unités par an.
+Comme l'ont rappelé les experts lors des auditions à la CPE-E, la pratique concernant les accords économiques avec les États tiers invite également à ne pas interpréter l'article 121a comme une interdiction absolue de tout droit de séjour nouveau. Les accords avec la Chine, l'Inde et le Kosovo comportent des dispositions relatives à la présence de catégories déterminées de personnes, notamment dans le cadre des prestations de services. Cela génère donc l'arrivée de personnes supplémentaires. Aucun de ces accords n'a été soumis au référendum obligatoire et, surtout, aucun membre de ce Parlement n'en a fait la demande. Leurs dispositions et leur portée ne sont certes pas identiques à l'Accord sur la libre circulation des personnes, mais ces précédents montrent néanmoins que l'existence d'un droit de séjour limité ne suffit pas à elle seule à imposer une modification constitutionnelle et la double majorité.
+Lors de la séance du 21 mai dernier, la CPE-E a ainsi opté, par 8 voix contre 5, pour le référendum facultatif et rejeté la proposition défendue par la minorité Rieder. La voie d'un référendum obligatoire sui generis a également été écartée au cours des débats. Enfin, dans un vote consultatif, la CPE n'a pas donné suite à l'initiative de la CIP-E 26.425. Certes, la commission s'est prononcée de manière consultative, dès lors qu'elle n'avait pas la compétence matérielle pour se prononcer, mais cela donne toutefois le sentiment ressenti au sein de la CPE.
+Permettez-moi, Monsieur le président, avant de conclure, de répondre en italien à M. Chiesa, puisqu'il a fait des déclarations sur la question du référendum lors du débat d'entrée en matière.
+Caro collega Chiesa, lunedì, nel dibattito d'entrata in materia, Lei ha rimproverato a quelli che sostengono il referendum facoltativo di voler cambiare le regole per ottenere il risultato sperato. Ma qui è il bue che da del cornuto all'asino! Ricordo che le regole vigenti, ossia gli articoli 140 e 141 della Costituzione federale, prevedono il referendum facoltativo per questo tipo di accordo. Chi propone una nuova disposizione costituzionale o vuole imporre un referendum obbligatorio sui generis senza che siano soddisfatte le condizioni è proprio chi, come Lei, chiede di cambiare le regole di questa votazione.
+Per la Commissione di politica estera, bisogna rispettare la Costituzione nell'applicazione anche quando il risultato politico è incerto.
+En conclusion, la majorité de la CPE-E vous invite à appliquer les règles constitutionnelles en vigueur. Les accords relèvent du référendum facultatif. Ils ne remplissent pas les conditions exceptionnelles d'un référendum obligatoire et sui generis. Il n'y a pas de conflit avec l'article 121a de la Constitution fédérale nécessitant une dérogation constitutionnelle.
+Je vous invite, au nom de la majorité de la CPE-E, à suivre le Conseil fédéral, à opter pour le référendum facultatif et à écarter toutes les autres options.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die vorliegende parlamentarische Initiative 26.425 ist Ihnen bereits aus der ersten Phase gut bekannt. Unser Rat beauftragte unsere Kommission am 11. Juni mit der Ausarbeitung einer Vorlage. Diese verabschiedete unsere Kommission Ende Juni mit 7 zu 6 Stimmen. Eine Vernehmlassung war nicht nötig. Der Bundesrat beantragt Nichteintreten, eine Minderheit ebenso. Die Kommissionspräsidentin, Kollegin Z'graggen, hat dazu das Wichtige gesagt.
+Ziel der parlamentarischen Initiative ist die korrekte verfas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die vorliegende parlamentarische Initiative 26.425 ist Ihnen bereits aus der ersten Phase gut bekannt. Unser Rat beauftragte unsere Kommission am 11. Juni mit der Ausarbeitung einer Vorlage. Diese verabschiedete unsere Kommission Ende Juni mit 7 zu 6 Stimmen. Eine Vernehmlassung war nicht nötig. Der Bundesrat beantragt Nichteintreten, eine Minderheit ebenso. Die Kommissionspräsidentin, Kollegin Z'graggen, hat dazu das Wichtige gesagt.
+Ziel der parlamentarischen Initiative ist die korrekte verfassungsrechtliche Verankerung der Bilateralen III. Im Kern steht die Forderung, dass diese Verträge in einer Verfassungsbestimmung genehmigt werden sollen. Dies hat drei Vorzüge: Erstens kann man der Bedeutung der Verträge damit auf verfassungskonforme Art und Weise gerecht werden. Zweitens löst man den Konflikt mit der bestehenden Verfassung, konkret mit Artikel 121a BV. Drittens kann man, wenn man möchte, später en passant auch die Frage der Schubert-Praxis auf Verfassungsstufe klären.
+Zum ersten Punkt, dass man der Bedeutung der Verträge damit auf verfassungskonforme Weise gerecht werden kann: Wer der Meinung ist - wir haben solche Meinungen heute schon gehört -, dass die Verträge quasi eine verfassungsmässige Bedeutung haben, wie z. B. auch Professor Glaser es in unserer öffentlichen Anhörung ausführte, kann dieser Bedeutung so gerecht werden. Argumente dafür sind der starke Einfluss des Pakets auf unsere Rechtsetzung bis hinunter zu den Volksrechten, aber auch die Streitbeilegung. Man müsste, um der Bedeutung der Verträge gerecht zu werden, also nicht die wie erwähnt doch umstrittene Figur des obligatorischen Staatsvertragsreferendums sui generis herbeiziehen, sondern man könnte das entsprechende Verfahren korrekt in der Verfassung abbilden.
+Denn ein solches Referendum sui generis, Sie sehen das bei jeder Durchsicht der Verfassung, steht dort nirgends. Es wurde in der Geschichte dreimal angewandt, zum ersten Mal in grauer Vorzeit, beim Beitritt der Schweiz zum Völkerbund. Damals gab es noch überhaupt kein Staatsvertragsreferendum; man betrachtete die Frage des Beitritts quasi als Verfassungsfrage. Das zweite Mal wurde es 50 Jahre später angewandt, nämlich 1972 beim Freihandelsabkommen mit der Europäischen Gemeinschaft. Damals war der Hauptgrund, dass der Bundesrat früh versprochen hatte, es gebe dann sicher eine Abstimmung; am Schluss musste er dieses Versprechen irgendwie einlösen. Das war 1972, bevor man das obligatorische Staatsvertragsreferendum überhaupt kodifizierte - dies geschah erst 1977.
+Sie sehen also: Die ersten beiden Anwendungsfälle des obligatorischen Staatsvertragsreferendums sui generis stammen alle aus der Zeit vor dem Festschreiben des obligatorischen Staatsvertragsreferendums in der Verfassung.
+Der dritte Anwendungsfall, das wurde auch erwähnt, war die Frage des Beitritts der Schweiz zum EWR. Dort herrschte wiederum eine spezielle Ausgangslage. Es gab nämlich gleichzeitig auch einen Beschluss zur Änderung der Bundesverfassung. In diesem Zusammenhang betrachtete man es als naheliegend, dass man die Frage des Beitritts zum EWR nur schon aus diesem Grunde damit auf eine Stufe setzte. Das geschah ebenfalls noch unter der alten Bundesverfassung.
+Zur Frage, ob die Referendumsbestimmung in der Verfassung abschliessend sei oder ob es noch irgendein Notventil gebe, gingen die Voten in den Räten jeweils etwas auseinander. Der Bundesrat sagt, es gebe noch ein Notventil, aber nur in ganz aussergewöhnlichen Situationen. Manche sagen, das Parlament sei hier freier. Einen zusätzlichen Vorteil jedenfalls hat die in der Vorlage zur Umsetzung der parlamentarischen Initiative vorgesehene Verfassungsnorm, nämlich eine besonders starke Legitimität dieses Pakets, wenn es denn angenommen wird, bei zugegebenermassen höherer Hürde. Das ist ja genau der Kern eines doppelten Ja, das unsere Verfassung verlangt.
+Nun stellt sich die Frage, ob es denn zulässig ist, diesen Weg der Verfassungsrevision zu wählen, wenn bereits das obligatorische Staatsvertragsreferendum sui generis umstritten ist. Ich sage Ihnen, auch namens unserer Kommission: Dies ist klar der Fall. Das kommt auch in der Stellungnahme des Bundesrates zum Entwurf der Kommission zum Ausdruck. Denn unsere Verfassung kennt fast keine Revisionsschranken. Die wenigen bestehenden Revisionsschranken sind Ihnen bekannt: zwingendes Völkerrecht, Einheit der Materie und der Form sowie die sachliche Durchführbarkeit; es gibt keine weiteren. Es gibt also keine Schranke, die sagt, man dürfe einzelne Verträge nicht zum Gegenstand einer Verfassungsrevision machen.
+Im weiteren Sinne gibt es hierfür auch schon Präjudizien, allerdings nicht genau in dieser Konstellation. Aber zur Erinnerung: Der Beitritt der Schweiz zur UNO beispielsweise kam über eine Verfassungsänderung zustande. Man muss sagen, dass er auf eine Volksinitiative zurückging, daher hätte es sowieso eines obligatorischen Referendums bedurft. Er stand jedoch am Schluss als Übergangsbestimmung in der Verfassung. Auch bei der Frage des EWR-Beitritts gab es, wie vorhin erwähnt, eine Verfassungsnorm, die parallel zum Genehmigungsbeschluss daherkam. Man darf so etwas also tun.
+Dann kann man sich fragen, ob man generell freiwillig einen Regelungsgegenstand auf eine höhere Normstufe als die verlangte heben darf. Kommt man zum Schluss, dass an sich ein fakultatives Referendum reicht, kann man sich also die Frage stellen, ob man den Regelungsgegenstand einfach auf eine höhere Normstufe heben darf. Dazu kann man sagen: Das tun wir in diesem Hause regelmässig. Es gibt ganz viele Gesetzesbestimmungen, die materiell eigentlich Verordnungscharakter hätten.
+Um nur eine solche Bestimmung zu erwähnen: Letzte Woche schrieben wir eine Bankenverordnung ins Gesetz. Auch etwas, was nachweislich immer Verordnungsthema war, nämlich die Unterlegung einer Bank mit Eigenkapital, schrieben wir ins Gesetz. Viele unterstützten das, mit dem Gedanken, dass die entsprechende Bestimmung damit besser legitimiert ist; allenfalls könnte man dagegen sogar das Referendum ergreifen. Die Gesetzesform für einen solchen Verordnungsinhalt fanden viele deshalb attraktiv. Auch Beschaffungen von Kampfflugzeugen regeln wir regelmässig in Form von referendumsfähigen Bundesbeschlüssen, obwohl rechtlich sonnenklar ist, dass wir auf Bundesebene kein Finanzreferendum haben und man solche Beschaffungen auch einfach im Rahmen des Budgets beschliessen könnte.
+Diese Beispiele sollte bedenken, wer sagt, es sei jetzt quasi ein unzulässiges Plebiszit, dass man hier die Verfassung bemühe. Man darf. Das ist der erste Punkt. Man kann der Bedeutung gerecht werden, und man darf es tun, und man hat Ähnliches auch schon öfters getan. 
+Der zweite von drei Vorteilen dieser Verfassungsnorm ist der folgende. Er beantwortet die Frage: Muss man denn nicht sogar eine Verfassungsnorm entwerfen? Auch hier würde ich zustimmend antworten. Wir klären damit nämlich die Frage, ob wir nicht mit der bestehenden Verfassung ein Problem haben, mit Artikel 121a Absatz 4. Unsere Vorlage löst dieses Problem. Sie muss es gar nicht explizit tun. Sie schafft eine neuere, eine jüngere, eine speziellere Verfassungsnorm, und diese würde der bestehenden in diesem Punkt, in dieser Konstellation entsprechend vorgehen. Es gibt sehr starke Gründe, die Ihre Kommission zur Annahme bewogen haben, dass hier ein Konflikt vorliegt. Aus der Anhörung sei Herr Professor Stefan G. Schmid erwähnt. Er hat das herausgeschält und gezeigt - nicht als Einziger, aber bei uns in der Anhörung -, dass Artikel 121a Absatz 4 es verbietet, Verträge abzuschliessen, die der Bestimmung selber widersprechen. Und diese Bestimmung selber verlangt in ihrem Absatz 2 Kontingente und Höchstzahlen. Und im vorliegenden Paket werden eben nachweislich neue Freizügigkeitsrechte eingeräumt, und genau das wollte Artikel 121a Absatz 4 nicht.
+Wenn Sie sich erinnern wollen: Ich war damals wie viele von Ihnen gegen diese Initiative, die sogenannte Masseneinwanderungs-Initiative. Aber sie steht in der Verfassung, und eines ihrer Ziele war, keine Ausdehnung der Personenfreizügigkeit als Mechanismus zulassen. Wir haben nun in diesem Paket eine solche Ausdehnung, und ich räume gleich vorweg schon ein, dass sie, wie sie daherkommt, quantitativ überschaubar ist. Aber qualitativ geht es um verschiedene Kategorien. Es geht um gleichgeschlechtliche Partner, die man nachziehen kann. Es geht um deren Familiennachzug. Es geht generell um den Familiennachzug ohne ausreichende Wohnung - heute wird diese noch verlangt - und auch um den erleichterten Familiennachzug im Allgemeinen. Wenn man sagt, das seien zahlenmässig sehr wenige Leute, dann muss ich darauf hinweisen, dass die Bestimmung von Artikel 121a Absatz 4 der Bundesverfassung nicht von Mengen spricht, sondern von einem Mechanismus, dass man eben keine Freizügigkeitsrechte als Ansprüche geben möchte, egal, wie viele oder wie wenige Personen es dann sind. Wenn man dann sagt, dass es trotzdem sehr wenige sind, dann möchte ich noch auf die Dynamik verweisen. Denn mit diesen neuen Abkommen unterschreiben wir nicht irgendein Memorandum of Understanding (MOU), wo wir dann sagen, dass wir mal schauen, was künftig vielleicht noch passiert. Nein, wir versprechen im Grundsatz, dass wir künftige Änderungen nachführen. Ich sage nicht, die liegen schon auf dem Tisch - und wenn sie das täten, wären sie ja gar nicht mehr künftig. Aber irgendwann können sie kommen, und wir haben im Grundsatz zugesagt, sie dann zu übernehmen. Natürlich können wir nach unseren Mechanismen das dann nicht übernehmen, und dann sind wir im Vertragsverletzungsverfahren. Das können Sie bei allen Verträgen. Sie können Verträge immer verletzen. Neu ist, dass quasi der Gerichtsmechanismus auch schon definiert ist. Es ändert nichts daran, dass Sie im Grundsatz beschliessen, auch künftige Anpassungen in diesem Bereich zu übernehmen. Und wenn Sie das nicht tun, hat es Konsequenzen, und das hat eine neue Qualität. Also wenn Sie auch das berücksichtigen, kommen Sie zum Schluss, dass es hier mit der bestehenden Verfassung eng wird. Und von den Daueraufenthaltsrechten habe ich noch gar nicht gesprochen.
+Der Bundesrat findet nun erstens, es seien eben nur untergeordnete Ausweitungen, und das sei zulässig. Er findet dazu auch einige Lehrmeinungen, die ihm das bestätigen. Ich muss sagen, diese Lehrmeinungen finde ich äusserst generös. Sie wischen diese Pflicht aus Artikel 121a Absatz 2, dass alle Bewilligungen durch Kontingente und Höchstzahlen begrenzt werden, die ich Ihnen beschrieben habe, mit einem Verweis auf Absatz 1 weg. Dort steht, dass der Bund die Zuwanderung von Ausländerinnen und Ausländern eigenständig steuern soll. Und Sie sagen, wenn nur wenige Leute kommen, ist das in der Sache immer noch eigenständig; es geht ja nur um wenige. Aber man kann nicht das konkrete Instrument mit Verweis auf das allgemeine im Absatz 1 weginterpretieren. Es gibt auch viel strengere Lehrmeinungen. Ich verweise auf die St. Galler Kommentare oder den Verfassungskommentar von Professor Giovanni Biaggini. 
+Der Bundesrat sagt nicht nur, man könne das generöser interpretieren, sondern zweitens auch, dass wir auch sonst schon eine grosszügige Praxis mit den Freihandelsabkommen hätten. Da habe es auch Freizügigkeitsrechte drin, und das hätten wir auch schon akzeptiert. Aber wenn man diese Beispiele anschaut, sieht man, dass diese entweder fast alle älter als diese Verfassungsbestimmung sind - dann sind sie hier irrelevant - oder keine neuen Freizügigkeitsrechte vorsehen. Beispiele, die man genauer anschauen muss, sind Kroatien, das UK und China. Das sind allesamt Sonderfälle. Bei Kroatien hat der Bundesrat ausgeweitet, und das Parlament hat ihm gesagt, dass er immer verfassungskonform bleiben muss. Beim UK ging es nur um bestehende Rechte für Leute, die schon im Lande waren, also nicht um neue Rechte für künftige Einwanderer. Es ging also nur um den Status quo, nicht um künftige Migration. Bei China hatte der Erstrat schon zugestimmt, bevor die Initiative angenommen wurde. Da war man quasi nicht genügend schnell auf der Bremse. Seither respektieren sämtliche Freihandelsabkommen ohne Weiteres diese Bestimmung, mit einer Ausnahme. Beim Freihandelsabkommen mit der Türkei von 2018, scheint mir, hat man den Vorbehalt bezüglich der Kontingente vergessen. Das würde man künftig bestimmt nicht mehr tun. Denn die Wirtschaft wirft eine wichtige Frage auf: Haben wir dann nicht ein Problem mit künftigen Freihandelsabkommen?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi ringrazio per l'approfondita discussione istituzionale. Vi ringrazio per i chiarimenti e per le prospettive che avete messo in risalto. Vi posso assicurare che anche il Consiglio federale ha largamente e approfonditamente discusso questa questione.
+Il Consiglio federale è giunto alla conclusione di attenersi strettamente alla Costituzione e alla prassi seguita dalla Confederazione con i Bilaterali I e II. Perché? Perché così facendo ha concesso ai Cantoni e al Parlamento un'ampia libertà nel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vi ringrazio per l'approfondita discussione istituzionale. Vi ringrazio per i chiarimenti e per le prospettive che avete messo in risalto. Vi posso assicurare che anche il Consiglio federale ha largamente e approfonditamente discusso questa questione.
+Il Consiglio federale è giunto alla conclusione di attenersi strettamente alla Costituzione e alla prassi seguita dalla Confederazione con i Bilaterali I e II. Perché? Perché così facendo ha concesso ai Cantoni e al Parlamento un'ampia libertà nel processo decisionale di cui oggi abbiamo avuto spettacolo. Signore e signori consiglieri agli Stati, oggi ne avete davvero fatto uso e me ne rallegro molto. Il giusto equilibrio tra democrazia e federalismo, lo abbiamo capito, è davvero un'arte.
+Auch der Bundesrat hat die Frage des Referendums vertieft analysiert und in mehreren Sitzungen diskutiert. Die Kommissionspräsidentin hat erwähnt, wie es in der Kommission war, und auch ich habe das miterlebt, es ist überall dasselbe. Man spürt, diese Frage geht unter die Haut, sie trifft die Essenz unseres Wesens.
+Der Bundesrat hat sich am 30. April 2025 für ein fakultatives Staatsvertragsreferendum ausgesprochen und seinen Standpunkt in seiner Stellungnahme vom 12. August dieses Jahres zur parlamentarischen Initiative der SPK-S nochmals bekräftigt. Der Bundesrat hat seine Begründung für ein fakultatives Referendum auch transparent und ausführlich in der Botschaft vom 13. März 2026 dargelegt.
+In aller Kürze: Erstens hat sich der Bundesrat an die Bundesverfassung gehalten. Diese sieht für die Abkommen des Stabilisierungsteils des Paketes Schweiz-EU ein fakultatives Referendum vor. Zweitens entspricht das fakultative Referendum der bisherigen Praxis bei den Bilateralen I und II. Es stellt damit Kohärenz und Kontinuität sicher und schafft die notwendige Rechtssicherheit. Drittens erfüllen die Abkommen nach Meinung des Bundesrates auch die Voraussetzungen für ein sogenanntes obligatorisches Referendum sui generis nicht. Ein solches kann nach Ansicht des Bundesrates in Ausnahmefällen zur Anwendung kommen, wie auch Sie korrekterweise immer wieder zitiert haben. Es müssen dafür zwei Bedingungen erfüllt sein:
+1 Ein Staatsvertrag bringt einen schwerwiegenden Eingriff in die innere Struktur der Schweiz mit sich, das heisst, die verfassungsmässige Ordnung wird tangiert.
+2. Ein Staatsvertrag bewirkt eine grundlegende Neuorientierung der Aussenpolitik.
+Um eine grundlegende Neuorientierung der Aussenpolitik handelt es sich nicht, das hat heute auch niemand behauptet; dieser zweite Punkt ist also klar. Über den ersten Punkt haben wir etwa vier oder fünf Stunden lang diskutiert, die Quintessenz der Diskussion ist: Das Paket Schweiz-EU stellt für den Bundesrat keinen schwerwiegenden Eingriff in die innere Struktur der Schweiz dar. Jede dynamische Übernahme eines EU-Rechtsaktes erfordert die Zustimmung der Schweiz, sie untersteht also dem normalen innerstaatlichen Genehmigungsverfahren. Grundsätzlich heisst das, es braucht eine Genehmigung durch das Parlament, und allenfalls gibt es ein Referendum, wenn Sie, das Parlament, keine Kompetenzdelegation an den Bundesrat vorgenommen haben. Die Streitbeilegung erfolgt über ein paritätisches Schiedsgericht, wie es im Völkerrecht und bei 34 von 37 Freihandelsabkommen der Schweiz üblich ist. Das Schiedsgericht zieht den europäischen Gerichtshof nur zur Auslegung von EU-Recht bei, falls es relevant und notwendig ist. Der Streit selbst wird stets vom Schiedsgericht beurteilt. Die verfassungsmässigen Rechte und Zuständigkeiten der Kantone, des Parlamentes, des Bundesgerichtes und des Bundesrates bleiben gewahrt.
+Vergessen Sie nicht, dass wir die dynamische Rechtsübernahme bereits seit 20 Jahren, seit 2004 mit Schengen/Dublin üben. Die Konsequenzen einer Nichtübernahme eines EU-Rechtsaktes bei der dynamischen Rechtsübernahme bei den Schengen/Dublin-Assoziierungsabkommen gehen sogar wesentlich weiter als heute bei den Bilateralen III. Wird ein relevanter EU-Rechtsakt nämlich nicht übernommen, werden die Assoziierungsabkommen nach Ablauf einer bestimmten Frist automatisch beendet. Der Bundesrat und das Parlament haben sich auch bei dem Schengen/Dublin-Assoziierungsabkommen für das fakultative Referendum entschieden. Das war für den Bundesrat bindend.
+Das Paket Schweiz-EU bewirkt auch keine grundlegende Neuorientierung der Schweizer Aussenpolitik; das habe ich Ihnen bereits gesagt. 
+Und viertens ermöglicht das fakultative Referendum die formelle Verknüpfung der Abkommen mit deren innenstaatlicher Umsetzung ohne Ausschluss des Referendums für die inländische Umsetzung und ohne Durchführung von zwei separaten Volksabstimmungen. Das war für den Bundesrat auch sehr wichtig. Das wurde heute in der Diskussion kaum erwähnt, aber diese vertikale Bündelung mit einer einzigen Abstimmung war demokratiepolitisch eine wichtige Begründung für den Entscheid des Bundesrates. 
+In der Vernehmlassung, das wurde gesagt, begrüsste ausserdem eine Mehrheit der ständigen Vernehmlassungsteilnehmenden den Vorschlag des Bundesrates, das Paket dem fakultativen Referendum zu unterstellen: 15 der 26 Kantone sowie 5 der 7 politischen Parteien, die im Parlament vertreten sind. 
+Der Bundesrat hat auch das von der SPK-S vorgeschlagene Vorgehen einer Übergangsbestimmung in der Bundesverfassung bereits eingehend in der Botschaft vom März 2026 geprüft. Wir haben es diskutiert, geprüft und verworfen; Sie können dies eben in der Botschaft nachlesen. Der Bundesrat ist zum Schluss gekommen, dass diese Option staatspolitische Risiken mit sich bringt. Diese wurden heute genannt. Es würde vom verfassungsmässigen Verfahren für die Genehmigung völkerrechtlicher Verträge abgewichen. Es gibt für dieses Vorgehen ausserdem keinen vergleichbaren Präzedenzfall, und es besteht das Risiko, dass ein Präzedenzfall für zukünftige völkerrechtliche Verträge geschaffen wird, beispielsweise - es wurde gesagt - für Freihandelsabkommen. 
+Im Verhandlungsmandat ist zudem festgehalten, dass die verfassungsrechtliche Ordnung eingehalten werden muss, und dies ist mit dem vorliegenden Paket Schweiz-EU in den Augen des Bundesrates erfüllt. Die Abkommen des Stabilisierungsteils des Paketes Schweiz-EU, insbesondere die Anpassung am Freizügigkeitsabkommen, sind nach der Haltung des Bundesrats verfassungskonform; hier komme ich zum Artikel 121a BV. Dieser Artikel bezieht sich nur auf Ausländerinnen und Ausländer, die neu zuwandern. Wir haben auch im medialen Diskurs verschiedene Zahlen gehört. Es geht also um Neuzuwanderer. Der Familiennachzug wird zudem nur leicht erweitert. Ja, er wird erweitert, aber nur leicht. Neue Ansprüche gibt es einzig beim Recht auf Familiennachzug von Familienangehörigen von eingetragenen Partnerinnen und Partnern. Das haben Sie gestern mit dem Kollegen Bundesrat Jans diskutieren können. 
+Zwischen 2012 und 2021 wurden jährlich zwischen 100 und 160 Aufenthaltsbewilligungen an nachgezogene Personen in eingetragener Partnerschaft erteilt. Diese eingetragenen Paare konnten jährlich etwa 7 bis 12 Kinder nachziehen. Das haben Sie heute gehört. Das sind die Zahlen, die das SEM zur Verfügung gestellt hat. Wir sprechen hier also von einer doch relativ kleinen Anzahl zusätzlicher Personen, die neu zuwandern. Dies widerspricht dem Steuerungsziel von Artikel 121a BV nicht. Dem Steuerungsziel wird nicht widersprochen. Gemäss bestehender Praxis ist es unter Artikel 121a BV zulässig, völkerrechtliche Abkommen abzuschliessen, solange diese Verträge die Möglichkeit der Schweiz, die Zuwanderung durch Höchstzahlen und Kontingente zu steuern, weitgehend unberührt lassen. Der Bundesrat ist der Meinung, dass dies auch bei den Bilateralen III der Fall ist.
+Dies war beispielsweise bei den Freihandelsabkommen mit der Türkei und China der Fall, wie gesagt wurde. Sie haben diese Abkommen genehmigt und diese Praxis insofern auch bestätigt. 
+Auch die Verpflichtung zur dynamischen Rechtsübernahme führt nicht zu einer Preisgabe der eigenständigen Steuerung der Zuwanderung gemäss Artikel 121a BV, denn die Schweiz muss auch in Zukunft der Übernahme von neuen EU-Rechtsakten ins Freizügigkeitsabkommen jeweils explizit zustimmen. Das ist ja die Quintessenz der dynamischen Rechtsübernahme. Aus Sicht des Bundesrates behalten die genannten Überlegungen weiterhin ihre Gültigkeit.
+Pour conclure, permettez-moi de résumer. Le référendum facultatif correspond à ce qui est prévu par la Constitution en vigueur et s'inscrit dans la continuité de la pratique suivie pour les Bilatérales I et II. Il permet, en outre, de lier formellement les accords et leur mise en oeuvre en droit interne, sans exclure le référendum sur le droit de l'application interne et sans devoir organiser deux votations populaires distinctes. Du point de vue de la politique démocratique, il s'agit de la solution la plus claire et la plus cohérente. Par ailleurs, le référendum facultatif ne crée aucun précédent pour les futurs traités internationaux, par exemple, pour les accords de libre-échange.
+C'est pour toutes ces raisons que le Conseil fédéral vous propose de soumettre le paquet Suisse-Union européenne au référendum facultatif.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie Sie gehört haben, beantrage ich Ihnen mit der Minderheit der SPK und der Mehrheit der APK gemäss Bundesrat das fakultative Referendum, das heisst, die Bilateralen III sollen dem Volksmehr unterstellt werden. Dies aus den folgenden Gründen. 
+Die Verfassung ist klar, die Verfassung sagt genau, wann es das doppelte Mehr braucht: beim Beitritt zu einer supranationalen Gemeinschaft und zu einer Organisation der kollektiven Sicherheit. Bekanntlich ist beides bei den Bilateralen III nicht der Fall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie Sie gehört haben, beantrage ich Ihnen mit der Minderheit der SPK und der Mehrheit der APK gemäss Bundesrat das fakultative Referendum, das heisst, die Bilateralen III sollen dem Volksmehr unterstellt werden. Dies aus den folgenden Gründen. 
+Die Verfassung ist klar, die Verfassung sagt genau, wann es das doppelte Mehr braucht: beim Beitritt zu einer supranationalen Gemeinschaft und zu einer Organisation der kollektiven Sicherheit. Bekanntlich ist beides bei den Bilateralen III nicht der Fall. Das obligatorische Referendum für die Bilateralen III hat deshalb keine Grundlage in der Verfassung. Wer trotzdem ein obligatorisches Referendum bei den Bilateralen III verlangt, schafft für einen politischen Fall neue Spielregeln mit weitreichenden Konsequenzen. Das Ständemehr bei den Bilateralen III wäre ein Bruch mit unserer bisherigen Praxis. Für die Bilateralen I und II, das haben Sie heute bereits mehrfach gehört, galt das Volksmehr. 
+Auch bei Schengen und Dublin kennen wir eine dynamische Rechtsübernahme. Sie geht sogar weiter als bei den Bilateralen III. Übernehmen wir eine weitere Entwicklung in Schengen nicht, kann dies das Ende des ganzen Abkommens bedeuten. Bei den Bilateralen III ist das anders. Es gibt ein geregeltes Verfahren zur Streitbeilegung, und allfällige Ausgleichsmassnahmen müssen entsprechend auch verhältnismässig sein. Damit setzen die Bilateralen III den möglichen Konsequenzen einen klaren Rahmen. 
+Eine dynamische Rechtsübernahme ist also nicht Neues. Auch bei Schengen und Dublin galt wie bei den Bilateralen I und II das einfache Volksmehr. Damit sind auch die Voraussetzungen für ein Referendum sui generis nicht gegeben. Auch ein theoretisches Referendum sui generis müsste - wenn man davon ausgeht, dass es existiert - gewisse Voraussetzungen erfüllen. Es ist auch das Referendum sui generis nicht rein plebiszitär. Es müsste entweder eine grundlegende Neuausrichtung der Aussenpolitik vorliegen. Das ist nicht der Fall. Wir beraten hier die Fortsetzung der Bilateralen I und II, wir bleiben also auf dem bilateralen Weg. Oder es müsste ein schwerwiegender Eingriff in die innere Struktur unseres Landes sein. Auch wenn die Bilateralen III gewisse institutionelle Elemente wie die dynamische Rechtsübernahme haben, ist dies, wie gesagt, nicht neu. Das kennen wir bereits von Schengen/Dublin, und es ist, wie gesagt, auch eng begrenzt. Sogar aus demokratischer Sicht ist es eine Verbesserung gegenüber heute, weil die Konsequenzen klar eingeschränkt sind. Und Sie haben es anlässlich der Beratung der parlamentarischen Einflussnahme gehört: Die innerstaatliche Kompetenzordnung ist gewahrt. Hier gibt es also keine Veränderung. 
+Ich möchte noch auf das Votum der Mehrheitssprecherin der SPK und also der Vertreterin des Referendums sui generis eingehen: Es ist nicht so, dass Rechtsentwicklungen bisher nie von aussen an die Schweiz herangetragen wurden, von ausserhalb der Schweiz angestossen wurden. Auch das ist etwas, das wir bereits kennen. Wir kennen das selbstverständlich von den Bilateralen I. Im Rahmen der Bilateralen I wurden bisher über 1000 Rechtsakte übernommen. Das ist also etwas, was bekannt ist. Entscheidend ist vielmehr, wie die Kompetenzordnung ist. Die Kompetenzordnung im Inland ist gewahrt. Sie ist sichergestellt. Wichtig ist, dass wir selbständig entscheiden können und auch immer selbständig entscheiden werden. 
+Jetzt ein Ständemehr einzufordern, missachtet auch den Willen von Volk und Ständen. Eine Ausweitung des Ständemehrs auf Staatsverträge, das hat vorher auch der Sprecher der APK dargelegt, wurde mehrfach abgelehnt, etwa mit der Initiative "Staatsverträge vors Volk". Sie wurde nicht nur mit 75 Prozent Nein-Stimmen abgelehnt, sondern auch von allen Kantonen, und in der Vernehmlassung haben die Kantone dies noch einmal bestätigt: 15 Kantone haben sich für das fakultative Referendum, also für das Volksmehr, und damit gegen das obligatorische Referendum ausgesprochen. Nun soll ausgerechnet im Namen der Kantone eine Regel eingeführt werden, obwohl diese sich mehrheitlich für das fakultative Referendum, für das Volksmehr, ausgesprochen haben.
+Das obligatorische Referendum für dieses Vertragspaket hat also keine Verfassungsgrundlage, es widerspricht der bewährten Praxis sowie dem Willen des Volkes und der Mehrheit der Kantone. In einer Demokratie ändert man die Spielregeln nicht mitten im Spiel, und schon gar nicht für einen politischen Einzelfall. Selbst manche Befürworter des Ständemehrs räumen ein, dass die Verfassungsgrundlage fehlt. Ihre Lösung: Was die Verfassung nicht vorsieht, schreibt man eigens für den Fall hinein. Natürlich kann das Parlament das tun, da gebe ich sogar Herrn Caroni Recht, aber dann entscheiden nicht bewährte Regeln, sondern schlichtes politisches Kalkül. Das ist willkürlich, das passt nicht zur Schweiz, und es passt auch nicht zu unserer demokratischen Kultur. Das ist nicht das Land, das wir kennen. Referenden auf Bestellung der jeweiligen Mehrheit kennen wir in der Schweiz nicht. Plebiszitäre Referenden kennen wir aus anderen Ländern. Das bekannteste Beispiel dafür ist der Brexit, für den ein Referendum vom Premierminister angesetzt wurde, um einen Streit in der eigenen Partei zu beenden. Der Ausgang ist bekannt, der Schaden auch.
+Die Mehrheit der SPK-S und die Minderheit Rieder, die ihren Antrag inzwischen zurückgezogen hat, begründen ihre Anträge auf eine Änderung der Verfassung auch mit deren Artikel 121a Absatz 4. Die Bilateralen III würden gegen den im Zuge der Annahme der Masseneinwanderungs-Initiative in die Bundesverfassung aufgenommenen Artikel verstossen. Sinn und Zweck des Artikels ist die eigenständige Steuerung der Zuwanderung. Damit die Bilateralen III zu einem Konflikt mit diesem Verfassungsartikel führen, müsste es zu einer substanziellen Neuzuwanderung kommen - zu einer Neuzuwanderung, die gegenüber heute mengenmässig bedeutsam ist. Das ist aber nicht der Fall. Die Personenfreizügigkeit ist bekanntlich nicht neu, sie ist bewährt. Die Bevölkerung hat sich auch mehrfach klar zu ihr bekannt. Beim erleichterten Familiennachzug bleiben sämtliche Entscheide über die Kernfamilie hinaus im Ermessen der Schweizer Behörden; es gibt keinen Rechtsanspruch darauf. Die restriktive Praxis der Schweiz bleibt somit bestehen.
+Neu ist einzig der Rechtsanspruch für die Kinder eingetragener Partnerinnen und Partner. Das macht gerade einmal 7 bis 12 Kinder pro Jahr aus. 7 bis 12 Kinder pro Jahr: Das ist keine Masseneinwanderung, das ist eine halbe Schulklasse pro Jahr auf das ganze Land. Daraus einen Verfassungsverstoss abzuleiten, ist schlicht und einfach nicht sachgerecht; es widerspricht auch unserer Praxis. Auch das Freihandelsabkommen mit China, das wurde bereits erwähnt, enthält kleine ausländerrechtliche Kontingente. Es ist nicht das einzige - jenes mit der Türkei wurde vorhin auch erwähnt -, das ohne Ständemehr geschlossen wurde. Wer wegen 7 bis 12 Kindern pro Jahr das Ständemehr verlangt, müsste künftig jedes Freihandelsabkommen mit Regeln für Fach- und Führungskräfte vor Volk und Stände bringen. Das ist eine Hypothek für unsere Aussenwirtschaftspolitik weit über die EU hinaus. Bedenken Sie also den zukünftigen Schaden einer voreiligen Entscheidung.
+Schliesslich sollten wir das Paket nicht auseinanderreissen. Beim Referendum sui generis und der Verfassungsänderung gemäss Antrag der Minderheit der Aussenpolitischen Kommission müssen aufgrund des Verbots der Überkreuzverknüpfung nach Artikel 141a der Bundesverfassung zwei Abstimmungen durchgeführt werden. Die Abkommen unterstünden dem obligatorischen, die Umsetzungsgesetze dem fakultativen Referendum. Die Bilateralen III bestehen aber aus Verträgen mit der EU und den innenpolitischen Begleitmassnahmen; wir haben das in den letzten Tagen intensiv diskutiert. Sie bilden ein Gesamtpaket, auch das wurde wiederholt gesagt. Beides gehört zusammen und bildet ein Gleichgewicht. Eine Trennung könnte dazu führen, dass Volk und Stände in der ersten Abstimmung die Abkommen annehmen und in der zweiten Abstimmung die Umsetzungsgesetzgebung ablehnen, womit das Gesamtpaket fällt. Wer Verträge und innenpolitische Umsetzung auseinanderreisst, gefährdet den fein austarierten Kompromiss zwischen Bundesrat, Kantonen und Sozialpartnern der letzten Jahre.
+Die Kommissionsinitiative der Staatspolitischen Kommission verspricht eine einzige Abstimmung, erkauft diese aber mit einem verfassungspolitisch höchst fragwürdigen Manöver. Sie schreibt die Ratifikation der Abkommen in die Bundesverfassung, einzig um das obligatorische Referendum und das Ständemehr zu erzwingen.
+Zudem entzieht sie den Stimmberechtigten per Verfassung das Referendumsrecht gegen die Umsetzungsgesetzgebung. Die Volksrechte werden eingeschränkt, um eine einzige Abstimmung mit Ständemehr zu konstruieren. Das schränkt die unverfälschte Stimmabgabe ein. Wer die Bilateralen III will, diese staatspolitisch bedenkliche Verfassungsänderung aber ablehnt, kann dies bei der Abstimmung nicht zum Ausdruck bringen.
+Solche Manöver schaffen ein gefährliches Präjudiz. Wenn das Parlament nach politischem Gutdünken bestimmen kann, wann in unserem Land das Ständemehr gilt und wann das Referendum entfällt, gerät unsere Verfassungsordnung ins Wanken. Der ehemalige Direktor des Bundesamtes für Justiz und Staatsrechtler Martin Dumermuth warnt deshalb, dass die in der Verfassung vorgesehene differenzierte und regelgeleitete Referendumsordnung ausgehöhlt und zu einem plebiszitären System degenerieren würde.
+Die Verfassungsänderung gemäss der Kommissionsinitiative ist daher ein trojanisches Pferd - Stärkung der direkten Demokratie steht drauf, Schwächung der Volksrechte steckt drin.
+Es geht um unseren nationalen Zusammenhalt. Die Befürworter argumentieren mit dem Schutz der kleinen Kantone. Unbestritten, der Föderalismus ist fundamentaler Bestandteil unseres Staatswesens, selbstverständlich. Er ist zentral für den Ausgleich und für unsere Identität. Die Mitbestimmung der Kantone gehört zum Wesen der Schweiz, dieser Rat ist das beste Beispiel dafür. Das Ständemehr ist wichtig und richtig; ohne das Ständemehr stünde die Schweiz nicht dort, wo sie heute steht - da sind wir uns in diesem Rat wohl alle einig.
+Aber die klaren Regeln unserer Verfassung schützen nicht nur die kleinen Kantone, die klaren Regeln schützen auch vor Willkür, dass der Grundsatz, jede Stimme zählt gleich viel, nach Belieben eingeschränkt werden kann. Deshalb begrenzt die Verfassung die Anwendung des Ständemehrs. Das ist wichtig, denn das Ständemehr benachteiligt systematisch jene Kantone, die in der Minderheit sind: die bevölkerungsreichen Kantone oder die sprachlichen Minderheiten wie die Romandie. In den zehn Abstimmungen, in denen die Stände das Volk überstimmt haben, verloren die Städte durchwegs, die Romandie wurde siebenmal, das Tessin neunmal überstimmt. Wer das Ständemehr nach Belieben, willkürlich, anwendet, schränkt nicht nur die Gleichheit der Stimmen ein, der spielt auch mit dem nationalen Zusammenhalt. Es werden nicht Gräben geschlossen, es werden Gräben vertieft. Die Balance zwischen Volk- und Ständemehr ist Teil des Schweizer Erfolgsmodells, gerade deshalb dürfen wir diese Balance nicht willkürlich verschieben.
+Die Verfassung ist klar: Für die Bilateralen III ist kein Ständemehr vorgesehen; das entspricht unserer bewährten Praxis bei den Bilateralen I und II, und es entspricht dem Willen von Volk und Ständen. Die Zuwanderung liefert keinen Grund für die Ausnahme, 7 bis 12 Kinder pro Jahr sind keine Masseneinwanderung. Wer jetzt ein Ständemehr verlangt, ändert die Spielregeln mitten im Spiel für einen einzelnen politischen Fall. Das ist Willkür. Und es gefährdet, was die Schweiz zusammenhält: das fein austarierte Gleichgewicht zwischen dem Schutz der kleinen Kantone und dem demokratischen Grundprinzip, dass jede Stimme in diesem Land gleich viel zählt. Unsere Demokratie ist stark, weil die Regeln vorher feststehen und nicht geändert werden, weil uns das mögliche Ergebnis nicht gefällt.
+Ich bitte Sie deshalb, mit der Minderheit der SPK und der Mehrheit der APK dem Bundesrat zu folgen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Verstetigung des Schweizer Beitrags ab 2030 ist, das habe ich schon in der Eintretensdebatte gesagt, ein notwendiges Element des Pakets Schweiz-EU. Von dem her hat Frau Friedli schon recht, wenn sie sagt, dass es auch hier um etwas Grundsätzlicheres gehe; es gehört zum Paket, es ist Teil davon. Wir investieren damit in die Stabilität und den Zusammenhalt in Europa und vertiefen unsere Beziehungen mit den EU-Mitgliedstaaten. Wir investieren hier auch in den Frieden um uns herum.
+Teil des Pake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Verstetigung des Schweizer Beitrags ab 2030 ist, das habe ich schon in der Eintretensdebatte gesagt, ein notwendiges Element des Pakets Schweiz-EU. Von dem her hat Frau Friedli schon recht, wenn sie sagt, dass es auch hier um etwas Grundsätzlicheres gehe; es gehört zum Paket, es ist Teil davon. Wir investieren damit in die Stabilität und den Zusammenhalt in Europa und vertiefen unsere Beziehungen mit den EU-Mitgliedstaaten. Wir investieren hier auch in den Frieden um uns herum.
+Teil des Pakets sind das Beitragsabkommen, das einen vorhersehbaren Rahmen für den Schweizer Beitrag schafft, das Kohäsionsbeitragsgesetz als neue innerstaatliche Rechtsgrundlage, das ist eben ein neues Gesetz, und die drei Verpflichtungskredite für den ersten Beitrag, für die Periode 2030-2036. Ich werde mich an dieser Stelle zu allen drei Bundesbeschlüssen und zu den Verpflichtungskrediten äussern.
+En ce qui concerne la première contribution pour la période 2030-2036, l'accord contient déjà certains éléments, notamment le montant de la contribution fixée à 350 millions de francs par année. Dans le cadre des négociations, nous avons obtenu que cette contribution soit nettement inférieure à celle des États de l'Espace économique européen : - nous l'avons déjà entendu - 40 francs par habitant et par année au lieu de 80 francs par habitant et par année que paye par exemple la Norvège en tant que pays membre de l'Espace économique européen.
+Sur ces 350 millions de francs par an, 88 pour cent seront consacrés au domaine de la cohésion et 12 pour cent au domaine de la migration. Avec le crédit pour la cohésion, la Suisse continue de contribuer à la réduction des inégalités économiques et sociales entre les États, et ce - et je m'adresse surtout à la minorité -, dans le but de garder la stabilité autour de nous et continuer à pouvoir faire des affaires - c'est donc le but principal ; on n'ose presque pas le dire, mais c'est cela qui est important - sur un continent, sur le marché intérieur de l'Union européenne, qui est la principale source de richesses à l'étranger de la Suisse.
+L'accord relatif à la contribution financière régulière de la Suisse visant à réduire les disparités économiques et sociales au sein de l'Union européenne définit à cet effet quatre grands domaines thématiques : - cela aussi, on l'a défini - le développement social et humain inclusif, le développement économique inclusif et durable, la transition vers une économie verte et la démocratie et la participation. Lors de la définition des axes thématiques détaillés, la Suisse fera valoir ses priorités et ses intérêts stratégiques. Nous vous avons déjà dit que cet argent ne finit ni dans les caisses de l'Union européenne ni directement dans les caisses des États membres de l'Union européenne, mais dans des projets faits ensemble avec les États membres et - comme on l'a décidé l'autre jour - le SECO en Suisse.
+Les fonds du crédit d'engagement pour la migration peuvent être utilisés pour des mesures visant à réduire la migration irrégulière. Ici, c'est le SEM qui a le leadership. Cela comprend notamment l'harmonisation des procédures d'asile et des conditions d'accueil dans les États membres de l'Union européenne. En outre, des mesures visant à soutenir le retour volontaire de la réintégration sont envisageables. Vous voyez tout le panel d'instruments que la Suisse utilise pour gérer ensemble, avec les pays voisins en particulier, les flux migratoires.
+C'est pourquoi le Conseil fédéral soumet à votre approbation deux arrêtés fédéraux : le premier pour la cohésion - je vous l'ai dit - et le second pour la migration.
+Als Teil des Paketes der Bilateralen III hat sich die Schweiz zudem bereit erklärt, eine einmalige zusätzliche finanzielle Verpflichtung für den Zeitraum zwischen dem materiellen Abschluss der Verhandlungen, das war Ende 2024, und dem Start der ersten Beitragsperiode, das ist 2030, einzugehen. Also für diese sechs Jahre ist der dritte Verpflichtungskredit. Die zusätzliche Verpflichtung widerspiegelt also den Umfang der Partnerschaft und der Zusammenarbeit Schweiz-EU in diesem Übergangszeitraum. Dies wird in einer gemeinsamen Erklärung festgehalten. Sie umfasst unter anderem die Übergangslösung bei den EU-Programmen ab Anfang letzten Jahres, 2025, sowie die Weiterführung der Übergangsmassnahmen, namentlich in den Bereichen Strom, Gesundheit, Landverkehr und Finanzregulierungsdialog. Es ist das berühmte Übergangsabkommen, das bis zum Inkrafttreten nötig sein wird. Gegenwärtig ist es bis Ende 2028 terminiert. 
+Teil der Vorlage ist daher auch der Verpflichtungskredit für die zusätzliche finanzielle Verpflichtung. Die Höhe dieses Verpflichtungskredites, 1,01 Milliarden Franken, geht von einem frühestmöglichen Inkrafttreten des Stabilisierungsteils des Paketes per 1. Januar 2028 aus. Bei einem späteren Inkrafttreten würde der Verpflichtungskredit entsprechend nicht ausgeschöpft. Sollte also dieses Paket am 1. Januar 2029 in Kraft treten, wären es nur noch 809 Millionen Franken, sollte es am 1. Januar 2030 in Kraft treten, wären es nur noch 604 Millionen Franken. So ist dieser Übergang geregelt.
+Gemeinsam ist allen drei Verpflichtungskrediten, dass die Mittel erst mit dem Inkrafttreten des Paketes und über einen Zeitraum von zehn Jahren, von 2030 bis 2039, umgesetzt und ausbezahlt werden. Die Höhe der drei Verpflichtungskredite entspricht jeweils 93 Prozent des mit der EU vereinbarten Beitrags. Weitere 5 Prozent kann die Schweiz für Personal- und Sachaufwand für die Projektauswahl, die Risikokontrolle und die Qualitätssicherung einsetzen. Das ist schon heute der Fall. Auch dies entspricht also dem bisherigen Ansatz. Wichtig ist: Diese Verwaltungskosten fallen nicht zusätzlich zum vereinbarten Beitrag an, sondern sind schon Teil davon.
+Die hierfür nötigen Mittel werden im Eigenaufwand der Bundesverwaltung budgetiert. Gleiches, und das ist neu nach der Vernehmlassung, gilt für die restlichen 2 Prozent, welche für den Swiss Expertise and Partnership Fund reserviert sind. Für diesen Fonds ist die Schweiz zuständig. Er kann unter anderem für den Einbezug von Schweizer Expertise und Partnerschaften sowie für die Unterstützung der Swissness und der Qualität der Programme und Projekte eingesetzt werden. Sowohl die 5 Prozent Eigenmittel wie auch die 2 Prozent für diesen Fonds werden durch den Globalkredit finanziert und sind somit nicht Teil der Transferkredite.
+Der Bundesrat empfiehlt Ihnen, allen drei Bundesbeschlüssen zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich unterstütze den Vorschlag des Bundesrates, diese Verträge dem fakultativen Referendum zu unterstellen, so, wie es die Bundesverfassung vorsieht. Es war schliesslich auch der Auftrag des Bundesrates, bei diesen Verträgen so zu verhandeln, dass die verfassungsmässige Ordnung nicht tangiert, kein schwerwiegender Eingriff in die innere Struktur der Schweiz vorgenommen und auch keine grundlegende Neuorientierung der schweizerischen Aussenpolitik vorgenommen werden. Das ist nachzulesen auf der Sei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich unterstütze den Vorschlag des Bundesrates, diese Verträge dem fakultativen Referendum zu unterstellen, so, wie es die Bundesverfassung vorsieht. Es war schliesslich auch der Auftrag des Bundesrates, bei diesen Verträgen so zu verhandeln, dass die verfassungsmässige Ordnung nicht tangiert, kein schwerwiegender Eingriff in die innere Struktur der Schweiz vorgenommen und auch keine grundlegende Neuorientierung der schweizerischen Aussenpolitik vorgenommen werden. Das ist nachzulesen auf der Seite 1039 der Botschaft, wo der Bundesrat diesen Beweis ausführt. Infolgedessen lehne ich auch den Kommissionsantrag ab und auch ein Staatsvertragsreferendum sui generis. Ich befinde mich damit in der knappen Minderheit der Staatspolitischen Kommission (SPK) und entspreche dafür der Mehrheit ihrer Aussenpolitischen Kommission (APK). 
+Zuerst zur Kommissionsinitiative. Diese will spezifisch für diese Verträge eine Bestimmung in die Bundesverfassung einführen, wir haben es gehört, welche in der Folge durch die Verfassungsänderung ein obligatorisches Referendum erfordern würde. Also ist man sich im Klaren, die Bundesverfassung erfordert kein obligatorisches Referendum, also löst man es mit einer Übergangsbestimmung. Deshalb, oder einfach ausgedrückt, die Diskussion über den Mehrheitsantrag kann nicht geführt werden, ohne ihn in den Kontext zu stellen, weshalb wir diese Übung durchführen und welches die Intention ist. Ziel der Kommissionsmehrheit ist es, die Bilateralen III dem obligatorischen Referendum zu unterstellen, und weil die Verfassung keine Grundlage dazu liefert, will man ad hoc eine schaffen. Dieses Vorgehen ist verfassungswidrig, denn das Vorgehen ist in der Verfassung festgelegt. Will man es ändern, muss man die Verfassung ändern, das kann man machen. Und diesen Anlauf hat man ja schon mehrmals unternommen. Teilweise wurde jetzt auch in diesem Zusammenhang argumentiert, wir seien frei, die Verfassung auszulegen, wie wir das möchten, wir hätten schliesslich keine Verfassungsgerichtsbarkeit. Das ist richtig, wir haben keine Verfassungsgerichtsbarkeit, aber das gibt doch unserem Parlament keinen Freipass zur Legiferierung gegen die Verfassung. Vielmehr, meine ich, ist das Gegenteil richtig, weil keine Überprüfung durch das Bundesgericht möglich ist, steht das Parlament erst recht in der Verantwortung, verfassungskonform zu legiferieren.
+Die Bundesverfassung bietet aktuell keine Grundlage dafür, die ausgehandelten Verträge mit der EU, so, wie sie uns vorliegen, dem obligatorischen Referendum zu unterstellen. Vielmehr ist das fakultative Referendum gemäss Artikel 141 BV einschlägig. Verlangen es 50 000 Stimmberechtigte oder acht Kantone, werden die Verträge mit der EU dem Volk zur Abstimmung unterbreitet. Das war bei den bilateralen Verträgen auch so, im Speziellen bei den Bilateralen I im Jahr 2000 und bei den Bilateralen II mit dem Schengen-Dublin-Assoziierungsabkommen im Jahr 2005. Und gerade Letzteres bildet, wenn schon, einen schwerwiegenden Eingriff in unsere Autonomie, als es die Bilateralen III heute wären. Der damalige Justizminister Blocher sagte dazu, wir können es wagen. Zur Erinnerung zusätzlich zu sui generis. Der Bundesrat machte bei den Bilateralen II geltend, anders als bei den Bilateralen I, es existiere ausserhalb des geschriebenen Verfassungsrechts ein obligatorisches Staatsvertragsreferendum sui generis, welches dann zur Anwendung kommen könne, wenn ein Staatsvertrag von derartiger Bedeutung sei, dass im Verfassungsrang zukomme. Dem widersprach aber die Mehrheit des Parlamentes, und ich meine zu Recht. Das als erster Punkt. Die drei immer wieder angerufenen Beispiele für die Begründung eines Referendums sui generis - Beitritt Völkerbund 1920, EFTA-Freihandelsabkommen 1972, Beitritt zum Europäischen Wirtschaftsraum EWR 1992 - sind allesamt unter der alten Verfassung erfolgt und nicht unter der Bundesverfassung von 1999.
 </t>
   </si>
 </sst>
@@ -2504,8 +3013,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I96" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I119" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I119"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -5549,6 +6058,663 @@
         <v>379</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B97" t="s">
+        <v>381</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" t="s">
+        <v>46</v>
+      </c>
+      <c r="E97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F97" t="s">
+        <v>48</v>
+      </c>
+      <c r="G97" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" t="s">
+        <v>382</v>
+      </c>
+      <c r="I97" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>384</v>
+      </c>
+      <c r="B98" t="s">
+        <v>381</v>
+      </c>
+      <c r="C98" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" t="s">
+        <v>46</v>
+      </c>
+      <c r="E98" t="s">
+        <v>47</v>
+      </c>
+      <c r="F98" t="s">
+        <v>48</v>
+      </c>
+      <c r="G98" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" t="s">
+        <v>385</v>
+      </c>
+      <c r="I98" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>386</v>
+      </c>
+      <c r="B99" t="s">
+        <v>381</v>
+      </c>
+      <c r="C99" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" t="s">
+        <v>387</v>
+      </c>
+      <c r="E99" t="s">
+        <v>47</v>
+      </c>
+      <c r="F99" t="s">
+        <v>161</v>
+      </c>
+      <c r="G99" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" t="s">
+        <v>388</v>
+      </c>
+      <c r="I99" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>390</v>
+      </c>
+      <c r="B100" t="s">
+        <v>381</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" t="s">
+        <v>387</v>
+      </c>
+      <c r="E100" t="s">
+        <v>47</v>
+      </c>
+      <c r="F100" t="s">
+        <v>161</v>
+      </c>
+      <c r="G100" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" t="s">
+        <v>391</v>
+      </c>
+      <c r="I100" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>392</v>
+      </c>
+      <c r="B101" t="s">
+        <v>381</v>
+      </c>
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E101" t="s">
+        <v>47</v>
+      </c>
+      <c r="F101" t="s">
+        <v>48</v>
+      </c>
+      <c r="G101" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" t="s">
+        <v>393</v>
+      </c>
+      <c r="I101" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>394</v>
+      </c>
+      <c r="B102" t="s">
+        <v>381</v>
+      </c>
+      <c r="C102" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" t="s">
+        <v>395</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" t="s">
+        <v>297</v>
+      </c>
+      <c r="G102" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" t="s">
+        <v>396</v>
+      </c>
+      <c r="I102" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>397</v>
+      </c>
+      <c r="B103" t="s">
+        <v>381</v>
+      </c>
+      <c r="C103" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" t="s">
+        <v>56</v>
+      </c>
+      <c r="E103" t="s">
+        <v>47</v>
+      </c>
+      <c r="F103" t="s">
+        <v>30</v>
+      </c>
+      <c r="G103" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" t="s">
+        <v>398</v>
+      </c>
+      <c r="I103" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>400</v>
+      </c>
+      <c r="B104" t="s">
+        <v>381</v>
+      </c>
+      <c r="C104" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" t="s">
+        <v>35</v>
+      </c>
+      <c r="G104" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" t="s">
+        <v>401</v>
+      </c>
+      <c r="I104" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>403</v>
+      </c>
+      <c r="B105" t="s">
+        <v>381</v>
+      </c>
+      <c r="C105" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" t="s">
+        <v>89</v>
+      </c>
+      <c r="E105"/>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" t="s">
+        <v>404</v>
+      </c>
+      <c r="I105" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>406</v>
+      </c>
+      <c r="B106" t="s">
+        <v>381</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="s">
+        <v>211</v>
+      </c>
+      <c r="E106" t="s">
+        <v>124</v>
+      </c>
+      <c r="F106" t="s">
+        <v>35</v>
+      </c>
+      <c r="G106" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" t="s">
+        <v>407</v>
+      </c>
+      <c r="I106" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>409</v>
+      </c>
+      <c r="B107" t="s">
+        <v>381</v>
+      </c>
+      <c r="C107" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" t="s">
+        <v>56</v>
+      </c>
+      <c r="E107" t="s">
+        <v>47</v>
+      </c>
+      <c r="F107" t="s">
+        <v>30</v>
+      </c>
+      <c r="G107" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" t="s">
+        <v>410</v>
+      </c>
+      <c r="I107" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>412</v>
+      </c>
+      <c r="B108" t="s">
+        <v>381</v>
+      </c>
+      <c r="C108" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108" t="s">
+        <v>124</v>
+      </c>
+      <c r="F108" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" t="s">
+        <v>30</v>
+      </c>
+      <c r="H108" t="s">
+        <v>413</v>
+      </c>
+      <c r="I108" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>414</v>
+      </c>
+      <c r="B109" t="s">
+        <v>381</v>
+      </c>
+      <c r="C109" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" t="s">
+        <v>211</v>
+      </c>
+      <c r="E109" t="s">
+        <v>124</v>
+      </c>
+      <c r="F109" t="s">
+        <v>35</v>
+      </c>
+      <c r="G109" t="s">
+        <v>30</v>
+      </c>
+      <c r="H109" t="s">
+        <v>415</v>
+      </c>
+      <c r="I109" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>417</v>
+      </c>
+      <c r="B110" t="s">
+        <v>381</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" t="s">
+        <v>304</v>
+      </c>
+      <c r="E110"/>
+      <c r="F110" t="s">
+        <v>101</v>
+      </c>
+      <c r="G110" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" t="s">
+        <v>418</v>
+      </c>
+      <c r="I110" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>420</v>
+      </c>
+      <c r="B111" t="s">
+        <v>381</v>
+      </c>
+      <c r="C111" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" t="s">
+        <v>304</v>
+      </c>
+      <c r="E111"/>
+      <c r="F111" t="s">
+        <v>101</v>
+      </c>
+      <c r="G111" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" t="s">
+        <v>421</v>
+      </c>
+      <c r="I111" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>423</v>
+      </c>
+      <c r="B112" t="s">
+        <v>381</v>
+      </c>
+      <c r="C112" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" t="s">
+        <v>424</v>
+      </c>
+      <c r="E112" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" t="s">
+        <v>348</v>
+      </c>
+      <c r="G112" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" t="s">
+        <v>425</v>
+      </c>
+      <c r="I112" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>427</v>
+      </c>
+      <c r="B113" t="s">
+        <v>381</v>
+      </c>
+      <c r="C113" t="s">
+        <v>13</v>
+      </c>
+      <c r="D113" t="s">
+        <v>288</v>
+      </c>
+      <c r="E113" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" t="s">
+        <v>71</v>
+      </c>
+      <c r="G113" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" t="s">
+        <v>428</v>
+      </c>
+      <c r="I113" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>430</v>
+      </c>
+      <c r="B114" t="s">
+        <v>381</v>
+      </c>
+      <c r="C114" t="s">
+        <v>13</v>
+      </c>
+      <c r="D114" t="s">
+        <v>288</v>
+      </c>
+      <c r="E114" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" t="s">
+        <v>71</v>
+      </c>
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" t="s">
+        <v>431</v>
+      </c>
+      <c r="I114" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>433</v>
+      </c>
+      <c r="B115" t="s">
+        <v>381</v>
+      </c>
+      <c r="C115" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" t="s">
+        <v>355</v>
+      </c>
+      <c r="E115" t="s">
+        <v>116</v>
+      </c>
+      <c r="F115" t="s">
+        <v>356</v>
+      </c>
+      <c r="G115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" t="s">
+        <v>434</v>
+      </c>
+      <c r="I115" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>436</v>
+      </c>
+      <c r="B116" t="s">
+        <v>381</v>
+      </c>
+      <c r="C116" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" t="s">
+        <v>304</v>
+      </c>
+      <c r="E116"/>
+      <c r="F116" t="s">
+        <v>101</v>
+      </c>
+      <c r="G116" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" t="s">
+        <v>437</v>
+      </c>
+      <c r="I116" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>439</v>
+      </c>
+      <c r="B117" t="s">
+        <v>381</v>
+      </c>
+      <c r="C117" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>250</v>
+      </c>
+      <c r="E117" t="s">
+        <v>124</v>
+      </c>
+      <c r="F117" t="s">
+        <v>48</v>
+      </c>
+      <c r="G117" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" t="s">
+        <v>440</v>
+      </c>
+      <c r="I117" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>442</v>
+      </c>
+      <c r="B118" t="s">
+        <v>381</v>
+      </c>
+      <c r="C118" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" t="s">
+        <v>304</v>
+      </c>
+      <c r="E118"/>
+      <c r="F118" t="s">
+        <v>101</v>
+      </c>
+      <c r="G118" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" t="s">
+        <v>443</v>
+      </c>
+      <c r="I118" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>445</v>
+      </c>
+      <c r="B119" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" t="s">
+        <v>245</v>
+      </c>
+      <c r="E119" t="s">
+        <v>20</v>
+      </c>
+      <c r="F119" t="s">
+        <v>246</v>
+      </c>
+      <c r="G119" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" t="s">
+        <v>446</v>
+      </c>
+      <c r="I119" t="s">
+        <v>447</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -2492,16 +2492,16 @@
   </si>
   <si>
     <t xml:space="preserve">Die SVP-Fraktion steht ohne Wenn und Aber hinter einer starken und verteidigungsfähigen Schweizer Armee. Es braucht mehr Geld für die Verteidigungsfähigkeit und nicht wie bisher für mehr Bürokratie, gescheiterte Projekte und schlecht verhandelte Beschaffungen. Aber wir sagen ebenso klar: Die notwendige Stärkung unserer Armee darf nicht zum Freipass für immer mehr neue Steuern werden. 
-Die Bundesverfassung gibt uns den klaren Auftrag. Artikel 58 Absatz 2 hält fest: "Die Armee dient der Kriegsverh</t>
+Die Bundesverfassung gibt uns einen klaren Auftrag. Artikel 58 Absatz 2 hält fest: "Die Armee dient der Kriegsve</t>
   </si>
   <si>
     <t xml:space="preserve">Die SVP-Fraktion steht ohne Wenn und Aber hinter einer starken und verteidigungsfähigen Schweizer Armee. Es braucht mehr Geld für die Verteidigungsfähigkeit und nicht wie bisher für mehr Bürokratie, gescheiterte Projekte und schlecht verhandelte Beschaffungen. Aber wir sagen ebenso klar: Die notwendige Stärkung unserer Armee darf nicht zum Freipass für immer mehr neue Steuern werden. 
-Die Bundesverfassung gibt uns den klaren Auftrag. Artikel 58 Absatz 2 hält fest: "Die Armee dient der Kriegsverhinderung und trägt bei zur Erhaltung des Friedens; sie verteidigt das Land und seine Bevölkerung." Das ist kein Wunschkonzert, das ist ein klarer Verfassungsauftrag. Wer einen Verfassungsauftrag erfüllen muss, hat im Bundeshaushalt entsprechende Prioritäten zu setzen.
+Die Bundesverfassung gibt uns einen klaren Auftrag. Artikel 58 Absatz 2 hält fest: "Die Armee dient der Kriegsverhinderung und trägt bei zur Erhaltung des Friedens; sie verteidigt das Land und seine Bevölkerung." Das ist kein Wunschkonzert, das ist ein klarer Verfassungsauftrag. Wer einen Verfassungsauftrag erfüllen muss, hat im Bundeshaushalt entsprechende Prioritäten zu setzen.
 Der Bund gibt 2027 rund 94 Milliarden Franken aus. Mir kann niemand erklären, dass es bei einem solchen Haushalt unmöglich sein soll, die Verteidigungsfähigkeit unseres eigenen Landes ordentlich zu finanzieren. Es fehlt nicht am Geld, es fehlt an der Prioritätensetzung. Bevor man den Bürgerinnen und Bürgern über die Mehrwertsteuer erneut ins Portemonnaie greifen will, muss der Bund zuerst seine Hausaufgaben machen. Dazu gehört auch ausdrücklich das VBS. 
 Die SVP-Fraktion fordert nicht einfach mehr Finanzen für die Armee. Nein, wir fordern mehr Kampfkraft, mehr Verteidigungsfähigkeit für jeden eingesetzten Franken. Das bedeutet weniger Bürokratie, weniger Doppelspurigkeiten, schlankere Verwaltungsstrukturen und effizientere Beschaffungsprozesse. Wir brauchen mehr Soldaten und Systeme, die im Ernstfall funktionieren, und nicht immer mehr Stellen, Sitzungen, Konzepte und Papier im Büroapparat. Das heisst kurz und bündig: Büroapparat verkleinern, Effizienz erhöhen, Mittel konsequent zur Truppe und nah an die Verteidigungsfähigkeit verschieben. Genau dies muss ab heute auch das Credo im VBS sein. Dass dies möglich ist, zeigt der Bundesrat ansatzweise auch selbst. Zusätzliche Mittel für NDB und BABS sollen durch Priorisierungen innerhalb des VBS finanziert sein. Genau dieses Prinzip muss zukünftig überall konsequent angewendet werden. 
 Aber auch ausserhalb des VBS müssen wir endlich Prioritäten setzen. Wir geben Milliarden Franken für die internationale Zusammenarbeit aus. Wir haben hohe Ausgaben im Asyl- und Migrationsbereich. Gleichzeitig sollen wir unserer eigenen Bevölkerung erklären, für die Verteidigung unseres Landes sei im ordentlichen Bundeshaushalt kein Geld mehr vorhanden. Das versteht doch kein Mensch. 
 Für die SVP gilt deshalb ein klarer Grundsatz, nämlich "Switzerland first". Das bedeutet nicht, dass sich die Schweiz von der Welt abwendet. Es bedeutet aber sehr wohl, dass die Sicherheit der eigenen Bevölkerung und die Verteidigung des eigenen Landes zuerst kommt. Wir haben die Armee über Jahrzehnte hinweg finanziell zurückgefahren. 1990 flossen noch 1,33 Prozent des BIP in die Armee. 2025 waren es nur noch 0,67 Prozent. So geht es nicht weiter. Wir müssen dies dringend jetzt und heute korrigieren. 
-Diese Korrektur muss über Priorisierung, Umschichtung und Effizienzsteigerung erfolgen und nicht, wie fast schon auf Bundesebene üblich, reflexartig immer über neue Einnahmen und Steuern. Die SVP verlangt ganz klar, dass das Aufwuchsziel der Armee im ordentlichen Bundeshaushalt sichergestellt wird. Das VBS muss seinen Büroapparat verkleinern und seine Effizienz deutlich steigern. Nicht sicherheitsrelevante Bundesausgaben, insbesondere auch bei der Entwicklungshilfe sowie im Asyl- und Migrationsbereich, müssen konsequent überprüft und priorisiert werden. Es stellt sich hier einmal mehr die Frage: Was ist die erste Pflicht unseres Staates? Die Antwort steht in der Bundesverfassung: Land und Bevölkerung schützen. Wer fast 94 Milliarden Franken pro Jahr ausgibt, muss fähig sein, genügend Geld für die Kernaufgabe bereitzustellen. 
+Diese Korrektur muss über Priorisierung, Umschichtung und Effizienzsteigerung erfolgen und nicht, wie auf Bundesebene fast schon üblich, reflexartig immer über neue Einnahmen und Steuern. Die SVP verlangt ganz klar, dass das Aufwuchsziel der Armee im ordentlichen Bundeshaushalt sichergestellt wird. Das VBS muss seinen Büroapparat verkleinern und seine Effizienz deutlich steigern. Nicht sicherheitsrelevante Bundesausgaben, insbesondere auch bei der Entwicklungshilfe sowie im Asyl- und Migrationsbereich, müssen konsequent überprüft und priorisiert werden. Es stellt sich hier einmal mehr die Frage: Was ist die erste Pflicht unseres Staates? Die Antwort steht in der Bundesverfassung: Land und Bevölkerung zu schützen. Wer fast 94 Milliarden Franken pro Jahr ausgibt, muss fähig sein, genügend Geld für die Kernaufgabe bereitzustellen. 
 Ich danke Ihnen für die Unterstützung unserer Motion.
 </t>
   </si>
@@ -2509,7 +2509,7 @@
     <t xml:space="preserve">422370</t>
   </si>
   <si>
-    <t xml:space="preserve">Sie vermischen hier etwas: Ich habe nicht vom Klima gesprochen, ich habe von Kürzungen im Asylwesen und bei der Entwicklungshilfe gesprochen. Ich denke, wir werden das Klima nicht retten, indem wir nur demonstrieren und grüne Anliegen einbringen. Wir müssen uns der Situation stellen. Wir können z. B. Wasser zurückhalten, Staubecken bauen - das wäre richtig. Mit einer guten Armee können wir diese Staubecken und all das, was wir tun, gut sichern.
+    <t xml:space="preserve">Sie vermischen hier etwas: Ich habe nicht vom Klima gesprochen, ich habe von Kürzungen im Asylwesen und bei der Entwicklungshilfe gesprochen. Ich denke, wir werden das Klima nicht retten, indem wir nur demonstrieren und grüne Anliegen einbringen. Wir müssen uns der Situation stellen. Wir können z. B. Wasser zurückhalten, Staubecken bauen - das wäre richtig. Mit einer guten Armee können wir solche Staubecken und all das, was wir tun, gut sichern.
 </t>
   </si>
   <si>
@@ -2526,7 +2526,7 @@
     <t xml:space="preserve">De Ventura Linda</t>
   </si>
   <si>
-    <t xml:space="preserve">Diese Forderung ist in diesem Vorstoss so nicht enthalten. Darum möchte ich auf Ihre Frage auch keine differenzierte Antwort geben. Aber ich bin dagegen, dass man bei der Diskussion der Armeefinanzierung immer auf die Sans-Papiers und die Flüchtlinge schiesst, wie Sie es tun. Dagegen wehre ich mich.
+    <t xml:space="preserve">Diese Forderung ist im Vorstoss so nicht enthalten. Darum möchte ich auf Ihre Frage auch keine differenzierte Antwort geben. Ich bin aber dagegen, dass man bei der Diskussion über die Armeefinanzierung immer auf die Sans-Papiers und die Flüchtlinge schiesst, wie Sie es tun. Dagegen wehre ich mich.
 </t>
   </si>
   <si>
@@ -2718,6 +2718,207 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">422641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jost Marc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieses Geschäft hat teilweise eine längere Vorgeschichte und auch mehrere Runden zwischen den Räten und dem Bundesrat hinter sich. Ausgangspunkt war die Motion Dobler Marcel 17.3067, "Wenn die Schweiz teure Spezialisten ausbildet, sollen sie auch hier arbeiten können". Nachdem beide Räte die Motion angenommen hatten, legte der Bundesrat im Herbst 2022 eine Revision des Ausländer- und Integrationsgesetzes vor. Vorgesehen war eine Erleichterung beim Arbeitsmarktzugang für Drittstaatsangehörige mit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieses Geschäft hat teilweise eine längere Vorgeschichte und auch mehrere Runden zwischen den Räten und dem Bundesrat hinter sich. Ausgangspunkt war die Motion Dobler Marcel 17.3067, "Wenn die Schweiz teure Spezialisten ausbildet, sollen sie auch hier arbeiten können". Nachdem beide Räte die Motion angenommen hatten, legte der Bundesrat im Herbst 2022 eine Revision des Ausländer- und Integrationsgesetzes vor. Vorgesehen war eine Erleichterung beim Arbeitsmarktzugang für Drittstaatsangehörige mit einem Schweizer Master- oder Doktoratsabschluss in Berufen mit Fachkräftemangel, namentlich durch eine Ausnahme von den Kontingenten. Während unser Rat den Kreis der Begünstigten auf alle Personen mit tertiären Abschlüssen und Postdoktorierende ausweiten wollte, meldete der Ständerat verfassungsrechtliche Bedenken an - insbesondere mit Blick auf Artikel 121a der Bundesverfassung und die Drittstaatenkontingente. Im Dezember 2023 wurde die Vorlage an den Bundesrat zurückgewiesen mit dem Auftrag, einen verfassungskonformen Vorschlag auszuarbeiten, der das Anliegen dennoch erfüllt.
+In der nun vorliegenden Überarbeitung hat der Bundesrat drei Themen zusammengeführt: Erstens das angesprochene Anliegen der Motion Dobler Marcel, zweitens das Anliegen der Motion Atici 22.4105, wonach auch Absolventinnen und Absolventen der höheren Berufsbildung einbezogen werden sollen, sowie drittens Massnahmen zur besseren Arbeitsmarktintegration von Personen mit Schutzstatus S.
+Zum ersten und zweiten Thema: Künftig sollen Absolventinnen und Absolventen einer höheren Berufsbildung sowie Postdoktorierende, gleich wie bisher schon die universitären Hochschulabgängerinnen und -abgänger, von einem erleichterten Zugang profitieren, indem sie vom Inländervorrang ausgenommen werden. Damit bezieht sich die Vorlage nun auf den gesamten Bereich der höheren Berufsbildung in der Schweiz und nicht bloss auf den akademischen Bereich. Hier geht es aus Sicht der Kommission um eine Frage der Logik, aber auch der wirtschaftlichen Vernunft. Die Schweiz investiert beträchtliche Summen in die Ausbildung von Talenten an unseren Hochschulen und in der höheren Berufsbildung. Es wäre paradox, wenn wir diese hochqualifizierten Spezialistinnen und Spezialisten ausbilden würden, nur um sie nach dem Abschluss wieder auszuweisen, während wir gleichzeitig mühsam versuchen, ähnliche Fachkräfte aus dem Ausland zu rekrutieren. Indem wir die Vorrangprüfung für diese Personen lockern - sofern ihre Tätigkeit von hohem wissenschaftlichem oder wirtschaftlichem Interesse ist -, nutzen wir Wissen, das bereits hier im Land vorhanden ist.
+Die Frage der Postdoktorierenden gab in der Kommission zu vertieften Diskussionen Anlass. Ein Postdoktorat ist kein regulärer Ausbildungsgang. Es bestand die Sorge vor Missbrauchspotenzial oder Umgehungstatbeständen. Deshalb haben wir dort noch einmal Präzisierungen vorgenommen.
+Zum dritten Thema: Zur besseren Arbeitsmarktintegration von Personen mit Schutzstatus S werden die Kantone verpflichtet, diese Personen bei der öffentlichen Arbeitsvermittlung (RAV) anzumelden - analog zu den Regelungen bei anerkannten Flüchtlingen und vorläufig aufgenommenen Personen. Wir wissen: Integration gelingt am besten über die Arbeit. Es ist im Interesse der Betroffenen, aber auch im Interesse der gesamten Gesellschaft, dass Menschen mit Schutzstatus S so rasch wie möglich eine Erwerbstätigkeit finden und auch aus der Sozialhilfe herausfinden.
+Weiter erhalten Schutzbedürftige mit Status S, die in einem anderen Kanton arbeiten oder eine Ausbildung absolvieren, die Möglichkeit eines Kantonswechsels, sofern sie keine Sozialhilfe beziehen und das Arbeitsverhältnis bereits seit mehr als zwölf Monaten besteht oder der Arbeitsweg unzumutbar ist.
+Eintreten war in der Kommission unbestritten und wurde einstimmig beschlossen. Ich bitte Sie im Namen der Kommission, ebenfalls auf die Vorlage einzutreten und diese nicht zurückzuweisen. Ein Antrag auf Rückweisung wurde in der Kommission mit 16 zu 9 Stimmen abgelehnt. Auf die Minderheitsanträge werde ich in einem zweiten Votum eingehen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir beantragen Ihnen die Rückweisung der Vorlage an den Bundesrat. Sie vermischt zwei komplett unterschiedliche Themen miteinander, einerseits geht es um Personen mit dem Status S, also um den Asylbereich, und andererseits um Personen aus Drittstaaten, also um den Inländervorrang, um das Ausländerrecht. Die Änderungen, die bei Ihnen auf dem Tisch liegen, wirken auf den ersten Blick eher technisch und harmlos, auf den zweiten Blick sieht es jedoch ein bisschen anders aus. Tatsächlich weichen sie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir beantragen Ihnen die Rückweisung der Vorlage an den Bundesrat. Sie vermischt zwei komplett unterschiedliche Themen miteinander, einerseits geht es um Personen mit dem Status S, also um den Asylbereich, und andererseits um Personen aus Drittstaaten, also um den Inländervorrang, um das Ausländerrecht. Die Änderungen, die bei Ihnen auf dem Tisch liegen, wirken auf den ersten Blick eher technisch und harmlos, auf den zweiten Blick sieht es jedoch ein bisschen anders aus. Tatsächlich weichen sie zwei Grundprinzipien im Migrationsbereich auf. Beim Status S verschiebt sich das Gewicht vom provisorischen Schutz zum definitiven Bleiberecht, und bei Drittstaatsangehörigen, also bei Personen aus Nicht-EU- und Nicht-EFTA-Staaten, verschiebt sich das Gewicht von der Zuwanderungssteuerung mit Inländervorrang hin zu Bleiberechten ohne Inländervorrang. Aus diesen Gründen waren viele Vernehmlassungsantworten aus den Kantonen, auch die Antwort des Gemeindeverbandes, sehr kritisch. Wir sind klar der Meinung, dass die beiden Themen, die in dieser Vorlage vermischt werden, unabhängig voneinander diskutiert werden müssen, sie haben miteinander überhaupt nichts zu tun. Es handelt sich um eine merkwürdige, komische, Gemischtwarenvorlage. Das ist der Hauptgrund für die Rückweisung.
+Zum Schutzstatus S: Kurz nach dem russischen Angriff auf die Ukraine hat der Bundesrat den Schutzstatus S aktiviert. Der Bundesrat hat der Bevölkerung versprochen, der Schutzstatus S sei rückkehrorientiert. Genau so steht es ja auch im Gesetz. Davon ist heute keine Rede mehr. Der Status S wird auch hier schleichend überführt, von einem provisorischen Schutz hin zu einem definitiven Verbleib. Personen mit Status S sollen neu einen Rechtsanspruch auf einen Kantonswechsel bekommen. Ein Kantonswechsel ist für Erwerbstätige schon heute möglich, einfach ohne einen Rechtsanspruch, und den braucht es ja auch nicht. Es braucht ihn mindestens dann nicht, wenn es um einen provisorischen Schutz geht und nicht um definitive Bleiberechte. Auf diesen Punkt haben die Kantone Schaffhausen und Glarus hingewiesen, und auch der Kanton Tessin warnte eindringlich vor hohen Missbrauchsrisiken. Was der Bundesrat hier vorschlägt, ist einfach unehrliche Politik. Ich meine, ehrlicher wäre es, eine Grundsatzdiskussion über den Status S zu führen. Das wäre viel ehrlicher, als diese Salamitaktik, und es wäre ehrlicher, als schleichend immer mehr von der Rückkehrorientierung wegzukommen. Noch viel ehrlicher wäre es, die Versprechen, die man der Bevölkerung bei der Aktivierung des Schutzstatus S gegeben hat, auch zu halten. Wenn solche Versprechen nicht gehalten werden, dann müssen Sie sich in diesem Saal nicht wundern, wenn das Vertrauen der Bevölkerung zu Hause - vielleicht auch oben auf der Tribüne - immer mehr schwindet. Das ist etwas, was wir in diesem Land zunehmend feststellen, und es ist keine gute Entwicklung.
+Bei den Drittstaatsangehörigen will der Bundesrat den Inländervorrang aufweichen. Neu soll ein Bleiberecht erhalten, wer einen höheren Berufsabschluss oder ein Postdoktorat abgeschlossen hat. Es liegt auf der Hand, dass das zu mehr Einwanderung führen wird, und es ist eine Vorlage für noch mehr Zuwanderung. Und das nur drei Monate nach der Abstimmung über die Nachhaltigkeits-Initiative, nur drei Monate nach den vielen Versprechen, die wir gehört haben, dass man die Sorgen der Bevölkerung über die Migration, die viel zu grosse Migration in unserem Land, ernst nehmen wolle in der Politik. Das ist nicht nur unsensibel, das ist völlig deplatziert. Wie beim Schutzstatus S geht es auch hier um die Ehrlichkeit gegenüber der Bevölkerung, das Thema ist genau das gleiche. Man hat das Versprechen abgegeben, die Sorgen bezüglich Zuwanderung ernst zu nehmen, und was macht man drei Monate später? Eine Vorlage behandeln, die das Gegenteil macht; denn diese Vorlage, das ist offensichtlich, weicht Artikel 121a der Bundesverfassung, die von Volk und Ständen angenommene Masseneinwanderungs-Initiative, auf.
+Artikel 121a BV verlangt die Steuerung der Zuwanderung, die Begrenzung durch Höchstzahlen und den Vorrang - genau das, was hier auf dem Tisch liegt - der inländischen Arbeitskräfte. Dieser Inländervorrang, der sorgte genau dafür, dass niemand einwandert oder hierbleibt, wenn Inländer die Arbeit machen können. Nach dem Studium - das sind möglicherweise gut ausgebildete Leute - zu bleiben, wenn Inländer die Arbeit machen können, das ist falsch; das ist der Punkt. 
+Bei den EU-Staaten wird der Inländervorrang ohnehin bereits mit der Personenfreizügigkeit ausgehebelt, aber hier geht es um Drittstaaten, und da gilt er. Die geplante Aufweichung des Inländervorrangs schafft grosse Anreize für Bildungsaufenthalte in der Schweiz. Das wird völlig unterschätzt, das wird zur neuen Schiene, um in die Schweiz einzuwandern. Das spült Arbeitskräfte ins Land für Arbeiten, die auch Einheimische machen könnten. Das führt zu noch mehr Verdrängung auf dem Arbeitsmarkt, und denken Sie daran, die Arbeitslosigkeit ist stark angestiegen, wir sind bereits bei 3 Prozent, und für eine weitere Verdrängung wird mit Sicherheit die Entwicklung der künstlichen Intelligenz sorgen. 
+Man kann diese Aufweichung, wie das die Kommissionssprecher gesagt haben, bei besonders Qualifizierten, bei Leuten, die eine höhere Berufsprüfung oder ein Postdoktorat gemacht haben, wollen. Aber dann braucht es mindestens einen Ausgleich, mindestens eine Kompensation aus Respekt vor der Verfassung. Das ist das Minimum: einen zahlenmässigen Ausgleich für die zusätzlichen Einwanderer - am besten im Asylbereich, wo primär künftige Sozialhilfebezüger ins Land strömen. 
+Es ist bedenklich, dass der Bundesrat keinerlei Kompensation vorgeschlagen hat, er hat nicht einmal genaue Zahlen. Wir sind klar der Meinung, dass er da nochmals über die Bücher gehen muss. Das ist der weitere Grund für die Rückweisung, und wenn Sie nicht zurückweisen wollen, dann bitte ich Sie, wenigstens diese unangebrachte Aufweichung abzulehnen. In diesem Sinne danke ich Ihnen für die Annahme der beiden Minderheitsanträge.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Minderheit betrifft Artikel 53 Absatz 5. Der Entwurf des Bundesrates sieht vor, dass Personen mit Schutzstatus S neu obligatorisch beim RAV gemeldet werden sollen. Das ist in den Kantonen Aargau, Waadt und Zürich heute schon Praxis. In meinem Kanton, dem Kanton Zürich, erfolgt dies in Abweichung von den Voraussetzungen, die für andere gelten. So gilt auch eine Person mit Status S, die Englisch spricht, als für die Arbeitsvermittlung geeignet und wird zugelassen. Die Erfahrungen sind allerd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Minderheit betrifft Artikel 53 Absatz 5. Der Entwurf des Bundesrates sieht vor, dass Personen mit Schutzstatus S neu obligatorisch beim RAV gemeldet werden sollen. Das ist in den Kantonen Aargau, Waadt und Zürich heute schon Praxis. In meinem Kanton, dem Kanton Zürich, erfolgt dies in Abweichung von den Voraussetzungen, die für andere gelten. So gilt auch eine Person mit Status S, die Englisch spricht, als für die Arbeitsvermittlung geeignet und wird zugelassen. Die Erfahrungen sind allerdings im Kanton Zürich gar nicht gut. Mit etwa 180 zu vermittelnden Personen pro Betreuer sind die RAV heute schon überlastet, die Richtzahl wäre etwa 120 Personen pro Betreuer. Diese Entwicklung würde sich weiter verschärfen, wenn obligatorisch neu auch die Personen mit Schutzstatus S hinzukämen. Viele Kantone kritisieren diese Verpflichtung, auch wegen der hohen Bürokratiekosten. Ich verweise auf die von Pascal Schmid erwähnten Vorbehalte im Vernehmlassungsverfahren. Wenn nun noch mehr Personen die Voraussetzungen nicht erfüllen, könnte dies unter Umständen noch mehr Arbeitgeber abschrecken. Ich befürchte, dass diese Änderung keinen Nutzen und bloss hohe Kosten zeitigen würde.
+43 000 Personen mit Schutzstatus S sind im erwerbsfähigen Alter in der Schweiz. Die Sozialhilfequote liegt bei über 50 Prozent, und das würde ja dann heissen, dass mehr als 25 000 Personen neu bei den RAV unter dieses Obligatorium fallen würden, zur Vermittlung angemeldet zu werden.
+Deshalb beantrage ich Ihnen, dass die Meldung von Personen mit Schutzstatus S weiterhin freiwillig sein muss, d. h., bei Absatz 5 beim geltenden Recht zu bleiben.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kälin Irène</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir beklagen den Fachkräftemangel in der Pflege, auf dem Bau, in der IT und in vielen weiteren Berufen und machen gleichzeitig etwas ziemlich Absurdes: Wir bilden Menschen hier aus und schicken sie danach ins Ausland, weil unsere Zulassungsregeln zum Arbeitsmarkt zu eng sind, damit sie bleiben dürften. Wir investieren in ihre Ausbildung, sie lernen unsere Sprache, kennen unser System und unsere Arbeitswelt, und wenn sie dann als qualifizierte Fachkraft fertig ausgebildet sind und hier arbeiten w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir beklagen den Fachkräftemangel in der Pflege, auf dem Bau, in der IT und in vielen weiteren Berufen und machen gleichzeitig etwas ziemlich Absurdes: Wir bilden Menschen hier aus und schicken sie danach ins Ausland, weil unsere Zulassungsregeln zum Arbeitsmarkt zu eng sind, damit sie bleiben dürften. Wir investieren in ihre Ausbildung, sie lernen unsere Sprache, kennen unser System und unsere Arbeitswelt, und wenn sie dann als qualifizierte Fachkraft fertig ausgebildet sind und hier arbeiten wollen, dann sagen wir: Leider nein. Das ist keine sinnvolle Fachkräftepolitik.
+Genau deshalb geht es bei Artikel 21 Absatz 3 AIG um eine einfache Frage: Wollen wir Menschen, die wir in der Schweiz ausgebildet haben, auch ermöglichen, als Fachkräfte hier zu arbeiten? Die Vorlage geht hier einen Schritt in die richtige Richtung, indem die Ausnahme von der Vorrangprüfung auf die höhere Berufsbildung ausgeweitet werden soll. Das ist längst überfällig. Denn weshalb soll eine Ausländerin als ETH-Absolventin anders behandelt werden als jemand mit einem eidgenössischen Fachausweis oder einem HF-Diplom? Das soll sich nun ändern bzw. angleichen, und das ist gut und wichtig und richtig.
+Problematisch bleibt aber das Kriterium des hohen wissenschaftlichen oder wirtschaftlichen Interesses. Es ist vage und schafft Rechtsunsicherheit. Der Vorschlag gemäss unserem Minderheitsantrag ist deshalb klar: Entscheidend soll der Bezug zur Ausbildung sein. Wer hier ausgebildet wurde und eine Stelle findet, für die diese Ausbildung qualifiziert, bringt genau das mit, was wir brauchen. Er oder sie ist eine ausgebildete Fachkraft. Denn sonst droht der Irrweg weiterzugehen, wir schicken wieder Fachkräfte weg, die wir davor selbst ausgebildet und qualifiziert haben. Deshalb beantragen wir mit der Minderheit I (Kälin) bei Artikel 21 Absatz 3 AIG, dies entsprechend zu präzisieren.
+Damit komme ich zur Minderheit betreffend den Kantonswechsel für Personen mit Schutzstatus S. Die Möglichkeit eines Kantonswechsels für schutzbedürftige Personen ist grundsätzlich ein Fortschritt. Doch dieser Fortschritt droht für die meisten Betroffenen unerreichbar zu bleiben. Wieso? Die Vorlage verlangt mit Artikel 75a Absätze 1 und 2 AsylG vollständige Sozialhilfeunabhängigkeit und ein bereits bestehendes Arbeitsverhältnis von mindestens zwölf Monaten als Doppelvoraussetzung für einen Kantonswechsel. Überlegen wir kurz, was das bedeutet. Wer seit einem Jahr arbeitet und vollständig von der Sozialhilfe unabhängig ist, braucht den Kantonswechsel vielleicht gar nicht mehr; wer hingegen den Kantonswechsel braucht, um eine passende Arbeit zu finden und von der Sozialhilfe wegzukommen, kann ihn gar nicht erst machen - das ist doch genau eine falsche Logik. Gerade für Familien und Alleinerziehende entsteht wirtschaftliche Selbstständigkeit nicht von heute auf morgen. Es braucht Betreuung, einen passenden Arbeitsplatz, Arbeits- und Schulwege, die irgendwie zusammengehen, und oft auch Zeit und Qualifikation, um Berufserfahrung aufzubauen. Ein Kantonswechsel kann dabei der entscheidende Schritt sein.
+Nehmen wir als Beispiel eine Mutter aus der Ukraine mit zwei schulpflichtigen Kindern. In ihrem jetzigen Kanton findet sie keine Kinderbetreuung, die zu ihren Arbeitszeiten passt. In einem anderen Kanton hat sie eine Stelle in Aussicht und dort passen Betreuung sowie Schul- und Arbeitsweg besser zusammen, sodass sie in einem höheren Pensum arbeiten kann; sie ist heute jedoch noch auf Sozialhilfe angewiesen. Genau der Kantonswechsel könnte dazu führen, dass sie künftig keine Sozialhilfe mehr braucht oder ihre Sozialhilfeabhängigkeit zumindest reduzieren kann - und trotzdem würde ihr die beantragte Regelung den Wechsel verwehren. Wir verlangen also von ihr, zuerst unabhängig zu werden, und verwehren ihr gleichzeitig den Schritt, der sie unabhängig machen könnte.
+Das adressiert meine Minderheit: Ein Kantonswechsel soll möglich sein, wenn er in direktem Zusammenhang mit einer bestehenden oder konkret bevorstehenden Erwerbstätigkeit steht. Er soll auch dann möglich sein, wenn überwiegende, aber noch keine vollständige Sozialhilfeunabhängigkeit besteht, durch den Wechsel jedoch eine grössere Sozialhilfeunabhängigkeit erreicht werden kann. Das SEM soll zudem die konkreten Lebenssituationen berücksichtigen, sprich: Betreuungspflichten, Arbeitswege und Arbeitszeiten. Wenn wir Erwerbstätigkeit wirklich fördern wollen, müssen wir Hindernisse abbauen und nicht genau dort neue schaffen, wo Menschen den Schritt in die wirtschaftliche Selbstständigkeit machen könnten.
+Ich bitte Sie deshalb, auch die Minderheit I (Kälin) bei Artikel 75a Absätze 1 und 2 AsylG zu unterstützen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dünki-Bättig Michèle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Möglichkeit eines Kantonswechsels bei Erwerbstätigkeit ist ein wichtiger Bestandteil dieser Vorlage. Er folgt einem einfachen Gedanken: Menschen mit Schutzstatus S sollen dort arbeiten können, wo es eine passende Stelle gibt, und ein Kantonswechsel soll die Erwerbstätigkeit nicht unnötig erschweren.
+Die Minderheit I schafft unter bestimmten Voraussetzungen einen Anspruch auf einen Kantonswechsel, meine beiden Minderheitsanträge II und III setzen bewusst innerhalb des Modells von Bundesrat un</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Möglichkeit eines Kantonswechsels bei Erwerbstätigkeit ist ein wichtiger Bestandteil dieser Vorlage. Er folgt einem einfachen Gedanken: Menschen mit Schutzstatus S sollen dort arbeiten können, wo es eine passende Stelle gibt, und ein Kantonswechsel soll die Erwerbstätigkeit nicht unnötig erschweren.
+Die Minderheit I schafft unter bestimmten Voraussetzungen einen Anspruch auf einen Kantonswechsel, meine beiden Minderheitsanträge II und III setzen bewusst innerhalb des Modells von Bundesrat und Kommissionsmehrheit an. Sie sind als Kompromiss ausgestaltet. Es bleibt beim Gesuch und bei einer Prüfung des konkreten Einzelfalls. Wir wollen aber zwei Voraussetzungen so anpassen, dass der Kantonswechsel tatsächlich dazu beitragen kann, die Erwerbstätigkeit zu fördern. 
+Mein Minderheitsantrag II betrifft die Sozialhilfeabhängigkeit. Gemäss der Kommissionsmehrheit darf die betroffene Person weder für sich noch für ihre Familienangehörigen Sozialhilfe beziehen. Genau hier entsteht aus meiner Sicht aber ein Zielkonflikt. Wir verlangen vollständige Sozialhilfeunabhängigkeit bereits als Voraussetzung für einen Kantonswechsel, obwohl dieser Kantonswechsel unter Umständen erst ermöglicht, einen höheren Beschäftigungsgrad zu erreichen und so die Sozialhilfeabhängigkeit zu reduzieren. Das trifft insbesondere Familien und Alleinerziehende. Wer heute bereits arbeitet, wegen beispielsweise Betreuungspflichten aber nur Teilzeit arbeiten kann, ist möglicherweise noch ergänzend auf Sozialhilfe angewiesen. Eine passende Stelle in einem anderen Kanton könnte dann vielleicht einen höheren Beschäftigungsgrad ermöglichen. Nach den aktuellen Vorstellungen der Mehrheit kann aber gerade diese verbleibende teilweise Sozialhilfeabhängigkeit dem Kantonswechsel entgegenstehen. Mein Minderheitsantrag II bleibt beim Gesuchsmodell, lässt aber auch eine teilweise Sozialhilfeabhängigkeit zu. Das SEM soll weiterhin den konkreten Fall prüfen - und es besteht kein automatischer Anspruch. 
+Mein Minderheitsantrag III betrifft die familiären Betreuungspflichten. Der Entwurf berücksichtigt heute den Arbeitsweg und die Arbeitszeiten bei der Frage, ob ein Verbleib im bisherigen Wohnkanton noch zumutbar ist. Ich möchte diese Aufzählung um "familiäre Betreuungspflichten" ergänzen. Für die tatsächliche Möglichkeit, einer Erwerbsarbeit nachzugehen, reicht nämlich der Blick auf Kilometer und Arbeitszeiten nicht aus. Gerade bei Eltern und insbesondere bei Alleinerziehenden geht es um das Zusammenspiel von Arbeitsort, Arbeitszeiten, Schule oder Kindergarten und Kinderbetreuung. Eine Stelle kann auf dem Papier erreichbar und im Alltag trotzdem kaum mit den Betreuungspflichten vereinbar sein. Auch hier geht mein Antrag nicht so weit wie die Minderheit I. Er schafft keinen Anspruch. Er führt lediglich ein zusätzliches Kriterium ein, das das SEM bei seiner Einzelfallprüfung berücksichtigen kann.
+Die beiden Minderheitsanträge II und III sind also ein Mittelweg. Wir bleiben beim System vom Bundesrat und ihrer Kommissionsmehrheit. Wir verhindern aber, dass die Voraussetzungen so eng gefasst werden, dass ein Kantonswechsel erst dann möglich ist, wenn die Arbeitsmarktintegration praktisch schon vollständig gelungen ist. 
+Bitte unterstützen Sie daher meine Minderheitsanträge.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich kann es vorwegnehmen: Die Mitte-Fraktion unterstützt die vorliegende Revision des Ausländer- und Integrationsgesetzes und spricht sich klar für das Eintreten und gegen die Rückweisung aus. Die Vorlage beschreitet bei zwei klar eingegrenzten Themenfeldern einen vernünftigen, pragmatischen Mittelweg. 
+Beim ersten Thema geht es um die Nutzung von Talenten, die wir selbst ausgebildet haben. Es ist schlichtweg paradox und ökonomisch nicht vertretbar, wenn die Schweiz massiv in die Ausbildung von </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich kann es vorwegnehmen: Die Mitte-Fraktion unterstützt die vorliegende Revision des Ausländer- und Integrationsgesetzes und spricht sich klar für das Eintreten und gegen die Rückweisung aus. Die Vorlage beschreitet bei zwei klar eingegrenzten Themenfeldern einen vernünftigen, pragmatischen Mittelweg. 
+Beim ersten Thema geht es um die Nutzung von Talenten, die wir selbst ausgebildet haben. Es ist schlichtweg paradox und ökonomisch nicht vertretbar, wenn die Schweiz massiv in die Ausbildung von Drittstaatsangehörigen an unseren Hochschulen investiert, nur um diese Fachkräfte nach dem Abschluss wieder zu verabschieden. Diese Menschen sind bereits integriert, sie sprechen eine unserer Sprachen, und sie kennen unser System. In Zeiten eines bedeutsamen Fachkräftemangels in vielen Branchen ist es nur zielführend, dieses Potenzial zu nutzen, anstatt mühsam andere Kräfte rekrutieren und auch integrieren zu müssen. Das ist kein Privileg für die betroffenen Arbeitskräfte, sondern eine Investition in unseren eigenen Wirtschaftsstandort.
+Die zweite Neuerung betrifft die Integration von Personen mit Schutzstatus S durch Erwerbstätigkeit. Wir alle wissen, die beste Integration geschieht über den Arbeitsmarkt. Arbeit bedeutet Würde, Selbstständigkeit und soziale Teilhabe. Gleichzeitig ist es im Sinne der Steuerzahler zwingend, die Abhängigkeit von der Sozialhilfe auch bei Personen mit Schutzstatus S so rasch wie möglich zu reduzieren. Die Möglichkeit eines Kantonswechsels, wenn eine gefestigte Erwerbstätigkeit vorliegt, ist hier ein entscheidender Hebel. Wer arbeitet, entlastet die Sozialkassen und leistet einen aktiven Beitrag zu unserer Gesellschaft.
+Diese Anpassungen sind weit entfernt von einer totalen Neuausrichtung unserer Migrationspolitik. Die Vorlage ist deshalb der falsche Ort für jene Grundsatzdiskussionen, die wir beispielsweise im Rahmen der Umsetzung der Asylstrategie 2027 führen müssen und auch führen werden.
+Aus den vorgenannten Gründen bitte ich Sie im Namen der Mitte-Fraktion, beim Rückweisungsantrag der Minderheit Schmid Pascal der Mehrheit zu folgen und diesen abzulehnen. In der Detailberatung werden wir überall der Mehrheit folgen.
+Der Antrag der Minderheit I (Kälin) bei Artikel 21 Absatz 3 würde eine Aufweichung der Voraussetzungen für den Verbleib in der Schweiz darstellen. Für uns steht der Nutzen für unser Land im Vordergrund. Dieser wird mit der Formulierung der Mehrheit am besten gewährleistet.
+Wir wollen ebenfalls keine Aufweichung der Kriterien für den Kantonswechsel bei Personen mit Schutzstatus S. Der Vorschlag des Bundesrates ist ausgewogen. Er berücksichtigt das öffentliche Interesse an einer Integration via Arbeitsmarkt, nimmt aber auch darauf Rücksicht, dass Kantone nicht Gefahr laufen, nach dem Kantonswechsel neu für Personen im Schutzstatus S Sozialhilfe leisten zu müssen. Wir lehnen beim neuen Artikel 75a deshalb sowohl den Antrag der Minderheit I (Kälin) als auch die Minderheitsanträge II und III (Dünki-Bättig) ab.
+Zusammenfassend und auf die kürzestmögliche Formel gebracht, bitte ich Sie, überall der Mehrheit der Staatspolitischen Kommission zu folgen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schläfli Nina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SP-Fraktion begrüsst die Änderung des Ausländer- und Integrationsgesetzes aus folgenden drei Gründen:
+Erstens können arbeitsmarktfähige Menschen mit Schutzstatus S neu bei der öffentlichen Arbeitsvermittlung angemeldet werden. Der Zugang zu Beratung und Vermittlung stärkt die berufliche Integration bzw. die Integration grundsätzlich und vermeidet Doppelspurigkeit.
+Zweitens erhalten erwerbstätige Personen mit Schutzstatus S zudem unter bestimmten Voraussetzungen die Möglichkeit eines Kantonsw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die SP-Fraktion begrüsst die Änderung des Ausländer- und Integrationsgesetzes aus folgenden drei Gründen:
+Erstens können arbeitsmarktfähige Menschen mit Schutzstatus S neu bei der öffentlichen Arbeitsvermittlung angemeldet werden. Der Zugang zu Beratung und Vermittlung stärkt die berufliche Integration bzw. die Integration grundsätzlich und vermeidet Doppelspurigkeit.
+Zweitens erhalten erwerbstätige Personen mit Schutzstatus S zudem unter bestimmten Voraussetzungen die Möglichkeit eines Kantonswechsels. Das ist eine Praxis, die sich seit zwei Jahren für Menschen mit einer vorläufigen Aufnahme bewährt hat und für eine nachhaltigere Integration und bessere Lösungen für die Lebensgestaltung der Menschen selbst sorgt.
+Drittens werden die bestehenden Zulassungserleichterungen für Drittstaatsangehörige mit Schweizer Hochschulabschluss auf Personen mit höherer Berufsbildung sowie auf Postdoktorandinnen und Postdoktoranden ausgeweitet. Eine heute bestehende gesetzliche Lücke wird so geschlossen. Es ist nur konsequent, dass auch diese Personen nach Abschluss ihrer Ausbildung während sechs Monaten eine Stelle suchen können.
+Eintreten ist für die SP-Fraktion unbestritten. Die Rückweisung lehnen wir entschieden ab. In der Detailberatung werden wir jeweils die Minderheitsanträge I (Kälin) sowie II und III (Dünki-Bättig) unterstützen, um die Vorlage noch einmal zusätzlich zu verbessern. Die Minderheitsanträge II (Schmid Pascal) und Steinemann lehnen wir entschieden ab, weil sie den Kern der Verbesserung betreffen und wir ohne diese Gesetzesänderungen auch auf die Vorlage verzichten könnten.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riner Christoph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir unterstützen den Antrag der Minderheit auf Rückweisung der Vorlage an den Bundesrat. Warum? Wir tun dies, weil hier zwei völlig unterschiedliche migrationspolitische Fragen vermischt werden: der Schutzstatus S auf der einen Seite und die Regeln für Drittstaatsangehörige auf der anderen. Beides müsste separat und grundsätzlich diskutiert werden.
+Ich möchte mich insbesondere auf den zweiten Punkt konzentrieren, die geplante weitere Öffnung für Drittstaatsangehörige. Was wir hier erleben, ist e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir unterstützen den Antrag der Minderheit auf Rückweisung der Vorlage an den Bundesrat. Warum? Wir tun dies, weil hier zwei völlig unterschiedliche migrationspolitische Fragen vermischt werden: der Schutzstatus S auf der einen Seite und die Regeln für Drittstaatsangehörige auf der anderen. Beides müsste separat und grundsätzlich diskutiert werden.
+Ich möchte mich insbesondere auf den zweiten Punkt konzentrieren, die geplante weitere Öffnung für Drittstaatsangehörige. Was wir hier erleben, ist ein bekanntes Muster: noch eine Ausnahme von der Ausnahme bei der Zuwanderung, noch eine Erleichterung, noch ein neuer Zugang in die Schweiz, noch ein weiterer Weg zum Bleiberecht. Irgendwann muss man sich schon fragen: Wo endet das eigentlich? 
+Neu soll es eine Möglichkeit für ein Bleiberecht für Personen geben, die in der Schweiz ein Hochschulstudium, eine höhere Berufsbildung oder ein Postdoktorat abgeschlossen haben. Das klingt zunächst technisch, aber hinter dieser technischen Änderung steht eine politische Entscheidung. Der Zugang zum Schweizer Arbeitsmarkt und zum dauerhaften Aufenthalt wird für weitere Personengruppen erleichtert. Das bedeutet zusätzliche Zuwanderung, und zwar nicht irgendwo in der Theorie, sondern als Folge einer bewussten gesetzlichen Öffnung.
+Dabei haben wir in diesem Land gerade erst eine intensive Diskussion über die Folgen der Zuwanderung geführt. Vor der Abstimmung über die Nachhaltigkeits-Initiative wurde von verschiedenen Seiten immer wieder betont: Ja, die Zuwanderung bringt Herausforderungen, ja, die Sorgen müssen ernst genommen werden, ja, die Politik muss hinschauen und die Zuwanderung besser steuern. Kaum ist die Abstimmung vorbei, liegt schon wieder eine Vorlage auf dem Tisch, die neue Erleichterungen und zusätzliche Zuwanderungsmöglichkeiten schafft. Das ist genau das Problem: Die Worte und das Handeln gehen massiv auseinander. Wenn die Bevölkerung den Eindruck gewinnt, dass man ihre Sorgen vor einer Abstimmung ernst nimmt und wenige Monate später einfach wieder neue Ausnahmen schafft, finde ich das, äusserst milde ausgedrückt, einfach nicht in Ordnung, und das schadet der Glaubwürdigkeit der Politik. 
+Diese Glaubwürdigkeit ist zentral. Artikel 121a der Bundesverfassung verlangt, dass die Schweiz die Zuwanderung eigenständig steuert und dabei insbesondere den Vorrang der inländischen Arbeitskräfte berücksichtigt. Der Inländervorrang hat einen einfachen Grund. Wenn eine Stelle mit einer Person besetzt werden kann, die bereits hier lebt und arbeiten darf, soll nicht einfach zusätzlich jemand aus einem Drittstaat zuwandern. Genau dieses Prinzip wird mit jeder zusätzlichen Ausnahme ein Stück weiter ausgehöhlt. 
+Jetzt kommen eine weitere Ausnahme und Erleichterung hinzu. Man kann das politisch wollen, aber dann soll man auch ehrlich sagen, was man tut: Man erleichtert die Zuwanderung in unser Land. Wenn man die Zuwanderung erleichtert, braucht es auch eine Antwort auf die Frage, welche Auswirkungen das auf den Arbeitsmarkt hat. Da ist es legitim zu fragen: Warum muss der Staat den Zugang zum Schweizer Arbeitsmarkt immer weiter öffnen? Warum braucht es immer noch eine zusätzliche Ausnahme, immer noch eine zusätzliche Erleichterung, immer noch einen zusätzlichen Weg zum Bleiberecht? Noch mehr und noch mehr, das ist doch keine migrationspolitische Strategie. Das bedeutet, die Bürger nicht ernst zu nehmen. 
+Genau deshalb fehlt in dieser Vorlage etwas Entscheidendes: ein Gegengewicht. Wenn der Inländervorrang für weitere Gruppen gelockert wird, dann braucht es eine entsprechende Kompensation. Wenn zusätzliche Zuwanderung ermöglicht wird, kann man nicht einfach so tun, als hätte das keine Konsequenzen. Das fehlt vollständig; kein Vorschlag, kein Ansatz, wie die Zuwanderung auf anderem Weg besser gesteuert werden kann. Augen zu und durch, sollen doch die nächsten Generationen ausbaden, was wir heute anrichten.
+Damit sind wir wieder bei der Glaubwürdigkeit. Die Bevölkerung hat sehr wohl verstanden, dass Zuwanderung auch Probleme verursachen kann. Keine Frage, wir nehmen die Sorgen der Bevölkerung ernst, hiess es vor der Abstimmung über die Nachhaltigkeit-Initiative, wir haben die Bevölkerung verstanden. Jetzt wäre der Moment, das auch zu beweisen. Das Verstehen hatte nur eine sehr kurze Lebensdauer, und deshalb sagen wir: Der Bundesrat muss nochmals über die Bücher. Führen wir eine ehrliche Grundsatzdiskussion. Denn eines darf nicht passieren: Dass wir der Bevölkerung vor einer Abstimmung sagen, wir hätten ihre Sorgen verstanden, und danach einfach weitermachen wie bisher. 
+Deshalb bitte ich Sie, dem Antrag der Minderheit auf Rückweisung an den Bundesrat zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jauslin Matthias Samuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Grünliberale Fraktion begrüsst diese Vorlage, wir werden auf sie eintreten. Ich möchte drei Punkte hervorheben.
+1. Wer hier ausgebildet wird, soll hier auch arbeiten können. Jedes Jahr schliessen Menschen aus Drittstaaten eine Ausbildung an einer Hochschule oder einer höheren Fachschule ab. Sie haben hier gelernt, sie kennen unser Bildungssystem und unsere Arbeitswelt, sie sprechen unsere Sprache, haben Kontakte geknüpft und sich in der Schweiz integriert - und wir haben in diese Ausbildung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Grünliberale Fraktion begrüsst diese Vorlage, wir werden auf sie eintreten. Ich möchte drei Punkte hervorheben.
+1. Wer hier ausgebildet wird, soll hier auch arbeiten können. Jedes Jahr schliessen Menschen aus Drittstaaten eine Ausbildung an einer Hochschule oder einer höheren Fachschule ab. Sie haben hier gelernt, sie kennen unser Bildungssystem und unsere Arbeitswelt, sie sprechen unsere Sprache, haben Kontakte geknüpft und sich in der Schweiz integriert - und wir haben in diese Ausbildung investiert. Für uns ergibt es wenig Sinn, diese Fachkräfte wegzuschicken. Es geht ausdrücklich nicht nur um Hochschulabschlüsse. Die Schweiz hat ein hervorragendes duales Bildungssystem und eine starke höhere Berufsbildung. Deshalb unterstützen wir bei Artikel 21 Absatz 3 die Minderheit I (Kälin).
+Wenn jemand in der Schweiz einen Abschluss erworben hat und anschliessend in einem Beruf arbeiten möchte, der diesem Abschluss entspricht, dann sollte dieser Zusammenhang das entscheidende Kriterium sein. Weniger überzeugend ist hier die Haltung der Kommissionsmehrheit, die nur auf die Faktoren hohes wissenschaftliches Interesse oder hohes wirtschaftliches Interesse abstellen will. Fachkräftebedürfnisse verändern sich, Statistiken hinken der Realität hinterher, und gerade im Gastgewerbe zeigen jene beiden Indikatoren nicht den tatsächlichen Fachkräftebedarf.
+2. Wer von der Schweiz einen Schutzstatus erhält, soll auch arbeiten können. Das gilt insbesondere für die Menschen mit Status S. Wir sprechen hier über Menschen, die teilweise seit Jahren in der Schweiz leben. Unser Ziel muss es sein, diese Menschen möglichst rasch in den Arbeitsmarkt zu integrieren. Heute besteht gleichzeitig die Situation, dass wir Arbeitskräfte suchen, Fachkräftemangel beklagen und dass Menschen, die hier leben, teilweise auf Unterstützung angewiesen sind. Das ist kein nachhaltiger Zustand.
+Die Vorlage setzt deshalb richtigerweise bei der Arbeitsvermittlung an, auch schutzbedürftige Personen sollen systematisch den öffentlichen Arbeitsvermittlungsstellen zugeführt werden. Das kennen wir ja bereits von den anerkannten Flüchtlingen und den vorläufig aufgenommenen Personen. Wer arbeiten kann, soll arbeiten; wer eine Stelle findet, soll diese Stelle auch antreten. Das ist keine Frage von links oder rechts, das ist schlicht pragmatische Politik.
+3. Der Arbeitsmarkt endet nicht an der Kantonsgrenze. Wenn eine Person mit Status S in einem anderen Kanton arbeitet oder eine Ausbildung absolviert, muss es unter klaren Voraussetzungen möglich sein, den Wohnkanton zu wechseln. Die Vorlage schafft hier eine vernünftige Lösung. Wir sollten Menschen nicht daran hindern, zu arbeiten, nur weil ihr Wohnort und ihr Arbeitsplatz in verschiedenen Kantonen liegen.
+Nein sagen wir zu den Minderheitsanträgen, die einfach beim geltenden Recht bleiben möchten. Für uns wäre es falsch, auf der einen Seite über Integration und Fachkräftemangel zu sprechen, auf der anderen Seite Hürden belassen, die wir gerade abbauen wollten. Auch wir als GLP wollen zwar klare Regeln - und vor allem wollen wir keine kriminellen Zuwandernde oder Menschen, die unser System ausnützen -, aber wir sollten es uns auch nicht leisten, Menschen auszubilden und ihnen danach zu sagen, danke, aber eure Fähigkeiten möchten wir nicht.
+Ich fasse zusammen: Wir haben in Ausbildung investiert, nutzen wir diese Investitionen. Wir wollen Integration, dann ermöglichen wir auch Arbeit. Wir brauchen Fachkräfte, dann halten wir die Fachkräfte, die wir selber ausgebildet haben.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es wurde schon viel zu dieser Vorlage gesagt. Sie geht in weiten Teilen dorthin, wo wir auch hin möchten. Ich möchte nur zwei, drei Punkte kurz erwähnen. 
+Klar ist Folgendes: Wenn Drittstaatsangehörige an Schweizer Hochschulen oder im Tertiär-B-Bereich, also in der höheren Berufsbildung, teuer ausgebildet wurden, sollen sie auch hier arbeiten dürfen. Diese Forderung geht auf einen Vorstoss unseres Kollegen Marcel Dobler zurück, der diese Thematik einmal eingebracht hat. 
+Die vorliegende Lösung i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es wurde schon viel zu dieser Vorlage gesagt. Sie geht in weiten Teilen dorthin, wo wir auch hin möchten. Ich möchte nur zwei, drei Punkte kurz erwähnen. 
+Klar ist Folgendes: Wenn Drittstaatsangehörige an Schweizer Hochschulen oder im Tertiär-B-Bereich, also in der höheren Berufsbildung, teuer ausgebildet wurden, sollen sie auch hier arbeiten dürfen. Diese Forderung geht auf einen Vorstoss unseres Kollegen Marcel Dobler zurück, der diese Thematik einmal eingebracht hat. 
+Die vorliegende Lösung ist überzeugend: Wenn man in die Leute investiert, sollen sie auch hier arbeiten dürfen. Die Integration über die Arbeit ist wichtig. Es gilt allerdings zwischen zwei Gruppen zu unterscheiden: Arbeitsintegration für Leute, die einen Schutzstatus geniessen, ist gut, ist okay. Auf der anderen Seite darf aber nicht am System gerüttelt werden, wonach zum Beispiel ein Schutzstatus S klar rückkehrorientiert bleiben muss und bleiben soll. Unsere Bundesrätin Karin Keller-Sutter sagte als EJPD-Vorsteherin einmal, der Schutzstatus S sei für den Gesamtbundesrat ein klar rückkehrorientierter Status. Daran soll auch die Arbeitsintegration nichts ändern. 
+Zu einem inhaltlichen Punkt noch beim Kantonswechsel. Dort möchten wir schon, dass die Arbeitsverhältnisse geklärt sind. Wir möchten auch nicht, dass die Leute irgendwelche Möglichkeiten, sprich Schlupflöcher finden, um Sozialhilfe in anderen Kantonen zu beziehen, weil es dort vielleicht etwas einfacher ist, Sozialhilfe zu bekommen. Solche Schlupflöcher dürfen nicht geschaffen werden. Deshalb ist beim Vollzug darauf zu achten, dass nichts zwischen Stühle und Bänke fällt.
+Fazit: Wir unterstützen im Grundsatz diese Vorlage. Wir werden bei der Version des Bundesrates bleiben, das heisst überall den Mehrheiten folgen. Wir werden weder eine Ausweitung der Ansprüche und Bedürfnisse gemäss Minderheiten noch eine Verschärfung tolerieren, sondern die ausgewogene Vorlage so, wie sie uns jetzt vorliegt, unterstützen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich nehme nun im Namen der Kommission Stellung zu den Minderheitsanträgen. Ich habe bereits erwähnt, dass die Kommission den Rückweisungsantrag ablehnt. Aus Sicht der Kommission hat der Bundesrat pragmatisch gehandelt, indem er sachverwandte Anpassungen zum Teil in demselben Gesetz in einer Botschaft gebündelt hat. Nach jahrelangen Debatten das Geschäft nun erneut aufzuspalten, bringt keinen Mehrwert. Die Rückweisung wurde mit 16 zu 9 Stimmen abgelehnt.
+In Artikel 21 Absatz 3 verlangt die Minder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich nehme nun im Namen der Kommission Stellung zu den Minderheitsanträgen. Ich habe bereits erwähnt, dass die Kommission den Rückweisungsantrag ablehnt. Aus Sicht der Kommission hat der Bundesrat pragmatisch gehandelt, indem er sachverwandte Anpassungen zum Teil in demselben Gesetz in einer Botschaft gebündelt hat. Nach jahrelangen Debatten das Geschäft nun erneut aufzuspalten, bringt keinen Mehrwert. Die Rückweisung wurde mit 16 zu 9 Stimmen abgelehnt.
+In Artikel 21 Absatz 3 verlangt die Minderheit I (Kälin) eine Ausweitung der Zulassung, sofern die ausgeübte Erwerbstätigkeit der erworbenen Qualifikation entspricht. Die Mehrheit der Kommission will den Kantonen die Möglichkeit nicht entziehen, Zulassungen flexibel, bedarfsgerecht und den Bedürfnissen des Arbeitsmarkts entsprechend zu steuern. Die Kommission empfiehlt Ihnen mit 15 zu 9 Stimmen, den Minderheitsantrag abzulehnen.
+Der Antrag der Minderheit Schmid Pascal verlangt die ersatzlose Streichung des gesamten Absatzes 3. Dies, und das ist bemerkenswert, würde nicht nur die Motion Dobler ignorieren, sondern das geltende Recht sogar verschärfen, was hier keinesfalls die Absicht des Gesetzgebers war. Die Kommission hat diesen Minderheitsantrag mit 16 zu 9 Stimmen abgelehnt und empfiehlt Ihnen, dasselbe zu tun.
+Ich komme zu Artikel 53 Absatz 5, zur Meldepflicht unter anderem bei Schutzstatus S. Die Minderheit Steinemann möchte die Meldepflicht der Kantone an die öffentliche Arbeitsvermittlung streichen. Diese Pflicht gilt heute bereits für anerkannte Flüchtlinge und vorläufig Aufgenommene. Die Ausdehnung auf Personen mit Schutzstatus S bezweckt eine raschere Arbeitsmarktintegration. Das lohnt sich langfristig, und auch dieser Antrag würde hinter das heute geltende Recht zurückfallen. Deshalb lehnt die Kommission diesen Minderheitsantrag mit 15 zu 9 Stimmen ab.
+Ich komme nun zu Artikel 75a, Kantonswechsel bei Erwerbstätigkeit. Die drei Minderheitsanträge verlangen weitere Erleichterungen beim Kantonswechsel. Die Kommission anerkennt zwar das Integrationsanliegen, gewichtet aber generell das Risiko eines unerwünschten Sozialtourismus deutlich höher und lehnt deshalb diese drei Minderheitsanträge ab. 
+Beim Antrag der Minderheit I (Kälin) kommt hinzu, dass die Rechtsbegriffe sehr unbestimmt sind - ein "Arbeitsverhältnis im Zielkanton, das besteht oder konkret bevorsteht" oder eine Sozialhilfeabhängigkeit, die "voraussichtlich abgebaut werden kann" -, was das Missbrauchsrisiko erhöht. Dieser Minderheitsantrag wurde mit 17 zu 8 Stimmen abgelehnt. 
+Der Antrag der Minderheit II (Dünki-Bättig) wurde aus denselben Überlegungen bezüglich Rechtssicherheit und Missbrauch mit 16 zu 8 Stimmen bei 1 Enthaltung abgelehnt. 
+Die Minderheit III (Dünki-Bättig) will auch aufgrund des Arbeitsweges, der Arbeitszeiten oder, wie wir gehört haben, familiärer Betreuungspflichten den Kantonswechsel ermöglichen. Die Kommission lehnt auch diese Ausweitung mit 16 zu 8 Stimmen bei 1 Enthaltung ab.
+Ich komme zum Fazit: Mit dieser Gesetzesänderung stellen wir die richtigen Weichen. Wir erleichtern die Arbeitsmarktintegration jener Fachkräfte, deren Ausbildung in der Schweiz mitfinanziert wurde, und wir bringen Schutzbedürftige rascher in die Arbeit statt in die Sozialhilfe. 
+In der Gesamtabstimmung hat die Kommission die Vorlage mit 16 zu 9 Stimmen angenommen.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">422409</t>
   </si>
   <si>
@@ -2793,15 +2994,15 @@
     <t xml:space="preserve">Roth Franziska</t>
   </si>
   <si>
-    <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachten ist. W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachten ist. Wir schaffen damit aussenpolitisch viel Goodwill und verstärken das Interesse am Schweizer Know-how vor Ort. Als Land, das sektoriell in hohem Masse in den Binnenmarkt integriert ist und von diesem mehr als mancher EU-Mitgliedstaat profitiert, hat die Schweiz bisher zweimal einen Kohäsionsbeitrag angenommen und ihm zugestimmt. Zuerst tat sie dies im Rahmen der Bilateralen II als Erweiterungsbeitrag zugunsten der zehn im Jahre 2004 beigetretenen EU-Mitgliedstaaten. Seit 2009 gab es dann einen zweiten Beitrag, dessen Rechtsgrundlage aber im Jahr 2024 ausgelaufen ist. Deshalb braucht es zur Verstetigung nun ein neues Abkommen, ein neues Umsetzungsgesetz und dann im zweiten Schritt auch neue Kredite. Ihre Kommission hatte sich also in dreifacher Hinsicht mit dem Kommissionsbeitrag zu befassen: mit dem Abkommen zur Verstetigung des Beitrags, mit dem dazugehörenden innerstaatlichen Umsetzungsgesetz und mit drei Verpflichtungskrediten für die dritte Beitragsperiode in den sieben Jahren von 2030 bis und mit 2036 und einer Überbrückung.
+    <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, sondern als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, sondern als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachten ist. Wir schaffen damit aussenpolitisch viel Goodwill und verstärken das Interesse am Schweizer Know-how vor Ort. Als Land, das sektoriell in hohem Masse in den Binnenmarkt integriert ist und von diesem mehr als mancher EU-Mitgliedstaat profitiert, hat die Schweiz bisher zweimal einen Kohäsionsbeitrag angenommen und ihm zugestimmt. Zuerst tat sie dies im Rahmen der Bilateralen II als Erweiterungsbeitrag zugunsten der zehn im Jahre 2004 beigetretenen EU-Mitgliedstaaten. Seit 2009 gab es dann einen zweiten Beitrag, dessen Rechtsgrundlage aber im Jahr 2024 ausgelaufen ist. Deshalb braucht es zur Verstetigung nun ein neues Abkommen, ein neues Umsetzungsgesetz und dann im zweiten Schritt auch neue Kredite. Ihre Kommission hatte sich also in dreifacher Hinsicht mit dem Kohäsionsbeitrag zu befassen: mit dem Abkommen zur Verstetigung des Beitrags, mit dem dazugehörenden innerstaatlichen Umsetzungsgesetz und mit drei Verpflichtungskrediten für die dritte Beitragsperiode in den sieben Jahren von 2030 bis und mit 2036 und einer Überbrückung.
 Am wenigsten Diskussionen gab es in Ihrer Kommission über die Genehmigung des Abkommens mit der EU über den regelmässigen finanziellen Beitrag der Schweiz zur Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU. Dieses Abkommen gehört zum Stabilisierungsteil des Pakets. Es ist nicht möglich, separat darüber abzustimmen. Es kann nicht aus dem Paket gebrochen werden. Bekanntlich geht der Paketansatz auf einen Wunsch der Schweiz zurück, und die EU hat diesen Wunsch erfüllt. Entsprechend haben die Schweiz und die EU die Verhandlungen über das Paket je mit einer einzigen Unterschrift abgeschlossen. Das Paket bildet eine Einheit, und Sie stimmen dem Abkommen über die Verträge des Kohäsionsbeitrags also im Rahmen Ihrer Genehmigung des Gesamtpakets "Stabilisierung und Weiterentwicklung der Beziehungen Schweiz-EU (Bilaterale III)" zu. Ihre Kommission empfiehlt Ihnen, mit Ihrem Ja zum Bundesbeschluss über die Stabilisierung von fünf bestehenden Abkommen, zu zwei neuen Binnenmarktabkommen und zu einem neuen Kooperationsabkommen auch dem Abkommen über den Kohäsionsbeitrag zuzustimmen, das eben zum Stabilisierungsteil gehört. 
 Mehr zu reden gab in Ihrer Kommission das innerstaatliche Umsetzungsgesetz, das Bundesgesetz über die Beiträge der Schweiz zur Stärkung der Kohäsion in Europa. Das Kohäsionsbeitragsgesetz hält fest, wie die Schweiz die Programme und Projekte im Rahmen des Beitrags unterstützt. Es regelt die Zusammenarbeit mit Dritten, die Auswahl von Schweizer Partnern, die Finanzierung der Beiträge sowie die Zuständigkeiten. Zudem enthält es Bestimmungen zur Evaluation und Berichterstattung. Ihre Kommission trat an ihrer April-Sitzung auf das neue Kohäsionsbeitragsgesetz ein und befasste sich an zwei weiteren Sitzungen im Mai und August mit den Einzelheiten. Dazu unterbreitete Ihre Kommission der Verwaltung und dem Bundesrat zahlreiche Fragen. Sie betrafen die Konsultation des Parlamentes zu den Themenbereichen, die der Bundesrat dem gemischten Ausschuss vorlegen möchte, die laufende Berichterstattung über den Stand der Umsetzung des jeweils laufenden Beitrages, das Verhältnis des Kohäsionsbeitrags zum gesetzlichen Rahmen über das öffentliche Beschaffungswesen und die Finanzhilfe - der immer vorgeht -, den geplanten Überwachungsmechanismus der Schweiz, damit der Schweizer Beitrag auf allen Ebenen ordnungsgemäss umgesetzt wird, und, ganz wichtig, die Zusammenarbeit mit dem Schweizer Privatsektor und der Wissenschaft, die gezielt gefördert werden soll. Darunter fällt auch der Bereich der Berufsbildung, weil auch Schweizer Unternehmen ein genuines Interesse an Fachkräften vor Ort haben. Zudem wurden auch Fragen zu den in Artikel 11 verankerten periodischen Evaluations- und Wirksamkeitsberichten gestellt.
 Zusammenfassend lässt sich sagen, dass die Verwaltung all diese Fragen zur Befriedigung Ihrer Kommission beantwortet hat. Namentlich bekräftigte der Bundesrat, dass er bereits über das Parlamentsgesetz verpflichtet ist, Ihre Kommission zu den Prioritäten zu konsultieren, wie er den Kohäsionsbeitrag in seinem Memorandum of Understanding mit der EU umsetzen will. 
 Kritische Fragen löste der überraschende Antrag des Bundesrates aus, von der bewährten Zusammenarbeit des SECO und der DEZA bei der Umsetzung des Schweizer Kohäsionsbeitrages abzuweichen. Der Bundesrat hat die Zerschlagung dieser Zusammenarbeit am 24. Juni 2026 beschlossen, zeitlich gesehen also zwischen unseren beiden Kommissionssitzungen zur Beratung des Umsetzungsgesetzes. Wichtige Fragen konnten damit nicht wirklich vertieft werden. Im Vernehmlassungsverfahren war die gemeinsame Zuständigkeit von SECO und DEZA ja noch unbestritten gewesen. Entsprechend sah der Bundesrat in seiner Botschaft und im Gesetzesentwurf vom März 2026 in Artikel 10 vor, an der gemeinsamen Zuständigkeit von EDA, unserem Aussendepartement, und WBF, unserem Wirtschaftsdepartement, festzuhalten. Das ergibt auch Sinn, geht es doch beim Kohäsionsbeitrag sowohl um Aussenpolitik als auch um Wirtschaftspolitik.
-In der Kommission beantragte der Bundesrat aber, die explizite Erwähnung des EDA in Artikel 10 zu streichen und stattdessen in Artikel 9 und 11 die alleinige Zuständigkeit des SECO zur Umsetzung des Kohäsionsbeitrages vorzusehen. Zwar wurde uns gesagt, dass EDA solle auf einer politisch-strategischen Ebene weiterhin mitreden könne. Genau dies strich der Bundesrat aber aus seinem ursprünglichen Entwurf, was zu intensiven Diskussionen Anlass gab.
+In der Kommission beantragte der Bundesrat aber, die explizite Erwähnung des EDA in Artikel 10 zu streichen und stattdessen in Artikel 9 und 11 die alleinige Zuständigkeit des SECO zur Umsetzung des Kohäsionsbeitrages vorzusehen. Zwar wurde uns gesagt, das EDA solle auf einer politisch-strategischen Ebene weiterhin mitreden können. Genau dies strich der Bundesrat aber aus seinem ursprünglichen Entwurf, was zu intensiven Diskussionen Anlass gab.
 Fragen warf auch das Verhältnis zur Botschaft über die internationale Zusammenarbeit ab 2029 auf, die ja noch gar nicht vorliegt. So ist die DEZA in mehreren Beitrittskandidaten der EU engagiert, was im Fall des Beitritts zu neuen Problemen führen könnte, wenn gesetzlich vorgeschrieben ist, nur noch das SECO dürfe zuständig sein. Dann gibt es die Migrationsprogramme, die teilweise auch über den Kohäsionsbeitrag finanziert werden, für die heute aber das SEM zuständig ist. 
 Ein Kommissionsmitglied schlug deshalb vor, im Gesetz einfach von den zuständigen Behörden zu sprechen und offen zu lassen, wer wann was macht. Denn üblicherweise ist es nicht Sache des Gesetzgebers, sondern des Bundesrates, in diesem Detaillierungsgrad Zuständigkeiten zu definieren. 
 Zu reden gab auch die fehlende Information an die Öffentlichkeit über die Abänderung der Zuständigkeiten. Botschaften und Finanztabellen enthalten nun Angaben, die gar nicht mehr zutreffen. Der Bundesrat sieht dennoch nicht vor, das nachzuholen. Zwar liegt Ihnen dazu kein Antrag vor, möglicherweise wird sich der Nationalrat aber noch mit diesen Fragen befassen. 
@@ -2874,6 +3075,17 @@
 Wenn Sie sich erinnern wollen: Ich war damals wie viele von Ihnen gegen diese Initiative, die sogenannte Masseneinwanderungs-Initiative. Aber sie steht in der Verfassung, und eines ihrer Ziele war, keine Ausdehnung der Personenfreizügigkeit als Mechanismus zulassen. Wir haben nun in diesem Paket eine solche Ausdehnung, und ich räume gleich vorweg schon ein, dass sie, wie sie daherkommt, quantitativ überschaubar ist. Aber qualitativ geht es um verschiedene Kategorien. Es geht um gleichgeschlechtliche Partner, die man nachziehen kann. Es geht um deren Familiennachzug. Es geht generell um den Familiennachzug ohne ausreichende Wohnung - heute wird diese noch verlangt - und auch um den erleichterten Familiennachzug im Allgemeinen. Wenn man sagt, das seien zahlenmässig sehr wenige Leute, dann muss ich darauf hinweisen, dass die Bestimmung von Artikel 121a Absatz 4 der Bundesverfassung nicht von Mengen spricht, sondern von einem Mechanismus, dass man eben keine Freizügigkeitsrechte als Ansprüche geben möchte, egal, wie viele oder wie wenige Personen es dann sind. Wenn man dann sagt, dass es trotzdem sehr wenige sind, dann möchte ich noch auf die Dynamik verweisen. Denn mit diesen neuen Abkommen unterschreiben wir nicht irgendein Memorandum of Understanding (MOU), wo wir dann sagen, dass wir mal schauen, was künftig vielleicht noch passiert. Nein, wir versprechen im Grundsatz, dass wir künftige Änderungen nachführen. Ich sage nicht, die liegen schon auf dem Tisch - und wenn sie das täten, wären sie ja gar nicht mehr künftig. Aber irgendwann können sie kommen, und wir haben im Grundsatz zugesagt, sie dann zu übernehmen. Natürlich können wir nach unseren Mechanismen das dann nicht übernehmen, und dann sind wir im Vertragsverletzungsverfahren. Das können Sie bei allen Verträgen. Sie können Verträge immer verletzen. Neu ist, dass quasi der Gerichtsmechanismus auch schon definiert ist. Es ändert nichts daran, dass Sie im Grundsatz beschliessen, auch künftige Anpassungen in diesem Bereich zu übernehmen. Und wenn Sie das nicht tun, hat es Konsequenzen, und das hat eine neue Qualität. Also wenn Sie auch das berücksichtigen, kommen Sie zum Schluss, dass es hier mit der bestehenden Verfassung eng wird. Und von den Daueraufenthaltsrechten habe ich noch gar nicht gesprochen.
 Der Bundesrat findet nun erstens, es seien eben nur untergeordnete Ausweitungen, und das sei zulässig. Er findet dazu auch einige Lehrmeinungen, die ihm das bestätigen. Ich muss sagen, diese Lehrmeinungen finde ich äusserst generös. Sie wischen diese Pflicht aus Artikel 121a Absatz 2, dass alle Bewilligungen durch Kontingente und Höchstzahlen begrenzt werden, die ich Ihnen beschrieben habe, mit einem Verweis auf Absatz 1 weg. Dort steht, dass der Bund die Zuwanderung von Ausländerinnen und Ausländern eigenständig steuern soll. Und Sie sagen, wenn nur wenige Leute kommen, ist das in der Sache immer noch eigenständig; es geht ja nur um wenige. Aber man kann nicht das konkrete Instrument mit Verweis auf das allgemeine im Absatz 1 weginterpretieren. Es gibt auch viel strengere Lehrmeinungen. Ich verweise auf die St. Galler Kommentare oder den Verfassungskommentar von Professor Giovanni Biaggini. 
 Der Bundesrat sagt nicht nur, man könne das generöser interpretieren, sondern zweitens auch, dass wir auch sonst schon eine grosszügige Praxis mit den Freihandelsabkommen hätten. Da habe es auch Freizügigkeitsrechte drin, und das hätten wir auch schon akzeptiert. Aber wenn man diese Beispiele anschaut, sieht man, dass diese entweder fast alle älter als diese Verfassungsbestimmung sind - dann sind sie hier irrelevant - oder keine neuen Freizügigkeitsrechte vorsehen. Beispiele, die man genauer anschauen muss, sind Kroatien, das UK und China. Das sind allesamt Sonderfälle. Bei Kroatien hat der Bundesrat ausgeweitet, und das Parlament hat ihm gesagt, dass er immer verfassungskonform bleiben muss. Beim UK ging es nur um bestehende Rechte für Leute, die schon im Lande waren, also nicht um neue Rechte für künftige Einwanderer. Es ging also nur um den Status quo, nicht um künftige Migration. Bei China hatte der Erstrat schon zugestimmt, bevor die Initiative angenommen wurde. Da war man quasi nicht genügend schnell auf der Bremse. Seither respektieren sämtliche Freihandelsabkommen ohne Weiteres diese Bestimmung, mit einer Ausnahme. Beim Freihandelsabkommen mit der Türkei von 2018, scheint mir, hat man den Vorbehalt bezüglich der Kontingente vergessen. Das würde man künftig bestimmt nicht mehr tun. Denn die Wirtschaft wirft eine wichtige Frage auf: Haben wir dann nicht ein Problem mit künftigen Freihandelsabkommen?
+Wenn wir bei diesen Migrationsbestimmungen so streng sind, gehören diese dann nicht immer auch in die Verfassung? Ich glaube, ich kann hier mit Kollege Zopfi sagen: Fürchtet euch nicht. Denn problemlos sind Freihandelsabkommen, die gar keine Aufenthaltsrechte vorsehen, und das ist fast der Normalfall. Dann gibt es Freihandelsabkommen, die kurze Aufenthaltsrechte von bis zu drei Monaten vorsehen, z. B. für einen Serviceeinsatz als Werktätiger; das ist juristisch nicht als Zuwanderung zu werten und ist deshalb auch kein Problem. Ebenfalls problemlos sind schliesslich Freihandelsabkommen, die für längere Aufenthaltsrechte einen Kontingentvorbehalt vorsehen, wie die meisten das tun. Das wird flächendeckend eingehalten, und zwar auch bei den so gewichtigen Abkommen, die wir aktuell bei uns hatten oder haben - beim Abkommen mit Indien, mit dem Mercosur oder auch beim neuen Abkommen, das mit China verhandelt wird. Darüber habe ich mich ebenfalls informieren lassen. Diese Abkommen bewegen sich alle im Rahmen dessen, was die Verfassung heute schon zulässt. Es ist also wirklich kein Problem; man muss das mit dem Kontingentvorbehalt nur richtig machen. Das Elegante bei diesem rechtlichen Punkt ist aber - und damit schliesse ich meine Ausführungen zum zweiten Vorteil einer Verfassungsänderung -, dass man gar nicht abschliessend wie ein höchstes Gericht klären muss, ob jetzt eine Verfassungsverletzung vorliegt oder nicht; man ist einfach auf der sauberen, auf der korrekten, auf der sicheren Seite. 
+Noch zum dritten Vorteil einer Verfassungsänderung: Wenn man die BV schon anfasst, kann man en passant auch gleich sicherstellen, dass der Übersteuerungsmechanismus auch wirklich zum Tragen kommt und nicht vom Bundesgericht ausgebremst werden kann. Stichwort ist die Schubert-Praxis; sie wurde schon das eine oder andere Mal angesprochen. Angesichts seiner bisherigen Praxis lässt das Bundesgericht nicht unbedingt zwingend darauf vertrauen, dass es unsere allfälligen Abweichungen dereinst auch akzeptieren wird. Dies kann man deshalb auch gleich, en passant, sicherstellen; wir wurden auch von der WAK darum gebeten. Ihre Kommission - die Kommissionspräsidentin hat es ausgeführt - hat dazu die parlamentarische Initiative separat losgeschickt, weil es dafür eine Vernehmlassung braucht. Wenn wir dann zum Schluss kommen, jawohl, wir wollen die Schubert-Praxis auf Verfassungsstufe verankern, dann würde die vorliegende Verfassungsnorm vielleicht den Anknüpfungspunkt dazu bieten, um beides in einer Norm zu vereinen. Diese Norm ist also auch anschlussfähig. 
+Ganz zum Schluss möchte ich im Kontrast dazu noch einen Blick auf das Referendum sui generis werfen. Sie sehen, Ihre Kommission hat beide Punkte mit unterschiedlichen Mehrheiten verabschiedet. Ich lege Ihnen auch offen, dass die Enthaltung beim Abstimmungsresultat zur Frage, ob ein obligatorisches Referendum sui generis gegebenenfalls dem fakultativen Referendum vorzuziehen sei, auf mich zurückgeht, weil ich das Resultat zwar unterstütze, aber das Vorgehen nicht ideal finde. Die vorliegende Verfassungsnorm hat gegenüber dem Referendum sui generis folgende Vorteile: 
+Erstens, sie ist klar zulässig. Unsere Verfassung sieht Teilrevisionen explizit vor. Für ein Referendum sui generis finden Sie diese Grundlage nicht. 
+Zweitens klärt die Verfassungsnorm die Frage mit Artikel 121a Absatz 4 BV auf korrekte und saubere Art, und zwar in Form einer späteren, spezialisierten Verfassungsnorm im genau gleichen Verfassungsdokument. Beim Referendum sui generis bliebe diese Frage irgendwie offen. 
+Drittens, Sie können darin, wie soeben erwähnt, die Schubert-Praxis modular einbauen. Das können Sie beim Referendum sui generis nicht; dort müssten Sie dafür eine separate Verfassungsnorm lancieren. 
+Viertens, die Verfassungsnorm hat den Vorteil, dass es nur eine Abstimmung braucht. Ich muss das noch kurz erläutern: Wir beantragen - inspiriert vom Ansatz des Bundesrates bei der EWR-Abstimmung -, im Verfassungstext festzuhalten, dass, wenn man dieser Verfassungsnorm zustimmt, die Gesetzesregeln, wie wir sie in der Schlussabstimmung verabschieden, ohne nochmaliges Referendum gleich mitgenehmigt sind. Dieses "Ja zu allem" - also zu allen Verträgen, allen Gesetzen - hat der Bundesrat damals auch beim EWR so skizziert, und dies ist auch jetzt im bundesrätlichen Entwurf genauso vorgesehen. In unserer Kommission gab es den Wunsch, dass dieses "Ja zu allem" mit der Umsetzungsgesetzgebung nicht auseinanderfalle; das wäre mit dieser Verfassungsnorm also gewährleistet. Beim Referendum sui generis gäbe es einen separaten Bundesbeschluss, der später ebenfalls noch dem Referendum unterstellt würde. Man müsste dann mit der Ratifikation warten, bis dieses zweite Referendum durch wäre. Die Vorlagen wären also schon auch verknüpft, aber sie würden auf zwei Abstimmungen aufgeteilt. Das einmalige Abstimmen wäre also ein weiterer Vorteil dieser Verfassungsbestimmung aus einem Guss. 
+Ich anerkenne natürlich, dies ist noch mein letzter Gedanke, dass, wenn man im Resultat auf jeden Fall ein doppeltes Mehr erreichen will - egal, wie dieses zustande kommt, sei es via ein Referendum sui generis oder via eine Verfassungsanpassung -, es sich aus taktischen Überlegungen heraus in der Tat anbietet, sich bei einer Gegenüberstellung zuerst einmal für das Referendum sui generis zu entscheiden, denn dann wird dieses auf der Fahne aufgeführt, und dann kann man später noch Ja zur Verfassungsbestimmung sagen. Was die Fahne betrifft, ist das ein möglicher Ablauf; das lege ich transparent offen. Wenn Sie aber, wie ich, etwas puristischer sind und finden, dass es nur diese Verfassungsbestimmung geben soll, so nehmen Sie diese schon beim ersten Mal an. 
+Wir haben auch eine Minderheit, die sehr gross und stark ist; sie besteht aus sechs Mitgliedern. Sie wird dann durch Herrn Jositsch vertreten werden und ihre Argumente selbst begründen. 
+Ich möchte zusammenfassend nur noch einmal sagen: Die Vorteile der Verfassungsbestimmung liegen auf der Hand. Man wird damit erstens der Bedeutung der Verträge gerecht und stärkt ihre Legitimität, ohne das Referendum sui generis bemühen zu müssen; man klärt zweitens alle Bedenken im Hinblick auf Artikel 121a Absatz 4 BV; man kann drittens, en passant, die Schubert-Praxis regeln, und viertens kommt so alles aus einem Guss. 
+In diesem Sinne bitte ich Sie, dieser Vorlage, wo immer Sie können, spätestens am Schluss, zuzustimmen und sie so zu verabschieden. 
 </t>
   </si>
   <si>
@@ -2886,13 +3098,13 @@
   <si>
     <t xml:space="preserve">Vi ringrazio per l'approfondita discussione istituzionale. Vi ringrazio per i chiarimenti e per le prospettive che avete messo in risalto. Vi posso assicurare che anche il Consiglio federale ha largamente e approfonditamente discusso questa questione.
 Il Consiglio federale è giunto alla conclusione di attenersi strettamente alla Costituzione e alla prassi seguita dalla Confederazione con i Bilaterali I e II. Perché? Perché così facendo ha concesso ai Cantoni e al Parlamento un'ampia libertà nel processo decisionale di cui oggi abbiamo avuto spettacolo. Signore e signori consiglieri agli Stati, oggi ne avete davvero fatto uso e me ne rallegro molto. Il giusto equilibrio tra democrazia e federalismo, lo abbiamo capito, è davvero un'arte.
-Auch der Bundesrat hat die Frage des Referendums vertieft analysiert und in mehreren Sitzungen diskutiert. Die Kommissionspräsidentin hat erwähnt, wie es in der Kommission war, und auch ich habe das miterlebt, es ist überall dasselbe. Man spürt, diese Frage geht unter die Haut, sie trifft die Essenz unseres Wesens.
+Auch der Bundesrat hat die Frage des Referendums vertieft analysiert und in mehreren Sitzungen diskutiert. Die Kommissionspräsidentin hat erwähnt, wie es in der Kommission war, und auch ich habe das miterlebt, es ist überall dasselbe: Man spürt, diese Frage geht unter die Haut, sie trifft die Essenz unseres Wesens.
 Der Bundesrat hat sich am 30. April 2025 für ein fakultatives Staatsvertragsreferendum ausgesprochen und seinen Standpunkt in seiner Stellungnahme vom 12. August dieses Jahres zur parlamentarischen Initiative der SPK-S nochmals bekräftigt. Der Bundesrat hat seine Begründung für ein fakultatives Referendum auch transparent und ausführlich in der Botschaft vom 13. März 2026 dargelegt.
 In aller Kürze: Erstens hat sich der Bundesrat an die Bundesverfassung gehalten. Diese sieht für die Abkommen des Stabilisierungsteils des Paketes Schweiz-EU ein fakultatives Referendum vor. Zweitens entspricht das fakultative Referendum der bisherigen Praxis bei den Bilateralen I und II. Es stellt damit Kohärenz und Kontinuität sicher und schafft die notwendige Rechtssicherheit. Drittens erfüllen die Abkommen nach Meinung des Bundesrates auch die Voraussetzungen für ein sogenanntes obligatorisches Referendum sui generis nicht. Ein solches kann nach Ansicht des Bundesrates in Ausnahmefällen zur Anwendung kommen, wie auch Sie korrekterweise immer wieder zitiert haben. Es müssen dafür zwei Bedingungen erfüllt sein:
 1 Ein Staatsvertrag bringt einen schwerwiegenden Eingriff in die innere Struktur der Schweiz mit sich, das heisst, die verfassungsmässige Ordnung wird tangiert.
 2. Ein Staatsvertrag bewirkt eine grundlegende Neuorientierung der Aussenpolitik.
-Um eine grundlegende Neuorientierung der Aussenpolitik handelt es sich nicht, das hat heute auch niemand behauptet; dieser zweite Punkt ist also klar. Über den ersten Punkt haben wir etwa vier oder fünf Stunden lang diskutiert, die Quintessenz der Diskussion ist: Das Paket Schweiz-EU stellt für den Bundesrat keinen schwerwiegenden Eingriff in die innere Struktur der Schweiz dar. Jede dynamische Übernahme eines EU-Rechtsaktes erfordert die Zustimmung der Schweiz, sie untersteht also dem normalen innerstaatlichen Genehmigungsverfahren. Grundsätzlich heisst das, es braucht eine Genehmigung durch das Parlament, und allenfalls gibt es ein Referendum, wenn Sie, das Parlament, keine Kompetenzdelegation an den Bundesrat vorgenommen haben. Die Streitbeilegung erfolgt über ein paritätisches Schiedsgericht, wie es im Völkerrecht und bei 34 von 37 Freihandelsabkommen der Schweiz üblich ist. Das Schiedsgericht zieht den europäischen Gerichtshof nur zur Auslegung von EU-Recht bei, falls es relevant und notwendig ist. Der Streit selbst wird stets vom Schiedsgericht beurteilt. Die verfassungsmässigen Rechte und Zuständigkeiten der Kantone, des Parlamentes, des Bundesgerichtes und des Bundesrates bleiben gewahrt.
-Vergessen Sie nicht, dass wir die dynamische Rechtsübernahme bereits seit 20 Jahren, seit 2004 mit Schengen/Dublin üben. Die Konsequenzen einer Nichtübernahme eines EU-Rechtsaktes bei der dynamischen Rechtsübernahme bei den Schengen/Dublin-Assoziierungsabkommen gehen sogar wesentlich weiter als heute bei den Bilateralen III. Wird ein relevanter EU-Rechtsakt nämlich nicht übernommen, werden die Assoziierungsabkommen nach Ablauf einer bestimmten Frist automatisch beendet. Der Bundesrat und das Parlament haben sich auch bei dem Schengen/Dublin-Assoziierungsabkommen für das fakultative Referendum entschieden. Das war für den Bundesrat bindend.
+Um eine grundlegende Neuorientierung der Aussenpolitik handelt es sich nicht, das hat heute auch niemand behauptet; dieser zweite Punkt ist also klar. Über den ersten Punkt haben wir etwa vier oder fünf Stunden lang diskutiert, die Quintessenz der Diskussion ist: Das Paket Schweiz-EU stellt für den Bundesrat keinen schwerwiegenden Eingriff in die innere Struktur der Schweiz dar. Jede dynamische Übernahme eines EU-Rechtsaktes erfordert die Zustimmung der Schweiz, sie untersteht also dem normalen innerstaatlichen Genehmigungsverfahren. Grundsätzlich heisst das, es braucht eine Genehmigung durch das Parlament. Allenfalls gibt es ein Referendum, wenn Sie, das Parlament, keine Kompetenzdelegation an den Bundesrat vorgenommen haben. Die Streitbeilegung erfolgt über ein paritätisches Schiedsgericht, wie es im Völkerrecht und bei 34 von 37 Freihandelsabkommen der Schweiz üblich ist. Das Schiedsgericht zieht den europäischen Gerichtshof nur zur Auslegung von EU-Recht bei, falls es relevant und notwendig ist. Der Streit selbst wird stets vom Schiedsgericht beurteilt. Die verfassungsmässigen Rechte und Zuständigkeiten der Kantone, des Parlamentes, des Bundesgerichtes und des Bundesrates bleiben gewahrt.
+Vergessen Sie nicht, dass wir die dynamische Rechtsübernahme bereits seit zwanzig Jahren, seit 2004 mit Schengen/Dublin üben. Die Konsequenzen einer Nichtübernahme eines EU-Rechtsaktes bei der dynamischen Rechtsübernahme bei den Schengen/Dublin-Assoziierungsabkommen gehen sogar wesentlich weiter als heute bei den Bilateralen III. Wird ein relevanter EU-Rechtsakt nämlich nicht übernommen, werden die Assoziierungsabkommen nach Ablauf einer bestimmten Frist automatisch beendet. Der Bundesrat und das Parlament haben sich auch bei dem Schengen/Dublin-Assoziierungsabkommen für das fakultative Referendum entschieden. Das war für den Bundesrat bindend.
 Das Paket Schweiz-EU bewirkt auch keine grundlegende Neuorientierung der Schweizer Aussenpolitik; das habe ich Ihnen bereits gesagt. 
 Und viertens ermöglicht das fakultative Referendum die formelle Verknüpfung der Abkommen mit deren innenstaatlicher Umsetzung ohne Ausschluss des Referendums für die inländische Umsetzung und ohne Durchführung von zwei separaten Volksabstimmungen. Das war für den Bundesrat auch sehr wichtig. Das wurde heute in der Diskussion kaum erwähnt, aber diese vertikale Bündelung mit einer einzigen Abstimmung war demokratiepolitisch eine wichtige Begründung für den Entscheid des Bundesrates. 
 In der Vernehmlassung, das wurde gesagt, begrüsste ausserdem eine Mehrheit der ständigen Vernehmlassungsteilnehmenden den Vorschlag des Bundesrates, das Paket dem fakultativen Referendum zu unterstellen: 15 der 26 Kantone sowie 5 der 7 politischen Parteien, die im Parlament vertreten sind. 
@@ -2909,20 +3121,20 @@
     <t xml:space="preserve">422586</t>
   </si>
   <si>
-    <t xml:space="preserve">Wie Sie gehört haben, beantrage ich Ihnen mit der Minderheit der SPK und der Mehrheit der APK gemäss Bundesrat das fakultative Referendum, das heisst, die Bilateralen III sollen dem Volksmehr unterstellt werden. Dies aus den folgenden Gründen. 
+    <t xml:space="preserve">Wie Sie gehört haben, beantrage ich Ihnen mit der Minderheit der SPK und der Mehrheit der APK gemäss Bundesrat das fakultative Referendum, das heisst, die Bilateralen III sollen dem Volksmehr unterstellt werden; dies aus den folgenden Gründen. 
 Die Verfassung ist klar, die Verfassung sagt genau, wann es das doppelte Mehr braucht: beim Beitritt zu einer supranationalen Gemeinschaft und zu einer Organisation der kollektiven Sicherheit. Bekanntlich ist beides bei den Bilateralen III nicht der Fall.</t>
   </si>
   <si>
-    <t xml:space="preserve">Wie Sie gehört haben, beantrage ich Ihnen mit der Minderheit der SPK und der Mehrheit der APK gemäss Bundesrat das fakultative Referendum, das heisst, die Bilateralen III sollen dem Volksmehr unterstellt werden. Dies aus den folgenden Gründen. 
+    <t xml:space="preserve">Wie Sie gehört haben, beantrage ich Ihnen mit der Minderheit der SPK und der Mehrheit der APK gemäss Bundesrat das fakultative Referendum, das heisst, die Bilateralen III sollen dem Volksmehr unterstellt werden; dies aus den folgenden Gründen. 
 Die Verfassung ist klar, die Verfassung sagt genau, wann es das doppelte Mehr braucht: beim Beitritt zu einer supranationalen Gemeinschaft und zu einer Organisation der kollektiven Sicherheit. Bekanntlich ist beides bei den Bilateralen III nicht der Fall. Das obligatorische Referendum für die Bilateralen III hat deshalb keine Grundlage in der Verfassung. Wer trotzdem ein obligatorisches Referendum bei den Bilateralen III verlangt, schafft für einen politischen Fall neue Spielregeln mit weitreichenden Konsequenzen. Das Ständemehr bei den Bilateralen III wäre ein Bruch mit unserer bisherigen Praxis. Für die Bilateralen I und II, das haben Sie heute bereits mehrfach gehört, galt das Volksmehr. 
 Auch bei Schengen und Dublin kennen wir eine dynamische Rechtsübernahme. Sie geht sogar weiter als bei den Bilateralen III. Übernehmen wir eine weitere Entwicklung in Schengen nicht, kann dies das Ende des ganzen Abkommens bedeuten. Bei den Bilateralen III ist das anders. Es gibt ein geregeltes Verfahren zur Streitbeilegung, und allfällige Ausgleichsmassnahmen müssen entsprechend auch verhältnismässig sein. Damit setzen die Bilateralen III den möglichen Konsequenzen einen klaren Rahmen. 
 Eine dynamische Rechtsübernahme ist also nicht Neues. Auch bei Schengen und Dublin galt wie bei den Bilateralen I und II das einfache Volksmehr. Damit sind auch die Voraussetzungen für ein Referendum sui generis nicht gegeben. Auch ein theoretisches Referendum sui generis müsste - wenn man davon ausgeht, dass es existiert - gewisse Voraussetzungen erfüllen. Es ist auch das Referendum sui generis nicht rein plebiszitär. Es müsste entweder eine grundlegende Neuausrichtung der Aussenpolitik vorliegen. Das ist nicht der Fall. Wir beraten hier die Fortsetzung der Bilateralen I und II, wir bleiben also auf dem bilateralen Weg. Oder es müsste ein schwerwiegender Eingriff in die innere Struktur unseres Landes sein. Auch wenn die Bilateralen III gewisse institutionelle Elemente wie die dynamische Rechtsübernahme haben, ist dies, wie gesagt, nicht neu. Das kennen wir bereits von Schengen/Dublin, und es ist, wie gesagt, auch eng begrenzt. Sogar aus demokratischer Sicht ist es eine Verbesserung gegenüber heute, weil die Konsequenzen klar eingeschränkt sind. Und Sie haben es anlässlich der Beratung der parlamentarischen Einflussnahme gehört: Die innerstaatliche Kompetenzordnung ist gewahrt. Hier gibt es also keine Veränderung. 
-Ich möchte noch auf das Votum der Mehrheitssprecherin der SPK und also der Vertreterin des Referendums sui generis eingehen: Es ist nicht so, dass Rechtsentwicklungen bisher nie von aussen an die Schweiz herangetragen wurden, von ausserhalb der Schweiz angestossen wurden. Auch das ist etwas, das wir bereits kennen. Wir kennen das selbstverständlich von den Bilateralen I. Im Rahmen der Bilateralen I wurden bisher über 1000 Rechtsakte übernommen. Das ist also etwas, was bekannt ist. Entscheidend ist vielmehr, wie die Kompetenzordnung ist. Die Kompetenzordnung im Inland ist gewahrt. Sie ist sichergestellt. Wichtig ist, dass wir selbständig entscheiden können und auch immer selbständig entscheiden werden. 
+Ich möchte noch auf das Votum der Mehrheitssprecherin der SPK und also der Vertreterin des Referendums sui generis eingehen: Es ist nicht so, dass Rechtsentwicklungen bisher nie von aussen an die Schweiz herangetragen wurden, von ausserhalb der Schweiz angestossen wurden. Auch das ist etwas, das wir bereits kennen. Wir kennen das selbstverständlich von den Bilateralen I. Im Rahmen der Bilateralen I wurden bisher über 1000 Rechtsakte übernommen. Das ist also etwas, was bekannt ist. Entscheidend ist vielmehr, wie die Kompetenzordnung ist. Die Kompetenzordnung im Inland ist gewahrt. Sie ist sichergestellt. Wichtig ist, dass wir selbstständig entscheiden können und auch immer selbstständig entscheiden werden.
 Jetzt ein Ständemehr einzufordern, missachtet auch den Willen von Volk und Ständen. Eine Ausweitung des Ständemehrs auf Staatsverträge, das hat vorher auch der Sprecher der APK dargelegt, wurde mehrfach abgelehnt, etwa mit der Initiative "Staatsverträge vors Volk". Sie wurde nicht nur mit 75 Prozent Nein-Stimmen abgelehnt, sondern auch von allen Kantonen, und in der Vernehmlassung haben die Kantone dies noch einmal bestätigt: 15 Kantone haben sich für das fakultative Referendum, also für das Volksmehr, und damit gegen das obligatorische Referendum ausgesprochen. Nun soll ausgerechnet im Namen der Kantone eine Regel eingeführt werden, obwohl diese sich mehrheitlich für das fakultative Referendum, für das Volksmehr, ausgesprochen haben.
-Das obligatorische Referendum für dieses Vertragspaket hat also keine Verfassungsgrundlage, es widerspricht der bewährten Praxis sowie dem Willen des Volkes und der Mehrheit der Kantone. In einer Demokratie ändert man die Spielregeln nicht mitten im Spiel, und schon gar nicht für einen politischen Einzelfall. Selbst manche Befürworter des Ständemehrs räumen ein, dass die Verfassungsgrundlage fehlt. Ihre Lösung: Was die Verfassung nicht vorsieht, schreibt man eigens für den Fall hinein. Natürlich kann das Parlament das tun, da gebe ich sogar Herrn Caroni Recht, aber dann entscheiden nicht bewährte Regeln, sondern schlichtes politisches Kalkül. Das ist willkürlich, das passt nicht zur Schweiz, und es passt auch nicht zu unserer demokratischen Kultur. Das ist nicht das Land, das wir kennen. Referenden auf Bestellung der jeweiligen Mehrheit kennen wir in der Schweiz nicht. Plebiszitäre Referenden kennen wir aus anderen Ländern. Das bekannteste Beispiel dafür ist der Brexit, für den ein Referendum vom Premierminister angesetzt wurde, um einen Streit in der eigenen Partei zu beenden. Der Ausgang ist bekannt, der Schaden auch.
-Die Mehrheit der SPK-S und die Minderheit Rieder, die ihren Antrag inzwischen zurückgezogen hat, begründen ihre Anträge auf eine Änderung der Verfassung auch mit deren Artikel 121a Absatz 4. Die Bilateralen III würden gegen den im Zuge der Annahme der Masseneinwanderungs-Initiative in die Bundesverfassung aufgenommenen Artikel verstossen. Sinn und Zweck des Artikels ist die eigenständige Steuerung der Zuwanderung. Damit die Bilateralen III zu einem Konflikt mit diesem Verfassungsartikel führen, müsste es zu einer substanziellen Neuzuwanderung kommen - zu einer Neuzuwanderung, die gegenüber heute mengenmässig bedeutsam ist. Das ist aber nicht der Fall. Die Personenfreizügigkeit ist bekanntlich nicht neu, sie ist bewährt. Die Bevölkerung hat sich auch mehrfach klar zu ihr bekannt. Beim erleichterten Familiennachzug bleiben sämtliche Entscheide über die Kernfamilie hinaus im Ermessen der Schweizer Behörden; es gibt keinen Rechtsanspruch darauf. Die restriktive Praxis der Schweiz bleibt somit bestehen.
+Das obligatorische Referendum für dieses Vertragspaket hat also keine Verfassungsgrundlage, es widerspricht der bewährten Praxis sowie dem Willen von Volk und Ständen und der Mehrheit der Kantone. In einer Demokratie ändert man die Spielregeln nicht mitten im Spiel, und schon gar nicht für einen politischen Einzelfall. Selbst manche Befürworter des Ständemehrs räumen ein, dass die Verfassungsgrundlage fehlt. Ihre Lösung: Was die Bundesverfassung nicht vorsieht, schreibt man eigens für den Fall hinein. Natürlich kann das Parlament das tun, da gebe ich Herrn Caroni sogar Recht, aber dann entscheiden nicht bewährte Regeln, sondern schlicht politisches Kalkül. Das ist willkürlich, das passt nicht zur Schweiz, und es passt auch nicht zu unserer demokratischen Kultur. Das ist nicht das Land, das wir kennen. Referenden auf Bestellung der jeweiligen Mehrheit kennen wir in der Schweiz nicht. Plebiszitäre Referenden kennen wir aus anderen Ländern. Das bekannteste Beispiel dafür ist der Brexit, für den ein Referendum vom Premierminister angesetzt wurde, um einen Streit in der eigenen Partei zu beenden. Der Ausgang ist bekannt, der Schaden auch.
+Die Mehrheit der SPK-S und die Minderheit Rieder, die ihren Antrag inzwischen zurückgezogen hat, begründen ihre Anträge auf eine Änderung der Bundesverfassung auch mit deren Artikel 121a Absatz 4. Die Bilateralen III würden gegen den im Zuge der Annahme der Masseneinwanderungs-Initiative in die Bundesverfassung aufgenommenen Artikel verstossen. Sinn und Zweck des Artikels ist die eigenständige Steuerung der Zuwanderung. Damit die Bilateralen III zu einem Konflikt mit diesem Verfassungsartikel führen, müsste es zu einer substanziellen Neuzuwanderung kommen - zu einer Neuzuwanderung, die gegenüber heute mengenmässig bedeutsam ist. Das ist aber nicht der Fall. Die Personenfreizügigkeit ist bekanntlich nicht neu, sie ist bewährt. Die Bevölkerung hat sich auch mehrfach klar zu ihr bekannt. Beim erleichterten Familiennachzug bleiben sämtliche Entscheide über die Kernfamilie hinaus im Ermessen der Schweizer Behörden; es gibt keinen Rechtsanspruch darauf. Die restriktive Praxis der Schweiz bleibt somit bestehen.
 Neu ist einzig der Rechtsanspruch für die Kinder eingetragener Partnerinnen und Partner. Das macht gerade einmal 7 bis 12 Kinder pro Jahr aus. 7 bis 12 Kinder pro Jahr: Das ist keine Masseneinwanderung, das ist eine halbe Schulklasse pro Jahr auf das ganze Land. Daraus einen Verfassungsverstoss abzuleiten, ist schlicht und einfach nicht sachgerecht; es widerspricht auch unserer Praxis. Auch das Freihandelsabkommen mit China, das wurde bereits erwähnt, enthält kleine ausländerrechtliche Kontingente. Es ist nicht das einzige - jenes mit der Türkei wurde vorhin auch erwähnt -, das ohne Ständemehr geschlossen wurde. Wer wegen 7 bis 12 Kindern pro Jahr das Ständemehr verlangt, müsste künftig jedes Freihandelsabkommen mit Regeln für Fach- und Führungskräfte vor Volk und Stände bringen. Das ist eine Hypothek für unsere Aussenwirtschaftspolitik weit über die EU hinaus. Bedenken Sie also den zukünftigen Schaden einer voreiligen Entscheidung.
-Schliesslich sollten wir das Paket nicht auseinanderreissen. Beim Referendum sui generis und der Verfassungsänderung gemäss Antrag der Minderheit der Aussenpolitischen Kommission müssen aufgrund des Verbots der Überkreuzverknüpfung nach Artikel 141a der Bundesverfassung zwei Abstimmungen durchgeführt werden. Die Abkommen unterstünden dem obligatorischen, die Umsetzungsgesetze dem fakultativen Referendum. Die Bilateralen III bestehen aber aus Verträgen mit der EU und den innenpolitischen Begleitmassnahmen; wir haben das in den letzten Tagen intensiv diskutiert. Sie bilden ein Gesamtpaket, auch das wurde wiederholt gesagt. Beides gehört zusammen und bildet ein Gleichgewicht. Eine Trennung könnte dazu führen, dass Volk und Stände in der ersten Abstimmung die Abkommen annehmen und in der zweiten Abstimmung die Umsetzungsgesetzgebung ablehnen, womit das Gesamtpaket fällt. Wer Verträge und innenpolitische Umsetzung auseinanderreisst, gefährdet den fein austarierten Kompromiss zwischen Bundesrat, Kantonen und Sozialpartnern der letzten Jahre.
+Schliesslich sollten wir das Paket nicht auseinanderreissen. Beim Referendum sui generis und der Verfassungsänderung gemäss Antrag der Minderheit der Aussenpolitischen Kommission müssen aufgrund des Verbots der Überkreuzverknüpfung nach Artikel 141a der Bundesverfassung zwei Abstimmungen durchgeführt werden. Die Abkommen unterstünden dem obligatorischen, die Umsetzungsgesetze dem fakultativen Referendum. Die Bilateralen III bestehen aber aus Verträgen mit der EU und den innenpolitischen Begleitmassnahmen; wir haben das in den letzten Tagen intensiv diskutiert. Sie bilden ein Gesamtpaket, auch das wurde wiederholt gesagt. Beides gehört zusammen und bildet ein Gleichgewicht. Eine Trennung könnte dazu führen, dass Volk und Stände in der ersten Abstimmung die Abkommen annehmen und in der zweiten Abstimmung die Umsetzungsgesetzgebung ablehnen, womit das Gesamtpaket fällt. Wer Verträge und innenpolitische Umsetzung auseinanderreisst, gefährdet den in den letzten Jahren fein austarierten Kompromiss zwischen Bundesrat, Kantonen und Sozialpartnern.
 Die Kommissionsinitiative der Staatspolitischen Kommission verspricht eine einzige Abstimmung, erkauft diese aber mit einem verfassungspolitisch höchst fragwürdigen Manöver. Sie schreibt die Ratifikation der Abkommen in die Bundesverfassung, einzig um das obligatorische Referendum und das Ständemehr zu erzwingen.
 Zudem entzieht sie den Stimmberechtigten per Verfassung das Referendumsrecht gegen die Umsetzungsgesetzgebung. Die Volksrechte werden eingeschränkt, um eine einzige Abstimmung mit Ständemehr zu konstruieren. Das schränkt die unverfälschte Stimmabgabe ein. Wer die Bilateralen III will, diese staatspolitisch bedenkliche Verfassungsänderung aber ablehnt, kann dies bei der Abstimmung nicht zum Ausdruck bringen.
 Solche Manöver schaffen ein gefährliches Präjudiz. Wenn das Parlament nach politischem Gutdünken bestimmen kann, wann in unserem Land das Ständemehr gilt und wann das Referendum entfällt, gerät unsere Verfassungsordnung ins Wanken. Der ehemalige Direktor des Bundesamtes für Justiz und Staatsrechtler Martin Dumermuth warnt deshalb, dass die in der Verfassung vorgesehene differenzierte und regelgeleitete Referendumsordnung ausgehöhlt und zu einem plebiszitären System degenerieren würde.
@@ -2953,6 +3165,7 @@
 Gemeinsam ist allen drei Verpflichtungskrediten, dass die Mittel erst mit dem Inkrafttreten des Paketes und über einen Zeitraum von zehn Jahren, von 2030 bis 2039, umgesetzt und ausbezahlt werden. Die Höhe der drei Verpflichtungskredite entspricht jeweils 93 Prozent des mit der EU vereinbarten Beitrags. Weitere 5 Prozent kann die Schweiz für Personal- und Sachaufwand für die Projektauswahl, die Risikokontrolle und die Qualitätssicherung einsetzen. Das ist schon heute der Fall. Auch dies entspricht also dem bisherigen Ansatz. Wichtig ist: Diese Verwaltungskosten fallen nicht zusätzlich zum vereinbarten Beitrag an, sondern sind schon Teil davon.
 Die hierfür nötigen Mittel werden im Eigenaufwand der Bundesverwaltung budgetiert. Gleiches, und das ist neu nach der Vernehmlassung, gilt für die restlichen 2 Prozent, welche für den Swiss Expertise and Partnership Fund reserviert sind. Für diesen Fonds ist die Schweiz zuständig. Er kann unter anderem für den Einbezug von Schweizer Expertise und Partnerschaften sowie für die Unterstützung der Swissness und der Qualität der Programme und Projekte eingesetzt werden. Sowohl die 5 Prozent Eigenmittel wie auch die 2 Prozent für diesen Fonds werden durch den Globalkredit finanziert und sind somit nicht Teil der Transferkredite.
 Der Bundesrat empfiehlt Ihnen, allen drei Bundesbeschlüssen zuzustimmen.
+[VS]
 </t>
   </si>
   <si>
@@ -2962,9 +3175,174 @@
     <t xml:space="preserve">Ich unterstütze den Vorschlag des Bundesrates, diese Verträge dem fakultativen Referendum zu unterstellen, so, wie es die Bundesverfassung vorsieht. Es war schliesslich auch der Auftrag des Bundesrates, bei diesen Verträgen so zu verhandeln, dass die verfassungsmässige Ordnung nicht tangiert, kein schwerwiegender Eingriff in die innere Struktur der Schweiz vorgenommen und auch keine grundlegende Neuorientierung der schweizerischen Aussenpolitik vorgenommen werden. Das ist nachzulesen auf der Sei</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich unterstütze den Vorschlag des Bundesrates, diese Verträge dem fakultativen Referendum zu unterstellen, so, wie es die Bundesverfassung vorsieht. Es war schliesslich auch der Auftrag des Bundesrates, bei diesen Verträgen so zu verhandeln, dass die verfassungsmässige Ordnung nicht tangiert, kein schwerwiegender Eingriff in die innere Struktur der Schweiz vorgenommen und auch keine grundlegende Neuorientierung der schweizerischen Aussenpolitik vorgenommen werden. Das ist nachzulesen auf der Seite 1039 der Botschaft, wo der Bundesrat diesen Beweis ausführt. Infolgedessen lehne ich auch den Kommissionsantrag ab und auch ein Staatsvertragsreferendum sui generis. Ich befinde mich damit in der knappen Minderheit der Staatspolitischen Kommission (SPK) und entspreche dafür der Mehrheit ihrer Aussenpolitischen Kommission (APK). 
-Zuerst zur Kommissionsinitiative. Diese will spezifisch für diese Verträge eine Bestimmung in die Bundesverfassung einführen, wir haben es gehört, welche in der Folge durch die Verfassungsänderung ein obligatorisches Referendum erfordern würde. Also ist man sich im Klaren, die Bundesverfassung erfordert kein obligatorisches Referendum, also löst man es mit einer Übergangsbestimmung. Deshalb, oder einfach ausgedrückt, die Diskussion über den Mehrheitsantrag kann nicht geführt werden, ohne ihn in den Kontext zu stellen, weshalb wir diese Übung durchführen und welches die Intention ist. Ziel der Kommissionsmehrheit ist es, die Bilateralen III dem obligatorischen Referendum zu unterstellen, und weil die Verfassung keine Grundlage dazu liefert, will man ad hoc eine schaffen. Dieses Vorgehen ist verfassungswidrig, denn das Vorgehen ist in der Verfassung festgelegt. Will man es ändern, muss man die Verfassung ändern, das kann man machen. Und diesen Anlauf hat man ja schon mehrmals unternommen. Teilweise wurde jetzt auch in diesem Zusammenhang argumentiert, wir seien frei, die Verfassung auszulegen, wie wir das möchten, wir hätten schliesslich keine Verfassungsgerichtsbarkeit. Das ist richtig, wir haben keine Verfassungsgerichtsbarkeit, aber das gibt doch unserem Parlament keinen Freipass zur Legiferierung gegen die Verfassung. Vielmehr, meine ich, ist das Gegenteil richtig, weil keine Überprüfung durch das Bundesgericht möglich ist, steht das Parlament erst recht in der Verantwortung, verfassungskonform zu legiferieren.
-Die Bundesverfassung bietet aktuell keine Grundlage dafür, die ausgehandelten Verträge mit der EU, so, wie sie uns vorliegen, dem obligatorischen Referendum zu unterstellen. Vielmehr ist das fakultative Referendum gemäss Artikel 141 BV einschlägig. Verlangen es 50 000 Stimmberechtigte oder acht Kantone, werden die Verträge mit der EU dem Volk zur Abstimmung unterbreitet. Das war bei den bilateralen Verträgen auch so, im Speziellen bei den Bilateralen I im Jahr 2000 und bei den Bilateralen II mit dem Schengen-Dublin-Assoziierungsabkommen im Jahr 2005. Und gerade Letzteres bildet, wenn schon, einen schwerwiegenden Eingriff in unsere Autonomie, als es die Bilateralen III heute wären. Der damalige Justizminister Blocher sagte dazu, wir können es wagen. Zur Erinnerung zusätzlich zu sui generis. Der Bundesrat machte bei den Bilateralen II geltend, anders als bei den Bilateralen I, es existiere ausserhalb des geschriebenen Verfassungsrechts ein obligatorisches Staatsvertragsreferendum sui generis, welches dann zur Anwendung kommen könne, wenn ein Staatsvertrag von derartiger Bedeutung sei, dass im Verfassungsrang zukomme. Dem widersprach aber die Mehrheit des Parlamentes, und ich meine zu Recht. Das als erster Punkt. Die drei immer wieder angerufenen Beispiele für die Begründung eines Referendums sui generis - Beitritt Völkerbund 1920, EFTA-Freihandelsabkommen 1972, Beitritt zum Europäischen Wirtschaftsraum EWR 1992 - sind allesamt unter der alten Verfassung erfolgt und nicht unter der Bundesverfassung von 1999.
+    <t xml:space="preserve">Ich unterstütze den Vorschlag des Bundesrates, diese Verträge dem fakultativen Referendum zu unterstellen, so, wie es die Bundesverfassung vorsieht. Es war schliesslich auch der Auftrag des Bundesrates, bei diesen Verträgen so zu verhandeln, dass die verfassungsmässige Ordnung nicht tangiert, kein schwerwiegender Eingriff in die innere Struktur der Schweiz vorgenommen und auch keine grundlegende Neuorientierung der schweizerischen Aussenpolitik vorgenommen werden. Das ist nachzulesen auf der Seite 1039 der Botschaft, wo der Bundesrat diesen Beweis ausführt. Infolgedessen lehne ich auch den Kommissionsantrag ab und auch ein Staatsvertragsreferendum sui generis. Ich befinde mich damit in der knappen Minderheit der Staatspolitischen Kommission (SPK) und entspreche dafür der Mehrheit Ihrer Aussenpolitischen Kommission (APK). 
+Zuerst zur Kommissionsinitiative. Diese will spezifisch für diese Verträge eine Bestimmung in die Bundesverfassung aufnehmen, wir haben es gehört, welche in der Folge durch die Verfassungsänderung ein obligatorisches Referendum erfordern würde. Also ist man sich im Klaren, die Bundesverfassung erfordert kein obligatorisches Referendum, also löst man es mit einer Übergangsbestimmung. Insofern kann, einfach ausgedrückt, die Diskussion über den Mehrheitsantrag nicht geführt werden, ohne ihn in den Kontext zu stellen, weshalb wir diese Übung durchführen und welches die Intention ist. Ziel der Kommissionsmehrheit ist es, die Bilateralen III dem obligatorischen Referendum zu unterstellen, und weil die Bundesverfassung keine Grundlage dazu liefert, will man ad hoc eine schaffen. Dieses Vorgehen ist verfassungswidrig, denn das Vorgehen ist in der Bundesverfassung festgelegt. Will man es ändern, muss man die Bundesverfassung ändern. Das kann man machen, zumal man dazu ja schon mehrmals Anlauf genommen hat. Teilweise wurde jetzt auch in diesem Zusammenhang argumentiert, wir seien frei, die Bundesverfassung auszulegen, wie wir das möchten, wir hätten schliesslich keine Verfassungsgerichtsbarkeit. Das ist richtig, wir haben keine Verfassungsgerichtsbarkeit, aber das gibt doch unserem Parlament keinen Freipass zur Legiferierung gegen die Bundesverfassung. Vielmehr, meine ich, ist das Gegenteil richtig: Weil keine Überprüfung durch das Bundesgericht möglich ist, steht das Parlament erst recht in der Verantwortung, verfassungskonform zu legiferieren.
+Die Bundesverfassung bietet aktuell keine Grundlage dafür, die ausgehandelten Verträge mit der EU, so, wie sie uns vorliegen, dem obligatorischen Referendum zu unterstellen. Vielmehr ist das fakultative Referendum gemäss Artikel 141 der Bundesverfassung einschlägig. Verlangen es 50 000 Stimmberechtigte oder acht Kantone, werden die Verträge mit der EU dem Volk zur Abstimmung unterbreitet. Das war bei den bilateralen Verträgen auch so, im Speziellen bei den Bilateralen I im Jahr 2000 und bei den Bilateralen II mit dem Schengen-Dublin-Assoziierungsabkommen im Jahr 2005. Und gerade Letzteres stellt, wenn schon, einen schwerwiegenden Eingriff in unsere Autonomie dar, als es die Bilateralen III heute täten. Der damalige Justizminister Blocher sagte dazu, wir können es wagen. 
+Zur Erinnerung zusätzlich zu sui generis. Der Bundesrat machte bei den Bilateralen II geltend, anders als bei den Bilateralen I, es existiere ausserhalb des geschriebenen Verfassungsrechts ein obligatorisches Staatsvertragsreferendum sui generis, welches dann zur Anwendung kommen könne, wenn ein Staatsvertrag von derartiger Bedeutung sei, dass im Verfassungsrang zukomme. Dem widersprach aber die Mehrheit des Parlamentes, dies, wie ich meine, zu Recht. Das als erster Punkt. Die drei immer wieder angerufenen Beispiele für die Begründung eines Referendums sui generis - Beitritt Völkerbund 1920, EFTA-Freihandelsabkommen 1972, Beitritt zum Europäischen Wirtschaftsraum EWR 1992 - sind allesamt unter der alten Bundesverfassung erfolgt und nicht unter der Bundesverfassung von 1999.
+2. Mit lediglich drei Fällen in 100 Jahren lässt sich nie und nimmer ein angebliches Gewohnheitsrecht, auf welches eine Sui-generis-Argumentation juristisch abgestützt sein müsste, begründen. Für das Entstehen von ungeschriebenem Verfassungsrecht, welches die Unterstellung unter das Doppelmehrreferendum erfordern bzw. rechtfertigen würde, fehlt es an beiden dafür nach übereinstimmender Lehre und Rechtsprechung erforderlichen Grundvoraussetzungen: Es mangelt sowohl an einer langen und ununterbrochenen, andauernden, einheitlichen Praxis als auch an einer allgemeinen Rechtsüberzeugung. 
+3. Das seit Inkrafttreten der neuen Bundesverfassung von 1999 geltende Verfassungsrecht lässt ein Referendum sui generis nicht zu. Mit meiner Einschätzung befinde ich mich in Gesellschaft der grossen Mehrheit der Staatsrechtsexpertinnen und -experten, wenn die schon immer hier genannt werden. Vor ein paar Monaten haben nicht weniger als zehn von ihnen eine gemeinsame Abhandlung dazu veröffentlicht, nämlich Alberto Achermann, Veronique Boyer, Martin Dumermuth, Astrid Epiney, Maya Hertig Randall, Francesco Maiani, Andreas Müller, Benedikt Pirker, Christa Tobler und Peter Uebersax. Auch zwei renommierte, emeritierte Staatsrechtsprofessoren, die zugleich langjährige Mitglieder dieser Kammer waren, die sehr geschätzten ehemaligen Ständeräte Thomas Pfisterer und René Rhinow, vertreten dezidiert diese Rechtsauffassung, welche ich auch studiert habe. Letzterer hat gemeinsam mit dem emeritierten Staatsrechtsprofessor Georg Müller einen entsprechenden Artikel publiziert, der an Klarheit nichts zu wünschen übrig lässt. Aber ich befinde mich mit meiner Rechtsauffassung nicht nur in Übereinstimmung mit der klaren Mehrheit der Staatsrechtsexperten, sondern auch in Übereinstimmung mit der Mehrheit der Kantone, das heisst der Mehrheit der Stände, zu der auch derjenige gehört, den ich vertrete. Die Kantone haben ein zweifaches Vernehmlassungsverfahren, ein sorgfältiges Verfahren durchgeführt. Letztlich haben sich dann 21 Kantone zu diesen bilateralen Verträgen bekannt. Vier sind dagegen, bei einem Kanton steht der Entscheid noch aus. Wenn wir jetzt schon dabei sind, so sei auch erwähnt, dass 15 Kantone das fakultative Referendum unterstützen, während sich 10 für das obligatorische aussprechen; ein Kanton hat sich enthalten, der Kanton Bern. 
+Zur parlamentarischen Initiative der Staatspolitischen Kommission: Mit dem heute diskutierten Mehrheitsantrag liefert die knappe Mehrheit der Kommission schliesslich den Beweis, dass die Bilateralen III gemäss Bundesverfassung dem fakultativen Referendum unterstehen. Weshalb sonst würde es eine neue Übergangsbestimmung in der Bundesverfassung benötigen, um sie dem obligatorischen Referendum zu unterstellen, wenn dies die Bundesverfassung ja angeblich vorsieht? Nach Artikel 140 Absatz 1 Buchstabe b der Bundesverfassung gilt das obligatorische Referendum - wir haben es gehört - mit Volks- und Ständemehr beim Beitritt zu Organisationen für kollektive Sicherheit oder supranationale Gemeinschaften. Das wäre ein Beitritt zur Nato oder ein Beitritt zur EU. Die ständige Praxis der Bundesversammlung hat sich seit dem Inkrafttreten der neuen Bundesverfassung an diesen Wortlaut gehalten und stützt die hier vertretene Auslegung. Zwar ist die EU zweifellos eine supranationale Gemeinschaft, doch bilaterale Verträge mit ihr sind kein Beitritt zu ihr. Diese Verfassungsbestimmung gilt seit der Neuordnung des Staatsvertragsreferendums im Jahr 1977. Die Verfassungsnorm blieb sowohl bei der Totalrevision der Bundesverfassung im Jahr 1999 als auch im Rahmen der Reform der Volksrechte im Jahre 2003 unangetastet.
+Anlässlich der Verfassungsreform von 1999 lehnten es die eidgenössischen Räte ab, eine Bestimmung aufzunehmen, wonach Staatsverträge von besonderer Bedeutung Volk und Ständen vorgelegt werden müssen. Es sollte nicht bei jedem künftigen Staatsvertrag eine Diskussion eröffnet werden, ob er Volk und Ständen zu unterbreiten sei. Dem fakultativen Referendum unterstehen gemäss Artikel 141 Absatz 1 Buchstabe d Ziffer 3 BV völkerrechtliche Verträge, die wichtige rechtsetzende Bestimmungen enthalten oder deren Umsetzung den Erlass von Bundesgesetzen erfordert. Die Bilateralen III erfüllen exakt diese Bedingungen. Nochmals, es war ein Auftrag des Bundesrates, genau so zu verhandeln. 
+2003 wurde im Rahmen der Reform der Volksrechte das fakultative Staatsvertragsreferendum so ausgeweitet, dass nicht mehr wie bisher jene Staatsverträge dem fakultativen Referendum unterliegen, die eine multilaterale Rechtsvereinheitlichung enthalten, sondern jene, die wichtige rechtsetzende Bestimmungen enthalten oder den Erlass von Bundesgesetzen erfordern - Artikel 141 Absatz 1 Buchstabe d Ziffer 3 BV. Anders als das fakultative blieb das obligatorische Staatsvertragsreferendum im Rahmen der Reform der Volksrechte unverändert. Die neue Regelung zum fakultativen und obligatorischen Referendum wurde von Volk und Ständen so beschlossen.
+Der nächste Versuch, das obligatorische Referendum auszudehnen, folgte im Jahr 2012 mit der Volksinitiative "Staatsverträge vors Volk!", gemäss welcher das obligatorische Referendum dann anwendbar hätte sein sollen, wenn sich die Schweiz verpflichtet, zukünftige rechtsetzende Bestimmungen in wichtigen Bereichen zu übernehmen. Beide Kammern dieses Parlamentes sowie Volk und Stände lehnten die Initiative wuchtig ab.
+Anfang der 2020er-Jahre erfolgte schliesslich die nächste grosse Debatte zum Thema, ausgelöst durch eine Motion von Kollege Andrea Caroni. Die Motion forderte, dass völkerrechtliche Verträge mit verfassungsrechtlichem Charakter dem obligatorischen Referendum unterstellt werden. Der Bundesrat unterbreitete dem Parlament einen Vorschlag für eine entsprechende Verfassungsänderung. Die Vorlage scheiterte im Nationalrat. Im Rahmen der Beratung der Vorlage gab es Voten, in denen behauptet wurde, es gebe ein Referendum sui generis. Aber allein mit parlamentarischen Voten kann man nichts in die Verfassung hineinreden. Der Gesetzgeber ist vielmehr berufen, eine gewünschte Regelung in eine Verfassungsnorm zu giessen. Die Vorlage hätte dem Parlament die konkrete Möglichkeit gegeben, diese Verfassungsbestimmung zu formulieren, aber die Parlamentarier - ich war ja auch dabei - wussten nicht wie und was und gaben auf.
+Wie soll etwas ungeschriebenes Verfassungsrecht sein, das heisst auf einer allgemein akzeptierten Rechtsüberzeugung basieren, von dem man nicht in der Lage ist, es in geschriebene Worte zu fassen? Die Kommissionsmehrheit versucht nun, diese schlüssige Argumentation für die Anwendbarkeit des fakultativen Referendums zu umgehen. Sie verweist nämlich auf eine angeblich erforderliche Übergangsbestimmung in der Bundesverfassung betreffend die Bilateralen III. Dafür muss der Zuwanderungsartikel 121a herhalten, welcher - so wird behauptet - durch den neu möglichen Zuzug weniger Personen aus dem EU-Raum verletzt werden würde. Dass dem nicht so ist und die Schweiz die Zuwanderung von Ausländerinnen und Ausländern auch unter den Bilateralen III weiterhin eigenständig steuern kann - nämlich via Kompensation, via Drittstaatenkontingente -, hat der Bundesrat in seiner Botschaft im Kapitel 2.3.10.1.3, Seiten 459 bis 462, erläutert und nun auch in seiner Stellungnahme vom 12. August deutlich gemacht. Diese Position wird ebenso von der grossen Mehrheit der Staatsrechtsexpertinnen und -experten vertreten.
+Aber natürlich ist es niemandem verwehrt, eine Verfassungsbestimmung eigenwillig auszulegen, um ein bestimmtes Ziel zu erreichen. Ich meine, wir stehen hier in diesem Rat für den Schutz der Verfassung und der Institutionen. Wir begehen einen heiklen Weg, wenn wir nun in diesem einen Fall mittels Einzelfalllegiferierung die geltende Verfassung unterlaufen und Präjudizien schaffen, weil wir keine Verfassungsgrundlage finden. Wir werden bei allen künftigen internationalen Abkommen mit ähnlichen Anträgen konfrontiert werden. Die Linke hat längst angekündigt, dass sie bei jedem Freihandelsabkommen die Nachhaltigkeitskriterien überprüfen und jedes Mal das Referendum ergreifen werde. Wieso sich aber nicht viel besser das Sammeln von fünfzigtausend Unterschriften ersparen und stattdessen mit einem kreativen Vorschlag das obligatorische Referendum einfordern?
+Es sollte in unserem Land keine Rechtsetzung aus einzelnem Anlass geben, nur weil uns der Ausgang einer Abstimmung eventuell nicht passen könnte. Die Frage des obligatorischen oder des fakultativen Referendums ist keine politische, sondern allein eine rechtliche, und zwar eine verfassungsrechtliche.
+Ich komme zum Schluss. Das obligatorische Referendum ist ein zentrales Element, das die Schweiz zusammenhält, Kollegin Moser und Kollege Jositsch haben es erläutert, das Volk und Stände einbindet, grossen und kleinen Kantonen die gleichen Rechte einräumt. Das ist wichtig für die Kohäsion der Schweiz. Ich bin überzeugt, dass wir alle in diesem Rat uns der Bedeutung der Rechte der Kantone und der Wichtigkeit des Ständemehrs bewusst sind. Sonst würden wir nicht in diesem Rat sitzen.
+Kritik am Ständemehr kommt immer wieder auf; das letzte Mal wurde sie von den Verlierern der Konzernverantwortungs-Initiative geäussert. Aber das Ständemehr ist in die Bundesverfassung geschrieben und wichtig für den Zusammenhalt und die Institutionen. Deshalb kann ich auch dem Argument "hundert Zürcher versus ein Urner", oder ähnlich, in dieser Frage nicht viel abgewinnen. Aber ebenso wichtig für die Kohäsion der Schweiz sind die Rechte des Volkes. Wenn das Parlament dem Volk seine verfassungsmässigen Rechte vorenthält, ist das pläbiszitärer Parlamentarismus. Das Schweizervolk und die Stände haben sich mit der Verfassung selbst ermächtigt. Das Volk holt sich die Rechte, die es sich wünscht, und wartet nicht ab, dass ihm eine gnädige Obrigkeit, abhängig von ihrer Laune, Rechte gibt oder entzieht.
+Ich bitte Sie also, gemäss der Bundesverfassung mit der Minderheit Ihrer Staatspolitischen Kommission und mit der Mehrheit der Aussenpolitischen Kommission zu stimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe in meinem Eintretensvotum am Montag ausgeführt, dass der eigentliche Elefant im Raum die dynamische Rechtsübernahme sei oder generell die Übernahme von fremdem Recht, die ziemlich automatisch erfolgt, je nach Fall. Und damit hängt eben auch namentlich die Unionsbürgerrichtlinie zusammen. An dieser habe ich meine Beispiele und meine Ausführungen und Bedenken auch aufgehängt; ich werde gleich darauf zurückkommen. 
+Ich möchte zuerst aber noch eine Vorbemerkung anbringen betreffend grosse o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich habe in meinem Eintretensvotum am Montag ausgeführt, dass der eigentliche Elefant im Raum die dynamische Rechtsübernahme sei oder generell die Übernahme von fremdem Recht, die ziemlich automatisch erfolgt, je nach Fall. Und damit hängt eben auch namentlich die Unionsbürgerrichtlinie zusammen. An dieser habe ich meine Beispiele und meine Ausführungen und Bedenken auch aufgehängt; ich werde gleich darauf zurückkommen. 
+Ich möchte zuerst aber noch eine Vorbemerkung anbringen betreffend grosse oder kleine Kantone und zum Votum des Kollegen Broulis - 7 Millionen gegen 2 Millionen. Ja, bitte, dann frage ich Sie, Herr Kollege, was haben denn um Himmelswillen die 7 Millionen von den 2 Millionen zu befürchten? Als hätte dieser Staat nicht schon andere Abstimmungen überlebt. Die Leute wissen sehr wohl um ihre Verantwortung und nehmen diese auch wahr.
+Manchmal beklagen wir uns über den "Röstigraben". In letzter Zeit haben ab und zu auch die Westschweizer Kantone die Deutschschweizer majorisiert. Auch wir überleben das. Auch unsere Schweiz überlebt das. Wir sollten das nicht übermässig hochhängen. Auch nicht das Argument mit der Hürde des qualifizierten Mehrs, als wäre das fast ein Verbrechen. Ich muss Ihnen sagen, jeder Feld-, Wald- und Wiesenverein kennt qualifizierte Mehrheiten, wenn es um wichtige Entscheidungen im Verein geht. Das ist doch etwas ganz Normales. Warum um Himmelswillen sollte man das in der Schweiz nicht haben? 
+Denn jetzt frage ich Sie etwas: Ich habe in diesen drei Tagen niemanden gehört, der gesagt hätte, diese Verträge seien nicht enorm wichtig. Alle betonen die Bedeutung dieser Vertragswerke. Sehen Sie das auch so? Trotzdem werden sie hier heruntergespielt, und man geht gar nicht darauf ein, was sie bewirken. 
+Die Kantone sind doch direkt tangiert. In ihre Hoheit wird ebenfalls eingegriffen, sei es über die Beihilferegelung, die Wasserrechte, die Zuwanderung oder was auch immer; die kommen dann im Stromabkommen. Das bringt dann auch wieder Mehrkosten für die Kantone. Die Kantone sind direkt tangiert, und trotzdem negieren wir das und stellen es als völlig weltfremd dar, wenn jetzt das Ständemehr gelten würde. Als so dramatisch erachte ich das nun wirklich nicht. 
+Und Frau Moser, was Sie gesagt haben, hat mich etwas irritiert. Sie haben von einer halben Schulklasse gesprochen, die pro Jahr eine Aufenthaltsberechtigung erhalten würde - das ist also nun wirklich irritierend, aber Sie können schon bei dieser Version bleiben. Ich weiss auch, woher sie kommt und wie sie zustande kommt. Tatsache ist: Als wir das Freizügigkeitsabkommen übernommen haben, hat der Bundesrat von maximal 8000 Leuten gesprochen, die in unser Land einwandern würden. Am Ende waren es 80 000 - also Faktor 10. Wenn Sie von einer halben Schulklasse ausgehen, wäre auch der Faktor 10 noch nicht schlimm, oder? Das räume ich ein. Aber schauen Sie einmal an, was diese Unionsbürgerrichtlinie gegenüber dem Freizügigkeitsabkommen bringt. Ich nenne nur ein paar Stichworte: voraussetzungsloses, bewilligungsfreies Aufenthaltsrecht bis drei Monate, auch für Familienangehörige; für Erwerbstätige und Familienangehörige einen Anspruch auf Sozialhilfe; der Aufenthalt für Stellensuchende wird nicht mehr auf sechs Monate befristet; es gibt auch Anspruch auf Sozialhilfe für Nichterwerbstätige; die angemessene Wohnungsgrösse ist keine Voraussetzung mehr; der Anspruch auf Erwerbstätigkeit gilt übrigens auch für Enkel und Verwandte in aufsteigender Linie; und dann wird der Anspruch auf Nachzug weiterer Familienangehöriger ebenfalls stipuliert. Und das ist erst die Hälfte der Auswirkungen.
+Wir sehen das ja an den Zahlen, die daraus resultieren. Der Bundesrat spricht in seiner Botschaft davon, dass nebst den 690 000 Personen, die sich neu unbefristet in der Schweiz niederlassen könnten, pro Jahr 50 000 bis 70 000 weitere dazukämen. Das sind doch schon realistischere Zahlen, auch wenn wir es mit heute vergleichen.
+Nun ziehe ich einfach die Parallele und verzichte darauf, die weiteren Auswirkungen aufzuzählen. Frau Friedli hat bereits auf das Daueraufenthaltsrecht nach fünf Jahren, ebenfalls mit Anspruch auf Sozialhilfe, verwiesen. Ich verweise noch auf das Beispiel des bekannten Falls, er war, glaube ich, aus dem Kanton St. Gallen, und es ging um einen Nordmazedonier. Das Bundesgericht hatte seinen Rekurs gegen den Entzug der Aufenthaltsbewilligung abgewiesen. Aber nach neuer UBRL könnte er selbstverständlich bleiben. Das ist ja nur einer von vielen Fällen. Sie wissen, diese Entscheide sind ein Massengeschäft bei den Schweizer Gerichten. Dann könnte man auch das Beispiel eines EU-Bürgers nennen, der eine Frau aus, sagen wir, dem Maghreb heiratet. Kinder und Frau können logischerweise in die Schweiz kommen. Aber der Anspruch auf Familiennachzug gilt auch für die Schwiegereltern und allfällige Stiefkinder aus dem Maghreb. Es gibt aus Deutschland genügend Beispiele. Es gibt das Beispiel eines Bürgers, der es geschafft hat, zwei Dutzend Kinder als die seinen anzuerkennen. Das wird ja nicht überprüft. Also hier sehen wir, welches Potenzial dahintersteckt. Darum habe ich mit den Zahlen, die Sie hier nennen, wirklich meine liebe Mühe.
+Das alles widerspricht Artikel 121a der Bundesverfassung. Und hier könnte man sagen: Wenn wir das ändern wollen und diesen Verträgen zustimmen, wäre das einzig Konsequente, gleichzeitig Artikel 121a der Bundesverfassung zu revidieren. So wollte es Herr Rieder, aber er hat nun den Antrag seiner Minderheit zurückgezogen. Ich fände das nach wie vor eigentlich den richtigen Weg. So bleibt uns noch die Frage: Referendum sui generis, ja oder nein? Apropos Beliebigkeit, Herr Jositsch: Wie oft hat man dieses Referendum sui generis ergriffen? 1918 beim Völkerbund, 1972 beim Freihandelsabkommen mit der Europäischen Gemeinschaft, 1992 beim EWR, und jetzt wäre das eigentlich das vierte Mal in 100 Jahren. Ich frage Sie hier drin allen Ernstes: Ist das Beliebigkeit? Die Antwort brauche ich ja nicht zu geben. 
+Mein Fazit lautet: Nach dieser Güterabwägung und dem Rückzug des Antrages der Minderheit Rieder werde ich für den Antrag der Mehrheit der Staatspolitischen Kommission unseres Rates und natürlich auch für die Verfassungsänderung stimmen, so wie sie uns Kollege Caroni anbietet. Bei einer Stichfrage werde ich aber natürlich den Antrag der Mehrheit der SPK-S auf das Referendum sui generis bevorzugen. Ich finde das angemessen. Es gibt beide Möglichkeiten, die Kantone mit einzubeziehen und das doppelte Mehr zu machen. Aber das Referendum sui generis ist sicher ebenso valabel wie das obligatorische. 
+In diesem Sinne bitte ich Sie letztlich um Zustimmung zum Antrag der Mehrheit der Staatspolitischen Kommission.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es wurde jetzt sehr emotional argumentiert. Ich möchte den Fokus wieder auf das richten, was eigentlich im Zentrum steht. Für mich stehen die Fragen im Zentrum, wie weit diese neuen EU-Verträge in unsere Verfassungsordnung eingreifen und welche Auswirkungen sie auf unsere Verfassung, auf unsere Verfassungsordnung haben. Dazu haben wir in der Staatspolitischen Kommission verschiedene Anhörungen durchgeführt. Ja, es gibt zwei unterschiedliche Haltungen. Die Mehrheitssprecherin und somit die Sprech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es wurde jetzt sehr emotional argumentiert. Ich möchte den Fokus wieder auf das richten, was eigentlich im Zentrum steht. Für mich stehen die Fragen im Zentrum, wie weit diese neuen EU-Verträge in unsere Verfassungsordnung eingreifen und welche Auswirkungen sie auf unsere Verfassung, auf unsere Verfassungsordnung haben. Dazu haben wir in der Staatspolitischen Kommission verschiedene Anhörungen durchgeführt. Ja, es gibt zwei unterschiedliche Haltungen. Die Mehrheitssprecherin und somit die Sprecherin der Sui-generis-Variante hat bereits etwas ausgeführt, was sich in der Kommission ergeben hat. Ich möchte den Fokus aber nochmals kurz auf dieses Element richten.
+Aus meiner Sicht - und nicht nur aus meiner Sicht, die angehörten Professoren Andreas Glaser und Paul Richli sowie Altbundesrichter Hansjörg Seiler kamen zum selben Schluss - haben diese Verträge grosse Auswirkungen auf die Verfassungsbestimmungen in unserem Land. Teilweise widersprechen sie diesen Bestimmungen. 
+Es wurde bereits über Artikel 121a gesprochen. Ich erlaube mir, speziell darauf zurückzukommen, weil, wie es Herr Kollege Jositsch jetzt sagen würde, dieser Artikel auf die Initiative einer Gruppierung zurückgeht, die mir ideologisch nahesteht. Im Jahr 2014 hat das Volk entschieden, dass die Schweiz die Zuwanderung von Ausländerinnen und Ausländern wieder eigenständig steuert und keine völkerrechtlichen Verträge abgeschlossen werden dürfen, die gegen diesen Artikel verstossen. 
+Kollegin Moser hat gesagt, es gehe um eine halbe Schulklasse - das ist aber nur die halbe Wahrheit. In den neuen Verträgen, gerade im Bereich der Personenfreizügigkeit, führen die Bestimmungen neben der klaren Ausweitung der Zuwanderung auch zu einer Ausweitung des erleichterten Familiennachzugs. Z. B. können die pflegebedürftigen Angehörigen in Zukunft leichter in die Schweiz gebracht werden. 
+Bis jetzt vollends unerwähnt geblieben sind die neuen Bestimmungen zur Unionsbürgerrichtlinie. Wir ermöglichen, dass Leute aus der Europäischen Union, die fünf Jahre in unserem Land sind, ein Daueraufenthaltsrecht erlangen - wir haben das gestern diskutiert. Es ist ein Daueraufenthaltsrecht. Wir nehmen somit eine komplette Neuerung vor, die, ich habe es gestern ausgeführt, überhaupt nicht mit Artikel 121a vereinbar ist. Wer einmal ein Daueraufenthaltsrecht in unserem Land hat, den werden wir nie mehr los, der wird immer bei uns sein. Der Bundesrat sagt ja selber, er erwarte, dass sich dann auch die Zahl der Sozialhilfebezügerinnen und Sozialhilfebezüger vergrössern werde. Auch Altbundesrichter Hansjörg Seiler kommt übrigens zu diesem Schluss; er sagt, dass gerade die Unionsbürgerrichtlinie mit Artikel 121a kollidieren werde. Das ist ja auch der Hintergrund, weshalb die Mehrheit der Staatspolitischen Kommission eine Initiative lanciert hat.
+Aber auch Professor Andreas Glaser sieht einen Konflikt mit Artikel 121a der Bundesverfassung. 
+Es ist aber nicht nur Artikel 121a, der problematisch ist. Mit der dynamischen Rechtsübernahme verändert sich auch die Stellung unseres Parlamentes - das haben wir heute Morgen diskutiert. Natürlich können wir formal weiterhin Ja oder Nein zur Übernahme eines EU-Rechtsakts sagen, aber wir können diesen Rechtsakt nicht mehr so gestalten wie ein schweizerisches Gesetz. Wir können nicht sagen: Diesen Artikel übernehmen wir, jenen ändern wir und einen dritten formulieren wir anders. Der Inhalt wird in der EU beschlossen. Die Schweiz kann übernehmen, oder sie kann nicht übernehmen, und wenn sie nicht übernimmt, so können Ausgleichsmassnahmen folgen. Bei der Beratung zum AIG gestern wurde bei verschiedenen Artikeln immer wieder gedroht, dass die EU es nicht akzeptieren werde, wenn wir die Änderung des AIG nicht kompatibel mit dem Freizügigkeitsabkommen umsetzen würden. Professor Glaser weist zudem darauf hin, dass damit auch das Initiativ- und das Antragsrecht unseres Parlamentes berührt werden. 
+Genau dasselbe Problem stellt sich auch bei den Volksrechten. Professor Paul Richli verweist hier auf Artikel 34 Absatz 2 der Bundesverfassung, auf die Garantie der freien Willensbildung und der unverfälschten Stimmabgabe. Natürlich kann das Schweizervolk weiterhin abstimmen, aber wie frei ist eine Entscheidfindung tatsächlich, wenn als Folge eines Neins Ausgleichsmassnahmen drohen? Das ist keine theoretische Frage, denn unsere direkte Demokratie besteht nicht darin, dass einfach noch irgendeine Abstimmung stattfindet. 
+Die vorliegenden Verträge haben grösste Auswirkungen auf unsere Institutionen. In einigen Bereichen widersprechen sie meines Erachtens und auch gemäss verschiedenen Staatsrechtlern der Verfassung oder ritzen diese. Es geht um Artikel 121a der Bundesverfassung, die eigenständige Steuerung der Zuwanderung; es geht um Artikel 34 und die freie Ausübung unserer politischen Rechte; es geht um die Rechtsetzungskompetenzen unseres Parlamentes; es geht um die Kompetenzen der Kantone; es geht um die Stellung unserer Gerichte. Wenn wir die Verfassungsordnung derart weitreichend verändern, dann, so bin ich der Meinung, sollten wir diesen Entscheid auch dem obligatorischen Referendum und namentlich dem Referendum sui generis unterstellen. Es wurde ausgeführt, insbesondere von Kollegin Gössi, warum dies so zentral ist. 
+Ich empfehle Ihnen, zuerst beide Varianten zu unterstützen, also auch die Variante mit der Initiative der SPK-S, und dann in der Stichfrage der Variante mit dem Referendum sui generis zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir kommen nun doch noch einmal zu einem zentralen Punkt dieser neuen Verträge, und zwar zu den Finanzen. Die EU will von uns nicht nur institutionelle Elemente wie zum Beispiel die dynamische Rechtsübernahme, mit diesem Paket sollen auch die finanziellen Beiträge der Schweiz verstetigt werden. Was bisher politisch immer wieder neu beurteilt werden konnte, soll künftig zu einem regelmässigen und institutionalisierten Zahlungsmechanismus werden. 
+Es handelt sich neu quasi um eine jährliche Zugang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir kommen nun doch noch einmal zu einem zentralen Punkt dieser neuen Verträge, und zwar zu den Finanzen. Die EU will von uns nicht nur institutionelle Elemente wie zum Beispiel die dynamische Rechtsübernahme, mit diesem Paket sollen auch die finanziellen Beiträge der Schweiz verstetigt werden. Was bisher politisch immer wieder neu beurteilt werden konnte, soll künftig zu einem regelmässigen und institutionalisierten Zahlungsmechanismus werden. 
+Es handelt sich neu quasi um eine jährliche Zugangsprämie zum EU-Binnenmarkt: Ab 2030 350 Millionen Franken pro Jahr, bis dahin in der Übergangsphase 130 Millionen Franken pro Jahr. Mit dem Bundesbeschluss 6 sollen wir für die Jahre 2030 bis 2036 einen Verpflichtungskredit von etwas über 2 Milliarden Franken für die Kohäsion bewilligen. Mit dem Bundesbeschluss 7 kommen 273 Millionen Franken für den Bereich Migration hinzu. Und mit dem Bundesbeschluss 8 sollen wir nochmals über eine Milliarde Franken für die zusätzlichen finanziellen Verpflichtungen in der Übergangsphase bewilligen. 
+Wir sprechen mit diesen drei Bundesbeschlüssen zusammen Verpflichtungskredite von mehr als 3,2 Milliarden Franken, oder anders gesagt 3200 Millionen Franken - natürlich über eine gewisse Zeitspanne. Das Entscheidende ist aber: Damit ist es ja noch nicht getan. Es kommen noch weitere Beiträge für einzelne Programme wie Horizon - über Erasmus Plus werden wir morgen noch sprechen -, die Gesundheit, die Lebensmittelsicherheit usw. hinzu. Gewisse Gelder haben wir schon gesprochen, andere werden noch folgen. 
+Es geht heute also um etwas Grundsätzliches, es geht um einen Systemwechsel. Bis heute konnte dieses Parlament jeden Kohäsionsbeitrag politisch neu beurteilen und auch allfällige Eckpfeiler aushandeln. Künftig wird die Zahlung selbst zum Bestandteil der vertraglichen Beziehungen mit der Europäischen Union.
+Die Schweiz hat selbstverständlich ein Interesse an einem stabilen und prosperierenden Europa. Wir haben auch ein Interesse an guten Beziehungen mit unseren Nachbarstaaten und einem funktionierenden europäischen Wirtschaftsraum. Aber daraus folgt für mich nicht, dass die Schweizer Steuerzahlerinnen und Steuerzahler dauerhaft für die Verringerung wirtschaftlicher und sozialer Unterschiede innerhalb der Europäischen Union mit Beiträgen in Milliardenhöhe aufkommen müssen. Die Schweiz ist nicht Mitglied der Europäischen Union, die Schweiz ist auch nicht Mitglied des EWR. Die Kohäsion innerhalb der EU ist deshalb in erster Linie Aufgabe der Europäischen Union und ihrer Mitgliedstaaten.
+Hinzu kommt für mich auch noch die finanzpolitische Situation in unserem Land. Noch vor Kurzem diskutierten wir hier im Parlament über Entlastungsmassnahmen. Wir diskutierten darüber, wo der Bund sparen muss, und wir haben fast eine Milliarde Franken gespart. Vor einigen Tagen diskutierten wir zudem über die Finanzierung der Armee. Wir suchen Gelder für unsere Sozialwerke für die Bürgerinnen und Bürger in unserem Land. All das soll in unserem Land nun über höhere Konsumsteuern von den Bürgerinnen und Bürgern bezahlt werden. Gleichzeitig verteilen wir 3,2 Milliarden Franken an die Länder der Europäischen Union. Und gleichzeitig schaffen wir mit diesem Vertragspaket eine neue langfristige Verpflichtung von Hunderten Millionen Franken pro Jahr gegenüber der Europäischen Union, denn das wird auch nach dem Jahr 2036 weitergehen.
+Zum Abschluss kurz noch ein paar Worte zum Konstrukt, über das wir heute Abend abstimmen: Wir beschliessen einen neuen regelmässigen Betrag ab 2030, und gleichzeitig bezahlen wir zusätzlich dafür, dass davor keine finanzielle Lücke entsteht. Zuerst bezahlen wir die Übergangszeit, danach bezahlen wir regelmässig weiter. Das zeigt besonders deutlich, dass wir hier nicht einfach über drei isolierte Verpflichtungskredite sprechen. Wir entscheiden über einen grundlegenden Systemwechsel in den finanziellen Beziehungen zwischen der Schweiz und der Europäischen Union.
+Die Schweiz ist nicht Mitglied der Europäischen Union, sie ist auch nicht Mitglied des Europäischen Wirtschaftsraumes, und sie ist weder der Kohäsionsfonds noch die Zahlstelle der Europäischen Union. Ich will keine Verstetigung dieser Zahlungen und keinen neuen dauerhaften finanziellen Mechanismus.
+Vor diesem Hintergrund lehnt meine Minderheit die Bundesbeschlüsse 6, 7 und 8 ab und bittet Sie, dies ebenfalls zu tun.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.[NB]Bundesbeschluss über den Verpflichtungskredit für den Bereich der Migration im Rahmen des Schweizer Beitrags zur Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU für die Jahre 2030-2036[GZ]
+7.[NB]Arrêté fédéral sur le crédit d'engagement relatif au domaine de la migration dans le cadre de la contribution de la Suisse visant à réduire les disparités économiques et sociales au sein l'UE pour les années 2030-2036[GZ]
+[VS][GZ]
+Antrag APK-S/Mehrheit FK-S[GZ]
+Eintreten
+[VS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.[NB]Bundesbeschluss über den Verpflichtungskredit für den Bereich der Migration im Rahmen des Schweizer Beitrags zur Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU für die Jahre 2030-2036[GZ]
+7.[NB]Arrêté fédéral sur le crédit d'engagement relatif au domaine de la migration dans le cadre de la contribution de la Suisse visant à réduire les disparités économiques et sociales au sein l'UE pour les années 2030-2036[GZ]
+[VS][GZ]
+Antrag APK-S/Mehrheit FK-S[GZ]
+Eintreten
+[VS]
+Antrag der Minderheit FK-S[GZ]
+(Friedli Esther, Rieder, Stark)[GZ]
+Nichteintreten
+[VS]
+Proposition CPE-E/majorité CdF-E[GZ]
+Entrer en matière
+[VS]
+Proposition de la minorité CdF-E[GZ]
+(Friedli Esther, Rieder, Stark)[GZ]
+Ne pas entrer en matière
+[VS]
+Präsident (Engler Stefan, Präsident): Wir stimmen über den Nichteintretensantrag der Minderheit Friedli Esther der FK-S ab.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie heute bereits erläutert, befasste sich unsere Kommission als drittes Hauptelement mit den drei Verpflichtungskrediten zur Finanzierung des Kohäsionsprogramms in den Jahren 2030 bis 2036. Bis 2030 leistet die Schweiz den bisherigen Beitrag. Zur Finanzierung im Zeitraum zwischen dem materiellen Abschluss der Verhandlungen im Jahre 2024 und dem Start der ersten Beitragsperiode 2030 beantragt der Bundesrat eine einmalige Verpflichtung.
+Konkret wird mit dem ersten der drei Verpflichtungskredite f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie heute bereits erläutert, befasste sich unsere Kommission als drittes Hauptelement mit den drei Verpflichtungskrediten zur Finanzierung des Kohäsionsprogramms in den Jahren 2030 bis 2036. Bis 2030 leistet die Schweiz den bisherigen Beitrag. Zur Finanzierung im Zeitraum zwischen dem materiellen Abschluss der Verhandlungen im Jahre 2024 und dem Start der ersten Beitragsperiode 2030 beantragt der Bundesrat eine einmalige Verpflichtung.
+Konkret wird mit dem ersten der drei Verpflichtungskredite für den Bereich der Kohäsion für die Jahre 2030 bis 2036 ein Verpflichtungskredit von 2005,08 Millionen Franken beantragt, mit dem zweiten für den Bereich der Migration weitere 273,42 Millionen Franken und für die erwähnte einmalige, zusätzliche finanzielle Verpflichtung nochmals 1013,7 Millionen Franken.
+Zur Erinnerung: Diese Mittel fliessen nicht ins EU-Budget, sondern werden direkt in den Partnerstaaten für gemeinsam vereinbarte Programme und Projekte eingesetzt. Alle Länder, die am Binnenmarkt teilnehmen, tragen zur Kohäsion bei, darunter auch Norwegen, Island und Liechtenstein. Pro Kopf zahlt Norwegen rund doppelt so viel wie die Schweiz, derzeit 80 Schweizerfranken pro Kopf und Jahr - für die Schweiz wären es 40 Franken pro Kopf und Jahr. Von den 350 Millionen Franken pro Jahr sollen 308 Millionen Franken im Bereich Kohäsion und 42 Millionen Franken im Bereich Migration eingesetzt werden.
+Unserer Kommission lag ein Mitbericht Ihrer Finanzkommission vor, die mit 9 zu 2 Stimmen bei 2 Enthaltungen Zustimmung empfahl. Unsere Kommission stimmte allen drei Verpflichtungskrediten mit jeweils 10 zu 2 Stimmen bei 1 Enthaltung zu. Ich ersuche Sie im Namen unserer Kommission ebenfalls um Zustimmung.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich komme Ihrem Wunsch, Herr Präsident, gerne nach und werde nur auf zwei der zwanzig Voten eingehen, nämlich auf diejenigen der beiden Minderheitssprecher. Es geht um ein paar Einzelheiten zum Votum von Frau Moser und dann noch um etwas Grundsätzliches zum Votum von Herrn Jositsch.
+Frau Moser, Sie haben zu Artikel 121a Absatz 4 nochmals auf die geringe Menge betroffener Personen hingewiesen. Ich betone noch einmal: Es geht in dieser Bestimmung um die Qualität. Man will keine Freizügigkeit ausse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich komme Ihrem Wunsch, Herr Präsident, gerne nach und werde nur auf zwei der zwanzig Voten eingehen, nämlich auf diejenigen der beiden Minderheitssprecher. Es geht um ein paar Einzelheiten zum Votum von Frau Moser und dann noch um etwas Grundsätzliches zum Votum von Herrn Jositsch.
+Frau Moser, Sie haben zu Artikel 121a Absatz 4 nochmals auf die geringe Menge betroffener Personen hingewiesen. Ich betone noch einmal: Es geht in dieser Bestimmung um die Qualität. Man will keine Freizügigkeit ausserhalb von Kontingenten einräumen. Sie haben gesagt, es handle sich nur um ein paar Kinder. Ich habe verschiedene Kategorien aufgezählt, die jetzt staatsvertraglich neu erfasst werden, und auf die Dynamik. Es geht also darüber hinaus. Sie haben gesagt, und das war nun definitiv falsch, alle Freihandelsabkommen würden nun neu diesem doppelten Mehr unterstellt werden müssen. Ich habe aufgezählt, wie die Freihandelspraxis bis hierhin war, und habe auch gezeigt, wie einfach es ist, verfassungskonform zu sein. Wenn man personelle Migration darin überhaupt irgendwie vorkommen lässt, dann muss man einfach einen Kontingenzvorbehalt reinschreiben, und unter diesem Titel waren Indien, Mercosur und das neue Abkommen mit China alle problemlos. 
+Dann komme ich zum zweitletzten Punkt. Sie haben gesagt, mit dieser Verfassungsbestimmung verlöre man an Abstimmungsfreiheit. Wenn man nämlich die Verträge wolle, dann müsste man da Ja sagen und gleichzeitig zu einer unliebsamen Verfassungsbestimmung Ja sagen. Aber ich sehe das Problem überhaupt nicht. Also, wenn Sie die Verträge wollen, und da steht drin, die werden genehmigt: Was können Sie denn dagegen haben, dass das in der Bundesverfassung steht? Das ist ja dann noch stärker, als wenn es nicht darin stünde.
+Mein letzter Punkt ist derjenige des Plebiszits. Natürlich kann man sagen, dass hier jetzt die Bundesverfassung für einen Einzelfall bemüht werde. Ich habe Ihnen gesagt, weshalb dies aus meiner und auch aus der Sicht der Mehrheit der Kommission verfassungsrechtlich geboten ist. Ich habe Ihnen aber auch die Beispiele genannt, wo andere politische Kreise, wie selbstverständlich sagen, hier brauchen wir jetzt eine freiwillig schärfere Normstufe. Ein Beispiel sahen wir letzte Woche beim Bankengesetz, auch mit der Idee, dass wir das Referendum dank einem Gesetz erlauben. Ein anderes Beispiel sahen wir bei der Beschaffung der Kampfflugzeuge. Bei der Beschaffung der Kampfflugzeuge, für die ich immer war, musste ich auch immer einem Gesetz zustimmen, obwohl ich in der Form eigentlich kein Gesetz wollte. Ich glaube, hier ist das auch zu akzeptieren, wenn man einmal politisch auf der anderen Seite steht. Dies zu Ihnen als Minderheitssprecherin. 
+Bei Herrn Jositsch muss ich nur nach Herrn Fässler auch noch etwas historisch richtigstellen. Sie haben ja gesagt, jetzt, wenn es um die neuen Freizügigkeitsabkommen gehe, würden wir bei diesem Absatz 4 so streng tun. Aber damals, bei der inländischen Umsetzung, hätte das niemanden interessiert und mich sicher auch nicht. Das hätten wir sicher alle ganz locker genommen, jetzt würden wir aber auf eine willkürliche Art die Bundesverfassung so streng verstehen. Das stimmt nicht. Es gab damals Leute, die sich gegen diesen Inländervorrang light gewehrt haben. Sie haben zwar gesagt, der geschätzte Kollege Philipp Müller würde mir "ideologisch nahestehen", aber vielleicht können Sie sich aus eigener praktischer Erfahrung vorstellen, dass man nicht immer einig geht mit allem, was Parteikollegen so sagen. Ich habe damals gesagt, man bräuchte, wenn man das wolle, eine Verfassungsanpassung im Rahmen der Rasa-Initiative. Es gab diese Initiative. Ich war bei einem Gegenvorschlag dabei, weil ich gesagt habe, das müsse man eben auf dieser Verfassungsstufe korrekt durch Volk und Stände korrigieren lassen. Ich habe nachgeschaut, wer alles das damals fand und wer sich dafür einsetzte. Es waren nicht sehr viele. Aber ein Bericht vom 5. Dezember 2017 in einer Zeitung, die heute zur CH-Media-Gruppe gehört, zählt die wackeren Kämpen auf, die sich damals für eine Verfassungsänderung eingesetzt haben, damit man korrekt ist. Der Artikel sagt, im Ständerat gehörten zu den treibenden Kräften hinter einem solchen Verfassungsvorschlag erstens Hans Stöckli, zweitens, Sie werden nicht überrascht sein, meine Wenigkeit, und drittens Daniel Jositsch. Wir haben also damals die Bundesverfassung eng und streng verstanden und haben uns dafür eingesetzt, das auf der richtigen Stufe, auf der Verfassungsstufe zu korrigieren. Leider ist es uns nicht gelungen. Aber dort konnte man noch damit leben. Denn es gab das Argument, dass die völkerrechtlichen Verträge eine Light-Umsetzung erzwingen. Das wurde später in einer Abstimmung über die Begrenzungs-Initiative, auch Kündigungs-Initiative genannt, vom Souverän indirekt auch bestätigt. Er hat gesagt, ihr habt die Masseneinwanderungs-Initiative light umgesetzt, aber ihr müsst das Freizügigkeitsabkommen nicht kündigen, ihr müsst keine Änderung bei der Freizügigkeit machen. Aber in Bezug auf Absatz 4 ist es noch viel wichtiger, dass wir die Bundesverfassung ernst nehmen. Denn der Souverän von damals wollte keine zusätzlichen Verträge, damit es nicht zu zusätzlichen Konflikten kommt. Und daher bleibe ich wie damals streng. Und wenn Sie, Herr Jositsch, wie damals mit mir zusammen hier streng sein wollen, dann lade ich Sie herzlich ein, mit der Mehrheit zu stimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mühlemann Benjamin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Föderalismus ist keine organisatorische Besonderheit unseres Landes, sondern Teil seines Fundaments. Die Schweiz ist nicht einfach ein Staat mit 26 Verwaltungsregionen, sondern ein Bundesstaat, getragen von seinen Bürgerinnen und Bürgern und von seinen Kantonen. In dieser grossen Debatte geht es genau um dieses Zusammenspiel. Ich möchte Ihnen an diesem Punkt empfehlen, es so einzurichten, dass Volk und Stände über dieses Paket befinden können. Welchen verfassungsrechtlichen Weg wir einschlag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Föderalismus ist keine organisatorische Besonderheit unseres Landes, sondern Teil seines Fundaments. Die Schweiz ist nicht einfach ein Staat mit 26 Verwaltungsregionen, sondern ein Bundesstaat, getragen von seinen Bürgerinnen und Bürgern und von seinen Kantonen. In dieser grossen Debatte geht es genau um dieses Zusammenspiel. Ich möchte Ihnen an diesem Punkt empfehlen, es so einzurichten, dass Volk und Stände über dieses Paket befinden können. Welchen verfassungsrechtlichen Weg wir einschlagen, damit der Souverän diese Möglichkeit hat, ist ein Stück weit Geschmackssache. Ich erlaube mir diesen Begriff, auch wenn das die Staatsrechtler geschmacklos finden. Es gibt jedenfalls für beide Wege sehr gute Argumente, und zulässig scheinen diese Wege auch zu sein.
+Die Lösung der SPK-S über eine Verfassungsbestimmung hat für mich den Vorteil einer besonderen Klarheit. Wenn man der Auffassung ist, dass die geltende Verfassungsordnung materiell berührt ist, dann muss man das offen klarstellen und dafür auch formell eine Verfassungsgrundlage schaffen. Das hat jetzt wirklich nichts mit einer Trickserei zu tun, das ist ein ganz normaler politischer Prozess.
+Auch ein obligatorisches Referendum sui generis lässt sich staatspolitisch und verfassungsrechtlich herleiten, Kollegin Gössi hat es ausgeführt. Die Argumentation ist vielleicht anspruchsvoller, aber sie ist nicht aus der Luft gegriffen, wie man das immer wieder hört, wie das immer wieder behauptet wird. Ja, der Bundesrat hat am Montag in der Eintretensdebatte erneut seine Schlussfolgerung dargelegt, die Voraussetzungen seien bei diesem Punkt nicht erfüllt. Die grundsätzliche Möglichkeit eines obligatorischen Referendums sui generis hat der Bundesrat aber nie bestritten. Im Gegenteil, er selber hat diese Tür immer offen gelassen. Noch 2025 hielt er ausdrücklich fest, dass diese Frage vom Parlament abschliessend zu beurteilen, zu entscheiden sei. Auch grundsätzlich anerkennt der Bundesrat, dass ein solches Referendum bei Staatsverträgen von Verfassungsrang in Betracht kommen kann. Die Frage ist also nicht, ob es diese Tür gibt, sondern ob sie hier geöffnet werden soll. Welcher der beiden Wege am Schluss gewählt wird, ist für meine Überlegungen nicht der entscheidende Punkt. Entscheidend ist für mich etwas anderes: Wenn die Schweiz hier eine institutionelle Weichenstellung für Jahrzehnte vornimmt, dann soll sie möglichst breit legitimiert sein.
+Nun möchte ich noch einen kurzen Blick zurück machen. Am Montag haben wir in der Eintretensdebatte ja bereits die eine oder andere staatsrechtliche, professorale Vorlesung gehört. Ich erlaube mir nun auch noch ein kurzes historisches Seminar. Denn gerade der Blick ins Jahr 1848 hilft, einen Unterschied zu verstehen, den wir in dieser Debatte immer wieder sauber auseinanderhalten sollten: den Unterschied zwischen demokratischer und föderalistischer Legitimation. Das wird immer wieder vermischt, und das stört mich. Damals wurde eine Grundfrage beantwortet, die bis heute für unser Staatswesen prägend ist: Wie verbindet man eine gemeinsame staatliche Ordnung mit starken, eigenständigen Kantonen?
+Der Ständeratspräsident hat die Antwort heute Morgen mit seinem Gottfried-Keller-Zitat bereits geliefert, dieses sagt eigentlich das Wesentliche aus. 1848 gab es eine sogenannte Verfassungsrevisionskommission. Diese diskutierte ausdrücklich Modelle, bei denen grössere Kantone stärker und kleinere Kantone schwächer gewichtet worden wären. Sie verwarf das bewusst mit dem Grundgedanken unseres Staatswesens: Wenn Kantone Gliedstaaten des Bundes sind, dann sind sie als Kantone grundsätzlich gleich; nicht gleich gross, nicht gleich bevölkerungsreich, nicht gleich wirtschaftsstark, aber gleich in ihrer staatlichen Stellung.
+Diesen Unterschied leben wir bis heute, insbesondere in diesem Saal. Im Kanton Glarus sind wir gut 42 000 Einwohnerinnen und Einwohner. Der Kanton Zürich hat weit über eine Million. Wenn nun politische Legitimation einzig darin bestünde, Einwohnerzahlen gegeneinander aufzurechnen, dann müsste man sich tatsächlich fragen: Was tun wir denn hier in diesem Saal? Dann bräuchte es unseren Rat nämlich nicht. Aber genau das sah man 1848 anders. Die Verfassungsrevisionskommission sprach vom national-kantonalen oder vom gemischten System. Die Kommission verwendete für das Verhältnis der beiden Elemente ein starkes Bild. Jedes sollte sein eigenes Organ haben, jedes einen Wall gegen die Übergriffe des anderen.
+Ich gebe zu, das ist die Sprache von vor fast 180 Jahren, aber der Gedanke ist hochaktuell. Unser Bundesstaat lebt nicht nur von einer gesamtschweizerischen Mehrheit, er lebt auch von seinen Kantonen, die wir zusammenhalten müssen. Diese Kantone haben übrigens keine konsolidierte Stellungnahme abgegeben, wie das vorher kolportiert wurde. 10 sind für das obligatorische Referendum, 15 sind dagegen; aber die Konferenz der Kantonsregierungen gibt erst bei einem qualifizierten Mehr von 18 Kantonen eine Stellungnahme ab, das möchte ich hier zur Präzisierung festhalten. 
+Unser Bundesstaat lebt vom Zusammenwirken dieser Stände, und das nennt man Föderalismus. Genau deshalb habe ich wirklich grösste Mühe mit der Argumentation, dass das Ständemehr statt 50 Prozent, plötzlich 55 Prozent Zustimmung nötig mache. Solche Zahlen werden ja immer wieder herumgeboten. Natürlich kann das Ständemehr dazu führen, dass ein knappes Volksmehr alleine nicht genügt. Genau darin liegt ja sein inhärenter Sinn, aber eine 55-Prozent-Hürde gibt es in unserer Verfassung schlicht und einfach nicht. Beim Volksmehr zählen die Bürgerinnen und Bürger, beim Ständemehr zählen die Kantone, und deshalb geht es hier nicht um mehr oder um weniger Demokratie, es geht um die zusätzliche föderalistische Legitimation. 
+Die Verfassungsrevisionskommission brachte das 1848 in einem Satz auf den Punkt: Die Zustimmung der Mehrheit der Stände sei, ich zitiere "eine hinreichende Garantie für die kantonale Souveränität". Das Bemerkenswerte ist - an dieser Stelle muss der kleine Herr Mühlemann den grossen Herrn Jositsch, nein, Entschuldigung, muss der Herr Mühlemann aus dem kleinen Kanton Glarus, den Herrn Jositsch aus dem grossen Kanton Zürich, wirklich korrigieren, ich erlaube mir das (teilweise Heiterkeit) -, dass diese Garantie von Anfang an nicht nur für die kleinen Kantone gedacht war. Das Ständemehr schützt nicht Glarus vor Zürich oder Uri vor der Waadt, es schützt jeden einzelnen Kanton in seiner eigenen eigenständigen Stellung als Gliedstaat, also durchaus auch einen grossen Kanton vor einer gesamtschweizerischen Mehrheit, die seine kantonalen Interessen übergeht. Das ist der Massstab, und damit komme ich auf unser heutiges Geschäft zurück. 
+Was ich hier ausdrücklich festhalten will: Das Ganze ist keine Stellvertreterdebatte über ein Ja oder über ein Nein zu den Verträgen. Den Befürwortern des Ständemehrs wird ja immer wieder unterstellt, sie wollten damit einfach irgendwelche Hürden erhöhen, weil sie die Verträge ohnehin ablehnten. Eine solche Argumentation haben wir auch in diesem Saal sinngemäss gehört. Ich finde das wirklich völlig unangebracht. Denn genauso könnte man umgekehrt den Gegnern des Ständemehrs unterstellen, sie wollten nur darauf verzichten, um dem Paket den Weg zu ebnen. 
+Ich halte beides für falsch; beides wird jenen nicht gerecht, die sich ernsthaft mit der staatspolitischen Dimension dieser Vorlage auseinandersetzen. Persönlich kann ich mir Stand heute auch vorstellen, diesem Paket in einer Gesamtabwägung, je nachdem, was am Schluss herauskommt, zuzustimmen. Denn ich sehe die Bedeutung stabiler Beziehungen zur EU, ich sehe die wirtschaftlichen Interessen unseres Landes, und ich sehe die grossen Vorteile des bilateralen Wegs, insbesondere der Personenfreizügigkeit. Und gerade weil ich diese Vorteile sehe, nehme ich auch die Aussagen der überzeugten Befürworterinnen und Befürworter ernst, wenn sie diesem Paket eine ausserordentliche strategische Tragweite beimessen. Kollegin Graf sprach am Montag ausdrücklich vom wichtigsten strategischen Entscheid für die nächsten Jahrzehnte, für die nächsten Generationen, Kollege Juillard sagte, "c'est une question stratégique pour l'avenir de notre pays", und Kollegin Moser sprach von einem elementaren strategischen Interesse. Ich nehme diese Aussagen ernst, einfach mit dem Hinweis, dass man nicht auf der einen Seite von einem fundamentalen strategischen Entscheid für Generationen sprechen und auf der anderen Seite so tun kann, als sei seine föderalistische Legitimation Nebensache. 
+Wer von der Qualität dieses Pakets überzeugt ist, der muss vor dem Ausmehren der Kantone keine Angst haben. Ich behaupte sogar, eine breitere Legitimation kann diesem Paket helfen. Wir wissen aus der Politikwissenschaft, dass Redlichkeit im Verfahren, dass breite Einbindung und nachvollziehbare Legitimation die Akzeptanz von politischen Entscheiden fördern kann, gerade bei umstrittenen Fragen, gerade bei identitätsnahen Fragen. Das bedeutet selbstverständlich nicht, dass ein bestimmtes Verfahren automatisch ein bestimmtes Abstimmungsergebnis produziert. Politik ist nie reine Statistik, nie reine Mathematik. Politik ist nicht Excel. Es bedeutet hingegen, dass das Verfahren für das Vertrauen, für die Legitimität und für die Akzeptanz eine Rolle spielen kann. Gerade weil wir genau das in diesem Land zelebrieren, haben wir diese starke gesellschaftliche Kohäsion in diesem Land. 
+Ich erlebe das übrigens in vielen Gesprächen: Es gibt Menschen, die diesem Paket inhaltlich kritisch bis offen gegenüberstehen, sie wollen aber die Gewissheit, dass bei einer solchen institutionellen Weichenstellung nicht nur die gesamtschweizerische Mehrheit zustimmt, sondern auch die Kantone einverstanden sind. Bei einem Teil dieser Menschen kann das Skepsis abbauen und Vertrauen schaffen.
+Die Befragung von Volk und Ständen ist somit kein Risiko, sondern eine Chance für die Akzeptanz. Wenn man das Paket für einen strategischen Asset für Generationen hält, sollte man eine möglichst breite Legitimation nicht fürchten, sondern darin im Gegenteil Stärke sehen. Wer das ignoriert, riskiert nämlich einen Boomerang, man hätte dann aus lauter Angst vor einer zusätzlichen Hürde am Ende gleich selber eine solche Hürde aufgestellt.
+Nun will die SPK mit der angestrebten Verfassungsnorm die offenen Fragen rund um Artikel 121a klären. Für mich erschöpft sich die Frage nicht bei diesem Artikel 121a. Wir sollten uns nämlich nicht nur fragen, ob irgendein einzelner Satz eines Vertrages mit einem einzelnen Satz in der Verfassung kollidiert. Wir sollten auch fragen, was dieses Paket materiell an der Art und Weise, wie in unserem Land Recht entsteht und wie politische Entscheide zustande kommen, verändert. Unsere Verfassung weist Parlament und Kantonen eine klare Rolle zu. Die Mitwirkung der Kantone bei wichtigen Erlassen und bei wichtigen völkerrechtlichen Verträgen ist Teil unseres staatlichen Bauplans, das gehört zur Architektur der schweizerischen Politik, das wurde auch heute Morgen intensiv diskutiert. Klar, jetzt werden mir einzelne Kolleginnen und Kollegen zu Recht entgegnen, dynamische Rechtsübernahme sei für die Schweiz überhaupt nichts Neues - das stimmt. Der Unterschied liegt für mich aber nicht darin, dass diese Instrumente - dynamische Rechtsübernahme, einheitliche Auslegung, Streitbeilegung - plötzlich neu wären, der Unterschied liegt in ihrer dauerhaften institutionellen Verankerung im zentralen Binnenmarktabkommen. Genau weil diese Mechanismen auch kantonale Zuständigkeiten und Interessen betreffen können, werden nun eigens zusätzliche Mitwirkungsmechanismen geschaffen. Der entscheidende Punkt ist hier für mich, dass die schweizerischen Institutionen zwar nicht verschwinden, dass sich aber der Rahmen verändert, in dem sie künftig entscheiden. Die Schweiz kann sich beim sogenannten Decision Shaping einbringen - ja, das ist wichtig -, aber der EU-Rechtsakt entsteht im Rechtsetzungsverfahren der Europäischen Union, erst danach entscheidet die Schweiz nach ihren eigenen verfassungsmässigen Verfahren über eine Übernahme. Gerade mit Blick auf die Kantone, und damit bin ich wieder beim Föderalismus, ist dieser Unterschied alles andere als theoretisch. Die Kantone sind ja nicht bloss Zuschauer dieser institutionellen Ordnung, sie vollziehen wesentliche Teile davon, und die Kantone tragen ganz konkrete Folgen.
+Nehmen wir zum Beispiel die Personenfreizügigkeit. Kantonale Migrations- und Arbeitsmarktbehörden vollziehen zentrale Teile dieses Abkommens. Es geht um Aufenthalt, Zulassung, Arbeitsmarktfragen, grenzüberschreitende Dienstleistungen. Die Auswirkungen reichen noch weiter, der Regierungsrat meines Heimatkantons hat in seiner Vernehmlassungsstellungnahme ausdrücklich auf mögliche Folgen für Sozialhilfe, Integration, für Schulen, Langzeitpflege, Pflegerestkosten verwiesen, also auf klassische kantonale Aufgaben. Oder nehmen wir den Strombereich, obwohl, ich weiss es, dieser Teil erst später hier in den Rat kommt. Für einen Wasserkraftkanton wie Glarus kann man es besonders anschaulich zeigen, da geht es um Konzessionsvergaben, Konzessionsinhalte, Wasserzinsen, Heimfall, öffentliches Eigentum an Wasserkraft- und Versorgungsunternehmen etc. Der Regierungsrat meines Heimatkantons Glarus bezeichnet die dauerhafte Wahrung der kantonalen Hoheit in diesen Bereichen ausdrücklich als zentral.
+Fazit: Dieses Paket wird kantonale Zuständigkeiten, konkrete Vollzugsaufgaben und politische Handlungsspielräume im Migrationsbereich, Arbeitsmarktbereich, Sozialbereich, Energiebereich erheblich beeinflussen; die Mitwirkung der Kantone ist wirklich nichts Theoretisches.
+Ich war bis vor einer Weile selbst Regierungsrat und weiss nur zu gut, was es bedeutet, wenn beim Bund neue Vorgaben beschlossen werden, die dann in den Kantonen vollzogen werden müssen. Zwischen einer institutionellen Regelung hier in Bern und ihrer konkreten Umsetzung in einem Kanton liegen manchmal Welten, das muss man leider so sagen. Wenn nun die Rechtsentwicklung vermehrt in einem vorgelagerten europäischen Prozess stattfindet, dann ist entscheidend, wie die Kantone darauf Einfluss nehmen können. Gerade die Tatsache, dass dafür neue Mechanismen geschaffen werden müssen, zeigt doch ganz offensichtlich, dass sich hier etwas im institutionellen Gefüge verschiebt, dass die Architektur eine andere wird, und genau deshalb hat das für mich Verfassungsrang.
+Selbstverständlich bin auch ich als Mitglied dieses Rates an keine Weisung meiner Kantonsregierung gebunden, das gehört zum freien Mandat, aber wenn jetzt über die föderalistische Legitimation gesprochen wird, dann kann ich die klar geäusserte Haltung des Kantons, den ich hier vertrete, nicht einfach ausblenden, das wäre wirklich merkwürdig. Regierungsrat Glarner hat sich ausdrücklich und gut begründet für ein obligatorisches Referendum ausgesprochen. Das Paket Schweiz-EU bringt gewichtige Veränderungen: eine dauerhafte institutionelle Anbindung an künftige EU-Rechtsentwicklungen, einen veränderten Rahmen für die Rechtsetzung, neue Mechanismen und eine konkrete Betroffenheit kantonaler Zuständigkeiten. In ihrer Summe sind diese Veränderungen für mich gewichtig genug, dass dazu neben dem Volk auch die Stände befragt werden müssen, nicht als zusätzliche Hürde, sondern damit diese institutionelle Ordnung, wenn sie angenommen wird, auf dem breiten Fundament steht, das unseren Bundesstaat seit 1848 trägt.
 </t>
   </si>
 </sst>
@@ -3013,8 +3391,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I119" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I137" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I137"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -6386,27 +6764,27 @@
         <v>11</v>
       </c>
       <c r="D108" t="s">
-        <v>211</v>
+        <v>413</v>
       </c>
       <c r="E108" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F108" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I108" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B109" t="s">
         <v>381</v>
@@ -6415,304 +6793,826 @@
         <v>11</v>
       </c>
       <c r="D109" t="s">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="E109" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="F109" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G109" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I109" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B110" t="s">
         <v>381</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D110" t="s">
-        <v>304</v>
-      </c>
-      <c r="E110"/>
+        <v>134</v>
+      </c>
+      <c r="E110" t="s">
+        <v>47</v>
+      </c>
       <c r="F110" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="G110" t="s">
         <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I110" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B111" t="s">
         <v>381</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D111" t="s">
-        <v>304</v>
-      </c>
-      <c r="E111"/>
+        <v>423</v>
+      </c>
+      <c r="E111" t="s">
+        <v>40</v>
+      </c>
       <c r="F111" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="G111" t="s">
         <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="I111" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B112" t="s">
         <v>381</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D112" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E112" t="s">
         <v>13</v>
       </c>
       <c r="F112" t="s">
-        <v>348</v>
+        <v>48</v>
       </c>
       <c r="G112" t="s">
         <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I112" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B113" t="s">
         <v>381</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>288</v>
+        <v>185</v>
       </c>
       <c r="E113" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F113" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I113" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B114" t="s">
         <v>381</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>288</v>
+        <v>434</v>
       </c>
       <c r="E114" t="s">
         <v>13</v>
       </c>
       <c r="F114" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G114" t="s">
         <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I114" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B115" t="s">
         <v>381</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D115" t="s">
-        <v>355</v>
+        <v>438</v>
       </c>
       <c r="E115" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="F115" t="s">
-        <v>356</v>
+        <v>246</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="I115" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B116" t="s">
         <v>381</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>304</v>
-      </c>
-      <c r="E116"/>
+        <v>442</v>
+      </c>
+      <c r="E116" t="s">
+        <v>124</v>
+      </c>
       <c r="F116" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="G116" t="s">
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="I116" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B117" t="s">
         <v>381</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="E117" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F117" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="I117" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B118" t="s">
         <v>381</v>
       </c>
       <c r="C118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D118" t="s">
-        <v>304</v>
-      </c>
-      <c r="E118"/>
+        <v>413</v>
+      </c>
+      <c r="E118" t="s">
+        <v>20</v>
+      </c>
       <c r="F118" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="I118" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B119" t="s">
         <v>381</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D119" t="s">
+        <v>211</v>
+      </c>
+      <c r="E119" t="s">
+        <v>124</v>
+      </c>
+      <c r="F119" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119" t="s">
+        <v>30</v>
+      </c>
+      <c r="H119" t="s">
+        <v>452</v>
+      </c>
+      <c r="I119" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>453</v>
+      </c>
+      <c r="B120" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" t="s">
+        <v>211</v>
+      </c>
+      <c r="E120" t="s">
+        <v>124</v>
+      </c>
+      <c r="F120" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" t="s">
+        <v>30</v>
+      </c>
+      <c r="H120" t="s">
+        <v>454</v>
+      </c>
+      <c r="I120" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>456</v>
+      </c>
+      <c r="B121" t="s">
+        <v>381</v>
+      </c>
+      <c r="C121" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" t="s">
+        <v>304</v>
+      </c>
+      <c r="E121"/>
+      <c r="F121" t="s">
+        <v>101</v>
+      </c>
+      <c r="G121" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" t="s">
+        <v>457</v>
+      </c>
+      <c r="I121" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>459</v>
+      </c>
+      <c r="B122" t="s">
+        <v>381</v>
+      </c>
+      <c r="C122" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" t="s">
+        <v>304</v>
+      </c>
+      <c r="E122"/>
+      <c r="F122" t="s">
+        <v>101</v>
+      </c>
+      <c r="G122" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" t="s">
+        <v>460</v>
+      </c>
+      <c r="I122" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>462</v>
+      </c>
+      <c r="B123" t="s">
+        <v>381</v>
+      </c>
+      <c r="C123" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" t="s">
+        <v>463</v>
+      </c>
+      <c r="E123" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" t="s">
+        <v>348</v>
+      </c>
+      <c r="G123" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" t="s">
+        <v>464</v>
+      </c>
+      <c r="I123" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>466</v>
+      </c>
+      <c r="B124" t="s">
+        <v>381</v>
+      </c>
+      <c r="C124" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" t="s">
+        <v>288</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" t="s">
+        <v>71</v>
+      </c>
+      <c r="G124" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" t="s">
+        <v>467</v>
+      </c>
+      <c r="I124" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>469</v>
+      </c>
+      <c r="B125" t="s">
+        <v>381</v>
+      </c>
+      <c r="C125" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" t="s">
+        <v>288</v>
+      </c>
+      <c r="E125" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" t="s">
+        <v>71</v>
+      </c>
+      <c r="G125" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" t="s">
+        <v>470</v>
+      </c>
+      <c r="I125" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>472</v>
+      </c>
+      <c r="B126" t="s">
+        <v>381</v>
+      </c>
+      <c r="C126" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" t="s">
+        <v>355</v>
+      </c>
+      <c r="E126" t="s">
+        <v>116</v>
+      </c>
+      <c r="F126" t="s">
+        <v>356</v>
+      </c>
+      <c r="G126" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" t="s">
+        <v>473</v>
+      </c>
+      <c r="I126" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>475</v>
+      </c>
+      <c r="B127" t="s">
+        <v>381</v>
+      </c>
+      <c r="C127" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" t="s">
+        <v>304</v>
+      </c>
+      <c r="E127"/>
+      <c r="F127" t="s">
+        <v>101</v>
+      </c>
+      <c r="G127" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" t="s">
+        <v>476</v>
+      </c>
+      <c r="I127" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>478</v>
+      </c>
+      <c r="B128" t="s">
+        <v>381</v>
+      </c>
+      <c r="C128" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" t="s">
+        <v>250</v>
+      </c>
+      <c r="E128" t="s">
+        <v>124</v>
+      </c>
+      <c r="F128" t="s">
+        <v>48</v>
+      </c>
+      <c r="G128" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" t="s">
+        <v>479</v>
+      </c>
+      <c r="I128" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>481</v>
+      </c>
+      <c r="B129" t="s">
+        <v>381</v>
+      </c>
+      <c r="C129" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" t="s">
+        <v>304</v>
+      </c>
+      <c r="E129"/>
+      <c r="F129" t="s">
+        <v>101</v>
+      </c>
+      <c r="G129" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>482</v>
+      </c>
+      <c r="I129" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>484</v>
+      </c>
+      <c r="B130" t="s">
+        <v>381</v>
+      </c>
+      <c r="C130" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" t="s">
         <v>245</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E130" t="s">
         <v>20</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F130" t="s">
         <v>246</v>
       </c>
-      <c r="G119" t="s">
-        <v>15</v>
-      </c>
-      <c r="H119" t="s">
-        <v>446</v>
-      </c>
-      <c r="I119" t="s">
-        <v>447</v>
+      <c r="G130" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" t="s">
+        <v>485</v>
+      </c>
+      <c r="I130" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>487</v>
+      </c>
+      <c r="B131" t="s">
+        <v>381</v>
+      </c>
+      <c r="C131" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" t="s">
+        <v>296</v>
+      </c>
+      <c r="E131" t="s">
+        <v>47</v>
+      </c>
+      <c r="F131" t="s">
+        <v>297</v>
+      </c>
+      <c r="G131" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" t="s">
+        <v>488</v>
+      </c>
+      <c r="I131" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>490</v>
+      </c>
+      <c r="B132" t="s">
+        <v>381</v>
+      </c>
+      <c r="C132" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" t="s">
+        <v>160</v>
+      </c>
+      <c r="E132" t="s">
+        <v>47</v>
+      </c>
+      <c r="F132" t="s">
+        <v>161</v>
+      </c>
+      <c r="G132" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" t="s">
+        <v>491</v>
+      </c>
+      <c r="I132" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>493</v>
+      </c>
+      <c r="B133" t="s">
+        <v>381</v>
+      </c>
+      <c r="C133" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" t="s">
+        <v>160</v>
+      </c>
+      <c r="E133" t="s">
+        <v>47</v>
+      </c>
+      <c r="F133" t="s">
+        <v>161</v>
+      </c>
+      <c r="G133" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" t="s">
+        <v>494</v>
+      </c>
+      <c r="I133" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>496</v>
+      </c>
+      <c r="B134" t="s">
+        <v>381</v>
+      </c>
+      <c r="C134" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" t="s">
+        <v>60</v>
+      </c>
+      <c r="E134" t="s">
+        <v>20</v>
+      </c>
+      <c r="F134" t="s">
+        <v>61</v>
+      </c>
+      <c r="G134" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" t="s">
+        <v>497</v>
+      </c>
+      <c r="I134" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>499</v>
+      </c>
+      <c r="B135" t="s">
+        <v>381</v>
+      </c>
+      <c r="C135" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" t="s">
+        <v>463</v>
+      </c>
+      <c r="E135" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" t="s">
+        <v>348</v>
+      </c>
+      <c r="G135" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" t="s">
+        <v>500</v>
+      </c>
+      <c r="I135" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>502</v>
+      </c>
+      <c r="B136" t="s">
+        <v>381</v>
+      </c>
+      <c r="C136" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" t="s">
+        <v>355</v>
+      </c>
+      <c r="E136" t="s">
+        <v>116</v>
+      </c>
+      <c r="F136" t="s">
+        <v>356</v>
+      </c>
+      <c r="G136" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" t="s">
+        <v>503</v>
+      </c>
+      <c r="I136" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>505</v>
+      </c>
+      <c r="B137" t="s">
+        <v>381</v>
+      </c>
+      <c r="C137" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" t="s">
+        <v>506</v>
+      </c>
+      <c r="E137" t="s">
+        <v>116</v>
+      </c>
+      <c r="F137" t="s">
+        <v>124</v>
+      </c>
+      <c r="G137" t="s">
+        <v>30</v>
+      </c>
+      <c r="H137" t="s">
+        <v>507</v>
+      </c>
+      <c r="I137" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="604">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -798,8 +798,8 @@
   </si>
   <si>
     <t xml:space="preserve">Die Mehrheit der Kommission beantragt, die vorliegenden Motionen abzuschreiben. Wir folgen mehrheitlich der Argumentation des Bundesrates, wonach die Anliegen der Motionen durch entsprechende Praxisänderungen bereits weitgehend umgesetzt wurden.
-Konkret heisst das: Seit Anfang 2025 wird der Schutzstatus S beendet, wenn eine Person länger als zwei Monate abwesend ist. Bei einer Rückkehr wird das Schutzverfahren, inklusive möglicher Alternativen in anderen Staaten, neu geprüft. Zudem wurde die Regelung für Heimatreisen angepasst. Aufenthalte im Heimat- oder Herkunftsstaat sind neu auf höchstens fünfzehn Tage pro Halbjahr begrenzt. Längere Aufenthalte können zum Entzug des Status führen. Darüber hinaus wird seit dem 1. November 2025 die regionale Differenzierung angewendet. Sie sehen: Die Begründung des Bundesrates überzeugt die Mehrheit also, und da diese Instrumente bereits in der Praxis verankert sind, erachtet die Mehrheit eine weitere Beauftragung des Bundesrates als nicht notwendig. 
-Die Minderheit wird ihre Argumente selber vortragen. Für sie ist die Situation in der Praxis nach wie vor nicht zufriedenstellend, und deshalb seien diese Motionen aufrechtzuerhalten.
+Konkret heisst das: Seit Anfang 2025 wird der Schutzstatus S beendet, wenn eine Person länger als zwei Monate abwesend ist. Bei einer Rückkehr wird das Schutzverfahren, inklusive möglicher Alternativen in anderen Staaten, neu geprüft. Zudem wurde die Regelung für Heimatreisen angepasst. Aufenthalte im Heimat- oder Herkunftsstaat sind neu auf höchstens fünfzehn Tage pro Halbjahr begrenzt. Längere Aufenthalte können zum Entzug des Status führen. Darüber hinaus wird seit dem 1. November 2025 die regionale Differenzierung angewendet. Sie sehen: Die Begründung des Bundesrates überzeugt die Mehrheit also. Da diese Instrumente bereits in der Praxis verankert sind, erachtet die Mehrheit eine weitere Beauftragung des Bundesrates als nicht notwendig. 
+Die Minderheit wird ihre Argumente selber vortragen. Für sie ist die Situation in der Praxis nach wie vor nicht zufriedenstellend, deshalb seien diese Motionen aufrechtzuerhalten.
 </t>
   </si>
   <si>
@@ -812,18 +812,16 @@
     <t xml:space="preserve">SG</t>
   </si>
   <si>
-    <t xml:space="preserve">Meine Minderheit beantragt Ihnen, die zwei vorliegenden Motionen nicht abzuschreiben. 
-Was fordern diese beiden Motionen? Sie fordern Anpassungen beim Schutzstatus S. Insbesondere soll der Schutzstatus S aberkannt bzw. nicht wiedererlangt werden, wenn erstens eine Person für eine bestimmte Aufenthaltsdauer ausreist, zweitens eine Person Rückkehrhilfe oder andere rückkehrorientierte Hilfen bezogen hat oder drittens der Schutzstatus S missbräuchlich erlangt wurde. Des Weiteren soll sichergestellt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meine Minderheit beantragt Ihnen, die zwei vorliegenden Motionen nicht abzuschreiben. 
-Was fordern diese beiden Motionen? Sie fordern Anpassungen beim Schutzstatus S. Insbesondere soll der Schutzstatus S aberkannt bzw. nicht wiedererlangt werden, wenn erstens eine Person für eine bestimmte Aufenthaltsdauer ausreist, zweitens eine Person Rückkehrhilfe oder andere rückkehrorientierte Hilfen bezogen hat oder drittens der Schutzstatus S missbräuchlich erlangt wurde. Des Weiteren soll sichergestellt werden, dass der Schutzstatus innerhalb des Dublin-Raums nur einmal erteilt wird. 
-Die Sprecherin der Mehrheit hat gesagt, der Bundesrat habe diese Motionen im Jahr 2025 umgesetzt. Nach Ansicht der Minderheit ist dies jedoch nur teilweise der Fall. Insbesondere wird der Schutzstatus S in der Schweiz nicht gelöscht, wenn eine Person ausreist, sondern eigentlich fast aufrechterhalten. Ich kann Ihnen einige ganz konkrete Beispiele aus meinem Kanton geben, die mir die St. Galler Gemeinden in den letzten Wochen mitgeteilt haben. Ich nenne Ihnen drei Beispiele.
-Erstes Beispiel: Vier Frauen reisten im Jahr 2022 in die Schweiz ein, im Jahr 2024 aus und sind jetzt, im Jahr 2026, wieder zurückgekehrt. Sie kommen ganz aus dem Westen der Ukraine, also einem Gebiet, das die Schweiz seit letztem Jahr als sogenanntes sicheres Gebiet erklärt hat. Das SEM hat den Schutzstatus S sofort wieder aktiviert und diese vier Frauen auf die St. Galler Gemeinden verteilt.
-Zweites Beispiel einer Familie: Die Familie reiste 2022 in die Schweiz ein und erhielt einen positiven Entscheid zum S-Status. Im Sommer 2023 reiste sie in die Ukraine zurück und beantragte Rückkehrhilfe. Im Herbst 2023 reiste die Familie erneut in die Schweiz ein und erhielt wiederum Schutz. Im November 2024 reiste sie erneut aus und verzichtete schriftlich auf den Schutz. Im Sommer 2026 reiste die Familie erneut ein und erhielt nach fünf Tagen wiederum den positiven Entscheid zum Status S. 
-Oder noch ein letztes Beispiel einer männlichen Person mit Jahrgang 1973: Sie reiste im Jahr 2022 in die Schweiz ein und erhielt den Status S. Im Sommer 2024 verzichtete sie freiwillig auf den Schutz, beantragte Rückkehrhilfe und kehrte in die Ukraine zurück. Bereits zwei Monate später reiste sie erneut in die Schweiz ein und stellte erneut ein Schutzgesuch, das im November 2024 bewilligt wurde. Im März 2025 reiste sie erneut aus, worauf der Schutzstatus formell erlosch. Im Mai 2026 reiste sie erneut ein und stellte ein neues Schutzgesuch. 
-Das sind einige Beispiele, ich könnte Ihnen noch eine ganze Reihe anführen. Das sind alles Beispiele aus St. Galler Gemeinden. Wie Sie sehen, ist die aktuelle Praxis des SEM überhaupt nicht so, wie mit den vorliegenden Motionen eigentlich gefordert und beschlossen wurde. Die Leute haben sogar Rückkehrhilfe erhalten und haben danach wieder ein Gesuch gestellt. Der Bundesrat hat diese Motionen also nur beschränkt umgesetzt. Für die Gemeinden sind gerade solche Wiedereinreisen kostspielig und oft mit viel Aufwand verbunden. Sie erschweren die Prozesse, vor allem auch, weil ja sonst noch sehr viele Fälle pendent sind.
-Vor diesem Hintergrund beantrage ich Ihnen, die Motionen nicht abzuschreiben und den Bundesrat klar zu beauftragen, diese beiden Motionen nun endlich gemäss ihrem Wortlaut umzusetzen.
+    <t xml:space="preserve">Meine Minderheit beantragt Ihnen, die zwei vorliegenden Motionen nicht abzuschreiben. Was fordern diese beiden Motionen? Sie fordern Anpassungen beim Schutzstatus S. Insbesondere soll der Schutzstatus S aberkannt bzw. nicht wiedererlangt werden, wenn die betreffende Person für eine bestimmte Aufenthaltsdauer ausreist, wenn sie Rückkehrhilfe oder andere rückkehrorientierte Hilfen bezogen hat oder wenn der Schutzstatus S missbräuchlich erlangt wurde. Des Weiteren soll sichergestellt werden, dass d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Minderheit beantragt Ihnen, die zwei vorliegenden Motionen nicht abzuschreiben. Was fordern diese beiden Motionen? Sie fordern Anpassungen beim Schutzstatus S. Insbesondere soll der Schutzstatus S aberkannt bzw. nicht wiedererlangt werden, wenn die betreffende Person für eine bestimmte Aufenthaltsdauer ausreist, wenn sie Rückkehrhilfe oder andere rückkehrorientierte Hilfen bezogen hat oder wenn der Schutzstatus S missbräuchlich erlangt wurde. Des Weiteren soll sichergestellt werden, dass der Schutzstatus innerhalb des Dublin-Raums nur einmal erteilt wird. 
+Die Sprecherin der Mehrheit hat gesagt, der Bundesrat habe diese Motionen im Jahr 2025 umgesetzt. Nach Ansicht der Minderheit ist dies jedoch nur teilweise der Fall. Insbesondere wird der Schutzstatus S in der Schweiz nicht beendet, wenn eine Person ausreist, sondern eigentlich fast aufrechterhalten. Ich kann Ihnen einige ganz konkrete Beispiele aus meinem Kanton geben, die mir die St. Galler Gemeinden in den letzten Wochen mitgeteilt haben. Ich nenne Ihnen drei Beispiele.
+Erstes Beispiel: Vier Frauen reisten im Jahr 2022 in die Schweiz ein, reisten im Jahr 2024 aus und sind jetzt, im Jahr 2026, wieder zurückgekehrt. Sie kommen ganz aus dem Westen der Ukraine, also aus einem Gebiet, das die Schweiz seit letztem Jahr als sogenanntes sicheres Gebiet erklärt hat. Das SEM hat den Schutzstatus S sofort wieder aktiviert und diese vier Frauen auf die St. Galler Gemeinden verteilt.
+Zweites Beispiel: Eine Familie reiste 2022 in die Schweiz ein und erhielt einen positiven Entscheid zum S-Status. Im Sommer 2023 beantragte sie Rückkehrhilfe und reiste in die Ukraine zurück. Im Herbst 2023 reiste die Familie erneut in die Schweiz ein und erhielt wiederum Schutz. Im November 2024 reiste sie erneut aus und verzichtete schriftlich auf den Schutz. Im Sommer 2026 reiste die Familie erneut ein und erhielt nach fünf Tagen wiederum den positiven Entscheid zum Status S. 
+Als letztes das Beispiel einer männlichen Person mit Jahrgang 1973: Sie reiste im Jahr 2022 in die Schweiz ein und erhielt den Status S. Im Sommer 2024 verzichtete sie freiwillig auf den Schutz, beantragte Rückkehrhilfe und kehrte in die Ukraine zurück. Bereits zwei Monate später reiste sie erneut in die Schweiz ein und stellte erneut ein Schutzgesuch, das im November 2024 bewilligt wurde. Im März 2025 reiste sie erneut aus, worauf der Schutzstatus formell erlosch. Im Mai 2026 reiste sie erneut ein und stellte ein neues Schutzgesuch. 
+Das sind einige Beispiele, ich könnte Ihnen noch eine ganze Reihe anführen. Das sind alles Beispiele aus St. Galler Gemeinden. Wie Sie sehen, ist die aktuelle Praxis des SEM überhaupt nicht so, wie es mit den vorliegenden Motionen eigentlich gefordert und beschlossen wurde. Die Leute haben sogar Rückkehrhilfe erhalten und haben danach wieder ein Gesuch gestellt. Der Bundesrat hat diese Motionen also nur beschränkt umgesetzt. Für die Gemeinden sind gerade solche Wiedereinreisen kostspielig und oft mit viel Aufwand verbunden. Sie erschweren die Prozesse, vor allem auch, weil ja sonst noch sehr viele Fälle pendent sind.
+Vor diesem Hintergrund beantrage ich Ihnen, diese beiden Motionen nicht abzuschreiben und den Bundesrat klar zu beauftragen, sie nun endlich gemäss ihrem Wortlaut umzusetzen.
 </t>
   </si>
   <si>
@@ -1137,10 +1135,9 @@
   </si>
   <si>
     <t xml:space="preserve">Le but de cette motion est que l'exception absolue qu'accorde notre loi sur la transparence à la Finma soit retirée pour que la Finma, comme tout autre service de notre administration, même si elle ne l'est pas exactement comme le rappelle à juste titre le Conseil fédéral, doive fournir des renseignements qui lui sont demandés et puisse bien évidemment également invoquer les exceptions figurant à l'article 7.
-Je rappelle que la Finma, avec la Banque nationale suisse, sont les seules deux entités totalement couvertes par une absence de transparence, puisque l'on considère qu'elles mènent des activités dans des domaines extrêmement sensibles. Pour la Banque nationale suisse, je pense qu'il n'y a aucune discussion possible : il s'agit de la politique monétaire de notre pays et son activité ne peut pas faire l'objet d'un examen de la part des citoyens. C'est évidemment aux entités fédérales compétentes d'obtenir sur requête les explications voulues.
+Je rappelle que la Finma, avec la Banque nationale suisse, sont les seules deux entités totalement couvertes par une absence de transparence, puisque l'on considère qu'elles mènent des activités dans des domaines extrêmement sensibles. Pour la Banque nationale suisse, je pense qu'il n'y a aucune discussion possible ; il s'agit de la politique monétaire de notre pays et son activité ne peut pas faire l'objet d'un examen de la part des citoyens. C'est évidemment aux entités fédérales compétentes d'obtenir sur requête les explications voulues.
 En ce qui concerne la Finma, la situation est différente. Nous avons une autorité de surveillance, dont on a beaucoup parlé ces derniers temps, pas forcément en bien, qui s'occupe des marchés financiers, du système bancaire, mais également de l'ensemble des assurances privées. Aujourd'hui, la Finma n'a aucune information à donner à qui que ce soit et se retranche effectivement, comme la Banque nationale, derrière une totale opacité.
-Je rappelle que notre Département fédéral des finances et l'armée, qui, eux aussi, par définition, exercent des activités dans des domaines sensibles, sont soumis à la loi sur la transparence et peuvent faire valoir les exceptions figurant dans la loi. Je les rappelle : celles qui s'appliquent ici, c'est lorsque l'on considère que la transparence pourrait entraver l'exécution de mesures concrètes prises par l'autorité conformément à ses objectifs, le risque de compromettre la sûreté intérieure ou extérieure de la Suisse, le risque de compromettre les intérêts de la politique économique ou monétaire et le risque de révéler des secrets professionnels d'affaires ou de fabrication. Il y a donc évidemment cette protection des tiers qui peut être invoquée ou le risque de divulguer des informations fournies librement par un tiers à une autorité qui en a garanti le secret.
-On voit donc que les moyens, pour la Finma, de s'opposer à ce qu'elle devienne un livre ouvert pour le citoyen de notre pays sont présents. Ce qui est demandé, c'est simplement que la Finma soit, comme les autres interlocuteurs dans le domaine de la transparence, soumise à l'obligation de fournir des renseignements.
+Je rappelle que le Département fédéral des finances et l'armée, qui, eux aussi, par définition, exercent des activités dans des domaines sensibles, sont soumis à la loi sur la transparence et peuvent faire valoir les exceptions figurant dans la loi. Je les rappelle : elles s'appliquent lorsque l'on considère que la transparence pourrait entraver l'exécution de mesures concrètes prises par l'autorité conformément à ses objectifs, risquer de compromettre la sûreté intérieure ou extérieure de la Suisse, risquer de compromettre les intérêts de la politique économique ou monétaire et risquer de révéler des secrets professionnels d'affaires ou de fabrication. Il y a donc évidemment cette protection des tiers qui peut être invoquée ou le risque de divulguer des informations fournies librement par un tiers à une autorité qui en a garanti le secret. On voit donc que les moyens, pour la Finma, de s'opposer à ce qu'elle devienne un livre ouvert pour le citoyen de notre pays sont présents. Ce qui est demandé, c'est simplement que la Finma soit, comme les autres interlocuteurs dans le domaine de la transparence, soumise à l'obligation de fournir des renseignements.
 J'ai été moi-même confronté à une problématique évidemment inquiétante, puisque nous avons des assureurs privés qui mènent une politique en invoquant les instructions qui leur sont données par la Finma, qui n'indiquent pas quelles sont ces instructions, parce qu'ils considèrent que la Finma leur interdit de le faire. Lorsque l'on demande à la Finma quelles sont ses instructions, elle se réfugie évidemment derrière le secret.
 Finalement, cette opacité sert donc à des mesures totalement incontrôlées par qui que ce soit, y compris par les tribunaux, puisque - je le répète - le fait de ne pas être soumis à la loi sur la transparence signifie que l'on ne peut même pas s'adresser à un tribunal pour qu'il puisse contrôler si le refus opposé par la Finma se fonde sur des intérêts supérieurs, qui existent évidemment, mais qui doivent au moins être invoqués. Ici, ce n'est pas le cas.
 Voilà la raison pour laquelle je vous demande d'adopter la motion, pour que cette exception, qui n'a pas plus de raison d'être que dans d'autres domaines sensibles de notre administration, soit enfin levée.
@@ -1804,7 +1801,12 @@
 Dem Vernehmen nach war dies der Preis für die Schutzklausel. Mag die Schutzklausel diesen Preis aufwiegen? Das Personenfreizügigkeitsabkommen ist ein Frontalzusammenstoss mit Artikel 121a unserer Bundesverfassung; darüber werden wir ja noch reden. Es widerspricht ebenso dem klaren Auftrag zur eigenständigen Steuerung der Zuwanderung. Allein das Abkommen über die Personenfreizügigkeit, die Erweiterung, würden wir in dieser Form wohl nicht unterschreiben.
 Zweitens kommen mit den Protokollen, wie wir mehrfach ausgeführt gehört haben, die institutionellen Elemente zu den Verträgen hinzu. Dies ist ein fundamentaler Paradigmenwechsel. Die bilateralen Verträge I und II basieren auf dem klassischen Völkerrecht: Gleichberechtigung der Parteien, Änderungen nur im gegenseitigen Einvernehmen, Auslegung nach Treu und Glauben. Das, was heute vorliegt, bricht mit diesem Fundament.
 "Bilaterale III" - dies ist eine Verharmlosung. Tatsächlich handelt es sich um einen massiven institutionellen Integrationsschritt. Entscheidend ist nicht nur der heutige Vertragsinhalt, also jene Blackbox, die ich am Anfang erwähnt habe, sondern der Mechanismus für das Recht von morgen. Mit der dynamischen Rechtsübernahme verpflichten wir uns auf Vorrat, künftige EU-Rechtsentwicklungen zu übernehmen, die meist von der EU-Kommission erlassen werden und die wir heute noch gar nicht kennen.
-Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und oppositionslos so in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Taking.Drittens bedeuten die Verträge eine unannehmbare Schwächung der direkten Demokratie und des Föderalismus. Die Rechtsetzung verschiebt sich bei den betroffenen Abkommen räumlich und institutionell. Die EU und die Schweiz haben grundverschiedene Rechtssysteme: Die EU erlässt neues Recht von oben nach unten, bei uns funktioniert es gerade umgekehrt, von unten nach oben - ausgehend vom Souverän, dem Volk. Diese Systeme lassen sich nicht verbinden.Entscheidend ist, darüber spricht fast niemand, dass wir selber keine Gesetzgebung innerhalb der betroffenen Abkommen mehr anstossen können; wir geben die Input-Funktion für die entsprechende Gesetzgebung in die Hände der EU-Kommission.Zudem, das führte Herr Ständerat Schmid gerade aus, erfährt die Exekutive einen massiven Machtzuwachs. Bundesrat und Verwaltung bestimmen die Positionen, führen das Mandat und wählen die Experten aus, die uns in Brüssel vertreten sollen. Die Schweiz ist kein von oben nach unten organisierter Expertenstaat: "Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut! Komm, lass uns gehen."Viertens können die innerstaatlichen Reformen, die wir noch diskutieren werden, das Grundproblem nicht heilen. Massnahmen zur Stärkung des Parlamentes und der Kantone und Anpassungen im innerstaatlichen Recht ändern nichts an der harten Realität:Die Schweiz gibt die inhaltliche Kontrolle über ihr eigenes Recht ab. Wenn das Volk oder das Parlament neues Recht ablehnt, darf die EU uns mit sachfremden, sektionsübergreifenden Ausgleichsmassnahmen - ich sage das Wort jetzt halt - abstrafen. Das und die mangelnde Konkretisierung dieser Sanktionen ist doch hochproblematisch: Wenn die Folgen einer Ablehnung nicht präzise definiert sind, ist doch eine freie, informierte Willensbildung der Stimmbürgerinnen nicht mehr möglich. Dies verletzt Artikel 34 der Bundesverfassung; die freie Willensbildung und die unverfälschte Stimmabgabe sind in Artikel 34 Absatz 2 der Bundesverfassung garantiert. Es ist eines souveränen Staates unwürdig, wenn ein externer Akteur ihn vertraglich bestrafen darf. 
+Die EU-Rechtsänderungen gelten im Integrations- oder Äquivalenzverfahren, unmittelbar nach der Notifikation. Das birgt die enorme Gefahr, dass politisch hochgradig umstrittene EU-Regeln unbemerkt und oppositionslos so in unser Recht einsickern. Decision Shaping bedeutet nur, dass die Schweiz im Vorfeld zwar mitreden, aber am Ende nicht gleichberechtigt mitentscheiden darf; es ist kein Decision Taking.
+Drittens bedeuten die Verträge eine unannehmbare Schwächung der direkten Demokratie und des Föderalismus. Die Rechtsetzung verschiebt sich bei den betroffenen Abkommen räumlich und institutionell. Die EU und die Schweiz haben grundverschiedene Rechtssysteme: Die EU erlässt neues Recht von oben nach unten, bei uns funktioniert es gerade umgekehrt, von unten nach oben - ausgehend vom Souverän, dem Volk. Diese Systeme lassen sich nicht verbinden.
+Entscheidend ist, darüber spricht fast niemand, dass wir selber keine Gesetzgebung innerhalb der betroffenen Abkommen mehr anstossen können; wir geben die Input-Funktion für die entsprechende Gesetzgebung in die Hände der EU-Kommission.
+Zudem, das führte Herr Ständerat Schmid gerade aus, erfährt die Exekutive einen massiven Machtzuwachs. Bundesrat und Verwaltung bestimmen die Positionen, führen das Mandat und wählen die Experten aus, die uns in Brüssel vertreten sollen. Die Schweiz ist kein von oben nach unten organisierter Expertenstaat: "Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut! Komm, lass uns gehen."
+Viertens können die innerstaatlichen Reformen, die wir noch diskutieren werden, das Grundproblem nicht heilen. Massnahmen zur Stärkung des Parlamentes und der Kantone und Anpassungen im innerstaatlichen Recht ändern nichts an der harten Realität:
+Die Schweiz gibt die inhaltliche Kontrolle über ihr eigenes Recht ab. Wenn das Volk oder das Parlament neues Recht ablehnt, darf die EU uns mit sachfremden, sektionsübergreifenden Ausgleichsmassnahmen - ich sage das Wort jetzt halt - abstrafen. Das und die mangelnde Konkretisierung dieser Sanktionen ist doch hochproblematisch: Wenn die Folgen einer Ablehnung nicht präzise definiert sind, ist doch eine freie, informierte Willensbildung der Stimmbürgerinnen nicht mehr möglich. Dies verletzt Artikel 34 der Bundesverfassung; die freie Willensbildung und die unverfälschte Stimmabgabe sind in Artikel 34 Absatz 2 der Bundesverfassung garantiert. Es ist eines souveränen Staates unwürdig, wenn ein externer Akteur ihn vertraglich bestrafen darf. 
 Auslöser für die Verhandlungen war, gemäss den Medienmitteilungen des Bundesrates in den Anfängen, ein Stromabkommen. Für diesen Gegenwert hat die Schweiz weitreichende Konzessionen gemacht: die dynamische Rechtsübernahme und die innerstaatliche Umsetzung des EU-Beihilferechts. Wie sieht es heute aus? Nun soll ausgerechnet der Strombereich ausgeklammert und separat vorgelegt werden, weil er politisch hoch umstritten ist - das kommt nicht vom Bundesrat, das ist eine Diskussion in den Räten. Damit gerät doch die gesamte Logik des Pakets ins Wanken. Die weitreichenden Konzessionen der Schweiz bleiben bestehen, während der ursprüngliche Auslöser und zentrale Gegenwert, wegen dem man überhaupt verhandelt hat, entfällt. Die Schweiz soll also den vollen Preis für das Paket bezahlen, und das wirft die Frage auf: Wie kann man an den Verpflichtungen festhalten, wenn der Gegenwert, der die Verhandlungen ursprünglich ausgelöst hat, entfällt?
 Manchmal frage ich mich, wann genau wir in der Schweiz aufgehört haben, stolz auf unsere Freiheit, auf unser einzigartiges politisches System zu sein. Ich sehe die Versprechen eines wirtschaftlichen Nutzens. Doch die Realität zeigt, dass die tatsächliche Grössenordnung dieses Nutzens sehr umstritten ist und gar als gering beurteilt wird. Wenn wir diesen vermeintlichen Nutzen gegen den realen Verlust der Souveränität aufwiegen, ist das Ergebnis eindeutig: Der staatspolitische Preis ist zu hoch. Wenn wir auf den Zustand der EU schauen, sehen wir eine zunehmende Zentralisierung, wir sehen, dass das Subsidiaritätsprinzip ignoriert wird, und wir sehen eine enorme Machtkonzentration bei der EU-Kommission. Die wirtschaftlichen und politischen Schwächen grosser Mitgliedstaaten wie Deutschland oder Frankreich sind unübersehbar. Es gibt keinen zwingenden Grund, warum wir uns enger an dieses System binden sollten. Wer behauptet, dieses Paket sei alternativlos, verkennt die Realität und die Stärken unseres Landes. Wir sind ein finanziell gesunder, wir sind ein erfolgreicher Stabilitätsanker im Herzen Europas. Wir halten unser staatliches Haus in Ordnung. Wir haben für Milliarden von Franken eine Jahrhundertinfrastruktur gebaut, die Neat, den Alpentransit, und dies im vitalen Interesse des gesamten Kontinents.Dieses starke Schweizer Fundament beweist, dass die EU ein ebenso grosses Eigeninteresse an geordneten Beziehungen hat wie wir. Lassen wir uns wirklich von der Drohkulisse einschüchtern, wonach die Bilateralen I und die Bilateralen II bei einem Nein sofort beendet würden? Es gibt immer Alternativen. Wir können bestehende Abkommen punktuell und klassisch völkerrechtlich modernisieren. Die EU beweist zudem, wie beim Ceta-Abkommen oder den aktuellen Plänen für eine assoziierte Mitgliedschaft Kanadas, dass massgeschneiderte Verträge mit Drittstaaten möglich sind, ohne dass diese auf ihre Souveränität verzichten oder eine automatische Rechtsübernahme akzeptieren müssten."Ei, Vater, sieh den Hut dort auf der Stange." - "Was kümmert uns der Hut? Komm, lass uns gehen." Ja, gehen wir selbstbewusst an diesem Hut vorbei, treten wir nicht ein.</t>
   </si>
@@ -2020,12 +2022,7 @@
 In diesem Zusammenhang sind spezifische Regelungen und Instrumente vorgesehen. Im Zentrum steht die Konkretisierung der Schutzklausel. Ein Kernpunkt der Umsetzung ist die präzise Definition der Schutzklausel. Der Bundesrat will im AIG festlegen, unter welchen Bedingungen schwerwiegende wirtschaftliche oder soziale Probleme vorliegen. Er präzisiert hierzu das Verfahren für die Schutzklausel, die kantonale Mitwirkung und das Ziel der Schutzklausel. 
 Ein weiterer Punkt betrifft den Nachzug pflegebedürftiger Familienangehöriger. Der Bundesrat beabsichtigt, den Familiennachzug in Härtefällen zu erleichtern, knüpft diesen jedoch an strikte Voraussetzungen, um eine Ausweitung des Rechtsanspruchs zu verhindern.
 Das Fazit des Bundesrates war, dass die vorgeschlagene Umsetzung im AIG ein massgeschneidertes Paket darstellt, welches die Interessen der Schweiz optimal wahre. Wir haben in der Kommission an mehreren Sitzungen über das AIG debattiert und Beschlüsse gefasst. Die Vorlage des Bundesrates wurde einer eingehenden Prüfung unterzogen. Im Zentrum des Austausches standen insbesondere die Verfassungskonformität, die faktischen Auswirkungen auf die Zuwanderung sowie die staatspolitischen Implikationen der dynamischen Rechtsübernahme.
-In Bezug auf die Zuwanderungssteuerung und die Verfassungskonformität wurde in unserer Kommission intensiv diskutiert, ob die Vorlage mit Artikel 121a der Bundesverfassung vereinbar sei. Die Kommission äusserte deutliche Bedenken, ob die neuen Regelungen insbesondere im Bereich des Familiennachzugs und des Daueraufenthaltsrechts eine zusätzliche Zuwanderung generieren und damit die staatliche Steuerung untergraben bzw. Artikel 121a der Bundesverfassung verletzen würden. Das wird morgen bei der Beratung unserer parlamentarischen Initiative im Detail zu diskutieren sein. 
-Weiter ging es um das Thema des Daueraufenthaltsrechts und der Integrationsfrage. Die Kommission hinterfragte kritisch die Kriterien für das neue Daueraufenthaltsrecht. Insbesondere wurde die Sorge geäussert, dass dieses Recht eine Sogwirkung entfalten könnte oder insbesondere für Personen attraktiv werde, die aufgrund mangelnder Integration die Voraussetzungen für eine Niederlassungsbewilligung C nicht erfüllen würden. Hierzu wurde uns erläutert, dass die Kernbedingung einer Erwerbstätigkeit über fünf Jahre quasi identisch mit der für die C-Bewilligung bleibe. Es wurde eingeräumt, dass das Daueraufenthaltsrecht aufgrund des Wegfalls der Integrationsprüfung eine Alternative für bestimmte Gruppen darstelle, wobei aber die wirtschaftliche Bedingung, die echte Erwerbstätigkeit, die massgebliche Hürde sei. 
-In der Kommission hat im Zusammenhang mit dem Ausländer- und Integrationsgesetz (AIG) eine intensive Debatte über das Verhältnis zwischen dem Freizügigkeitsabkommen und dem innerstaatlichen Recht stattgefunden. Die Kommission thematisierte mit Nachdruck die sogenannte Schubert-Praxis und die Gefahr, dass hier Völkerrecht dem Landesrecht vorgehe, selbst wenn das Parlament explizit abweichende Regelungen beschliesse. Der Bundesrat legte dar, dass die neuen institutionellen Protokolle die völkerrechtliche Ausgangslage veränderten, da die Schweiz nun explizit die Möglichkeit besitze, unter Inkaufnahme von Ausgleichsmassnahmen vom Abkommen abzuweichen. In der Diskussion wurde präzisiert, dass hierbei zwei unterschiedliche Prozesse zu unterscheiden seien, die innerstaatliche Rechtsanwendung durch das Bundesgericht auf der einen Seite und das internationale Streitbeilegungsverfahren auf der anderen Seite.
-Das Thema der Schubert-Praxis, das ein Teil der parlamentarischen Initiative war, wird ja dann in der Kommission nach dieser Session vertieft. Diese Vorlage wird Ihnen in einer der nächsten Sessionen vorgelegt werden können, wahrscheinlich in der Frühjahrssession, sofern die Vernehmlassung plangemäss verläuft.
-Weiter hat die Kommission sich kritisch mit der Praxistauglichkeit der Schutzklausel auseinandergesetzt und auch hinterfragt, ob die Indikatoren genügend stark sein würden, um die Schutzmassnahmen auch wirksam zu machen. Hierzu wurde uns ausgeführt, dass vor einem Schiedsgericht primär starke Indikatoren, zum Beispiel die Arbeitslosenquote, eine erfolgreiche Aktivierung wahrscheinlich machen würden.
-Als zusätzlichen Punkt, der in der Detailberatung thematisiert und von mir kommentiert wird, hat die Kommission die Schutzklausel um eine Lenkungsabgabe ergänzt. Ein zentraler Aspekt der Diskussion war die staatspolitische Dimension der sogenannten Ausgleichsmassnahmen, die von der Kommission als Damoklesschwert bezeichnet wurden. Es wurde hinterfragt, inwiefern dies einen Eingriff in die direkte Demokratie darstellte. Der Bundesrat argumentierte, dass Ausgleichsmassnahmen ein Standardinstrument in fast allen Freihandelsabkommen seien und die neue Regelung im Vergleich zum aktuellen Status quo sogar einen Gewinn an Rechtssicherheit bedeute. Abschliessend wurden weitere Detailfragen geklärt, auf die wir in der Beratung der einzelnen Artikel zurückkommen werden.
+In Bezug auf die Zuwanderungssteuerung und die Verfassungskonformität wurde in unserer Kommission intensiv diskutiert, ob die Vorlage mit Artikel 121a der Bundesverfassung vereinbar sei. Die Kommission äusserte deutliche Bedenken, ob die neuen Regelungen insbesondere im Bereich des Familiennachzugs und des Daueraufenthaltsrechts eine zusätzliche Zuwanderung generieren und damit die staatliche Steuerung untergraben bzw. Artikel 121a der Bundesverfassung verletzen würden. Das wird morgen bei der Beratung unserer parlamentarischen Initiative im Detail zu diskutieren sein. Weiter ging es um das Thema des Daueraufenthaltsrechts und der Integrationsfrage. Die Kommission hinterfragte kritisch die Kriterien für das neue Daueraufenthaltsrecht. Insbesondere wurde die Sorge geäussert, dass dieses Recht eine Sogwirkung entfalten könnte oder insbesondere für Personen attraktiv werde, die aufgrund mangelnder Integration die Voraussetzungen für eine Niederlassungsbewilligung C nicht erfüllen würden. Hierzu wurde uns erläutert, dass die Kernbedingung einer Erwerbstätigkeit über fünf Jahre quasi identisch mit der für die C-Bewilligung bleibe. Es wurde eingeräumt, dass das Daueraufenthaltsrecht aufgrund des Wegfalls der Integrationsprüfung eine Alternative für bestimmte Gruppen darstelle, wobei aber die wirtschaftliche Bedingung, die echte Erwerbstätigkeit, die massgebliche Hürde sei. In der Kommission hat im Zusammenhang mit dem Ausländer- und Integrationsgesetz (AIG) eine intensive Debatte über das Verhältnis zwischen dem Freizügigkeitsabkommen und dem innerstaatlichen Recht stattgefunden. Die Kommission thematisierte mit Nachdruck die sogenannte Schubert-Praxis und die Gefahr, dass hier Völkerrecht dem Landesrecht vorgehe, selbst wenn das Parlament explizit abweichende Regelungen beschliesse. Der Bundesrat legte dar, dass die neuen institutionellen Protokolle die völkerrechtliche Ausgangslage veränderten, da die Schweiz nun explizit die Möglichkeit besitze, unter Inkaufnahme von Ausgleichsmassnahmen vom Abkommen abzuweichen. In der Diskussion wurde präzisiert, dass hierbei zwei unterschiedliche Prozesse zu unterscheiden seien, die innerstaatliche Rechtsanwendung durch das Bundesgericht auf der einen Seite und das internationale Streitbeilegungsverfahren auf der anderen Seite.Das Thema der Schubert-Praxis, das ein Teil der parlamentarischen Initiative war, wird ja dann in der Kommission nach dieser Session vertieft. Diese Vorlage wird Ihnen in einer der nächsten Sessionen vorgelegt werden können, wahrscheinlich in der Frühjahrssession, sofern der politische Prozess plangemäss verläuft.Weiter hat die Kommission sich kritisch mit der Praxistauglichkeit der Schutzklausel auseinandergesetzt und auch hinterfragt, ob die Indikatoren genügend stark sein würden, um die Schutzmassnahmen auch wirksam zu machen. Hierzu wurde uns ausgeführt, dass vor einem Schiedsgericht primär starke Indikatoren, zum Beispiel die Arbeitslosenquote, eine erfolgreiche Aktivierung wahrscheinlich machen würden.Als zusätzlichen Punkt, der in der Detailberatung thematisiert und von mir kommentiert wird, hat die Kommission die Schutzklausel um eine Lenkungsabgabe ergänzt. Ein zentraler Aspekt der Diskussion war die staatspolitische Dimension der sogenannten Ausgleichsmassnahmen, die von der Kommission als Damoklesschwert bezeichnet wurden. Es wurde hinterfragt, inwiefern dies einen Eingriff in die direkte Demokratie darstellte. Der Bundesrat argumentierte, dass Ausgleichsmassnahmen ein Standardinstrument in fast allen Freihandelsabkommen seien und die neue Regelung im Vergleich zum aktuellen Status quo sogar einen Gewinn an Rechtssicherheit bedeute. Abschliessend wurden weitere Detailfragen geklärt, auf die wir in der Beratung der einzelnen Artikel zurückkommen werden.
 Damit bin ich am Ende meines Eintretensvotums angelangt. Die SPK-S musste kein Eintreten beschliessen, da dies für das gesamte Paket bereits von der APK-S beschlossen worden war.
 </t>
   </si>
@@ -2060,10 +2057,7 @@
     <t xml:space="preserve">Ich möchte einleitend ebenfalls darauf hinweisen, dass wir vor drei Monaten in diesem Rat die Motion Chiesa 26.3229 gutgeheissen haben, und zwar mit einem klaren Verhältnis von 26 zu 11 Stimmen bei 5 Enthaltungen. Sie verlangt erstens von allen Personen, welche in der Schweiz eine Aufenthaltsbewilligung beantragen, einen Strafregisterauszug zu verlangen, und zweitens, dass Personen, bei denen die Prüfung ihres Strafregisterauszuges ergibt, dass sie eine Gefahr darstellen, kein Aufenthaltsrecht e</t>
   </si>
   <si>
-    <t xml:space="preserve">Ich möchte einleitend ebenfalls darauf hinweisen, dass wir vor drei Monaten in diesem Rat die Motion Chiesa 26.3229 gutgeheissen haben, und zwar mit einem klaren Verhältnis von 26 zu 11 Stimmen bei 5 Enthaltungen. Sie verlangt erstens von allen Personen, welche in der Schweiz eine Aufenthaltsbewilligung beantragen, einen Strafregisterauszug zu verlangen, und zweitens, dass Personen, bei denen die Prüfung ihres Strafregisterauszuges ergibt, dass sie eine Gefahr darstellen, kein Aufenthaltsrecht erhalten. Wir haben diese Motion im Wissen darum gutgeheissen, dass die Forderung sowohl Personen aus Drittstaaten als auch Personen aus EU/EFTA-Ländern betrifft. Wir haben die Entscheidung im Wissen um die Begründung der ablehnenden Stellungnahme des Bundesrates getroffen, dass diese Forderung in Bezug auf EU/EFTA-Staatsangehörige gegen das Freizügigkeitsabkommen verstösst.
-Drei Monate später geht es nun darum, auch Tatsachen folgen zu lassen. Bei Artikel 13 AIG macht die Kommission das: In Abweichung zum Entwurf des Bundesrates, der beim geltenden Recht bleiben möchte, beantragt Ihnen die Staatspolitische Kommission mit Absatz 2, dass die Behörden bei Drittstaatsangehörigen nicht nur einen Strafregisterauszug verlangen können, sondern einen Strafregisterauszug verlangen müssen. Vor allem bekommen die Behörden mit Absatz 4, der neu eingefügt werden soll, die klare Vorgabe, dass der Aufenthalt zu verweigern ist, wenn sich aus der Prüfung des Strafregisterauszuges oder anderer Unterlagen ergibt, dass die betreffende Person eine Gefahr darstellt. Das steht heute so nicht im Gesetz. Dazu liegt kein Minderheitsantrag vor. Ich bin gespannt, wie der Bundesrat sich dazu äussert und ob er sich mit der entsprechenden Ergänzung des Ausländer- und Integrationsgesetzes einverstanden erklärt.
-Nun stellt sich die Frage, wie wir mit EU- und EFTA-Staatsangehörigen umgehen. Das erste Beispiel ist eigentlich ein Paradebeispiel dafür, in welcher Situation wir uns befinden. Vor drei Monaten haben wir noch eigenständig gesagt: Wir wollen auch bei EU- und EFTA-Staatsangehörigen, dass ein Strafregisterauszug verlangt wird. Drei Monate später werden wir nun zu entscheiden haben, wie wir auf die Information reagieren, dass es gegen das Freizügigkeitsabkommen verstösst, wenn wir die neuen Bestimmungen jetzt wirklich in das Gesetz schreiben und konkret umsetzen. Es wird dann jene geben, die sagen: Gut, dann tun wir das nicht, wir distanzieren uns von der Motion, wir machen einen Kniefall vor dem Freizügigkeitsabkommen und verzichten darauf, eigenständig Gesetzgebung zu betreiben. Das ist eigentlich das erste Paradebeispiel, das wir hier haben.
-Auch ich liefere Ihnen eine Anekdote. Ich habe vor einem Jahr meinen Eintrag im Anwaltsregister des Kantons St. Gallen in jenes des Kantons Appenzell Innerhoden verlegt. Ich kann Ihnen sagen, was ich vorlegen musste: Ich musste einen Betreibungsregisterauszug und selbstverständlich auch einen Strafregisterauszug vorlegen. Zudem musste ich noch eine Bestätigung der Kindes- und Erwachsenenschutzbehörde vorlegen, dass keine Verdachtsmomente vorliegen, die mich als handlungs- und urteilsunfähig erscheinen liessen. Das ist also sogar die Praxis bei Anwälten, wenn ein Eintrag im Anwaltsregister vorgenommen oder geändert werden soll. 
+    <t xml:space="preserve">Ich möchte einleitend ebenfalls darauf hinweisen, dass wir vor drei Monaten in diesem Rat die Motion Chiesa 26.3229 gutgeheissen haben, und zwar mit einem klaren Verhältnis von 26 zu 11 Stimmen bei 5 Enthaltungen. Sie verlangt erstens von allen Personen, welche in der Schweiz eine Aufenthaltsbewilligung beantragen, einen Strafregisterauszug zu verlangen, und zweitens, dass Personen, bei denen die Prüfung ihres Strafregisterauszuges ergibt, dass sie eine Gefahr darstellen, kein Aufenthaltsrecht erhalten. Wir haben diese Motion im Wissen darum gutgeheissen, dass die Forderung sowohl Personen aus Drittstaaten als auch Personen aus EU/EFTA-Ländern betrifft. Wir haben die Entscheidung im Wissen um die Begründung der ablehnenden Stellungnahme des Bundesrates getroffen, dass diese Forderung in Bezug auf EU/EFTA-Staatsangehörige gegen das Freizügigkeitsabkommen verstösst.Drei Monate später geht es nun darum, auch Tatsachen folgen zu lassen. Bei Artikel 13 AIG macht die Kommission das: In Abweichung zum Entwurf des Bundesrates, der beim geltenden Recht bleiben möchte, beantragt Ihnen die Staatspolitische Kommission mit Absatz 2, dass die Behörden bei Drittstaatsangehörigen nicht nur einen Strafregisterauszug verlangen können, sondern einen Strafregisterauszug verlangen müssen. Vor allem bekommen die Behörden mit Absatz 4, der neu eingefügt werden soll, die klare Vorgabe, dass der Aufenthalt zu verweigern ist, wenn sich aus der Prüfung des Strafregisterauszuges oder anderer Unterlagen ergibt, dass die betreffende Person eine Gefahr darstellt. Das steht heute so nicht im Gesetz. Dazu liegt kein Minderheitsantrag vor. Ich bin gespannt, wie der Bundesrat sich dazu äussert und ob er sich mit der entsprechenden Ergänzung des Ausländer- und Integrationsgesetzes einverstanden erklärt.Nun stellt sich die Frage, wie wir mit EU- und EFTA-Staatsangehörigen umgehen. Das erste Beispiel ist eigentlich ein Paradebeispiel dafür, in welcher Situation wir uns befinden. Vor drei Monaten haben wir noch eigenständig gesagt: Wir wollen auch bei EU- und EFTA-Staatsangehörigen, dass ein Strafregisterauszug verlangt wird. Drei Monate später werden wir nun zu entscheiden haben, wie wir auf die Information reagieren, dass es gegen das Freizügigkeitsabkommen verstösst, wenn wir die neuen Bestimmungen jetzt wirklich in das Gesetz schreiben und konkret umsetzen. Es wird dann jene geben, die sagen: Gut, dann tun wir das nicht, wir distanzieren uns von der Motion, wir machen einen Kniefall vor dem Freizügigkeitsabkommen und verzichten darauf, eigenständig Gesetzgebung zu betreiben. Das ist eigentlich das erste Paradebeispiel, das wir hier haben.Auch ich liefere Ihnen eine Anekdote. Ich habe vor einem Jahr meinen Eintrag im Anwaltsregister des Kantons St. Gallen in jenes des Kantons Appenzell Innerhoden verlegt. Ich kann Ihnen sagen, was ich vorlegen musste: Ich musste einen Betreibungsregisterauszug und selbstverständlich auch einen Strafregisterauszug vorlegen. Zudem musste ich noch eine Bestätigung der Kindes- und Erwachsenenschutzbehörde vorlegen, dass keine Verdachtsmomente vorliegen, die mich als handlungs- und urteilsunfähig erscheinen liessen. Das ist also sogar die Praxis bei Anwälten, wenn ein Eintrag im Anwaltsregister vorgenommen oder geändert werden soll. 
 Und wir diskutieren jetzt darüber, ob wir zur Gewährleistung der Sicherheit in unserem Land auch von EU- und EFTA-Staatsangehörigen einen Strafregisterauszug verlangen wollen. Wichtig ist: Es geht nicht nur um EU- und EFTA-Staatsangehörige, sondern es geht auch um Familienangehörige von EU- und EFTA-Staatsangehörigen, die aus Drittstaaten kommen. Auch diese würden gemäss dem Entwurf des Bundesrates keinen Strafregisterauszug vorlegen müssen. 
 Ich empfehle Ihnen, hier bei der Entscheidung zu bleiben, die wir vor drei Monaten gefällt haben. Ja, das wird die EU nicht freuen. Der EU-Ministerrat wird entscheiden müssen, ob er deswegen das Vertragswerk mit der Schweiz in die Schublade legt oder ob er daran festhält. Ich meine, wir sollten unsere Souveränität nicht aufgeben, und das ist ein erster Testfall. 
 Bitte stimmen Sie bei Artikel 15a Absatz 6 mit der Minderheit.
@@ -2084,7 +2078,7 @@
 Die SPK-S beantragt ausserdem, Artikel 13 um einen Absatz 4 zu ergänzen, wonach das Aufenthaltsrecht verweigert wird, wenn eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit vorliegt. Dieser Absatz 4 hält lediglich fest, was bereits heute schon gilt. Aus Sicht des Bundesrates kann dieser Absatz 4 angenommen werden. 
 Der neue Artikel 15a regelt nun die Pflichten von Staatsangehörigen der EU-Mitgliedstaaten und ihren Familienangehörigen, die sich länger als drei Monate in der Schweiz aufhalten. Er regelt zudem die Pflichten der Grenzgängerinnen und Grenzgänger, die während mehr als drei Monaten in der Schweiz arbeiten. 
 Eine Minderheit der SPK beantragt, dass systematisch ein Strafregisterauszug aus dem Herkunfts- und Heimatstaat einverlangt wird. Dieser Antrag ist abzulehnen, da er gegen das FZA verstösst. Ein Strafregisterauszug darf bei freizügigkeitsberechtigten Personen nur einverlangt werden, wenn ernsthafte Anhaltspunkte bestehen, die es rechtfertigen, einen Strafregisterauszug zum Schutz der öffentlichen Ordnung und Sicherheit einzuholen.
-Es ist zudem wichtig, zu erwähnen, dass das Einverlangen von Strafregisterauszügen nur ein Teil des Sicherheitsdispositives darstellt. Strafregister sind in der Regel erst von praktischem Nutzen, wenn eine Person rechtskräftig strafrechtlich verurteilt wurde. Andere relevante Informationen sind in der Regel darin nicht sichtbar.
+Es ist zudem wichtig, zu erwähnen, dass das Einverlangen von Strafregisterauszügen nur ein Teil des Sicherheitsdispositives darstellt. Strafregisterauszüge sind in der Regel erst von praktischem Nutzen, wenn eine Person rechtskräftig strafrechtlich verurteilt wurde. Andere relevante Informationen sind in der Regel darin nicht sichtbar.
 An dieser Stelle möchte ich auch noch das Schreiben der KdK vom 24. September an den Ständerat erwähnen, welches der Bundesrat in Kopie erhielt. Das Anliegen kommt aus der Vollzugsperspektive und scheint mir daher wichtig. Ich zitiere: "So hätten allfällige systematische Strafregisterauszüge, die im Rahmen des Bewilligungs- und Anmeldeverfahrens des Ausländer- und Integrationsgesetzes für Bürgerinnen und Bürger der EU eingeführt würden, einen unverhältnismässigen Aufwand für die Kantone zur Folge und dürften darüber hinaus ohnehin nur schwer mit dem FZA vereinbar sein."
 Der Bundesrat und die Mehrheit der SPK-S sehen deshalb eine andere und, wie wir denken, bessere Lösung vor. Diese knüpft an das heutige System an. Bereits heute prüfen die Behörden bei einer Anmeldung automatisch Ripol und Interpol-Abfragen. In besonderen Verdachtsfällen überprüfen sie weitere Datenbanken. Damit sieht man, ob nach einer Person gefahndet wird oder diese die Sicherheit und Ordnung gefährden könnte. Wenn eine Datenbank sicherheitsrelevante Hinweise gibt, machen die Migrationsbehörden eine vertiefte Prüfung. Ergibt diese Überprüfung, dass die betroffene Person eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit darstellt, so wird ihr das Aufenthaltsrecht nach dem FZA verweigert.
 Hinzu kommt nun der Antrag der Mehrheit Ihrer Kommission. Die Mehrheit der SPK-S schlägt einen neuen Artikel 15abis vor, der den sicherheitspolitischen Bedenken Rechnung trägt und gleichzeitig FZA-kompatibel ist. Das wäre ein gangbarer Weg. Mit diesem Antrag sind die kantonalen Behörden verpflichtet, zu überprüfen, ob EU-Staatsangehörige sowie ihre Familienangehörigen eine Gefahr für die öffentliche Sicherheit, Ordnung oder Gesundheit darstellen. Wie sie diese Pflicht erfüllen, entscheiden die kantonalen Behörden unter Berücksichtigung der konkreten Umstände. Denkbar wäre die Selbstdeklaration, wonach die Personen angeben müssen, ob sie strafrechtlich verurteilt worden sind oder ein Strafverfahren gegen sie hängig ist. Liegt ein Verdachtsfall vor, so können die zuständigen Behörden einen Strafregisterauszug einverlangen.
@@ -2714,7 +2708,6 @@
 (Dünki-Bättig, Gysin Greta, Kälin, Klopfenstein Broggini, Marti Samira, Masshardt, Schläfli Nina, Tschopp)[GZ]
 Al. 2 let. b [GZ]
 b. ... l'horaire de travail, le trajet pour se rendre au travail ou des obligations familiales ne permettent pas d'exiger raisonnablement qu'elle reste dans son canton de résidence.
-[VS]
 </t>
   </si>
   <si>
@@ -2978,12 +2971,12 @@
 Der Bundesrat sieht vor, die Mitwirkung der Kantone im Bereich des Pakets Schweiz-EU in einer Vereinbarung zwischen dem Bund und den Kantonen zu regeln, analog zur bestehenden Vereinbarung zwischen Bund und Kantonen im Bereich der Schengen/Dublin-Assoziierung. Die Vereinbarung zwischen Bund und Kantonen zum Paket Schweiz-EU wurde von der Bundesverwaltung und der Konferenz der Kantonsregierungen ausgearbeitet. Der Bundesrat hat den Entwurf an seiner Sitzung vom 22. April 2026 genehmigt und veröffentlicht. Damit die Vereinbarung in Kraft treten kann, braucht es aber eine Kompetenzgrundlage im Bundesgesetz über die Mitwirkung der Kantone an der Aussenpolitik des Bundes. Entsprechend ist in Anhang 6 des Entwurfs 1 ein Vorschlag für einen neuen Artikel 5a dieses Bundesgesetzes enthalten. Materiell bleibt die Vereinbarung im Rahmen des geltenden Bundesgesetzes und des Artikels 55 der Bundesverfassung.
 Zu den Vorschlägen des Bundesrates betreffend die Mitwirkung des Parlamentes: Im Parlamentsgesetz sieht der Bundesrat die Schaffung zweier neuer Bestimmungen, nämlich Artikel 147a und Artikel 152a, sowie formelle Änderungen des bestehenden Artikels 148 vor. Mit dem neuen Artikel 147a sieht der Bundesrat vor, dem Parlament einmal pro Legislaturperiode im Rahmen seines Berichts über den Stand der Beziehungen zur EU ein Monitoring über die Funktionsweise der institutionellen Elemente des Pakets Schweiz-EU vorzulegen. Zudem sieht der Bundesrat vor, alle Informationen zu den aussenpolitischen Berichten in diesem neuen Artikel 147a zusammenzufassen, was zu Änderungen des bestehenden Artikels 148 führt.
 Der Bundesrat beabsichtigt zudem, die Rolle des Parlamentes bei allen institutionellen Mechanismen sicherzustellen und klare interne Prozesse zu definieren. Die Grundlage für diesen Ansatz des Bundesrates ist die Informationsplattform. Auf dieser Plattform werden alle öffentlichen Dokumente der EU zum Decision Shaping zugänglich gemacht werden. Auch das Parlament wird auf diese Dokumente Zugriff haben. Diese Veröffentlichungspflicht ist in einem neuen Artikel 40a des Regierungs- und Verwaltungsorganisationsgesetzes vorgesehen; ich werde darauf zurückkommen.
-Basierend auf dieser totalen Transparenz sieht der Bundesrat in Bezug auf die Mitwirkung des Parlamentes vor, einen neuen Artikel 152a ParlG zu schaffen. Dieser soll die Informations- und Konsultationsprozesse und -rechte des Parlamentes im Rahmen des Decision Shaping spezifisch regeln. In diesem Rahmen werden die für die Aussenpolitik zuständigen Kommissionen sowie neu auch die anderen kompetenten Fachkommissionen miteinbezogen. Zudem will der Bundesrat die Mitwirkung des Parlamentes an den weiteren Prozessen der institutionellen Elemente - dynamische Rechtsübernahme, Streitbeilegung und Ausgleichsmassnahmen - im Rahmen des bestehenden Artikels 152 ParlG sicherstellen. Die genauen Modalitäten der Mitwirkung des Parlamentes auf der Grundlage von Artikel 152 und 152a ParlG werden in einer Weisung des Bundesrates geregelt werden. Die Weisung soll parallel zur Beratung dieses Pakets unter Einbezug der Ratspräsidien, der zuständigen Kommissionen und der Parlamentsdienste erarbeitet werden. Diese Konsultation wurde bereits am 13. März dieses Jahres lanciert.
+Basierend auf dieser totalen Transparenz sieht der Bundesrat in Bezug auf die Mitwirkung des Parlamentes vor, einen neuen Artikel 152a ParlG zu schaffen. Dieser soll die Informations- und Konsultationsprozesse und -rechte des Parlamentes im Rahmen des Decision Shaping spezifisch regeln. In diesem Rahmen werden die für die Aussenpolitik zuständigen Kommissionen sowie neu auch die anderen kompetenten Fachkommissionen mit einbezogen. Zudem will der Bundesrat die Mitwirkung des Parlamentes an den weiteren Prozessen der institutionellen Elemente - dynamische Rechtsübernahme, Streitbeilegung und Ausgleichsmassnahmen - im Rahmen des bestehenden Artikels 152 ParlG sicherstellen. Die genauen Modalitäten der Mitwirkung des Parlamentes auf der Grundlage von Artikel 152 und 152a ParlG werden in einer Weisung des Bundesrates geregelt werden. Die Weisung soll parallel zur Beratung dieses Pakets unter Einbezug der Ratspräsidien, der zuständigen Kommissionen und der Parlamentsdienste erarbeitet werden. Diese Konsultation wurde bereits am 13. März dieses Jahres lanciert.
 Mit diesen Vorschlägen will der Bundesrat die geltende Kompetenzordnung und die bewährten Prozesse auch im Bereich der institutionellen Elemente beibehalten. Konkret: Die bestehenden, in der Praxis bewährten Kriterien, die eine Information des Parlamentes bei wichtigen Entwicklungen und eine Konsultation des Parlamentes zu wesentlichen Vorhaben und bedeutenden Verhandlungen vorsehen, sollen auf die verschiedenen Etappen der institutionellen Elemente angewendet werden. Im Bereich des Decision Shaping und der dynamischen Rechtsübernahme sieht der Bundesrat auch bei wichtigen Rechtsakten eine Information der zuständigen parlamentarischen Kommissionen sowie bei wesentlichen Rechtsakten eine Konsultation vor. Wichtig sind Rechtsakte, die in den Kompetenzbereich des Parlamentes fallen. Wesentlich sind Rechtsakte von einer zusätzlichen besonderen Wichtigkeit und/oder politischen Sensibilität.
 Pro memoria: Die Übernahme von EU-Rechtsakten in das jeweils betroffene Abkommen muss am Schluss vom Parlament genehmigt werden, sofern dieses die Kompetenz dafür nicht in einem Bundesgesetz an den Bundesrat delegiert. Das ist eine sehr wichtige Bemerkung, auch für die Souveränitätsdebatte.
 Der Bundesrat schlägt auch vor, dass das Parlament bei wichtigen und wesentlichen Etappen des Streitbeilegungsverfahrens inklusive Ausgleichsmassnahmen informiert bzw. konsultiert wird. Sie sehen also immer diese zwei Schienen, je nach Wichtigkeit der Information.
-Zusätzlich gestützt auf Artikel 152 Absatz 5 ParlG und den neuen Artikel 152a Absatz 4 ParlG kann das Parlament bereits heute und in Zukunft jederzeit eine Information oder eine Konsultation verlangen. Die Veröffentlichung aller öffentlichen Dokumente der EU betreffend das "decision shaping" wird es dem Parlament erlauben, den Überblick über die Rechtsentwicklungen im Binnenmarktbereich und beim Gesundheitsabkommen zu behalten und sich eigenständig einzubringen.
-Schliesslich zur Mitwirkung der Öffentlichkeit: Wie bereits erwähnt, will der Bundesrat im Zusammenhang mit dem "decision shaping" Transparenz und Inklusivität schaffen. In Artikel 40a RVOG schlägt er daher die Veröffentlichung aller für das "decision shaping" relevanten öffentlichen Dokumente der EU an einem zentralen Ort vor, eine sogenannte elektronische Informationsplattform. Die ständigen Teilnehmer an den Vernehmlassungsverfahren und die weiteren interessierten Kreise sollen zusätzlich über die Veröffentlichung benachrichtigt werden. Die Arbeiten, die die Gestaltung dieser Informationsplattform betreffen, sind bereits in Gang. Die Schaffung dieses neuen Artikels 40a RVOG würde eine Änderung des Titels des bestehenden Artikels 40 zur Folge haben.
+Zusätzlich gestützt auf Artikel 152 Absatz 5 ParlG und den neuen Artikel 152a Absatz 4 ParlG kann das Parlament bereits heute und in Zukunft jederzeit eine Information oder eine Konsultation verlangen. Die Veröffentlichung aller öffentlichen Dokumente der EU betreffend das Decision Shaping wird es dem Parlament erlauben, den Überblick über die Rechtsentwicklungen im Binnenmarktbereich und beim Gesundheitsabkommen zu behalten und sich eigenständig einzubringen.
+Schliesslich zur Mitwirkung der Öffentlichkeit: Wie bereits erwähnt, will der Bundesrat im Zusammenhang mit dem Decision Shaping Transparenz und Inklusivität schaffen. In Artikel 40a RVOG schlägt er daher die Veröffentlichung aller für das Decision Shaping relevanten öffentlichen Dokumente der EU an einem zentralen Ort vor, eine sogenannte elektronische Informationsplattform. Die ständigen Teilnehmer an den Vernehmlassungsverfahren und die weiteren interessierten Kreise sollen zusätzlich über die Veröffentlichung benachrichtigt werden. Die Arbeiten, die die Gestaltung dieser Informationsplattform betreffen, sind bereits in Gang. Die Schaffung dieses neuen Artikels 40a RVOG würde eine Änderung des Titels des bestehenden Artikels 40 zur Folge haben.
 Zusammengefasst: Der Bundesrat misst der innerstaatlichen Umsetzung des Pakets Schweiz-EU und insbesondere der institutionellen Elemente eine grosse Bedeutung zu. Wie ich zu Beginn meiner Ausführungen erwähnt habe, haben seine Vorschläge im Bereich der Mitwirkung der Kantone, des Parlamentes und der Öffentlichkeit zum Ziel, grösstmögliche Transparenz und Inklusivität sicherzustellen, klare und vorhersehbare Prozesse zu definieren sowie Vertrauen zu schaffen. Gleichzeitig ist es wichtig, dass der geltenden Kompetenzordnung und den in der Praxis bewährten Prozessen grundsätzlich Rechnung getragen wird und dass in diesem Zusammenhang kein Bürokratiemonster geschaffen wird.
 </t>
   </si>
@@ -2998,8 +2991,8 @@
   </si>
   <si>
     <t xml:space="preserve">Die Verstetigung des Schweizer Kohäsionsbeitrages ist ein integraler Bestandteil des Verhandlungspaketes. Der Verringerung der wirtschaftlichen und sozialen Unsicherheiten kommt grosse Bedeutung für die Stabilität und den Zusammenhalt zwischen allen am Binnenmarkt teilnehmenden Staaten zu. Der Bundesrat betonte in Ihrer Kommission, dass der Schweizer Beitrag weniger als ein finanzieller Aufwand, sondern als eine Investition in wachsende Märkte und stabile wirtschaftliche Beziehungen zu betrachten ist. Wir schaffen damit aussenpolitisch viel Goodwill und verstärken das Interesse am Schweizer Know-how vor Ort. Als Land, das sektoriell in hohem Masse in den Binnenmarkt integriert ist und von diesem mehr als mancher EU-Mitgliedstaat profitiert, hat die Schweiz bisher zweimal einen Kohäsionsbeitrag angenommen und ihm zugestimmt. Zuerst tat sie dies im Rahmen der Bilateralen II als Erweiterungsbeitrag zugunsten der zehn im Jahre 2004 beigetretenen EU-Mitgliedstaaten. Seit 2009 gab es dann einen zweiten Beitrag, dessen Rechtsgrundlage aber im Jahr 2024 ausgelaufen ist. Deshalb braucht es zur Verstetigung nun ein neues Abkommen, ein neues Umsetzungsgesetz und dann im zweiten Schritt auch neue Kredite. Ihre Kommission hatte sich also in dreifacher Hinsicht mit dem Kohäsionsbeitrag zu befassen: mit dem Abkommen zur Verstetigung des Beitrags, mit dem dazugehörenden innerstaatlichen Umsetzungsgesetz und mit drei Verpflichtungskrediten für die dritte Beitragsperiode in den sieben Jahren von 2030 bis und mit 2036 und einer Überbrückung.
-Am wenigsten Diskussionen gab es in Ihrer Kommission über die Genehmigung des Abkommens mit der EU über den regelmässigen finanziellen Beitrag der Schweiz zur Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU. Dieses Abkommen gehört zum Stabilisierungsteil des Pakets. Es ist nicht möglich, separat darüber abzustimmen. Es kann nicht aus dem Paket gebrochen werden. Bekanntlich geht der Paketansatz auf einen Wunsch der Schweiz zurück, und die EU hat diesen Wunsch erfüllt. Entsprechend haben die Schweiz und die EU die Verhandlungen über das Paket je mit einer einzigen Unterschrift abgeschlossen. Das Paket bildet eine Einheit, und Sie stimmen dem Abkommen über die Verträge des Kohäsionsbeitrags also im Rahmen Ihrer Genehmigung des Gesamtpakets "Stabilisierung und Weiterentwicklung der Beziehungen Schweiz-EU (Bilaterale III)" zu. Ihre Kommission empfiehlt Ihnen, mit Ihrem Ja zum Bundesbeschluss über die Stabilisierung von fünf bestehenden Abkommen, zu zwei neuen Binnenmarktabkommen und zu einem neuen Kooperationsabkommen auch dem Abkommen über den Kohäsionsbeitrag zuzustimmen, das eben zum Stabilisierungsteil gehört. 
-Mehr zu reden gab in Ihrer Kommission das innerstaatliche Umsetzungsgesetz, das Bundesgesetz über die Beiträge der Schweiz zur Stärkung der Kohäsion in Europa. Das Kohäsionsbeitragsgesetz hält fest, wie die Schweiz die Programme und Projekte im Rahmen des Beitrags unterstützt. Es regelt die Zusammenarbeit mit Dritten, die Auswahl von Schweizer Partnern, die Finanzierung der Beiträge sowie die Zuständigkeiten. Zudem enthält es Bestimmungen zur Evaluation und Berichterstattung. Ihre Kommission trat an ihrer April-Sitzung auf das neue Kohäsionsbeitragsgesetz ein und befasste sich an zwei weiteren Sitzungen im Mai und August mit den Einzelheiten. Dazu unterbreitete Ihre Kommission der Verwaltung und dem Bundesrat zahlreiche Fragen. Sie betrafen die Konsultation des Parlamentes zu den Themenbereichen, die der Bundesrat dem gemischten Ausschuss vorlegen möchte, die laufende Berichterstattung über den Stand der Umsetzung des jeweils laufenden Beitrages, das Verhältnis des Kohäsionsbeitrags zum gesetzlichen Rahmen über das öffentliche Beschaffungswesen und die Finanzhilfe - der immer vorgeht -, den geplanten Überwachungsmechanismus der Schweiz, damit der Schweizer Beitrag auf allen Ebenen ordnungsgemäss umgesetzt wird, und, ganz wichtig, die Zusammenarbeit mit dem Schweizer Privatsektor und der Wissenschaft, die gezielt gefördert werden soll. Darunter fällt auch der Bereich der Berufsbildung, weil auch Schweizer Unternehmen ein genuines Interesse an Fachkräften vor Ort haben. Zudem wurden auch Fragen zu den in Artikel 11 verankerten periodischen Evaluations- und Wirksamkeitsberichten gestellt.
+Am wenigsten Diskussionen gab es in Ihrer Kommission über die Genehmigung des Abkommens mit der EU über den regelmässigen finanziellen Beitrag der Schweiz zur Verringerung der wirtschaftlichen und sozialen Ungleichheiten in der EU. Dieses Abkommen gehört zum Stabilisierungsteil des Pakets. Es ist nicht möglich, separat darüber abzustimmen. Es kann nicht aus dem Paket gebrochen werden. Bekanntlich geht der Paketansatz auf einen Wunsch der Schweiz zurück, und die EU hat diesen Wunsch erfüllt. Entsprechend haben die Schweiz und die EU die Verhandlungen über das Paket je mit einer einzigen Unterschrift abgeschlossen. Das Paket bildet eine Einheit, und Sie stimmen dem Abkommen über die Verträge des Kohäsionsbeitrages also im Rahmen Ihrer Genehmigung des Gesamtpakets "Stabilisierung und Weiterentwicklung der Beziehungen Schweiz-EU (Bilaterale III)" zu. Ihre Kommission empfiehlt Ihnen, mit Ihrem Ja zum Bundesbeschluss über die Stabilisierung von fünf bestehenden Abkommen, zu zwei neuen Binnenmarktabkommen und zu einem neuen Kooperationsabkommen auch dem Abkommen über den Kohäsionsbeitrag zuzustimmen, das eben zum Stabilisierungsteil gehört. 
+Mehr zu reden gab in Ihrer Kommission das innerstaatliche Umsetzungsgesetz, das Bundesgesetz über die Beiträge der Schweiz zur Stärkung der Kohäsion in Europa. Das Kohäsionsbeitragsgesetz hält fest, wie die Schweiz die Programme und Projekte im Rahmen des Beitrags unterstützt. Es regelt die Zusammenarbeit mit Dritten, die Auswahl von Schweizer Partnern, die Finanzierung der Beiträge sowie die Zuständigkeiten. Zudem enthält es Bestimmungen zur Evaluation und Berichterstattung. Ihre Kommission trat an ihrer April-Sitzung auf das neue Kohäsionsbeitragsgesetz ein und befasste sich an zwei weiteren Sitzungen im Mai und August mit den Einzelheiten. Dazu unterbreitete Ihre Kommission der Verwaltung und dem Bundesrat zahlreiche Fragen. Sie betrafen die Konsultation des Parlamentes zu den Themenbereichen, die der Bundesrat dem gemischten Ausschuss vorlegen möchte, die laufende Berichterstattung über den Stand der Umsetzung des jeweils laufenden Beitrages, das Verhältnis des Kohäsionsbeitrages zum gesetzlichen Rahmen über das öffentliche Beschaffungswesen und die Finanzhilfe - der immer vorgeht -, den geplanten Überwachungsmechanismus der Schweiz, damit der Schweizer Beitrag auf allen Ebenen ordnungsgemäss umgesetzt wird, und, ganz wichtig, die Zusammenarbeit mit dem Schweizer Privatsektor und der Wissenschaft, die gezielt gefördert werden soll. Darunter fällt auch der Bereich der Berufsbildung, weil auch Schweizer Unternehmen ein genuines Interesse an Fachkräften vor Ort haben. Zudem wurden auch Fragen zu den in Artikel 11 verankerten periodischen Evaluations- und Wirksamkeitsberichten gestellt.
 Zusammenfassend lässt sich sagen, dass die Verwaltung all diese Fragen zur Befriedigung Ihrer Kommission beantwortet hat. Namentlich bekräftigte der Bundesrat, dass er bereits über das Parlamentsgesetz verpflichtet ist, Ihre Kommission zu den Prioritäten zu konsultieren, wie er den Kohäsionsbeitrag in seinem Memorandum of Understanding mit der EU umsetzen will. 
 Kritische Fragen löste der überraschende Antrag des Bundesrates aus, von der bewährten Zusammenarbeit des SECO und der DEZA bei der Umsetzung des Schweizer Kohäsionsbeitrages abzuweichen. Der Bundesrat hat die Zerschlagung dieser Zusammenarbeit am 24. Juni 2026 beschlossen, zeitlich gesehen also zwischen unseren beiden Kommissionssitzungen zur Beratung des Umsetzungsgesetzes. Wichtige Fragen konnten damit nicht wirklich vertieft werden. Im Vernehmlassungsverfahren war die gemeinsame Zuständigkeit von SECO und DEZA ja noch unbestritten gewesen. Entsprechend sah der Bundesrat in seiner Botschaft und im Gesetzesentwurf vom März 2026 in Artikel 10 vor, an der gemeinsamen Zuständigkeit von EDA, unserem Aussendepartement, und WBF, unserem Wirtschaftsdepartement, festzuhalten. Das ergibt auch Sinn, geht es doch beim Kohäsionsbeitrag sowohl um Aussenpolitik als auch um Wirtschaftspolitik.
 In der Kommission beantragte der Bundesrat aber, die explizite Erwähnung des EDA in Artikel 10 zu streichen und stattdessen in Artikel 9 und 11 die alleinige Zuständigkeit des SECO zur Umsetzung des Kohäsionsbeitrages vorzusehen. Zwar wurde uns gesagt, das EDA solle auf einer politisch-strategischen Ebene weiterhin mitreden können. Genau dies strich der Bundesrat aber aus seinem ursprünglichen Entwurf, was zu intensiven Diskussionen Anlass gab.
@@ -3049,6 +3042,7 @@
 Per la Commissione di politica estera, bisogna rispettare la Costituzione nell'applicazione anche quando il risultato politico è incerto.
 En conclusion, la majorité de la CPE-E vous invite à appliquer les règles constitutionnelles en vigueur. Les accords relèvent du référendum facultatif. Ils ne remplissent pas les conditions exceptionnelles d'un référendum obligatoire et sui generis. Il n'y a pas de conflit avec l'article 121a de la Constitution fédérale nécessitant une dérogation constitutionnelle.
 Je vous invite, au nom de la majorité de la CPE-E, à suivre le Conseil fédéral, à opter pour le référendum facultatif et à écarter toutes les autres options.
+[VS]
 </t>
   </si>
   <si>
@@ -3343,6 +3337,514 @@
 Fazit: Dieses Paket wird kantonale Zuständigkeiten, konkrete Vollzugsaufgaben und politische Handlungsspielräume im Migrationsbereich, Arbeitsmarktbereich, Sozialbereich, Energiebereich erheblich beeinflussen; die Mitwirkung der Kantone ist wirklich nichts Theoretisches.
 Ich war bis vor einer Weile selbst Regierungsrat und weiss nur zu gut, was es bedeutet, wenn beim Bund neue Vorgaben beschlossen werden, die dann in den Kantonen vollzogen werden müssen. Zwischen einer institutionellen Regelung hier in Bern und ihrer konkreten Umsetzung in einem Kanton liegen manchmal Welten, das muss man leider so sagen. Wenn nun die Rechtsentwicklung vermehrt in einem vorgelagerten europäischen Prozess stattfindet, dann ist entscheidend, wie die Kantone darauf Einfluss nehmen können. Gerade die Tatsache, dass dafür neue Mechanismen geschaffen werden müssen, zeigt doch ganz offensichtlich, dass sich hier etwas im institutionellen Gefüge verschiebt, dass die Architektur eine andere wird, und genau deshalb hat das für mich Verfassungsrang.
 Selbstverständlich bin auch ich als Mitglied dieses Rates an keine Weisung meiner Kantonsregierung gebunden, das gehört zum freien Mandat, aber wenn jetzt über die föderalistische Legitimation gesprochen wird, dann kann ich die klar geäusserte Haltung des Kantons, den ich hier vertrete, nicht einfach ausblenden, das wäre wirklich merkwürdig. Regierungsrat Glarner hat sich ausdrücklich und gut begründet für ein obligatorisches Referendum ausgesprochen. Das Paket Schweiz-EU bringt gewichtige Veränderungen: eine dauerhafte institutionelle Anbindung an künftige EU-Rechtsentwicklungen, einen veränderten Rahmen für die Rechtsetzung, neue Mechanismen und eine konkrete Betroffenheit kantonaler Zuständigkeiten. In ihrer Summe sind diese Veränderungen für mich gewichtig genug, dass dazu neben dem Volk auch die Stände befragt werden müssen, nicht als zusätzliche Hürde, sondern damit diese institutionelle Ordnung, wenn sie angenommen wird, auf dem breiten Fundament steht, das unseren Bundesstaat seit 1848 trägt.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20261001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Land, in dem vier Sprachen gesprochen werden, in dem ganz viele verschiedene Kulturen und Minderheiten friedlich zusammenleben, in dem ein Klima der Toleranz, der Freiheit und der Demokratie herrscht, ist ein wundervolles Land. Unsere direkte Demokratie und der föderalistische Staatsaufbau sind der Boden für Wohlstand und Wohlergehen in der Schweiz. Das hängt damit zusammen, dass ganz viele Menschen daran mitarbeiten. Darum gibt es in unserem Land auch nicht einfach nur Rechte, sondern auch </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Land, in dem vier Sprachen gesprochen werden, in dem ganz viele verschiedene Kulturen und Minderheiten friedlich zusammenleben, in dem ein Klima der Toleranz, der Freiheit und der Demokratie herrscht, ist ein wundervolles Land. Unsere direkte Demokratie und der föderalistische Staatsaufbau sind der Boden für Wohlstand und Wohlergehen in der Schweiz. Das hängt damit zusammen, dass ganz viele Menschen daran mitarbeiten. Darum gibt es in unserem Land auch nicht einfach nur Rechte, sondern auch Pflichten, wie es der Initiant formuliert hat. Diese Verbindung zwischen Bürgerrechten und Bürgerpflichten ist für das Funktionieren unseres Landes ganz elementar. 
+Wir müssen aufpassen, da bin ich genau gleicher Meinung wie der Initiant, dass wir hier nicht zunehmend mit Rosinenpickerei konfrontiert sind. Die Schweiz ermöglicht allen - ob Schweizer Bürger oder nicht - Rechte in einem Umfang, den man in keinem anderen Land kennt. Wer das Stimm- und Wahlrecht in der Schweiz besitzt, kann während eines Jahres häufiger abstimmen, als das die meisten anderen Menschen auf dieser Welt in ihrem ganzen Leben tun können. Die Schweiz ermöglicht In- und Ausländern ein Maximum an Freiheit. In der Schweiz dürfen Ausländer demonstrieren, sie dürfen ihre politische Meinung äussern, sie dürfen Petitionen unterschreiben. In vielen anderen Ländern auf der Welt würden sie dafür verhaftet, kämen ins Gefängnis oder hätten Nachteile zu befürchten. 
+Wir dürfen stolz darauf sein, dass die Mündigkeit und die Freiheit jedes Einzelnen bei uns einen grossen Stellenwert haben. Wir nehmen jeden Einzelnen ernst, ob er Schweizer Bürger ist oder nicht. Bei uns kommt es auch nicht darauf an, welche Sprache er spricht, welche politische Ausrichtung, welche sexuelle Orientierung, welche Religion er hat und welche kulturellen Bräuche er pflegt. Wichtig ist natürlich die Einhaltung gewisser Grundregeln. Wir stellen fest, da möchte ich meinen Vorredner unterstützen, dass hier ein gewisser Handlungsbedarf besteht. 
+Wir müssen wieder viel genauer darauf schauen, wie und wo der Schweizer Pass vergeben wird - und ob die Integration auch tatsächlich stattgefunden hat. Die Integration ist keine Staatsaufgabe, wie man bisweilen und auch in diesem Saal hört. Der Staat hat keine Pflicht, hier Mittel bereitzustellen, um diese Integration zu fördern. Nein, es ist vielmehr eine Obliegenheit derjenigen, die zu uns kommen, die hier leben und partizipieren möchten. Darum ist es ganz wichtig, darauf zu schauen, dass diese Integration stattgefunden hat und die Einbürgerung allenfalls nach erfolgreich abgeschlossener Integration stattfindet. Tatsächlich beobachten wir immer wieder Fälle, in denen Leute verschiedene Pässe haben, und im entscheidenden Moment der Schweizer Pass dann eben nicht der wichtigste ist, sondern man sich vielleicht seinem ursprünglichen Heimatland doch noch mehr verpflichtet fühlt - im kritischeren Fall sogar einer anderen Rechtsordnung als der hier geltenden. 
+Auf diese Punkte sollten wir schauen, und aus diesem Grund bitte ich Sie auch, diese Initiative zu unterstützen und ihr Folge zu geben. Es kann nicht sein, dass sich jemand in der Schweiz einbürgern lässt, weil es einfach noch nett ist, auch noch den Schweizer Pass zu haben, und man hier von gewissen Leistungen profitieren kann. 
+Um dies zu vermeiden, auch um Loyalitätskonflikte zu vermeiden, und um sicherzustellen, dass die Leute, die hier leben und den Schweizer Pass haben, eben nicht nur die Rechte, sondern vor allem auch die Pflichten kennen, bitten wir Sie, dieser parlamentarischen Initiative Folge zu geben. Es geht ja um Folgegeben, um die Frage, ob Handlungsbedarf besteht. Wir meinen Ja. Geben Sie Folge, damit wir uns in einem zweiten Schritt etwas genauer mit dieser Thematik auseinandersetzen können.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strupler Manuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zum Glück habe ich nicht auch noch eine Krawatte, sonst hätte ich sie auch anziehen müssen.
+Zu meiner parlamentarischen Initiative: gleiche Rechte und Pflichten für alle - kein Doppelbürgerrecht für Eingebürgerte. Die Schweiz hat sich nicht, wie die meisten europäischen Staaten, um eine Sprache herum geformt, sondern um die politischen Rechte und Pflichten, die den Kern der Nation bilden. Deshalb ist es typisch schweizerisch, dass wir eine Willensnation sind und als solche bezeichnet werden.
+Mit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zum Glück habe ich nicht auch noch eine Krawatte, sonst hätte ich sie auch anziehen müssen.
+Zu meiner parlamentarischen Initiative: gleiche Rechte und Pflichten für alle - kein Doppelbürgerrecht für Eingebürgerte. Die Schweiz hat sich nicht, wie die meisten europäischen Staaten, um eine Sprache herum geformt, sondern um die politischen Rechte und Pflichten, die den Kern der Nation bilden. Deshalb ist es typisch schweizerisch, dass wir eine Willensnation sind und als solche bezeichnet werden.
+Mit der seit 1992 unbegrenzten Ausweitung der Mehrstaatigkeit gibt es aber zwei Gruppen von Schweizer Bürgern: solche mit nur einem Pass und solche mit zwei oder mehreren Staatszugehörigkeiten. Somit haben nicht alle die gleichen Rechte und Pflichten; die Gruppe der Doppelbürger geniesst ungerechtfertigterweise Vorteile und profitiert teilweise von zusätzlichen politischen Möglichkeiten, also zusätzlichen Wahl- und Mitbestimmungsmöglichkeiten in anderen Staaten. Das ist ungerecht, und diese Ungleichheit möchte ich mit meiner parlamentarischen Initiative einschränken.
+Die Gruppe der Doppelbürger wächst rasant; das sieht man, wenn man zum Beispiel auf Genf schaut. In Genf hat schon mehr als die Hälfte der Bürgerinnen und Bürger zwei oder mehrere Staatszugehörigkeiten. Nicht nur ich möchte das ändern, sondern auch viele Personen kommen immer wieder mit dieser Forderung auf mich zu. Sie stören sich berechtigterweise an der Rosinenpickerei der Doppelbürger. Es ist schliesslich eine bewusste und eine freiwillige Entscheidung, das Schweizer Bürgerrecht anzunehmen. Wie bei vielen Entscheidungen im Leben soll es auch hier gelten: Man kann nicht den Fünfer und das Weggli haben und am liebsten noch die Bäckerstochter gratis dazu.
+Wer die relativ leichten Bedingungen für eine Einbürgerung in der Schweiz erfüllt, soll sich klar zur Schweiz und nur zur Schweiz bekennen und somit freiwillig - oder zukünftig nicht mehr freiwillig - auf den bisherigen Pass verzichten. Für alle anderen reicht in der Schweiz die Niederlassungsbewilligung. Einbürgerungen, die nur dazu dienen, Vorteile, Sicherheiten und Privilegien beider Staatsangehörigkeiten zu erlangen, führen zu Loyalitätskonflikten und untergraben - und das ist ganz wichtig - das uralte demokratische Prinzip von einer Person und einer Stimme.
+Die aktive Einbürgerung soll, wie ich bereits sagte, eine klare Entscheidung für die Schweiz sein. Sie darf nicht zu 50 Prozent oder mehr mit anderen Staatszugehörigkeiten geteilt werden, sondern muss aus Überzeugung, Loyalität und als Abschluss einer erfolgreichen Integration erfolgen. Deshalb sollen bei der Einbürgerung aktiv keine neuen Doppelbürgerrechte mehr geschaffen werden, so wie es bis 1992 bei uns der Fall war und ziemlich unüberlegt erst in der parlamentarischen Beratung über Bord geworfen wurde. In der Zeit, als die Berliner Mauer gefallen ist, glaubte man natürlich auch an den ewigen Weltfrieden. Leider wissen wir es heute besser.
+Unser altes System kennen übrigens auch unsere Nachbarländer Österreich und Liechtenstein. Deutschland hat das erst vor Kurzem, im Jahr 2024, aufgegeben. Wichtig ist: Wer von Geburt an binationale Eltern hat und daher ohne eigenes Zutun über zwei Staatsbürgerschaften verfügt, ist von dieser Regel nicht betroffen; ebenso Auslandschweizer, die eine weitere Staatsbürgerschaft erlangen.
+Ich bin Ihnen dankbar, wenn Sie heute den ersten Schritt machen und zum bewährten und fairen System zurückkehren, das damals, wie gesagt, sehr unüberlegt in der parlamentarischen Beratung über den Haufen geworfen wurde, wodurch wir diese Situation bei den Doppelbürgern geschaffen haben. Ich habe es gesagt: Es sind immer mehr, die Anzahl der Doppelbürger steigt.
+Ich möchte nicht, dass niemand mehr Schweizer Bürger oder Bürgerin werden kann. Ich möchte aber, dass alle in der Schweiz die gleichen Rechte haben. Man soll nicht Bürger werden, nur um die Vorteile beider Staatszugehörigkeiten zu nutzen, sondern aus Überzeugung und aus dem Willen heraus, in der Schweiz mitzubestimmen, mitzugestalten und die Schweiz gemeinsam mit allen anderen in eine erfolgreiche Zukunft zu führen.
+Ich danke Ihnen, wenn Sie meine parlamentarische Initiative unterstützen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Sprecher der Staatspolitischen Kommission darf ich Ihnen aus der Sitzung vom 27. Februar 2026 berichten. Wir haben diese parlamentarische Initiative, die den Bundesrat beauftragt, das Bürgerrechtsgesetz so anzupassen, dass künftig bei Einbürgerungen in der Schweiz keine Doppelbürgerschaften mehr möglich sind, vorgeprüft. Wer sich einbürgern lässt, müsste dann eben eine Nichtigkeitserklärung oder einen Rückzug des ehemaligen Heimatrechts beantragen. Nicht davon betroffen wären Einbürgerungen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Sprecher der Staatspolitischen Kommission darf ich Ihnen aus der Sitzung vom 27. Februar 2026 berichten. Wir haben diese parlamentarische Initiative, die den Bundesrat beauftragt, das Bürgerrechtsgesetz so anzupassen, dass künftig bei Einbürgerungen in der Schweiz keine Doppelbürgerschaften mehr möglich sind, vorgeprüft. Wer sich einbürgern lässt, müsste dann eben eine Nichtigkeitserklärung oder einen Rückzug des ehemaligen Heimatrechts beantragen. Nicht davon betroffen wären Einbürgerungen durch Geburt oder Ehe oder eben Fälle, in denen die familiäre Beziehung eine andere Grundvoraussetzung geschaffen hat.
+Ich kann Ihnen vorab das Resultat sagen: Die Staatspolitische Kommission hat mit 14 zu 8 Stimmen bei 1 Enthaltung der parlamentarischen Initiative keine Folge gegeben.
+Zuerst zum Hintergrund: Was der Initiant gesagt hat, ist richtig; 1992 wurde das Recht geändert. Es galt ab dann keine Einschränkung mehr, welche zu einem Verzicht auf die bisherigen Staatsbürgerschaften geführt hätte. Schweizer Bürger, welche im Ausland eine andere Staatsangehörigkeit erwerben, müssen nicht auf das Schweizer Bürgerrecht verzichten - das war eben auch ein Grund dafür, dass man diese Gleichschaltung erzielt hatte. Es sei denn, und das ist der Nachsatz, der neue Heimatstaat - Österreich wurde genannt - würde dies verlangen. 
+Auch noch wichtig ist, dass man zu diesem Zeitpunkt nochmals definiert hat, was eigentlich eine Doppelbürgerschaft bezüglich des Militärdienstes bedeutet. Auf der Website des SEM steht geschrieben: "Der Militärdienst wird in der Regel in demjenigen Staat geleistet, in dem der Bewerber im Zeitpunkt der Aushebung wohnhaft ist. Wer im Ausland Militärdienst geleistet hat, wird in der Schweiz nicht mehr aufgeboten." 
+Schauen wir uns nun noch die Tendenz an: 1992, als diese Gesetzesänderung in Kraft trat, akzeptierten gesamthaft betrachtet im Durchschnitt etwa 50 Prozent der Staaten Doppelbürgerschaften - in Europa waren es 51,3 Prozent, in Amerika, als weiteres Beispiel, 57 Prozent. Heute, es gibt einen Statusbericht von 2015, kennen weltweit durchschnittlich etwa 75 Prozent der Staaten diese Regel; in Europa sind wir bei rund 73 Prozent und in Amerika bei 91 Prozent. Sie sehen also, dass sich der Umgang mit Doppelbürgerschaften weltweit verändert hat.
+Wie wird man eingebürgert? Auch diesbezüglich hat es eine grosse Veränderung gegeben. Waren es in früheren Jahren vielleicht zwei von zehn Fällen, in denen jemand durch Geburt Schweizer wurde, sind es heute nahezu vier. Auch hier hat sich eine grosse Anpassung ergeben. 
+Wenn ich Ihnen nun aus der Kommission berichte, muss ich mich leider kurzhalten, denn die wesentlichste Feststellung war diejenige, dass der Nationalrat im Jahr 2021 der parlamentarischen Initiative Reimann Lukas 20.501, "Optionsmodell statt automatisches Doppelbürgerrecht", mit 136 zu 49 Stimmen keine Folge gegeben hat. Das Thema war damals also auf dem Tisch, und der Nationalrat hat entschieden, dass kein Handlungsbedarf besteht. Aus diesem Grund fiel die ganze Diskussion in der Staatspolitischen Kommission relativ kurz aus. 
+Ich kann also zusammenfassen, dass der Handlungsbedarf seitens der Staatspolitischen Kommission nicht gesehen wird. Wir bitten Sie aus diesem Grund und aufgrund der Erkenntnisse aus den früheren Diskussionen, dieser parlamentarischen Initiative keine Folge zu geben.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Weniger Bürokratie bei Mehrfachtätern ohne ordentlichen Wohnsitz- oder Aufenthaltsstatus. Effiziente Strafverfolgung ermöglichen": Mit dieser Motion wird gefordert, dass bei Verfahren gegen Personen ohne Wohnsitz in der Schweiz oder mit unsicherem Aufenthaltsstatus die Verfolgung von Seriendelikten einfacher wird. Dazu soll bei losen Tätergruppierungen die Verpflichtung zur Überweisung aller Verfahren an die zuerst tätige Staatsanwaltschaft gelockert werden. Normalerweise ist immer die Staatsan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Weniger Bürokratie bei Mehrfachtätern ohne ordentlichen Wohnsitz- oder Aufenthaltsstatus. Effiziente Strafverfolgung ermöglichen": Mit dieser Motion wird gefordert, dass bei Verfahren gegen Personen ohne Wohnsitz in der Schweiz oder mit unsicherem Aufenthaltsstatus die Verfolgung von Seriendelikten einfacher wird. Dazu soll bei losen Tätergruppierungen die Verpflichtung zur Überweisung aller Verfahren an die zuerst tätige Staatsanwaltschaft gelockert werden. Normalerweise ist immer die Staatsanwaltschaft zuständig, die zuerst tätig wurde. Bei kleinen Kantonen und bei vielen kleinen Delikten an verschiedenen Orten entsteht oft ein nicht bewältigbarer Aufwand. Auch die Auseinandersetzungen zwischen den kantonalen Gerichten verlängern die gerichtlichen Beurteilungen sehr stark. Eine effiziente Strafverfolgung ist hier absolut sinnvoll, daher sollte die Abtrennung der Verfahren einzelner Täter aus einer Tätergruppierung ermöglicht werden.
+Die Strafprozessordnung soll hier eine Richtschnur dazu vorlegen, unter welchen Umständen die Trennung von Verfahren möglich ist. Oft handelt es sich um abgewiesene Asylsuchende oder andere mobile Personen ohne festen Wohnsitz in der Schweiz.
+Die Mehrheit der Kommission für Rechtsfragen steht voll und ganz hinter diesem Motionsanliegen, denn es besteht Handlungsbedarf. Die Verfahrensökonomie ist zentral. Eine gezielte Strafverfolgung muss hier im Vordergrund stehen; die Mehrheit der Kommission für Rechtsfragen ist deshalb klar dafür.
+Die Minderheit argumentierte, dies könne kostspielig sein, konnte dies aber nicht belegen. Eine effiziente Strafverfolgung kann die Kosten auch verringern, da die Verfahren vermutlich kürzer wären und Synergien genutzt werden könnten. Bei losen Tätergruppierungen wäre eine gewisse Flexibilität definitiv sinnvoll.
+Daher unterstützen wir diese Motion grossmehrheitlich, wie es auch der Bundesrat tut. Eine Vereinfachung dient allen. Besten Dank für die Unterstützung.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsere Rechtsordnung gilt für alle Personen in unserem Land. In der Schweiz gibt es keinen Platz für parallele Normen oder Rechtssysteme. Wir wollen keine Parallelgesellschaften. Das geltende Asyl- und Ausländerrecht trägt diesem Grundsatz Rechnung, und so umfassen die Integrationskriterien unter anderem die Beachtung der öffentlichen Sicherheit und Ordnung sowie die Respektierung der Werte der Bundesverfassung. Die einzelnen Anforderungen werden auf Verordnungsstufe weiter präzisiert. Wer bei u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsere Rechtsordnung gilt für alle Personen in unserem Land. In der Schweiz gibt es keinen Platz für parallele Normen oder Rechtssysteme. Wir wollen keine Parallelgesellschaften. Das geltende Asyl- und Ausländerrecht trägt diesem Grundsatz Rechnung, und so umfassen die Integrationskriterien unter anderem die Beachtung der öffentlichen Sicherheit und Ordnung sowie die Respektierung der Werte der Bundesverfassung. Die einzelnen Anforderungen werden auf Verordnungsstufe weiter präzisiert. Wer bei uns lebt, muss unsere Verfassung und unsere Gesetze respektieren. Das ist so, ob Sie die Motion annehmen oder nicht. 
+Zurzeit haben wir keine Hinweise darauf, dass die bestehenden Rechtsgrundlagen und Instrumente nicht ausreichen würden, um die Entstehung von Parallelgesellschaften zu verhindern. Die Motion bietet jedoch die Möglichkeit, die geltenden Grundlagen noch einmal gesamthaft zu überprüfen. Dabei soll festgestellt werden, ob sie das Anliegen der Motion bereits ausreichend abdecken oder ob punktuelle Präzisierungen angezeigt wären. 
+In diesem Sinne wäre der Bundesrat bereit gewesen, diese Prüfung vorzunehmen, wenn aus Ihrem Rat aber kein Minderheitsantrag erfolgt, verzichtet der Bundesrat darauf.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besten Dank, Herr Schilliger, das ist wirklich eine wichtige Frage. Der Bundesrat hat seine Aufgaben mit grösster Motivation angepackt. Als ich vor über zwei Jahren anfing, gab es 10 000 Pendenzen; jetzt sind es noch 2500. Ich glaube, dass wir sie bis Ende Jahr abgearbeitet haben werden und dass dann an jedem Asylgesuch gearbeitet wird. Diese Reduktion der Pendenzen war möglich, obwohl der Bundesrat beim SEM auch Einsparungen vornahm; über 150 Stellen mussten in diesem und im letzten Jahr gestri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besten Dank, Herr Schilliger, das ist wirklich eine wichtige Frage. Der Bundesrat hat seine Aufgaben mit grösster Motivation angepackt. Als ich vor über zwei Jahren anfing, gab es 10 000 Pendenzen; jetzt sind es noch 2500. Ich glaube, dass wir sie bis Ende Jahr abgearbeitet haben werden und dass dann an jedem Asylgesuch gearbeitet wird. Diese Reduktion der Pendenzen war möglich, obwohl der Bundesrat beim SEM auch Einsparungen vornahm; über 150 Stellen mussten in diesem und im letzten Jahr gestrichen werden. Wir werden es also schaffen, da sind wir zuversichtlich.
+Wenn es mehr Fälle gibt, werden tatsächlich mehr Fälle ans Bundesverwaltungsgericht überwiesen, und dort ist ein neuer Engpass entstanden. Ich bin als Mitglied der Exekutive nicht befugt, dem Bundesgericht oder irgendeinem Gericht zu sagen, was es zu tun hat. Das ist Aufgabe des Parlamentes - das Parlament hat die Oberaufsicht über die Gerichte und muss zusammen mit den Gerichten dafür sorgen, dass diese ihre Aufgaben erfüllen, Pendenzen rasch abbauen und genügend Personal dafür zur Verfügung stellen.
+Was ich gesagt habe, ist Folgendes: Innerhalb der Asylstrategie schauen wir auch, ob gesetzliche Anpassungen möglich sind, die die Verfahren zumindest beschleunigen können. Was wir in diesem Rahmen vorschlagen werden, kann ich Ihnen jetzt noch nicht sagen; dazu ist es noch zu früh. Es ist aber eine Piste, die wir verfolgen, weil wir die Einschätzung teilen, dass zu lange Wartezeiten bei Asylentscheiden für die Gesellschaft, aber auch für die Betroffenen sehr schlecht sind.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie gesagt, wir schauen das ganz genau an, was die Gründe sind usw. Vor dem Jahr 2015 gab es in Dänemark während vieler Jahre anders als in der Schweiz jährlich etwa 5000 Asylgesuche. Deren Zahl ist dann sehr stark angestiegen, weil Schweden wegen seines Einbürgerungssystems für viele Asylsuchende sehr attraktiv wurde. In Schweden konnte man als Asylsuchender nach zwei Jahren, wenn man Arbeit hatte, eingebürgert werden. Das hat tatsächlich dazu geführt, dass Schweden plötzlich auch eine Destinat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie gesagt, wir schauen das ganz genau an, was die Gründe sind usw. Vor dem Jahr 2015 gab es in Dänemark während vieler Jahre anders als in der Schweiz jährlich etwa 5000 Asylgesuche. Deren Zahl ist dann sehr stark angestiegen, weil Schweden wegen seines Einbürgerungssystems für viele Asylsuchende sehr attraktiv wurde. In Schweden konnte man als Asylsuchender nach zwei Jahren, wenn man Arbeit hatte, eingebürgert werden. Das hat tatsächlich dazu geführt, dass Schweden plötzlich auch eine Destination für sehr viele Asylsuchende wurde, und Dänemark, das auf dem Weg nach Schweden liegt, wurde dann, so wie wir, für viele Asylsuchende quasi zu einem Durchgangsland. Nachdem Schweden seine Politik massiv verändert hat, sind auch die Zahlen in Dänemark wieder stark zurückgegangen. Das ist ein Grund, aber sicher nicht der einzige; da gibt es ganz viele. Wir schauen das an, wie gesagt. Das sind sicher wichtige Faktoren im Zusammenhang mit den Entwicklungen in Dänemark.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich beginne mit den guten Nachrichten. Die Asylzahlen in der Schweiz haben in diesem Jahr um rund 20 Prozent abgenommen. Der Bundesrat hat seine Prognose für dieses Jahr korrigiert und um 3000 Gesuche gesenkt. Wenn diese Prognose eintrifft, dann haben wir Ende dieses Jahres 27 Prozent weniger Asylgesuche als noch 2023. Ebenfalls erstaunlich stark zurückgegangen sind die irregulären Einwanderungen. Die Aufgriffe sind gegenüber dem Vorjahr um 50 Prozent zurückgegangen. Das heisst einerseits, der S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich beginne mit den guten Nachrichten. Die Asylzahlen in der Schweiz haben in diesem Jahr um rund 20 Prozent abgenommen. Der Bundesrat hat seine Prognose für dieses Jahr korrigiert und um 3000 Gesuche gesenkt. Wenn diese Prognose eintrifft, dann haben wir Ende dieses Jahres 27 Prozent weniger Asylgesuche als noch 2023. Ebenfalls erstaunlich stark zurückgegangen sind die irregulären Einwanderungen. Die Aufgriffe sind gegenüber dem Vorjahr um 50 Prozent zurückgegangen. Das heisst einerseits, der Schutz der Schengen-Aussengrenzen funktioniert; andererseits funktionieren aber auch die Massnahmen, die wir in diesem Bereich zum Schutz, zur Sicherheit unserer Bevölkerung ergriffen haben. Auch sie führen zu guten Zahlen. Ich komme noch darauf zurück.
+Trotzdem, obwohl wir in all diesen Bereichen heute bessere Zahlen haben, hat sich der Bundesrat dazu entschlossen, mit den Kantonen und den Gemeinden zusammen eine Asylstrategie zu erarbeiten. Damit wollen wir weitere Massnahmen ergreifen können und das Asylsystem in diesem Sinne stärken; und zwar, Herr Schmid, für die Bevölkerung unseres Landes. Für diese wollen wir eine echte Asylstrategie.
+Wir machen das mit Kantonen, Städten und Gemeinden zusammen. Warum? Wir produzieren ganz konkrete Ergebnisse, und eines dieser Ergebnisse ist ein Revisionspaket im Asyl- und Ausländerrecht; dazu komme ich gleich. Von den sechs Zielen der Motion Germann deckt diese Asylstrategie bereits heute fünf ab.
+Erstens wollen wir die Zahl unbegründeter Asylgesuche weiter senken. Dazu entwickeln wir ein vorgelagertes Zuständigkeitsverfahren. Künftig wird das SEM vorab klären, ob überhaupt ein Schutzbedarf im Sinne des Asylgesetzes besteht. Das betrifft alle Personen, die voraussichtlich keines Schutzes durch die Schweiz bedürfen, wie Personen aus Ländern mit sehr tiefer Asylgewährungsquote, Personen aus EU-EFTA-Staaten und solche, die bereits in einem EU-EFTA-Staat Schutz erhalten haben. Besteht kein Schutzinteresse, geht das SEM gar nicht auf das Gesuch ein. Diese Personen erhalten in der Folge auch keinen Zutritt zu den Bundesasylzentren. Basierend auf den Erfahrungen der vergangenen Jahre gehen wir davon aus, dass das etwa 20 Prozent der Asylgesuche betreffen würde.
+Ein solches Verfahren hat aber Folgen für alle drei Staatsebenen. Wenn kein Asylgesuch vorliegt, kommt das Ausländer- und Integrationsgesetz zur Anwendung. Das heisst, die Kantone sind dann für diese Personen zuständig. Und darum entwickeln wir diese Lösung gemeinsam mit den Kantonen, den Gemeinden und den Städten. Die Strategie darf und will Probleme nicht einfach vom Bund zu den Kantonen und Gemeinden verschieben. Das übergeordnete Ziel des vorgelagerten Zuständigkeitsverfahrens ist es, dass Personen ohne Aussicht auf Schutz gar nicht mehr in die Schweiz kommen. Damit werden alle drei Staatsebenen entlastet.
+Zweitens beschleunigen wir die Verfahren weiter. Wir überarbeiten unter anderem das Konzept der sicheren Herkunftsstaaten, und wir schauen auch auf die Beschwerdeverfahren. Konkret analysieren wir die Fristen und die Pendenzen beim Bundesverwaltungsgericht. Das Gericht ist unabhängig, aber für die betroffenen Menschen und für das Gesamtsystem spielt es keine Rolle, wo eine Pendenz liegt. 
+Drittens stärken wir die Sicherheit. Bund und Kantone führen die gemeinsame "Taskforce Intensivtäter" aus dem Asyl- und Ausländerbereich weiter. Wir schrauben an den ausländerrechtlichen Zwangsmassnahmen. Das Ziel ist klar: Verbesserungen beim Wegweisungsvollzug und konsequentes Handeln der Behörden gegenüber diesen Intensivtätern. 
+Viertens - da kommt gleich der nächste Punkt - wollen wir mehr ausreisepflichtige Personen zurückführen. Die Schweiz verfügt über ein gut funktionierendes Migrationssystem mit Herkunftsstaaten. Wir haben mit 60 Staaten Partnerschaften etabliert, und wir bauen das weiter aus. In den kommenden Jahren werden wir uns in diesem Saal auch mit der Übernahme der EU-Rückkehrverordnung befassen. Diese Schengen-Weiterentwicklung ergänzt unsere Arbeit im Rahmen der Asylstrategie.
+Vielleicht noch schnell ein Wort zu Dänemark; es ist schon wichtig, dass ich das hier auch sage. Wir schauen genau, was die Unterschiede zwischen der Schweiz und Dänemark sind. Aber einen Hinweis darf ich Ihnen jetzt schon machen. Dänemark hatte schon immer viel tiefere Asylzahlen als die Schweiz. Sie sind in Dänemark hochgeschnellt, wie bei uns, und erreichten 2023 die Spitze, um dann wieder zurückzugehen, auch wie bei uns. Der entscheidende Unterschied zwischen Schweiz und Dänemark ist die Tatsache, dass Dänemark hinter den Migrationsströmen der Asylsuchenden liegt. Und die Schweiz liegt mittendrin. Das ist ein ganz entscheidender Unterschied. Nichtsdestotrotz schauen wir aufgrund einer Motion, die angenommen wurde, die Unterschiede ganz genau an und werden Ihnen auch sagen, wo es allenfalls Anpassungsmöglichkeiten gibt. 
+Nun zu den Kosten: Weniger offensichtlich begründete Gesuche, weniger Pendenzen und schnellere Verfahren entlasten die Strukturen für alle. Deshalb verfolgen wir diese Strategie. Nur bei einem Punkt besteht eben ein Unterschied zwischen der laufenden Asylstrategie und dieser Motion. Die Asylstrategie enthält kein Ziel zur Einschränkung des Familiennachzuges. Auch Ihre Kommission hat diesen Punkt der Motion nicht unterstützt. Das Anliegen haben wir in der aktuellen Legislatur mehrmals diskutiert. Sowohl Bundesrat als auch Parlament haben es abgelehnt, den Familiennachzug weiter einzuschränken. 
+Zur Umsetzung der Asylstrategie müssen wir einzelne Gesetzesbestimmungen anpassen. Wo gesetzgeberischer Handlungsbedarf besteht, schlägt Ihnen der Bundesrat noch dieses Jahr Änderungen am Asylgesetz und am Ausländer- und Integrationsgesetz vor. Die Vernehmlassung ist für Ende 2026 vorgesehen. Die vorliegende Motion verlangt eine neue, grundlegende Strategie. Eine breit abgestützte Strategie liegt aber bereits vor. Über das entsprechende Gesetzespaket werden wir im nächsten Jahr diskutieren. Eine zweite Strategie bringt uns deshalb weder schneller ans Ziel noch kann sie bessere Vorschläge machen. Der Bundesrat beantragt Ihnen deshalb, die Motion 25.4674 abzulehnen.
+Jetzt komme ich zum Postulat Ihrer Staatspolitischen Kommission. Das Postulat verlangt mehr Sicherheit und mehr Integration. Es verlangt zudem Anpassungen im Asyl- und Ausländerrecht. Der Bundesrat, wie ich dargelegt habe, teilt dieses Anliegen, denn es ist durch das politische Mandat der Asylstrategie thematisch abgedeckt. Das Postulat fordert keine neue Strategie; es ergänzt die laufenden Arbeiten. Wir können die Ideen des Parlamentes hier direkt in das Gesetzgebungspaket, an dem wir im Moment arbeiten, einfliessen lassen. Die kantonalen Konferenzen sowie der Schweizerische Gemeinde- und der Städteverband tragen das mit. Es ist eine Strategie der Bevölkerung für die Bevölkerung.
+Der Bundesrat beantragt Ihnen deshalb, das Postulat 26.4062 anzunehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es kommt darauf an, wo auf der Asylroute sich ein Staat befindet. Wir sind nun einmal mitten in Europa. Früher kamen Asylsuchende noch sehr häufig von Osten. Diese Migrationsroute ist aber nicht mehr so attraktiv. Es kommen immer noch sehr, sehr viele von Süden und wollen in den Norden. Das ist eine Realität, der wir begegnen müssen. Schweden war innerhalb von Europa wegen des Einbürgerungssystems wirklich ausserordentlich attraktiv. Schweden hat dieses System in der Zwischenzeit korrigiert, hat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es kommt darauf an, wo auf der Asylroute sich ein Staat befindet. Wir sind nun einmal mitten in Europa. Früher kamen Asylsuchende noch sehr häufig von Osten. Diese Migrationsroute ist aber nicht mehr so attraktiv. Es kommen immer noch sehr, sehr viele von Süden und wollen in den Norden. Das ist eine Realität, der wir begegnen müssen. Schweden war innerhalb von Europa wegen des Einbürgerungssystems wirklich ausserordentlich attraktiv. Schweden hat dieses System in der Zwischenzeit korrigiert, hat also die entsprechenden Beschlüsse gefasst. Die Schweden waren in der Schweiz, um sich zu informieren, wie wir einbürgern. Sie haben sich also an uns orientiert, wie man das System handhaben soll. Umgekehrt konnte ich von den Schweden bisher noch nichts lernen.
+[VS]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Da ich als Kommissionssprecher für zwei Vorstösse fünf Minuten Redezeit habe, muss ich mich auf die wichtigsten Punkte beider Vorstösse und vor allem auf die Beschlüsse der Kommission beschränken.
+Die Motion Germann wurde im Ständerat am 10. März 2026 mit 27 zu 15 Stimmen bei 1 Enthaltung angenommen. Die Kommission hat in ihrer Beratung fünf von sechs Zielen dieser Motion zugestimmt: dem Ziel 1, "Deutliche Reduktion der Asylgesuche", mit 13 zu 11 Stimmen bei 1 Enthaltung; dem Ziel 2, "Deutliche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Da ich als Kommissionssprecher für zwei Vorstösse fünf Minuten Redezeit habe, muss ich mich auf die wichtigsten Punkte beider Vorstösse und vor allem auf die Beschlüsse der Kommission beschränken.
+Die Motion Germann wurde im Ständerat am 10. März 2026 mit 27 zu 15 Stimmen bei 1 Enthaltung angenommen. Die Kommission hat in ihrer Beratung fünf von sechs Zielen dieser Motion zugestimmt: dem Ziel 1, "Deutliche Reduktion der Asylgesuche", mit 13 zu 11 Stimmen bei 1 Enthaltung; dem Ziel 2, "Deutliche Reduktion der Asylkosten", mit 13 zu 11 bei 1 Enthaltung; dem Ziel 3, "Eindämmung der Asylkriminalität", mit 16 zu 8 Stimmen bei 1 Enthaltung; dem Ziel 4, "Beschleunigung der Asyl- und Beschwerdeverfahren", mit 17 zu 8 Stimmen; dem Ziel 6, "Erhöhung der Rückführungen", mit 15 zu 8 Stimmen bei 2 Enthaltungen.
+Beim Ziel 5, "Einschränkung des Familiennachzugs", beantragt Ihnen die Kommission mit 12 zu 11 Stimmen bei 2 Enthaltungen die Ablehnung. Hier ist die Mehrheit der Auffassung, dass dieses Ziel dem in der Verfassung verankerten Recht auf Familie widerspricht, das unter anderem auch den Bestand einer Familie schützt.
+Mit dieser Einschränkung beim Ziel 5 teilt die Kommission mit dem Bundesrat die Auffassung, dass die Ziele kompatibel bis identisch mit den Zielen der Asylstrategie 2027 sind - im Unterschied zur Begründung des Motionärs, der eine neue Asylstrategie mit diesen Zielen verlangt. Die politische Auseinandersetzung dreht sich deshalb im Grunde nicht um diese Ziele, sondern um die Beurteilung, wie diese erreicht werden sollen, bzw. wann sie erreicht sind.
+Ein Beispiel dazu: Die Anzahl Asylgesuche in der Schweiz nimmt seit zwei Jahren ab. 2023 hatten wir ungefähr 30 000 Gesuche, 2024 waren es etwa 27 000 Gesuche und 2025 noch gut 25 000 Gesuche. Auch für 2026, dieses Jahr, rechnet das SEM mit weniger Asylgesuchen, nämlich um die 22 000. In knapp drei Jahren konnte also eine Reduktion von rund 25 Prozent umgesetzt werden. Das heisst, die Auseinandersetzung zum Ziel einer deutlichen Reduktion der Asylgesuche liegt in der Beurteilung, ob das als "deutlich reduziert" gilt.
+Deshalb hat die Kommissionsmehrheit entschieden, nebst der Unterstützung dieser Motion in einem Postulat konkrete weitere Massnahmen zur Umsetzung der Strategie zu fordern. Dabei geht es um vier Punkte:
+1. Sicherheit: Es müssen mehr Massnahmen gegen die Minderheit von Asylsuchenden getroffen werden, die die öffentliche Sicherheit gefährdet und kriminell wird. Beispielsweise sollen die Anordnung von Administrativhaft und der Vollzug der Wegweisung erleichtert werden. Das Parlament hat diesbezüglich bereits Motionen angenommen, die jetzt umgesetzt werden sollen.
+2. Einführung eines neuen Zuständigkeitsverfahrens: Die Idee dieses in Europa neuen Verfahrens ist es, dass eine Person ohne Asylgründe gar nicht erst ins Asylsystem gelangt. Nach Schätzungen des SEM handelt es sich bei den Asylgesuchen bei rund 20 Prozent um offensichtlich unbegründete Gesuche. Das wäre eine potenziell sehr wesentliche Entlastungsmöglichkeit des Asylsystems.
+3. Angleichung des Schutzstatus S und der vorläufigen Aufnahme: Dies mit dem Ziel, einer Forderung insbesondere aus Kreisen der Wirtschaft und der Arbeitgeber nachzukommen. Einerseits hat der Begriff "vorläufige Aufnahme" eine integrationshemmende Wirkung, insbesondere im Arbeitsmarkt, und andererseits muss der Schutzstatus S im Frühjahr 2027 ohnehin für diejenigen Flüchtlinge aus der Ukraine, die als erste gekommen sind, angepasst werden. Ziel muss es sein, denjenigen, die in der Lage sind, sich im Arbeitsmarkt der Schweiz zu bewähren oder die bereits eine Stelle haben, eine verlässliche Perspektive in der Schweiz zu geben. Eine Nivellierung der beiden Status soll nicht möglich sein, weder nach oben noch nach unten.
+4. Integration: Das vierte Element dieses Postulates ist die Integration. Die Schweiz ist ein sehr integrationsstarkes Land. Das verdankt sie einerseits der hohen Integrationsbereitschaft der überwiegenden Mehrheit der Ausländerinnen und Ausländer in der Schweiz und andererseits auch der Bereitschaft der schweizerischen Gesellschaft zur Offenheit sowie der wirtschaftlichen Attraktivität. Dennoch gibt es in bestimmten Bereichen Verbesserungspotenzial, so sind ausländische Frauen deutlich weniger erwerbstätig als Männer. Ausserdem müssen Kinder mit sprachlichen Defiziten bessere Möglichkeiten haben, diese aufzuholen, um ihre Integration in unser Bildungssystem zu fördern. Ebenso muss die wirtschaftliche Selbstständigkeit von Ausländerinnen und Ausländern stärker gefördert werden.
+In diesem Sinne beantragt Ihnen die Kommissionsmehrheit Zustimmung zur Motion Germann - mit Ausnahme von Punkt 5 - sowie Zustimmung zum Postulat Ihrer Kommission, letzteres mit 13 zu 11 Stimmen bei 1 Enthaltung.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion fordert eine echte Asylstrategie: eine Asylstrategie im Interesse unserer Bevölkerung. Am 11. März haben Sie hier die gleichlautende Motion 25.4589 klar angenommen. Auch der Ständerat hat deutlich zugestimmt. Was diese Motion fordert, ist ein Gebot des gesunden Menschenverstandes. Die Asylgesuche, die Asylkosten und die Asylkriminalität müssen endlich markant sinken. Die Verfahren müssen beschleunigt werden, die Rückführungen müssen forciert werden und der Familiennachzug muss einge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion fordert eine echte Asylstrategie: eine Asylstrategie im Interesse unserer Bevölkerung. Am 11. März haben Sie hier die gleichlautende Motion 25.4589 klar angenommen. Auch der Ständerat hat deutlich zugestimmt. Was diese Motion fordert, ist ein Gebot des gesunden Menschenverstandes. Die Asylgesuche, die Asylkosten und die Asylkriminalität müssen endlich markant sinken. Die Verfahren müssen beschleunigt werden, die Rückführungen müssen forciert werden und der Familiennachzug muss eingeschränkt werden. Die Kommissionsmehrheit unterstützt fünf dieser sechs Forderungen. Beim Familiennachzug hat eine knappe Mehrheit von 12 gegen 11 Stimmen kalte Füsse bekommen. 
+Wieso braucht es eine echte Asylstrategie? In der Asylstrategie 2027 des Bundesrates steht drin, die Asylreform 2016 habe sich bewährt und das Asylsystem funktioniere gut. Das ist also wirklich nicht mehr als ein schlechter Witz. Schneller, besser und billiger, so verkaufte der Bundesrat dem Volk die Asylreform von 2016, und die Realität heute ist: langsamer, teurer, schlechter, viel mehr, und vor allem viel mehr Kriminalität. Dänemark hatte letztes Jahr noch 1950 Gesuche im ganzen Jahr, und wir hatten allein diesen Juli 2808 Gesuche im Asylbereich, und die Bestände sind auf Rekordniveau. Jede vierte Straftat in diesem Land geht aufs Konto von Asylmigranten und Illegalen; jede vierte Straftat! Über 80 Prozent der Asylmigranten aus Nordafrika sind kriminell. Das sind Zahlen, die eigentlich alle schockieren müssten. Diese Motion verlangt genau das: die Eindämmung der Asylkriminalität. Jetzt haben wir sie auf dem Tisch.
+Dann haben wir noch eine linke Minderheit Tschopp. Herr Tschopp bekämpft mit seiner Minderheit allen Ernstes die Eindämmung der Asylkriminalität. Er bekämpft die Eindämmung der Asylkriminalität! Wir haben über 80 Prozent Kriminelle aus Nordafrika im System. Ich glaube, Herr Tschopp, da müssen Sie schon mal ein bisschen über die Bücher mit Ihren völlig verblendeten ideologischen Forderungen und Positionen, die wirklich nur noch grotesk sind, statt die ganze Zeit über Männergewalt zu sprechen, obwohl wir aus der Statistik wissen, dass der grosse Teil der Zunahme der Männergewalt ein importiertes Problem ist. Das muss man mal klar sagen.
+Monat für Monat strömen Tausende von Asylmigranten in unser Land. Es sind vor allem Afghanen, Eritreer, Somalier, es sind jene Nationalitäten, die ausserordentlich negativ auffallen. Algerier sind 45-mal krimineller als Schweizer bei Gewalttaten und 17-mal häufiger bei Sexualdelikten. Diese Zuwanderung bringt uns doch keine Fachkräfte, sie bringt uns Probleme, Gewalt und Kriminalität. Da den Kopf in den Sand zu stecken, ist verantwortungslos. Sie geben vor, in ihrer Heimat verfolgt zu sein, und zum Dank werden sie hier bei uns zu Tausenden kriminell. Wir haben jedes Jahr in diesem Land Tausende von Opfern - Tausende von Opfern, die wir nicht hätten, wenn wir diese Art von Migration nicht hätten.
+Es gibt nicht nur Menschenrechte für Asylmigranten, Herr Tschopp. Es gibt vor allem Menschenrechte für unsere Bevölkerung. Es gibt ein Menschenrecht in diesem Land, nicht von Asylmigranten bestohlen, ausgeraubt und vergewaltigt zu werden. Deshalb braucht es dringend eine echte Asylstrategie, die diese Probleme anpackt, eine Strategie, die den Namen verdient und eine Asylpolitik für unsere Bevölkerung - für Sie da oben auf der Tribüne und für alle jene zuhause. Die heutige Asylpolitik ist das Gegenteil davon, sie ist eine Zumutung. Die Asylstrategie des Bundesrates ändert daran nichts. Es ist keine Strategie, es ist nur eine Möglichkeit, um die ganzen Probleme auf die lange Bank zu schieben, und das wollen wir nicht.
+Deshalb bitte ich Sie, dieser Motion vollständig zuzustimmen, auch der Einschränkung des Familiennachzugs; genauso, wie es der Ständerat getan hat. Genau so machen es bereits unser Nachbarland Österreich sowie Dänemark und Schweden. Ich danke Ihnen vielmals im Namen der schweizerischen Bevölkerung, die unter diesen Zuständen leidet.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egger Mike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geschätzter Herr Bundesrat Jans, Sie haben über Dänemark gesprochen und erwähnt, dass Dänemark die Gesuche nur aufgrund seiner geografischen Lage reduzieren konnte. 2015 gab es in Dänemark über 21 000 Gesuche, 2025 konnte das Land diese Zahl auf etwa 1950 reduzieren. Das hat doch wesentlich mehr mit den Massnahmen zu tun, die Dänemark in der Asylpolitik veranlasst hat.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieses Postulat, das an und für sich einen sehr harmlosen und sinnvollen Titel hat, enthält im eingereichten Text leider zwei Punkte, die nicht wirklich befriedigend sind und sogar kontraproduktive Auswirkungen haben können oder an der Realität vorbeizielen.
+Ich komme zur Ausgangslage der Diskussion über die Forderungen dieses Postulates: Leider wurde in dieser Session die Motion 25.4067 der FDP-Liberalen Fraktion, "Geordneter Ausstieg für Schutzstatus S", abgelehnt, die eine geordnete Aufhebung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieses Postulat, das an und für sich einen sehr harmlosen und sinnvollen Titel hat, enthält im eingereichten Text leider zwei Punkte, die nicht wirklich befriedigend sind und sogar kontraproduktive Auswirkungen haben können oder an der Realität vorbeizielen.
+Ich komme zur Ausgangslage der Diskussion über die Forderungen dieses Postulates: Leider wurde in dieser Session die Motion 25.4067 der FDP-Liberalen Fraktion, "Geordneter Ausstieg für Schutzstatus S", abgelehnt, die eine geordnete Aufhebung des Schutzstatus S für Flüchtlinge aus der Ukraine forderte. In der Motion haben wir mit Fachexperten einen Massnahmenkatalog erarbeitet, um den Schutzstatus S aufzuheben.
+Das wird in der Zukunft eine enorm wichtige Aufgabe werden. Stand heute befinden sich in der Schweiz über 73 000 Personen im Schutzstatus S - über 73 000 Personen! Das ist ein namhafter Teil der Asylbevölkerung. Das entspricht der Grösse einer Stadt wie St. Gallen. Wenn wir eine geordnete Aufhebung dieses Schutzstatus erreichen wollen, müssen wir jetzt einige Dinge richtig machen, damit die Situation nicht in einem Chaos mündet.
+Deshalb ist dieses Postulat nicht wirklich hilfreich. Warum nicht? In einem Satz steht, es solle eine Namensänderung des Schutzstatus S sowie eine Angleichung zwischen der vorläufigen Aufnahme und dem Schutzstatus S vorgenommen werden. Eine vorläufige Aufnahme würde jedoch bedeuten, dass Personen aus der Ukraine mit Schutzstatus S nicht mehr als rückkehrorientiert zu betrachten sind. Frau Bundesrätin Karin Keller-Sutter hat, als sie noch das EJPD führte, in einer Pressekonferenz gegenüber der Schweizer Bevölkerung ganz klar gesagt: Ja, wir führen den Schutzstatus S ein und nehmen die Flüchtlinge aus der Ukraine unbürokratisch auf, aber es handelt sich um einen rückkehrorientierten Schutzstatus.
+Wenn man nun versucht, die über 73 000 Personen, die sich mit Schutzstatus S im Land befinden, in eine vorläufige Aufnahme zu verschieben, sodass sie dann dauerhaft hierbleiben, ist das eine fundamentale Abkehr von dem, was der Bundesrat der Bevölkerung damals versprochen hat. Es sollte im Parlament nicht die Forderung entstehen, dieser Politik Vorschub zu leisten. Das ist der eine gravierende Punkt, der völlig verkehrt ist.
+Der zweite Punkt: Die gesellschaftliche und wirtschaftliche Integration von Frauen soll spezifisch gefördert werden. Wenn wir anschauen, mit wem wir im Asylvollzug und im Asylbereich echte Probleme haben, dann sehen wir, dass das nicht die Frauen sind. Die Frauen machen beinahe keine Probleme; das ist eine sehr gute Botschaft.
+Die Problemfälle sind die jungen Männer, die Wirtschaftsflüchtlinge, die sich Nacht für Nacht an den Bahnhöfen usw. in den Städten und in den Dörfern aufhalten. Mit diesen Leuten müssen wir zu arbeiten versuchen. Auf der einen Seite gibt es eben harte Massnahmen; wenn sie illegal im Land sind, müssen sie das Land verlassen. Auf der anderen Seite müssen sie, wenn sie Probleme machen oder Straftaten verüben, dem Strafvollzug zugeführt werden.
+Am besten soll es gar nicht erst so weit kommen. Da kann man als Staatspolitische Kommission aber doch nicht auf die Idee kommen, dass es hier vor allem um die Integration von Frauen gehe. Das ist wirklich eine sehr seltsame Forderung in diesem Postulat, das in der Staatspolitischen Kommission leider eine Mehrheit fand.
+Noch ein Schlusswort zum Vollzug im Asylbereich in Bezug auf die Asylstrategie 2027: Ich glaube, es ist nicht sinnvoll, das Dublin-System und die Weiterentwicklung des europäischen Asylvollzugs, namentlich den EU-Asyl- und Migrationspakt, zu verteufeln, wie das einige tun wollen. Ebenso wenig zielführend ist jedoch die Forderung, wie man sie jetzt hier sieht, pauschal über 73 000 Personen einfach vorläufig aufzunehmen.
+Der Mittelweg ist wahrscheinlich der bessere. Man muss aktiv beim Dublin-System und bei dessen Weiterentwicklung dabei sein, damit schon an der Schengen-Aussengrenze solche Screenings gemacht werden können und damit man vor allem Personen aus Ländern, deren Asylanerkennungsquote deutlich unter 10 Prozent liegt, im Schnellverfahren zurückschicken kann. Das ist wahrscheinlich effektiv das Wichtigste, das man in Zukunft tun kann. Denn all diese Leute, die auf der Suche nach einem besseren Leben in die Schweiz kommen, haben hier wirklich keine Zukunft, sondern führen nur zu Problemen, und da müssen wir schon mit einer etwas härteren Hand agieren.
+Deshalb bitte ich Sie, dieses Postulat, das in diesen zwei Punkten wirklich schief ist, abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des institutions politiques de notre conseil a traité la motion Germann 25.4674, "Pour une stratégie d'asile qui soit réellement dans l'intérêt de la population suisse", à sa séance des 13 et 14 août derniers. Cette motion a été acceptée par le Conseil des États, par 27 voix contre 15 et 1 abstention. Cette motion est en tout point identique à la motion du groupe UDC 25.4589 qui a été acceptée par notre conseil le 11 mars dernier. Pour mémoire, cette motion comprend six chiffres, s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des institutions politiques de notre conseil a traité la motion Germann 25.4674, "Pour une stratégie d'asile qui soit réellement dans l'intérêt de la population suisse", à sa séance des 13 et 14 août derniers. Cette motion a été acceptée par le Conseil des États, par 27 voix contre 15 et 1 abstention. Cette motion est en tout point identique à la motion du groupe UDC 25.4589 qui a été acceptée par notre conseil le 11 mars dernier. Pour mémoire, cette motion comprend six chiffres, sur lesquels notre conseil a voté séparément, mais qui ont tous été adoptés par notre conseil.
+Lors des travaux de la commission, le chiffre 5 de la motion Germann, qui vise à limiter le regroupement familial, a cependant été rejeté à une courte majorité, par 12 voix contre 11, créant ainsi une différence par rapport à ce que notre conseil avait voté pour la motion du groupe UDC 25.4589. À l'exception du chiffre 5, l'ensemble des autres chiffres de la motion ont été acceptés ; le chiffre 1, par 13 voix contre 11 et 1 abstention, le chiffre 2, par 13 voix contre 11 et 1 abstention, le chiffre 3, par 16 voix contre 8 et 1 abstention, le chiffre 4, par 17 voix contre 8, et enfin le chiffre 6, par 16 voix contre 8 et 2 abstentions. Au nom de la majorité de la commission, je vous invite par conséquent à accepter les chiffres 1, 2, 3, 4 et 6.
+Ceci dit, votre commission a largement débattu de la question de savoir si une stratégie d'asile pouvait se limiter aux seuls points mentionnés dans cette motion, à savoir un simple durcissement de certains points de la politique d'asile actuelle. Il est facile en effet de demander que l'asile coûte toujours moins cher, mais il est plus difficile de définir une vue d'ensemble des mesures à prendre et de ne pas systématiquement remettre en cause ce qui est déjà fait. Des auditions de représentantes et représentants des trois niveaux de l'État, qui avaient été conduites par la commission en février dernier, avaient en effet montré que les représentants de ces échelons souhaitent qu'on les laisse travailler dans le sens des objectifs définis par la stratégie sur l'asile, plutôt que de les inonder régulièrement avec une avalanche de motions, de manière non coordonnée et sans faire d'évaluation sur ce qui marche et ce qui ne marche pas. Le domaine de l'asile est une tâche commune aux trois échelons. Les problèmes ne peuvent pas être résolus par des initiatives parlementaires isolées, mais par la collaboration entre les communes, les cantons et la Confédération.
+Cela dit, les auditions ont aussi montré que certains points appelaient encore des mesures supplémentaires. Il s'agit premièrement du renforcement de la sécurité et de la mise en place d'une procédure anticipée, afin de réduire le nombre de demandes d'asile manifestement infondées en faisant en quelque sorte un tri préliminaire. Deuxièmement, il s'agit de favoriser l'indépendance économique des personnes admises en prévoyant, dans le cadre du statut d'admission provisoire, non seulement un changement de dénomination, mais aussi une équivalence entre l'admission provisoire et le statut de protection S. Troisièmement, il s'agit d'encourager l'intégration sur le marché du travail de manière ciblée, tout spécialement pour les femmes, qui sont encore largement sous-représentées sur le marché du travail. L'intégration sociale et économique des femmes doit par conséquent faire l'objet d'un soutien spécifique.
+En résumé, avec ce postulat, la commission vous propose un outil qui permet de travailler dans la continuité, de manière coordonnée, plutôt qu'à coups d'interventions monothématiques, qui ont plus d'effets sur les réseaux sociaux que dans la réalité.
+La commission a décidé de déposer ce postulat, par 13 voix contre 11. Au nom de la commission, je vous invite à l'adopter à votre tour.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gobet Nadine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des affaires juridiques du Conseil national a procédé le 2 juillet dernier à l'examen de la motion qui vise à moins de bureaucratie dans le cas des auteurs d'infractions multirécidivistes sans statut de résidence ou de séjour régulier. Par 16 voix contre 8, la commission vous propose d'adopter la motion. Une minorité propose, pour sa part, le rejet de cette motion. Par ailleurs, le Conseil des États avait déjà préalablement tacitement adopté la motion en mars 2026.
+La motion charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Commission des affaires juridiques du Conseil national a procédé le 2 juillet dernier à l'examen de la motion qui vise à moins de bureaucratie dans le cas des auteurs d'infractions multirécidivistes sans statut de résidence ou de séjour régulier. Par 16 voix contre 8, la commission vous propose d'adopter la motion. Une minorité propose, pour sa part, le rejet de cette motion. Par ailleurs, le Conseil des États avait déjà préalablement tacitement adopté la motion en mars 2026.
+La motion charge le Conseil fédéral de prévoir une exception au principe de l'unité de la procédure, afin d'améliorer l'efficacité des poursuites pénales visant des groupes d'auteurs sans domicile fixe en Suisse ou dont le statut de séjour est incertain. Pour rappel, le principe d'unité de la procédure est prévu à l'article 29 alinéa 1 du code de procédure pénale et implique qu'une procédure pénale doit être menée dans son ensemble par le ministère public qui s'est saisi le premier de l'affaire. Dans un cas où plusieurs coauteurs font l'objet de la procédure pénale, un seul ministère public est donc compétent.
+Si ce principe est judicieux dans la plupart des situations, il se heurte immanquablement aux affaires plus complexes, comprenant une série d'infractions commises dans des lieux différents, parfois dans plusieurs cantons, par des individus sans domicile fixe ou dont le statut de séjour est incertain. Il s'agit, par exemple, d'une série de cambriolages commis en peu de temps à travers toute la Suisse par plusieurs auteurs. Dans ce cas, le principe de concentration des procédures impose que toutes les affaires soient traitées par une seule autorité de poursuite, généralement celle qui a ouvert la procédure en premier.
+Cette règle, bien que fondée sur l'idée d'une peine globale unique, conduit à une surcharge importante de certaines autorités et à un allongement considérable des procédures. Par ailleurs, l'application stricte du principe de l'unité à différentes procédures entraîne régulièrement des conflits de compétences entre les cantons au sujet de la détermination du for. Ces litiges coûtent rapidement très cher et prennent surtout beaucoup de temps pour être résolus. Ce faisant, ils retardent considérablement le jugement des prévenus et en particulier les décisions d'expulsion du territoire suisse qui sont souvent associées à ce type d'auteurs d'infractions.
+Aussi, afin de lutter plus efficacement contre les infractions commises par des requérants d'asile déboutés ainsi que des personnes itinérantes, la motion a pour but de permettre de séparer les procédures engagées contre les différents auteurs d'infractions appartenant à un même groupe. Concrètement, il est demandé au Conseil fédéral de préciser ou de compléter les exceptions d'ores et déjà prévues à l'article 30 du code de procédure pénale, afin de permettre un assouplissement du principe de l'unité de procédure lorsqu'un intérêt majeur à obtenir une condamnation rapide l'emporte sur les inconvénients éventuels d'une séparation.
+La majorité de notre commission estime, comme le Conseil fédéral, qu'il existe un besoin d'agir afin de permettre au ministère public d'oeuvrer avec plus de célérité contre les groupes de malfaiteurs précités. Par ailleurs, elle considère qu'un assouplissement des règles de procédure est le meilleur moyen de garantir à la fois des économies de procédure, une réduction de la bureaucratie et une répression plus ciblée. La commission rappelle au passage que notre conseil avait déjà adopté une motion similaire le 11 mars dernier, lors de notre session extraordinaire dédiée au thème de la sécurité. 
+Vu ce qui précède, la majorité de la commission vous recommande d'adopter la motion 25.4640.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette motion n'a pas de stratégie que le nom. Elle vise "une stratégie d'asile qui soit réellement dans l'intérêt de la population suisse" en six chiffres exclusifs. Premièrement, nette diminution des demandes d'asile ; deuxièmement, nette réduction des coûts liés à l'asile ; troisièmement, lutte contre la criminalité liée à l'asile ; quatrièmement, accélération des procédures d'asile et de renvoi ; cinquièmement, limitation du regroupement familial ; sixième et dernier chiffre, augmentation du </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette motion n'a pas de stratégie que le nom. Elle vise "une stratégie d'asile qui soit réellement dans l'intérêt de la population suisse" en six chiffres exclusifs. Premièrement, nette diminution des demandes d'asile ; deuxièmement, nette réduction des coûts liés à l'asile ; troisièmement, lutte contre la criminalité liée à l'asile ; quatrièmement, accélération des procédures d'asile et de renvoi ; cinquièmement, limitation du regroupement familial ; sixième et dernier chiffre, augmentation du nombre de rapatriements. Le Conseil fédéral reçoit l'injonction d'atteindre ces objectifs et de proposer des modifications législatives. 
+Pour répondre à M. Pascal Schmid, qui vient de s'exprimer, les membres de la minorité sont déterminés à lutter contre la criminalité liée à l'asile, comme contre toute forme de criminalité. Cher collègue Schmid, la criminalité, dans ce pays, comme dans tous les autres d'ailleurs, n'est pas le fait d'une seule nationalité ou de requérants d'asile exclusivement. Nous combattons toute forme de criminalité avec véhémence, quelle que soit l'origine de son auteur. Je ne veux aucune ambiguïté à ce sujet. De la même manière, les droits humains auxquels sont attachés les membres de la minorité sont aussi valables pour toutes les personnes habitantes de ce pays.
+Nous sommes habitués à ce que le groupe auquel appartient l'auteur de la motion, M. le conseiller aux État Germann, propose ce genre d'intervention parlementaire. Cette motion ressemble plutôt à un tract électoral - Mme Céline Weber a parlé de post sur les réseaux sociaux, l'idée est la même. Cette motion ressemble plutôt à ce type d'effet déclamatoire à courte vue, qui a une prétendue stratégie. Le fait que cette motion obtienne une majorité au sein de la Commission des institutions politiques est plus inhabituel et c'est, ma foi, assez préoccupant.
+On peut toujours poser sur une réalité migratoire un chablon préétabli. Le risque est que ce chablon dissimule toute une partie des enjeux qui s'imposent à nous, et c'est ce que fait, aux yeux de la minorité, la majorité de la commission. Pas un mot dans cette stratégie sur les enjeux d'intégration essentiels, en particulier pour les réfugiés, pas un mot non plus sur les enfants, les mineurs non accompagnés qui sont massivement représentés au sein des populations réfugiées, pas un mot non plus sur la santé mentale de personnes fuyant la guerre, devant se reconstruire dans un pays qui n'est pas le leur. Éviter de nommer une réalité donne le sentiment qu'elle n'existe pas. On peut rappeler au passage, ne vous en déplaise, que le nombre de demandes d'asile diminue massivement depuis la troisième année consécutive, à tel point que plusieurs centres ont fermé.
+Enfin, la motion ignore les décisions de première instance qui, dans 60 à 80 pour cent des cas, sont rendues dans un délai maximal de 140 jours, selon la procédure accélérée.
+La raison, aussi, pour laquelle le Conseil fédéral propose de rejeter cette motion est bien liée au fait qu'il y a déjà une stratégie, une stratégie 2027, qui a été établie non pas de manière unilatérale, mais avec une vision plus large - on peut évidemment la discuter -, mais qui a été faite avec les cantons et les communes, qui sont bien évidemment, sur le terrain, des partenaires incontournables aux responsabilités et qui voient la réalité qui s'impose à eux.
+En conclusion, il n'y a pas de raison - et je reprends aussi les mots de Mme Weber - de remettre systématiquement en cause une stratégie avant même qu'elle ait pu déployer ses effets, avant même qu'elle soit entrée en vigueur. Le fait de déposer une avalanche de motions qui, pour partie, ont déjà, d'ailleurs, été renvoyées au Conseil fédéral, ne change rien à l'affaire.
+C'est la raison pour laquelle les huit membres qui composent ma minorité vous proposent de rejeter la motion Germann 25.4674.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonio Giorgio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A nome della maggioranza della Commissione delle istituzioni politiche vi propongo di non dare seguito all'iniziativa parlamentare Strupler 25.459. È necessario ricordare che questo Parlamento ha già espresso una volontà chiara e univoca su questa tematica. Era il 2021 ed era in merito all'iniziativa parlamentare Reimann Lukas 20.501, che conteneva una richiesta identica a quella odierna. Era stata respinta a larga maggioranza, più precisamente con 136 voti contrari e solo 49 favorevoli.
+Durante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A nome della maggioranza della Commissione delle istituzioni politiche vi propongo di non dare seguito all'iniziativa parlamentare Strupler 25.459. È necessario ricordare che questo Parlamento ha già espresso una volontà chiara e univoca su questa tematica. Era il 2021 ed era in merito all'iniziativa parlamentare Reimann Lukas 20.501, che conteneva una richiesta identica a quella odierna. Era stata respinta a larga maggioranza, più precisamente con 136 voti contrari e solo 49 favorevoli.
+Durante i lavori commissionali è emerso che dal voto sull'iniziativa parlamentare Reimann Lukas ad oggi non sono intervenuti mutamenti sostanziali nel contesto giuridico e sociale che abbiano in qualche modo potuto giustificare un riesame della materia e una valutazione differente rispetto alla decisione precedente. 
+In un secondo tempo, la commissione ha approfondito l'analisi del legame tra cittadinanza e lealtà. È emerso che il punto centrale della questione non risiede nel possesso formale di più cittadinanze, bensì nel grado effettivo di integrazione della persona all'interno della nostra società. La doppia cittadinanza non costituisce di per sé un ostacolo all'integrazione, né una prova di mancata lealtà verso la nostra nazione. Al contrario, l'acquisizione della cittadinanza svizzera dovrebbe essere considerata il coronamento di un processo di integrazione riuscito, indipendentemente dal fatto che l'interessato conservi un legame formale con il proprio Paese di origine.
+Inoltre, occorre considerare anche l'impatto di una simile misura su una parte significativa della nostra popolazione. Attualmente circa 1 125 000 persone, ovvero circa il 20 per cento della popolazione sopra i 15 anni, possiede uno o più passaporti. Imporre l'obbligo di rinunciare alla cittadinanza d'origine potrebbe avere anche un effetto di stigmatizzazione verso le persone naturalizzate. Tale misura risulterebbe particolarmente ingiusta per coloro che hanno già dimostrato un profondo impegno di lealtà verso la nostra nazione. Come? Ad esempio attraverso il servizio militare.
+Una minoranza della commissione propone invece di dar seguito a questa iniziativa, in quanto ritiene che la naturalizzazione debba essere l'espressione di un impegno chiaro e inequivocabile nei confronti della Svizzera. Secondo questa posizione diventare cittadini svizzeri dovrebbe rappresentare una scelta consapevole, fondata su una piena adesione ai valori e alle istituzioni del nostro Paese, superando l'idea che la cittadinanza possa essere intesa come un mero vantaggio amministrativo.
+Con le considerazioni poco fa espresse, la maggioranza della commissione, con 14 voti contro 8 e 1 astensione, propone di non dar seguito all'iniziativa parlamentare.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3664 [GZ]
+[VS][GZ]
+Ordnungsantrag Zopfi [GZ]
+Zuweisung der Motion 26.3664 an die zuständige Kommission zur Vorprüfung
+[VS]
+Motion d'ordre Zopfi [GZ]
+Transmettre la motion 26.3664 à la commission compétente pour examen préalable
+[VS]
+Präsident (Engler Stefan, Präsident): Ich eröffne die ausserordentliche Session zum Thema "Asyl", welche mit Schreiben vom 17. Juni 2026 von über 50 Mitgliedern der SVP-Fraktion zur Behandlung gleichlautender Vorstösse in beiden Räten verlangt wurde. Gegenstand de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3664 [GZ]
+[VS][GZ]
+Ordnungsantrag Zopfi [GZ]
+Zuweisung der Motion 26.3664 an die zuständige Kommission zur Vorprüfung
+[VS]
+Motion d'ordre Zopfi [GZ]
+Transmettre la motion 26.3664 à la commission compétente pour examen préalable
+[VS]
+Präsident (Engler Stefan, Präsident): Ich eröffne die ausserordentliche Session zum Thema "Asyl", welche mit Schreiben vom 17. Juni 2026 von über 50 Mitgliedern der SVP-Fraktion zur Behandlung gleichlautender Vorstösse in beiden Räten verlangt wurde. Gegenstand der ausserordentlichen Session sind im Ständerat die Motionen Chiesa 26.3630, "Ablehnung der einseitigen Regeländerung seitens EU betreffend Entschädigung von arbeitslosen EU/EFTA-Grenzgängern", Friedli Esther 26.3571, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein", Salzmann 26.3626, "Bei Terrorismus und Schwerverbrechen werden Doppelbürger ausgebürgert", Schwander 26.3655, "Keine neuen Asylunterkünfte ohne Zustimmung der betroffenen Bevölkerung. Vetorecht für Standortgemeinden", sowie Friedli Esther 26.3664, "Korrektur der Praxisänderung in Bezug auf Asylgesuche von Afghaninnen".
+Ich begrüsse Herrn Bundespräsident Guy Parmelin sowie Herrn Bundesrat Beat Jans zu dieser ausserordentlichen Session.
+Bevor wir zur materiellen Diskussion der Motionen kommen, werden wir über den Ordnungsantrag Zopfi befinden.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmür-Schönenberger Andrea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich kann mich meinem Vorredner uneingeschränkt anschliessen. Frau Ständerätin Friedli hat natürlich recht: Es ist ein demokratisches Recht, ausserordentliche Sessionen zu verlangen. Ich habe aber schon den Eindruck, dass dieses demokratische Recht zunehmend missbraucht wird.
+Wir haben praktisch in jeder Session eine ausserordentliche Session durchgeführt, und zwar meistens zum Thema Asyl und Migration; und wir haben sehr viele Vorstösse einfach durchgewunken, die dann vom Nationalrat gestoppt wu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich kann mich meinem Vorredner uneingeschränkt anschliessen. Frau Ständerätin Friedli hat natürlich recht: Es ist ein demokratisches Recht, ausserordentliche Sessionen zu verlangen. Ich habe aber schon den Eindruck, dass dieses demokratische Recht zunehmend missbraucht wird.
+Wir haben praktisch in jeder Session eine ausserordentliche Session durchgeführt, und zwar meistens zum Thema Asyl und Migration; und wir haben sehr viele Vorstösse einfach durchgewunken, die dann vom Nationalrat gestoppt wurden. Obwohl ich gewisse Vorstösse noch selbst unterstützt habe, muss ich sagen, der Nationalrat hat meines Erachtens jeweils richtig entschieden. Ich möchte im Übrigen nicht, dass jetzt passiert, was wir früher immer andersherum gesehen haben: dass unser Rat den Nationalrat korrigieren musste. Ich habe manchmal den Eindruck, es ist jetzt zunehmend umgekehrt der Fall.
+In diesem Sinne werde ich sämtliche Vorstösse der ausserordentlichen Session ablehnen. Ich werde auch die Vorstösse ablehnen, die direkt anschliessend zu diesem Thema auf der Traktandenliste sind und die der Bundesrat zur Ablehnung empfiehlt. Ich bitte aber die Staatspolitische Kommission, einmal eine breite Auslegeordnung dazu zu machen, wo tatsächlich Handlungsbedarf besteht und wo wir tatsächlich auch die Möglichkeit haben, etwas zu ändern.
+[VS]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie Sie gehört haben, habe ich den Antrag gestellt, die Motion 26.3664 an die zuständige Kommission zur Vorberatung zu überweisen. Ich fasse mich recht kurz mit der Begründung, weil mir die Motionärin bereits signalisiert hat, dass sie nicht allzu grossen Widerstand leisten wird, wenn ich das richtig interpretiere. Sie wird sich aber sicher noch selbst äussern. 
+Meine Begründung ist, dass wir uns eigentlich im Rahmen der Motion unseres ehemaligen Kollegen, der Motion Bauer 23.4247, "Die Anpassun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wie Sie gehört haben, habe ich den Antrag gestellt, die Motion 26.3664 an die zuständige Kommission zur Vorberatung zu überweisen. Ich fasse mich recht kurz mit der Begründung, weil mir die Motionärin bereits signalisiert hat, dass sie nicht allzu grossen Widerstand leisten wird, wenn ich das richtig interpretiere. Sie wird sich aber sicher noch selbst äussern. 
+Meine Begründung ist, dass wir uns eigentlich im Rahmen der Motion unseres ehemaligen Kollegen, der Motion Bauer 23.4247, "Die Anpassung der Praxis bei Asylanträgen afghanischen Bürgerinnen korrigieren", und auch der Motion 24.3008, "Schutz von Afghaninnen. Einzelfallprüfung und Sicherheitsüberprüfung", schon vertieft mit der Thematik auseinandergesetzt haben. In der Kommission haben wir uns auch vertieft damit auseinandergesetzt, was die konkrete Kritik des Bundesverwaltungsgerichts an der Praxis ist. Wir haben damals auch Anforderungen und Erwartungen an das SEM formuliert. Aus dieser Logik heraus würde es sich anbieten, dass die Kommission dies nochmals berät und prüft, was sich bezüglich dieser Praxis und der Frage der Einzelfallprüfung getan hat. Das ist der eine Grund. 
+Der andere Grund sind die konkreten Auswirkungen, die diese nicht unerhebliche Motion haben könnte. Wir haben es hier ja mit einer ausserordentlichen Session zu tun. Das heisst, dass die gleichlautende Motion im Nationalrat bereits angenommen wurde. Wenn die vorliegende Motion bei uns durchkommen würde, ohne dass wir sie vertieft geprüft haben, würde das faktisch bedeuten, dass die vorliegende Motion zwar noch im Nationalrat behandelt würde und die nationalrätliche Motion noch bei uns in der Kommission beraten würde, dass wir aber inhaltlich eigentlich schon an das heutige Resultat gebunden wären. Das finde ich generell und in diesem Fall speziell unglücklich. Wenn wir die vorliegende Motion an die Kommission überweisen würden, hätten wir die Chance, die im Nationalrat angenommene Motion zusammen mit der vorliegenden Motion von Kollegin Friedli zeitnah in der SPK zu prüfen. 
+Ich beantrage Ihnen deshalb, meinem Ordnungsantrag zuzustimmen, erlaube mir aber, da ich nun schon am Reden bin, noch eine generelle Bemerkung.
+Sie wissen, und ich kann mir in der Energie des frühen Nachmittags die Bemerkung nicht verkneifen, dass mir diese ausserordentlichen Sessionen nicht besonders gut gefallen. Ich finde es mittlerweile etwas bemühend, dass wir in jeder Session eine ausserordentliche Session zum gleichen Thema haben; mit Vorstössen - und da meine ich jetzt natürlich nicht den von Kollegin Friedli, obwohl wir auch den schon gesehen haben -, die man in gleicher Form nicht erst ein- oder zweimal, sondern vielleicht schon dreimal gesehen hat. Zum Teil sind es Vorstösse in Bereichen, in denen bereits Vorstösse überwiesen wurden, die Aufträge in diesem Sinne also bereits erteilt wurden. 
+Sie wissen ja, dass ein Vorstoss von mir hängig ist, dass man diese Praxis der ausserordentlichen Sessionen ändert und gleichlautende Vorstösse nicht mehr als Grund für eine ausserordentliche Session zulässt. Ich möchte den Kolleginnen und Kollegen, die diese Vorstösse eingereicht haben, nicht zu nahe treten, aber ich muss Ihnen sagen, dass es meiner Meinung nach der Arbeitsweise und der Seriosität des Ständerates entgegenkäme, wenn man den ordentlichen Weg gehen und die jeweils im Erstrat überwiesenen Vorstösse wenigstens als Zweitrat noch seriös prüfen würde. 
+Für mich besteht einfach die Gefahr, dass man in gewichtigen Themen Vorstösse annimmt, die auf den ersten Blick gut aussehen und sich so anhören, als ob sie umsetzbar wären, dann aber das eine oder andere Mal etwas macht, das man nachher bereut. Das muss man dann lösen, indem man diese Vorstösse irgendwie auf die mittellange Bank schiebt oder sie nicht wortgetreu umsetzt. Das wiederum stört mich, weil ich finde, dass Motionen umgesetzt werden müssen, und zwar so, wie sie gemeint waren. 
+Ich kann Ihnen sagen, dass ich alle diese Vorstösse nur schon aus diesem Grundsatz ablehne. Diejenigen Vorstösse, die im Nationalrat angenommen wurden, werden ja bei uns landen, wo sie seriös vorberaten und dann diesem Rat wieder vorgelegt werden. Wie gesagt, wenn Sie hier etwas Ärger über diese Praxis raushören, dann hören Sie richtig.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Motion 26.3571, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein", fordert, dass ein ausländischer Staatsangehöriger, der in der Schweiz derart schwer straffällig wird, dass ein Gericht eine Freiheitsstrafe von mindestens einem Jahr ausspricht, automatisch ausgeschafft wird. Es geht hierbei nicht um Bagatelldelikte oder Personen, die lediglich eine Busse erhalten oder wegen einer geringfügigen Übertretung vor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meine Motion 26.3571, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein", fordert, dass ein ausländischer Staatsangehöriger, der in der Schweiz derart schwer straffällig wird, dass ein Gericht eine Freiheitsstrafe von mindestens einem Jahr ausspricht, automatisch ausgeschafft wird. Es geht hierbei nicht um Bagatelldelikte oder Personen, die lediglich eine Busse erhalten oder wegen einer geringfügigen Übertretung vor Gericht stehen. Eine Freiheitsstrafe von einem Jahr oder mehr stellt eine erhebliche Sanktion dar; bevor ein Schweizer Gericht eine solche Strafe ausspricht, muss ein entsprechend schwerwiegender Sachverhalt vorliegen.
+Im Jahr 2010 nahmen Volk und Stände die Ausschaffungs-Initiative an, woraufhin Artikel 121 Absätze 3 bis 6 in die Bundesverfassung aufgenommen wurden. Anschliessend wurde die obligatorische Landesverweisung ins Strafgesetzbuch (StGB) eingefügt. Dennoch bedeutet "obligatorisch" heute nicht in jedem Fall eine zwingende Umsetzung. Aus meiner Sicht ist es nun nach einigen Jahren Erfahrung Zeit für eine Justierung.
+Aktuell funktioniert die obligatorische Landesverweisung primär über den Deliktskatalog gemäss Artikel 66a StGB; entscheidend ist somit wesentlich das begangene Delikt. Die Motion verlangt einen anderen Ansatz, nämlich einen verständlichen Massstab - die Höhe der Strafe. Als Grenze gilt eine Freiheitsstrafe von einem Jahr.
+Im Rahmen der Umsetzung der Ausschaffungs-Initiative wurde zudem die Härtefallklausel eingefügt. Nun zeigt sich, dass die obligatorische Landesverweisung in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen wird. Die Hauptursache ist aus meiner Sicht die zu häufige Anwendung der Härtefallklausel, obwohl diese ursprünglich als Ausnahme konzipiert war.
+Im Jahr 2024 wurden 2446 Landesverweise ausgesprochen. Bis zum Jahr 2025 - es gibt ja immer eine gewisse Verzögerung - wurden lediglich 69 Prozent dieser rechtskräftig verurteilten Landesverweise vollzogen. Weiter sind die Unterschiede im kantonalen Vollzug mit einer Spanne von 30 bis 100 Prozent enorm, was unseren Rechtsstaat unglaubwürdig macht. Ich bin überzeugt, dass es der Glaubwürdigkeit des Rechtsstaates förderlich wäre, wenn bei schweren Straftaten konsequent eine Ausschaffung vollzogen würde.
+Daher ist es Zeit für Änderungen, wobei sich ein Blick nach Dänemark lohnt. Dänemark verfolgt seit Jahren eine wesentlich konsequentere Politik gegenüber ausländischen Straftätern. Das dänische Ausländerrecht misst dabei insbesondere der ausgesprochenen Freiheitsstrafe grosses Gewicht bei und schafft Kriminelle ab einer Strafe von einem Jahr automatisch aus. Dieses Gesetz, das am 1. Mai 2016 in Kraft trat, hat zudem eine abschreckende Wirkung. In Kombination mit weiteren Massnahmen sind die Asylzahlen seither stark zurückgegangen.
+Dänemark geht sogar noch weiter. Das Land hat mit dem Kosovo eine Vereinbarung getroffen, um dort bis zu 300 Gefängnisplätze für ausländische Straftäter bereitzustellen, die nach Verbüssung ihrer Strafe ausgeschafft werden sollen. Straftäter aus Drittstaaten, d. h. aus Staaten ausserhalb der Europäischen Union, verbüssen ihre Haftstrafen direkt im Kosovo und werden danach ausgeschafft. Dies zeigt, dass Dänemark nicht nur über die formale Gestaltung einer Ausweisung diskutiert, sondern sich konkret mit der Frage des Vollzugs dieser Entscheide befasst. Eine Landesverweisung, die lediglich in einem Gerichtsurteil steht, aber nicht vollzogen wird, erreicht ihren Zweck nicht.
+Vor diesem Hintergrund bitte ich Sie, meiner Motion zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwander Pirmin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was will meine Motion? Der Bundesrat soll beauftragt werden, eine Anpassung des Asylgesetzes vorzulegen und die erforderlichen Massnahmen zu ergreifen, damit die Schaffung neuer Asylzentren des Bundes bei Nichtzustimmung (Veto) der betroffenen Standortgemeinden ausgeschlossen wird. Davon kann nur abgewichen werden, wenn gleichzeitig Massnahmen gemäss Artikel 55 Absatz 2 AsylG (Asylnotstand) ergriffen werden.
+Vielleicht muss ich darauf hinweisen, was die Wörter "Nichtzustimmung (Veto)" bedeuten. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was will meine Motion? Der Bundesrat soll beauftragt werden, eine Anpassung des Asylgesetzes vorzulegen und die erforderlichen Massnahmen zu ergreifen, damit die Schaffung neuer Asylzentren des Bundes bei Nichtzustimmung (Veto) der betroffenen Standortgemeinden ausgeschlossen wird. Davon kann nur abgewichen werden, wenn gleichzeitig Massnahmen gemäss Artikel 55 Absatz 2 AsylG (Asylnotstand) ergriffen werden.
+Vielleicht muss ich darauf hinweisen, was die Wörter "Nichtzustimmung (Veto)" bedeuten. Da geht es nicht um die rein rechtliche Situation. Der Bundesrat schreibt in seiner Antwort: "Sowohl für Privatpersonen wie auch für die Gemeinde und den Kanton besteht die Möglichkeit, sich im Verfahren einzubringen und Einsprache zu erheben." Es ist schon klar, dass eine Mitwirkung der Bürgerinnen und Bürger im Sachplan- und im Plangenehmigungsverfahren und sogar gemäss Raumplanungsverordnung möglich ist und dabei Einsprache gemacht werden kann. Es geht aber um die Berücksichtigung der betroffenen Bürgerinnen und Bürger in der Nähe von Asylzentren oder eben auch in der Gemeinde. Es geht eben nicht nur um die rein rechtliche Mitwirkung, es geht nicht nur um die rein rechtliche Schiene. Warum?
+Ich habe meine Motion insbesondere damit begründet, dass einzelne Asylsuchende sich nicht korrekt verhalten und allenfalls die Bürgerinnen und Bürger belästigen. Das ist der eine Aspekt. Es gibt daneben noch zwei andere Aspekte, die ich in den vergangenen zwei Jahren im Kanton Schwyz beobachten konnte. 
+In einem Beispiel geht es um eine Asylunterkunft, die jetzt - rechtlich gesehen - bewilligt wird, obwohl in den vergangenen zehn Jahren in diesem Gebiet keine Baute bewilligt wurde mit der Begründung, dass in der Nähe eine denkmalgeschützte Kirche stehe. Der Denkmalschutz hat bisherige Bauten verhindert. Im aktuellen Verfahren ist es so, dass der Denkmalschutz gar keine Stellung mehr abgibt und die Behörde sagt, man könne eine Ausnahmebewilligung machen. Da gibt es dann rechtlich immer Ausnahmebewilligungen! 
+Im zweiten Fall dasselbe. Da geht es nicht um Denkmalschutz, sondern um sensible Landschaften. Da wurde bisher über Jahrzehnte nichts bewilligt, weil die Landschaft sensibel ist. Offenbar ist es jetzt möglich, hier ein Asylzentrum zu bauen. Um diese Fälle geht es. Diese Fälle verstehen die Bürgerinnen und Bürger nicht mehr. Über Jahrzehnte darf aus landschafts- und denkmalschützerischen Gründen nichts gebaut werden, und plötzlich, wenn es um ein Asylzentrum geht, darf gebaut werden. Ich bin immer davon ausgegangen, dass in unserem Staat die gleichen Richtlinien gelten sollen, egal, was gebaut wird. Da fehlt meines Erachtens das Fingerspitzengefühl, insbesondere das der Bundesbehörden. Jetzt komme ich auf den konkreten Fall Buosingen zu sprechen. Da zeigte der Bund im Umgang mit den Mieterinnen und Mietern gar kein Fingerspitzengefühl. Das habe ich hautnah erlebt. Den Bewohnerinnen und Bewohnern wurde derart Angst vor den rechtlichen Möglichkeiten gemacht, dass sie zugestimmt haben. Sie wurden verängstigt. Ich war dabei, sie wurden verängstigt. Herr Bundesrat, Sie können schon den Kopf schütteln, aber es war so. Es ist ein Unterschied, ob Sie von Mitarbeiterinnen und Mitarbeitern darüber orientiert werden, was passiert ist, oder ob Sie vor Ort sind und mitbekommen, wie die Bürgerinnen und Bürger Angst haben. Sie haben Angst, Herr Bundesrat! Sie hatten Angst. Dies einfach, damit Sie das von mir hören. Ich habe mit all diesen Menschen gesprochen. Es geht also einerseits um dieses fehlende Fingerspitzengefühl. 
+Auf der anderen Seite ist man nun daran, die Planung zu machen in einer Landschaft, die sehr sensibel ist und wo in den vergangenen Jahren nichts gebaut werden konnte. Gar nichts! Man hat alles verhindert! Jetzt soll es plötzlich möglich sein! Das verstehe ich aus rechtlicher Sicht nicht, auch nicht aus Bürgersicht. Der Bevölkerung, die da zuschauen muss, sagt man, du kannst ja Einsprache erheben, aber dann kommt eine Bewilligung mit dem Hinweis, man könne jetzt eine Ausnahme machen. Das ist mir auch bekannt. Es ist mir bekannt, dass man ausserhalb der Bauzone Ausnahmen macht. Ich stelle aber fest, dass die Spielregeln offenbar sehr viel weniger streng sind, wenn es um Asylzentren geht, als wenn einzelne Bürgerinnen und Bürger etwas bauen wollen - nicht nur im Kanton Schwyz, sondern auch in anderen Kantonen -, und das kann ich nicht verstehen.
+Das ist mit dieser Motion gemeint: Dass man mehr Rücksicht auf die Standortgemeinden und die Bürgerinnen und Bürger nimmt, wenn sie entsprechende Fragen haben, insbesondere wenn es um objektiv messbare Kriterien wie den Denkmalschutz und den Landschaftsschutz geht. Diese sollen auch berücksichtigt werden, nicht nur rechtlich, sondern auch politisch.
+Ich bitte Sie, dieser Motion zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salzmann Werner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am 11. September dieses Jahres jährte sich der Terroranschlag vom 11. September 2001, bekannt als "9/11" und als der schlimmste der Geschichte, zum 25. Mal. Die Schweiz blieb glücklicherweise lange verschont. Noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Doch diese Zeiten sind vorbei. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano. Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Am 11. September dieses Jahres jährte sich der Terroranschlag vom 11. September 2001, bekannt als "9/11" und als der schlimmste der Geschichte, zum 25. Mal. Die Schweiz blieb glücklicherweise lange verschont. Noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Doch diese Zeiten sind vorbei. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano. Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorbestraft, islamistisch radikalisiert. Er griff wahllos Menschen an, gefährdete zahlreiche Kinder und verletzte drei Personen, teilweise schwer. Das ist die Realität, mit der wir heute konfrontiert sind. 
+Bei der Bundesanwaltschaft laufen aktuell über 140 Terrorverfahren. Der Nachrichtendienst des Bundes sagt auch klar, dass die Terrorbedrohung erhöht ist. Sie ist vor allem durch den Dschihadismus geprägt. Und die allermeisten Dschihadisten sind Ausländer oder Doppelbürger. Das bestätigt auch die Studie der Zürcher Hochschule für angewandte Wissenschaften. Auch in unseren Gefängnissen zeigt sich leider eine entsprechende Entwicklung: 70 Prozent der Insassen sind Ausländer, weitere 15 Prozent sind Schweizer mit Migrationshintergrund. Das heisst, für Schweizer ohne Migrationshintergrund würden 15 Prozent unserer Gefängnisplätze genügen. Das sind Zahlen, die man nicht schönreden kann. Wir haben immer mehr importierte Probleme, importierte Kriminalität und importierte Gewalt. Und wir haben immer mehr Opfer. Darum geht es bei dieser Motion.
+Seit 1992 muss ein Ausländer bei der Einbürgerung seinen bisherigen Pass nicht mehr abgeben. Ein wichtiges Argument für die Anerkennung der Doppelbürgerschaft war damals, dass man einem Doppelbürger, der später schwer kriminell wird, den Schweizer Pass wieder entziehen könne. Das klingt gut in der Theorie, aber was ist in der Praxis passiert? Der Bundesrat schreibt in seiner Stellungnahme zu dieser Motion, dass er den Passentzug zur Terrorbekämpfung einsetze. Schauen wir uns die Zahlen an: Seit dem Jahr 2000 gab es gerade einmal 10 Entzugsverfahren - nur 10! In 7 Fällen wurde ein Entzug angeordnet, nur in 3 Fällen ist er rechtskräftig geworden - das bei rund einer Million Einbürgerungen seit dem Jahr 2000. Diese Zahlen sprechen eine deutliche Sprache. Gerade bei schwersten Verbrechen und Terrorgefährdung muss der Staat konsequent handeln. Die heutige Rechtsgrundlage, Artikel 42 des Bürgerrechtsgesetzes, ist ein zahnloser Tiger. 
+Wir brauchen eine griffige Regelung, nicht nur eine Kann-Bestimmung, sondern eine Muss-Bestimmung für klar definierte schwerste Fälle. Bei Kapitalverbrechen und bei terroristischer Gefährdung muss der Entzug des Schweizer Bürgerrechts möglich sein und in den entsprechenden Fällen zwingend erfolgen. Wer seinen ausländischen Pass zusätzlich zum Schweizer Pass behalten will, muss auch wissen, dass später bei schweren Verbrechen der Schweizer Pass entzogen werden kann. Ich betone: Staatenlos wird dadurch niemand.
+Dschihadisten und Terroristen sind zu allem fähig. Sie wollen unseren Rechtsstaat, unsere Werte und auch unsere westliche Lebensweise zerstören. Wenn es Ihnen selber an den Kragen geht, berufen sie sich plötzlich auf genau diesen Rechtsstaat und seine Annehmlichkeiten. Das kann nicht unser Verständnis von Rechtsstaatlichkeit sein. Wir dürfen nicht warten, bis der nächste Anschlag passiert. Unsere erste Pflicht ist es, unsere Bevölkerung zu schützen. Denn die Sicherheit ist eine Kernaufgabe des Staates; sie ist eine der wichtigsten Aufgaben. Wer unser Land terroristisch angreift oder Kapitalverbrechen begeht, verwirkt damit aus meiner Sicht das Recht, Schweizerbürger zu bleiben. 
+Wir müssen aber noch früher ansetzen: Wir müssen alles daransetzen, dass solche Personen gar nicht erst in unser Land kommen. Und wenn sie trotzdem hier sind, müssen wir alles tun, um sie wieder aus unserem Land zu schaffen. Es ist schlicht ein Gebot des gesunden Menschenverstands. Wer unser Land mit Terror und schwerster Gewalt bedroht, hat bei uns nichts verloren. Solche Personen gehören ins Gefängnis. Und wenn die gesetzlichen Voraussetzungen erfüllt sind, müssen sie ausgebürgert und in ihr Heimatland zurückgeführt werden. 
+Ich bitte Sie deshalb, dieser Motion zuzustimmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Russland die Ukraine angriff, gewährte die Schweiz rasch Schutz. Das war richtig, der Schutzstatus S wurde für solche ausserordentlichen Lagen geschaffen. Er ermöglicht vorübergehenden Schutz, ohne dass jedes Gesuch zuerst in einem ordentlichen Asylverfahren geprüft werden muss. Viele der aufgenommenen Menschen arbeiten heute, lernen eine Landessprache oder absolvieren eine Ausbildung. Das verdient natürlich Anerkennung.
+Nun stellt sich die Frage, was nach fünf Jahren geschieht. Nach geltend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Als Russland die Ukraine angriff, gewährte die Schweiz rasch Schutz. Das war richtig, der Schutzstatus S wurde für solche ausserordentlichen Lagen geschaffen. Er ermöglicht vorübergehenden Schutz, ohne dass jedes Gesuch zuerst in einem ordentlichen Asylverfahren geprüft werden muss. Viele der aufgenommenen Menschen arbeiten heute, lernen eine Landessprache oder absolvieren eine Ausbildung. Das verdient natürlich Anerkennung.
+Nun stellt sich die Frage, was nach fünf Jahren geschieht. Nach geltendem Recht erhalten Schutzbedürftige dann eine Aufenthaltsbewilligung B, solange der vorübergehende Schutz besteht. Diese Bewilligung ist kein dauerhaftes Aufenthaltsrecht. Sie endet grundsätzlich mit der Aufhebung des Schutzes. Das stelle ich bekanntlich nicht infrage.
+Meine Motion betrifft den Schritt davor. Vor Erteilung der B-Bewilligung soll geprüft werden, ob die betroffene Person weiterhin Schutz benötigt. Bei der Aufnahme 2022 wurde der Schutzbedarf nur summarisch beurteilt. Fünf Jahre später sollte nicht allein der Zeitablauf über den nächsten Schritt entscheiden. Für neue Gesuche wird inzwischen berücksichtigt, ob eine Rückkehr in die Herkunftsregion auch zumutbar ist. Für bereits aufgenommene Personen gilt diese neue Regel nicht rückwirkend. Gerade deshalb ist eine faire und praxistaugliche Regelung für den Übergang nach fünf Jahren wichtig.
+Auch die Kantone verlangen Klarheit. Die Zentralschweizer Sozialdirektorinnen und Sozialdirektoren haben auf erhebliche Mehrkosten bei der Sozialhilfe hingewiesen. Sie wollen individuelle Härtefälle weiterhin berücksichtigen. Der Bundesrat hat eine Anpassung der Sozialhilferegeln vorgeschlagen. Das begrüsse ich. Sie regelt aber nur, welche Unterstützung nach Erteilung der B-Bewilligung gilt. 
+Meine Motion fragt, unter welchen Voraussetzungen dann die Bewilligung erteilt wird. Der Bundesrat warnt vor zusätzlichem Aufwand. Diesen Einwand nehme ich ernst. Ich verlange kein neues Asylverfahren für alle. Ich verlange eine gesetzliche Lösung, die den Schutzbedarf prüft, Integration würdigt und Härtefälle berücksichtigt. Sie muss für die Behörden umsetzbar sein und den Betroffenen eine klare Perspektive geben. Wer weiterhin Schutz braucht, soll ihn erhalten. Wer hier arbeitet oder eine Ausbildung absolviert, soll fair behandelt werden. Nach fünf Jahren brauchen wir Regeln, die beiden Anliegen gerecht werden.
+Ich bitte Sie, meine Motion anzunehmen, da insbesondere auch Gemeinden und Kantone bezüglich der Sozialhilfekosten die Alarmstufe Rot ausgerufen haben.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielleicht zuerst zum Verständnis: Es gibt zwei verschiedene Aufenthaltsbewilligungen B, die normale und die, die an den Schutzstatus geknüpft ist. Diese gilt es zu unterscheiden. Die, die an den Schutzstatus geknüpft ist, schuf der Gesetzgeber im Rahmen der Revision des Asylgesetzes von 1995. Diese Aufenthaltsbewilligung gilt nur so lange wie der vorübergehende Schutz. Hebt der Bundesrat den Schutzstatus auf, erlischt also auch diese Aufenthaltsbewilligung automatisch. Auf diese befristete Aufe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielleicht zuerst zum Verständnis: Es gibt zwei verschiedene Aufenthaltsbewilligungen B, die normale und die, die an den Schutzstatus geknüpft ist. Diese gilt es zu unterscheiden. Die, die an den Schutzstatus geknüpft ist, schuf der Gesetzgeber im Rahmen der Revision des Asylgesetzes von 1995. Diese Aufenthaltsbewilligung gilt nur so lange wie der vorübergehende Schutz. Hebt der Bundesrat den Schutzstatus auf, erlischt also auch diese Aufenthaltsbewilligung automatisch. Auf diese befristete Aufenthaltsbewilligung haben Personen mit Schutzstatus S gemäss Gesetz nach fünf Jahren Anspruch. Die ersten Personen werden das Ende dieser Frist im März 2027 erreichen.
+Nun zu den vier Gründen, warum der Bundesrat die Motion ablehnt, obwohl er die Begründung sehr gut nachvollziehen kann und auch die Ziele auf seine Art mitverfolgt - so geht das jedoch nicht -:
+1. Die von der Motion geforderte Gesetzesanpassung kommt schlicht und einfach zu spät. Sie würde frühestens in einigen Jahren in Kraft treten, und dann hätte die Mehrheit der betroffenen Personen bereits eine solche Aufenthaltsbewilligung, weil sie sie per Gesetz erhalten darf. Alle betroffenen Personen müssten dann also - das ist ein weiterer Grund, warum wir gegen die Motion sind - umständlich nachträglich zurückgestuft werden. Der Rechtsweg wäre nicht ausgeschlossen. Wir stünden also nach langen Verfahren und einer Periode der Rechtsunsicherheit für Betroffene eigentlich wieder am selben Ort wie 1995, als diese Gesetzgebung beschlossen wurde. Das wäre wirklich ein absurder Bürokratieakt. Bund, Kantone, Gemeinden, Städte und Arbeitgebende sind jedoch auf Planungssicherheit angewiesen. Es wäre nicht zielführend, heute ein solches Gesetzgebungsprojekt in die Wege zu leiten.
+Der Bundesrat hat schon mehrfach betont, dass es konzeptionelle Anpassungen beim Schutzstatus braucht. Aber wir sollten sozusagen nicht so grundsätzlich am Flugzeug schrauben, während es noch in der Luft ist. Stattdessen wird Ihnen der Bundesrat Ende Jahr ein Gesetzgebungspaket zur Debatte vorlegen. Der Bundesrat ist der Ansicht, dass die Diskussion solcher Grundsatzfragen dann durchgeführt werden sollte.
+2. Die Motion widerspricht einem eben erst gefassten Beschluss des Parlamentes. Die Motion Friedli Esther zu den sicheren Oblasten in der Ukraine wurde gemäss Beschluss des Parlamentes nur auf neu ankommende Personen mit Schutzstatus angewandt. Sie wird inzwischen umgesetzt. Die Forderung der vorliegenden Motion widerspricht also explizit diesem Beschluss des Parlamentes, der eben erst gefasst und im Sommer dieses Jahres in Kraft gesetzt wurde. Eine rückwirkende Anwendung würde auch hier eine Einzelfallprüfung erfordern, was einen sehr hohen Verwaltungsaufwand bedeuten würde. Ich möchte Sie daran erinnern, dass 70 000 ukrainische Geflüchtete in der Schweiz leben. Aufgrund des andauernden Krieges könnten die meisten Betroffenen sowieso nicht zurückgeführt werden. Der Aufwand würde sich also nicht lohnen.
+3. Das Hauptproblem wird ohnehin entschärft, und das ist ernst zu nehmen. Das Hauptproblem der Kantone wären die finanziellen Auswirkungen, die durch eine automatische Umwandlung entstehen würden, weil die Sozialhilfekosten dadurch ansteigen würden. Hier kommen wir den Kantonen jedoch entgegen; das hat der Bundesrat bereits beschlossen. Er lancierte im August eine entsprechende Vernehmlassung, und die neue Bestimmung wird am 1. März 2027, also rechtzeitig, in Kraft treten. Die Kantone haben somit neu Planungssicherheit und können selbst entscheiden, welche Beiträge sie Ukrainerinnen und Ukrainern zuführen; sie müssen aus Sicht des Bundesrates also keine Erhöhung der Sozialhilfe vornehmen.
+4. Die Kantone, Gemeinden und Städte wurden diesen Sommer zur Beibehaltung des Schutzstatus S nach März 2027 konsultiert. In diesem Zusammenhang konnten sie sich auch zum Übergang zur Aufenthaltsbewilligung nach fünf Jahren äussern. Die Kantone, die Städte und die Gemeinden unterstützen das Vorgehen des Bundesrates.
+Aus diesen Gründen beantrage ich Ihnen, die Motion abzulehnen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsident (Engler Stefan, Präsident): Die Motion wurde im Rahmen der ausserordentlichen Session (26.9019) beraten und per Ordnungsantrag an die zuständige Kommission zur Vorprüfung zugewiesen. Die ausserordentliche Session zum Thema "Asyl" ist damit beendet.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nach der ausserordentlich intensiven und interessanten Debatte zum EU-Schweiz-Paket sind Sie sicher auch froh, wenn wir wieder zu den ordentlichen Geschäften der Session übergehen können. Dazu gehören ja inzwischen auch die ausserordentlichen Sessionen zum Thema Asyl, die ich immer wieder gerne dazu nutze, Ihnen auch ausserordentlich den Stand der Situation im Asylwesen mitzuteilen. Dieser ist, das darf ich Ihnen mitteilen, ausserordentlich interessant und positiv.
+Die Asylgesuche gehen weiter z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nach der ausserordentlich intensiven und interessanten Debatte zum EU-Schweiz-Paket sind Sie sicher auch froh, wenn wir wieder zu den ordentlichen Geschäften der Session übergehen können. Dazu gehören ja inzwischen auch die ausserordentlichen Sessionen zum Thema Asyl, die ich immer wieder gerne dazu nutze, Ihnen auch ausserordentlich den Stand der Situation im Asylwesen mitzuteilen. Dieser ist, das darf ich Ihnen mitteilen, ausserordentlich interessant und positiv.
+Die Asylgesuche gehen weiter zurück. Wir haben in diesem Jahr fast 20 Prozent weniger Gesuche als letztes Jahr. Das SEM hat seine Prognose für 2026 um 3000 Asylgesuche gesenkt. Die Zahl der Asylgesuche sinkt im dritten Jahr in Folge. Wenn die tieferen Prognosen zutreffen, liegen wir Ende Jahr um 27 Prozent tiefer als Ende 2023.
+Auch die Pendenzen konnten stark reduziert werden. Als ich mein Amt antrat, hatten wir fast 10 000 offene Pendenzen. Aktuell sind wir bei etwa 2500 und bis Ende Jahr wollen wir alle Pendenzen abgearbeitet haben. Dies obwohl das SEM aufgrund der Entlastungsmassnahmen im letzten und in diesem Jahr 150 Stellen streichen muss. Weniger Asylgesuche und weniger Pendenzen entlasten das System. Die Kantone und Gemeinden beginnen das jetzt zu spüren.
+Noch stärker sind die Rückgänge bei den irregulären Einreisen. Der Schutz der Schengen-Aussengrenzen durch die EU-Staaten, aber auch durch die Schweiz zeigt beeindruckende Wirkung. Die irregulären Einreisen sind um 50 Prozent zurückgegangen. Auch weitere Massnahmen, die wir ergriffen haben, zeigen Wirkung. Für Asylsuchende aus nordafrikanischen Ländern beispielsweise haben wir die Verfahren stark beschleunigt, was ebenfalls das ganze System entlastet. Die Übernachtungen dieser Gruppe sind um 50 Prozent zurückgegangen. Damit wird die Schweiz als Zielland für diese Gruppe weniger attraktiv.
+Dann haben wir diese Einzelfallbehandlung an den runden Tischen aller Asylregionen an die Hand genommen. Wir haben eine neue Taskforce eingesetzt und damit konnten straffällige Asylsuchende deutlich häufiger der Strafverfolgung zugeführt werden. Die Zahl der Sicherheitsvorfälle in den Bundesasylzentren hat sich innerhalb von zwei Jahren mehr als halbiert.
+Wir führen etwa doppelt so viele abgewiesene Asylsuchende zurück als alle anderen vergleichbaren europäischen Länder. Dabei stützen wir uns auf mehr als sechzig Abkommen mit Herkunftsstaaten. Ende Mai haben wir ein Abkommen mit Marokko abschliessen können. Damit konnten wir auch die Rückführungen in dieses Land verbessern. Das schaffen viele andere Länder nicht.
+Doch nicht nur bei der Rückkehr sind wir in Europa Vorreiter, wir sind es auch bei der Integration. Mehr als 50 Prozent der Flüchtlinge und vorläufig Aufgenommenen haben bei uns nach fünf Jahren einen Job. Wir sind damit europaweit führend. Das bestätigt auch die OECD in ihrem neuesten Bericht.
+Wir sind daran, auch in diesen Bereichen weitere Massnahmen umzusetzen. Wir verbessern uns laufend und kommen im nächsten Jahr mit einem weiteren Gesetzespaket, um diese Bereiche weiter verbessern zu können.
+Nun komme ich zu diesen vier Motionen. Wenn ich Ihnen einleitend darstellen konnte, dass die Zahlen positiv sind, kann ich auch deutlich machen, dass die Ausserordentlichkeit oder die Dringlichkeit bei keiner dieser Motionen gegeben ist. Der Bundesrat lehnt sie alle ab.
+Ich beginne mit der Motion Friedli Esther 26.3571, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung tatsächlich obligatorisch sein." Die Motion verlangt, dass ausländische Straftäter ab einer Freiheitsstrafe von einem Jahr zwingend und ohne Ausnahme des Landes verwiesen werden. Das bedeutet konkret, dass in solchen Fällen weder die Härtefallklausel angewendet noch im Einzelfall geprüft werden soll, ob die Landesverweisung verhältnismässig ist. Der Bundesrat lehnt diese Forderung aus drei Gründen ab:
+1. Ich möchte daran erinnern, dass das Parlament bei der Umsetzung der Ausschaffungs-Initiative bewusst eine Härtefallklausel geschaffen hat und dass die Durchsetzungs-Initiative, die diese abschaffen wollte, von der Stimmbevölkerung deutlich abgelehnt wurde. Die Härtefallklausel stellt sicher, dass zentrale verfassungs- und völkerrechtliche Vorgaben eingehalten werden. Dazu gehören insbesondere das Verhältnismässigkeitsprinzip, der Schutz des Privat- und Familienlebens sowie das Non-Refoulement-Prinzip. Die Rechtsprechung des Bundesgerichtes und des Europäischen Gerichtshofes für Menschenrechte verlangt zudem eine Prüfung des Einzelfalles. Eine zwingende Landesverweisung ab einem Jahr Freiheitsstrafe würde diese ausschliessen. Damit könnte das Gericht auch die konkreten Umstände des Einzelfalles nicht mehr berücksichtigen. Dies ist mit übergeordnetem Recht nicht vereinbar.
+2. Eine zwingende Landesverweisung bedeutet noch nicht, dass diese auch tatsächlich vollzogen werden kann, auch nicht in Dänemark. Fehlende Reisedokumente oder die mangelnde Kooperation des Herkunftsstaates können den Vollzug weiterhin verhindern. Daran ändert diese Motion nichts. Bei schweren Straftaten werden Landesverweisungen bereits heute konsequent ausgesprochen.
+3. Die heutige Praxis zeigt: Je schwerer die Straftat, desto häufiger wird eine Landesverweisung ausgesprochen. Bei Freiheitsstrafen von ein bis zwei Jahren liegt die Quote im Jahr 2025 bei 79 Prozent, bei Freiheitsstrafen von zwei bis drei Jahren sind es bereits 86 Prozent, bei drei bis vier Jahren rund 96 Prozent. Bei schweren Straftaten ist die Landesverweisung damit bereits heute klar die Regel. Die Härtefallklausel kommt in diesen Fällen also nur zurückhaltend zur Anwendung.
+Ich komme zum Fazit: Eine weitere Verschärfung ist weder mit dem übergeordneten Recht vereinbar noch geeignet, die bestehenden Vollzugsprobleme zu lösen.
+Aus all diesen Gründen beantragt Ihnen der Bundesrat, diese Motion abzulehnen.
+Nun zur Motion 26.3626, die Herr Salzmann begründet hat: Mit dem Entzug des Bürgerrechts lässt sich kein Terrorakt verhindern, weil der Entzug zu spät kommt. Für Terrorprävention braucht es andere Massnahmen. Genau deshalb hat die Schweiz seit 2020 ihr Sicherheitsdispositiv deutlich verstärkt. Fedpol, der Nachrichtendienst und die kantonalen Strafverfolgungsbehörden greifen bei konkreten Hinweisen auf eine terroristische Gefahr präventiv ein. Dafür stehen inzwischen Instrumente zur Verfügung, etwa Meldepflichten, Kontakt- und Ausreiseverbote, Ein- oder Ausgrenzungen sowie in bestimmten Fällen auch Hausarrest.
+Im Rahmen eines Strafverfahrens können weitere Massnahmen angeordnet werden. So wird eine beschuldigte Person in Untersuchungs- und Sicherheitshaft genommen, wenn ein dringender Tatverdacht besteht, dass die Person weitere schwere Straftaten begeht, oder wenn die Person konkret damit gedroht hat, ein schwerwiegendes Verbrechen zu begehen.
+Kommen wir nun zum Entzug des Schweizer Bürgerrechts - diesen fordert ja die Motion. Der Entzug des Bürgerrechts dient nicht dazu, einer möglichen Gefahr im Voraus zu begegnen. Er greift erst nach einer strafrechtlichen Verurteilung. Die Motion verlangt, dass ein Entzug des Bürgerrechts auch bei Straftaten möglich sein soll, die keinen unmittelbaren Bezug zum Terrorismus haben. Er soll selbst dann in Betracht kommen, wenn keine strafrechtliche Verurteilung vorliegt. Das geht dem Bundesrat zu weit.
+Zu weit geht dem Bundesrat auch der in der Motion vorgesehene Automatismus. Die zuständigen Behörden müssen auch künftig prüfen können, ob ein Entzug des Bürgerrechts im konkreten Einzelfall verhältnismässig ist. Der Entzug des Bürgerrechts ist ein schwerwiegender Eingriff. Deshalb braucht es auch weiterhin eine sorgfältige Prüfung aller Umstände.
+Sie haben es bereits gehört: Bund und Kantone haben ihre Zusammenarbeit gegen Terrorismus in den letzten Jahren deutlich verstärkt. Die Behörden verfügen heute über wirksame Instrumente, um Gefahren früh zu erkennen und Straftaten zu verhindern. Die Motion würde dazu nichts beitragen, sie würde mit ihrem Automatismus aber das Prinzip der Verhältnismässigkeit verletzen. Das lehnt der Bundesrat ab. Er beantragt Ihnen, diese Motion abzulehnen.
+Nun komme ich zur Motion 26.3655, die Herr Schwander begründet hat. Ihre Forderung ist bereits erfüllt. Der Bund ist gesetzlich verpflichtet, die Kantone und Gemeinden bei der Einrichtung der Zentren frühzeitig einzubeziehen. Sowohl im Rahmen des Sachplanverfahrens als auch beim Plangenehmigungsverfahren werden der betroffene Kanton und die Gemeinde angehört; das wird immer so gemacht.
+Das Asylwesen ist eine Verbundaufgabe von Bund, Kantonen und Gemeinden. An zwei nationalen Asylkonferenzen in den Jahren 2013 und 2014 wurde einstimmig beschlossen, den Asylbereich neu zu strukturieren und in sechs Asylregionen aufzuteilen. Die drei Staatsebenen verständigten sich anschliessend im gegenseitigen Einvernehmen darauf, wie viele Unterbringungsplätze zur Verfügung stehen sollen.
+Seit über zehn Jahren arbeitet der Bund am Aufbau der vereinbarten 5000 Plätze, aber das macht er nicht alleine. Sowohl Privatpersonen als auch Gemeinden und Kantone haben immer die Möglichkeit, sich in das Verfahren einzubringen und Einsprache zu erheben. Das Anliegen der vorliegenden Motion ist somit bereits erfüllt. Der Bundesrat beantragt, die Motion abzulehnen.
+Zur letzten Motion äussere ich mich, sobald sie wieder in diesen Rat kommt, nachdem sie von der vorberatenden Kommission geprüft wurde.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Würth Benedikt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir beraten in dieser reich befrachteten Session jetzt PFAS Teil 2, aber die Ausgangslage ist mehr oder weniger die gleiche wie die bei PFAS Teil 1 in der ersten Sessionswoche. Ich bin sicher, dass Sie sich noch an meine Ausführungen in der ersten Sessionswoche zu PFAS Teil 1 erinnern. Das Problem ist, dass wir in der Kommission eine globale Gesamtbeurteilung aller dieser Motionen vornehmen wollten. Ein Teil der Motionen ist im Zuständigkeitsbereich des EDI - diesen Teil haben wir in der ersten </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wir beraten in dieser reich befrachteten Session jetzt PFAS Teil 2, aber die Ausgangslage ist mehr oder weniger die gleiche wie die bei PFAS Teil 1 in der ersten Sessionswoche. Ich bin sicher, dass Sie sich noch an meine Ausführungen in der ersten Sessionswoche zu PFAS Teil 1 erinnern. Das Problem ist, dass wir in der Kommission eine globale Gesamtbeurteilung aller dieser Motionen vornehmen wollten. Ein Teil der Motionen ist im Zuständigkeitsbereich des EDI - diesen Teil haben wir in der ersten Sessionswoche beraten -, und der zweite Teil der Motionen ist im Zuständigkeitsbereich des UVEK. Darum wurde die Beratung in unserem Rat in zwei Teile aufgesplittet. In der Sache ist die Angelegenheit jedoch unverändert.
+Ich fasse die Ausgangslage jetzt nochmals zusammen, aber wirklich nur kurz: Wir entschieden in der UREK-S, dass wir im Grundsatz mit der vom Parlament angenommenen Motion der UREK-S 25.3421 weiterarbeiten sollten. Wir führten sehr umfassende Anhörungen durch. Diese Motion ist so aufgegleist, dass die verschiedenen Vorstösse, die jetzt hier im Raum sind, davon mehr oder weniger abgedeckt sind. Auch die Verwaltung äusserte in der Kommission die Meinung, dass alle Anliegen, die in den anderen Motionen enthalten sind, in dieser Motion adressiert sind.
+Parallel zur erwähnten Motion beraten wir auch das Postulat Moser 22.4585, "Aktionsplan zur Reduktion der Belastung von Mensch und Umwelt durch langlebige Chemikalien". Den Bericht in Erfüllung dieses Postulates berieten wir ebenfalls in der Kommission. Anhand dieses Berichts stellten wir der Verwaltung verschiedene Zusatzfragen und beauftragten sie mit Zusatzaufgaben. Aus diesem Prozess, ich hatte es letzte Woche ausgeführt, steht also noch die Erfüllung weiterer Zusatzaufträge aus; die entsprechenden Informationen werden uns dann zugeleitet werden.
+Vor diesem Hintergrund kamen wir in der Kommission zum Schluss, dass wir Ihnen alle diese Motionen, auch diejenigen im Zuständigkeitsbereich des UVEK, zur Ablehnung empfehlen.
+Es kommt hinzu, dass wir seit dem 27. Mai 2026 auch konkrete Beschlüsse des Bundesrates auf dem Tisch haben: einerseits die Vernehmlassungsvorlage zur erwähnten Motion 25.3421 der UREK-S, andererseits aber auch Beschlüsse des Bundesrates, was die Härtefallregelung für PFAS-belastete Landwirtschaftsbetriebe anbelangt. Hier geht es um eine Lösung, die mit Zielrichtung 2027 ausgearbeitet und per 2028 in Kraft treten soll.
+Schliesslich befassten wir uns in der ersten Sessionswoche auch mit der Frage des Vollzugs. Damals entschieden wir anhand meiner Motion 26.3897, dass man pragmatisch vorgehen und mit dem Vollzug zuwarten sollte; zuerst sollte man diese Rechtsetzungsprozesse abschliessen und dann entsprechend den Vollzug vorantreiben.
+Zusammengefasst: Aufgrund dieser Überlegungen kamen wir zum Schluss, dass alle diese Motionen, die in den Zuständigkeitsbereich des UVEK fallen, abgelehnt werden sollen, also die Motion Graf Maya 25.3746, die Motion Crevoisier Crelier 25.3868, die Motion Moser 25.3865, die Motion Silberschmidt 25.3835 und die Motion Mühlemann 25.3855. Die einzelnen Abstimmungsergebnisse können Sie den Kommissionsberichten entnehmen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">423020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je suis d'abord étonné que la motion Chiesa soit placée dans un paquet de motions concernant l'asile. Peut-être l'auteur lui-même fait-il que sa motion ait été attirée dans un paquet qui ne concerne pas le texte qu'il a déposé. Cette motion n'a évidemment rien à voir avec l'asile puisqu'elle concerne les prestations de chômage pour les travailleurs frontaliers. Les frontaliers ne sont pas des requérants d'asile, tout le monde est bien d'accord, donc on parle de quelque chose de tout à fait diffé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je suis d'abord étonné que la motion Chiesa soit placée dans un paquet de motions concernant l'asile. Peut-être l'auteur lui-même fait-il que sa motion ait été attirée dans un paquet qui ne concerne pas le texte qu'il a déposé. Cette motion n'a évidemment rien à voir avec l'asile puisqu'elle concerne les prestations de chômage pour les travailleurs frontaliers. Les frontaliers ne sont pas des requérants d'asile, tout le monde est bien d'accord, donc on parle de quelque chose de tout à fait différent.
+Indépendamment de la manière dont le texte a été présenté par certains responsables ministériels français, notamment avec des positions un peu agressives vis-à-vis de la Suisse, qui a été accusée de profiter de la situation des travailleurs frontaliers, à la base, il y a effectivement quelque chose qui mérite la réflexion. Nous avons des travailleurs frontaliers qui travaillent chez nous, en Suisse, qui payent des cotisations sociales, en Suisse, conformément d'ailleurs à l'Accord sur la libre circulation des personnes qui impose que l'ensemble des assurances sociales doivent être acquittées au lieu où l'on exerce une activité professionnelle, et qui, lorsque le risque pour lequel ils ont versé des cotisations se réalise, doivent s'adresser à leur lieu de domicile. C'était à l'époque Pôle emploi, maintenant cela s'appelle France travail. Ainsi, les travailleurs frontaliers français - je connais bien la situation puisque Genève, vous le savez, est le canton qui reçoit le plus grand nombre de travailleurs frontaliers en provenance de l'Union européenne -, lorsqu'ils sont au chômage et bien qu'ils aient versé des cotisations, ne reçoivent pas de contre-prestations de la Suisse pour les cotisations qu'ils ont versées, qu'ils ont versées uniquement à titre de solidarité par rapport à l'ensemble des travailleurs qui exercent leur activité en Suisse. Donc, sur le fond, la réaction française, qui porte le fer de lance de cette réforme qui a finalement été acceptée au niveau de l'Union européenne, s'explique par le fait que, pour la France, il y a une injustice à corriger.
+Faut-il la corriger comme l'Union européenne le demande, c'est-à-dire en prévoyant qu'à l'avenir un travailleur frontalier qui perd son travail en Suisse devrait s'adresser à nos offices régionaux de placement (ORP), non seulement pour recevoir les indemnités journalières, mais aussi pour recevoir l'aide au placement ? Ceci signifierait que nos fonctionnaires des ORP devraient s'occuper de retrouver un travail pour des travailleurs frontaliers en les plaçant sur un pied d'égalité avec nos chômeurs résidant en Suisse. Pour moi, c'est tout simplement impensable. Il y a déjà une forte concurrence sur le marché de l'emploi, notamment à Genève et dans les cantons qui reçoivent des travailleurs frontaliers. Si, en plus, lorsque le travailleur frontalier perd son emploi, il se trouve sur un pied d'égalité avec le travailleur suisse par rapport au soutien étatique suisse pour retrouver un travail en Suisse, vous imaginez la tension que cela va générer sur la paix sociale.
+Cela ne veut pas dire qu'il ne faut rien faire. Je fais une petite parenthèse. Nous pouvons en discuter aujourd'hui parce que nous sommes encore sur l'Accord sur la libre circulation des personnes de 1999. Si la stabilisation est acceptée par la Suisse, nous n'en parlerions même pas, parce que la décision européenne de renvoyer les chômeurs frontaliers auprès de nos ORP en Suisse devrait être automatiquement acceptée telle qu'elle. Nous n'aurions pas de discussion, puisque cette disposition qui s'applique pour l'ensemble des pays de l'Union européenne serait automatiquement appliquée à la Suisse. Je ferme la parenthèse.
+Est-ce que cela veut dire qu'il ne faut rien faire et continuer à prélever les cotisations sociales pour le chômage, les mettre dans la poche de notre assurance sociale et renvoyer les chômeurs frontaliers auprès des caisses de chômage françaises ? Certainement pas. Il faut trouver une solution, mais pas celle que l'Union européenne nous impose. Je pense que ce que nous encaissons au titre de la couverture du risque chômage en Suisse par les versements des frontaliers doit être versé au pays qui, ensuite, leur verse des prestations. Les travailleurs frontaliers ne devraient donc plus être obligés de cotiser dans le cadre de la solidarité avec l'ensemble des travailleurs en Suisse. Nous pouvons faire évidemment cette concession aux grands principes que nous avons dans le domaine de la sécurité sociale en général pour renoncer à cette solidarité, parce qu'il est absolument impératif - et là je rejoins notre collègue Marco Chiesa et ses conclusions - que ces travailleurs frontaliers, s'ils se retrouvent au chômage, ne soient pas pris en charge par nos ORP.
 </t>
   </si>
 </sst>
@@ -3391,8 +3893,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I137" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:I166" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I166"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="MeetingDate"/>
@@ -6911,9 +7413,7 @@
       <c r="D113" t="s">
         <v>185</v>
       </c>
-      <c r="E113" t="s">
-        <v>20</v>
-      </c>
+      <c r="E113"/>
       <c r="F113" t="s">
         <v>161</v>
       </c>
@@ -7613,6 +8113,833 @@
       </c>
       <c r="I137" t="s">
         <v>508</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>509</v>
+      </c>
+      <c r="B138" t="s">
+        <v>510</v>
+      </c>
+      <c r="C138" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" t="s">
+        <v>93</v>
+      </c>
+      <c r="E138" t="s">
+        <v>47</v>
+      </c>
+      <c r="F138" t="s">
+        <v>48</v>
+      </c>
+      <c r="G138" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" t="s">
+        <v>511</v>
+      </c>
+      <c r="I138" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>513</v>
+      </c>
+      <c r="B139" t="s">
+        <v>510</v>
+      </c>
+      <c r="C139" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" t="s">
+        <v>514</v>
+      </c>
+      <c r="E139" t="s">
+        <v>47</v>
+      </c>
+      <c r="F139" t="s">
+        <v>76</v>
+      </c>
+      <c r="G139" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" t="s">
+        <v>515</v>
+      </c>
+      <c r="I139" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>517</v>
+      </c>
+      <c r="B140" t="s">
+        <v>510</v>
+      </c>
+      <c r="C140" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" t="s">
+        <v>129</v>
+      </c>
+      <c r="E140" t="s">
+        <v>116</v>
+      </c>
+      <c r="F140" t="s">
+        <v>130</v>
+      </c>
+      <c r="G140" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" t="s">
+        <v>518</v>
+      </c>
+      <c r="I140" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>520</v>
+      </c>
+      <c r="B141" t="s">
+        <v>510</v>
+      </c>
+      <c r="C141" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" t="s">
+        <v>80</v>
+      </c>
+      <c r="E141" t="s">
+        <v>47</v>
+      </c>
+      <c r="F141" t="s">
+        <v>48</v>
+      </c>
+      <c r="G141" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" t="s">
+        <v>521</v>
+      </c>
+      <c r="I141" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>523</v>
+      </c>
+      <c r="B142" t="s">
+        <v>510</v>
+      </c>
+      <c r="C142" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" t="s">
+        <v>89</v>
+      </c>
+      <c r="E142"/>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" t="s">
+        <v>524</v>
+      </c>
+      <c r="I142" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>526</v>
+      </c>
+      <c r="B143" t="s">
+        <v>510</v>
+      </c>
+      <c r="C143" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" t="s">
+        <v>89</v>
+      </c>
+      <c r="E143"/>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" t="s">
+        <v>527</v>
+      </c>
+      <c r="I143" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>529</v>
+      </c>
+      <c r="B144" t="s">
+        <v>510</v>
+      </c>
+      <c r="C144" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" t="s">
+        <v>89</v>
+      </c>
+      <c r="E144"/>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" t="s">
+        <v>530</v>
+      </c>
+      <c r="I144" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>532</v>
+      </c>
+      <c r="B145" t="s">
+        <v>510</v>
+      </c>
+      <c r="C145" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" t="s">
+        <v>89</v>
+      </c>
+      <c r="E145"/>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" t="s">
+        <v>533</v>
+      </c>
+      <c r="I145" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>535</v>
+      </c>
+      <c r="B146" t="s">
+        <v>510</v>
+      </c>
+      <c r="C146" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" t="s">
+        <v>89</v>
+      </c>
+      <c r="E146"/>
+      <c r="F146" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" t="s">
+        <v>536</v>
+      </c>
+      <c r="I146" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>538</v>
+      </c>
+      <c r="B147" t="s">
+        <v>510</v>
+      </c>
+      <c r="C147" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" t="s">
+        <v>195</v>
+      </c>
+      <c r="E147" t="s">
+        <v>20</v>
+      </c>
+      <c r="F147" t="s">
+        <v>145</v>
+      </c>
+      <c r="G147" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" t="s">
+        <v>539</v>
+      </c>
+      <c r="I147" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>541</v>
+      </c>
+      <c r="B148" t="s">
+        <v>510</v>
+      </c>
+      <c r="C148" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" t="s">
+        <v>75</v>
+      </c>
+      <c r="E148" t="s">
+        <v>47</v>
+      </c>
+      <c r="F148" t="s">
+        <v>76</v>
+      </c>
+      <c r="G148" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" t="s">
+        <v>542</v>
+      </c>
+      <c r="I148" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>544</v>
+      </c>
+      <c r="B149" t="s">
+        <v>510</v>
+      </c>
+      <c r="C149" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" t="s">
+        <v>545</v>
+      </c>
+      <c r="E149" t="s">
+        <v>47</v>
+      </c>
+      <c r="F149" t="s">
+        <v>161</v>
+      </c>
+      <c r="G149" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" t="s">
+        <v>546</v>
+      </c>
+      <c r="I149" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>547</v>
+      </c>
+      <c r="B150" t="s">
+        <v>510</v>
+      </c>
+      <c r="C150" t="s">
+        <v>11</v>
+      </c>
+      <c r="D150" t="s">
+        <v>115</v>
+      </c>
+      <c r="E150" t="s">
+        <v>116</v>
+      </c>
+      <c r="F150" t="s">
+        <v>85</v>
+      </c>
+      <c r="G150" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="s">
+        <v>548</v>
+      </c>
+      <c r="I150" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>550</v>
+      </c>
+      <c r="B151" t="s">
+        <v>510</v>
+      </c>
+      <c r="C151" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" t="s">
+        <v>211</v>
+      </c>
+      <c r="E151" t="s">
+        <v>124</v>
+      </c>
+      <c r="F151" t="s">
+        <v>35</v>
+      </c>
+      <c r="G151" t="s">
+        <v>30</v>
+      </c>
+      <c r="H151" t="s">
+        <v>551</v>
+      </c>
+      <c r="I151" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>553</v>
+      </c>
+      <c r="B152" t="s">
+        <v>510</v>
+      </c>
+      <c r="C152" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" t="s">
+        <v>554</v>
+      </c>
+      <c r="E152" t="s">
+        <v>116</v>
+      </c>
+      <c r="F152" t="s">
+        <v>30</v>
+      </c>
+      <c r="G152" t="s">
+        <v>30</v>
+      </c>
+      <c r="H152" t="s">
+        <v>555</v>
+      </c>
+      <c r="I152" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>557</v>
+      </c>
+      <c r="B153" t="s">
+        <v>510</v>
+      </c>
+      <c r="C153" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" t="s">
+        <v>207</v>
+      </c>
+      <c r="E153" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" t="s">
+        <v>35</v>
+      </c>
+      <c r="G153" t="s">
+        <v>30</v>
+      </c>
+      <c r="H153" t="s">
+        <v>558</v>
+      </c>
+      <c r="I153" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>560</v>
+      </c>
+      <c r="B154" t="s">
+        <v>510</v>
+      </c>
+      <c r="C154" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" t="s">
+        <v>561</v>
+      </c>
+      <c r="E154" t="s">
+        <v>20</v>
+      </c>
+      <c r="F154" t="s">
+        <v>101</v>
+      </c>
+      <c r="G154" t="s">
+        <v>322</v>
+      </c>
+      <c r="H154" t="s">
+        <v>562</v>
+      </c>
+      <c r="I154" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>564</v>
+      </c>
+      <c r="B155" t="s">
+        <v>510</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" t="s">
+        <v>60</v>
+      </c>
+      <c r="E155" t="s">
+        <v>20</v>
+      </c>
+      <c r="F155" t="s">
+        <v>61</v>
+      </c>
+      <c r="G155" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" t="s">
+        <v>565</v>
+      </c>
+      <c r="I155" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>567</v>
+      </c>
+      <c r="B156" t="s">
+        <v>510</v>
+      </c>
+      <c r="C156" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156" t="s">
+        <v>568</v>
+      </c>
+      <c r="E156" t="s">
+        <v>20</v>
+      </c>
+      <c r="F156" t="s">
+        <v>130</v>
+      </c>
+      <c r="G156" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" t="s">
+        <v>569</v>
+      </c>
+      <c r="I156" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>571</v>
+      </c>
+      <c r="B157" t="s">
+        <v>510</v>
+      </c>
+      <c r="C157" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" t="s">
+        <v>260</v>
+      </c>
+      <c r="E157" t="s">
+        <v>40</v>
+      </c>
+      <c r="F157" t="s">
+        <v>124</v>
+      </c>
+      <c r="G157" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" t="s">
+        <v>572</v>
+      </c>
+      <c r="I157" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>574</v>
+      </c>
+      <c r="B158" t="s">
+        <v>510</v>
+      </c>
+      <c r="C158" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158" t="s">
+        <v>160</v>
+      </c>
+      <c r="E158" t="s">
+        <v>47</v>
+      </c>
+      <c r="F158" t="s">
+        <v>161</v>
+      </c>
+      <c r="G158" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
+        <v>575</v>
+      </c>
+      <c r="I158" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>577</v>
+      </c>
+      <c r="B159" t="s">
+        <v>510</v>
+      </c>
+      <c r="C159" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" t="s">
+        <v>578</v>
+      </c>
+      <c r="E159" t="s">
+        <v>47</v>
+      </c>
+      <c r="F159" t="s">
+        <v>579</v>
+      </c>
+      <c r="G159" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" t="s">
+        <v>580</v>
+      </c>
+      <c r="I159" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>582</v>
+      </c>
+      <c r="B160" t="s">
+        <v>510</v>
+      </c>
+      <c r="C160" t="s">
+        <v>13</v>
+      </c>
+      <c r="D160" t="s">
+        <v>583</v>
+      </c>
+      <c r="E160" t="s">
+        <v>47</v>
+      </c>
+      <c r="F160" t="s">
+        <v>85</v>
+      </c>
+      <c r="G160" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" t="s">
+        <v>584</v>
+      </c>
+      <c r="I160" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>586</v>
+      </c>
+      <c r="B161" t="s">
+        <v>510</v>
+      </c>
+      <c r="C161" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" t="s">
+        <v>292</v>
+      </c>
+      <c r="E161" t="s">
+        <v>116</v>
+      </c>
+      <c r="F161" t="s">
+        <v>130</v>
+      </c>
+      <c r="G161" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" t="s">
+        <v>587</v>
+      </c>
+      <c r="I161" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>589</v>
+      </c>
+      <c r="B162" t="s">
+        <v>510</v>
+      </c>
+      <c r="C162" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" t="s">
+        <v>89</v>
+      </c>
+      <c r="E162"/>
+      <c r="F162" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" t="s">
+        <v>590</v>
+      </c>
+      <c r="I162" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>592</v>
+      </c>
+      <c r="B163" t="s">
+        <v>510</v>
+      </c>
+      <c r="C163" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" t="s">
+        <v>60</v>
+      </c>
+      <c r="E163" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163" t="s">
+        <v>61</v>
+      </c>
+      <c r="G163" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" t="s">
+        <v>593</v>
+      </c>
+      <c r="I163" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>594</v>
+      </c>
+      <c r="B164" t="s">
+        <v>510</v>
+      </c>
+      <c r="C164" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" t="s">
+        <v>89</v>
+      </c>
+      <c r="E164"/>
+      <c r="F164" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" t="s">
+        <v>595</v>
+      </c>
+      <c r="I164" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>597</v>
+      </c>
+      <c r="B165" t="s">
+        <v>510</v>
+      </c>
+      <c r="C165" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165" t="s">
+        <v>598</v>
+      </c>
+      <c r="E165" t="s">
+        <v>20</v>
+      </c>
+      <c r="F165" t="s">
+        <v>161</v>
+      </c>
+      <c r="G165" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="s">
+        <v>599</v>
+      </c>
+      <c r="I165" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>601</v>
+      </c>
+      <c r="B166" t="s">
+        <v>510</v>
+      </c>
+      <c r="C166" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" t="s">
+        <v>230</v>
+      </c>
+      <c r="E166" t="s">
+        <v>47</v>
+      </c>
+      <c r="F166" t="s">
+        <v>71</v>
+      </c>
+      <c r="G166" t="s">
+        <v>30</v>
+      </c>
+      <c r="H166" t="s">
+        <v>602</v>
+      </c>
+      <c r="I166" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/Debats_SEM_Migration.xlsx
+++ b/Debats_SEM_Migration.xlsx
@@ -380,17 +380,17 @@
     <t xml:space="preserve">TG</t>
   </si>
   <si>
-    <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont, noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
+    <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont; noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
 Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorbestraft und islamistisch radikalisiert. Er griff wahllos Mens</t>
   </si>
   <si>
-    <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont, noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
+    <t xml:space="preserve">25 Jahre ist es her seit 9/11, dem schlimmsten Terroranschlag der Geschichte. Unser Land blieb glücklicherweise lange verschont; noch 2010 sagte das Fedpol, es gebe keine Hinweise auf Terrorziele in der Schweiz. Es war eine Frage der Zeit, bis sich das änderte. Die Zäsur kam 2020 mit den Messerangriffen von Morges und Lugano.
 Der jüngste Fall ist der schreckliche Messerterror von Winterthur. Der Täter ist ein eingebürgerter Türke, vorbestraft und islamistisch radikalisiert. Er griff wahllos Menschen an, gefährdete zahlreiche Kinder und verletzte drei Personen teils schwer. Die einst sichere Schweiz wird immer unsicherer. Bei der Bundesanwaltschaft laufen aktuell über 140 Terrorverfahren - ein trauriger Rekord. Gemäss Nachrichtendienst des Bundes ist die Terrorbedrohung erhöht und geprägt vom Dschihadismus. Die allermeisten Dschihadisten sind Ausländer oder Doppelbürger, das bestätigte eine Studie der Fachhochschule ZHAW.
-Auch in den Gefängnissen zeigen sich die Folgen der unkontrollierten Massenmigration in unser Land. 70 Prozent der Insassen sind Ausländer, und weitere 15 Prozent sind Schweizer mit Migrationshintergrund. Das bedeutet, für Schweizer ohne Migrationshintergrund würden 15 Prozent unserer Gefängnisplätze genügen. Diese Zahlen bestätigen es eben klar, man kann es nicht schönreden: Wir haben immer mehr importierte Probleme, importierte Kriminalität und importierte Gewalt; und wir haben immer mehr Opfer.
-Personen, die eingebürgert werden, müssen seit 1992 ihren bisherigen Pass nicht mehr abgeben. Man könne ihnen - das war das Hauptargument für das Doppelbürgerrecht - den Schweizer Pass dann einfacher entziehen, wenn irgendetwas passiere und sie kriminell würden. Der Bundesrat behauptet auch heute in der Stellungnahme zur Motion 26.3617, er nutze den Passentzug zur Terrorbekämpfung. Tatsächlich gab es seit dem Jahr 2000 nur gerade zehn Entzugsverfahren: Siebenmal wurde ein Entzug angeordnet, und nur drei Fälle sind rechtskräftig geworden; und das bei einer Million Einbürgerungen seit dem Jahr 2000. Das beweist, dass die Behörden auch bei den schwersten Verbrechen, bei Terrorgefährdern wegschauen.
+Auch in den Gefängnissen zeigen sich die Folgen der unkontrollierten Massenmigration in unser Land. 70 Prozent der Insassen sind Ausländer, und weitere 15 Prozent sind Schweizer mit Migrationshintergrund. Das bedeutet, für Schweizer ohne Migrationshintergrund würden 15 Prozent unserer Gefängnisplätze genügen. Diese Zahlen bestätigen es eben klar, man kann es nicht schönreden: Wir haben immer mehr importierte Probleme, importierte Kriminalität und importierte Gewalt, und wir haben immer mehr Opfer.
+Personen, die eingebürgert werden, müssen seit 1992 ihren bisherigen Pass nicht mehr abgeben. Man könne ihnen - das war das Hauptargument für das Doppelbürgerrecht - den Schweizer Pass dann einfacher entziehen, wenn irgendetwas passiere und sie kriminell würden. Der Bundesrat behauptet auch heute in der Stellungnahme zur Motion 26.3617, er nutze den Passentzug zur Terrorbekämpfung. Tatsächlich gab es seit dem Jahr 2000 nur gerade zehn Entzugsverfahren: Siebenmal wurde ein Entzug angeordnet, und nur drei Fälle sind rechtskräftig geworden, und das bei einer Million Einbürgerungen seit dem Jahr 2000. Das beweist, dass die Behörden auch bei den schwersten Verbrechen, bei Terrorgefährdern wegschauen.
 Die heutige Rechtsgrundlage für Ausbürgerungen, Artikel 42 des Bürgerrechtsgesetzes, ist eben ein zahnloser Tiger; das bestätigen die Zahlen. Deshalb braucht es eine griffige Grundlage, nicht nur eine Kann-Bestimmung, sondern eine Muss-Bestimmung. Man muss in bestimmten Fällen den Pass entziehen. Die Motion 26.3617 soll das bei Kapitalverbrechen und bei radikalisierten Gefährdern sicherstellen. Den Fünfer und das Weggli darf es halt nicht mehr geben: Wer seinen Heimatpass bei einer Einbürgerung behalten will, der muss es in Kauf nehmen, dass der Schweizer Pass bei schwersten Verbrechen entzogen wird; staatenlos wird dadurch niemand.
 Dschihadisten und Terroristen sind zu allem fähig. Sie wollen unseren Rechtsstaat, unsere Werte und unsere westliche Lebensweise zerstören. Nur wenn es ihnen dann irgendwann selber an den Kragen geht, berufen Sie sich gerne auf die Annehmlichkeiten unseres Rechtsstaates.
-Wir dürfen nicht warten, bis der nächste Anschlag geschieht. Unsere Bevölkerung hat ein Recht darauf, vor Verbrechern und Terroristen geschützt zu werden. Das ist die Kernaufgabe, das ist die wichtigste Aufgabe unseres Staates. Jedes Opfer ist eines zu viel. Wer unser Land terroristisch angreift oder Kapitalverbrechen begeht, hat sein Bürgerrecht verwirkt. Er ist nicht mehr Teil dieses Landes, er ist nicht mehr Teil dieser Wertegemeinschaft. Wir müssen alles daransetzen, dass solche Leute erst gar nicht zu uns kommen; und wenn sie dennoch hier sind, müssen wir alles tun, um sie aus dem Land zu schaffen. Sie haben bei uns nichts verloren, sie gehören ins Gefängnis, wenn nötig ausgebürgert und zurück in ihr Heimatland gebracht.
+Wir dürfen nicht warten, bis der nächste Anschlag geschieht. Unsere Bevölkerung hat ein Recht darauf, vor Verbrechern und Terroristen geschützt zu werden. Das ist die Kernaufgabe, das ist die wichtigste Aufgabe unseres Staates. Jedes Opfer ist eines zu viel. Wer unser Land terroristisch angreift oder Kapitalverbrechen begeht, hat sein Bürgerrecht verwirkt. Er ist nicht mehr Teil dieses Landes, er ist nicht mehr Teil dieser Wertegemeinschaft. Wir müssen alles daransetzen, dass solche Leute erst gar nicht zu uns kommen, und wenn sie dennoch hier sind, müssen wir alles tun, um sie aus dem Land zu schaffen. Sie haben bei uns nichts verloren, sie gehören ins Gefängnis, wenn nötig ausgebürgert und zurück in ihr Heimatland gebracht.
 Es ist ein Gebot des gesunden Menschenverstandes. Kein vernünftiger Mensch in diesem Land will Terroristen und Dschihadisten hierbehalten. Das will niemand, das will kein Schweizer, das will kein Ausländer, das will kein Doppelbürger - das will niemand. Niemand will solche Leute hier bei uns behalten. Wir müssen alles dafür tun, dass sie gehen müssen.
 Ich danke Ihnen deshalb für die Annahme dieser Motion. Sie macht unser Land wieder sicherer.
 </t>
@@ -408,8 +408,9 @@
   <si>
     <t xml:space="preserve">Die Motion 26.3131, "Von Dänemark lernen. Bei längerfristigen Freiheitsstrafen muss die obligatorische Landesverweisung obligatorisch sein", beauftragt den Bund, die erforderlichen Gesetzesanpassungen vorzulegen, damit kriminelle Ausländer bei einer Freiheitsstrafe ab einem Jahr zwingend eine Landesverweisung erhalten und diese dann auch vollzogen wird.
 Die obligatorische Landesverweisung wird in vielen Fällen trotz schwerer Straftaten nicht ausgesprochen oder nicht vollzogen. Die Hauptursache ist die viel zu large, oft angewendete Härtefallklausel, obwohl sie eigentlich als Ausnahme ausgestaltet wurde. Leider ist die Härtefallklausel keine Ausnahme mehr. Von den angeordneten Landesverweisungen werden gemäss SEM schweizweit nur 63 Prozent vollzogen, und die Unterschiede im kantonalen Vollzug sind enorm. Dies macht unseren Rechtsstaat unglaubwürdig. Der Grossteil der Bevölkerung fordert bei schweren Straftaten von Ausländern mehr Ausschaffungen.
-Dänemark macht es vor und schafft Kriminelle ab einem Jahr Freiheitsstrafe automatisch aus. Dieses Gesetz trat am 1. Mai 2016 in Kraft. Es hat natürlich auch eine abschreckende Wirkung; die Asylzahlen sind seither stark zurückgegangen - ein Erfolg. Diesem wegweisenden Beispiel soll auch die Schweiz folgen: Der Gesetzgeber soll die Landesverweisung bei längeren Freiheitsstrafen für alle Konstellationen als verhältnismässig und Härtefälle als ausgeschlossen erklären.
-Der Bundesrat ist hier leider sehr zurückhaltend. Einmal mehr bringt er als Grund vor, dass fehlende Reisedokumente oder mangelnde Kooperation den Vollzug verunmöglichen können. Diese Hindernisse dürfen aber keinen Grund gegen einen Vollzug darstellen. Ich habe auf dem Gericht und auf der Staatsanwaltschaft gearbeitet und es oft erlebt, dass Pässe und Reisedokumente verschwunden sind, vielleicht auch durch Absicht, um einer Ausschaffung zu entgehen. Wir müssen uns Dänemark anschliessen und unsere Praxis endlich verschärfen. Es darf bei Ausschaffungen auch nicht so grosse kantonale Unterschiede geben. Um eine Freiheitsstrafe von einem Jahr zu erhalten, sei dies bedingt oder unbedingt, braucht es etwas. Man kriegt nicht einfach so eine längere Freiheitsstrafe, es handelt sich nicht um Bagatelldelikte. Die Bevölkerung fordert bei Ausschaffungen schon seit längerer Zeit eine härtere Praxis, und die Europäische Menschenrechtskonvention (EMRK) darf nicht immer als Grund dagegen vorgebracht werden.
+Dänemark macht es vor und schafft Kriminelle ab einem Jahr Freiheitsstrafe automatisch aus. Dieses Gesetz trat am 1.[NB]Mai 2016 in Kraft. Es hat natürlich auch eine abschreckende Wirkung; die Asylzahlen sind seither stark zurückgegangen - ein Erfolg. Diesem wegweisenden Beispiel soll auch die Schweiz folgen: Der Gesetzgeber soll die Landesverweisung bei längeren Freiheitsstrafen für alle Konstellationen als verhältnismässig und Härtefälle als ausgeschlossen erklären.
+Der Bundesrat ist hier leider sehr zurückhaltend. Einmal mehr bringt er als Grund vor, dass fehlende Reisedokumente oder mangelnde Kooperation den Vollzug verunmöglichen können. Diese Hindernisse dürfen aber keinen Grund gegen einen Vollzug darstellen. Ich habe auf dem Gericht und auf der Staatsanwaltschaft gearbeitet und es oft erlebt, dass Pässe und Reisedokumente verschwunden sind, vielleicht auch durch Absicht, um einer Ausschaffung zu entgehen. Wir müssen uns Dänemark anschliessen und unsere Praxis endlich verschärfen. 
+Es darf bei Ausschaffungen auch nicht so grosse kantonale Unterschiede geben. Um eine Freiheitsstrafe von einem Jahr zu erhalten, sei dies bedingt oder unbedingt, braucht es etwas. Man kriegt nicht einfach so eine längere Freiheitsstrafe, es handelt sich nicht um Bagatelldelikte. Die Bevölkerung fordert bei Ausschaffungen schon seit längerer Zeit eine härtere Praxis, und die Europäische Menschenrechtskonvention (EMRK) darf nicht immer als Grund dagegen vorgebracht werden.
 Bitte unterstützen Sie unsere Fraktionsmotion.
 </t>
   </si>
@@ -428,12 +429,12 @@
   </si>
   <si>
     <t xml:space="preserve">Bei der Motion 26.3616 geht es um eine einfache Frage: Darf der Bund einer Gemeinde eine Asylunterkunft vor die Nase setzen, auch wenn die betroffene Bevölkerung dies nicht will? Wir von der SVP-Fraktion sagen ganz klar Nein. Genau deshalb braucht es unseren Vorstoss.
-Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5000 regulären Unterbringungsplätzen in seinen Bundesasylzentren; in besonderen Situationen soll die Kapazität sogar auf 10 000 Plätze erhöht werden können. Diese grossen Einrichtungen wirken sich auf die Gemeinde, die Schulen, den Verkehr, die Sicherheit, das lokale Gewerbe sowie grundsätzlich auf das Zusammenleben vor Ort aus. Wer diese Auswirkungen tragen muss, soll entsprechend mitbestimmen können.
-Der Bundesrat führt an, dass die Gemeinden angehört würden. Doch angehört zu werden, ist nicht dasselbe wie mitzuentscheiden. Weder eine Informationsveranstaltung noch eine Stellungnahme oder ein Einspracheverfahren ersetzen die demokratische Mitsprache bzw. das Recht einer Gemeinde, einen Standort abzulehnen.
+Wir reden hier nicht von einem Büro des Bundes, das irgendwo eröffnet wird, sondern von grossen Bundesasylzentren mit 250, 350 oder mehr Plätzen. Der Bund selbst definiert diese Grössenordnung als Standard und plant weiterhin mit 5000 regulären Unterbringungsplätzen in seinen Bundesasylzentren; in besonderen Situationen soll die Kapazität sogar auf 10[NB]000 Plätze erhöht werden können. Diese grossen Einrichtungen wirken sich auf die Gemeinde, die Schulen, den Verkehr, die Sicherheit, das lokale Gewerbe sowie grundsätzlich auf das Zusammenleben vor Ort aus. Wer diese Auswirkungen tragen muss, soll entsprechend mitbestimmen können.
+Der Bundesrat führt an, dass die Gemeinden angehört würden. Doch angehört zu werden, ist nicht dasselbe, wie mitzuentscheiden. Weder eine Informationsveranstaltung noch eine Stellungnahme oder ein Einspracheverfahren ersetzen die demokratische Mitsprache bzw. das Recht einer Gemeinde, einen Standort abzulehnen.
 Hier setzt der Vorstoss an. Wir wollen weder zusätzliche Bürokratie noch eine Blockade, sondern etwas ganz Einfaches: Will der Bund in einer Gemeinde ein neues Bundesasylzentrum errichten, muss die betroffene Standortgemeinde zustimmen. Dies ist kein radikaler Gedanke, sondern Ausdruck des Föderalismus und der Gemeindeautonomie - und es entspricht unserem Verständnis von Demokratie. Es darf nicht sein, dass der Bund am grünen Tisch über den Standort grosser Asylunterkünfte entscheidet, während die betroffene Bevölkerung lediglich informiert wird.
-Niemand bestreitet die Verantwortung des Bundes im Asylwesen. Sie bedeutet jedoch nicht, dass er über die Köpfe der Gemeinden hinweg entscheiden darf. Die letzten Jahre haben gezeigt, wie schnell sich die Situation im Asylbereich verändern kann. Im Jahr 2025 wurden in der Schweiz 25 000 Asylgesuche gestellt. Der Bund musste seine Unterbringungskapazitäten massiv ausbauen und hält fest, dass die Bereitstellung von Unterbringungsplätzen für Kantone und Gemeinden eine grosse Herausforderung darstellt.
+Niemand bestreitet die Verantwortung des Bundes im Asylwesen. Sie bedeutet jedoch nicht, dass er über die Köpfe der Gemeinden hinweg entscheiden darf. Die letzten Jahre haben gezeigt, wie schnell sich die Situation im Asylbereich verändern kann. Im Jahr 2025 wurden in der Schweiz 25[NB]000 Asylgesuche gestellt. Der Bund musste seine Unterbringungskapazitäten massiv ausbauen und hält fest, dass die Bereitstellung von Unterbringungsplätzen für Kantone und Gemeinden eine grosse Herausforderung darstellt.
 Daher muss die Verantwortung dort wahrgenommen werden, wo sie hingehört. Immer grössere Strukturen zu schaffen und den Gemeinden erst danach zu erklären, warum sie diese akzeptieren müssen - das geht nicht. Zuerst muss gefragt werden, ob eine Gemeinde dies überhaupt will. Der Bund fordert Planungssicherheit, doch auch die Gemeinden benötigen Planungssicherheit. Eine Gemeinde muss wissen, was auf ihrem Gebiet geschieht, und die Bevölkerung hat Anspruch darauf, dass ihre demokratischen Rechte ernst genommen werden.
-Des Weiteren enthält der Vorstoss eine ausdrückliche Ausnahme für den Asylnotstand. Es geht nicht darum, dass eine Gemeinde in einer ausserordentlichen Krisensituation jede staatliche Massnahme verhindern kann. Ausserhalb eines Notstandes muss jedoch gelten: keine neuen, grossen Asylunterkünfte gegen den ausdrücklichen Willen der betroffenen Standortgemeinde.
+Des Weiteren enthält der Vorstoss eine ausdrückliche Ausnahme für den Asylnotstand. Es geht nicht darum, dass eine Gemeinde in einer ausserordentlichen Krisensituation jede staatliche Massnahme verhindern kann. Ausserhalb eines Notstandes muss jedoch gelten: keine neuen, grossen Asylunterkünfte gegen den ausdrücklichen Willen der betroffenen Standortgemeinde. [GZ]
 Ich bitte Sie, den Vorstoss zu unterstützen.
 </t>
   </si>
@@ -459,13 +460,16 @@
     <t xml:space="preserve">Rutz Gregor</t>
   </si>
   <si>
-    <t xml:space="preserve">In meiner Motion 26.3668 geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze We</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In meiner Motion 26.3668 geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17. Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist, hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, sodass Leute, die schon in sicheren Staaten leben, hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige, neue Motive ergänzt hat und dass es eben einen Unterschied gibt zwischen einer Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
-Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27. Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." (AB 2024 N 809) Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4. Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." Es erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist diese Orientierung am EuGH sicher nicht das Relevante. Trotzdem sagen Sie dann, nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, die über alle Gesuche 97,5 Prozent Zustimmung ergibt. Das erstaunt und sieht dann doch eher nach einer pauschalen Prüfung aus. Wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das erhellende Fakten zutage bringt. Dieser Fragebogen lag dem Bundesverwaltungsgericht nämlich vor. Es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche sie gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen - also Ihr Staatssekretariat, das mit diesen Fragen befasst ist - den eigentlichen Willen des Gesetzgebers, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhalte, werde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiell-rechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
+    <t xml:space="preserve">In meiner Motion 26.3668 geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17.[NB]Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In meiner Motion 26.3668 geht es einmal mehr um die Praxisänderung des Staatssekretariats für Migration vom 17.[NB]Juli 2023 in Bezug auf die Asylgewährung für Afghaninnen - eine Praxisänderung, die stillschweigend, ohne Konsultation vorgenommen worden ist. Wir haben hier im Saal schon mehrmals darüber debattiert: im Dezember 2023 und im Mai 2024. Ich habe Ihnen damals schon ausgeführt, warum diese Praxisänderung gegen das Asylgesetz verstösst und im Übrigen natürlich eine Einladung an die ganze Welt ist hierherzukommen. Wenn man weiss, dass man in der Schweiz, wenn man das richtige Geschlecht und den richtigen Pass hat, automatisch aufgenommen wird, befördert das natürlich die Sekundärmigration, sodass Leute, die schon in sicheren Staaten leben, hierherkommen. Die Gesetzeswidrigkeit liegt darin, dass das Staatssekretariat für Migration Artikel 3 des Asylgesetzes in unzulässiger Weise um selbstständige, neue Motive ergänzt hat und dass es eben einen Unterschied gibt zwischen einer Diskriminierung und einer asylrechtlich relevanten Verfolgung. 
+Wir haben das im Detail schon debattiert. Es wurde dann argumentiert, das sei halt jetzt in ganz Europa so, dieser Trend, diese Praxis habe sich so entsprechend bewährt. Ich habe Sie, Herr Bundesrat Jans, dann gefragt, ob es statthaft sei, dass Verwaltungsabteilungen Gesetze nach eigenem Gutdünken interpretieren: "Müsste nicht der Rahmen, den wir Ihnen als Gesetzgeber vorgeben, die Richtschnur des Handelns sein und nicht europäische Empfehlungen?" Sie haben mir damals, das war am 27.[NB]Mai 2024, geantwortet: "Da bin ich bei Ihnen, Herr Rutz. Der Rahmen sind Ihre Vorgaben, das muss so sein." (AB 2024 N 809) Umso erstaunter war ich dann über die Antwort von Ihrer Seite auf die Interpellation Knutti 26.3845 vor etwa zwei Wochen, wo Sie darauf verweisen, dass sich die Asyl- und Wegweisungspraxis betreffend Frauen aus Afghanistan in ganz Europa etabliert habe. Sie schreiben dort: "So hat der Gerichtshof der Europäischen Union (EuGH) mit Urteil vom 4.[NB]Oktober 2024 entschieden, dass Geschlecht und Staatsangehörigkeit ausreichen, um Frauen aus Afghanistan als Flüchtlinge anzuerkennen. [...] Der EuGH verpflichtet die Mitgliedstaaten der EU nicht zu einer Einzelfallprüfung." 
+Es erstaunt doch etwas, dass man sich immer noch an solchen Sachen orientiert. Es ist vielleicht auch ein guter Hinweis auf die Debatte über das Vertragspaket Schweiz-EU, darauf, was das heisst, was da auf uns zukommt. Aber auf jeden Fall ist diese Orientierung am EuGH sicher nicht das Relevante. Trotzdem sagen Sie dann: Nein, nein, wir machen eine Einzelfallprüfung - eine Einzelfallprüfung, die über alle Gesuche 97,5 Prozent Zustimmung ergibt. Das erstaunt und sieht dann doch eher nach einer pauschalen Prüfung aus. 
+Wenn man genauer hinschaut, sieht man, dass Sie das mit einem Fragebogen machen. Dazu gibt es jetzt wieder ein Urteil des Bundesverwaltungsgerichtes, das erhellende Fakten zutage bringt. Dieser Fragebogen lag dem Bundesverwaltungsgericht nämlich vor. Es hat ihn beurteilt und ist zum Schluss gekommen, dass sich dieser Fragebogen nicht für die Begründung von Mehrfachgesuchen eignet. Warum? Mit dem vorgedruckten Fragebogen werden den Gesuchstellerinnen in unzulässiger Weise Asylgründe nahegelegt, welche sie gemäss Artikel 111c Absatz 1 des Asylgesetzes eigentlich selber vorbringen müssten. Das Gericht führt dann aus, wie dieser Fragebogen, also Ihr Staatssekretariat, das mit diesen Fragen befasst ist, den eigentlichen Willen des Gesetzgebers, der im Asylgesetz festgehalten ist, unterläuft, nämlich den Willen, dass man die Fälle eben wirklich separat und für sich anschaut. 
+Es wird dann noch besser, wenn Sie dieses Urteil lesen und die Korrespondenz zwischen dem Staatssekretariat für Migration und den Gesuchstellern einmal dokumentiert sehen. Das Staatssekretariat für Migration schreibt, wenn die Beschwerde beim Bundesverwaltungsgericht zurückgezogen und die Rechtskraft abgewartet werde, könne anschliessend ein Mehrfachgesuch eingereicht werden, welches dann auch an die Hand genommen werden könne. Der Beschwerdeführer sagt dann, wenn ihm also garantiert werden könne, dass die Mandantin dann einen positiven Bescheid erhalte, werde er das machen. Das Bundesverwaltungsgericht hält ganz klar fest, dass hier Erwartungen geschürt werden, die mit den einschlägigen verfahrensrechtlichen, aber auch materiell-rechtlichen Vorgaben des Asylgesetzes nicht zu vereinbaren sind. 
 Hier müssen Sie, Herr Bundesrat, einmal ganz gründlich aufräumen und wirklich noch einmal über die Bücher gehen. Es geht nicht an, dass Bundesämter arbeiten, ohne sich ans Gesetz zu halten. Sie werden jetzt sagen, dass Sie keine Einzelfälle dokumentieren oder kommentieren. Sie werden sagen, dieses Urteil sei ein Einzelfallurteil. Ja, aber man kann dieses Urteil lesen, und es ist ganz genau dokumentiert und aktenkundig, wie hier korrespondiert wird, wie man mit diesen Einzelfällen umgeht. Das geht so nicht. 
-Meine Motion möchte etwas ganz Einfaches: Sie möchte erstens, dass man sich im Staatssekretariat für Migration ans Gesetz hält, und zweitens, dass man diese Praxisänderung, die offensichtlich gesetzeswidrig ist, rückgängig macht und die Fälle einzeln prüft, damit diejenigen Leute Schutz und Aufnahme erhalten, die es nötig haben, und nicht die ganze Welt eingeladen wird, in die Schweiz zu kommen. 
+Meine Motion möchte etwas ganz Einfaches: Sie möchte erstens, dass man sich im Staatssekretariat für Migration ans Gesetz hält, und zweitens, dass man diese Praxisänderung, die offensichtlich gesetzeswidrig ist, rückgängig macht und die Fälle einzeln prüft, damit diejenigen Leute Schutz und Aufnahme erhalten, die es nötig haben, und nicht die ganze Welt eingeladen wird, in die Schweiz zu kommen. [GZ]
 Darum bitte ich Sie hier um Zustimmung.
 </t>
   </si>
@@ -501,7 +505,7 @@
     <t xml:space="preserve">Was bedeutet eigentlich das Adjektiv "vorläufig", wenn ein Zustand zehn, fünfzehn oder noch mehr Jahre dauert? Genau um diese einfache Frage geht es in meiner Motion 24.4063.
 Die vorläufige Aufnahme ist für Situationen gedacht, in denen eine Wegweisung nicht vollzogen werden kann, weil sie nicht möglich, nicht zulässig oder nicht zumutbar ist. In der Realität dauert diese vorläufige Situation für viele Betroffene Jahre. Diese Menschen leben hier, arbeiten hier, ihre Kinder gehen hier zur Schule, sie bauen sich ein soziales Umfeld auf, und trotzdem bleibt ihr Aufenthaltsstatus provisorisch.
 Meine Motion verlangt deshalb eine pragmatische Lösung: Wer seit zehn Jahren vorläufig in der Schweiz aufgenommen ist, soll eine Aufenthaltsbewilligung erhalten. Ausnahmen bleiben selbstverständlich möglich, insbesondere bei schweren Straftaten oder wenn die Sicherheit der Schweiz gefährdet ist. Es geht nicht darum, nach kurzer Zeit automatisch ein dauerhaftes Aufenthaltsrecht zu gewähren. Es geht darum, nach zehn Jahren die rechtliche Situation an eine Realität anzupassen, die längst besteht.
-Der Bundesrat anerkennt das Problem selbst. Er weist darauf hin, dass die vorläufige Aufnahme in vielen Fällen länger dauert und dass deshalb verschiedene Massnahmen zur Verbesserung der Integration getroffen wurden. Genau hier liegt der Widerspruch. Wir investieren zu Recht in die Integration dieser Menschen. Wir wollen, dass sie eine Sprache lernen, arbeiten, eine Ausbildung absolvieren und wirtschaftlich selbstständig werden. Gleichzeitig halten wir sie über Jahre in einem Status, der ihnen sagt, eure Zukunft hier bleibt ungewiss. Das ist integrationspolitisch nicht sinnvoll.
+Der Bundesrat anerkennt das Problem selbst. Er weist darauf hin, dass die vorläufige Aufnahme in vielen Fällen länger dauert und dass deshalb verschiedene Massnahmen zur Verbesserung der Integration getroffen wurden. Genau hier liegt der Widerspruch. Wir investieren zu Recht in die Integration dieser Menschen. Wir wollen, dass sie eine Sprache lernen, arbeiten, eine Ausbildung absolvieren und wirtschaftlich selbstständig werden. Gleichzeitig halten wir sie über Jahre in einem Status, der ihnen sagt: Eure Zukunft hier bleibt ungewiss. Das ist integrationspolitisch nicht sinnvoll.
 Oggi, dopo cinque anni è possibile presentare una domanda per ottenere un permesso di dimora. Ma questa possibilità non risolve il problema di fondo. Con la mia mozione, pongo volutamente una soglia molto alta, una soglia di dieci anni. Dopo dieci anni, non possiamo più sostenere di essere di fronte ad una situazione temporanea. Continuare a chiamarla "ammissione provvisoria" non cambia la realtà dei fatti.
 Il Consiglio federale sostiene che il sistema attuale, attraverso la possibilità di ottenere un permesso in caso di buona integrazione, crei un incentivo a integrarsi. Ma l'integrazione non dovrebbe dipendere dal mantenere le persone il più a lungo possibile in uno stato di incertezza. È vero piuttosto il contrario. Chi ha una prospettiva può pianificare la propria vita, investire nella formazione, trovare una maggiore stabilità professionale e assumersi delle responsabilità anche sul lungo termine. La sicurezza giuridica facilita l'integrazione, non la ostacola.
 Dobbiamo porci una domanda concreta. Che cosa otteniamo mantenendo lo statu quo? Se dopo dieci anni una persona non può ancora essere allontanata dalla Svizzera, non sparirà semplicemente perché continuiamo a definire provvisorio il suo statuto e rimarrà qui, ma con maggiori ostacoli alla propria integrazione sociale e professionale. Un provvisorio non può durare per sempre ed è con queste motivazioni che vi invito ad accogliere la mia mozione.
@@ -541,16 +545,16 @@
   <si>
     <t xml:space="preserve">Der Bundesrat lehnt die neun ausserordentlich traktandierten Motionen ab. Seiner Ansicht nach ist bei diesen weder die Ausserordentlichkeit noch die Dringlichkeit gegeben.
 Die Ausgangslage im Bereich Asyl präsentiert sich wie folgt: Die Asylgesuche gehen weiter zurück. In diesem Jahr verzeichnen wir fast 20 Prozent weniger Gesuche als im Vorjahr. Das SEM hat seine Prognose für 2026 um 3000 Asylgesuche gesenkt. Sie sinken somit im dritten Jahr in Folge, und wenn die tieferen Prognosen zutreffen, liegen wir Ende Jahr 27 Prozent tiefer als 2023.
-Auch die Pendenzen konnten stark reduziert werden. Als ich mein Amt antrat, hatten wir fast 10 000 Pendenzen; aktuell sind wir bei 2500 und wollen bis Ende Jahr alle abgebaut haben, obwohl das SEM wegen des Entlastungsprogrammes 150 Stellen streichen musste. Weniger Asylgesuche und Pendenzen entlasten das System; die Kantone und Gemeinden beginnen dies zu spüren.
+Auch die Pendenzen konnten stark reduziert werden. Als ich mein Amt antrat, hatten wir fast 10[NB]000 Pendenzen; aktuell sind wir bei 2500 und wollen bis Ende Jahr alle abgebaut haben, obwohl das SEM wegen des Entlastungsprogrammes 150 Stellen streichen musste. Weniger Asylgesuche und Pendenzen entlasten das System; die Kantone und Gemeinden beginnen, dies zu spüren.
 Die Zahl der Aufgriffe von irregulär Eingereisten ist gegenüber dem Vorjahr um 50 Prozent zurückgegangen. Verschiedene Massnahmen, die wir ergriffen haben, zeigen Wirkung. Für Asylsuchende aus nordafrikanischen Ländern haben wir die Verfahren stark beschleunigt, was ebenfalls das ganze System entlastet und die Schweiz als Zielland weniger attraktiv macht. Dank der neuen Einzelfallbehandlung an den runden Tischen aller Asylregionen sowie der neu eingesetzten Taskforce konnten mehr straffällige Asylsuchende der Strafverfolgung zugeführt werden. Die Zahl der Sicherheitsvorfälle in den Bundesasylzentren hat sich innerhalb von zwei Jahren mehr als halbiert.
-Wir führen etwa doppelt so viele abgewiesene Asylsuchende zurück wie alle anderen vergleichbaren europäischen Länder. Dabei stützen wir uns auf mehr als sechzig Abkommen mit Herkunftsstaaten. Ende Mai haben wir sogar ein Abkommen mit Marokko abgeschlossen; damit konnten wir auch die Rückführungen in dieses Land verbessern. Das schaffen viele andere Länder nicht. Doch nicht nur bei der Rückkehr sind wir in Europa Vorreiter. Mehr als fünfzig Prozent der Flüchtlinge und vorläufig Aufgenommenen haben bei uns nach fünf Jahren einen Job, was dank Arbeit durch Ausbildung möglich ist. Dies setzen wir zusammen mit den Kantonen erfolgreich um, wie auch die OECD anerkennt. So viel zur Ausgangslage.
-Nun komme ich zu den einzelnen Vorstössen. Ich beginne mit der Motion 26.3615 der SVP-Fraktion: Es geht hier um einen Vorstoss, den ich im Auftrag des abwesenden Bundespräsidenten vertreten muss; sie ist seinem Departement zugeordnet. Es geht um die Frage, welches Land die Arbeitslosengelder von Grenzgängerinnen und Grenzgängern bezahlt, die ihren Job verloren haben. Diese Motion will diese Frage beantworten, bevor sie sich überhaupt stellt, bevor wir überhaupt die Ausgangslage kennen. Es ist schlicht und einfach zu früh, hier schon Entscheide zu fällen. Deshalb lehnt der Bundesrat diese Motion ab. Die Änderung der EU-Verordnung 883/2004 sieht vor, dass künftig der letzte Beschäftigungsstaat für die Ausrichtung der Arbeitslosenentschädigung von Grenzgängerinnen und Grenzgängern zuständig sein soll. Aktuell ist die Situation umgekehrt geregelt, in Kombination mit einem Rückerstattungssystem zwischen Beschäftigungs- und Wohnsitzstaat. 
+Wir führen etwa doppelt so viele abgewiesene Asylsuchende zurück wie alle anderen vergleichbaren europäischen Länder. Dabei stützen wir uns auf mehr als sechzig Abkommen mit Herkunftsstaaten. Ende Mai haben wir sogar ein Abkommen mit Marokko abgeschlossen; damit konnten wir auch die Rückführungen in dieses Land verbessern. Das schaffen viele andere Länder nicht. Doch nicht nur bei der Rückkehr sind wir in Europa Vorreiter. Mehr als 50 Prozent der Flüchtlinge und vorläufig Aufgenommenen haben bei uns nach fünf Jahren einen Job, was dank Arbeit durch Ausbildung möglich ist. Dies setzen wir zusammen mit den Kantonen erfolgreich um, wie auch die OECD anerkennt. So viel zur Ausgangslage.
+Nun komme ich zu den einzelnen Vorstössen. Ich beginne mit der Motion 26.3615 der SVP-Fraktion: Es geht hier um einen Vorstoss, den ich im Auftrag des abwesenden Bundespräsidenten vertreten muss; die Motion ist seinem Departement zugeordnet. Es geht um die Frage, welches Land die Arbeitslosengelder von Grenzgängerinnen und Grenzgängern bezahlt, die ihren Job verloren haben. Diese Motion will diese Frage beantworten, bevor sie sich überhaupt stellt, bevor wir überhaupt die Ausgangslage kennen. Es ist schlicht und einfach zu früh, hier schon Entscheide zu fällen. Deshalb lehnt der Bundesrat diese Motion ab. Die Änderung der EU-Verordnung 883/2004 sieht vor, dass künftig der letzte Beschäftigungsstaat für die Ausrichtung der Arbeitslosenentschädigung von Grenzgängerinnen und Grenzgängern zuständig sein soll. Aktuell ist die Situation umgekehrt geregelt, in Kombination mit einem Rückerstattungssystem zwischen Beschäftigungs- und Wohnsitzstaat. 
 Die Schweiz beteiligt sich seit dem Inkrafttreten des Freizügigkeitsabkommens an der EU-weiten Koordinierung der Systeme der sozialen Sicherheit. Dazu gehört auch die erwähnte EU-Verordnung. Heute profitieren davon nicht zuletzt Schweizerinnen und Schweizer, die in einem EU-Mitgliedstaat leben und arbeiten. Das vergessen Sie immer wieder. Es gibt Schweizer, die in der EU leben, und für diese gelten auch Regeln, von denen sie profitieren können. Wenn Sie eine Auslegeordnung des Systems machen, müssen Sie das berücksichtigen, bevor Sie hierzu Entscheide fällen. 
 Seit 2013 hat die Arbeitslosenversicherung mit den Leistungen der Grenzgängerinnen und Grenzgänger einen jährlichen Überschuss von durchschnittlich 280 Millionen Schweizerfranken gemacht. Aktuell wissen wir nicht, wann die Revision in der EU in Kraft treten wird. Wie frühere Anpassungen muss auch dieser EU-Beschluss das innerstaatliche Genehmigungsverfahren durchlaufen. Dann muss die EU die Verordnungsanpassung für eine nächste Sitzung des Gemischten Ausschusses anmelden. Dies ist bis jetzt noch nicht geschehen. Das liegt unter anderem daran, dass das Revisionsverfahren auf EU-Ebene noch nicht abgeschlossen ist. Es fehlen noch die formelle Verabschiedung durch den Rat der EU, die Unterzeichnung durch die Rats- und Parlamentspräsidien sowie die Veröffentlichung im Amtsblatt der EU. 
 Die Haltung des Bundesrates lässt sich also wie folgt zusammenfassen: Der Bundesrat lehnt einen verfrühten Positionsbezug ab. Es ist zu früh, um einen Entscheid über eine allfällige Übernahme oder Nichtübernahme der noch nicht abgeschlossenen Revision zu fällen. Der Bundesrat verfolgt die Entwicklungen aufmerksam und informiert die zuständigen parlamentarischen Kommissionen über den Stand der Arbeiten. Bisher sind die SGK-S und beide APK informiert worden. Der Bundesrat wird demnächst eine Aussprache über die Revision und die damit aufgeworfenen Fragen führen. Dabei wird er über alle möglichen Lösungen diskutieren und diese sorgfältig prüfen. Aus diesen Gründen beantragt Ihnen der Bundesrat, die Motion abzulehnen.
 Ich komme zur Motion 26.3617. Mit dem Entzug des Bürgerrechtes lässt sich kein Terrorakt verhindern. Dafür braucht es andere Massnahmen. Deshalb hat die Schweiz seit 2020 ihr Sicherheitsdispositiv deutlich verstärkt. Das Fedpol, der Nachrichtendienst und die kantonalen Strafverfolgungsbehörden greifen bei konkreten Hinweisen auf eine terroristische Gefahr präventiv ein; dazu haben sie neue Instrumente erhalten. Es stehen hier verschiedene Instrumente zur Verfügung, etwa Meldepflichten, Kontakt- und Ausreiseverbote, Ein- oder Ausgrenzungen sowie in bestimmten Fällen auch Hausarrest. Im Rahmen eines Strafverfahrens können weitere Massnahmen angeordnet werden. So wird eine beschuldigte Person in Untersuchungs- oder Sicherheitshaft genommen, wenn ein dringender Verdacht besteht, dass sie weitere schwere Straftaten begehen wird, oder wenn sie konkret damit gedroht hat, eine schwerwiegende Tat zu begehen.
 Kommen wir nun zum Entzug des Schweizer Bürgerrechtes - darum geht es ja in dieser Motion. Der Entzug des Bürgerrechtes dient nicht dazu, einer möglichen Gefahr im Voraus zu begegnen, er greift erst nach einer strafrechtlichen Verurteilung. Die Motion verlangt, dass ein Entzug des Bürgerrechtes auch bei Straftaten möglich sein soll, die keinen unmittelbaren Bezug zum Terrorismus haben. Er soll selbst dann in Betracht kommen, wenn keine strafrechtliche Verurteilung vorliegt. Das geht dem Bundesrat zu weit. Zu weit geht dem Bundesrat auch der in der Motion vorgesehene Automatismus. Die zuständigen Behörden müssen auch künftig prüfen können, ob ein Entzug des Bürgerrechtes im konkreten Einzelfall verhältnismässig ist. Der Entzug des Bürgerrechtes ist ein schwerwiegender Eingriff, und deshalb braucht es auch weiterhin eine sorgfältige Prüfung aller Umstände des Einzelfalles.
-Sie haben es bereits gehört, Bund und Kantone haben ihre Zusammenarbeit gegen Terrorismus in den letzten Jahren deutlich verstärkt. Die Behörden verfügen heute über wirksame Instrumente, um Gefahren frühzeitig zu erkennen und Straftaten zu verhindern. Die Motion würde dazu nichts beitragen, sie würde mit ihrem Automatismus aber das Prinzip der Verhältnismässigkeit verletzen - und das lehnt der Bundesrat ab. Der Bundesrat beantragt Ihnen, die Motion abzulehnen.
+Sie haben es bereits gehört, Bund und Kantone haben ihre Zusammenarbeit gegen Terrorismus in den letzten Jahren deutlich verstärkt. Die Behörden verfügen heute über wirksame Instrumente, um Gefahren frühzeitig zu erkennen und Straftaten zu verhindern. Die Motion würde dazu nichts beitragen, sie würde mit ihrem Automatismus aber das Prinzip der Verhältnismässigkeit verletzen, und das lehnt der Bundesrat ab. Der Bundesrat beantragt Ihnen, die Motion abzulehnen.
 Ich komme nun zur Motion 26.3131. Diese Motion verlangt, dass ausländische Straftäter ab einer Freiheitsstrafe von einem Jahr zwingend und ohne Ausnahme des Landes verwiesen werden. Das bedeutet konkret, in solchen Fällen soll weder die Härtefallklausel angewendet werden noch soll im Einzelfall geprüft werden, ob die Landesverweisung verhältnismässig ist. Der Bundesrat lehnt diese Forderung aus drei Gründen ab.
 Erstens möchte ich daran erinnern, dass das Parlament bei der Umsetzung der Ausschaffungs-Initiative bewusst eine Härtefallklausel geschaffen hat und dass die Durchsetzungs-Initiative, welche diese abschaffen wollte, von der Stimmbevölkerung deutlich abgelehnt wurde. Die Härtefallklausel stellt sicher, dass zentrale verfassungs- und völkerrechtliche Vorgaben eingehalten werden, und dazu gehören insbesondere das Verhältnismässigkeitsprinzip, der Schutz des Privat- und Familienlebens sowie das Non-Refoulement-Prinzip. Die Rechtsprechungen des Bundesgerichtes und des Europäischen Gerichtshofes für Menschenrechte verlangen zudem eine Prüfung des Einzelfalls. Eine zwingende Landesverweisung ab einem Jahr Freiheitsstrafe würde dies ausschliessen. Damit könnte das Gericht auch die konkreten Umstände des Einzelfalls nicht mehr berücksichtigen, und das wäre mit dem übergeordneten Recht nicht vereinbar.
 Zweitens bedeutet eine zwingende Landesverweisung noch nicht, dass diese auch tatsächlich vollzogen werden kann. Fehlende Reisedokumente oder die mangelnde Kooperation des Herkunftsstaates können den Vollzug weiterhin verhindern; daran ändert diese Motion nichts.
@@ -587,12 +591,12 @@
     <t xml:space="preserve">RL</t>
   </si>
   <si>
-    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Fragen beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; die Letzten, die sich beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Wir müssen zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Fragen beantworten möchte. Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; die Letzten, die sich beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Wir müssen zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in geordneten Bahnen vorangetrieben werden kann. Das Resultat in anderen Ländern, wo man das seit Jahrzehnten nicht macht, ist Zeichen genug. Dieses Resultat wollen wir in unserem Land nicht erzielen. Nehmen Sie das vielleicht einmal zur Kenntnis, wenn Sie so reagieren. 
-Es gibt in der Schweiz - um zur Motion 25.4067 der FDP-Fraktion zu kommen - 73 800 Personen mit Schutzstatus S aus der Ukraine. Das ist ein knapper Drittel aller Personen, die sich momentan in der Schweiz im Asylbereich aufhalten. Das ist eine Anzahl Personen in der Grössenordnung der Stadt St. Gallen. Hier müssen wir schon eine Strategie haben. Deshalb verlangt die FDP-Fraktion eine klare Exit-Strategie in Bezug auf den Schutzstatus S unter Berücksichtigung auch der europäischen Entwicklungen, welche zur Verlängerung desselben bis im März 2028 geführt haben. Es geht nicht, dass man den Schutzstatus S einfach pauschal in eine vorläufige Aufnahme überführt. Das würde bedeuten, dass diese Leute wahrscheinlich nie mehr zurückgehen. Es war damals unsere Bundesrätin Keller-Sutter, die im Namen des Bundesrates klar gesagt hat, beim Schutzstatus S handle es sich um einen "rückkehrorientierten" Status. Diesen rückkehrorientierten Status wollen wir beibehalten. Deshalb lehnen wir es eben entschieden ab, dass man die 73 800 aktiven Leute mit Schutzstatus S dann ohne Einzelfallprüfung in eine kollektive vorläufige Aufnahme überführt. Es muss individuell geprüft werden.
-Ja, zur individuellen Prüfung von über 70 000 Personen braucht es Ressourcen. Genau aus diesem Grund beantragen wir mit dieser Motion hier eine Exit-Strategie. Wir sind ehrlich gesagt etwas irritiert darüber, dass der Bundesrat diesen Vorstoss bekämpft. Die Schweiz soll ihre Hausaufgaben machen und Ressourcen für Abklärungen einsetzen, wie diese Personen geordnet und möglichst früh zurückgeschickt und dabei juristisch unterstützt werden können. Ein sauberes Asylverfahren dieser Art ist die Grundlage dafür, dass man die Leute zurückschicken kann, sobald der Krieg - hoffentlich - einmal zu Ende ist. Es gilt dann ebenfalls, zum Beispiel Personen in Ausbildung zu berücksichtigen und eine verhältnismässige Frist festzusetzen, bis wann sie das Land zu verlassen haben. Das sind harte Entscheidungen, ja, aber es sind nötige Entscheidungen. Wenn wir pauschal einfach über alles hinwegsehen, dann werden wieder neue Diskussionen in diesem Land entstehen. Wir wollen nicht wieder in das alte Fahrwasser einer Asylpolitik zurückkehren, bei welcher diese Dinge eben zu wenig Berücksichtigung gefunden haben. 
+    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Fragen beantworten möchte: Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; die Letzten, die sich beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Wir müssen zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vielleicht ein kurzes Vorwort auch an die Vertreterin der Grünen, Frau Gysin, die keine Fragen beantworten möchte: Es ist doch ein offensichtliches Problem, dass wir in der Schweizer Asylpolitik Herausforderungen haben. Wenn wir diese gemeinsam lösen wollen, ohne die Augen zu verschliessen, hilft das uns allen am meisten; die Letzten, die sich beschweren dürfen, wenn das Ganze aus dem Ruder läuft, sind Sie. Wir müssen zusammen griffige Massnahmen definieren, damit die Asylpolitik der Schweiz in geordneten Bahnen vorangetrieben werden kann. Das Resultat in anderen Ländern, wo man das seit Jahrzehnten nicht macht, ist Zeichen genug. Dieses Resultat wollen wir in unserem Land nicht erzielen. Nehmen Sie das vielleicht einmal zur Kenntnis, wenn Sie so reagieren. 
+Es gibt in der Schweiz - um zur Motion 25.4067 der FDP-Fraktion zu kommen - 73[NB]800 Personen mit Schutzstatus S aus der Ukraine. Das ist ein knapper Drittel aller Personen, die sich momentan in der Schweiz im Asylbereich aufhalten. Das ist eine Anzahl Personen in der Grössenordnung der Stadt St.[NB]Gallen. Hier müssen wir schon eine Strategie haben. Deshalb verlangt die FDP-Fraktion eine klare Exit-Strategie in Bezug auf den Schutzstatus S unter Berücksichtigung auch der europäischen Entwicklungen, welche zur Verlängerung desselben bis im März 2028 geführt haben. Es geht nicht, dass man den Schutzstatus S einfach pauschal in eine vorläufige Aufnahme überführt. Das würde bedeuten, dass diese Leute wahrscheinlich nie mehr zurückgehen. Es war damals unsere Bundesrätin Keller-Sutter, die im Namen des Bundesrates klar gesagt hat, beim Schutzstatus S handle es sich um einen "rückkehrorientierten" Status. Diesen rückkehrorientierten Status wollen wir beibehalten. Deshalb lehnen wir es eben entschieden ab, dass man die 73[NB]800 aktiven Leute mit Schutzstatus S dann ohne Einzelfallprüfung in eine kollektive vorläufige Aufnahme überführt. Es muss individuell geprüft werden.
+Ja, zur individuellen Prüfung von über 70[NB]000 Personen braucht es Ressourcen. Genau aus diesem Grund beantragen wir mit dieser Motion hier eine Exit-Strategie. Wir sind ehrlich gesagt etwas irritiert darüber, dass der Bundesrat diesen Vorstoss bekämpft. Die Schweiz soll ihre Hausaufgaben machen und Ressourcen für Abklärungen einsetzen, wie diese Personen geordnet und möglichst früh zurückgeschickt und dabei juristisch unterstützt werden können. Ein sauberes Asylverfahren dieser Art ist die Grundlage dafür, dass man die Leute zurückschicken kann, sobald der Krieg hoffentlich einmal zu Ende ist. Es gilt dann ebenfalls, zum Beispiel Personen in Ausbildung zu berücksichtigen und eine verhältnismässige Frist festzusetzen, bis wann sie das Land zu verlassen haben. Das sind harte Entscheidungen, ja, aber es sind nötige Entscheidungen. Wenn wir pauschal einfach über alles hinwegsehen, dann werden wieder neue Diskussionen in diesem Land entstehen. Wir wollen nicht wieder in das alte Fahrwasser einer Asylpolitik zurückkehren, bei welcher diese Dinge eben zu wenig Berücksichtigung gefunden haben. 
 Und ja, es muss dann halt im einen oder anderen Fall die Ablehnung eines Asylgesuches stattfinden. Wir haben über die Kommission auch politisch erwirkt, dass gewisse Regionen der Ukraine als sichere Zonen eingestuft werden. Es wurde hier drin auch schon in Abrede gestellt, es gibt aber sichere Bereiche in der Ukraine. Dort müssen andere Massstäbe gelten als in den aktiven Kriegsgebieten, denn sonst werden wir schlicht und ergreifend überschwemmt. Wenn Personen dann halt nicht freiwillig zurückgehen, muss man Druck aufsetzen, damit sie das Land verlassen. Wie gesagt, es ist ein rückkehrorientierter Status.
 Dazu benötigen wir auf Bundesebene, im Staatssekretariat, eine konkrete Personalplanung. Es braucht Personal, das ist für uns klar, und auch Bundesrat Jans müsste das grösste Interesse daran haben. Die Kantone und Gemeinden - da deckt sich meine Beobachtung mit derjenigen meines Vorvorredners aus der SVP-Fraktion - müssen in diesen Prozess integriert werden, sie können das nicht alles alleine ausbaden, während der Bund zuschaut. Also lieber vorher eine Exit-Strategie definieren, so, wie wir sie in der Motion verlangen, anstatt dann mit "Pflästerlipolitik" in diesem heiklen Bereich die falschen Entscheidungen zu fällen.
 Ich danke Ihnen für die Unterstützung dieser Motion.
@@ -645,7 +649,7 @@
   </si>
   <si>
     <t xml:space="preserve">Die Motion 26.3100 der FDP-Liberalen Fraktion will eine strengere Durchsetzung von Rücknahmen abgewiesener Asylbewerber, meist Wirtschaftsflüchtlingen. Sie will, dass neue Alternativinstrumente wie Sanktionen oder Drittstaatenlösungen gesucht werden. Wir beauftragen den Bundesrat, die notwendigen Gesetzesänderungen anzugehen und uns zu unterbreiten. Wir wollen, dass zielgerichtete Sanktionen gegenüber nicht kooperierenden Herkunftsstaaten auch gesetzlich ermöglicht werden und dass damit die rechtlichen Grundlagen für die Verhandlung und den Einsatz sicherer Drittstaatenlösungen geschaffen werden. 
-Europa sucht seit Jahren nach Instrumenten, um die irreguläre Migration zu reduzieren, Schleusernetze zu bekämpfen und die Asylverfahren zu beschleunigen. Das Europäische Parlament hat am 5. Februar 2026 neue Regeln verabschiedet, nach denen unter anderem eine EU-weite Liste sicherer Herkunftsstaaten geschaffen wird und es Mitgliedstaaten ermöglicht wird, Abkommen mit Drittstaaten abzuschliessen, in denen Asylanträge geprüft werden können. Das Modell der Rückführungszentren und die verstärkte Verknüpfung von Rücknahmekooperationen mit anderen politischen Hebeln wie Visa oder Entwicklungshilfe werden in mehreren europäischen Debatten bereits behandelt. 
+Europa sucht seit Jahren nach Instrumenten, um die irreguläre Migration zu reduzieren, Schleusernetze zu bekämpfen und die Asylverfahren zu beschleunigen. Das Europäische Parlament hat am 5.[NB]Februar 2026 neue Regeln verabschiedet, nach denen unter anderem eine EU-weite Liste sicherer Herkunftsstaaten geschaffen wird und es Mitgliedstaaten ermöglicht wird, Abkommen mit Drittstaaten abzuschliessen, in denen Asylanträge geprüft werden können. Das Modell der Rückführungszentren und die verstärkte Verknüpfung von Rücknahmekooperationen mit anderen politischen Hebeln wie Visa oder Entwicklungshilfe werden in mehreren europäischen Debatten bereits behandelt. 
 Die Schweiz registriert immer wieder Asylgesuche von Personen, die vor ihrer Einreise bereits längere Zeit in Drittstaaten lebten, in denen keine unmittelbare Gefährdung bestand. Nach geltendem Recht ist ein Nichteintreten möglich, wenn der Drittstaat als sicher gilt. In der Praxis scheitert eine Rückführung aber häufig an fehlenden Abkommen oder an der Weigerung der betreffenden Staaten, Personen wieder aufzunehmen. Diese Lücke schwächt die Glaubwürdigkeit des Asylsystems, das dort Schutz bieten soll, wo er effektiv erforderlich ist. Dies ist Gegenstand des Postulates Caroni 23.4490, welches den Bundesrat beauftragt, in einem Bericht eine Auslegeordnung zu Asylverfahren und zum Wegweisungsvollzug im Ausland, insbesondere in Drittstaaten, vorzulegen und die Vereinbarkeit mit schweizerischen Standards zu prüfen. 
 Der Bundesrat lehnt die Motion mit der Begründung ab, die Schweiz habe eine der höchsten Rückkehrraten in Europa. Diese Aussage blendet jedoch aus, dass vor allem die Wirtschaftsflüchtlinge aus Nordafrika einen zu grossen Platz in unserer Asylstatistik einnehmen. Nicht dies allein ist ein grosses Ärgernis, sondern die Tatsache, dass genau diese Personen in der Statistik der Straftaten mit einem sehr hohen Wert von über 80 Prozent negativ auffallen. Dies führt nicht nur zu einer hohen Gefährdung der Sicherheit unserer Bevölkerung, sondern auch zu einer schlechten Akzeptanz gegenüber nachweislich schutzberechtigten Flüchtlingen. Diese nicht ausgewiesenen abgewiesenen Flüchtlinge schaden damit der humanitären Grundhaltung unserer Bevölkerung. 
 Geschätzter Herr Bundesrat Jans, die Schweiz braucht neben verstärkten Rücknahmekooperationen handhabbare Instrumente, um die Staaten, die Rücknahmen systematisch verweigern oder behindern, konsequent umgehen zu können. Gezielt eingesetzte Visa-Restriktionen und Konditionalität sind verhältnismässige internationale Standardinstrumente, die die Rücknahmebereitschaft erhöhen können, ohne den Schutzberechtigten die Rechtsmittel oder den Zugang zu internationalem Schutz zu entziehen. Ergänzend ermöglichen es Rückführungszentren und Drittstaatenlösungen, Fälle abgewiesener Personen konsequent ausserhalb Europas zu bearbeiten oder diese Personen unterzubringen, sofern menschenrechtliche und verfahrensrechtliche Mindeststandards garantiert sind. 
@@ -868,7 +872,7 @@
   </si>
   <si>
     <t xml:space="preserve">Zuerst muss ich etwas klären: Sie entscheiden bei dieser Motion nicht darüber, ob der Wegweisungsvollzug weiter optimiert und effizienter gemacht wird oder ob es mehr Rückweisungen geben wird. Nein, das wollen alle. Sie entscheiden lediglich darüber, ob der Bund eine kantonale Kompetenz an sich ziehen soll - und das, bevor eine brauchbare Lagebeschreibung, ein offensichtlicher Handlungsbedarf oder die zusätzlichen Kosten bekannt wären.
-Die gesetzlichen Grundlagen sind klar: Die Kantone sind verpflichtet, Wegweisungen und Landesverweisungen zu vollziehen. Schon heute ist es gemäss Ausländer- und Integrationsgesetz möglich, dass ein anderer Kanton den Vollzug übernimmt. Gewisse Kantone machen davon Gebrauch. Die Kantone regeln die Entschädigung für diese sogenannte Amtshilfe. Gleichzeitig verfügen wir heute schon über ein Anreizsystem, um die Kantone zum Vollzug zu bewegen. Einerseits haben die Kantone ein finanzielles Eigeninteresse an einem effizienten Vollzug. Jede vollzogene Wegweisung oder Landesverweisung reduziert die Kosten, die sie wegen dem Aufenthalt der betroffenen Person tragen müssen. Andererseits kann der Bund finanzielle Sanktionen ergreifen, wenn die Kantone ihre Vollzugsaufgaben im Asylbereich nicht oder nur ungenügend erfüllen. In diesen Fällen ordnet das SEM einen Subventionsstopp an.
+Die gesetzlichen Grundlagen sind klar: Die Kantone sind verpflichtet, Wegweisungen und Landesverweisungen zu vollziehen. Schon heute ist es gemäss Ausländer- und Integrationsgesetz möglich, dass ein anderer Kanton den Vollzug übernimmt. Gewisse Kantone machen davon Gebrauch. Die Kantone regeln die Entschädigung für diese sogenannte Amtshilfe. Gleichzeitig verfügen wir heute schon über ein Anreizsystem, um die Kantone zum Vollzug zu bewegen. Einerseits haben die Kantone ein finanzielles Eigeninteresse an einem effizienten Vollzug. Jede vollzogene Wegweisung oder Landesverweisung reduziert die Kosten, die sie wegen des Aufenthalts der betroffenen Person tragen müssen. Andererseits kann der Bund finanzielle Sanktionen ergreifen, wenn die Kantone ihre Vollzugsaufgaben im Asylbereich nicht oder nur ungenügend erfüllen. In diesen Fällen ordnet das SEM einen Subventionsstopp an.
 Im Wegweisungsvollzug haben wir genügend Anreize, die eine einheitliche Umsetzung des Bundesrechts fördern. Der Bund soll den Kantonen für eine klar geregelte gesetzliche Pflicht keine zusätzlichen finanziellen Mittel oder Entschädigungen zahlen, die über die bestehenden Pauschalen hinausgehen. Das ist weder nachhaltig noch sachlich gerechtfertigt. Angesichts der angespannten Finanzlage des Bundes ist eine solche zusätzliche Finanzhilfe auch nicht angezeigt.
 Mit der geforderten flexiblen Zuständigkeitsregelung würde der Bund erheblich in die Souveränität der Kantone eingreifen. Zudem ist unklar, wie die geforderte Regelung in der Praxis funktionieren soll. Kantonale Polizeibehörden fahnden grundsätzlich nicht eigenmächtig und ohne Absprache im Hoheitsgebiet eines anderen Kantons nach Personen, um diese festzunehmen. Sie tun dies nur, wenn eine Person flüchtet oder bei Gefahr im Verzug. Ansonsten arbeiten die kantonalen Polizeibehörden im Rahmen der Amtshilfe zusammen. Das ist auch beim Vollzug der Wegweisungen bereits heute möglich.
 Der Bundesrat unterstützt zwar das Bestreben des Motionärs, den Wegweisungsvollzug weiter zu optimieren und effizienter zu machen. Diese Motion stellt aber keine Lösung dar. Konkrete Massnahmen werden derzeit im Rahmen der Umsetzung der Motion Salzmann 23.3082 ausgearbeitet. Der Bundesrat legt das gewünschte Konzept voraussichtlich bis Ende Jahr vor.
@@ -885,7 +889,7 @@
   <si>
     <t xml:space="preserve">Auch hier stehe ich bei der Abstimmung wahrscheinlich wieder alleine da. Der Bundesrat kann jedoch - dies ist eine wichtige Botschaft - das Kernanliegen der Motion der GPK-S gut nachvollziehen: Nur wenn geschäftsrelevante Unterlagen korrekt abgelegt und aufbewahrt werden, ist das Verwaltungshandeln nachvollziehbar. Transparenz über die Tätigkeit der Bundesverwaltung ist wichtig, um das Vertrauen in den Staat und die Akzeptanz staatlichen Handelns zu stärken.
 Nach Ansicht des Bundesrates ist die in der Motion vorgeschlagene Verlängerung des Zugriffes auf inaktive Mailaccounts des Bundes jedoch keine zweckmässige Lösung. Einerseits wäre der Nutzen einer längerfristigen Zugriffs- und Aufbewahrungsfrist nur sehr begrenzt, da alle geschäftsrelevanten Informationen ohnehin fortlaufend aus den Mailaccounts in das elektronische Geschäftsverwaltungssystem überführt und dort bearbeitet werden müssen. Die restlichen Informationen in den Mailaccounts werden als nicht geschäftsrelevant betrachtet; jede Verwaltungseinheit muss hierzu Organisationsvorschriften erlassen und deren Einhaltung regelmässig kontrollieren.
-Andererseits stehen datenschutzrechtliche, technische sowie finanzielle Gründe einer längeren Aufbewahrungsfrist entgegen. Der im Datenschutzgesetz verankerte Grundsatz der Verhältnismässigkeit verlangt, dass Personendaten nicht länger als unbedingt erforderlich aufbewahrt werden dürfen. Zudem erfordert eine längere Aufbewahrungsdauer zusätzliche Speicherkapazitäten und erhöht das Risiko von Überschneidungen bei der Datenspeicherung. Der damit verbundene Personalaufwand sowie die Kosten für den Speicherplatz würden beachtliche Finanzmittel erfordern. Kurz gesagt stehen Kosten und Nutzen eines längeren Zugriffes auf inaktive Mailaccounts des Bundes in keinem sinnvollen Verhältnis.
+Andererseits stehen datenschutzrechtliche, technische sowie finanzielle Gründe einer längeren Aufbewahrungsfrist entgegen. Der im Datenschutzgesetz verankerte Grundsatz der Verhältnismässigkeit verlangt, dass Personendaten nicht länger als unbedingt erforderlich aufbewahrt werden dürfen. Zudem erfordert eine längere Aufbewahrungsdauer zusätzliche Speicherkapazitäten und erhöht das Risiko von Überschneidungen bei der Datenspeicherung. Der damit verbundene Personalaufwand sowie die Kosten für den Speicherplatz würden beachtliche Finanzmittel erfordern. Kurz gesagt, stehen Kosten und Nutzen eines längeren Zugriffes auf inaktive Mailaccounts des Bundes in keinem sinnvollen Verhältnis.
 Ich erlaube mir hier noch eine Bemerkung anzufügen: In jeder Session verlasse ich die Sitzungen beider Räte mit zusätzlichen Kosten und Aufträgen - jedes Mal. Ich möchte dies hier festhalten. Mit dem Entlastungspaket verlangen Sie viel von uns; allein das SEM musste in den letzten zwei Jahren 150 Personen entlassen. Wir setzen dies um, da wir effizienter werden wollen. Dennoch werden uns jedes Mal zusätzliche Kosten aufgebürdet, was auch hier der Fall ist. Diese Beobachtung wollte ich anbringen und werde sie mir künftig angewöhnen.
 </t>
   </si>
@@ -904,7 +908,7 @@
 Nach Ansicht des Bundesrates sollte ein nationales Rahmengesetz Minimalstandards in sämtlichen Bereichen des Gewaltschutzes umfassen. Da die Kantone jedoch für zentrale Aufgaben, wie polizeiliche Schutzmassnahmen oder das Bedrohungsmanagement, zuständig sind, ist für die Umsetzung der Motion eine Verfassungsänderung nötig.
 Die Kantone haben in den letzten Jahren bei der Bekämpfung häuslicher Gewalt wichtige Arbeit geleistet; sie analysieren derzeit die kantonalen Rechtsgrundlagen und beabsichtigen, diese noch stärker zu harmonisieren. An diese Arbeiten wollen wir anknüpfen. Bei einer Annahme der Motion wird der Bundesrat die Kantone von Beginn an eng einbeziehen und gemeinsam mit ihnen prüfen, welche Kompetenzen beim Bund angesiedelt werden sollen und wofür eine Verfassungsänderung erforderlich ist.
 Am 3. Juli 2026 hat sich Ihre Kommission für Rechtsfragen mit der vorliegenden Motion befasst und sie angenommen. Dabei hat sie auch einem Antrag zugestimmt, der die Präzisierung fordert, dass der Bundesrat ein Rahmengesetz nicht nur zum Schutz vor häuslicher, sondern auch vor sexualisierter und geschlechtsbezogener Gewalt vorlegen soll. Eine solche Änderung kostet zwar Zeit, da das Geschäft nochmals in den Ständerat geht, entscheidend ist jedoch, dass diese Motion die nachfolgenden Arbeiten tatsächlich erleichtert.
-Daraus lässt sich schliessen, dass Sie für die Umsetzung ein umfassendes Gewaltverständnis anstreben. Die Änderung passt zur künftigen nationalen Strategie, wie bereits erwähnt, da sie genau diese drei Gewaltformen umfassen wird. Sie ist daher aus Sicht des Bundesrates zu begrüssen.
+Daraus lässt sich schliessen, dass Sie für die Umsetzung ein umfassendes Gewaltverständnis anstreben. Die Änderung passt, wie bereits erwähnt, zur künftigen nationalen Strategie, da sie genau diese drei Gewaltformen umfassen wird. Sie ist daher aus Sicht des Bundesrates zu begrüssen.
 Aus den eingangs genannten Gründen beantragt Ihnen der Bundesrat, die Motion anzunehmen.
 </t>
   </si>
@@ -935,14 +939,14 @@
   </si>
   <si>
     <t xml:space="preserve">Die Kantone engagieren sich beim Vollzug von Wegweisungsentscheiden des Bundes in unterschiedlichem Ausmass. In den am 13. August dieses Jahres erfolgten Diskussionen in der Staatspolitischen Kommission Ihres Rates zur vorliegenden Motion kam über diesen Umstand ein grosser Unmut zum Ausdruck. Trotzdem beantrage ich Ihnen im Namen der Mehrheit der Kommission, die Motion Müller Damian, welche die Förderung des Vollzugs von Wegweisungen durch alle Kantone zur einheitlichen Umsetzung des Bundesrechtes verlangt, abzulehnen. Der Ständerat hat die Motion am 10. März 2026 mit 31 zu 10 Stimmen angenommen.
-Unsere Kommission hat dieses Geschäft eingehend beraten. Der Bundesrat unterstützt das Ziel und das Anliegen der Motion vollumfänglich, nämlich dass der Wegweisungsvollzug von den Kantonen konsequent umgesetzt wird. Doch sieht er, wie die Mehrheit der Kommission, in der vorliegenden Motion keine geeigneten Mittel zur Zielerreichung.
+Unsere Kommission hat dieses Geschäft eingehend beraten. Der Bundesrat unterstützt das Ziel und das Anliegen der Motion vollumfänglich, wonach der Wegweisungsvollzug von den Kantonen konsequent umgesetzt werden soll. Doch sieht er, wie die Mehrheit der Kommission, in der vorliegenden Motion kein geeignetes Mittel zur Zielerreichung.
 Die Mehrheit der Kommission begründet die Ablehnung wie folgt: Erstens wird bereits an einer umfassenden Lösung gearbeitet. Im Rahmen der Umsetzung der Motion Salzmann 23.3082 erarbeitet der Bundesrat derzeit ein ausführliches Konzept zur Verbesserung des Wegweisungsvollzugs und zur Erhöhung der Zahl der Ausreisenden. Dieses Konzept basiert auf einer fundierten Analyse des gesamten Rückkehrbereichs und wird bald vorliegen. Es ist daher nicht sinnvoll, parallel dazu eine Motion zu verabschieden, die grundlegend in die Mechanik der Rückkehrprozesse eingreift, bevor die Kommission diese Berichte und Empfehlungen zur Kenntnis nehmen und diskutieren kann.
 Zweitens, und das ist der Hauptpunkt, stösst der Ansatz der Motion aus föderalistischer Sicht auf grosse Vorbehalte. Die Motion sieht finanzielle Anreize dafür vor, dass Kantone den Vollzug in anderen Kantonen übernehmen. Der Wegweisungsvollzug ist jedoch eine gesetzliche Pflicht der Kantone. Es wäre dem Wesen des Föderalismus fremd, die Kantone finanziell dafür zu belohnen, dass sie eine ihrer Kernpflichten erfüllen. Das wäre das Eingeständnis, dass Kantone ihre Pflichten nicht mehr selber wahrnehmen müssen und der Bund dann die Ersatzvornahme durch andere Kantone finanziell berappen muss. Mit Verlaub, das wäre föderalismuspolitisch gesehen eine Bankrotterklärung.
-Zudem ist die praktische Umsetzung auch kaum vorstellbar. Unsere Mehrheit in der Kommission kann sich schlicht nicht vorstellen, dass Kantone ihre Polizeikräfte aufgrund finanzieller Anreize zum Beispiel in andere Sprachregionen entsenden würden. Der Kanton Zug mit einer 100-Prozent-Quote beim Vollzug der Wegweisungsentscheidungen sucht Wege, sein Zuviel an Geld an die Einwohnerinnen und Einwohner zu bringen, aber ganz bestimmt sucht er keine neuen Einnahmequellen durch den Einsatz seiner Polizei beispielsweise in der Westschweiz. 
+Zudem ist eine praktische Umsetzung kaum vorstellbar. Die Mehrheit der Kommission kann sich schlicht nicht vorstellen, dass Kantone ihre Polizeikräfte aufgrund finanzieller Anreize zum Beispiel in andere Sprachregionen entsenden würden. Der Kanton Zug mit einer 100-Prozent-Quote beim Vollzug der Wegweisungsentscheidungen sucht Wege, sein Zuviel an Geld an die Einwohnerinnen und Einwohner zu bringen, aber ganz bestimmt sucht er keine neuen Einnahmen durch den Einsatz seiner Polizei beispielsweise in der Westschweiz. 
 Drittens gibt es Vollzugshürden, welche finanzielle Anreize nicht zum Verschwinden bringen können. Fehlende Reisedokumente etwa oder die Weigerung von Drittstaaten, ihre Staatsangehörigen zurückzunehmen, sind Hürden, die nicht einfach so beseitigt werden können.
 Was bereits heute funktioniert, sind negative Anreize. In den letzten Jahren wurden säumigen Kantonen durchschnittlich rund 3 Millionen Franken an Bundessubventionen gekürzt. Auch dafür brauchen wir keine neue Motion. 
 Für die Minderheit der Kommission ist das vorgeschlagene System ein Schritt in die richtige Richtung. Es würde den Kantonen zusätzliche Anreize bieten, Wegweisungen und Landesverweisungen systematisch und einheitlich zu vollziehen. 
-Im Namen der Kommissionsmehrheit - bei 13 zu 12 Stimmen - ersuche ich Sie aber, die vorliegende Motion abzulehnen. 
+Im Namen der Kommissionsmehrheit - der Entscheid fiel mit 13 zu 12 Stimmen - ersuche ich Sie aber, die vorliegende Motion abzulehnen. 
 </t>
   </si>
   <si>
@@ -972,12 +976,13 @@
     <t xml:space="preserve">Pfister Gerhard</t>
   </si>
   <si>
-    <t xml:space="preserve">Diese Motion wurde am 10. März dieses Jahres im Ständerat angenommen, ohne dass ein anderslautender Antrag gestellt worden wäre. Der Bundesrat hat damals und wird hoffentlich auch heute die Annahme der Motion beantragen. Ihre Kommission hat sie an der Sitzung vom 13. und 14. August beraten. Die Motion will, dass die Ablehnung häuslicher Gewalt und der Schutz von Frauen und Kindern als verbindliche Integrationskriterien ab dem ersten Aufenthaltstag festgelegt werden. Zudem sind ab der Ankunft in </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diese Motion wurde am 10. März dieses Jahres im Ständerat angenommen, ohne dass ein anderslautender Antrag gestellt worden wäre. Der Bundesrat hat damals und wird hoffentlich auch heute die Annahme der Motion beantragen. Ihre Kommission hat sie an der Sitzung vom 13. und 14. August beraten. Die Motion will, dass die Ablehnung häuslicher Gewalt und der Schutz von Frauen und Kindern als verbindliche Integrationskriterien ab dem ersten Aufenthaltstag festgelegt werden. Zudem sind ab der Ankunft in der Schweiz obligatorische Schulungen gegen häusliche Gewalt, zu den Rechten der Betroffenen sowie zu den straf-, zivil- und ausländerrechtlichen Konsequenzen von Gewalt durchzuführen und verbindlich in allen Integrationsprogrammen auf Bundes-, Kantons- und Gemeindeebene zu verankern. Schliesslich soll der Bundesrat aufzeigen, welche Rechtsfolgen bei Verstössen gegen diese Integrationspflichten gelten und ob gesetzliche Anpassungen im Hinblick auf Asylstatus, Aufenthaltsrecht, Einbürgerung und Ausweisung erforderlich sind.
-Die Mehrheit Ihrer Kommission beantragt Ihnen die Annahme der Motion aus folgenden Gründen:
-Erstens ist die Bekämpfung häuslicher Gewalt eine Priorität, die eine klare rechtliche Verankerung erfordert. Zwar gehören die Beachtung der öffentlichen Sicherheit sowie die Respektierung der Werte der Bundesverfassung bereits heute zu den Integrationskriterien. Indem wir die Ablehnung häuslicher Gewalt jedoch als spezifisches Kriterium explizit auf Gesetzesstufe festhalten, verleihen wir diesem Anliegen das notwendige Gewicht und schaffen eine eindeutige Grundlage für die Praxis.
+    <t xml:space="preserve">Diese Motion wurde am 10. März dieses Jahres im Ständerat angenommen, ohne dass ein anderslautender Antrag gestellt worden wäre. Der Bundesrat hatte damals und wird hoffentlich auch heute die Annahme der Motion beantragen. Ihre Kommission hat sie an der Sitzung vom 13. und 14. August beraten.
+Die Motion will, dass die Ablehnung häuslicher Gewalt und der Schutz von Frauen und Kindern als verbindliche Integrationskriterien ab dem ersten Aufenthaltstag festgelegt werden. Zudem sind ab der Ankunft i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diese Motion wurde am 10. März dieses Jahres im Ständerat angenommen, ohne dass ein anderslautender Antrag gestellt worden wäre. Der Bundesrat hatte damals und wird hoffentlich auch heute die Annahme der Motion beantragen. Ihre Kommission hat sie an der Sitzung vom 13. und 14. August beraten.
+Die Motion will, dass die Ablehnung häuslicher Gewalt und der Schutz von Frauen und Kindern als verbindliche Integrationskriterien ab dem ersten Aufenthaltstag festgelegt werden. Zudem sind ab der Ankunft in der Schweiz obligatorische Schulungen gegen häusliche Gewalt, zu den Rechten der Betroffenen sowie zu den straf-, zivil- und ausländerrechtlichen Konsequenzen von Gewalt durchzuführen und verbindlich in allen Integrationsprogrammen auf Bundes-, Kantons- und Gemeindeebene zu verankern. Schliesslich soll der Bundesrat aufzeigen, welche Rechtsfolgen bei Verstössen gegen diese Integrationspflichten gelten und ob gesetzliche Anpassungen im Hinblick auf Asylstatus, Aufenthaltsrecht, Einbürgerung und Ausweisung erforderlich sind.
+Die Mehrheit Ihrer Kommission beantragt Ihnen die Annahme der Motion aus folgenden Gründen: Erstens ist die Bekämpfung häuslicher Gewalt eine Priorität, die eine klare rechtliche Verankerung erfordert. Zwar gehören die Beachtung der öffentlichen Sicherheit sowie die Respektierung der Werte der Bundesverfassung bereits heute zu den Integrationskriterien. Indem wir die Ablehnung häuslicher Gewalt jedoch als spezifisches Kriterium explizit auf Gesetzesstufe festhalten, verleihen wir diesem Anliegen das notwendige Gewicht und schaffen eine eindeutige Grundlage für die Praxis.
 Zweitens ist es zwar eine Selbstverständlichkeit, dass sich alle Personen, die in die Schweiz kommen, an unsere Rechtsordnung zu halten haben. Um dies aber sicherzustellen, müssen die geltenden Regeln und das hiesige Menschenbild von Beginn an unmissverständlich kommuniziert werden. Obligatorische Schulungen und Sensibilisierungsmassnahmen stellen sicher, dass jede Person über ihre Rechte und Pflichten sowie über die straf- und ausländerrechtlichen Konsequenzen von Gewalt informiert wird. 
 Drittens wird die Umsetzung dieser Massnahmen pragmatisch und ohne übermässigen bürokratischen Aufwand erfolgen können. Die Schulungen müssen keine komplexen Ausbildungsmodule sein. Sie können beispielsweise in Form von kurzen digitalen Modulen, Informationsflyern oder als integrierte Elemente in bestehenden Sprachkursen realisiert werden. Damit wird eine effektive Information gewährleistet, ohne die Kantone oder Gemeinden finanziell oder administrativ übermässig zu belasten. Aufgrund dieser Versicherung seitens des SEM lehnte die Kommission denn auch einen Antrag, auf die Verpflichtung zur Schulung zu verzichten, mit 14 zu 10 Stimmen ab. 
 Die Kommission beantragt Ihnen mit 18 zu 5 Stimmen bei 1 Enthaltung, die Motion anzunehmen.
@@ -1999,14 +2004,7 @@
   <si>
     <t xml:space="preserve">En introduction, il faut mentionner que, ces dernières années, les cantons ont régulièrement rappelé que les dispositions en vigueur relatives au financement des soins et de la santé des détenus ne sont pas toujours claires et peuvent être sujettes à d'importantes fluctuations financières. C'est pourquoi le Conseil fédéral, soutenu en consultation par une majorité des cantons et de la Conférence des directrices et directeurs des départements cantonaux de justice et police (CCDJP), a élaboré un projet visant à ce qu'à l'avenir tous les détenus disposent d'une assurance-maladie. En 2023, environ 2300 personnes détenues sur 6450, donc à peu près le tiers, n'étaient pas couvertes par l'assurance-maladie obligatoire, car elles n'avaient pas de domicile en Suisse et n'étaient donc pas soumises à l'obligation d'assurance. Comme les dispositions y relatives varient d'un canton à l'autre, il arrive que des personnes détenues sans assurance n'aient parfois qu'un accès limité aux soins médicaux, ce qui contrevient au principe d'égalité de traitement prévu dans la Constitution.
 Lors de la consultation, il a été tenu compte notamment de la préoccupation d'une majorité des participants qui s'étaient exprimés en faveur du transfert de la compétence au canton qui ordonne la détention, tant en matière de restriction du choix de l'assureur et du prestataire de soins que de respect et de contrôle de l'obligation d'assurance. Auparavant, l'avant-projet attribuait cette compétence au canton où se trouve l'établissement pénitentiaire, ce qui n'était pas considéré comme une bonne solution en cas de transfert intercantonal. Cependant, malgré les restrictions apportées, le Conseil des États a refusé d'entrer en matière sur le projet, par 33 voix contre 9. Il a émis les réserves suivantes. Les personnes concernées n'ont aucun lien avec la Suisse, puisqu'elles ne sont pas domiciliées en Suisse, et la révision proposée est en contradiction avec la systématique de la LAMal. De plus, une telle obligation risque d'entraîner une charge administrative disproportionnée si tous les détenus devaient s'affilier à une caisse d'assurance-maladie.
-Réunie en séance le 2 juillet, notre commission se rallie à la décision du Conseil des États, en insistant sur six éléments. Premièrement, on ne doit pas déroger au principe, prévu par la LAMal, selon lequel l'obligation de s'assurer ne s'applique en règle générale qu'aux personnes domiciliées en Suisse et y percevant un revenu ; cela constituerait même un avantage pour les personnes incarcérées par rapport à d'autres personnes qui se trouvent temporairement en Suisse sans avoir commis d'infraction.
-Deuxièmement, un transfert des coûts des cantons vers l'assurance obligatoire des soins n'est pas judicieux. Aujourd'hui, ce sont les cantons qui prennent en charge ces coûts ; demain, ils seraient financés par les primes. On peut craindre une charge supplémentaire pour l'ensemble des assurés, notamment en raison des frais administratifs et des coûts des prestations supérieurs à la moyenne pendant le séjour, généralement de courte durée, de ces personnes en Suisse. Dit très clairement : les coûts des traitements médicaux de ces personnes qui ne paient pas d'impôts et n'ont versé aucune prime ni aucune autre cotisation sociale dans notre pays doivent rester à la charge des cantons et être financés par les impôts.
-Troisièmement, un bon nombre des personnes concernées devraient de toute façon bénéficier de réductions de primes. En effet, la plupart des détenus sans domicile en Suisse n'ayant pas d'argent, ce sont de toute façon les communes ou le canton qui prendraient en charge les primes.
-Quatrièmement, les primes impayées ne seraient plus recouvrables pour les assureurs en raison de l'expulsion qui souvent suit la détention.
-Cinquièmement, la prise en charge médicale de ces personnes devra de toute manière être garantie, conformément à la Constitution, et cela indépendamment de l'obligation de s'assurer.
-Sixièmement, il ressort des documents que la mise en oeuvre ne serait pas aisée. En réalité, il s'agit de proposer une solution d'assurance pour les cantons, au motif d'une meilleure clarté et prévisibilité. C'est ce que souhaitent la CCDJP et la Conférence des chefs des services pénitentiaires cantonaux dans leur prise de position adressée à notre commission. Or, aujourd'hui, les cantons ont déjà une marge de manoeuvre et elle est suffisante, en matière de paiement et de restriction concernant les médecins qui traitent les personnes détenues sans domicile en Suisse.
-Vu ce qui précède, notre commission vous propose, par 16 voix contre 0 et 9 abstentions, de ne pas entrer en matière sur le projet.
-</t>
+Réunie en séance le 2 juillet, notre commission se rallie à la décision du Conseil des États, en insistant sur six éléments. Premièrement, on ne doit pas déroger au principe, prévu par la LAMal, selon lequel l'obligation de s'assurer ne s'applique en règle générale qu'aux personnes domiciliées en Suisse et y percevant un revenu ; cela constituerait même un avantage pour les personnes incarcérées par rapport à d'autres personnes qui se trouvent temporairement en Suisse sans avoir commis d'infraction.Deuxièmement, un transfert des coûts des cantons vers l'assurance obligatoire des soins n'est pas judicieux. Aujourd'hui, ce sont les cantons qui prennent en charge ces coûts ; demain, ils seraient financés par les primes. On peut craindre une charge supplémentaire pour l'ensemble des assurés, notamment en raison des frais administratifs et des coûts des prestations supérieurs à la moyenne pendant le séjour, généralement de courte durée, de ces personnes en Suisse. Dit très clairement : les coûts des traitements médicaux de ces personnes qui ne paient pas d'impôts et n'ont versé aucune prime ni aucune autre cotisation sociale dans notre pays doivent rester à la charge des cantons et être financés par les impôts.Troisièmement, un bon nombre des personnes concernées devraient de toute façon bénéficier de réductions de primes. En effet, la plupart des détenus sans domicile en Suisse n'ayant pas d'argent, ce sont de toute façon les communes ou le canton qui prendraient en charge les primes.Quatrièmement, les primes impayées ne seraient plus recouvrables pour les assureurs en raison de l'expulsion qui souvent suit la détention.Cinquièmement, la prise en charge médicale de ces personnes devra de toute manière être garantie, conformément à la Constitution, et cela indépendamment de l'obligation de s'assurer.Sixièmement, il ressort des documents que la mise en oeuvre ne serait pas aisée. En réalité, il s'agit de proposer une solution d'assurance pour les cantons, au motif d'une meilleure clarté et prévisibilité. C'est ce que souhaitent la CCDJP et la Conférence des chefs des services pénitentiaires cantonaux dans leur prise de position adressée à notre commission. Or, aujourd'hui, les cantons ont déjà une marge de manoeuvre - et elle est suffisante - en matière de paiement et de restriction concernant les médecins qui traitent les personnes détenues sans domicile en Suisse.Vu ce qui précède, notre commission vous propose, par 16 voix contre 0 et 9 abstentions, de ne pas entrer en matière sur le projet.</t>
   </si>
   <si>
     <t xml:space="preserve">421935</t>
@@ -3349,10 +3347,10 @@
     <t xml:space="preserve">Ein Land, in dem vier Sprachen gesprochen werden, in dem ganz viele verschiedene Kulturen und Minderheiten friedlich zusammenleben, in dem ein Klima der Toleranz, der Freiheit und der Demokratie herrscht, ist ein wundervolles Land. Unsere direkte Demokratie und der föderalistische Staatsaufbau sind der Boden für Wohlstand und Wohlergehen in der Schweiz. Das hängt damit zusammen, dass ganz viele Menschen daran mitarbeiten. Darum gibt es in unserem Land auch nicht einfach nur Rechte, sondern auch </t>
   </si>
   <si>
-    <t xml:space="preserve">Ein Land, in dem vier Sprachen gesprochen werden, in dem ganz viele verschiedene Kulturen und Minderheiten friedlich zusammenleben, in dem ein Klima der Toleranz, der Freiheit und der Demokratie herrscht, ist ein wundervolles Land. Unsere direkte Demokratie und der föderalistische Staatsaufbau sind der Boden für Wohlstand und Wohlergehen in der Schweiz. Das hängt damit zusammen, dass ganz viele Menschen daran mitarbeiten. Darum gibt es in unserem Land auch nicht einfach nur Rechte, sondern auch Pflichten, wie es der Initiant formuliert hat. Diese Verbindung zwischen Bürgerrechten und Bürgerpflichten ist für das Funktionieren unseres Landes ganz elementar. 
-Wir müssen aufpassen, da bin ich genau gleicher Meinung wie der Initiant, dass wir hier nicht zunehmend mit Rosinenpickerei konfrontiert sind. Die Schweiz ermöglicht allen - ob Schweizer Bürger oder nicht - Rechte in einem Umfang, den man in keinem anderen Land kennt. Wer das Stimm- und Wahlrecht in der Schweiz besitzt, kann während eines Jahres häufiger abstimmen, als das die meisten anderen Menschen auf dieser Welt in ihrem ganzen Leben tun können. Die Schweiz ermöglicht In- und Ausländern ein Maximum an Freiheit. In der Schweiz dürfen Ausländer demonstrieren, sie dürfen ihre politische Meinung äussern, sie dürfen Petitionen unterschreiben. In vielen anderen Ländern auf der Welt würden sie dafür verhaftet, kämen ins Gefängnis oder hätten Nachteile zu befürchten. 
+    <t xml:space="preserve">Ein Land, in dem vier Sprachen gesprochen werden, in dem ganz viele verschiedene Kulturen und Minderheiten friedlich zusammenleben, in dem ein Klima der Toleranz, der Freiheit und der Demokratie herrscht, ist ein wundervolles Land. Unsere direkte Demokratie und der föderalistische Staatsaufbau sind der Boden für Wohlstand und Wohlergehen in der Schweiz. Das hängt damit zusammen, dass ganz viele Menschen daran mitarbeiten. Darum gibt es in unserem Land auch nicht einfach nur Rechte, sondern auch Pflichten - so, wie es der Initiant formuliert hat. Diese Verbindung zwischen Bürgerrechten und Bürgerpflichten ist für das Funktionieren unseres Landes ganz elementar. 
+Wir müssen aufpassen, da bin ich gleicher Meinung wie der Initiant, dass wir hier nicht zunehmend mit Rosinenpickerei konfrontiert sind. Die Schweiz ermöglicht allen - ob Schweizer Bürger oder nicht - Rechte in einem Umfang, den man in keinem anderen Land kennt. Wer das Stimm- und Wahlrecht in der Schweiz besitzt, kann während eines Jahres häufiger abstimmen, als das die meisten anderen Menschen auf dieser Welt in ihrem ganzen Leben tun können. Die Schweiz ermöglicht In- und Ausländern ein Maximum an Freiheit. In der Schweiz dürfen Ausländer demonstrieren, sie dürfen ihre politische Meinung äussern, sie dürfen Petitionen unterschreiben. In vielen anderen Ländern auf der Welt würden sie dafür verhaftet, kämen ins Gefängnis oder hätten Nachteile zu befürchten. 
 Wir dürfen stolz darauf sein, dass die Mündigkeit und die Freiheit jedes Einzelnen bei uns einen grossen Stellenwert haben. Wir nehmen jeden Einzelnen ernst, ob er Schweizer Bürger ist oder nicht. Bei uns kommt es auch nicht darauf an, welche Sprache er spricht, welche politische Ausrichtung, welche sexuelle Orientierung, welche Religion er hat und welche kulturellen Bräuche er pflegt. Wichtig ist natürlich die Einhaltung gewisser Grundregeln. Wir stellen fest, da möchte ich meinen Vorredner unterstützen, dass hier ein gewisser Handlungsbedarf besteht. 
-Wir müssen wieder viel genauer darauf schauen, wie und wo der Schweizer Pass vergeben wird - und ob die Integration auch tatsächlich stattgefunden hat. Die Integration ist keine Staatsaufgabe, wie man bisweilen und auch in diesem Saal hört. Der Staat hat keine Pflicht, hier Mittel bereitzustellen, um diese Integration zu fördern. Nein, es ist vielmehr eine Obliegenheit derjenigen, die zu uns kommen, die hier leben und partizipieren möchten. Darum ist es ganz wichtig, darauf zu schauen, dass diese Integration stattgefunden hat und die Einbürgerung allenfalls nach erfolgreich abgeschlossener Integration stattfindet. Tatsächlich beobachten wir immer wieder Fälle, in denen Leute verschiedene Pässe haben, und im entscheidenden Moment der Schweizer Pass dann eben nicht der wichtigste ist, sondern man sich vielleicht seinem ursprünglichen Heimatland doch noch mehr verpflichtet fühlt - im kritischeren Fall sogar einer anderen Rechtsordnung als der hier geltenden. 
+Wir müssen wieder viel genauer darauf schauen, wie und wo der Schweizer Pass vergeben wird - und ob die Integration auch tatsächlich stattgefunden hat. Die Integration ist keine Staatsaufgabe, wie man es bisweilen auch in diesem Saal hört. Der Staat hat keine Pflicht, Mittel bereitzustellen, um die Integration zu fördern. Nein, es ist vielmehr eine Obliegenheit derjenigen, die zu uns kommen, die hier leben und partizipieren möchten. Darum ist es ganz wichtig, darauf zu schauen, dass diese Integration stattgefunden hat und die Einbürgerung allenfalls nach erfolgreich abgeschlossener Integration stattfindet. Tatsächlich beobachten wir immer wieder Fälle, in denen Leute verschiedene Pässe haben, und im entscheidenden Moment der Schweizer Pass dann eben nicht der wichtigste ist, sondern man sich vielleicht seinem ursprünglichen Heimatland doch noch mehr verpflichtet fühlt - im kritischeren Fall sogar einer anderen Rechtsordnung als der hier geltenden. 
 Auf diese Punkte sollten wir schauen, und aus diesem Grund bitte ich Sie auch, diese Initiative zu unterstützen und ihr Folge zu geben. Es kann nicht sein, dass sich jemand in der Schweiz einbürgern lässt, weil es einfach noch nett ist, auch noch den Schweizer Pass zu haben, und man hier von gewissen Leistungen profitieren kann. 
 Um dies zu vermeiden, auch um Loyalitätskonflikte zu vermeiden, und um sicherzustellen, dass die Leute, die hier leben und den Schweizer Pass haben, eben nicht nur die Rechte, sondern vor allem auch die Pflichten kennen, bitten wir Sie, dieser parlamentarischen Initiative Folge zu geben. Es geht ja um Folgegeben, um die Frage, ob Handlungsbedarf besteht. Wir meinen Ja. Geben Sie Folge, damit wir uns in einem zweiten Schritt etwas genauer mit dieser Thematik auseinandersetzen können.
 </t>
@@ -3462,7 +3460,7 @@
 Drittens stärken wir die Sicherheit. Bund und Kantone führen die gemeinsame "Taskforce Intensivtäter" aus dem Asyl- und Ausländerbereich weiter. Wir schrauben an den ausländerrechtlichen Zwangsmassnahmen. Das Ziel ist klar: Verbesserungen beim Wegweisungsvollzug und konsequentes Handeln der Behörden gegenüber diesen Intensivtätern. 
 Viertens - da kommt gleich der nächste Punkt - wollen wir mehr ausreisepflichtige Personen zurückführen. Die Schweiz verfügt über ein gut funktionierendes Migrationssystem mit Herkunftsstaaten. Wir haben mit 60 Staaten Partnerschaften etabliert, und wir bauen das weiter aus. In den kommenden Jahren werden wir uns in diesem Saal auch mit der Übernahme der EU-Rückkehrverordnung befassen. Diese Schengen-Weiterentwicklung ergänzt unsere Arbeit im Rahmen der Asylstrategie.
 Vielleicht noch schnell ein Wort zu Dänemark; es ist schon wichtig, dass ich das hier auch sage. Wir schauen genau, was die Unterschiede zwischen der Schweiz und Dänemark sind. Aber einen Hinweis darf ich Ihnen jetzt schon machen. Dänemark hatte schon immer viel tiefere Asylzahlen als die Schweiz. Sie sind in Dänemark hochgeschnellt, wie bei uns, und erreichten 2023 die Spitze, um dann wieder zurückzugehen, auch wie bei uns. Der entscheidende Unterschied zwischen Schweiz und Dänemark ist die Tatsache, dass Dänemark hinter den Migrationsströmen der Asylsuchenden liegt. Und die Schweiz liegt mittendrin. Das ist ein ganz entscheidender Unterschied. Nichtsdestotrotz schauen wir aufgrund einer Motion, die angenommen wurde, die Unterschiede ganz genau an und werden Ihnen auch sagen, wo es allenfalls Anpassungsmöglichkeiten gibt. 
-Nun zu den Kosten: Weniger offensichtlich begründete Gesuche, weniger Pendenzen und schnellere Verfahren entlasten die Strukturen für alle. Deshalb verfolgen wir diese Strategie. Nur bei einem Punkt besteht eben ein Unterschied zwischen der laufenden Asylstrategie und dieser Motion. Die Asylstrategie enthält kein Ziel zur Einschränkung des Familiennachzuges. Auch Ihre Kommission hat diesen Punkt der Motion nicht unterstützt. Das Anliegen haben wir in der aktuellen Legislatur mehrmals diskutiert. Sowohl Bundesrat als auch Parlament haben es abgelehnt, den Familiennachzug weiter einzuschränken. 
+Nun zu den Kosten: Weniger offensichtlich begründete Gesuche, weniger Pendenzen und schnellere Verfahren entlasten die Strukturen für alle. Deshalb verfolgen wir diese Strategie. Nur bei einem Punkt besteht eben ein Unterschied zwischen der laufenden Asylstrategie und dieser Motion. Die Asylstrategie enthält kein Ziel zur Einschränkung des Familiennachzuges. Auch Ihre Kommission hat diese Ziffer der Motion nicht unterstützt. Das Anliegen haben wir in der aktuellen Legislatur mehrmals diskutiert. Sowohl Bundesrat als auch Parlament haben es abgelehnt, den Familiennachzug weiter einzuschränken. 
 Zur Umsetzung der Asylstrategie müssen wir einzelne Gesetzesbestimmungen anpassen. Wo gesetzgeberischer Handlungsbedarf besteht, schlägt Ihnen der Bundesrat noch dieses Jahr Änderungen am Asylgesetz und am Ausländer- und Integrationsgesetz vor. Die Vernehmlassung ist für Ende 2026 vorgesehen. Die vorliegende Motion verlangt eine neue, grundlegende Strategie. Eine breit abgestützte Strategie liegt aber bereits vor. Über das entsprechende Gesetzespaket werden wir im nächsten Jahr diskutieren. Eine zweite Strategie bringt uns deshalb weder schneller ans Ziel noch kann sie bessere Vorschläge machen. Der Bundesrat beantragt Ihnen deshalb, die Motion 25.4674 abzulehnen.
 Jetzt komme ich zum Postulat Ihrer Staatspolitischen Kommission. Das Postulat verlangt mehr Sicherheit und mehr Integration. Es verlangt zudem Anpassungen im Asyl- und Ausländerrecht. Der Bundesrat, wie ich dargelegt habe, teilt dieses Anliegen, denn es ist durch das politische Mandat der Asylstrategie thematisch abgedeckt. Das Postulat fordert keine neue Strategie; es ergänzt die laufenden Arbeiten. Wir können die Ideen des Parlamentes hier direkt in das Gesetzgebungspaket, an dem wir im Moment arbeiten, einfliessen lassen. Die kantonalen Konferenzen sowie der Schweizerische Gemeinde- und der Städteverband tragen das mit. Es ist eine Strategie der Bevölkerung für die Bevölkerung.
 Der Bundesrat beantragt Ihnen deshalb, das Postulat 26.4062 anzunehmen.
@@ -3497,7 +3495,7 @@
 2. Einführung eines neuen Zuständigkeitsverfahrens: Die Idee dieses in Europa neuen Verfahrens ist es, dass eine Person ohne Asylgründe gar nicht erst ins Asylsystem gelangt. Nach Schätzungen des SEM handelt es sich bei den Asylgesuchen bei rund 20 Prozent um offensichtlich unbegründete Gesuche. Das wäre eine potenziell sehr wesentliche Entlastungsmöglichkeit des Asylsystems.
 3. Angleichung des Schutzstatus S und der vorläufigen Aufnahme: Dies mit dem Ziel, einer Forderung insbesondere aus Kreisen der Wirtschaft und der Arbeitgeber nachzukommen. Einerseits hat der Begriff "vorläufige Aufnahme" eine integrationshemmende Wirkung, insbesondere im Arbeitsmarkt, und andererseits muss der Schutzstatus S im Frühjahr 2027 ohnehin für diejenigen Flüchtlinge aus der Ukraine, die als erste gekommen sind, angepasst werden. Ziel muss es sein, denjenigen, die in der Lage sind, sich im Arbeitsmarkt der Schweiz zu bewähren oder die bereits eine Stelle haben, eine verlässliche Perspektive in der Schweiz zu geben. Eine Nivellierung der beiden Status soll nicht möglich sein, weder nach oben noch nach unten.
 4. Integration: Das vierte Element dieses Postulates ist die Integration. Die Schweiz ist ein sehr integrationsstarkes Land. Das verdankt sie einerseits der hohen Integrationsbereitschaft der überwiegenden Mehrheit der Ausländerinnen und Ausländer in der Schweiz und andererseits auch der Bereitschaft der schweizerischen Gesellschaft zur Offenheit sowie der wirtschaftlichen Attraktivität. Dennoch gibt es in bestimmten Bereichen Verbesserungspotenzial, so sind ausländische Frauen deutlich weniger erwerbstätig als Männer. Ausserdem müssen Kinder mit sprachlichen Defiziten bessere Möglichkeiten haben, diese aufzuholen, um ihre Integration in unser Bildungssystem zu fördern. Ebenso muss die wirtschaftliche Selbstständigkeit von Ausländerinnen und Ausländern stärker gefördert werden.
-In diesem Sinne beantragt Ihnen die Kommissionsmehrheit Zustimmung zur Motion Germann - mit Ausnahme von Punkt 5 - sowie Zustimmung zum Postulat Ihrer Kommission, letzteres mit 13 zu 11 Stimmen bei 1 Enthaltung.
+In diesem Sinne beantragt Ihnen die Kommissionsmehrheit Zustimmung zur Motion Germann - mit Ausnahme von Ziffer 5 - sowie Zustimmung zum Postulat Ihrer Kommission, letzteres mit 13 zu 11 Stimmen bei 1 Enthaltung.
 </t>
   </si>
   <si>
@@ -3537,8 +3535,8 @@
 Ich komme zur Ausgangslage der Diskussion über die Forderungen dieses Postulates: Leider wurde in dieser Session die Motion 25.4067 der FDP-Liberalen Fraktion, "Geordneter Ausstieg für Schutzstatus S", abgelehnt, die eine geordnete Aufhebung des Schutzstatus S für Flüchtlinge aus der Ukraine forderte. In der Motion haben wir mit Fachexperten einen Massnahmenkatalog erarbeitet, um den Schutzstatus S aufzuheben.
 Das wird in der Zukunft eine enorm wichtige Aufgabe werden. Stand heute befinden sich in der Schweiz über 73 000 Personen im Schutzstatus S - über 73 000 Personen! Das ist ein namhafter Teil der Asylbevölkerung. Das entspricht der Grösse einer Stadt wie St. Gallen. Wenn wir eine geordnete Aufhebung dieses Schutzstatus erreichen wollen, müssen wir jetzt einige Dinge richtig machen, damit die Situation nicht in einem Chaos mündet.
 Deshalb ist dieses Postulat nicht wirklich hilfreich. Warum nicht? In einem Satz steht, es solle eine Namensänderung des Schutzstatus S sowie eine Angleichung zwischen der vorläufigen Aufnahme und dem Schutzstatus S vorgenommen werden. Eine vorläufige Aufnahme würde jedoch bedeuten, dass Personen aus der Ukraine mit Schutzstatus S nicht mehr als rückkehrorientiert zu betrachten sind. Frau Bundesrätin Karin Keller-Sutter hat, als sie noch das EJPD führte, in einer Pressekonferenz gegenüber der Schweizer Bevölkerung ganz klar gesagt: Ja, wir führen den Schutzstatus S ein und nehmen die Flüchtlinge aus der Ukraine unbürokratisch auf, aber es handelt sich um einen rückkehrorientierten Schutzstatus.
-Wenn man nun versucht, die über 73 000 Personen, die sich mit Schutzstatus S im Land befinden, in eine vorläufige Aufnahme zu verschieben, sodass sie dann dauerhaft hierbleiben, ist das eine fundamentale Abkehr von dem, was der Bundesrat der Bevölkerung damals versprochen hat. Es sollte im Parlament nicht die Forderung entstehen, dieser Politik Vorschub zu leisten. Das ist der eine gravierende Punkt, der völlig verkehrt ist.
-Der zweite Punkt: Die gesellschaftliche und wirtschaftliche Integration von Frauen soll spezifisch gefördert werden. Wenn wir anschauen, mit wem wir im Asylvollzug und im Asylbereich echte Probleme haben, dann sehen wir, dass das nicht die Frauen sind. Die Frauen machen beinahe keine Probleme; das ist eine sehr gute Botschaft.
+Wenn man nun versucht, die über 73 000 Personen, die sich mit Schutzstatus S im Land befinden, in eine vorläufige Aufnahme zu verschieben, sodass sie dann dauerhaft hierbleiben, ist das eine fundamentale Abkehr von dem, was der Bundesrat der Bevölkerung damals versprochen hat. Es sollte im Parlament nicht die Forderung entstehen, dieser Politik Vorschub zu leisten. Das ist der eine gravierende Punkte, der völlig verkehrt ist.
+Die zweite Punkt: Die gesellschaftliche und wirtschaftliche Integration von Frauen soll spezifisch gefördert werden. Wenn wir anschauen, mit wem wir im Asylvollzug und im Asylbereich echte Probleme haben, dann sehen wir, dass das nicht die Frauen sind. Die Frauen machen beinahe keine Probleme; das ist eine sehr gute Botschaft.
 Die Problemfälle sind die jungen Männer, die Wirtschaftsflüchtlinge, die sich Nacht für Nacht an den Bahnhöfen usw. in den Städten und in den Dörfern aufhalten. Mit diesen Leuten müssen wir zu arbeiten versuchen. Auf der einen Seite gibt es eben harte Massnahmen; wenn sie illegal im Land sind, müssen sie das Land verlassen. Auf der anderen Seite müssen sie, wenn sie Probleme machen oder Straftaten verüben, dem Strafvollzug zugeführt werden.
 Am besten soll es gar nicht erst so weit kommen. Da kann man als Staatspolitische Kommission aber doch nicht auf die Idee kommen, dass es hier vor allem um die Integration von Frauen gehe. Das ist wirklich eine sehr seltsame Forderung in diesem Postulat, das in der Staatspolitischen Kommission leider eine Mehrheit fand.
 Noch ein Schlusswort zum Vollzug im Asylbereich in Bezug auf die Asylstrategie 2027: Ich glaube, es ist nicht sinnvoll, das Dublin-System und die Weiterentwicklung des europäischen Asylvollzugs, namentlich den EU-Asyl- und Migrationspakt, zu verteufeln, wie das einige tun wollen. Ebenso wenig zielführend ist jedoch die Forderung, wie man sie jetzt hier sieht, pauschal über 73 000 Personen einfach vorläufig aufzunehmen.
